--- a/output/universe_analysis_result.xlsx
+++ b/output/universe_analysis_result.xlsx
@@ -37616,12 +37616,12 @@
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>3060.TW</t>
+          <t>2330.TW</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>銘異</t>
+          <t>台積電</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
@@ -37630,28 +37630,28 @@
         </is>
       </c>
       <c r="D272" t="n">
-        <v>34.25</v>
+        <v>2420</v>
       </c>
       <c r="E272" t="n">
-        <v>35.51</v>
+        <v>2436</v>
       </c>
       <c r="F272" t="n">
-        <v>35.91</v>
+        <v>2446.5</v>
       </c>
       <c r="G272" t="n">
-        <v>36.58</v>
+        <v>2426.25</v>
       </c>
       <c r="H272" t="n">
-        <v>3712376</v>
+        <v>42857055</v>
       </c>
       <c r="I272" t="n">
-        <v>5394556</v>
+        <v>33953781</v>
       </c>
       <c r="J272" t="n">
-        <v>42.2</v>
+        <v>2535</v>
       </c>
       <c r="K272" t="n">
-        <v>31.9</v>
+        <v>2325</v>
       </c>
       <c r="L272" t="inlineStr">
         <is>
@@ -37659,52 +37659,52 @@
         </is>
       </c>
       <c r="M272" t="n">
-        <v>248926</v>
+        <v>-8299971</v>
       </c>
       <c r="N272" t="n">
-        <v>-745393</v>
+        <v>-21807340</v>
       </c>
       <c r="O272" t="n">
-        <v>-1934637</v>
+        <v>-24379515</v>
       </c>
       <c r="P272" t="n">
-        <v>-1845758</v>
+        <v>-35301926</v>
       </c>
       <c r="Q272" t="n">
-        <v>244744</v>
+        <v>-12416209</v>
       </c>
       <c r="R272" t="n">
-        <v>-753706</v>
+        <v>-27209552</v>
       </c>
       <c r="S272" t="n">
-        <v>-1943154</v>
+        <v>-31281582</v>
       </c>
       <c r="T272" t="n">
-        <v>-1851733</v>
+        <v>-50338873</v>
       </c>
       <c r="U272" t="n">
-        <v>0</v>
+        <v>1546459</v>
       </c>
       <c r="V272" t="n">
-        <v>0</v>
+        <v>2119760</v>
       </c>
       <c r="W272" t="n">
-        <v>0</v>
+        <v>3388536</v>
       </c>
       <c r="X272" t="n">
-        <v>0</v>
+        <v>10268240</v>
       </c>
       <c r="Y272" t="n">
-        <v>4182</v>
+        <v>2569779</v>
       </c>
       <c r="Z272" t="n">
-        <v>8313</v>
+        <v>3282452</v>
       </c>
       <c r="AA272" t="n">
-        <v>8517</v>
+        <v>3513531</v>
       </c>
       <c r="AB272" t="n">
-        <v>5975</v>
+        <v>4768707</v>
       </c>
       <c r="AC272" t="n">
         <v>-30</v>
@@ -37713,10 +37713,10 @@
         <v>-30</v>
       </c>
       <c r="AE272" t="n">
-        <v>-45</v>
+        <v>-20</v>
       </c>
       <c r="AF272" t="n">
-        <v>-30</v>
+        <v>-55</v>
       </c>
       <c r="AG272" t="n">
         <v>0</v>
@@ -37736,17 +37736,17 @@
       </c>
       <c r="AM272" t="inlineStr">
         <is>
-          <t>跌破5日線、空頭排列、量能未放大</t>
+          <t>跌破5日線、量能溫和放大、接近20日低點</t>
         </is>
       </c>
       <c r="AN272" t="inlineStr">
         <is>
-          <t>5日法人明顯賣超</t>
+          <t>法人連續偏賣、5日法人明顯賣超、投信買外資賣</t>
         </is>
       </c>
       <c r="AO272" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、空頭排列、量能未放大、5日法人明顯賣超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、量能溫和放大、接近20日低點、法人連續偏賣、5日法人明顯賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
@@ -37890,12 +37890,12 @@
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>2330.TW</t>
+          <t>3060.TW</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>台積電</t>
+          <t>銘異</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
@@ -37904,28 +37904,28 @@
         </is>
       </c>
       <c r="D274" t="n">
-        <v>2420</v>
+        <v>34.25</v>
       </c>
       <c r="E274" t="n">
-        <v>2436</v>
+        <v>35.51</v>
       </c>
       <c r="F274" t="n">
-        <v>2446.5</v>
+        <v>35.91</v>
       </c>
       <c r="G274" t="n">
-        <v>2426.25</v>
+        <v>36.58</v>
       </c>
       <c r="H274" t="n">
-        <v>42857055</v>
+        <v>3712376</v>
       </c>
       <c r="I274" t="n">
-        <v>33953781</v>
+        <v>5394556</v>
       </c>
       <c r="J274" t="n">
-        <v>2535</v>
+        <v>42.2</v>
       </c>
       <c r="K274" t="n">
-        <v>2325</v>
+        <v>31.9</v>
       </c>
       <c r="L274" t="inlineStr">
         <is>
@@ -37933,52 +37933,52 @@
         </is>
       </c>
       <c r="M274" t="n">
-        <v>-8299971</v>
+        <v>248926</v>
       </c>
       <c r="N274" t="n">
-        <v>-21807340</v>
+        <v>-745393</v>
       </c>
       <c r="O274" t="n">
-        <v>-24379515</v>
+        <v>-1934637</v>
       </c>
       <c r="P274" t="n">
-        <v>-35301926</v>
+        <v>-1845758</v>
       </c>
       <c r="Q274" t="n">
-        <v>-12416209</v>
+        <v>244744</v>
       </c>
       <c r="R274" t="n">
-        <v>-27209552</v>
+        <v>-753706</v>
       </c>
       <c r="S274" t="n">
-        <v>-31281582</v>
+        <v>-1943154</v>
       </c>
       <c r="T274" t="n">
-        <v>-50338873</v>
+        <v>-1851733</v>
       </c>
       <c r="U274" t="n">
-        <v>1546459</v>
+        <v>0</v>
       </c>
       <c r="V274" t="n">
-        <v>2119760</v>
+        <v>0</v>
       </c>
       <c r="W274" t="n">
-        <v>3388536</v>
+        <v>0</v>
       </c>
       <c r="X274" t="n">
-        <v>10268240</v>
+        <v>0</v>
       </c>
       <c r="Y274" t="n">
-        <v>2569779</v>
+        <v>4182</v>
       </c>
       <c r="Z274" t="n">
-        <v>3282452</v>
+        <v>8313</v>
       </c>
       <c r="AA274" t="n">
-        <v>3513531</v>
+        <v>8517</v>
       </c>
       <c r="AB274" t="n">
-        <v>4768707</v>
+        <v>5975</v>
       </c>
       <c r="AC274" t="n">
         <v>-30</v>
@@ -37987,10 +37987,10 @@
         <v>-30</v>
       </c>
       <c r="AE274" t="n">
-        <v>-20</v>
+        <v>-45</v>
       </c>
       <c r="AF274" t="n">
-        <v>-55</v>
+        <v>-30</v>
       </c>
       <c r="AG274" t="n">
         <v>0</v>
@@ -38010,17 +38010,17 @@
       </c>
       <c r="AM274" t="inlineStr">
         <is>
-          <t>跌破5日線、量能溫和放大、接近20日低點</t>
+          <t>跌破5日線、空頭排列、量能未放大</t>
         </is>
       </c>
       <c r="AN274" t="inlineStr">
         <is>
-          <t>法人連續偏賣、5日法人明顯賣超、投信買外資賣</t>
+          <t>5日法人明顯賣超</t>
         </is>
       </c>
       <c r="AO274" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、量能溫和放大、接近20日低點、法人連續偏賣、5日法人明顯賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、空頭排列、量能未放大、5日法人明顯賣超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
@@ -38301,12 +38301,12 @@
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>2428.TW</t>
+          <t>2505.TW</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>興勤</t>
+          <t>國揚</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
@@ -38315,28 +38315,28 @@
         </is>
       </c>
       <c r="D277" t="n">
-        <v>291</v>
+        <v>17.7</v>
       </c>
       <c r="E277" t="n">
-        <v>304.4</v>
+        <v>17.87</v>
       </c>
       <c r="F277" t="n">
-        <v>311.45</v>
+        <v>17.96</v>
       </c>
       <c r="G277" t="n">
-        <v>274.95</v>
+        <v>18.24</v>
       </c>
       <c r="H277" t="n">
-        <v>2227926</v>
+        <v>292410</v>
       </c>
       <c r="I277" t="n">
-        <v>2993493</v>
+        <v>218860</v>
       </c>
       <c r="J277" t="n">
-        <v>363.5</v>
+        <v>19.25</v>
       </c>
       <c r="K277" t="n">
-        <v>201.5</v>
+        <v>17.6</v>
       </c>
       <c r="L277" t="inlineStr">
         <is>
@@ -38344,64 +38344,64 @@
         </is>
       </c>
       <c r="M277" t="n">
-        <v>195350</v>
+        <v>28000</v>
       </c>
       <c r="N277" t="n">
-        <v>-102735</v>
+        <v>-14000</v>
       </c>
       <c r="O277" t="n">
-        <v>-1476799</v>
+        <v>-98047</v>
       </c>
       <c r="P277" t="n">
-        <v>506210</v>
+        <v>9600</v>
       </c>
       <c r="Q277" t="n">
-        <v>202158</v>
+        <v>15000</v>
       </c>
       <c r="R277" t="n">
-        <v>-80022</v>
+        <v>-33000</v>
       </c>
       <c r="S277" t="n">
-        <v>-1918885</v>
+        <v>-113047</v>
       </c>
       <c r="T277" t="n">
-        <v>-1159265</v>
+        <v>-1400</v>
       </c>
       <c r="U277" t="n">
         <v>0</v>
       </c>
       <c r="V277" t="n">
-        <v>-1000</v>
+        <v>0</v>
       </c>
       <c r="W277" t="n">
-        <v>499000</v>
+        <v>0</v>
       </c>
       <c r="X277" t="n">
-        <v>1699000</v>
+        <v>0</v>
       </c>
       <c r="Y277" t="n">
-        <v>-6808</v>
+        <v>13000</v>
       </c>
       <c r="Z277" t="n">
-        <v>-21713</v>
+        <v>19000</v>
       </c>
       <c r="AA277" t="n">
-        <v>-56914</v>
+        <v>15000</v>
       </c>
       <c r="AB277" t="n">
-        <v>-33525</v>
+        <v>11000</v>
       </c>
       <c r="AC277" t="n">
-        <v>-30</v>
+        <v>-32</v>
       </c>
       <c r="AD277" t="n">
-        <v>-30</v>
+        <v>-32</v>
       </c>
       <c r="AE277" t="n">
-        <v>-20</v>
+        <v>-45</v>
       </c>
       <c r="AF277" t="n">
-        <v>-55</v>
+        <v>-35</v>
       </c>
       <c r="AG277" t="n">
         <v>0</v>
@@ -38421,29 +38421,29 @@
       </c>
       <c r="AM277" t="inlineStr">
         <is>
-          <t>跌破5日線、量能未放大</t>
+          <t>跌破5日線、空頭排列、量能溫和放大、接近20日低點</t>
         </is>
       </c>
       <c r="AN277" t="inlineStr">
         <is>
-          <t>中期買超轉短線賣壓、5日法人明顯賣超、投信買外資賣</t>
+          <t>中期買超轉短線賣壓、5日法人小幅賣超</t>
         </is>
       </c>
       <c r="AO277" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、量能未放大、中期買超轉短線賣壓、5日法人明顯賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、空頭排列、量能溫和放大、接近20日低點、中期買超轉短線賣壓、5日法人小幅賣超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>3376.TW</t>
+          <t>2832.TW</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>新日興</t>
+          <t>台產</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
@@ -38452,81 +38452,81 @@
         </is>
       </c>
       <c r="D278" t="n">
-        <v>197.5</v>
+        <v>55.9</v>
       </c>
       <c r="E278" t="n">
-        <v>195.4</v>
+        <v>56.4</v>
       </c>
       <c r="F278" t="n">
-        <v>196.85</v>
+        <v>56.48</v>
       </c>
       <c r="G278" t="n">
-        <v>198.8</v>
+        <v>56.13</v>
       </c>
       <c r="H278" t="n">
-        <v>3460093</v>
+        <v>535022</v>
       </c>
       <c r="I278" t="n">
-        <v>2503014</v>
+        <v>258353</v>
       </c>
       <c r="J278" t="n">
-        <v>214.5</v>
+        <v>57.5</v>
       </c>
       <c r="K278" t="n">
-        <v>190</v>
+        <v>52</v>
       </c>
       <c r="L278" t="inlineStr">
         <is>
-          <t>無明顯異常</t>
+          <t>爆量價未漲</t>
         </is>
       </c>
       <c r="M278" t="n">
-        <v>-249671</v>
+        <v>-54000</v>
       </c>
       <c r="N278" t="n">
-        <v>-1164868</v>
+        <v>-16069</v>
       </c>
       <c r="O278" t="n">
-        <v>-1951518</v>
+        <v>-44972</v>
       </c>
       <c r="P278" t="n">
-        <v>-4844108</v>
+        <v>136126</v>
       </c>
       <c r="Q278" t="n">
-        <v>21856</v>
+        <v>-66000</v>
       </c>
       <c r="R278" t="n">
-        <v>-754656</v>
+        <v>-7090</v>
       </c>
       <c r="S278" t="n">
-        <v>-1261353</v>
+        <v>-43993</v>
       </c>
       <c r="T278" t="n">
-        <v>-4234611</v>
+        <v>-324673</v>
       </c>
       <c r="U278" t="n">
-        <v>-1000</v>
+        <v>0</v>
       </c>
       <c r="V278" t="n">
-        <v>-31000</v>
+        <v>-3979</v>
       </c>
       <c r="W278" t="n">
-        <v>-31000</v>
+        <v>-3979</v>
       </c>
       <c r="X278" t="n">
-        <v>129000</v>
+        <v>530271</v>
       </c>
       <c r="Y278" t="n">
-        <v>-270527</v>
+        <v>12000</v>
       </c>
       <c r="Z278" t="n">
-        <v>-379212</v>
+        <v>-5000</v>
       </c>
       <c r="AA278" t="n">
-        <v>-659165</v>
+        <v>3000</v>
       </c>
       <c r="AB278" t="n">
-        <v>-738497</v>
+        <v>-69472</v>
       </c>
       <c r="AC278" t="n">
         <v>-32</v>
@@ -38535,13 +38535,13 @@
         <v>-32</v>
       </c>
       <c r="AE278" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="AF278" t="n">
-        <v>-75</v>
+        <v>-70</v>
       </c>
       <c r="AG278" t="n">
-        <v>0</v>
+        <v>-20</v>
       </c>
       <c r="AH278" t="inlineStr"/>
       <c r="AI278" t="inlineStr"/>
@@ -38558,29 +38558,29 @@
       </c>
       <c r="AM278" t="inlineStr">
         <is>
-          <t>站上5日線、空頭排列、量能溫和放大、接近20日低點</t>
+          <t>跌破5日線、爆量、爆量價未漲</t>
         </is>
       </c>
       <c r="AN278" t="inlineStr">
         <is>
-          <t>法人連續偏賣、5日法人明顯賣超、外資投信同步賣超</t>
+          <t>法人連續偏賣、中期買超轉短線賣壓、外資投信同步賣超</t>
         </is>
       </c>
       <c r="AO278" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、空頭排列、量能溫和放大、接近20日低點、法人連續偏賣、5日法人明顯賣超、外資投信同步賣超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、爆量、爆量價未漲、法人連續偏賣、中期買超轉短線賣壓、外資投信同步賣超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>2505.TW</t>
+          <t>2331.TW</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>國揚</t>
+          <t>精英</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
@@ -38589,28 +38589,28 @@
         </is>
       </c>
       <c r="D279" t="n">
-        <v>17.7</v>
+        <v>20.4</v>
       </c>
       <c r="E279" t="n">
-        <v>17.87</v>
+        <v>20.58</v>
       </c>
       <c r="F279" t="n">
-        <v>17.96</v>
+        <v>20.88</v>
       </c>
       <c r="G279" t="n">
-        <v>18.24</v>
+        <v>21.29</v>
       </c>
       <c r="H279" t="n">
-        <v>292410</v>
+        <v>3260481</v>
       </c>
       <c r="I279" t="n">
-        <v>218860</v>
+        <v>2386183</v>
       </c>
       <c r="J279" t="n">
-        <v>19.25</v>
+        <v>23.9</v>
       </c>
       <c r="K279" t="n">
-        <v>17.6</v>
+        <v>19.75</v>
       </c>
       <c r="L279" t="inlineStr">
         <is>
@@ -38618,52 +38618,52 @@
         </is>
       </c>
       <c r="M279" t="n">
-        <v>28000</v>
+        <v>-254704</v>
       </c>
       <c r="N279" t="n">
-        <v>-14000</v>
+        <v>282818</v>
       </c>
       <c r="O279" t="n">
-        <v>-98047</v>
+        <v>-764690</v>
       </c>
       <c r="P279" t="n">
-        <v>9600</v>
+        <v>-49851</v>
       </c>
       <c r="Q279" t="n">
-        <v>15000</v>
+        <v>-238200</v>
       </c>
       <c r="R279" t="n">
-        <v>-33000</v>
+        <v>524322</v>
       </c>
       <c r="S279" t="n">
-        <v>-113047</v>
+        <v>-220845</v>
       </c>
       <c r="T279" t="n">
-        <v>-1400</v>
+        <v>1012774</v>
       </c>
       <c r="U279" t="n">
-        <v>0</v>
+        <v>-17000</v>
       </c>
       <c r="V279" t="n">
-        <v>0</v>
+        <v>-287000</v>
       </c>
       <c r="W279" t="n">
-        <v>0</v>
+        <v>-537000</v>
       </c>
       <c r="X279" t="n">
-        <v>0</v>
+        <v>-1037000</v>
       </c>
       <c r="Y279" t="n">
-        <v>13000</v>
+        <v>496</v>
       </c>
       <c r="Z279" t="n">
-        <v>19000</v>
+        <v>45496</v>
       </c>
       <c r="AA279" t="n">
-        <v>15000</v>
+        <v>-6845</v>
       </c>
       <c r="AB279" t="n">
-        <v>11000</v>
+        <v>-25625</v>
       </c>
       <c r="AC279" t="n">
         <v>-32</v>
@@ -38700,24 +38700,24 @@
       </c>
       <c r="AN279" t="inlineStr">
         <is>
-          <t>中期買超轉短線賣壓、5日法人小幅賣超</t>
+          <t>短線籌碼止穩、5日法人明顯賣超、外資投信同步賣超</t>
         </is>
       </c>
       <c r="AO279" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、空頭排列、量能溫和放大、接近20日低點、中期買超轉短線賣壓、5日法人小幅賣超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、空頭排列、量能溫和放大、接近20日低點、短線籌碼止穩、5日法人明顯賣超、外資投信同步賣超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>2331.TW</t>
+          <t>3376.TW</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>精英</t>
+          <t>新日興</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
@@ -38726,28 +38726,28 @@
         </is>
       </c>
       <c r="D280" t="n">
-        <v>20.4</v>
+        <v>197.5</v>
       </c>
       <c r="E280" t="n">
-        <v>20.58</v>
+        <v>195.4</v>
       </c>
       <c r="F280" t="n">
-        <v>20.88</v>
+        <v>196.85</v>
       </c>
       <c r="G280" t="n">
-        <v>21.29</v>
+        <v>198.8</v>
       </c>
       <c r="H280" t="n">
-        <v>3260481</v>
+        <v>3460093</v>
       </c>
       <c r="I280" t="n">
-        <v>2386183</v>
+        <v>2503014</v>
       </c>
       <c r="J280" t="n">
-        <v>23.9</v>
+        <v>214.5</v>
       </c>
       <c r="K280" t="n">
-        <v>19.75</v>
+        <v>190</v>
       </c>
       <c r="L280" t="inlineStr">
         <is>
@@ -38755,52 +38755,52 @@
         </is>
       </c>
       <c r="M280" t="n">
-        <v>-254704</v>
+        <v>-249671</v>
       </c>
       <c r="N280" t="n">
-        <v>282818</v>
+        <v>-1164868</v>
       </c>
       <c r="O280" t="n">
-        <v>-764690</v>
+        <v>-1951518</v>
       </c>
       <c r="P280" t="n">
-        <v>-49851</v>
+        <v>-4844108</v>
       </c>
       <c r="Q280" t="n">
-        <v>-238200</v>
+        <v>21856</v>
       </c>
       <c r="R280" t="n">
-        <v>524322</v>
+        <v>-754656</v>
       </c>
       <c r="S280" t="n">
-        <v>-220845</v>
+        <v>-1261353</v>
       </c>
       <c r="T280" t="n">
-        <v>1012774</v>
+        <v>-4234611</v>
       </c>
       <c r="U280" t="n">
-        <v>-17000</v>
+        <v>-1000</v>
       </c>
       <c r="V280" t="n">
-        <v>-287000</v>
+        <v>-31000</v>
       </c>
       <c r="W280" t="n">
-        <v>-537000</v>
+        <v>-31000</v>
       </c>
       <c r="X280" t="n">
-        <v>-1037000</v>
+        <v>129000</v>
       </c>
       <c r="Y280" t="n">
-        <v>496</v>
+        <v>-270527</v>
       </c>
       <c r="Z280" t="n">
-        <v>45496</v>
+        <v>-379212</v>
       </c>
       <c r="AA280" t="n">
-        <v>-6845</v>
+        <v>-659165</v>
       </c>
       <c r="AB280" t="n">
-        <v>-25625</v>
+        <v>-738497</v>
       </c>
       <c r="AC280" t="n">
         <v>-32</v>
@@ -38809,10 +38809,10 @@
         <v>-32</v>
       </c>
       <c r="AE280" t="n">
-        <v>-45</v>
+        <v>-5</v>
       </c>
       <c r="AF280" t="n">
-        <v>-35</v>
+        <v>-75</v>
       </c>
       <c r="AG280" t="n">
         <v>0</v>
@@ -38832,29 +38832,29 @@
       </c>
       <c r="AM280" t="inlineStr">
         <is>
-          <t>跌破5日線、空頭排列、量能溫和放大、接近20日低點</t>
+          <t>站上5日線、空頭排列、量能溫和放大、接近20日低點</t>
         </is>
       </c>
       <c r="AN280" t="inlineStr">
         <is>
-          <t>短線籌碼止穩、5日法人明顯賣超、外資投信同步賣超</t>
+          <t>法人連續偏賣、5日法人明顯賣超、外資投信同步賣超</t>
         </is>
       </c>
       <c r="AO280" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、空頭排列、量能溫和放大、接近20日低點、短線籌碼止穩、5日法人明顯賣超、外資投信同步賣超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、空頭排列、量能溫和放大、接近20日低點、法人連續偏賣、5日法人明顯賣超、外資投信同步賣超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>2832.TW</t>
+          <t>2753.TW</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>台產</t>
+          <t>八方雲集</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
@@ -38863,96 +38863,96 @@
         </is>
       </c>
       <c r="D281" t="n">
-        <v>55.9</v>
+        <v>175.5</v>
       </c>
       <c r="E281" t="n">
-        <v>56.4</v>
+        <v>177.2</v>
       </c>
       <c r="F281" t="n">
-        <v>56.48</v>
+        <v>180.65</v>
       </c>
       <c r="G281" t="n">
-        <v>56.13</v>
+        <v>184.8</v>
       </c>
       <c r="H281" t="n">
-        <v>535022</v>
+        <v>436368</v>
       </c>
       <c r="I281" t="n">
-        <v>258353</v>
+        <v>319069</v>
       </c>
       <c r="J281" t="n">
-        <v>57.5</v>
+        <v>192</v>
       </c>
       <c r="K281" t="n">
-        <v>52</v>
+        <v>174</v>
       </c>
       <c r="L281" t="inlineStr">
         <is>
-          <t>爆量價未漲</t>
+          <t>無明顯異常</t>
         </is>
       </c>
       <c r="M281" t="n">
-        <v>-54000</v>
+        <v>11877</v>
       </c>
       <c r="N281" t="n">
-        <v>-16069</v>
+        <v>-137928</v>
       </c>
       <c r="O281" t="n">
-        <v>-44972</v>
+        <v>-241054</v>
       </c>
       <c r="P281" t="n">
-        <v>136126</v>
+        <v>-503430</v>
       </c>
       <c r="Q281" t="n">
-        <v>-66000</v>
+        <v>9345</v>
       </c>
       <c r="R281" t="n">
-        <v>-7090</v>
+        <v>-135640</v>
       </c>
       <c r="S281" t="n">
-        <v>-43993</v>
+        <v>-234890</v>
       </c>
       <c r="T281" t="n">
-        <v>-324673</v>
+        <v>-747297</v>
       </c>
       <c r="U281" t="n">
         <v>0</v>
       </c>
       <c r="V281" t="n">
-        <v>-3979</v>
+        <v>-2841</v>
       </c>
       <c r="W281" t="n">
-        <v>-3979</v>
+        <v>-3717</v>
       </c>
       <c r="X281" t="n">
-        <v>530271</v>
+        <v>253057</v>
       </c>
       <c r="Y281" t="n">
-        <v>12000</v>
+        <v>2532</v>
       </c>
       <c r="Z281" t="n">
-        <v>-5000</v>
+        <v>553</v>
       </c>
       <c r="AA281" t="n">
-        <v>3000</v>
+        <v>-2447</v>
       </c>
       <c r="AB281" t="n">
-        <v>-69472</v>
+        <v>-9190</v>
       </c>
       <c r="AC281" t="n">
-        <v>-32</v>
+        <v>-34</v>
       </c>
       <c r="AD281" t="n">
-        <v>-32</v>
+        <v>-34</v>
       </c>
       <c r="AE281" t="n">
-        <v>0</v>
+        <v>-45</v>
       </c>
       <c r="AF281" t="n">
-        <v>-70</v>
+        <v>-40</v>
       </c>
       <c r="AG281" t="n">
-        <v>-20</v>
+        <v>0</v>
       </c>
       <c r="AH281" t="inlineStr"/>
       <c r="AI281" t="inlineStr"/>
@@ -38969,29 +38969,29 @@
       </c>
       <c r="AM281" t="inlineStr">
         <is>
-          <t>跌破5日線、爆量、爆量價未漲</t>
+          <t>跌破5日線、空頭排列、量能溫和放大、接近20日低點</t>
         </is>
       </c>
       <c r="AN281" t="inlineStr">
         <is>
-          <t>法人連續偏賣、中期買超轉短線賣壓、外資投信同步賣超</t>
+          <t>5日法人賣超、外資投信同步賣超</t>
         </is>
       </c>
       <c r="AO281" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、爆量、爆量價未漲、法人連續偏賣、中期買超轉短線賣壓、外資投信同步賣超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、空頭排列、量能溫和放大、接近20日低點、5日法人賣超、外資投信同步賣超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>2753.TW</t>
+          <t>2390.TW</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>八方雲集</t>
+          <t>云辰</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
@@ -39000,28 +39000,28 @@
         </is>
       </c>
       <c r="D282" t="n">
-        <v>175.5</v>
+        <v>11.75</v>
       </c>
       <c r="E282" t="n">
-        <v>177.2</v>
+        <v>12.49</v>
       </c>
       <c r="F282" t="n">
-        <v>180.65</v>
+        <v>12.55</v>
       </c>
       <c r="G282" t="n">
-        <v>184.8</v>
+        <v>12.32</v>
       </c>
       <c r="H282" t="n">
-        <v>436368</v>
+        <v>1169679</v>
       </c>
       <c r="I282" t="n">
-        <v>319069</v>
+        <v>1544977</v>
       </c>
       <c r="J282" t="n">
-        <v>192</v>
+        <v>14.25</v>
       </c>
       <c r="K282" t="n">
-        <v>174</v>
+        <v>11.45</v>
       </c>
       <c r="L282" t="inlineStr">
         <is>
@@ -39029,52 +39029,52 @@
         </is>
       </c>
       <c r="M282" t="n">
-        <v>11877</v>
+        <v>-142165</v>
       </c>
       <c r="N282" t="n">
-        <v>-137928</v>
+        <v>-430620</v>
       </c>
       <c r="O282" t="n">
-        <v>-241054</v>
+        <v>-738773</v>
       </c>
       <c r="P282" t="n">
-        <v>-503430</v>
+        <v>-421523</v>
       </c>
       <c r="Q282" t="n">
-        <v>9345</v>
+        <v>-143991</v>
       </c>
       <c r="R282" t="n">
-        <v>-135640</v>
+        <v>-393014</v>
       </c>
       <c r="S282" t="n">
-        <v>-234890</v>
+        <v>-699166</v>
       </c>
       <c r="T282" t="n">
-        <v>-747297</v>
+        <v>-382668</v>
       </c>
       <c r="U282" t="n">
         <v>0</v>
       </c>
       <c r="V282" t="n">
-        <v>-2841</v>
+        <v>0</v>
       </c>
       <c r="W282" t="n">
-        <v>-3717</v>
+        <v>0</v>
       </c>
       <c r="X282" t="n">
-        <v>253057</v>
+        <v>0</v>
       </c>
       <c r="Y282" t="n">
-        <v>2532</v>
+        <v>1826</v>
       </c>
       <c r="Z282" t="n">
-        <v>553</v>
+        <v>-37606</v>
       </c>
       <c r="AA282" t="n">
-        <v>-2447</v>
+        <v>-39607</v>
       </c>
       <c r="AB282" t="n">
-        <v>-9190</v>
+        <v>-38855</v>
       </c>
       <c r="AC282" t="n">
         <v>-34</v>
@@ -39083,10 +39083,10 @@
         <v>-34</v>
       </c>
       <c r="AE282" t="n">
-        <v>-45</v>
+        <v>-30</v>
       </c>
       <c r="AF282" t="n">
-        <v>-40</v>
+        <v>-55</v>
       </c>
       <c r="AG282" t="n">
         <v>0</v>
@@ -39106,17 +39106,17 @@
       </c>
       <c r="AM282" t="inlineStr">
         <is>
-          <t>跌破5日線、空頭排列、量能溫和放大、接近20日低點</t>
+          <t>跌破5日線、量能未放大、接近20日低點</t>
         </is>
       </c>
       <c r="AN282" t="inlineStr">
         <is>
-          <t>5日法人賣超、外資投信同步賣超</t>
+          <t>法人連續偏賣、5日法人明顯賣超</t>
         </is>
       </c>
       <c r="AO282" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、空頭排列、量能溫和放大、接近20日低點、5日法人賣超、外資投信同步賣超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、量能未放大、接近20日低點、法人連續偏賣、5日法人明顯賣超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
@@ -39260,12 +39260,12 @@
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>2390.TW</t>
+          <t>3231.TW</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>云辰</t>
+          <t>緯創</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
@@ -39274,28 +39274,28 @@
         </is>
       </c>
       <c r="D284" t="n">
-        <v>11.75</v>
+        <v>142.5</v>
       </c>
       <c r="E284" t="n">
-        <v>12.49</v>
+        <v>146.5</v>
       </c>
       <c r="F284" t="n">
-        <v>12.55</v>
+        <v>152.6</v>
       </c>
       <c r="G284" t="n">
-        <v>12.32</v>
+        <v>155.78</v>
       </c>
       <c r="H284" t="n">
-        <v>1169679</v>
+        <v>27925626</v>
       </c>
       <c r="I284" t="n">
-        <v>1544977</v>
+        <v>35613396</v>
       </c>
       <c r="J284" t="n">
-        <v>14.25</v>
+        <v>166</v>
       </c>
       <c r="K284" t="n">
-        <v>11.45</v>
+        <v>139</v>
       </c>
       <c r="L284" t="inlineStr">
         <is>
@@ -39303,52 +39303,52 @@
         </is>
       </c>
       <c r="M284" t="n">
-        <v>-142165</v>
+        <v>4212866</v>
       </c>
       <c r="N284" t="n">
-        <v>-430620</v>
+        <v>-4763612</v>
       </c>
       <c r="O284" t="n">
-        <v>-738773</v>
+        <v>-17291118</v>
       </c>
       <c r="P284" t="n">
-        <v>-421523</v>
+        <v>-31204606</v>
       </c>
       <c r="Q284" t="n">
-        <v>-143991</v>
+        <v>2463559</v>
       </c>
       <c r="R284" t="n">
-        <v>-393014</v>
+        <v>-5570869</v>
       </c>
       <c r="S284" t="n">
-        <v>-699166</v>
+        <v>-13780172</v>
       </c>
       <c r="T284" t="n">
-        <v>-382668</v>
+        <v>-56080222</v>
       </c>
       <c r="U284" t="n">
-        <v>0</v>
+        <v>385107</v>
       </c>
       <c r="V284" t="n">
-        <v>0</v>
+        <v>-371031</v>
       </c>
       <c r="W284" t="n">
-        <v>0</v>
+        <v>3378090</v>
       </c>
       <c r="X284" t="n">
-        <v>0</v>
+        <v>30660958</v>
       </c>
       <c r="Y284" t="n">
-        <v>1826</v>
+        <v>1364200</v>
       </c>
       <c r="Z284" t="n">
-        <v>-37606</v>
+        <v>1178288</v>
       </c>
       <c r="AA284" t="n">
-        <v>-39607</v>
+        <v>-6889036</v>
       </c>
       <c r="AB284" t="n">
-        <v>-38855</v>
+        <v>-5785342</v>
       </c>
       <c r="AC284" t="n">
         <v>-34</v>
@@ -39357,10 +39357,10 @@
         <v>-34</v>
       </c>
       <c r="AE284" t="n">
+        <v>-55</v>
+      </c>
+      <c r="AF284" t="n">
         <v>-30</v>
-      </c>
-      <c r="AF284" t="n">
-        <v>-55</v>
       </c>
       <c r="AG284" t="n">
         <v>0</v>
@@ -39380,29 +39380,29 @@
       </c>
       <c r="AM284" t="inlineStr">
         <is>
-          <t>跌破5日線、量能未放大、接近20日低點</t>
+          <t>跌破5日線、空頭排列、量能未放大、接近20日低點</t>
         </is>
       </c>
       <c r="AN284" t="inlineStr">
         <is>
-          <t>法人連續偏賣、5日法人明顯賣超</t>
+          <t>5日法人明顯賣超、投信買外資賣</t>
         </is>
       </c>
       <c r="AO284" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、量能未放大、接近20日低點、法人連續偏賣、5日法人明顯賣超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、空頭排列、量能未放大、接近20日低點、5日法人明顯賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>2104.TW</t>
+          <t>2467.TW</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>國際中橡</t>
+          <t>志聖</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
@@ -39411,28 +39411,28 @@
         </is>
       </c>
       <c r="D285" t="n">
-        <v>10.4</v>
+        <v>536</v>
       </c>
       <c r="E285" t="n">
-        <v>10.63</v>
+        <v>570.4</v>
       </c>
       <c r="F285" t="n">
-        <v>10.7</v>
+        <v>604.6</v>
       </c>
       <c r="G285" t="n">
-        <v>10.47</v>
+        <v>594.1</v>
       </c>
       <c r="H285" t="n">
-        <v>3713641</v>
+        <v>1981077</v>
       </c>
       <c r="I285" t="n">
-        <v>4117049</v>
+        <v>2366189</v>
       </c>
       <c r="J285" t="n">
-        <v>11.65</v>
+        <v>672</v>
       </c>
       <c r="K285" t="n">
-        <v>9.92</v>
+        <v>536</v>
       </c>
       <c r="L285" t="inlineStr">
         <is>
@@ -39440,52 +39440,52 @@
         </is>
       </c>
       <c r="M285" t="n">
-        <v>-454689</v>
+        <v>-1100277</v>
       </c>
       <c r="N285" t="n">
-        <v>-2356132</v>
+        <v>-546681</v>
       </c>
       <c r="O285" t="n">
-        <v>-4420125</v>
+        <v>-1994147</v>
       </c>
       <c r="P285" t="n">
-        <v>-2737938</v>
+        <v>-456794</v>
       </c>
       <c r="Q285" t="n">
-        <v>-489597</v>
+        <v>-1080997</v>
       </c>
       <c r="R285" t="n">
-        <v>-2415177</v>
+        <v>-543008</v>
       </c>
       <c r="S285" t="n">
-        <v>-4464504</v>
+        <v>-1891620</v>
       </c>
       <c r="T285" t="n">
-        <v>-2924730</v>
+        <v>-271512</v>
       </c>
       <c r="U285" t="n">
-        <v>0</v>
+        <v>11000</v>
       </c>
       <c r="V285" t="n">
-        <v>0</v>
+        <v>8073</v>
       </c>
       <c r="W285" t="n">
-        <v>0</v>
+        <v>2029</v>
       </c>
       <c r="X285" t="n">
-        <v>0</v>
+        <v>-129911</v>
       </c>
       <c r="Y285" t="n">
-        <v>34908</v>
+        <v>-30280</v>
       </c>
       <c r="Z285" t="n">
-        <v>59045</v>
+        <v>-11746</v>
       </c>
       <c r="AA285" t="n">
-        <v>44379</v>
+        <v>-104556</v>
       </c>
       <c r="AB285" t="n">
-        <v>186792</v>
+        <v>-55371</v>
       </c>
       <c r="AC285" t="n">
         <v>-34</v>
@@ -39522,24 +39522,24 @@
       </c>
       <c r="AN285" t="inlineStr">
         <is>
-          <t>法人連續偏賣、5日法人明顯賣超</t>
+          <t>法人連續偏賣、5日法人明顯賣超、投信買外資賣</t>
         </is>
       </c>
       <c r="AO285" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、量能未放大、接近20日低點、法人連續偏賣、5日法人明顯賣超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、量能未放大、接近20日低點、法人連續偏賣、5日法人明顯賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>3231.TW</t>
+          <t>2104.TW</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>國際中橡</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
@@ -39548,28 +39548,28 @@
         </is>
       </c>
       <c r="D286" t="n">
-        <v>142.5</v>
+        <v>10.4</v>
       </c>
       <c r="E286" t="n">
-        <v>146.5</v>
+        <v>10.63</v>
       </c>
       <c r="F286" t="n">
-        <v>152.6</v>
+        <v>10.7</v>
       </c>
       <c r="G286" t="n">
-        <v>155.78</v>
+        <v>10.47</v>
       </c>
       <c r="H286" t="n">
-        <v>27925626</v>
+        <v>3713641</v>
       </c>
       <c r="I286" t="n">
-        <v>35613396</v>
+        <v>4117049</v>
       </c>
       <c r="J286" t="n">
-        <v>166</v>
+        <v>11.65</v>
       </c>
       <c r="K286" t="n">
-        <v>139</v>
+        <v>9.92</v>
       </c>
       <c r="L286" t="inlineStr">
         <is>
@@ -39577,52 +39577,52 @@
         </is>
       </c>
       <c r="M286" t="n">
-        <v>4212866</v>
+        <v>-454689</v>
       </c>
       <c r="N286" t="n">
-        <v>-4763612</v>
+        <v>-2356132</v>
       </c>
       <c r="O286" t="n">
-        <v>-17291118</v>
+        <v>-4420125</v>
       </c>
       <c r="P286" t="n">
-        <v>-31204606</v>
+        <v>-2737938</v>
       </c>
       <c r="Q286" t="n">
-        <v>2463559</v>
+        <v>-489597</v>
       </c>
       <c r="R286" t="n">
-        <v>-5570869</v>
+        <v>-2415177</v>
       </c>
       <c r="S286" t="n">
-        <v>-13780172</v>
+        <v>-4464504</v>
       </c>
       <c r="T286" t="n">
-        <v>-56080222</v>
+        <v>-2924730</v>
       </c>
       <c r="U286" t="n">
-        <v>385107</v>
+        <v>0</v>
       </c>
       <c r="V286" t="n">
-        <v>-371031</v>
+        <v>0</v>
       </c>
       <c r="W286" t="n">
-        <v>3378090</v>
+        <v>0</v>
       </c>
       <c r="X286" t="n">
-        <v>30660958</v>
+        <v>0</v>
       </c>
       <c r="Y286" t="n">
-        <v>1364200</v>
+        <v>34908</v>
       </c>
       <c r="Z286" t="n">
-        <v>1178288</v>
+        <v>59045</v>
       </c>
       <c r="AA286" t="n">
-        <v>-6889036</v>
+        <v>44379</v>
       </c>
       <c r="AB286" t="n">
-        <v>-5785342</v>
+        <v>186792</v>
       </c>
       <c r="AC286" t="n">
         <v>-34</v>
@@ -39631,10 +39631,10 @@
         <v>-34</v>
       </c>
       <c r="AE286" t="n">
+        <v>-30</v>
+      </c>
+      <c r="AF286" t="n">
         <v>-55</v>
-      </c>
-      <c r="AF286" t="n">
-        <v>-30</v>
       </c>
       <c r="AG286" t="n">
         <v>0</v>
@@ -39654,29 +39654,29 @@
       </c>
       <c r="AM286" t="inlineStr">
         <is>
-          <t>跌破5日線、空頭排列、量能未放大、接近20日低點</t>
+          <t>跌破5日線、量能未放大、接近20日低點</t>
         </is>
       </c>
       <c r="AN286" t="inlineStr">
         <is>
-          <t>5日法人明顯賣超、投信買外資賣</t>
+          <t>法人連續偏賣、5日法人明顯賣超</t>
         </is>
       </c>
       <c r="AO286" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、空頭排列、量能未放大、接近20日低點、5日法人明顯賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、量能未放大、接近20日低點、法人連續偏賣、5日法人明顯賣超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>2467.TW</t>
+          <t>2362.TW</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>志聖</t>
+          <t>藍天</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
@@ -39685,28 +39685,28 @@
         </is>
       </c>
       <c r="D287" t="n">
-        <v>536</v>
+        <v>41.55</v>
       </c>
       <c r="E287" t="n">
-        <v>570.4</v>
+        <v>42.82</v>
       </c>
       <c r="F287" t="n">
-        <v>604.6</v>
+        <v>42.47</v>
       </c>
       <c r="G287" t="n">
-        <v>594.1</v>
+        <v>44.21</v>
       </c>
       <c r="H287" t="n">
-        <v>1981077</v>
+        <v>820728</v>
       </c>
       <c r="I287" t="n">
-        <v>2366189</v>
+        <v>1140783</v>
       </c>
       <c r="J287" t="n">
-        <v>672</v>
+        <v>50</v>
       </c>
       <c r="K287" t="n">
-        <v>536</v>
+        <v>40.5</v>
       </c>
       <c r="L287" t="inlineStr">
         <is>
@@ -39714,52 +39714,52 @@
         </is>
       </c>
       <c r="M287" t="n">
-        <v>-1100277</v>
+        <v>-54478</v>
       </c>
       <c r="N287" t="n">
-        <v>-546681</v>
+        <v>-359715</v>
       </c>
       <c r="O287" t="n">
-        <v>-1994147</v>
+        <v>-968703</v>
       </c>
       <c r="P287" t="n">
-        <v>-456794</v>
+        <v>-1173105</v>
       </c>
       <c r="Q287" t="n">
-        <v>-1080997</v>
+        <v>-68628</v>
       </c>
       <c r="R287" t="n">
-        <v>-543008</v>
+        <v>-380211</v>
       </c>
       <c r="S287" t="n">
-        <v>-1891620</v>
+        <v>-964041</v>
       </c>
       <c r="T287" t="n">
-        <v>-271512</v>
+        <v>-1153882</v>
       </c>
       <c r="U287" t="n">
-        <v>11000</v>
+        <v>0</v>
       </c>
       <c r="V287" t="n">
-        <v>8073</v>
+        <v>0</v>
       </c>
       <c r="W287" t="n">
-        <v>2029</v>
+        <v>0</v>
       </c>
       <c r="X287" t="n">
-        <v>-129911</v>
+        <v>0</v>
       </c>
       <c r="Y287" t="n">
-        <v>-30280</v>
+        <v>14150</v>
       </c>
       <c r="Z287" t="n">
-        <v>-11746</v>
+        <v>20496</v>
       </c>
       <c r="AA287" t="n">
-        <v>-104556</v>
+        <v>-4662</v>
       </c>
       <c r="AB287" t="n">
-        <v>-55371</v>
+        <v>-19223</v>
       </c>
       <c r="AC287" t="n">
         <v>-34</v>
@@ -39796,12 +39796,12 @@
       </c>
       <c r="AN287" t="inlineStr">
         <is>
-          <t>法人連續偏賣、5日法人明顯賣超、投信買外資賣</t>
+          <t>法人連續偏賣、5日法人明顯賣超</t>
         </is>
       </c>
       <c r="AO287" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、量能未放大、接近20日低點、法人連續偏賣、5日法人明顯賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、量能未放大、接近20日低點、法人連續偏賣、5日法人明顯賣超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
@@ -40493,12 +40493,12 @@
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>2362.TW</t>
+          <t>6757.TW</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>藍天</t>
+          <t>台灣虎航</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
@@ -40507,28 +40507,28 @@
         </is>
       </c>
       <c r="D293" t="n">
-        <v>41.55</v>
+        <v>57.3</v>
       </c>
       <c r="E293" t="n">
-        <v>42.82</v>
+        <v>58.72</v>
       </c>
       <c r="F293" t="n">
-        <v>42.47</v>
+        <v>59.94</v>
       </c>
       <c r="G293" t="n">
-        <v>44.21</v>
+        <v>60.2</v>
       </c>
       <c r="H293" t="n">
-        <v>820728</v>
+        <v>1621093</v>
       </c>
       <c r="I293" t="n">
-        <v>1140783</v>
+        <v>1683065</v>
       </c>
       <c r="J293" t="n">
-        <v>50</v>
+        <v>67.3</v>
       </c>
       <c r="K293" t="n">
-        <v>40.5</v>
+        <v>55.7</v>
       </c>
       <c r="L293" t="inlineStr">
         <is>
@@ -40536,28 +40536,28 @@
         </is>
       </c>
       <c r="M293" t="n">
-        <v>-54478</v>
+        <v>132906</v>
       </c>
       <c r="N293" t="n">
-        <v>-359715</v>
+        <v>-525644</v>
       </c>
       <c r="O293" t="n">
-        <v>-968703</v>
+        <v>-584677</v>
       </c>
       <c r="P293" t="n">
-        <v>-1173105</v>
+        <v>-794776</v>
       </c>
       <c r="Q293" t="n">
-        <v>-68628</v>
+        <v>63852</v>
       </c>
       <c r="R293" t="n">
-        <v>-380211</v>
+        <v>-657007</v>
       </c>
       <c r="S293" t="n">
-        <v>-964041</v>
+        <v>-633211</v>
       </c>
       <c r="T293" t="n">
-        <v>-1153882</v>
+        <v>-803695</v>
       </c>
       <c r="U293" t="n">
         <v>0</v>
@@ -40572,16 +40572,16 @@
         <v>0</v>
       </c>
       <c r="Y293" t="n">
-        <v>14150</v>
+        <v>69054</v>
       </c>
       <c r="Z293" t="n">
-        <v>20496</v>
+        <v>131363</v>
       </c>
       <c r="AA293" t="n">
-        <v>-4662</v>
+        <v>48534</v>
       </c>
       <c r="AB293" t="n">
-        <v>-19223</v>
+        <v>8919</v>
       </c>
       <c r="AC293" t="n">
         <v>-34</v>
@@ -40590,10 +40590,10 @@
         <v>-34</v>
       </c>
       <c r="AE293" t="n">
+        <v>-55</v>
+      </c>
+      <c r="AF293" t="n">
         <v>-30</v>
-      </c>
-      <c r="AF293" t="n">
-        <v>-55</v>
       </c>
       <c r="AG293" t="n">
         <v>0</v>
@@ -40613,29 +40613,29 @@
       </c>
       <c r="AM293" t="inlineStr">
         <is>
-          <t>跌破5日線、量能未放大、接近20日低點</t>
+          <t>跌破5日線、空頭排列、量能未放大、接近20日低點</t>
         </is>
       </c>
       <c r="AN293" t="inlineStr">
         <is>
-          <t>法人連續偏賣、5日法人明顯賣超</t>
+          <t>5日法人明顯賣超</t>
         </is>
       </c>
       <c r="AO293" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、量能未放大、接近20日低點、法人連續偏賣、5日法人明顯賣超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、空頭排列、量能未放大、接近20日低點、5日法人明顯賣超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>6757.TW</t>
+          <t>2337.TW</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>台灣虎航</t>
+          <t>旺宏</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
@@ -40644,28 +40644,28 @@
         </is>
       </c>
       <c r="D294" t="n">
-        <v>57.3</v>
+        <v>139.5</v>
       </c>
       <c r="E294" t="n">
-        <v>58.72</v>
+        <v>139.7</v>
       </c>
       <c r="F294" t="n">
-        <v>59.94</v>
+        <v>143</v>
       </c>
       <c r="G294" t="n">
-        <v>60.2</v>
+        <v>154.9</v>
       </c>
       <c r="H294" t="n">
-        <v>1621093</v>
+        <v>67740693</v>
       </c>
       <c r="I294" t="n">
-        <v>1683065</v>
+        <v>60279245</v>
       </c>
       <c r="J294" t="n">
-        <v>67.3</v>
+        <v>192</v>
       </c>
       <c r="K294" t="n">
-        <v>55.7</v>
+        <v>130.5</v>
       </c>
       <c r="L294" t="inlineStr">
         <is>
@@ -40673,64 +40673,64 @@
         </is>
       </c>
       <c r="M294" t="n">
-        <v>132906</v>
+        <v>-3187341</v>
       </c>
       <c r="N294" t="n">
-        <v>-525644</v>
+        <v>-6632689</v>
       </c>
       <c r="O294" t="n">
-        <v>-584677</v>
+        <v>-13148502</v>
       </c>
       <c r="P294" t="n">
-        <v>-794776</v>
+        <v>-114810713</v>
       </c>
       <c r="Q294" t="n">
-        <v>63852</v>
+        <v>-4002630</v>
       </c>
       <c r="R294" t="n">
-        <v>-657007</v>
+        <v>-8095912</v>
       </c>
       <c r="S294" t="n">
-        <v>-633211</v>
+        <v>-14151824</v>
       </c>
       <c r="T294" t="n">
-        <v>-803695</v>
+        <v>-109844875</v>
       </c>
       <c r="U294" t="n">
-        <v>0</v>
+        <v>19000</v>
       </c>
       <c r="V294" t="n">
-        <v>0</v>
+        <v>37000</v>
       </c>
       <c r="W294" t="n">
-        <v>0</v>
+        <v>76000</v>
       </c>
       <c r="X294" t="n">
-        <v>0</v>
+        <v>-5666000</v>
       </c>
       <c r="Y294" t="n">
-        <v>69054</v>
+        <v>796289</v>
       </c>
       <c r="Z294" t="n">
-        <v>131363</v>
+        <v>1426223</v>
       </c>
       <c r="AA294" t="n">
-        <v>48534</v>
+        <v>927322</v>
       </c>
       <c r="AB294" t="n">
-        <v>8919</v>
+        <v>700162</v>
       </c>
       <c r="AC294" t="n">
-        <v>-34</v>
+        <v>-36</v>
       </c>
       <c r="AD294" t="n">
-        <v>-34</v>
+        <v>-36</v>
       </c>
       <c r="AE294" t="n">
+        <v>-35</v>
+      </c>
+      <c r="AF294" t="n">
         <v>-55</v>
-      </c>
-      <c r="AF294" t="n">
-        <v>-30</v>
       </c>
       <c r="AG294" t="n">
         <v>0</v>
@@ -40750,29 +40750,29 @@
       </c>
       <c r="AM294" t="inlineStr">
         <is>
-          <t>跌破5日線、空頭排列、量能未放大、接近20日低點</t>
+          <t>跌破5日線、空頭排列、量能溫和放大</t>
         </is>
       </c>
       <c r="AN294" t="inlineStr">
         <is>
-          <t>5日法人明顯賣超</t>
+          <t>法人連續偏賣、5日法人明顯賣超、投信買外資賣</t>
         </is>
       </c>
       <c r="AO294" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、空頭排列、量能未放大、接近20日低點、5日法人明顯賣超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、空頭排列、量能溫和放大、法人連續偏賣、5日法人明顯賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>2337.TW</t>
+          <t>3057.TW</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>旺宏</t>
+          <t>喬鼎</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
@@ -40781,28 +40781,28 @@
         </is>
       </c>
       <c r="D295" t="n">
-        <v>139.5</v>
+        <v>16.2</v>
       </c>
       <c r="E295" t="n">
-        <v>139.7</v>
+        <v>18.11</v>
       </c>
       <c r="F295" t="n">
-        <v>143</v>
+        <v>18.66</v>
       </c>
       <c r="G295" t="n">
-        <v>154.9</v>
+        <v>19.23</v>
       </c>
       <c r="H295" t="n">
-        <v>67740693</v>
+        <v>304445</v>
       </c>
       <c r="I295" t="n">
-        <v>60279245</v>
+        <v>273955</v>
       </c>
       <c r="J295" t="n">
-        <v>192</v>
+        <v>21.15</v>
       </c>
       <c r="K295" t="n">
-        <v>130.5</v>
+        <v>16.05</v>
       </c>
       <c r="L295" t="inlineStr">
         <is>
@@ -40810,52 +40810,52 @@
         </is>
       </c>
       <c r="M295" t="n">
-        <v>-3187341</v>
+        <v>-14000</v>
       </c>
       <c r="N295" t="n">
-        <v>-6632689</v>
+        <v>-184000</v>
       </c>
       <c r="O295" t="n">
-        <v>-13148502</v>
+        <v>-319000</v>
       </c>
       <c r="P295" t="n">
-        <v>-114810713</v>
+        <v>-296629</v>
       </c>
       <c r="Q295" t="n">
-        <v>-4002630</v>
+        <v>-19000</v>
       </c>
       <c r="R295" t="n">
-        <v>-8095912</v>
+        <v>-188000</v>
       </c>
       <c r="S295" t="n">
-        <v>-14151824</v>
+        <v>-322000</v>
       </c>
       <c r="T295" t="n">
-        <v>-109844875</v>
+        <v>-301629</v>
       </c>
       <c r="U295" t="n">
-        <v>19000</v>
+        <v>0</v>
       </c>
       <c r="V295" t="n">
-        <v>37000</v>
+        <v>0</v>
       </c>
       <c r="W295" t="n">
-        <v>76000</v>
+        <v>0</v>
       </c>
       <c r="X295" t="n">
-        <v>-5666000</v>
+        <v>0</v>
       </c>
       <c r="Y295" t="n">
-        <v>796289</v>
+        <v>5000</v>
       </c>
       <c r="Z295" t="n">
-        <v>1426223</v>
+        <v>4000</v>
       </c>
       <c r="AA295" t="n">
-        <v>927322</v>
+        <v>3000</v>
       </c>
       <c r="AB295" t="n">
-        <v>700162</v>
+        <v>5000</v>
       </c>
       <c r="AC295" t="n">
         <v>-36</v>
@@ -40864,10 +40864,10 @@
         <v>-36</v>
       </c>
       <c r="AE295" t="n">
-        <v>-35</v>
+        <v>-45</v>
       </c>
       <c r="AF295" t="n">
-        <v>-55</v>
+        <v>-45</v>
       </c>
       <c r="AG295" t="n">
         <v>0</v>
@@ -40887,88 +40887,88 @@
       </c>
       <c r="AM295" t="inlineStr">
         <is>
-          <t>跌破5日線、空頭排列、量能溫和放大</t>
+          <t>跌破5日線、空頭排列、量能溫和放大、接近20日低點</t>
         </is>
       </c>
       <c r="AN295" t="inlineStr">
         <is>
-          <t>法人連續偏賣、5日法人明顯賣超、投信買外資賣</t>
+          <t>法人連續偏賣、5日法人賣超</t>
         </is>
       </c>
       <c r="AO295" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、空頭排列、量能溫和放大、法人連續偏賣、5日法人明顯賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、空頭排列、量能溫和放大、接近20日低點、法人連續偏賣、5日法人賣超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>3057.TW</t>
+          <t>00692.TW</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>喬鼎</t>
+          <t>富邦公司治理</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>個股</t>
+          <t>ETF</t>
         </is>
       </c>
       <c r="D296" t="n">
-        <v>16.2</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="E296" t="n">
-        <v>18.11</v>
+        <v>91.65000000000001</v>
       </c>
       <c r="F296" t="n">
-        <v>18.66</v>
+        <v>92.59</v>
       </c>
       <c r="G296" t="n">
-        <v>19.23</v>
+        <v>92.42</v>
       </c>
       <c r="H296" t="n">
-        <v>304445</v>
+        <v>2199215</v>
       </c>
       <c r="I296" t="n">
-        <v>273955</v>
+        <v>1084622</v>
       </c>
       <c r="J296" t="n">
-        <v>21.15</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="K296" t="n">
-        <v>16.05</v>
+        <v>88.84999999999999</v>
       </c>
       <c r="L296" t="inlineStr">
         <is>
-          <t>無明顯異常</t>
+          <t>爆量價未漲</t>
         </is>
       </c>
       <c r="M296" t="n">
-        <v>-14000</v>
+        <v>-456065</v>
       </c>
       <c r="N296" t="n">
-        <v>-184000</v>
+        <v>-218252</v>
       </c>
       <c r="O296" t="n">
-        <v>-319000</v>
+        <v>-124563</v>
       </c>
       <c r="P296" t="n">
-        <v>-296629</v>
+        <v>589408</v>
       </c>
       <c r="Q296" t="n">
-        <v>-19000</v>
+        <v>-3420</v>
       </c>
       <c r="R296" t="n">
-        <v>-188000</v>
+        <v>26618</v>
       </c>
       <c r="S296" t="n">
-        <v>-322000</v>
+        <v>-104065</v>
       </c>
       <c r="T296" t="n">
-        <v>-301629</v>
+        <v>26240</v>
       </c>
       <c r="U296" t="n">
         <v>0</v>
@@ -40983,16 +40983,16 @@
         <v>0</v>
       </c>
       <c r="Y296" t="n">
-        <v>5000</v>
+        <v>-452645</v>
       </c>
       <c r="Z296" t="n">
-        <v>4000</v>
+        <v>-244870</v>
       </c>
       <c r="AA296" t="n">
-        <v>3000</v>
+        <v>-20498</v>
       </c>
       <c r="AB296" t="n">
-        <v>5000</v>
+        <v>563168</v>
       </c>
       <c r="AC296" t="n">
         <v>-36</v>
@@ -41001,13 +41001,13 @@
         <v>-36</v>
       </c>
       <c r="AE296" t="n">
-        <v>-45</v>
+        <v>-10</v>
       </c>
       <c r="AF296" t="n">
-        <v>-45</v>
+        <v>-70</v>
       </c>
       <c r="AG296" t="n">
-        <v>0</v>
+        <v>-20</v>
       </c>
       <c r="AH296" t="inlineStr"/>
       <c r="AI296" t="inlineStr"/>
@@ -41024,59 +41024,59 @@
       </c>
       <c r="AM296" t="inlineStr">
         <is>
-          <t>跌破5日線、空頭排列、量能溫和放大、接近20日低點</t>
+          <t>跌破5日線、爆量、接近20日低點、爆量價未漲</t>
         </is>
       </c>
       <c r="AN296" t="inlineStr">
         <is>
-          <t>法人連續偏賣、5日法人賣超</t>
+          <t>法人連續偏賣、中期買超轉短線賣壓、5日法人賣超</t>
         </is>
       </c>
       <c r="AO296" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、空頭排列、量能溫和放大、接近20日低點、法人連續偏賣、5日法人賣超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、爆量、接近20日低點、爆量價未漲、法人連續偏賣、中期買超轉短線賣壓、5日法人賣超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>00692.TW</t>
+          <t>3130.TW</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>富邦公司治理</t>
+          <t>一零四</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>ETF</t>
+          <t>個股</t>
         </is>
       </c>
       <c r="D297" t="n">
-        <v>90.59999999999999</v>
+        <v>204</v>
       </c>
       <c r="E297" t="n">
-        <v>91.65000000000001</v>
+        <v>217.3</v>
       </c>
       <c r="F297" t="n">
-        <v>92.59</v>
+        <v>219.5</v>
       </c>
       <c r="G297" t="n">
-        <v>92.42</v>
+        <v>221.4</v>
       </c>
       <c r="H297" t="n">
-        <v>2199215</v>
+        <v>313623</v>
       </c>
       <c r="I297" t="n">
-        <v>1084622</v>
+        <v>136214</v>
       </c>
       <c r="J297" t="n">
-        <v>96.59999999999999</v>
+        <v>227.5</v>
       </c>
       <c r="K297" t="n">
-        <v>88.84999999999999</v>
+        <v>203</v>
       </c>
       <c r="L297" t="inlineStr">
         <is>
@@ -41084,28 +41084,28 @@
         </is>
       </c>
       <c r="M297" t="n">
-        <v>-456065</v>
+        <v>-223253</v>
       </c>
       <c r="N297" t="n">
-        <v>-218252</v>
+        <v>-344981</v>
       </c>
       <c r="O297" t="n">
-        <v>-124563</v>
+        <v>-427080</v>
       </c>
       <c r="P297" t="n">
-        <v>589408</v>
+        <v>-651501</v>
       </c>
       <c r="Q297" t="n">
-        <v>-3420</v>
+        <v>-147935</v>
       </c>
       <c r="R297" t="n">
-        <v>26618</v>
+        <v>-267663</v>
       </c>
       <c r="S297" t="n">
-        <v>-104065</v>
+        <v>-350762</v>
       </c>
       <c r="T297" t="n">
-        <v>26240</v>
+        <v>-576183</v>
       </c>
       <c r="U297" t="n">
         <v>0</v>
@@ -41120,16 +41120,16 @@
         <v>0</v>
       </c>
       <c r="Y297" t="n">
-        <v>-452645</v>
+        <v>-75318</v>
       </c>
       <c r="Z297" t="n">
-        <v>-244870</v>
+        <v>-77318</v>
       </c>
       <c r="AA297" t="n">
-        <v>-20498</v>
+        <v>-76318</v>
       </c>
       <c r="AB297" t="n">
-        <v>563168</v>
+        <v>-75318</v>
       </c>
       <c r="AC297" t="n">
         <v>-36</v>
@@ -41138,10 +41138,10 @@
         <v>-36</v>
       </c>
       <c r="AE297" t="n">
-        <v>-10</v>
+        <v>-35</v>
       </c>
       <c r="AF297" t="n">
-        <v>-70</v>
+        <v>-45</v>
       </c>
       <c r="AG297" t="n">
         <v>-20</v>
@@ -41161,29 +41161,29 @@
       </c>
       <c r="AM297" t="inlineStr">
         <is>
-          <t>跌破5日線、爆量、接近20日低點、爆量價未漲</t>
+          <t>跌破5日線、空頭排列、爆量、接近20日低點、爆量價未漲</t>
         </is>
       </c>
       <c r="AN297" t="inlineStr">
         <is>
-          <t>法人連續偏賣、中期買超轉短線賣壓、5日法人賣超</t>
+          <t>法人連續偏賣、5日法人賣超</t>
         </is>
       </c>
       <c r="AO297" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、爆量、接近20日低點、爆量價未漲、法人連續偏賣、中期買超轉短線賣壓、5日法人賣超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、空頭排列、爆量、接近20日低點、爆量價未漲、法人連續偏賣、5日法人賣超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>3130.TW</t>
+          <t>2314.TW</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>一零四</t>
+          <t>台揚</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
@@ -41192,57 +41192,57 @@
         </is>
       </c>
       <c r="D298" t="n">
-        <v>204</v>
+        <v>13.25</v>
       </c>
       <c r="E298" t="n">
-        <v>217.3</v>
+        <v>13.58</v>
       </c>
       <c r="F298" t="n">
-        <v>219.5</v>
+        <v>14.03</v>
       </c>
       <c r="G298" t="n">
-        <v>221.4</v>
+        <v>14.38</v>
       </c>
       <c r="H298" t="n">
-        <v>313623</v>
+        <v>79278</v>
       </c>
       <c r="I298" t="n">
-        <v>136214</v>
+        <v>126427</v>
       </c>
       <c r="J298" t="n">
-        <v>227.5</v>
+        <v>16.1</v>
       </c>
       <c r="K298" t="n">
-        <v>203</v>
+        <v>13.15</v>
       </c>
       <c r="L298" t="inlineStr">
         <is>
-          <t>爆量價未漲</t>
+          <t>無明顯異常</t>
         </is>
       </c>
       <c r="M298" t="n">
-        <v>-223253</v>
+        <v>-11000</v>
       </c>
       <c r="N298" t="n">
-        <v>-344981</v>
+        <v>-44000</v>
       </c>
       <c r="O298" t="n">
-        <v>-427080</v>
+        <v>-84000</v>
       </c>
       <c r="P298" t="n">
-        <v>-651501</v>
+        <v>-87000</v>
       </c>
       <c r="Q298" t="n">
-        <v>-147935</v>
+        <v>-11000</v>
       </c>
       <c r="R298" t="n">
-        <v>-267663</v>
+        <v>-44000</v>
       </c>
       <c r="S298" t="n">
-        <v>-350762</v>
+        <v>-84000</v>
       </c>
       <c r="T298" t="n">
-        <v>-576183</v>
+        <v>-87000</v>
       </c>
       <c r="U298" t="n">
         <v>0</v>
@@ -41257,16 +41257,16 @@
         <v>0</v>
       </c>
       <c r="Y298" t="n">
-        <v>-75318</v>
+        <v>0</v>
       </c>
       <c r="Z298" t="n">
-        <v>-77318</v>
+        <v>0</v>
       </c>
       <c r="AA298" t="n">
-        <v>-76318</v>
+        <v>0</v>
       </c>
       <c r="AB298" t="n">
-        <v>-75318</v>
+        <v>0</v>
       </c>
       <c r="AC298" t="n">
         <v>-36</v>
@@ -41275,13 +41275,13 @@
         <v>-36</v>
       </c>
       <c r="AE298" t="n">
+        <v>-55</v>
+      </c>
+      <c r="AF298" t="n">
         <v>-35</v>
       </c>
-      <c r="AF298" t="n">
-        <v>-45</v>
-      </c>
       <c r="AG298" t="n">
-        <v>-20</v>
+        <v>0</v>
       </c>
       <c r="AH298" t="inlineStr"/>
       <c r="AI298" t="inlineStr"/>
@@ -41298,17 +41298,17 @@
       </c>
       <c r="AM298" t="inlineStr">
         <is>
-          <t>跌破5日線、空頭排列、爆量、接近20日低點、爆量價未漲</t>
+          <t>跌破5日線、空頭排列、量能未放大、接近20日低點</t>
         </is>
       </c>
       <c r="AN298" t="inlineStr">
         <is>
-          <t>法人連續偏賣、5日法人賣超</t>
+          <t>法人連續偏賣、5日法人小幅賣超</t>
         </is>
       </c>
       <c r="AO298" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、空頭排列、爆量、接近20日低點、爆量價未漲、法人連續偏賣、5日法人賣超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、空頭排列、量能未放大、接近20日低點、法人連續偏賣、5日法人小幅賣超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
@@ -41726,12 +41726,12 @@
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>2314.TW</t>
+          <t>1304.TW</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>台揚</t>
+          <t>台聚</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
@@ -41740,28 +41740,28 @@
         </is>
       </c>
       <c r="D302" t="n">
-        <v>13.25</v>
+        <v>13.55</v>
       </c>
       <c r="E302" t="n">
+        <v>13.7</v>
+      </c>
+      <c r="F302" t="n">
+        <v>13.98</v>
+      </c>
+      <c r="G302" t="n">
         <v>13.58</v>
       </c>
-      <c r="F302" t="n">
-        <v>14.03</v>
-      </c>
-      <c r="G302" t="n">
-        <v>14.38</v>
-      </c>
       <c r="H302" t="n">
-        <v>79278</v>
+        <v>9415359</v>
       </c>
       <c r="I302" t="n">
-        <v>126427</v>
+        <v>8386638</v>
       </c>
       <c r="J302" t="n">
-        <v>16.1</v>
+        <v>15.8</v>
       </c>
       <c r="K302" t="n">
-        <v>13.15</v>
+        <v>12.55</v>
       </c>
       <c r="L302" t="inlineStr">
         <is>
@@ -41769,28 +41769,28 @@
         </is>
       </c>
       <c r="M302" t="n">
-        <v>-11000</v>
+        <v>-55502</v>
       </c>
       <c r="N302" t="n">
-        <v>-44000</v>
+        <v>-828233</v>
       </c>
       <c r="O302" t="n">
-        <v>-84000</v>
+        <v>-2152008</v>
       </c>
       <c r="P302" t="n">
-        <v>-87000</v>
+        <v>1103571</v>
       </c>
       <c r="Q302" t="n">
-        <v>-11000</v>
+        <v>43623</v>
       </c>
       <c r="R302" t="n">
-        <v>-44000</v>
+        <v>-695359</v>
       </c>
       <c r="S302" t="n">
-        <v>-84000</v>
+        <v>-1761752</v>
       </c>
       <c r="T302" t="n">
-        <v>-87000</v>
+        <v>1432448</v>
       </c>
       <c r="U302" t="n">
         <v>0</v>
@@ -41805,16 +41805,16 @@
         <v>0</v>
       </c>
       <c r="Y302" t="n">
-        <v>0</v>
+        <v>-99125</v>
       </c>
       <c r="Z302" t="n">
-        <v>0</v>
+        <v>-132874</v>
       </c>
       <c r="AA302" t="n">
-        <v>0</v>
+        <v>-390256</v>
       </c>
       <c r="AB302" t="n">
-        <v>0</v>
+        <v>-328877</v>
       </c>
       <c r="AC302" t="n">
         <v>-36</v>
@@ -41823,10 +41823,10 @@
         <v>-36</v>
       </c>
       <c r="AE302" t="n">
-        <v>-55</v>
+        <v>-10</v>
       </c>
       <c r="AF302" t="n">
-        <v>-35</v>
+        <v>-80</v>
       </c>
       <c r="AG302" t="n">
         <v>0</v>
@@ -41846,29 +41846,29 @@
       </c>
       <c r="AM302" t="inlineStr">
         <is>
-          <t>跌破5日線、空頭排列、量能未放大、接近20日低點</t>
+          <t>跌破5日線、量能溫和放大</t>
         </is>
       </c>
       <c r="AN302" t="inlineStr">
         <is>
-          <t>法人連續偏賣、5日法人小幅賣超</t>
+          <t>法人連續偏賣、中期買超轉短線賣壓、5日法人明顯賣超</t>
         </is>
       </c>
       <c r="AO302" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、空頭排列、量能未放大、接近20日低點、法人連續偏賣、5日法人小幅賣超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、量能溫和放大、法人連續偏賣、中期買超轉短線賣壓、5日法人明顯賣超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>1304.TW</t>
+          <t>5469.TW</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>台聚</t>
+          <t>瀚宇博</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
@@ -41877,28 +41877,28 @@
         </is>
       </c>
       <c r="D303" t="n">
-        <v>13.55</v>
+        <v>74.8</v>
       </c>
       <c r="E303" t="n">
-        <v>13.7</v>
+        <v>80.42</v>
       </c>
       <c r="F303" t="n">
-        <v>13.98</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="G303" t="n">
-        <v>13.58</v>
+        <v>85.66</v>
       </c>
       <c r="H303" t="n">
-        <v>9415359</v>
+        <v>5463723</v>
       </c>
       <c r="I303" t="n">
-        <v>8386638</v>
+        <v>3618580</v>
       </c>
       <c r="J303" t="n">
-        <v>15.8</v>
+        <v>94</v>
       </c>
       <c r="K303" t="n">
-        <v>12.55</v>
+        <v>72.7</v>
       </c>
       <c r="L303" t="inlineStr">
         <is>
@@ -41906,64 +41906,64 @@
         </is>
       </c>
       <c r="M303" t="n">
-        <v>-55502</v>
+        <v>-2011823</v>
       </c>
       <c r="N303" t="n">
-        <v>-828233</v>
+        <v>-3782479</v>
       </c>
       <c r="O303" t="n">
-        <v>-2152008</v>
+        <v>-4944825</v>
       </c>
       <c r="P303" t="n">
-        <v>1103571</v>
+        <v>-4698496</v>
       </c>
       <c r="Q303" t="n">
-        <v>43623</v>
+        <v>-1937123</v>
       </c>
       <c r="R303" t="n">
-        <v>-695359</v>
+        <v>-3899123</v>
       </c>
       <c r="S303" t="n">
-        <v>-1761752</v>
+        <v>-7149610</v>
       </c>
       <c r="T303" t="n">
-        <v>1432448</v>
+        <v>-17528334</v>
       </c>
       <c r="U303" t="n">
-        <v>0</v>
+        <v>-2000</v>
       </c>
       <c r="V303" t="n">
-        <v>0</v>
+        <v>208000</v>
       </c>
       <c r="W303" t="n">
-        <v>0</v>
+        <v>2390000</v>
       </c>
       <c r="X303" t="n">
-        <v>0</v>
+        <v>13232000</v>
       </c>
       <c r="Y303" t="n">
-        <v>-99125</v>
+        <v>-72700</v>
       </c>
       <c r="Z303" t="n">
-        <v>-132874</v>
+        <v>-91356</v>
       </c>
       <c r="AA303" t="n">
-        <v>-390256</v>
+        <v>-185215</v>
       </c>
       <c r="AB303" t="n">
-        <v>-328877</v>
+        <v>-402162</v>
       </c>
       <c r="AC303" t="n">
-        <v>-36</v>
+        <v>-38</v>
       </c>
       <c r="AD303" t="n">
-        <v>-36</v>
+        <v>-38</v>
       </c>
       <c r="AE303" t="n">
-        <v>-10</v>
+        <v>-40</v>
       </c>
       <c r="AF303" t="n">
-        <v>-80</v>
+        <v>-55</v>
       </c>
       <c r="AG303" t="n">
         <v>0</v>
@@ -41983,59 +41983,59 @@
       </c>
       <c r="AM303" t="inlineStr">
         <is>
-          <t>跌破5日線、量能溫和放大</t>
+          <t>跌破5日線、空頭排列、成交量放大、接近20日低點</t>
         </is>
       </c>
       <c r="AN303" t="inlineStr">
         <is>
-          <t>法人連續偏賣、中期買超轉短線賣壓、5日法人明顯賣超</t>
+          <t>法人連續偏賣、5日法人明顯賣超、投信買外資賣</t>
         </is>
       </c>
       <c r="AO303" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、量能溫和放大、法人連續偏賣、中期買超轉短線賣壓、5日法人明顯賣超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、空頭排列、成交量放大、接近20日低點、法人連續偏賣、5日法人明顯賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>00927.TW</t>
+          <t>1609.TW</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>群益半導體收益</t>
+          <t>大亞</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>ETF</t>
+          <t>個股</t>
         </is>
       </c>
       <c r="D304" t="n">
-        <v>40</v>
+        <v>38.65</v>
       </c>
       <c r="E304" t="n">
-        <v>40.99</v>
+        <v>39.86</v>
       </c>
       <c r="F304" t="n">
-        <v>41.71</v>
+        <v>39.77</v>
       </c>
       <c r="G304" t="n">
-        <v>41.44</v>
+        <v>38.6</v>
       </c>
       <c r="H304" t="n">
-        <v>108430692</v>
+        <v>7981971</v>
       </c>
       <c r="I304" t="n">
-        <v>70861650</v>
+        <v>17824127</v>
       </c>
       <c r="J304" t="n">
-        <v>44.59</v>
+        <v>44.25</v>
       </c>
       <c r="K304" t="n">
-        <v>38.64</v>
+        <v>35.3</v>
       </c>
       <c r="L304" t="inlineStr">
         <is>
@@ -42043,52 +42043,52 @@
         </is>
       </c>
       <c r="M304" t="n">
-        <v>-62019509</v>
+        <v>-1631880</v>
       </c>
       <c r="N304" t="n">
-        <v>-123183351</v>
+        <v>-239810</v>
       </c>
       <c r="O304" t="n">
-        <v>-206870780</v>
+        <v>-1754188</v>
       </c>
       <c r="P304" t="n">
-        <v>-397080679</v>
+        <v>7990586</v>
       </c>
       <c r="Q304" t="n">
-        <v>1315475</v>
+        <v>-1519309</v>
       </c>
       <c r="R304" t="n">
-        <v>-481845</v>
+        <v>-170092</v>
       </c>
       <c r="S304" t="n">
-        <v>-6137060</v>
+        <v>-820942</v>
       </c>
       <c r="T304" t="n">
-        <v>-15263435</v>
+        <v>7819748</v>
       </c>
       <c r="U304" t="n">
-        <v>0</v>
+        <v>-2000</v>
       </c>
       <c r="V304" t="n">
-        <v>230000</v>
+        <v>-3000</v>
       </c>
       <c r="W304" t="n">
-        <v>230000</v>
+        <v>-3000</v>
       </c>
       <c r="X304" t="n">
-        <v>230000</v>
+        <v>-2000</v>
       </c>
       <c r="Y304" t="n">
-        <v>-63334984</v>
+        <v>-110571</v>
       </c>
       <c r="Z304" t="n">
-        <v>-122931506</v>
+        <v>-66718</v>
       </c>
       <c r="AA304" t="n">
-        <v>-200963720</v>
+        <v>-930246</v>
       </c>
       <c r="AB304" t="n">
-        <v>-382047244</v>
+        <v>172838</v>
       </c>
       <c r="AC304" t="n">
         <v>-38</v>
@@ -42097,10 +42097,10 @@
         <v>-38</v>
       </c>
       <c r="AE304" t="n">
-        <v>-40</v>
+        <v>5</v>
       </c>
       <c r="AF304" t="n">
-        <v>-55</v>
+        <v>-100</v>
       </c>
       <c r="AG304" t="n">
         <v>0</v>
@@ -42120,17 +42120,17 @@
       </c>
       <c r="AM304" t="inlineStr">
         <is>
-          <t>跌破5日線、死亡交叉、成交量放大、接近20日低點</t>
+          <t>跌破5日線、多頭排列、量能未放大</t>
         </is>
       </c>
       <c r="AN304" t="inlineStr">
         <is>
-          <t>法人連續偏賣、5日法人明顯賣超、投信買外資賣</t>
+          <t>法人連續偏賣、中期買超轉短線賣壓、5日法人明顯賣超、外資投信同步賣超</t>
         </is>
       </c>
       <c r="AO304" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、死亡交叉、成交量放大、接近20日低點、法人連續偏賣、5日法人明顯賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、多頭排列、量能未放大、法人連續偏賣、中期買超轉短線賣壓、5日法人明顯賣超、外資投信同步賣超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
@@ -42685,12 +42685,12 @@
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>5469.TW</t>
+          <t>2897.TW</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>瀚宇博</t>
+          <t>王道銀行</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
@@ -42699,28 +42699,28 @@
         </is>
       </c>
       <c r="D309" t="n">
-        <v>74.8</v>
+        <v>10.4</v>
       </c>
       <c r="E309" t="n">
-        <v>80.42</v>
+        <v>10.52</v>
       </c>
       <c r="F309" t="n">
-        <v>84.09999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="G309" t="n">
-        <v>85.66</v>
+        <v>10.52</v>
       </c>
       <c r="H309" t="n">
-        <v>5463723</v>
+        <v>7172361</v>
       </c>
       <c r="I309" t="n">
-        <v>3618580</v>
+        <v>4577917</v>
       </c>
       <c r="J309" t="n">
-        <v>94</v>
+        <v>10.7</v>
       </c>
       <c r="K309" t="n">
-        <v>72.7</v>
+        <v>10.3</v>
       </c>
       <c r="L309" t="inlineStr">
         <is>
@@ -42728,52 +42728,52 @@
         </is>
       </c>
       <c r="M309" t="n">
-        <v>-2011823</v>
+        <v>-2333000</v>
       </c>
       <c r="N309" t="n">
-        <v>-3782479</v>
+        <v>-4032537</v>
       </c>
       <c r="O309" t="n">
-        <v>-4944825</v>
+        <v>-1831979</v>
       </c>
       <c r="P309" t="n">
-        <v>-4698496</v>
+        <v>1776815</v>
       </c>
       <c r="Q309" t="n">
-        <v>-1937123</v>
+        <v>-2603000</v>
       </c>
       <c r="R309" t="n">
-        <v>-3899123</v>
+        <v>-4286938</v>
       </c>
       <c r="S309" t="n">
-        <v>-7149610</v>
+        <v>-2245108</v>
       </c>
       <c r="T309" t="n">
-        <v>-17528334</v>
+        <v>-710739</v>
       </c>
       <c r="U309" t="n">
-        <v>-2000</v>
+        <v>118000</v>
       </c>
       <c r="V309" t="n">
-        <v>208000</v>
+        <v>201000</v>
       </c>
       <c r="W309" t="n">
-        <v>2390000</v>
+        <v>373000</v>
       </c>
       <c r="X309" t="n">
-        <v>13232000</v>
+        <v>2492000</v>
       </c>
       <c r="Y309" t="n">
-        <v>-72700</v>
+        <v>152000</v>
       </c>
       <c r="Z309" t="n">
-        <v>-91356</v>
+        <v>53401</v>
       </c>
       <c r="AA309" t="n">
-        <v>-185215</v>
+        <v>40129</v>
       </c>
       <c r="AB309" t="n">
-        <v>-402162</v>
+        <v>-4446</v>
       </c>
       <c r="AC309" t="n">
         <v>-38</v>
@@ -42782,10 +42782,10 @@
         <v>-38</v>
       </c>
       <c r="AE309" t="n">
-        <v>-40</v>
+        <v>-15</v>
       </c>
       <c r="AF309" t="n">
-        <v>-55</v>
+        <v>-80</v>
       </c>
       <c r="AG309" t="n">
         <v>0</v>
@@ -42805,17 +42805,17 @@
       </c>
       <c r="AM309" t="inlineStr">
         <is>
-          <t>跌破5日線、空頭排列、成交量放大、接近20日低點</t>
+          <t>跌破5日線、成交量放大、接近20日低點</t>
         </is>
       </c>
       <c r="AN309" t="inlineStr">
         <is>
-          <t>法人連續偏賣、5日法人明顯賣超、投信買外資賣</t>
+          <t>法人連續偏賣、中期買超轉短線賣壓、5日法人明顯賣超、投信買外資賣</t>
         </is>
       </c>
       <c r="AO309" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、空頭排列、成交量放大、接近20日低點、法人連續偏賣、5日法人明顯賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、成交量放大、接近20日低點、法人連續偏賣、中期買超轉短線賣壓、5日法人明顯賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
@@ -43781,12 +43781,12 @@
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>1609.TW</t>
+          <t>1905.TW</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>大亞</t>
+          <t>華紙</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
@@ -43795,28 +43795,28 @@
         </is>
       </c>
       <c r="D317" t="n">
-        <v>38.65</v>
+        <v>14.75</v>
       </c>
       <c r="E317" t="n">
-        <v>39.86</v>
+        <v>15.49</v>
       </c>
       <c r="F317" t="n">
-        <v>39.77</v>
+        <v>16.07</v>
       </c>
       <c r="G317" t="n">
-        <v>38.6</v>
+        <v>16.16</v>
       </c>
       <c r="H317" t="n">
-        <v>7981971</v>
+        <v>4336931</v>
       </c>
       <c r="I317" t="n">
-        <v>17824127</v>
+        <v>4784034</v>
       </c>
       <c r="J317" t="n">
-        <v>44.25</v>
+        <v>18.8</v>
       </c>
       <c r="K317" t="n">
-        <v>35.3</v>
+        <v>12.75</v>
       </c>
       <c r="L317" t="inlineStr">
         <is>
@@ -43824,52 +43824,52 @@
         </is>
       </c>
       <c r="M317" t="n">
-        <v>-1631880</v>
+        <v>862143</v>
       </c>
       <c r="N317" t="n">
-        <v>-239810</v>
+        <v>19900</v>
       </c>
       <c r="O317" t="n">
-        <v>-1754188</v>
+        <v>-1842216</v>
       </c>
       <c r="P317" t="n">
-        <v>7990586</v>
+        <v>1310282</v>
       </c>
       <c r="Q317" t="n">
-        <v>-1519309</v>
+        <v>892300</v>
       </c>
       <c r="R317" t="n">
-        <v>-170092</v>
+        <v>155500</v>
       </c>
       <c r="S317" t="n">
-        <v>-820942</v>
+        <v>-1646440</v>
       </c>
       <c r="T317" t="n">
-        <v>7819748</v>
+        <v>1541264</v>
       </c>
       <c r="U317" t="n">
-        <v>-2000</v>
+        <v>0</v>
       </c>
       <c r="V317" t="n">
-        <v>-3000</v>
+        <v>-6000</v>
       </c>
       <c r="W317" t="n">
-        <v>-3000</v>
+        <v>-11000</v>
       </c>
       <c r="X317" t="n">
-        <v>-2000</v>
+        <v>-18000</v>
       </c>
       <c r="Y317" t="n">
-        <v>-110571</v>
+        <v>-30157</v>
       </c>
       <c r="Z317" t="n">
-        <v>-66718</v>
+        <v>-129600</v>
       </c>
       <c r="AA317" t="n">
-        <v>-930246</v>
+        <v>-184776</v>
       </c>
       <c r="AB317" t="n">
-        <v>172838</v>
+        <v>-212982</v>
       </c>
       <c r="AC317" t="n">
         <v>-38</v>
@@ -43878,10 +43878,10 @@
         <v>-38</v>
       </c>
       <c r="AE317" t="n">
-        <v>5</v>
+        <v>-45</v>
       </c>
       <c r="AF317" t="n">
-        <v>-100</v>
+        <v>-50</v>
       </c>
       <c r="AG317" t="n">
         <v>0</v>
@@ -43901,29 +43901,29 @@
       </c>
       <c r="AM317" t="inlineStr">
         <is>
-          <t>跌破5日線、多頭排列、量能未放大</t>
+          <t>跌破5日線、空頭排列、量能未放大</t>
         </is>
       </c>
       <c r="AN317" t="inlineStr">
         <is>
-          <t>法人連續偏賣、中期買超轉短線賣壓、5日法人明顯賣超、外資投信同步賣超</t>
+          <t>5日法人明顯賣超、外資投信同步賣超</t>
         </is>
       </c>
       <c r="AO317" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、多頭排列、量能未放大、法人連續偏賣、中期買超轉短線賣壓、5日法人明顯賣超、外資投信同步賣超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、空頭排列、量能未放大、5日法人明顯賣超、外資投信同步賣超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>1905.TW</t>
+          <t>2413.TW</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>華紙</t>
+          <t>環科</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
@@ -43932,28 +43932,28 @@
         </is>
       </c>
       <c r="D318" t="n">
-        <v>14.75</v>
+        <v>44</v>
       </c>
       <c r="E318" t="n">
-        <v>15.49</v>
+        <v>45.4</v>
       </c>
       <c r="F318" t="n">
-        <v>16.07</v>
+        <v>46.84</v>
       </c>
       <c r="G318" t="n">
-        <v>16.16</v>
+        <v>50.48</v>
       </c>
       <c r="H318" t="n">
-        <v>4336931</v>
+        <v>3365200</v>
       </c>
       <c r="I318" t="n">
-        <v>4784034</v>
+        <v>2011650</v>
       </c>
       <c r="J318" t="n">
-        <v>18.8</v>
+        <v>67.3</v>
       </c>
       <c r="K318" t="n">
-        <v>12.75</v>
+        <v>43</v>
       </c>
       <c r="L318" t="inlineStr">
         <is>
@@ -43961,52 +43961,52 @@
         </is>
       </c>
       <c r="M318" t="n">
-        <v>862143</v>
+        <v>-919978</v>
       </c>
       <c r="N318" t="n">
-        <v>19900</v>
+        <v>-1572699</v>
       </c>
       <c r="O318" t="n">
-        <v>-1842216</v>
+        <v>-2068313</v>
       </c>
       <c r="P318" t="n">
-        <v>1310282</v>
+        <v>-3430881</v>
       </c>
       <c r="Q318" t="n">
-        <v>892300</v>
+        <v>-923000</v>
       </c>
       <c r="R318" t="n">
-        <v>155500</v>
+        <v>-1575023</v>
       </c>
       <c r="S318" t="n">
-        <v>-1646440</v>
+        <v>-2071076</v>
       </c>
       <c r="T318" t="n">
-        <v>1541264</v>
+        <v>-3430371</v>
       </c>
       <c r="U318" t="n">
         <v>0</v>
       </c>
       <c r="V318" t="n">
-        <v>-6000</v>
+        <v>0</v>
       </c>
       <c r="W318" t="n">
-        <v>-11000</v>
+        <v>0</v>
       </c>
       <c r="X318" t="n">
-        <v>-18000</v>
+        <v>0</v>
       </c>
       <c r="Y318" t="n">
-        <v>-30157</v>
+        <v>3022</v>
       </c>
       <c r="Z318" t="n">
-        <v>-129600</v>
+        <v>2324</v>
       </c>
       <c r="AA318" t="n">
-        <v>-184776</v>
+        <v>2763</v>
       </c>
       <c r="AB318" t="n">
-        <v>-212982</v>
+        <v>-510</v>
       </c>
       <c r="AC318" t="n">
         <v>-38</v>
@@ -44015,10 +44015,10 @@
         <v>-38</v>
       </c>
       <c r="AE318" t="n">
-        <v>-45</v>
+        <v>-40</v>
       </c>
       <c r="AF318" t="n">
-        <v>-50</v>
+        <v>-55</v>
       </c>
       <c r="AG318" t="n">
         <v>0</v>
@@ -44038,59 +44038,59 @@
       </c>
       <c r="AM318" t="inlineStr">
         <is>
-          <t>跌破5日線、空頭排列、量能未放大</t>
+          <t>跌破5日線、空頭排列、成交量放大、接近20日低點</t>
         </is>
       </c>
       <c r="AN318" t="inlineStr">
         <is>
-          <t>5日法人明顯賣超、外資投信同步賣超</t>
+          <t>法人連續偏賣、5日法人明顯賣超</t>
         </is>
       </c>
       <c r="AO318" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、空頭排列、量能未放大、5日法人明顯賣超、外資投信同步賣超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、空頭排列、成交量放大、接近20日低點、法人連續偏賣、5日法人明顯賣超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>2413.TW</t>
+          <t>00927.TW</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>環科</t>
+          <t>群益半導體收益</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>個股</t>
+          <t>ETF</t>
         </is>
       </c>
       <c r="D319" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="E319" t="n">
-        <v>45.4</v>
+        <v>40.99</v>
       </c>
       <c r="F319" t="n">
-        <v>46.84</v>
+        <v>41.71</v>
       </c>
       <c r="G319" t="n">
-        <v>50.48</v>
+        <v>41.44</v>
       </c>
       <c r="H319" t="n">
-        <v>3365200</v>
+        <v>108430692</v>
       </c>
       <c r="I319" t="n">
-        <v>2011650</v>
+        <v>70861650</v>
       </c>
       <c r="J319" t="n">
-        <v>67.3</v>
+        <v>44.59</v>
       </c>
       <c r="K319" t="n">
-        <v>43</v>
+        <v>38.64</v>
       </c>
       <c r="L319" t="inlineStr">
         <is>
@@ -44098,52 +44098,52 @@
         </is>
       </c>
       <c r="M319" t="n">
-        <v>-919978</v>
+        <v>-62019509</v>
       </c>
       <c r="N319" t="n">
-        <v>-1572699</v>
+        <v>-123183351</v>
       </c>
       <c r="O319" t="n">
-        <v>-2068313</v>
+        <v>-206870780</v>
       </c>
       <c r="P319" t="n">
-        <v>-3430881</v>
+        <v>-397080679</v>
       </c>
       <c r="Q319" t="n">
-        <v>-923000</v>
+        <v>1315475</v>
       </c>
       <c r="R319" t="n">
-        <v>-1575023</v>
+        <v>-481845</v>
       </c>
       <c r="S319" t="n">
-        <v>-2071076</v>
+        <v>-6137060</v>
       </c>
       <c r="T319" t="n">
-        <v>-3430371</v>
+        <v>-15263435</v>
       </c>
       <c r="U319" t="n">
         <v>0</v>
       </c>
       <c r="V319" t="n">
-        <v>0</v>
+        <v>230000</v>
       </c>
       <c r="W319" t="n">
-        <v>0</v>
+        <v>230000</v>
       </c>
       <c r="X319" t="n">
-        <v>0</v>
+        <v>230000</v>
       </c>
       <c r="Y319" t="n">
-        <v>3022</v>
+        <v>-63334984</v>
       </c>
       <c r="Z319" t="n">
-        <v>2324</v>
+        <v>-122931506</v>
       </c>
       <c r="AA319" t="n">
-        <v>2763</v>
+        <v>-200963720</v>
       </c>
       <c r="AB319" t="n">
-        <v>-510</v>
+        <v>-382047244</v>
       </c>
       <c r="AC319" t="n">
         <v>-38</v>
@@ -44175,17 +44175,17 @@
       </c>
       <c r="AM319" t="inlineStr">
         <is>
-          <t>跌破5日線、空頭排列、成交量放大、接近20日低點</t>
+          <t>跌破5日線、死亡交叉、成交量放大、接近20日低點</t>
         </is>
       </c>
       <c r="AN319" t="inlineStr">
         <is>
-          <t>法人連續偏賣、5日法人明顯賣超</t>
+          <t>法人連續偏賣、5日法人明顯賣超、投信買外資賣</t>
         </is>
       </c>
       <c r="AO319" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、空頭排列、成交量放大、接近20日低點、法人連續偏賣、5日法人明顯賣超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、死亡交叉、成交量放大、接近20日低點、法人連續偏賣、5日法人明顯賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
@@ -44329,12 +44329,12 @@
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>2897.TW</t>
+          <t>6409.TW</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>王道銀行</t>
+          <t>旭隼</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
@@ -44343,28 +44343,28 @@
         </is>
       </c>
       <c r="D321" t="n">
-        <v>10.4</v>
+        <v>1080</v>
       </c>
       <c r="E321" t="n">
-        <v>10.52</v>
+        <v>1113</v>
       </c>
       <c r="F321" t="n">
-        <v>10.5</v>
+        <v>1151</v>
       </c>
       <c r="G321" t="n">
-        <v>10.52</v>
+        <v>1048.55</v>
       </c>
       <c r="H321" t="n">
-        <v>7172361</v>
+        <v>1207542</v>
       </c>
       <c r="I321" t="n">
-        <v>4577917</v>
+        <v>1342761</v>
       </c>
       <c r="J321" t="n">
-        <v>10.7</v>
+        <v>1380</v>
       </c>
       <c r="K321" t="n">
-        <v>10.3</v>
+        <v>900</v>
       </c>
       <c r="L321" t="inlineStr">
         <is>
@@ -44372,61 +44372,61 @@
         </is>
       </c>
       <c r="M321" t="n">
-        <v>-2333000</v>
+        <v>-259749</v>
       </c>
       <c r="N321" t="n">
-        <v>-4032537</v>
+        <v>-589918</v>
       </c>
       <c r="O321" t="n">
-        <v>-1831979</v>
+        <v>-681344</v>
       </c>
       <c r="P321" t="n">
-        <v>1776815</v>
+        <v>791465</v>
       </c>
       <c r="Q321" t="n">
-        <v>-2603000</v>
+        <v>-283985</v>
       </c>
       <c r="R321" t="n">
-        <v>-4286938</v>
+        <v>-592865</v>
       </c>
       <c r="S321" t="n">
-        <v>-2245108</v>
+        <v>-1075809</v>
       </c>
       <c r="T321" t="n">
-        <v>-710739</v>
+        <v>-1298277</v>
       </c>
       <c r="U321" t="n">
-        <v>118000</v>
+        <v>-753</v>
       </c>
       <c r="V321" t="n">
-        <v>201000</v>
+        <v>-8693</v>
       </c>
       <c r="W321" t="n">
-        <v>373000</v>
+        <v>446798</v>
       </c>
       <c r="X321" t="n">
-        <v>2492000</v>
+        <v>2148557</v>
       </c>
       <c r="Y321" t="n">
-        <v>152000</v>
+        <v>24989</v>
       </c>
       <c r="Z321" t="n">
-        <v>53401</v>
+        <v>11640</v>
       </c>
       <c r="AA321" t="n">
-        <v>40129</v>
+        <v>-52333</v>
       </c>
       <c r="AB321" t="n">
-        <v>-4446</v>
+        <v>-58815</v>
       </c>
       <c r="AC321" t="n">
-        <v>-38</v>
+        <v>-40</v>
       </c>
       <c r="AD321" t="n">
-        <v>-38</v>
+        <v>-40</v>
       </c>
       <c r="AE321" t="n">
-        <v>-15</v>
+        <v>-20</v>
       </c>
       <c r="AF321" t="n">
         <v>-80</v>
@@ -44449,7 +44449,7 @@
       </c>
       <c r="AM321" t="inlineStr">
         <is>
-          <t>跌破5日線、成交量放大、接近20日低點</t>
+          <t>跌破5日線、量能未放大</t>
         </is>
       </c>
       <c r="AN321" t="inlineStr">
@@ -44459,102 +44459,102 @@
       </c>
       <c r="AO321" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、成交量放大、接近20日低點、法人連續偏賣、中期買超轉短線賣壓、5日法人明顯賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、量能未放大、法人連續偏賣、中期買超轉短線賣壓、5日法人明顯賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>6409.TW</t>
+          <t>00403A.TW</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>旭隼</t>
+          <t>主動統一升級50</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>個股</t>
+          <t>ETF</t>
         </is>
       </c>
       <c r="D322" t="n">
-        <v>1080</v>
+        <v>10.11</v>
       </c>
       <c r="E322" t="n">
-        <v>1113</v>
+        <v>10.37</v>
       </c>
       <c r="F322" t="n">
-        <v>1151</v>
+        <v>10.72</v>
       </c>
       <c r="G322" t="n">
-        <v>1048.55</v>
+        <v>10.81</v>
       </c>
       <c r="H322" t="n">
-        <v>1207542</v>
+        <v>752371033</v>
       </c>
       <c r="I322" t="n">
-        <v>1342761</v>
+        <v>346500375</v>
       </c>
       <c r="J322" t="n">
-        <v>1380</v>
+        <v>11.45</v>
       </c>
       <c r="K322" t="n">
-        <v>900</v>
+        <v>9.789999999999999</v>
       </c>
       <c r="L322" t="inlineStr">
         <is>
-          <t>無明顯異常</t>
+          <t>爆量價未漲</t>
         </is>
       </c>
       <c r="M322" t="n">
-        <v>-259749</v>
+        <v>-466902557</v>
       </c>
       <c r="N322" t="n">
-        <v>-589918</v>
+        <v>-414302522</v>
       </c>
       <c r="O322" t="n">
-        <v>-681344</v>
+        <v>-658674528</v>
       </c>
       <c r="P322" t="n">
-        <v>791465</v>
+        <v>-227479113</v>
       </c>
       <c r="Q322" t="n">
-        <v>-283985</v>
+        <v>-261565985</v>
       </c>
       <c r="R322" t="n">
-        <v>-592865</v>
+        <v>-230585414</v>
       </c>
       <c r="S322" t="n">
-        <v>-1075809</v>
+        <v>-416598119</v>
       </c>
       <c r="T322" t="n">
-        <v>-1298277</v>
+        <v>-185763085</v>
       </c>
       <c r="U322" t="n">
-        <v>-753</v>
+        <v>0</v>
       </c>
       <c r="V322" t="n">
-        <v>-8693</v>
+        <v>0</v>
       </c>
       <c r="W322" t="n">
-        <v>446798</v>
+        <v>0</v>
       </c>
       <c r="X322" t="n">
-        <v>2148557</v>
+        <v>0</v>
       </c>
       <c r="Y322" t="n">
-        <v>24989</v>
+        <v>-205336572</v>
       </c>
       <c r="Z322" t="n">
-        <v>11640</v>
+        <v>-183717108</v>
       </c>
       <c r="AA322" t="n">
-        <v>-52333</v>
+        <v>-242076409</v>
       </c>
       <c r="AB322" t="n">
-        <v>-58815</v>
+        <v>-41716028</v>
       </c>
       <c r="AC322" t="n">
         <v>-40</v>
@@ -44563,13 +44563,13 @@
         <v>-40</v>
       </c>
       <c r="AE322" t="n">
+        <v>-35</v>
+      </c>
+      <c r="AF322" t="n">
+        <v>-55</v>
+      </c>
+      <c r="AG322" t="n">
         <v>-20</v>
-      </c>
-      <c r="AF322" t="n">
-        <v>-80</v>
-      </c>
-      <c r="AG322" t="n">
-        <v>0</v>
       </c>
       <c r="AH322" t="inlineStr"/>
       <c r="AI322" t="inlineStr"/>
@@ -44586,17 +44586,17 @@
       </c>
       <c r="AM322" t="inlineStr">
         <is>
-          <t>跌破5日線、量能未放大</t>
+          <t>跌破5日線、空頭排列、爆量、接近20日低點、爆量價未漲</t>
         </is>
       </c>
       <c r="AN322" t="inlineStr">
         <is>
-          <t>法人連續偏賣、中期買超轉短線賣壓、5日法人明顯賣超、投信買外資賣</t>
+          <t>法人連續偏賣、5日法人明顯賣超</t>
         </is>
       </c>
       <c r="AO322" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、量能未放大、法人連續偏賣、中期買超轉短線賣壓、5日法人明顯賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、空頭排列、爆量、接近20日低點、爆量價未漲、法人連續偏賣、5日法人明顯賣超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
@@ -45014,71 +45014,71 @@
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>00403A.TW</t>
+          <t>3673.TW</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>主動統一升級50</t>
+          <t>TPK-KY</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>ETF</t>
+          <t>個股</t>
         </is>
       </c>
       <c r="D326" t="n">
-        <v>10.11</v>
+        <v>72.2</v>
       </c>
       <c r="E326" t="n">
-        <v>10.37</v>
+        <v>76.42</v>
       </c>
       <c r="F326" t="n">
-        <v>10.72</v>
+        <v>78.61</v>
       </c>
       <c r="G326" t="n">
-        <v>10.81</v>
+        <v>80.31999999999999</v>
       </c>
       <c r="H326" t="n">
-        <v>752371033</v>
+        <v>9482750</v>
       </c>
       <c r="I326" t="n">
-        <v>346500375</v>
+        <v>8365839</v>
       </c>
       <c r="J326" t="n">
-        <v>11.45</v>
+        <v>91</v>
       </c>
       <c r="K326" t="n">
-        <v>9.789999999999999</v>
+        <v>70.2</v>
       </c>
       <c r="L326" t="inlineStr">
         <is>
-          <t>爆量價未漲</t>
+          <t>無明顯異常</t>
         </is>
       </c>
       <c r="M326" t="n">
-        <v>-466902557</v>
+        <v>-2115827</v>
       </c>
       <c r="N326" t="n">
-        <v>-414302522</v>
+        <v>-2551944</v>
       </c>
       <c r="O326" t="n">
-        <v>-658674528</v>
+        <v>-2901553</v>
       </c>
       <c r="P326" t="n">
-        <v>-227479113</v>
+        <v>-3645072</v>
       </c>
       <c r="Q326" t="n">
-        <v>-261565985</v>
+        <v>-1883140</v>
       </c>
       <c r="R326" t="n">
-        <v>-230585414</v>
+        <v>-2141318</v>
       </c>
       <c r="S326" t="n">
-        <v>-416598119</v>
+        <v>-2000431</v>
       </c>
       <c r="T326" t="n">
-        <v>-185763085</v>
+        <v>-2720517</v>
       </c>
       <c r="U326" t="n">
         <v>0</v>
@@ -45093,16 +45093,16 @@
         <v>0</v>
       </c>
       <c r="Y326" t="n">
-        <v>-205336572</v>
+        <v>-232687</v>
       </c>
       <c r="Z326" t="n">
-        <v>-183717108</v>
+        <v>-410626</v>
       </c>
       <c r="AA326" t="n">
-        <v>-242076409</v>
+        <v>-901122</v>
       </c>
       <c r="AB326" t="n">
-        <v>-41716028</v>
+        <v>-924555</v>
       </c>
       <c r="AC326" t="n">
         <v>-40</v>
@@ -45111,13 +45111,13 @@
         <v>-40</v>
       </c>
       <c r="AE326" t="n">
-        <v>-35</v>
+        <v>-45</v>
       </c>
       <c r="AF326" t="n">
         <v>-55</v>
       </c>
       <c r="AG326" t="n">
-        <v>-20</v>
+        <v>0</v>
       </c>
       <c r="AH326" t="inlineStr"/>
       <c r="AI326" t="inlineStr"/>
@@ -45134,7 +45134,7 @@
       </c>
       <c r="AM326" t="inlineStr">
         <is>
-          <t>跌破5日線、空頭排列、爆量、接近20日低點、爆量價未漲</t>
+          <t>跌破5日線、空頭排列、量能溫和放大、接近20日低點</t>
         </is>
       </c>
       <c r="AN326" t="inlineStr">
@@ -45144,7 +45144,7 @@
       </c>
       <c r="AO326" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、空頭排列、爆量、接近20日低點、爆量價未漲、法人連續偏賣、5日法人明顯賣超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、空頭排列、量能溫和放大、接近20日低點、法人連續偏賣、5日法人明顯賣超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
@@ -45425,12 +45425,12 @@
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>2454.TW</t>
+          <t>1611.TW</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>聯發科</t>
+          <t>中電</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
@@ -45439,28 +45439,28 @@
         </is>
       </c>
       <c r="D329" t="n">
-        <v>3660</v>
+        <v>12.6</v>
       </c>
       <c r="E329" t="n">
-        <v>3887</v>
+        <v>13.04</v>
       </c>
       <c r="F329" t="n">
-        <v>4068</v>
+        <v>13.3</v>
       </c>
       <c r="G329" t="n">
-        <v>4197.25</v>
+        <v>13.22</v>
       </c>
       <c r="H329" t="n">
-        <v>12479607</v>
+        <v>1082455</v>
       </c>
       <c r="I329" t="n">
-        <v>8539021</v>
+        <v>785317</v>
       </c>
       <c r="J329" t="n">
-        <v>4785</v>
+        <v>14.2</v>
       </c>
       <c r="K329" t="n">
-        <v>3515</v>
+        <v>12.3</v>
       </c>
       <c r="L329" t="inlineStr">
         <is>
@@ -45468,52 +45468,52 @@
         </is>
       </c>
       <c r="M329" t="n">
-        <v>-144571</v>
+        <v>-610396</v>
       </c>
       <c r="N329" t="n">
-        <v>-1826135</v>
+        <v>-966300</v>
       </c>
       <c r="O329" t="n">
-        <v>-2751340</v>
+        <v>-1523935</v>
       </c>
       <c r="P329" t="n">
-        <v>-5974791</v>
+        <v>-1030359</v>
       </c>
       <c r="Q329" t="n">
-        <v>224947</v>
+        <v>-636992</v>
       </c>
       <c r="R329" t="n">
-        <v>-1237325</v>
+        <v>-1024952</v>
       </c>
       <c r="S329" t="n">
-        <v>-2093865</v>
+        <v>-1551202</v>
       </c>
       <c r="T329" t="n">
-        <v>-4255511</v>
+        <v>-1056600</v>
       </c>
       <c r="U329" t="n">
-        <v>158853</v>
+        <v>0</v>
       </c>
       <c r="V329" t="n">
-        <v>-187152</v>
+        <v>0</v>
       </c>
       <c r="W329" t="n">
-        <v>239404</v>
+        <v>0</v>
       </c>
       <c r="X329" t="n">
-        <v>-1188343</v>
+        <v>0</v>
       </c>
       <c r="Y329" t="n">
-        <v>-528371</v>
+        <v>26596</v>
       </c>
       <c r="Z329" t="n">
-        <v>-401658</v>
+        <v>58652</v>
       </c>
       <c r="AA329" t="n">
-        <v>-896879</v>
+        <v>27267</v>
       </c>
       <c r="AB329" t="n">
-        <v>-530937</v>
+        <v>26241</v>
       </c>
       <c r="AC329" t="n">
         <v>-40</v>
@@ -45545,17 +45545,17 @@
       </c>
       <c r="AM329" t="inlineStr">
         <is>
-          <t>跌破5日線、空頭排列、量能溫和放大、接近20日低點</t>
+          <t>跌破5日線、死亡交叉、量能溫和放大、接近20日低點</t>
         </is>
       </c>
       <c r="AN329" t="inlineStr">
         <is>
-          <t>法人連續偏賣、5日法人明顯賣超、投信買外資賣</t>
+          <t>法人連續偏賣、5日法人明顯賣超</t>
         </is>
       </c>
       <c r="AO329" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、空頭排列、量能溫和放大、接近20日低點、法人連續偏賣、5日法人明顯賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、死亡交叉、量能溫和放大、接近20日低點、法人連續偏賣、5日法人明顯賣超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
@@ -46521,12 +46521,12 @@
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>3673.TW</t>
+          <t>2454.TW</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>TPK-KY</t>
+          <t>聯發科</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
@@ -46535,28 +46535,28 @@
         </is>
       </c>
       <c r="D337" t="n">
-        <v>72.2</v>
+        <v>3660</v>
       </c>
       <c r="E337" t="n">
-        <v>76.42</v>
+        <v>3887</v>
       </c>
       <c r="F337" t="n">
-        <v>78.61</v>
+        <v>4068</v>
       </c>
       <c r="G337" t="n">
-        <v>80.31999999999999</v>
+        <v>4197.25</v>
       </c>
       <c r="H337" t="n">
-        <v>9482750</v>
+        <v>12479607</v>
       </c>
       <c r="I337" t="n">
-        <v>8365839</v>
+        <v>8539021</v>
       </c>
       <c r="J337" t="n">
-        <v>91</v>
+        <v>4785</v>
       </c>
       <c r="K337" t="n">
-        <v>70.2</v>
+        <v>3515</v>
       </c>
       <c r="L337" t="inlineStr">
         <is>
@@ -46564,52 +46564,52 @@
         </is>
       </c>
       <c r="M337" t="n">
-        <v>-2115827</v>
+        <v>-144571</v>
       </c>
       <c r="N337" t="n">
-        <v>-2551944</v>
+        <v>-1826135</v>
       </c>
       <c r="O337" t="n">
-        <v>-2901553</v>
+        <v>-2751340</v>
       </c>
       <c r="P337" t="n">
-        <v>-3645072</v>
+        <v>-5974791</v>
       </c>
       <c r="Q337" t="n">
-        <v>-1883140</v>
+        <v>224947</v>
       </c>
       <c r="R337" t="n">
-        <v>-2141318</v>
+        <v>-1237325</v>
       </c>
       <c r="S337" t="n">
-        <v>-2000431</v>
+        <v>-2093865</v>
       </c>
       <c r="T337" t="n">
-        <v>-2720517</v>
+        <v>-4255511</v>
       </c>
       <c r="U337" t="n">
-        <v>0</v>
+        <v>158853</v>
       </c>
       <c r="V337" t="n">
-        <v>0</v>
+        <v>-187152</v>
       </c>
       <c r="W337" t="n">
-        <v>0</v>
+        <v>239404</v>
       </c>
       <c r="X337" t="n">
-        <v>0</v>
+        <v>-1188343</v>
       </c>
       <c r="Y337" t="n">
-        <v>-232687</v>
+        <v>-528371</v>
       </c>
       <c r="Z337" t="n">
-        <v>-410626</v>
+        <v>-401658</v>
       </c>
       <c r="AA337" t="n">
-        <v>-901122</v>
+        <v>-896879</v>
       </c>
       <c r="AB337" t="n">
-        <v>-924555</v>
+        <v>-530937</v>
       </c>
       <c r="AC337" t="n">
         <v>-40</v>
@@ -46646,12 +46646,12 @@
       </c>
       <c r="AN337" t="inlineStr">
         <is>
-          <t>法人連續偏賣、5日法人明顯賣超</t>
+          <t>法人連續偏賣、5日法人明顯賣超、投信買外資賣</t>
         </is>
       </c>
       <c r="AO337" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、空頭排列、量能溫和放大、接近20日低點、法人連續偏賣、5日法人明顯賣超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、空頭排列、量能溫和放大、接近20日低點、法人連續偏賣、5日法人明顯賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
@@ -47069,12 +47069,12 @@
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>1611.TW</t>
+          <t>2317.TW</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>中電</t>
+          <t>鴻海</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
@@ -47083,28 +47083,28 @@
         </is>
       </c>
       <c r="D341" t="n">
-        <v>12.6</v>
+        <v>235.5</v>
       </c>
       <c r="E341" t="n">
-        <v>13.04</v>
+        <v>236.8</v>
       </c>
       <c r="F341" t="n">
-        <v>13.3</v>
+        <v>240.45</v>
       </c>
       <c r="G341" t="n">
-        <v>13.22</v>
+        <v>250.9</v>
       </c>
       <c r="H341" t="n">
-        <v>1082455</v>
+        <v>48112076</v>
       </c>
       <c r="I341" t="n">
-        <v>785317</v>
+        <v>43172526</v>
       </c>
       <c r="J341" t="n">
-        <v>14.2</v>
+        <v>275.5</v>
       </c>
       <c r="K341" t="n">
-        <v>12.3</v>
+        <v>230</v>
       </c>
       <c r="L341" t="inlineStr">
         <is>
@@ -47112,52 +47112,52 @@
         </is>
       </c>
       <c r="M341" t="n">
-        <v>-610396</v>
+        <v>-4287629</v>
       </c>
       <c r="N341" t="n">
-        <v>-966300</v>
+        <v>-302349</v>
       </c>
       <c r="O341" t="n">
-        <v>-1523935</v>
+        <v>-16369004</v>
       </c>
       <c r="P341" t="n">
-        <v>-1030359</v>
+        <v>-71275320</v>
       </c>
       <c r="Q341" t="n">
-        <v>-636992</v>
+        <v>-7038187</v>
       </c>
       <c r="R341" t="n">
-        <v>-1024952</v>
+        <v>-2474465</v>
       </c>
       <c r="S341" t="n">
-        <v>-1551202</v>
+        <v>-21099789</v>
       </c>
       <c r="T341" t="n">
-        <v>-1056600</v>
+        <v>-77385290</v>
       </c>
       <c r="U341" t="n">
-        <v>0</v>
+        <v>1222065</v>
       </c>
       <c r="V341" t="n">
-        <v>0</v>
+        <v>1277130</v>
       </c>
       <c r="W341" t="n">
-        <v>0</v>
+        <v>4183376</v>
       </c>
       <c r="X341" t="n">
-        <v>0</v>
+        <v>6982979</v>
       </c>
       <c r="Y341" t="n">
-        <v>26596</v>
+        <v>1528493</v>
       </c>
       <c r="Z341" t="n">
-        <v>58652</v>
+        <v>894986</v>
       </c>
       <c r="AA341" t="n">
-        <v>27267</v>
+        <v>547409</v>
       </c>
       <c r="AB341" t="n">
-        <v>26241</v>
+        <v>-873009</v>
       </c>
       <c r="AC341" t="n">
         <v>-40</v>
@@ -47189,29 +47189,29 @@
       </c>
       <c r="AM341" t="inlineStr">
         <is>
-          <t>跌破5日線、死亡交叉、量能溫和放大、接近20日低點</t>
+          <t>跌破5日線、空頭排列、量能溫和放大、接近20日低點</t>
         </is>
       </c>
       <c r="AN341" t="inlineStr">
         <is>
-          <t>法人連續偏賣、5日法人明顯賣超</t>
+          <t>法人連續偏賣、5日法人明顯賣超、投信買外資賣</t>
         </is>
       </c>
       <c r="AO341" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、死亡交叉、量能溫和放大、接近20日低點、法人連續偏賣、5日法人明顯賣超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、空頭排列、量能溫和放大、接近20日低點、法人連續偏賣、5日法人明顯賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>2317.TW</t>
+          <t>2515.TW</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>鴻海</t>
+          <t>中工</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
@@ -47220,28 +47220,28 @@
         </is>
       </c>
       <c r="D342" t="n">
-        <v>235.5</v>
+        <v>13.35</v>
       </c>
       <c r="E342" t="n">
-        <v>236.8</v>
+        <v>13.79</v>
       </c>
       <c r="F342" t="n">
-        <v>240.45</v>
+        <v>13.75</v>
       </c>
       <c r="G342" t="n">
-        <v>250.9</v>
+        <v>13.47</v>
       </c>
       <c r="H342" t="n">
-        <v>48112076</v>
+        <v>9557164</v>
       </c>
       <c r="I342" t="n">
-        <v>43172526</v>
+        <v>11438126</v>
       </c>
       <c r="J342" t="n">
-        <v>275.5</v>
+        <v>15.3</v>
       </c>
       <c r="K342" t="n">
-        <v>230</v>
+        <v>12.8</v>
       </c>
       <c r="L342" t="inlineStr">
         <is>
@@ -47249,64 +47249,64 @@
         </is>
       </c>
       <c r="M342" t="n">
-        <v>-4287629</v>
+        <v>-2214054</v>
       </c>
       <c r="N342" t="n">
-        <v>-302349</v>
+        <v>-6174978</v>
       </c>
       <c r="O342" t="n">
-        <v>-16369004</v>
+        <v>-7546823</v>
       </c>
       <c r="P342" t="n">
-        <v>-71275320</v>
+        <v>9654008</v>
       </c>
       <c r="Q342" t="n">
-        <v>-7038187</v>
+        <v>-2380157</v>
       </c>
       <c r="R342" t="n">
-        <v>-2474465</v>
+        <v>-6180219</v>
       </c>
       <c r="S342" t="n">
-        <v>-21099789</v>
+        <v>-7416380</v>
       </c>
       <c r="T342" t="n">
-        <v>-77385290</v>
+        <v>9321008</v>
       </c>
       <c r="U342" t="n">
-        <v>1222065</v>
+        <v>-6000</v>
       </c>
       <c r="V342" t="n">
-        <v>1277130</v>
+        <v>-9000</v>
       </c>
       <c r="W342" t="n">
-        <v>4183376</v>
+        <v>-9000</v>
       </c>
       <c r="X342" t="n">
-        <v>6982979</v>
+        <v>-16000</v>
       </c>
       <c r="Y342" t="n">
-        <v>1528493</v>
+        <v>172103</v>
       </c>
       <c r="Z342" t="n">
-        <v>894986</v>
+        <v>14241</v>
       </c>
       <c r="AA342" t="n">
-        <v>547409</v>
+        <v>-121443</v>
       </c>
       <c r="AB342" t="n">
-        <v>-873009</v>
+        <v>349000</v>
       </c>
       <c r="AC342" t="n">
-        <v>-40</v>
+        <v>-42</v>
       </c>
       <c r="AD342" t="n">
-        <v>-40</v>
+        <v>-42</v>
       </c>
       <c r="AE342" t="n">
-        <v>-45</v>
+        <v>-5</v>
       </c>
       <c r="AF342" t="n">
-        <v>-55</v>
+        <v>-100</v>
       </c>
       <c r="AG342" t="n">
         <v>0</v>
@@ -47326,17 +47326,17 @@
       </c>
       <c r="AM342" t="inlineStr">
         <is>
-          <t>跌破5日線、空頭排列、量能溫和放大、接近20日低點</t>
+          <t>跌破5日線、多頭排列、量能未放大、接近20日低點</t>
         </is>
       </c>
       <c r="AN342" t="inlineStr">
         <is>
-          <t>法人連續偏賣、5日法人明顯賣超、投信買外資賣</t>
+          <t>法人連續偏賣、中期買超轉短線賣壓、5日法人明顯賣超、外資投信同步賣超</t>
         </is>
       </c>
       <c r="AO342" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、空頭排列、量能溫和放大、接近20日低點、法人連續偏賣、5日法人明顯賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、多頭排列、量能未放大、接近20日低點、法人連續偏賣、中期買超轉短線賣壓、5日法人明顯賣超、外資投信同步賣超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
@@ -47480,12 +47480,12 @@
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>2515.TW</t>
+          <t>2731.TW</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>中工</t>
+          <t>雄獅</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
@@ -47494,28 +47494,28 @@
         </is>
       </c>
       <c r="D344" t="n">
-        <v>13.35</v>
+        <v>144.5</v>
       </c>
       <c r="E344" t="n">
-        <v>13.79</v>
+        <v>145.9</v>
       </c>
       <c r="F344" t="n">
-        <v>13.75</v>
+        <v>147.7</v>
       </c>
       <c r="G344" t="n">
-        <v>13.47</v>
+        <v>149.43</v>
       </c>
       <c r="H344" t="n">
-        <v>9557164</v>
+        <v>615293</v>
       </c>
       <c r="I344" t="n">
-        <v>11438126</v>
+        <v>726889</v>
       </c>
       <c r="J344" t="n">
-        <v>15.3</v>
+        <v>155</v>
       </c>
       <c r="K344" t="n">
-        <v>12.8</v>
+        <v>143.5</v>
       </c>
       <c r="L344" t="inlineStr">
         <is>
@@ -47523,52 +47523,52 @@
         </is>
       </c>
       <c r="M344" t="n">
-        <v>-2214054</v>
+        <v>105036</v>
       </c>
       <c r="N344" t="n">
-        <v>-6174978</v>
+        <v>-280249</v>
       </c>
       <c r="O344" t="n">
-        <v>-7546823</v>
+        <v>-852224</v>
       </c>
       <c r="P344" t="n">
-        <v>9654008</v>
+        <v>-696821</v>
       </c>
       <c r="Q344" t="n">
-        <v>-2380157</v>
+        <v>99036</v>
       </c>
       <c r="R344" t="n">
-        <v>-6180219</v>
+        <v>-273964</v>
       </c>
       <c r="S344" t="n">
-        <v>-7416380</v>
+        <v>-846897</v>
       </c>
       <c r="T344" t="n">
-        <v>9321008</v>
+        <v>-854707</v>
       </c>
       <c r="U344" t="n">
-        <v>-6000</v>
+        <v>0</v>
       </c>
       <c r="V344" t="n">
-        <v>-9000</v>
+        <v>-2266</v>
       </c>
       <c r="W344" t="n">
-        <v>-9000</v>
+        <v>-4539</v>
       </c>
       <c r="X344" t="n">
-        <v>-16000</v>
+        <v>177319</v>
       </c>
       <c r="Y344" t="n">
-        <v>172103</v>
+        <v>6000</v>
       </c>
       <c r="Z344" t="n">
-        <v>14241</v>
+        <v>-4019</v>
       </c>
       <c r="AA344" t="n">
-        <v>-121443</v>
+        <v>-788</v>
       </c>
       <c r="AB344" t="n">
-        <v>349000</v>
+        <v>-19433</v>
       </c>
       <c r="AC344" t="n">
         <v>-42</v>
@@ -47577,10 +47577,10 @@
         <v>-42</v>
       </c>
       <c r="AE344" t="n">
-        <v>-5</v>
+        <v>-55</v>
       </c>
       <c r="AF344" t="n">
-        <v>-100</v>
+        <v>-50</v>
       </c>
       <c r="AG344" t="n">
         <v>0</v>
@@ -47600,29 +47600,29 @@
       </c>
       <c r="AM344" t="inlineStr">
         <is>
-          <t>跌破5日線、多頭排列、量能未放大、接近20日低點</t>
+          <t>跌破5日線、空頭排列、量能未放大、接近20日低點</t>
         </is>
       </c>
       <c r="AN344" t="inlineStr">
         <is>
-          <t>法人連續偏賣、中期買超轉短線賣壓、5日法人明顯賣超、外資投信同步賣超</t>
+          <t>5日法人明顯賣超、外資投信同步賣超</t>
         </is>
       </c>
       <c r="AO344" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、多頭排列、量能未放大、接近20日低點、法人連續偏賣、中期買超轉短線賣壓、5日法人明顯賣超、外資投信同步賣超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、空頭排列、量能未放大、接近20日低點、5日法人明顯賣超、外資投信同步賣超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>2731.TW</t>
+          <t>1802.TW</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>雄獅</t>
+          <t>台玻</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
@@ -47631,28 +47631,28 @@
         </is>
       </c>
       <c r="D345" t="n">
-        <v>144.5</v>
+        <v>62.3</v>
       </c>
       <c r="E345" t="n">
-        <v>145.9</v>
+        <v>64.42</v>
       </c>
       <c r="F345" t="n">
-        <v>147.7</v>
+        <v>67.51000000000001</v>
       </c>
       <c r="G345" t="n">
-        <v>149.43</v>
+        <v>68.53</v>
       </c>
       <c r="H345" t="n">
-        <v>615293</v>
+        <v>48558539</v>
       </c>
       <c r="I345" t="n">
-        <v>726889</v>
+        <v>43514781</v>
       </c>
       <c r="J345" t="n">
-        <v>155</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="K345" t="n">
-        <v>143.5</v>
+        <v>58.4</v>
       </c>
       <c r="L345" t="inlineStr">
         <is>
@@ -47660,64 +47660,64 @@
         </is>
       </c>
       <c r="M345" t="n">
-        <v>105036</v>
+        <v>-10020511</v>
       </c>
       <c r="N345" t="n">
-        <v>-280249</v>
+        <v>-18908156</v>
       </c>
       <c r="O345" t="n">
-        <v>-852224</v>
+        <v>-36977966</v>
       </c>
       <c r="P345" t="n">
-        <v>-696821</v>
+        <v>-18628631</v>
       </c>
       <c r="Q345" t="n">
-        <v>99036</v>
+        <v>-8967455</v>
       </c>
       <c r="R345" t="n">
-        <v>-273964</v>
+        <v>-17405195</v>
       </c>
       <c r="S345" t="n">
-        <v>-846897</v>
+        <v>-35028381</v>
       </c>
       <c r="T345" t="n">
-        <v>-854707</v>
+        <v>-16553247</v>
       </c>
       <c r="U345" t="n">
-        <v>0</v>
+        <v>-6000</v>
       </c>
       <c r="V345" t="n">
-        <v>-2266</v>
+        <v>-168000</v>
       </c>
       <c r="W345" t="n">
-        <v>-4539</v>
+        <v>-168000</v>
       </c>
       <c r="X345" t="n">
-        <v>177319</v>
+        <v>-927000</v>
       </c>
       <c r="Y345" t="n">
-        <v>6000</v>
+        <v>-1047056</v>
       </c>
       <c r="Z345" t="n">
-        <v>-4019</v>
+        <v>-1334961</v>
       </c>
       <c r="AA345" t="n">
-        <v>-788</v>
+        <v>-1781585</v>
       </c>
       <c r="AB345" t="n">
-        <v>-19433</v>
+        <v>-1148384</v>
       </c>
       <c r="AC345" t="n">
-        <v>-42</v>
+        <v>-44</v>
       </c>
       <c r="AD345" t="n">
-        <v>-42</v>
+        <v>-44</v>
       </c>
       <c r="AE345" t="n">
-        <v>-55</v>
+        <v>-35</v>
       </c>
       <c r="AF345" t="n">
-        <v>-50</v>
+        <v>-75</v>
       </c>
       <c r="AG345" t="n">
         <v>0</v>
@@ -47737,17 +47737,17 @@
       </c>
       <c r="AM345" t="inlineStr">
         <is>
-          <t>跌破5日線、空頭排列、量能未放大、接近20日低點</t>
+          <t>跌破5日線、空頭排列、量能溫和放大</t>
         </is>
       </c>
       <c r="AN345" t="inlineStr">
         <is>
-          <t>5日法人明顯賣超、外資投信同步賣超</t>
+          <t>法人連續偏賣、5日法人明顯賣超、外資投信同步賣超</t>
         </is>
       </c>
       <c r="AO345" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、空頭排列、量能未放大、接近20日低點、5日法人明顯賣超、外資投信同步賣超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、空頭排列、量能溫和放大、法人連續偏賣、5日法人明顯賣超、外資投信同步賣超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
@@ -47891,12 +47891,12 @@
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>1802.TW</t>
+          <t>2420.TW</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>台玻</t>
+          <t>新巨</t>
         </is>
       </c>
       <c r="C347" t="inlineStr">
@@ -47905,28 +47905,28 @@
         </is>
       </c>
       <c r="D347" t="n">
-        <v>62.3</v>
+        <v>59.6</v>
       </c>
       <c r="E347" t="n">
-        <v>64.42</v>
+        <v>60.32</v>
       </c>
       <c r="F347" t="n">
-        <v>67.51000000000001</v>
+        <v>60.86</v>
       </c>
       <c r="G347" t="n">
-        <v>68.53</v>
+        <v>60.95</v>
       </c>
       <c r="H347" t="n">
-        <v>48558539</v>
+        <v>814388</v>
       </c>
       <c r="I347" t="n">
-        <v>43514781</v>
+        <v>470387</v>
       </c>
       <c r="J347" t="n">
-        <v>78.40000000000001</v>
+        <v>65</v>
       </c>
       <c r="K347" t="n">
-        <v>58.4</v>
+        <v>58</v>
       </c>
       <c r="L347" t="inlineStr">
         <is>
@@ -47934,52 +47934,52 @@
         </is>
       </c>
       <c r="M347" t="n">
-        <v>-10020511</v>
+        <v>-141773</v>
       </c>
       <c r="N347" t="n">
-        <v>-18908156</v>
+        <v>-51138</v>
       </c>
       <c r="O347" t="n">
-        <v>-36977966</v>
+        <v>-221893</v>
       </c>
       <c r="P347" t="n">
-        <v>-18628631</v>
+        <v>38591</v>
       </c>
       <c r="Q347" t="n">
-        <v>-8967455</v>
+        <v>-195301</v>
       </c>
       <c r="R347" t="n">
-        <v>-17405195</v>
+        <v>-135281</v>
       </c>
       <c r="S347" t="n">
-        <v>-35028381</v>
+        <v>-308238</v>
       </c>
       <c r="T347" t="n">
-        <v>-16553247</v>
+        <v>59017</v>
       </c>
       <c r="U347" t="n">
-        <v>-6000</v>
+        <v>0</v>
       </c>
       <c r="V347" t="n">
-        <v>-168000</v>
+        <v>0</v>
       </c>
       <c r="W347" t="n">
-        <v>-168000</v>
+        <v>0</v>
       </c>
       <c r="X347" t="n">
-        <v>-927000</v>
+        <v>-151452</v>
       </c>
       <c r="Y347" t="n">
-        <v>-1047056</v>
+        <v>53528</v>
       </c>
       <c r="Z347" t="n">
-        <v>-1334961</v>
+        <v>84143</v>
       </c>
       <c r="AA347" t="n">
-        <v>-1781585</v>
+        <v>86345</v>
       </c>
       <c r="AB347" t="n">
-        <v>-1148384</v>
+        <v>131026</v>
       </c>
       <c r="AC347" t="n">
         <v>-44</v>
@@ -47988,10 +47988,10 @@
         <v>-44</v>
       </c>
       <c r="AE347" t="n">
-        <v>-35</v>
+        <v>-40</v>
       </c>
       <c r="AF347" t="n">
-        <v>-75</v>
+        <v>-70</v>
       </c>
       <c r="AG347" t="n">
         <v>0</v>
@@ -48011,29 +48011,29 @@
       </c>
       <c r="AM347" t="inlineStr">
         <is>
-          <t>跌破5日線、空頭排列、量能溫和放大</t>
+          <t>跌破5日線、空頭排列、成交量放大、接近20日低點</t>
         </is>
       </c>
       <c r="AN347" t="inlineStr">
         <is>
-          <t>法人連續偏賣、5日法人明顯賣超、外資投信同步賣超</t>
+          <t>法人連續偏賣、中期買超轉短線賣壓、5日法人賣超</t>
         </is>
       </c>
       <c r="AO347" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、空頭排列、量能溫和放大、法人連續偏賣、5日法人明顯賣超、外資投信同步賣超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、空頭排列、成交量放大、接近20日低點、法人連續偏賣、中期買超轉短線賣壓、5日法人賣超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>2420.TW</t>
+          <t>2428.TW</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>新巨</t>
+          <t>興勤</t>
         </is>
       </c>
       <c r="C348" t="inlineStr">
@@ -48042,28 +48042,28 @@
         </is>
       </c>
       <c r="D348" t="n">
-        <v>59.6</v>
+        <v>291</v>
       </c>
       <c r="E348" t="n">
-        <v>60.32</v>
+        <v>304.4</v>
       </c>
       <c r="F348" t="n">
-        <v>60.86</v>
+        <v>313.75</v>
       </c>
       <c r="G348" t="n">
-        <v>60.95</v>
+        <v>308.07</v>
       </c>
       <c r="H348" t="n">
-        <v>814388</v>
+        <v>2227926</v>
       </c>
       <c r="I348" t="n">
-        <v>470387</v>
+        <v>2993493</v>
       </c>
       <c r="J348" t="n">
-        <v>65</v>
+        <v>363.5</v>
       </c>
       <c r="K348" t="n">
-        <v>58</v>
+        <v>279</v>
       </c>
       <c r="L348" t="inlineStr">
         <is>
@@ -48071,52 +48071,52 @@
         </is>
       </c>
       <c r="M348" t="n">
-        <v>-141773</v>
+        <v>195350</v>
       </c>
       <c r="N348" t="n">
-        <v>-51138</v>
+        <v>-102735</v>
       </c>
       <c r="O348" t="n">
-        <v>-221893</v>
+        <v>-1476799</v>
       </c>
       <c r="P348" t="n">
-        <v>38591</v>
+        <v>506210</v>
       </c>
       <c r="Q348" t="n">
-        <v>-195301</v>
+        <v>202158</v>
       </c>
       <c r="R348" t="n">
-        <v>-135281</v>
+        <v>-80022</v>
       </c>
       <c r="S348" t="n">
-        <v>-308238</v>
+        <v>-1918885</v>
       </c>
       <c r="T348" t="n">
-        <v>59017</v>
+        <v>-1159265</v>
       </c>
       <c r="U348" t="n">
         <v>0</v>
       </c>
       <c r="V348" t="n">
-        <v>0</v>
+        <v>-1000</v>
       </c>
       <c r="W348" t="n">
-        <v>0</v>
+        <v>499000</v>
       </c>
       <c r="X348" t="n">
-        <v>-151452</v>
+        <v>1699000</v>
       </c>
       <c r="Y348" t="n">
-        <v>53528</v>
+        <v>-6808</v>
       </c>
       <c r="Z348" t="n">
-        <v>84143</v>
+        <v>-21713</v>
       </c>
       <c r="AA348" t="n">
-        <v>86345</v>
+        <v>-56914</v>
       </c>
       <c r="AB348" t="n">
-        <v>131026</v>
+        <v>-33525</v>
       </c>
       <c r="AC348" t="n">
         <v>-44</v>
@@ -48125,10 +48125,10 @@
         <v>-44</v>
       </c>
       <c r="AE348" t="n">
-        <v>-40</v>
+        <v>-55</v>
       </c>
       <c r="AF348" t="n">
-        <v>-70</v>
+        <v>-55</v>
       </c>
       <c r="AG348" t="n">
         <v>0</v>
@@ -48148,17 +48148,17 @@
       </c>
       <c r="AM348" t="inlineStr">
         <is>
-          <t>跌破5日線、空頭排列、成交量放大、接近20日低點</t>
+          <t>跌破5日線、死亡交叉、量能未放大、接近20日低點</t>
         </is>
       </c>
       <c r="AN348" t="inlineStr">
         <is>
-          <t>法人連續偏賣、中期買超轉短線賣壓、5日法人賣超</t>
+          <t>中期買超轉短線賣壓、5日法人明顯賣超、投信買外資賣</t>
         </is>
       </c>
       <c r="AO348" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、空頭排列、成交量放大、接近20日低點、法人連續偏賣、中期買超轉短線賣壓、5日法人賣超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、死亡交叉、量能未放大、接近20日低點、中期買超轉短線賣壓、5日法人明顯賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>

--- a/output/universe_analysis_result.xlsx
+++ b/output/universe_analysis_result.xlsx
@@ -900,12 +900,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2867.TW</t>
+          <t>2206.TW</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>三商壽</t>
+          <t>三陽工業</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -914,96 +914,96 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>9.23</v>
+        <v>64.8</v>
       </c>
       <c r="E4" t="n">
-        <v>8.960000000000001</v>
+        <v>64</v>
       </c>
       <c r="F4" t="n">
-        <v>8.880000000000001</v>
+        <v>63.93</v>
       </c>
       <c r="G4" t="n">
-        <v>8.69</v>
+        <v>62.75</v>
       </c>
       <c r="H4" t="n">
-        <v>28061764</v>
+        <v>4242994</v>
       </c>
       <c r="I4" t="n">
-        <v>21620528</v>
+        <v>1775743</v>
       </c>
       <c r="J4" t="n">
-        <v>9.23</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="K4" t="n">
-        <v>8.25</v>
+        <v>60.2</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>無明顯異常</t>
+          <t>帶量突破20日高點</t>
         </is>
       </c>
       <c r="M4" t="n">
-        <v>8514700</v>
+        <v>205690</v>
       </c>
       <c r="N4" t="n">
-        <v>42355700</v>
+        <v>211692</v>
       </c>
       <c r="O4" t="n">
-        <v>55130600</v>
+        <v>139722</v>
       </c>
       <c r="P4" t="n">
-        <v>86177825</v>
+        <v>1632212</v>
       </c>
       <c r="Q4" t="n">
-        <v>6218700</v>
+        <v>-193310</v>
       </c>
       <c r="R4" t="n">
-        <v>38763700</v>
+        <v>-384308</v>
       </c>
       <c r="S4" t="n">
-        <v>49231600</v>
+        <v>-744278</v>
       </c>
       <c r="T4" t="n">
-        <v>77493825</v>
+        <v>-159788</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>375000</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>601000</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>879000</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>1786000</v>
       </c>
       <c r="Y4" t="n">
-        <v>2296000</v>
+        <v>24000</v>
       </c>
       <c r="Z4" t="n">
-        <v>3592000</v>
+        <v>-5000</v>
       </c>
       <c r="AA4" t="n">
-        <v>5899000</v>
+        <v>5000</v>
       </c>
       <c r="AB4" t="n">
-        <v>8684000</v>
+        <v>6000</v>
       </c>
       <c r="AC4" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="AD4" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="AE4" t="n">
         <v>80</v>
       </c>
       <c r="AF4" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AH4" t="inlineStr"/>
       <c r="AI4" t="inlineStr"/>
@@ -1020,29 +1020,29 @@
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、量能溫和放大、突破20日高點</t>
+          <t>站上5日線、多頭排列、爆量、接近20日高點、帶量突破20日高點</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>法人連續偏買、5日法人明顯買超</t>
+          <t>法人連續偏買、5日法人買超、投信買外資賣</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>偏多觀察：站上5日線、多頭排列、量能溫和放大、突破20日高點、法人連續偏買、5日法人明顯買超。條件不差，適合等待拉回或突破確認。</t>
+          <t>偏多觀察：站上5日線、多頭排列、爆量、接近20日高點、帶量突破20日高點、法人連續偏買、5日法人買超、投信買外資賣。條件不差，適合等待拉回或突破確認。</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2546.TW</t>
+          <t>2867.TW</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>根基</t>
+          <t>三商壽</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1051,28 +1051,28 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>96.90000000000001</v>
+        <v>9.23</v>
       </c>
       <c r="E5" t="n">
-        <v>95.64</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="F5" t="n">
-        <v>94.39</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="G5" t="n">
-        <v>93.95</v>
+        <v>8.69</v>
       </c>
       <c r="H5" t="n">
-        <v>232600</v>
+        <v>28061764</v>
       </c>
       <c r="I5" t="n">
-        <v>209553</v>
+        <v>21620528</v>
       </c>
       <c r="J5" t="n">
-        <v>97.7</v>
+        <v>9.23</v>
       </c>
       <c r="K5" t="n">
-        <v>91.40000000000001</v>
+        <v>8.25</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
@@ -1080,52 +1080,52 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>39200</v>
+        <v>8514700</v>
       </c>
       <c r="N5" t="n">
-        <v>213135</v>
+        <v>42355700</v>
       </c>
       <c r="O5" t="n">
-        <v>284137</v>
+        <v>55130600</v>
       </c>
       <c r="P5" t="n">
-        <v>242753</v>
+        <v>86177825</v>
       </c>
       <c r="Q5" t="n">
-        <v>37200</v>
+        <v>6218700</v>
       </c>
       <c r="R5" t="n">
-        <v>136135</v>
+        <v>38763700</v>
       </c>
       <c r="S5" t="n">
-        <v>177137</v>
+        <v>49231600</v>
       </c>
       <c r="T5" t="n">
-        <v>139753</v>
+        <v>77493825</v>
       </c>
       <c r="U5" t="n">
         <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>65000</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>65000</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>65000</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>2000</v>
+        <v>2296000</v>
       </c>
       <c r="Z5" t="n">
-        <v>12000</v>
+        <v>3592000</v>
       </c>
       <c r="AA5" t="n">
-        <v>42000</v>
+        <v>5899000</v>
       </c>
       <c r="AB5" t="n">
-        <v>38000</v>
+        <v>8684000</v>
       </c>
       <c r="AC5" t="n">
         <v>56</v>
@@ -1134,10 +1134,10 @@
         <v>56</v>
       </c>
       <c r="AE5" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="AF5" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="AG5" t="n">
         <v>0</v>
@@ -1157,29 +1157,29 @@
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、量能溫和放大、接近20日高點</t>
+          <t>站上5日線、多頭排列、量能溫和放大、突破20日高點</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>法人連續偏買、5日法人買超、外資投信同步買超</t>
+          <t>法人連續偏買、5日法人明顯買超</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>偏多觀察：站上5日線、多頭排列、量能溫和放大、接近20日高點、法人連續偏買、5日法人買超、外資投信同步買超。條件不差，適合等待拉回或突破確認。</t>
+          <t>偏多觀察：站上5日線、多頭排列、量能溫和放大、突破20日高點、法人連續偏買、5日法人明顯買超。條件不差，適合等待拉回或突破確認。</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2206.TW</t>
+          <t>2546.TW</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>三陽工業</t>
+          <t>根基</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1188,96 +1188,96 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>64.8</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="E6" t="n">
-        <v>64</v>
+        <v>95.64</v>
       </c>
       <c r="F6" t="n">
-        <v>63.93</v>
+        <v>94.39</v>
       </c>
       <c r="G6" t="n">
-        <v>62.75</v>
+        <v>93.95</v>
       </c>
       <c r="H6" t="n">
-        <v>2711994</v>
+        <v>232600</v>
       </c>
       <c r="I6" t="n">
-        <v>1469543</v>
+        <v>209553</v>
       </c>
       <c r="J6" t="n">
-        <v>65.09999999999999</v>
+        <v>97.7</v>
       </c>
       <c r="K6" t="n">
-        <v>60.2</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>帶量突破20日高點</t>
+          <t>無明顯異常</t>
         </is>
       </c>
       <c r="M6" t="n">
-        <v>205690</v>
+        <v>39200</v>
       </c>
       <c r="N6" t="n">
-        <v>211692</v>
+        <v>213135</v>
       </c>
       <c r="O6" t="n">
-        <v>139722</v>
+        <v>284137</v>
       </c>
       <c r="P6" t="n">
-        <v>1632212</v>
+        <v>242753</v>
       </c>
       <c r="Q6" t="n">
-        <v>-193310</v>
+        <v>37200</v>
       </c>
       <c r="R6" t="n">
-        <v>-384308</v>
+        <v>136135</v>
       </c>
       <c r="S6" t="n">
-        <v>-744278</v>
+        <v>177137</v>
       </c>
       <c r="T6" t="n">
-        <v>-159788</v>
+        <v>139753</v>
       </c>
       <c r="U6" t="n">
-        <v>375000</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>601000</v>
+        <v>65000</v>
       </c>
       <c r="W6" t="n">
-        <v>879000</v>
+        <v>65000</v>
       </c>
       <c r="X6" t="n">
-        <v>1786000</v>
+        <v>65000</v>
       </c>
       <c r="Y6" t="n">
-        <v>24000</v>
+        <v>2000</v>
       </c>
       <c r="Z6" t="n">
-        <v>-5000</v>
+        <v>12000</v>
       </c>
       <c r="AA6" t="n">
-        <v>5000</v>
+        <v>42000</v>
       </c>
       <c r="AB6" t="n">
-        <v>6000</v>
+        <v>38000</v>
       </c>
       <c r="AC6" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="AD6" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="AE6" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AF6" t="n">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="AG6" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="inlineStr"/>
       <c r="AI6" t="inlineStr"/>
@@ -1294,17 +1294,17 @@
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、成交量放大、接近20日高點、帶量突破20日高點</t>
+          <t>站上5日線、多頭排列、量能溫和放大、接近20日高點</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>法人連續偏買、5日法人買超、投信買外資賣</t>
+          <t>法人連續偏買、5日法人買超、外資投信同步買超</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>偏多觀察：站上5日線、多頭排列、成交量放大、接近20日高點、帶量突破20日高點、法人連續偏買、5日法人買超、投信買外資賣。條件不差，適合等待拉回或突破確認。</t>
+          <t>偏多觀察：站上5日線、多頭排列、量能溫和放大、接近20日高點、法人連續偏買、5日法人買超、外資投信同步買超。條件不差，適合等待拉回或突破確認。</t>
         </is>
       </c>
     </row>
@@ -3503,12 +3503,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2610.TW</t>
+          <t>2105.TW</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>華航</t>
+          <t>正新</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -3517,28 +3517,28 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>23.7</v>
+        <v>33.2</v>
       </c>
       <c r="E23" t="n">
-        <v>23.49</v>
+        <v>33.17</v>
       </c>
       <c r="F23" t="n">
-        <v>22.66</v>
+        <v>32.83</v>
       </c>
       <c r="G23" t="n">
-        <v>21.26</v>
+        <v>31.5</v>
       </c>
       <c r="H23" t="n">
-        <v>80188846</v>
+        <v>12767361</v>
       </c>
       <c r="I23" t="n">
-        <v>99569272</v>
+        <v>15651988</v>
       </c>
       <c r="J23" t="n">
-        <v>24.75</v>
+        <v>34.6</v>
       </c>
       <c r="K23" t="n">
-        <v>18.9</v>
+        <v>29.05</v>
       </c>
       <c r="L23" t="inlineStr">
         <is>
@@ -3546,52 +3546,52 @@
         </is>
       </c>
       <c r="M23" t="n">
-        <v>7409917</v>
+        <v>2206031</v>
       </c>
       <c r="N23" t="n">
-        <v>16616990</v>
+        <v>21516776</v>
       </c>
       <c r="O23" t="n">
-        <v>16028265</v>
+        <v>28059439</v>
       </c>
       <c r="P23" t="n">
-        <v>28255752</v>
+        <v>50316161</v>
       </c>
       <c r="Q23" t="n">
-        <v>1435561</v>
+        <v>4341307</v>
       </c>
       <c r="R23" t="n">
-        <v>17041423</v>
+        <v>31061921</v>
       </c>
       <c r="S23" t="n">
-        <v>46509284</v>
+        <v>36319835</v>
       </c>
       <c r="T23" t="n">
-        <v>55652435</v>
+        <v>56999712</v>
       </c>
       <c r="U23" t="n">
-        <v>6164000</v>
+        <v>-3163113</v>
       </c>
       <c r="V23" t="n">
-        <v>217825</v>
+        <v>-9836678</v>
       </c>
       <c r="W23" t="n">
-        <v>-29199625</v>
+        <v>-9531597</v>
       </c>
       <c r="X23" t="n">
-        <v>-24572118</v>
+        <v>-9419817</v>
       </c>
       <c r="Y23" t="n">
-        <v>-189644</v>
+        <v>1027837</v>
       </c>
       <c r="Z23" t="n">
-        <v>-642258</v>
+        <v>291533</v>
       </c>
       <c r="AA23" t="n">
-        <v>-1281394</v>
+        <v>1271201</v>
       </c>
       <c r="AB23" t="n">
-        <v>-2824565</v>
+        <v>2736266</v>
       </c>
       <c r="AC23" t="n">
         <v>42</v>
@@ -3777,12 +3777,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2105.TW</t>
+          <t>2015.TW</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>正新</t>
+          <t>豐興</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -3791,28 +3791,28 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>33.2</v>
+        <v>63.7</v>
       </c>
       <c r="E25" t="n">
-        <v>33.17</v>
+        <v>63.76</v>
       </c>
       <c r="F25" t="n">
-        <v>32.83</v>
+        <v>62.94</v>
       </c>
       <c r="G25" t="n">
-        <v>31.5</v>
+        <v>61.98</v>
       </c>
       <c r="H25" t="n">
-        <v>12767361</v>
+        <v>211770</v>
       </c>
       <c r="I25" t="n">
-        <v>15651988</v>
+        <v>348980</v>
       </c>
       <c r="J25" t="n">
-        <v>34.6</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="K25" t="n">
-        <v>29.05</v>
+        <v>60.2</v>
       </c>
       <c r="L25" t="inlineStr">
         <is>
@@ -3820,64 +3820,64 @@
         </is>
       </c>
       <c r="M25" t="n">
-        <v>2206031</v>
+        <v>32700</v>
       </c>
       <c r="N25" t="n">
-        <v>21516776</v>
+        <v>406626</v>
       </c>
       <c r="O25" t="n">
-        <v>28059439</v>
+        <v>962838</v>
       </c>
       <c r="P25" t="n">
-        <v>50316161</v>
+        <v>1515092</v>
       </c>
       <c r="Q25" t="n">
-        <v>4341307</v>
+        <v>10700</v>
       </c>
       <c r="R25" t="n">
-        <v>31061921</v>
+        <v>270626</v>
       </c>
       <c r="S25" t="n">
-        <v>36319835</v>
+        <v>811838</v>
       </c>
       <c r="T25" t="n">
-        <v>56999712</v>
+        <v>1410092</v>
       </c>
       <c r="U25" t="n">
-        <v>-3163113</v>
+        <v>4000</v>
       </c>
       <c r="V25" t="n">
-        <v>-9836678</v>
+        <v>109000</v>
       </c>
       <c r="W25" t="n">
-        <v>-9531597</v>
+        <v>109000</v>
       </c>
       <c r="X25" t="n">
-        <v>-9419817</v>
+        <v>80000</v>
       </c>
       <c r="Y25" t="n">
-        <v>1027837</v>
+        <v>18000</v>
       </c>
       <c r="Z25" t="n">
-        <v>291533</v>
+        <v>27000</v>
       </c>
       <c r="AA25" t="n">
-        <v>1271201</v>
+        <v>42000</v>
       </c>
       <c r="AB25" t="n">
-        <v>2736266</v>
+        <v>25000</v>
       </c>
       <c r="AC25" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AD25" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AE25" t="n">
-        <v>45</v>
+        <v>20</v>
       </c>
       <c r="AF25" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="AG25" t="n">
         <v>0</v>
@@ -3897,29 +3897,29 @@
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、量能未放大</t>
+          <t>跌破5日線、多頭排列、量能未放大、接近20日高點</t>
         </is>
       </c>
       <c r="AN25" t="inlineStr">
         <is>
-          <t>法人連續偏買、5日法人明顯買超、外資買投信賣</t>
+          <t>法人連續偏買、5日法人明顯買超、外資投信同步買超</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>整理觀察：站上5日線、多頭排列、量能未放大、法人連續偏買、5日法人明顯買超、外資買投信賣。多空訊號混合，建議降低追價衝動。</t>
+          <t>整理觀察：跌破5日線、多頭排列、量能未放大、接近20日高點、法人連續偏買、5日法人明顯買超、外資投信同步買超。多空訊號混合，建議降低追價衝動。</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2015.TW</t>
+          <t>1231.TW</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>豐興</t>
+          <t>聯華食</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -3928,28 +3928,28 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>63.7</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="E26" t="n">
-        <v>63.76</v>
+        <v>89.42</v>
       </c>
       <c r="F26" t="n">
-        <v>62.94</v>
+        <v>88.41</v>
       </c>
       <c r="G26" t="n">
-        <v>61.98</v>
+        <v>88.09</v>
       </c>
       <c r="H26" t="n">
-        <v>211770</v>
+        <v>455900</v>
       </c>
       <c r="I26" t="n">
-        <v>348980</v>
+        <v>626116</v>
       </c>
       <c r="J26" t="n">
-        <v>64.59999999999999</v>
+        <v>93</v>
       </c>
       <c r="K26" t="n">
-        <v>60.2</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="L26" t="inlineStr">
         <is>
@@ -3957,64 +3957,64 @@
         </is>
       </c>
       <c r="M26" t="n">
-        <v>32700</v>
+        <v>92201</v>
       </c>
       <c r="N26" t="n">
-        <v>406626</v>
+        <v>464911</v>
       </c>
       <c r="O26" t="n">
-        <v>962838</v>
+        <v>435762</v>
       </c>
       <c r="P26" t="n">
-        <v>1515092</v>
+        <v>-88195</v>
       </c>
       <c r="Q26" t="n">
-        <v>10700</v>
+        <v>82558</v>
       </c>
       <c r="R26" t="n">
-        <v>270626</v>
+        <v>451649</v>
       </c>
       <c r="S26" t="n">
-        <v>811838</v>
+        <v>419649</v>
       </c>
       <c r="T26" t="n">
-        <v>1410092</v>
+        <v>-105895</v>
       </c>
       <c r="U26" t="n">
-        <v>4000</v>
+        <v>0</v>
       </c>
       <c r="V26" t="n">
-        <v>109000</v>
+        <v>-1000</v>
       </c>
       <c r="W26" t="n">
-        <v>109000</v>
+        <v>-2000</v>
       </c>
       <c r="X26" t="n">
-        <v>80000</v>
+        <v>-4000</v>
       </c>
       <c r="Y26" t="n">
-        <v>18000</v>
+        <v>9643</v>
       </c>
       <c r="Z26" t="n">
-        <v>27000</v>
+        <v>14262</v>
       </c>
       <c r="AA26" t="n">
-        <v>42000</v>
+        <v>18113</v>
       </c>
       <c r="AB26" t="n">
-        <v>25000</v>
+        <v>21700</v>
       </c>
       <c r="AC26" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AD26" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AE26" t="n">
-        <v>20</v>
+        <v>45</v>
       </c>
       <c r="AF26" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="AG26" t="n">
         <v>0</v>
@@ -4034,17 +4034,17 @@
       </c>
       <c r="AM26" t="inlineStr">
         <is>
-          <t>跌破5日線、多頭排列、量能未放大、接近20日高點</t>
+          <t>站上5日線、多頭排列、量能未放大</t>
         </is>
       </c>
       <c r="AN26" t="inlineStr">
         <is>
-          <t>法人連續偏買、5日法人明顯買超、外資投信同步買超</t>
+          <t>法人連續偏買、5日法人買超、外資買投信賣</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>整理觀察：跌破5日線、多頭排列、量能未放大、接近20日高點、法人連續偏買、5日法人明顯買超、外資投信同步買超。多空訊號混合，建議降低追價衝動。</t>
+          <t>整理觀察：站上5日線、多頭排列、量能未放大、法人連續偏買、5日法人買超、外資買投信賣。多空訊號混合，建議降低追價衝動。</t>
         </is>
       </c>
     </row>
@@ -4188,12 +4188,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>1231.TW</t>
+          <t>2608.TW</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>聯華食</t>
+          <t>嘉里大榮</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -4202,28 +4202,28 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>90.59999999999999</v>
+        <v>29.35</v>
       </c>
       <c r="E28" t="n">
-        <v>89.42</v>
+        <v>29.32</v>
       </c>
       <c r="F28" t="n">
-        <v>88.41</v>
+        <v>29.32</v>
       </c>
       <c r="G28" t="n">
-        <v>88.09</v>
+        <v>29.13</v>
       </c>
       <c r="H28" t="n">
-        <v>455900</v>
+        <v>366191</v>
       </c>
       <c r="I28" t="n">
-        <v>626116</v>
+        <v>264994</v>
       </c>
       <c r="J28" t="n">
-        <v>93</v>
+        <v>29.7</v>
       </c>
       <c r="K28" t="n">
-        <v>85.09999999999999</v>
+        <v>28.6</v>
       </c>
       <c r="L28" t="inlineStr">
         <is>
@@ -4231,52 +4231,52 @@
         </is>
       </c>
       <c r="M28" t="n">
-        <v>92201</v>
+        <v>215800</v>
       </c>
       <c r="N28" t="n">
-        <v>464911</v>
+        <v>556882</v>
       </c>
       <c r="O28" t="n">
-        <v>435762</v>
+        <v>749363</v>
       </c>
       <c r="P28" t="n">
-        <v>-88195</v>
+        <v>868328</v>
       </c>
       <c r="Q28" t="n">
-        <v>82558</v>
+        <v>197800</v>
       </c>
       <c r="R28" t="n">
-        <v>451649</v>
+        <v>514882</v>
       </c>
       <c r="S28" t="n">
-        <v>419649</v>
+        <v>716882</v>
       </c>
       <c r="T28" t="n">
-        <v>-105895</v>
+        <v>832847</v>
       </c>
       <c r="U28" t="n">
         <v>0</v>
       </c>
       <c r="V28" t="n">
-        <v>-1000</v>
+        <v>0</v>
       </c>
       <c r="W28" t="n">
-        <v>-2000</v>
+        <v>0</v>
       </c>
       <c r="X28" t="n">
-        <v>-4000</v>
+        <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>9643</v>
+        <v>18000</v>
       </c>
       <c r="Z28" t="n">
-        <v>14262</v>
+        <v>42000</v>
       </c>
       <c r="AA28" t="n">
-        <v>18113</v>
+        <v>32481</v>
       </c>
       <c r="AB28" t="n">
-        <v>21700</v>
+        <v>35481</v>
       </c>
       <c r="AC28" t="n">
         <v>38</v>
@@ -4285,10 +4285,10 @@
         <v>38</v>
       </c>
       <c r="AE28" t="n">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="AF28" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="AG28" t="n">
         <v>0</v>
@@ -4308,29 +4308,29 @@
       </c>
       <c r="AM28" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、量能未放大</t>
+          <t>站上5日線、量能溫和放大、接近20日高點、接近20日低點</t>
         </is>
       </c>
       <c r="AN28" t="inlineStr">
         <is>
-          <t>法人連續偏買、5日法人買超、外資買投信賣</t>
+          <t>法人連續偏買、5日法人明顯買超</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>整理觀察：站上5日線、多頭排列、量能未放大、法人連續偏買、5日法人買超、外資買投信賣。多空訊號混合，建議降低追價衝動。</t>
+          <t>整理觀察：站上5日線、量能溫和放大、接近20日高點、接近20日低點、法人連續偏買、5日法人明顯買超。多空訊號混合，建議降低追價衝動。</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2608.TW</t>
+          <t>4763.TW</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>嘉里大榮</t>
+          <t>材料-KY</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -4339,28 +4339,28 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>29.35</v>
+        <v>48.6</v>
       </c>
       <c r="E29" t="n">
-        <v>29.32</v>
+        <v>46.82</v>
       </c>
       <c r="F29" t="n">
-        <v>29.32</v>
+        <v>47.7</v>
       </c>
       <c r="G29" t="n">
-        <v>29.13</v>
+        <v>47.31</v>
       </c>
       <c r="H29" t="n">
-        <v>366191</v>
+        <v>12820596</v>
       </c>
       <c r="I29" t="n">
-        <v>264994</v>
+        <v>7619303</v>
       </c>
       <c r="J29" t="n">
-        <v>29.7</v>
+        <v>52.7</v>
       </c>
       <c r="K29" t="n">
-        <v>28.6</v>
+        <v>42.5</v>
       </c>
       <c r="L29" t="inlineStr">
         <is>
@@ -4368,52 +4368,52 @@
         </is>
       </c>
       <c r="M29" t="n">
-        <v>215800</v>
+        <v>2546107</v>
       </c>
       <c r="N29" t="n">
-        <v>556882</v>
+        <v>427671</v>
       </c>
       <c r="O29" t="n">
-        <v>749363</v>
+        <v>769547</v>
       </c>
       <c r="P29" t="n">
-        <v>868328</v>
+        <v>-2686310</v>
       </c>
       <c r="Q29" t="n">
-        <v>197800</v>
+        <v>1643002</v>
       </c>
       <c r="R29" t="n">
-        <v>514882</v>
+        <v>-1274124</v>
       </c>
       <c r="S29" t="n">
-        <v>716882</v>
+        <v>-923233</v>
       </c>
       <c r="T29" t="n">
-        <v>832847</v>
+        <v>-3569512</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>719000</v>
       </c>
       <c r="V29" t="n">
-        <v>0</v>
+        <v>1635791</v>
       </c>
       <c r="W29" t="n">
-        <v>0</v>
+        <v>1626791</v>
       </c>
       <c r="X29" t="n">
-        <v>0</v>
+        <v>1604269</v>
       </c>
       <c r="Y29" t="n">
-        <v>18000</v>
+        <v>184105</v>
       </c>
       <c r="Z29" t="n">
-        <v>42000</v>
+        <v>66004</v>
       </c>
       <c r="AA29" t="n">
-        <v>32481</v>
+        <v>65989</v>
       </c>
       <c r="AB29" t="n">
-        <v>35481</v>
+        <v>-721067</v>
       </c>
       <c r="AC29" t="n">
         <v>38</v>
@@ -4445,29 +4445,29 @@
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>站上5日線、量能溫和放大、接近20日高點、接近20日低點</t>
+          <t>站上5日線、成交量放大</t>
         </is>
       </c>
       <c r="AN29" t="inlineStr">
         <is>
-          <t>法人連續偏買、5日法人明顯買超</t>
+          <t>法人連續偏買、5日法人明顯買超、投信買外資賣</t>
         </is>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>整理觀察：站上5日線、量能溫和放大、接近20日高點、接近20日低點、法人連續偏買、5日法人明顯買超。多空訊號混合，建議降低追價衝動。</t>
+          <t>整理觀察：站上5日線、成交量放大、法人連續偏買、5日法人明顯買超、投信買外資賣。多空訊號混合，建議降低追價衝動。</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>4763.TW</t>
+          <t>4904.TW</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>材料-KY</t>
+          <t>遠傳</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -4476,28 +4476,28 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>48.6</v>
+        <v>104.5</v>
       </c>
       <c r="E30" t="n">
-        <v>46.82</v>
+        <v>99.98</v>
       </c>
       <c r="F30" t="n">
-        <v>47.7</v>
+        <v>99.02</v>
       </c>
       <c r="G30" t="n">
-        <v>47.31</v>
+        <v>102.51</v>
       </c>
       <c r="H30" t="n">
-        <v>12820596</v>
+        <v>19211896</v>
       </c>
       <c r="I30" t="n">
-        <v>7619303</v>
+        <v>16001723</v>
       </c>
       <c r="J30" t="n">
-        <v>52.7</v>
+        <v>110</v>
       </c>
       <c r="K30" t="n">
-        <v>42.5</v>
+        <v>91.8</v>
       </c>
       <c r="L30" t="inlineStr">
         <is>
@@ -4505,61 +4505,61 @@
         </is>
       </c>
       <c r="M30" t="n">
-        <v>2546107</v>
+        <v>2358962</v>
       </c>
       <c r="N30" t="n">
-        <v>427671</v>
+        <v>12033586</v>
       </c>
       <c r="O30" t="n">
-        <v>769547</v>
+        <v>15172161</v>
       </c>
       <c r="P30" t="n">
-        <v>-2686310</v>
+        <v>18496891</v>
       </c>
       <c r="Q30" t="n">
-        <v>1643002</v>
+        <v>2621943</v>
       </c>
       <c r="R30" t="n">
-        <v>-1274124</v>
+        <v>13844254</v>
       </c>
       <c r="S30" t="n">
-        <v>-923233</v>
+        <v>16165122</v>
       </c>
       <c r="T30" t="n">
-        <v>-3569512</v>
+        <v>4637003</v>
       </c>
       <c r="U30" t="n">
-        <v>719000</v>
+        <v>-1536577</v>
       </c>
       <c r="V30" t="n">
-        <v>1635791</v>
+        <v>-5197005</v>
       </c>
       <c r="W30" t="n">
-        <v>1626791</v>
+        <v>-5735055</v>
       </c>
       <c r="X30" t="n">
-        <v>1604269</v>
+        <v>12691364</v>
       </c>
       <c r="Y30" t="n">
-        <v>184105</v>
+        <v>1273596</v>
       </c>
       <c r="Z30" t="n">
-        <v>66004</v>
+        <v>3386337</v>
       </c>
       <c r="AA30" t="n">
-        <v>65989</v>
+        <v>4742094</v>
       </c>
       <c r="AB30" t="n">
-        <v>-721067</v>
+        <v>1168524</v>
       </c>
       <c r="AC30" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AD30" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AE30" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="AF30" t="n">
         <v>60</v>
@@ -4582,17 +4582,17 @@
       </c>
       <c r="AM30" t="inlineStr">
         <is>
-          <t>站上5日線、成交量放大</t>
+          <t>站上5日線、量能溫和放大</t>
         </is>
       </c>
       <c r="AN30" t="inlineStr">
         <is>
-          <t>法人連續偏買、5日法人明顯買超、投信買外資賣</t>
+          <t>法人連續偏買、5日法人明顯買超、外資買投信賣</t>
         </is>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>整理觀察：站上5日線、成交量放大、法人連續偏買、5日法人明顯買超、投信買外資賣。多空訊號混合，建議降低追價衝動。</t>
+          <t>整理觀察：站上5日線、量能溫和放大、法人連續偏買、5日法人明顯買超、外資買投信賣。多空訊號混合，建議降低追價衝動。</t>
         </is>
       </c>
     </row>
@@ -4736,12 +4736,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>4904.TW</t>
+          <t>2850.TW</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>遠傳</t>
+          <t>新產</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -4750,28 +4750,28 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>104.5</v>
+        <v>147</v>
       </c>
       <c r="E32" t="n">
-        <v>99.98</v>
+        <v>146.7</v>
       </c>
       <c r="F32" t="n">
-        <v>99.02</v>
+        <v>146.1</v>
       </c>
       <c r="G32" t="n">
-        <v>102.51</v>
+        <v>144.03</v>
       </c>
       <c r="H32" t="n">
-        <v>19211896</v>
+        <v>264337</v>
       </c>
       <c r="I32" t="n">
-        <v>16001723</v>
+        <v>354645</v>
       </c>
       <c r="J32" t="n">
-        <v>110</v>
+        <v>151</v>
       </c>
       <c r="K32" t="n">
-        <v>91.8</v>
+        <v>139.5</v>
       </c>
       <c r="L32" t="inlineStr">
         <is>
@@ -4779,64 +4779,64 @@
         </is>
       </c>
       <c r="M32" t="n">
-        <v>2358962</v>
+        <v>-9831</v>
       </c>
       <c r="N32" t="n">
-        <v>12033586</v>
+        <v>35727</v>
       </c>
       <c r="O32" t="n">
-        <v>15172161</v>
+        <v>292487</v>
       </c>
       <c r="P32" t="n">
-        <v>18496891</v>
+        <v>385138</v>
       </c>
       <c r="Q32" t="n">
-        <v>2621943</v>
+        <v>-20831</v>
       </c>
       <c r="R32" t="n">
-        <v>13844254</v>
+        <v>16351</v>
       </c>
       <c r="S32" t="n">
-        <v>16165122</v>
+        <v>254111</v>
       </c>
       <c r="T32" t="n">
-        <v>4637003</v>
+        <v>369763</v>
       </c>
       <c r="U32" t="n">
-        <v>-1536577</v>
+        <v>0</v>
       </c>
       <c r="V32" t="n">
-        <v>-5197005</v>
+        <v>4000</v>
       </c>
       <c r="W32" t="n">
-        <v>-5735055</v>
+        <v>4000</v>
       </c>
       <c r="X32" t="n">
-        <v>12691364</v>
+        <v>3000</v>
       </c>
       <c r="Y32" t="n">
-        <v>1273596</v>
+        <v>11000</v>
       </c>
       <c r="Z32" t="n">
-        <v>3386337</v>
+        <v>15376</v>
       </c>
       <c r="AA32" t="n">
-        <v>4742094</v>
+        <v>34376</v>
       </c>
       <c r="AB32" t="n">
-        <v>1168524</v>
+        <v>12375</v>
       </c>
       <c r="AC32" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AD32" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AE32" t="n">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="AF32" t="n">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="AG32" t="n">
         <v>0</v>
@@ -4856,17 +4856,17 @@
       </c>
       <c r="AM32" t="inlineStr">
         <is>
-          <t>站上5日線、量能溫和放大</t>
+          <t>站上5日線、多頭排列、量能未放大</t>
         </is>
       </c>
       <c r="AN32" t="inlineStr">
         <is>
-          <t>法人連續偏買、5日法人明顯買超、外資買投信賣</t>
+          <t>5日法人買超、外資投信同步買超</t>
         </is>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>整理觀察：站上5日線、量能溫和放大、法人連續偏買、5日法人明顯買超、外資買投信賣。多空訊號混合，建議降低追價衝動。</t>
+          <t>整理觀察：站上5日線、多頭排列、量能未放大、5日法人買超、外資投信同步買超。多空訊號混合，建議降低追價衝動。</t>
         </is>
       </c>
     </row>
@@ -5010,12 +5010,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2850.TW</t>
+          <t>2637.TW</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>新產</t>
+          <t>慧洋-KY</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -5024,28 +5024,28 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>147</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="E34" t="n">
-        <v>146.7</v>
+        <v>81.73999999999999</v>
       </c>
       <c r="F34" t="n">
-        <v>146.1</v>
+        <v>81.38</v>
       </c>
       <c r="G34" t="n">
-        <v>144.03</v>
+        <v>77.69</v>
       </c>
       <c r="H34" t="n">
-        <v>264337</v>
+        <v>1921422</v>
       </c>
       <c r="I34" t="n">
-        <v>354645</v>
+        <v>2493994</v>
       </c>
       <c r="J34" t="n">
-        <v>151</v>
+        <v>88</v>
       </c>
       <c r="K34" t="n">
-        <v>139.5</v>
+        <v>70.8</v>
       </c>
       <c r="L34" t="inlineStr">
         <is>
@@ -5053,52 +5053,52 @@
         </is>
       </c>
       <c r="M34" t="n">
-        <v>-9831</v>
+        <v>184144</v>
       </c>
       <c r="N34" t="n">
-        <v>35727</v>
+        <v>234001</v>
       </c>
       <c r="O34" t="n">
-        <v>292487</v>
+        <v>633501</v>
       </c>
       <c r="P34" t="n">
-        <v>385138</v>
+        <v>13979935</v>
       </c>
       <c r="Q34" t="n">
-        <v>-20831</v>
+        <v>300092</v>
       </c>
       <c r="R34" t="n">
-        <v>16351</v>
+        <v>376748</v>
       </c>
       <c r="S34" t="n">
-        <v>254111</v>
+        <v>562786</v>
       </c>
       <c r="T34" t="n">
-        <v>369763</v>
+        <v>12368720</v>
       </c>
       <c r="U34" t="n">
-        <v>0</v>
+        <v>12787</v>
       </c>
       <c r="V34" t="n">
-        <v>4000</v>
+        <v>104787</v>
       </c>
       <c r="W34" t="n">
-        <v>4000</v>
+        <v>330787</v>
       </c>
       <c r="X34" t="n">
-        <v>3000</v>
+        <v>1567722</v>
       </c>
       <c r="Y34" t="n">
-        <v>11000</v>
+        <v>-128735</v>
       </c>
       <c r="Z34" t="n">
-        <v>15376</v>
+        <v>-247534</v>
       </c>
       <c r="AA34" t="n">
-        <v>34376</v>
+        <v>-260072</v>
       </c>
       <c r="AB34" t="n">
-        <v>12375</v>
+        <v>43493</v>
       </c>
       <c r="AC34" t="n">
         <v>34</v>
@@ -5107,10 +5107,10 @@
         <v>34</v>
       </c>
       <c r="AE34" t="n">
-        <v>45</v>
+        <v>5</v>
       </c>
       <c r="AF34" t="n">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="AG34" t="n">
         <v>0</v>
@@ -5130,17 +5130,17 @@
       </c>
       <c r="AM34" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、量能未放大</t>
+          <t>跌破5日線、多頭排列、量能未放大</t>
         </is>
       </c>
       <c r="AN34" t="inlineStr">
         <is>
-          <t>5日法人買超、外資投信同步買超</t>
+          <t>法人連續偏買、5日法人明顯買超、外資投信同步買超</t>
         </is>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>整理觀察：站上5日線、多頭排列、量能未放大、5日法人買超、外資投信同步買超。多空訊號混合，建議降低追價衝動。</t>
+          <t>整理觀察：跌破5日線、多頭排列、量能未放大、法人連續偏買、5日法人明顯買超、外資投信同步買超。多空訊號混合，建議降低追價衝動。</t>
         </is>
       </c>
     </row>
@@ -5421,12 +5421,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2637.TW</t>
+          <t>2534.TW</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>慧洋-KY</t>
+          <t>宏盛</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -5435,28 +5435,28 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>79.09999999999999</v>
+        <v>17.2</v>
       </c>
       <c r="E37" t="n">
-        <v>81.73999999999999</v>
+        <v>17.02</v>
       </c>
       <c r="F37" t="n">
-        <v>81.38</v>
+        <v>16.82</v>
       </c>
       <c r="G37" t="n">
-        <v>77.69</v>
+        <v>16.84</v>
       </c>
       <c r="H37" t="n">
-        <v>1921422</v>
+        <v>551288</v>
       </c>
       <c r="I37" t="n">
-        <v>2493994</v>
+        <v>655526</v>
       </c>
       <c r="J37" t="n">
-        <v>88</v>
+        <v>18.4</v>
       </c>
       <c r="K37" t="n">
-        <v>70.8</v>
+        <v>16.3</v>
       </c>
       <c r="L37" t="inlineStr">
         <is>
@@ -5464,64 +5464,64 @@
         </is>
       </c>
       <c r="M37" t="n">
-        <v>184144</v>
+        <v>114211</v>
       </c>
       <c r="N37" t="n">
-        <v>234001</v>
+        <v>606259</v>
       </c>
       <c r="O37" t="n">
-        <v>633501</v>
+        <v>968971</v>
       </c>
       <c r="P37" t="n">
-        <v>13979935</v>
+        <v>882537</v>
       </c>
       <c r="Q37" t="n">
-        <v>300092</v>
+        <v>96212</v>
       </c>
       <c r="R37" t="n">
-        <v>376748</v>
+        <v>585260</v>
       </c>
       <c r="S37" t="n">
-        <v>562786</v>
+        <v>915565</v>
       </c>
       <c r="T37" t="n">
-        <v>12368720</v>
+        <v>830565</v>
       </c>
       <c r="U37" t="n">
-        <v>12787</v>
+        <v>0</v>
       </c>
       <c r="V37" t="n">
-        <v>104787</v>
+        <v>0</v>
       </c>
       <c r="W37" t="n">
-        <v>330787</v>
+        <v>0</v>
       </c>
       <c r="X37" t="n">
-        <v>1567722</v>
+        <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>-128735</v>
+        <v>17999</v>
       </c>
       <c r="Z37" t="n">
-        <v>-247534</v>
+        <v>20999</v>
       </c>
       <c r="AA37" t="n">
-        <v>-260072</v>
+        <v>53406</v>
       </c>
       <c r="AB37" t="n">
-        <v>43493</v>
+        <v>51972</v>
       </c>
       <c r="AC37" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AD37" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AE37" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="AF37" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="AG37" t="n">
         <v>0</v>
@@ -5541,29 +5541,29 @@
       </c>
       <c r="AM37" t="inlineStr">
         <is>
-          <t>跌破5日線、多頭排列、量能未放大</t>
+          <t>站上5日線、量能未放大</t>
         </is>
       </c>
       <c r="AN37" t="inlineStr">
         <is>
-          <t>法人連續偏買、5日法人明顯買超、外資投信同步買超</t>
+          <t>法人連續偏買、5日法人明顯買超</t>
         </is>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>整理觀察：跌破5日線、多頭排列、量能未放大、法人連續偏買、5日法人明顯買超、外資投信同步買超。多空訊號混合，建議降低追價衝動。</t>
+          <t>整理觀察：站上5日線、量能未放大、法人連續偏買、5日法人明顯買超。多空訊號混合，建議降低追價衝動。</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2534.TW</t>
+          <t>2511.TW</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>宏盛</t>
+          <t>太子</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -5572,28 +5572,28 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>17.2</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="E38" t="n">
-        <v>17.02</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="F38" t="n">
-        <v>16.82</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="G38" t="n">
-        <v>16.84</v>
+        <v>8.35</v>
       </c>
       <c r="H38" t="n">
-        <v>551288</v>
+        <v>1246010</v>
       </c>
       <c r="I38" t="n">
-        <v>655526</v>
+        <v>1649286</v>
       </c>
       <c r="J38" t="n">
-        <v>18.4</v>
+        <v>8.73</v>
       </c>
       <c r="K38" t="n">
-        <v>16.3</v>
+        <v>8.039999999999999</v>
       </c>
       <c r="L38" t="inlineStr">
         <is>
@@ -5601,28 +5601,28 @@
         </is>
       </c>
       <c r="M38" t="n">
-        <v>114211</v>
+        <v>409200</v>
       </c>
       <c r="N38" t="n">
-        <v>606259</v>
+        <v>1283975</v>
       </c>
       <c r="O38" t="n">
-        <v>968971</v>
+        <v>1834415</v>
       </c>
       <c r="P38" t="n">
-        <v>882537</v>
+        <v>3399574</v>
       </c>
       <c r="Q38" t="n">
-        <v>96212</v>
+        <v>344200</v>
       </c>
       <c r="R38" t="n">
-        <v>585260</v>
+        <v>1220975</v>
       </c>
       <c r="S38" t="n">
-        <v>915565</v>
+        <v>1650415</v>
       </c>
       <c r="T38" t="n">
-        <v>830565</v>
+        <v>3255574</v>
       </c>
       <c r="U38" t="n">
         <v>0</v>
@@ -5637,16 +5637,16 @@
         <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>17999</v>
+        <v>65000</v>
       </c>
       <c r="Z38" t="n">
-        <v>20999</v>
+        <v>63000</v>
       </c>
       <c r="AA38" t="n">
-        <v>53406</v>
+        <v>184000</v>
       </c>
       <c r="AB38" t="n">
-        <v>51972</v>
+        <v>144000</v>
       </c>
       <c r="AC38" t="n">
         <v>32</v>
@@ -6106,12 +6106,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2511.TW</t>
+          <t>2520.TW</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>太子</t>
+          <t>冠德</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -6120,28 +6120,28 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>8.550000000000001</v>
+        <v>35.75</v>
       </c>
       <c r="E42" t="n">
-        <v>8.539999999999999</v>
+        <v>35.74</v>
       </c>
       <c r="F42" t="n">
-        <v>8.539999999999999</v>
+        <v>35.41</v>
       </c>
       <c r="G42" t="n">
-        <v>8.35</v>
+        <v>34.85</v>
       </c>
       <c r="H42" t="n">
-        <v>1246010</v>
+        <v>1746101</v>
       </c>
       <c r="I42" t="n">
-        <v>1649286</v>
+        <v>2212053</v>
       </c>
       <c r="J42" t="n">
-        <v>8.73</v>
+        <v>36.85</v>
       </c>
       <c r="K42" t="n">
-        <v>8.039999999999999</v>
+        <v>32.8</v>
       </c>
       <c r="L42" t="inlineStr">
         <is>
@@ -6149,64 +6149,64 @@
         </is>
       </c>
       <c r="M42" t="n">
-        <v>409200</v>
+        <v>-118492</v>
       </c>
       <c r="N42" t="n">
-        <v>1283975</v>
+        <v>258424</v>
       </c>
       <c r="O42" t="n">
-        <v>1834415</v>
+        <v>1683267</v>
       </c>
       <c r="P42" t="n">
-        <v>3399574</v>
+        <v>2620272</v>
       </c>
       <c r="Q42" t="n">
-        <v>344200</v>
+        <v>-11348</v>
       </c>
       <c r="R42" t="n">
-        <v>1220975</v>
+        <v>351889</v>
       </c>
       <c r="S42" t="n">
-        <v>1650415</v>
+        <v>1753392</v>
       </c>
       <c r="T42" t="n">
-        <v>3255574</v>
+        <v>2781595</v>
       </c>
       <c r="U42" t="n">
-        <v>0</v>
+        <v>-144000</v>
       </c>
       <c r="V42" t="n">
-        <v>0</v>
+        <v>-146000</v>
       </c>
       <c r="W42" t="n">
-        <v>0</v>
+        <v>-150000</v>
       </c>
       <c r="X42" t="n">
-        <v>0</v>
+        <v>-157000</v>
       </c>
       <c r="Y42" t="n">
-        <v>65000</v>
+        <v>36856</v>
       </c>
       <c r="Z42" t="n">
-        <v>63000</v>
+        <v>52535</v>
       </c>
       <c r="AA42" t="n">
-        <v>184000</v>
+        <v>79875</v>
       </c>
       <c r="AB42" t="n">
-        <v>144000</v>
+        <v>-4323</v>
       </c>
       <c r="AC42" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AD42" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AE42" t="n">
-        <v>20</v>
+        <v>45</v>
       </c>
       <c r="AF42" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="AG42" t="n">
         <v>0</v>
@@ -6226,17 +6226,17 @@
       </c>
       <c r="AM42" t="inlineStr">
         <is>
-          <t>站上5日線、量能未放大</t>
+          <t>站上5日線、多頭排列、量能未放大</t>
         </is>
       </c>
       <c r="AN42" t="inlineStr">
         <is>
-          <t>法人連續偏買、5日法人明顯買超</t>
+          <t>5日法人明顯買超、外資買投信賣</t>
         </is>
       </c>
       <c r="AO42" t="inlineStr">
         <is>
-          <t>整理觀察：站上5日線、量能未放大、法人連續偏買、5日法人明顯買超。多空訊號混合，建議降低追價衝動。</t>
+          <t>整理觀察：站上5日線、多頭排列、量能未放大、5日法人明顯買超、外資買投信賣。多空訊號混合，建議降低追價衝動。</t>
         </is>
       </c>
     </row>
@@ -6380,12 +6380,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2520.TW</t>
+          <t>1707.TW</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>冠德</t>
+          <t>葡萄王</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -6394,28 +6394,28 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>35.75</v>
+        <v>92.7</v>
       </c>
       <c r="E44" t="n">
-        <v>35.74</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="F44" t="n">
-        <v>35.41</v>
+        <v>91.79000000000001</v>
       </c>
       <c r="G44" t="n">
-        <v>34.85</v>
+        <v>93.18000000000001</v>
       </c>
       <c r="H44" t="n">
-        <v>1746101</v>
+        <v>544586</v>
       </c>
       <c r="I44" t="n">
-        <v>2212053</v>
+        <v>436684</v>
       </c>
       <c r="J44" t="n">
-        <v>36.85</v>
+        <v>100</v>
       </c>
       <c r="K44" t="n">
-        <v>32.8</v>
+        <v>90</v>
       </c>
       <c r="L44" t="inlineStr">
         <is>
@@ -6423,64 +6423,64 @@
         </is>
       </c>
       <c r="M44" t="n">
-        <v>-118492</v>
+        <v>216500</v>
       </c>
       <c r="N44" t="n">
-        <v>258424</v>
+        <v>127218</v>
       </c>
       <c r="O44" t="n">
-        <v>1683267</v>
+        <v>347822</v>
       </c>
       <c r="P44" t="n">
-        <v>2620272</v>
+        <v>339186</v>
       </c>
       <c r="Q44" t="n">
-        <v>-11348</v>
+        <v>142500</v>
       </c>
       <c r="R44" t="n">
-        <v>351889</v>
+        <v>119218</v>
       </c>
       <c r="S44" t="n">
-        <v>1753392</v>
+        <v>345822</v>
       </c>
       <c r="T44" t="n">
-        <v>2781595</v>
+        <v>337230</v>
       </c>
       <c r="U44" t="n">
-        <v>-144000</v>
+        <v>71000</v>
       </c>
       <c r="V44" t="n">
-        <v>-146000</v>
+        <v>3000</v>
       </c>
       <c r="W44" t="n">
-        <v>-150000</v>
+        <v>-1000</v>
       </c>
       <c r="X44" t="n">
-        <v>-157000</v>
+        <v>-1000</v>
       </c>
       <c r="Y44" t="n">
-        <v>36856</v>
+        <v>3000</v>
       </c>
       <c r="Z44" t="n">
-        <v>52535</v>
+        <v>5000</v>
       </c>
       <c r="AA44" t="n">
-        <v>79875</v>
+        <v>3000</v>
       </c>
       <c r="AB44" t="n">
-        <v>-4323</v>
+        <v>2956</v>
       </c>
       <c r="AC44" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AD44" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AE44" t="n">
-        <v>45</v>
+        <v>20</v>
       </c>
       <c r="AF44" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="AG44" t="n">
         <v>0</v>
@@ -6500,17 +6500,17 @@
       </c>
       <c r="AM44" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、量能未放大</t>
+          <t>站上5日線、量能溫和放大、接近20日低點</t>
         </is>
       </c>
       <c r="AN44" t="inlineStr">
         <is>
-          <t>5日法人明顯買超、外資買投信賣</t>
+          <t>法人連續偏買、5日法人買超、外資買投信賣</t>
         </is>
       </c>
       <c r="AO44" t="inlineStr">
         <is>
-          <t>整理觀察：站上5日線、多頭排列、量能未放大、5日法人明顯買超、外資買投信賣。多空訊號混合，建議降低追價衝動。</t>
+          <t>整理觀察：站上5日線、量能溫和放大、接近20日低點、法人連續偏買、5日法人買超、外資買投信賣。多空訊號混合，建議降低追價衝動。</t>
         </is>
       </c>
     </row>
@@ -6543,10 +6543,10 @@
         <v>1478</v>
       </c>
       <c r="H45" t="n">
-        <v>1275723</v>
+        <v>1285723</v>
       </c>
       <c r="I45" t="n">
-        <v>872109</v>
+        <v>874109</v>
       </c>
       <c r="J45" t="n">
         <v>1585</v>
@@ -6654,12 +6654,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>1707.TW</t>
+          <t>9945.TW</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>葡萄王</t>
+          <t>潤泰新</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -6668,28 +6668,28 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>92.7</v>
+        <v>26.4</v>
       </c>
       <c r="E46" t="n">
-        <v>91.90000000000001</v>
+        <v>26.35</v>
       </c>
       <c r="F46" t="n">
-        <v>91.79000000000001</v>
+        <v>26.07</v>
       </c>
       <c r="G46" t="n">
-        <v>93.18000000000001</v>
+        <v>26.41</v>
       </c>
       <c r="H46" t="n">
-        <v>544586</v>
+        <v>5071157</v>
       </c>
       <c r="I46" t="n">
-        <v>436684</v>
+        <v>6293520</v>
       </c>
       <c r="J46" t="n">
-        <v>100</v>
+        <v>27.55</v>
       </c>
       <c r="K46" t="n">
-        <v>90</v>
+        <v>25.2</v>
       </c>
       <c r="L46" t="inlineStr">
         <is>
@@ -6697,52 +6697,52 @@
         </is>
       </c>
       <c r="M46" t="n">
-        <v>216500</v>
+        <v>2127721</v>
       </c>
       <c r="N46" t="n">
-        <v>127218</v>
+        <v>5993444</v>
       </c>
       <c r="O46" t="n">
-        <v>347822</v>
+        <v>11254766</v>
       </c>
       <c r="P46" t="n">
-        <v>339186</v>
+        <v>10059010</v>
       </c>
       <c r="Q46" t="n">
-        <v>142500</v>
+        <v>2051893</v>
       </c>
       <c r="R46" t="n">
-        <v>119218</v>
+        <v>6047560</v>
       </c>
       <c r="S46" t="n">
-        <v>345822</v>
+        <v>11115035</v>
       </c>
       <c r="T46" t="n">
-        <v>337230</v>
+        <v>10034497</v>
       </c>
       <c r="U46" t="n">
-        <v>71000</v>
+        <v>0</v>
       </c>
       <c r="V46" t="n">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="W46" t="n">
-        <v>-1000</v>
+        <v>0</v>
       </c>
       <c r="X46" t="n">
-        <v>-1000</v>
+        <v>-182000</v>
       </c>
       <c r="Y46" t="n">
-        <v>3000</v>
+        <v>75828</v>
       </c>
       <c r="Z46" t="n">
-        <v>5000</v>
+        <v>-54116</v>
       </c>
       <c r="AA46" t="n">
-        <v>3000</v>
+        <v>139731</v>
       </c>
       <c r="AB46" t="n">
-        <v>2956</v>
+        <v>206513</v>
       </c>
       <c r="AC46" t="n">
         <v>28</v>
@@ -6751,10 +6751,10 @@
         <v>28</v>
       </c>
       <c r="AE46" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="AF46" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="AG46" t="n">
         <v>0</v>
@@ -6774,29 +6774,29 @@
       </c>
       <c r="AM46" t="inlineStr">
         <is>
-          <t>站上5日線、量能溫和放大、接近20日低點</t>
+          <t>站上5日線、量能未放大、接近20日低點</t>
         </is>
       </c>
       <c r="AN46" t="inlineStr">
         <is>
-          <t>法人連續偏買、5日法人買超、外資買投信賣</t>
+          <t>法人連續偏買、5日法人明顯買超</t>
         </is>
       </c>
       <c r="AO46" t="inlineStr">
         <is>
-          <t>整理觀察：站上5日線、量能溫和放大、接近20日低點、法人連續偏買、5日法人買超、外資買投信賣。多空訊號混合，建議降低追價衝動。</t>
+          <t>整理觀察：站上5日線、量能未放大、接近20日低點、法人連續偏買、5日法人明顯買超。多空訊號混合，建議降低追價衝動。</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>9945.TW</t>
+          <t>2603.TW</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>潤泰新</t>
+          <t>長榮</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -6805,28 +6805,28 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>26.4</v>
+        <v>196</v>
       </c>
       <c r="E47" t="n">
-        <v>26.35</v>
+        <v>197.6</v>
       </c>
       <c r="F47" t="n">
-        <v>26.07</v>
+        <v>195.7</v>
       </c>
       <c r="G47" t="n">
-        <v>26.41</v>
+        <v>191.3</v>
       </c>
       <c r="H47" t="n">
-        <v>5071157</v>
+        <v>10069119</v>
       </c>
       <c r="I47" t="n">
-        <v>6293520</v>
+        <v>11738519</v>
       </c>
       <c r="J47" t="n">
-        <v>27.55</v>
+        <v>202.5</v>
       </c>
       <c r="K47" t="n">
-        <v>25.2</v>
+        <v>180.5</v>
       </c>
       <c r="L47" t="inlineStr">
         <is>
@@ -6834,61 +6834,61 @@
         </is>
       </c>
       <c r="M47" t="n">
-        <v>2127721</v>
+        <v>993729</v>
       </c>
       <c r="N47" t="n">
-        <v>5993444</v>
+        <v>12942711</v>
       </c>
       <c r="O47" t="n">
-        <v>11254766</v>
+        <v>25578142</v>
       </c>
       <c r="P47" t="n">
-        <v>10059010</v>
+        <v>32680269</v>
       </c>
       <c r="Q47" t="n">
-        <v>2051893</v>
+        <v>1157175</v>
       </c>
       <c r="R47" t="n">
-        <v>6047560</v>
+        <v>13509565</v>
       </c>
       <c r="S47" t="n">
-        <v>11115035</v>
+        <v>26114743</v>
       </c>
       <c r="T47" t="n">
-        <v>10034497</v>
+        <v>34340174</v>
       </c>
       <c r="U47" t="n">
-        <v>0</v>
+        <v>-988263</v>
       </c>
       <c r="V47" t="n">
-        <v>0</v>
+        <v>-2447302</v>
       </c>
       <c r="W47" t="n">
-        <v>0</v>
+        <v>-3409863</v>
       </c>
       <c r="X47" t="n">
-        <v>-182000</v>
+        <v>-4380382</v>
       </c>
       <c r="Y47" t="n">
-        <v>75828</v>
+        <v>824817</v>
       </c>
       <c r="Z47" t="n">
-        <v>-54116</v>
+        <v>1880448</v>
       </c>
       <c r="AA47" t="n">
-        <v>139731</v>
+        <v>2873262</v>
       </c>
       <c r="AB47" t="n">
-        <v>206513</v>
+        <v>2720477</v>
       </c>
       <c r="AC47" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AD47" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AE47" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="AF47" t="n">
         <v>60</v>
@@ -6911,29 +6911,29 @@
       </c>
       <c r="AM47" t="inlineStr">
         <is>
-          <t>站上5日線、量能未放大、接近20日低點</t>
+          <t>跌破5日線、多頭排列、量能未放大</t>
         </is>
       </c>
       <c r="AN47" t="inlineStr">
         <is>
-          <t>法人連續偏買、5日法人明顯買超</t>
+          <t>法人連續偏買、5日法人明顯買超、外資買投信賣</t>
         </is>
       </c>
       <c r="AO47" t="inlineStr">
         <is>
-          <t>整理觀察：站上5日線、量能未放大、接近20日低點、法人連續偏買、5日法人明顯買超。多空訊號混合，建議降低追價衝動。</t>
+          <t>整理觀察：跌破5日線、多頭排列、量能未放大、法人連續偏買、5日法人明顯買超、外資買投信賣。多空訊號混合，建議降低追價衝動。</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2603.TW</t>
+          <t>2605.TW</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>長榮</t>
+          <t>新興</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -6942,28 +6942,28 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>196</v>
+        <v>30.65</v>
       </c>
       <c r="E48" t="n">
-        <v>197.6</v>
+        <v>30.94</v>
       </c>
       <c r="F48" t="n">
-        <v>195.7</v>
+        <v>30.74</v>
       </c>
       <c r="G48" t="n">
-        <v>191.3</v>
+        <v>30.55</v>
       </c>
       <c r="H48" t="n">
-        <v>10069119</v>
+        <v>6243566</v>
       </c>
       <c r="I48" t="n">
-        <v>11738519</v>
+        <v>5354357</v>
       </c>
       <c r="J48" t="n">
-        <v>202.5</v>
+        <v>32.75</v>
       </c>
       <c r="K48" t="n">
-        <v>180.5</v>
+        <v>28.65</v>
       </c>
       <c r="L48" t="inlineStr">
         <is>
@@ -6971,52 +6971,52 @@
         </is>
       </c>
       <c r="M48" t="n">
-        <v>993729</v>
+        <v>-410639</v>
       </c>
       <c r="N48" t="n">
-        <v>12942711</v>
+        <v>282890</v>
       </c>
       <c r="O48" t="n">
-        <v>25578142</v>
+        <v>4883905</v>
       </c>
       <c r="P48" t="n">
-        <v>32680269</v>
+        <v>5548834</v>
       </c>
       <c r="Q48" t="n">
-        <v>1157175</v>
+        <v>-350793</v>
       </c>
       <c r="R48" t="n">
-        <v>13509565</v>
+        <v>465496</v>
       </c>
       <c r="S48" t="n">
-        <v>26114743</v>
+        <v>4897139</v>
       </c>
       <c r="T48" t="n">
-        <v>34340174</v>
+        <v>5297052</v>
       </c>
       <c r="U48" t="n">
-        <v>-988263</v>
+        <v>12000</v>
       </c>
       <c r="V48" t="n">
-        <v>-2447302</v>
+        <v>178000</v>
       </c>
       <c r="W48" t="n">
-        <v>-3409863</v>
+        <v>174000</v>
       </c>
       <c r="X48" t="n">
-        <v>-4380382</v>
+        <v>170000</v>
       </c>
       <c r="Y48" t="n">
-        <v>824817</v>
+        <v>-71846</v>
       </c>
       <c r="Z48" t="n">
-        <v>1880448</v>
+        <v>-360606</v>
       </c>
       <c r="AA48" t="n">
-        <v>2873262</v>
+        <v>-187234</v>
       </c>
       <c r="AB48" t="n">
-        <v>2720477</v>
+        <v>81782</v>
       </c>
       <c r="AC48" t="n">
         <v>26</v>
@@ -7025,10 +7025,10 @@
         <v>26</v>
       </c>
       <c r="AE48" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="AF48" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AG48" t="n">
         <v>0</v>
@@ -7048,29 +7048,29 @@
       </c>
       <c r="AM48" t="inlineStr">
         <is>
-          <t>跌破5日線、多頭排列、量能未放大</t>
+          <t>跌破5日線、多頭排列、量能溫和放大</t>
         </is>
       </c>
       <c r="AN48" t="inlineStr">
         <is>
-          <t>法人連續偏買、5日法人明顯買超、外資買投信賣</t>
+          <t>5日法人明顯買超、外資投信同步買超</t>
         </is>
       </c>
       <c r="AO48" t="inlineStr">
         <is>
-          <t>整理觀察：跌破5日線、多頭排列、量能未放大、法人連續偏買、5日法人明顯買超、外資買投信賣。多空訊號混合，建議降低追價衝動。</t>
+          <t>整理觀察：跌破5日線、多頭排列、量能溫和放大、5日法人明顯買超、外資投信同步買超。多空訊號混合，建議降低追價衝動。</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2605.TW</t>
+          <t>2377.TW</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>新興</t>
+          <t>微星</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -7079,28 +7079,28 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>30.65</v>
+        <v>141.5</v>
       </c>
       <c r="E49" t="n">
-        <v>30.94</v>
+        <v>144.7</v>
       </c>
       <c r="F49" t="n">
-        <v>30.74</v>
+        <v>143.95</v>
       </c>
       <c r="G49" t="n">
-        <v>30.55</v>
+        <v>141.25</v>
       </c>
       <c r="H49" t="n">
-        <v>6243566</v>
+        <v>13485283</v>
       </c>
       <c r="I49" t="n">
-        <v>5354357</v>
+        <v>12964407</v>
       </c>
       <c r="J49" t="n">
-        <v>32.75</v>
+        <v>153</v>
       </c>
       <c r="K49" t="n">
-        <v>28.65</v>
+        <v>131</v>
       </c>
       <c r="L49" t="inlineStr">
         <is>
@@ -7108,52 +7108,52 @@
         </is>
       </c>
       <c r="M49" t="n">
-        <v>-410639</v>
+        <v>2313901</v>
       </c>
       <c r="N49" t="n">
-        <v>282890</v>
+        <v>370728</v>
       </c>
       <c r="O49" t="n">
-        <v>4883905</v>
+        <v>250144</v>
       </c>
       <c r="P49" t="n">
-        <v>5548834</v>
+        <v>24279233</v>
       </c>
       <c r="Q49" t="n">
-        <v>-350793</v>
+        <v>321307</v>
       </c>
       <c r="R49" t="n">
-        <v>465496</v>
+        <v>-221389</v>
       </c>
       <c r="S49" t="n">
-        <v>4897139</v>
+        <v>-2037822</v>
       </c>
       <c r="T49" t="n">
-        <v>5297052</v>
+        <v>15623405</v>
       </c>
       <c r="U49" t="n">
-        <v>12000</v>
+        <v>2035000</v>
       </c>
       <c r="V49" t="n">
-        <v>178000</v>
+        <v>615000</v>
       </c>
       <c r="W49" t="n">
-        <v>174000</v>
+        <v>662000</v>
       </c>
       <c r="X49" t="n">
-        <v>170000</v>
+        <v>6011000</v>
       </c>
       <c r="Y49" t="n">
-        <v>-71846</v>
+        <v>-42406</v>
       </c>
       <c r="Z49" t="n">
-        <v>-360606</v>
+        <v>-22883</v>
       </c>
       <c r="AA49" t="n">
-        <v>-187234</v>
+        <v>1625966</v>
       </c>
       <c r="AB49" t="n">
-        <v>81782</v>
+        <v>2644828</v>
       </c>
       <c r="AC49" t="n">
         <v>26</v>
@@ -7190,54 +7190,54 @@
       </c>
       <c r="AN49" t="inlineStr">
         <is>
-          <t>5日法人明顯買超、外資投信同步買超</t>
+          <t>法人連續偏買、5日法人買超、投信買外資賣</t>
         </is>
       </c>
       <c r="AO49" t="inlineStr">
         <is>
-          <t>整理觀察：跌破5日線、多頭排列、量能溫和放大、5日法人明顯買超、外資投信同步買超。多空訊號混合，建議降低追價衝動。</t>
+          <t>整理觀察：跌破5日線、多頭排列、量能溫和放大、法人連續偏買、5日法人買超、投信買外資賣。多空訊號混合，建議降低追價衝動。</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>00757.TW</t>
+          <t>3055.TW</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>統一FANG+</t>
+          <t>蔚華科</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>ETF</t>
+          <t>個股</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>131.35</v>
+        <v>161.5</v>
       </c>
       <c r="E50" t="n">
-        <v>132.69</v>
+        <v>174.6</v>
       </c>
       <c r="F50" t="n">
-        <v>131.46</v>
+        <v>169.9</v>
       </c>
       <c r="G50" t="n">
-        <v>129.09</v>
+        <v>141.06</v>
       </c>
       <c r="H50" t="n">
-        <v>975781</v>
+        <v>810224</v>
       </c>
       <c r="I50" t="n">
-        <v>2578943</v>
+        <v>1170516</v>
       </c>
       <c r="J50" t="n">
-        <v>135.45</v>
+        <v>201</v>
       </c>
       <c r="K50" t="n">
-        <v>121.35</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="L50" t="inlineStr">
         <is>
@@ -7245,28 +7245,28 @@
         </is>
       </c>
       <c r="M50" t="n">
-        <v>528637</v>
+        <v>219858</v>
       </c>
       <c r="N50" t="n">
-        <v>2945346</v>
+        <v>742952</v>
       </c>
       <c r="O50" t="n">
-        <v>4296148</v>
+        <v>967947</v>
       </c>
       <c r="P50" t="n">
-        <v>8128274</v>
+        <v>1999499</v>
       </c>
       <c r="Q50" t="n">
-        <v>7068</v>
+        <v>221858</v>
       </c>
       <c r="R50" t="n">
-        <v>549228</v>
+        <v>644507</v>
       </c>
       <c r="S50" t="n">
-        <v>1003224</v>
+        <v>849507</v>
       </c>
       <c r="T50" t="n">
-        <v>4383152</v>
+        <v>1762369</v>
       </c>
       <c r="U50" t="n">
         <v>0</v>
@@ -7281,16 +7281,16 @@
         <v>0</v>
       </c>
       <c r="Y50" t="n">
-        <v>521569</v>
+        <v>-2000</v>
       </c>
       <c r="Z50" t="n">
-        <v>2396118</v>
+        <v>98445</v>
       </c>
       <c r="AA50" t="n">
-        <v>3292924</v>
+        <v>118440</v>
       </c>
       <c r="AB50" t="n">
-        <v>3745122</v>
+        <v>237130</v>
       </c>
       <c r="AC50" t="n">
         <v>26</v>
@@ -7613,12 +7613,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2377.TW</t>
+          <t>2542.TW</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>微星</t>
+          <t>興富發</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -7627,28 +7627,28 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>141.5</v>
+        <v>43.3</v>
       </c>
       <c r="E53" t="n">
-        <v>144.7</v>
+        <v>43.36</v>
       </c>
       <c r="F53" t="n">
-        <v>143.95</v>
+        <v>43.61</v>
       </c>
       <c r="G53" t="n">
-        <v>141.25</v>
+        <v>43.3</v>
       </c>
       <c r="H53" t="n">
-        <v>13485283</v>
+        <v>14382651</v>
       </c>
       <c r="I53" t="n">
-        <v>12964407</v>
+        <v>9716324</v>
       </c>
       <c r="J53" t="n">
-        <v>153</v>
+        <v>45</v>
       </c>
       <c r="K53" t="n">
-        <v>131</v>
+        <v>41.95</v>
       </c>
       <c r="L53" t="inlineStr">
         <is>
@@ -7656,52 +7656,52 @@
         </is>
       </c>
       <c r="M53" t="n">
-        <v>2313901</v>
+        <v>308821</v>
       </c>
       <c r="N53" t="n">
-        <v>370728</v>
+        <v>3957796</v>
       </c>
       <c r="O53" t="n">
-        <v>250144</v>
+        <v>4024899</v>
       </c>
       <c r="P53" t="n">
-        <v>24279233</v>
+        <v>11372260</v>
       </c>
       <c r="Q53" t="n">
-        <v>321307</v>
+        <v>-7047630</v>
       </c>
       <c r="R53" t="n">
-        <v>-221389</v>
+        <v>-10674601</v>
       </c>
       <c r="S53" t="n">
-        <v>-2037822</v>
+        <v>-12185803</v>
       </c>
       <c r="T53" t="n">
-        <v>15623405</v>
+        <v>-6728898</v>
       </c>
       <c r="U53" t="n">
-        <v>2035000</v>
+        <v>7357000</v>
       </c>
       <c r="V53" t="n">
-        <v>615000</v>
+        <v>14531000</v>
       </c>
       <c r="W53" t="n">
-        <v>662000</v>
+        <v>16214000</v>
       </c>
       <c r="X53" t="n">
-        <v>6011000</v>
+        <v>18150000</v>
       </c>
       <c r="Y53" t="n">
-        <v>-42406</v>
+        <v>-549</v>
       </c>
       <c r="Z53" t="n">
-        <v>-22883</v>
+        <v>101397</v>
       </c>
       <c r="AA53" t="n">
-        <v>1625966</v>
+        <v>-3298</v>
       </c>
       <c r="AB53" t="n">
-        <v>2644828</v>
+        <v>-48842</v>
       </c>
       <c r="AC53" t="n">
         <v>26</v>
@@ -7710,10 +7710,10 @@
         <v>26</v>
       </c>
       <c r="AE53" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="AF53" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="AG53" t="n">
         <v>0</v>
@@ -7733,59 +7733,59 @@
       </c>
       <c r="AM53" t="inlineStr">
         <is>
-          <t>跌破5日線、多頭排列、量能溫和放大</t>
+          <t>跌破5日線、黃金交叉、量能溫和放大、接近20日低點</t>
         </is>
       </c>
       <c r="AN53" t="inlineStr">
         <is>
-          <t>法人連續偏買、5日法人買超、投信買外資賣</t>
+          <t>法人連續偏買、5日法人明顯買超、投信買外資賣</t>
         </is>
       </c>
       <c r="AO53" t="inlineStr">
         <is>
-          <t>整理觀察：跌破5日線、多頭排列、量能溫和放大、法人連續偏買、5日法人買超、投信買外資賣。多空訊號混合，建議降低追價衝動。</t>
+          <t>整理觀察：跌破5日線、黃金交叉、量能溫和放大、接近20日低點、法人連續偏買、5日法人明顯買超、投信買外資賣。多空訊號混合，建議降低追價衝動。</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>3055.TW</t>
+          <t>00757.TW</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>蔚華科</t>
+          <t>統一FANG+</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>個股</t>
+          <t>ETF</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>161.5</v>
+        <v>131.35</v>
       </c>
       <c r="E54" t="n">
-        <v>174.6</v>
+        <v>132.69</v>
       </c>
       <c r="F54" t="n">
-        <v>169.9</v>
+        <v>131.46</v>
       </c>
       <c r="G54" t="n">
-        <v>141.06</v>
+        <v>129.09</v>
       </c>
       <c r="H54" t="n">
-        <v>810224</v>
+        <v>975781</v>
       </c>
       <c r="I54" t="n">
-        <v>1170516</v>
+        <v>2578943</v>
       </c>
       <c r="J54" t="n">
-        <v>201</v>
+        <v>135.45</v>
       </c>
       <c r="K54" t="n">
-        <v>88.09999999999999</v>
+        <v>121.35</v>
       </c>
       <c r="L54" t="inlineStr">
         <is>
@@ -7793,28 +7793,28 @@
         </is>
       </c>
       <c r="M54" t="n">
-        <v>219858</v>
+        <v>528637</v>
       </c>
       <c r="N54" t="n">
-        <v>742952</v>
+        <v>2945346</v>
       </c>
       <c r="O54" t="n">
-        <v>967947</v>
+        <v>4296148</v>
       </c>
       <c r="P54" t="n">
-        <v>1999499</v>
+        <v>8128274</v>
       </c>
       <c r="Q54" t="n">
-        <v>221858</v>
+        <v>7068</v>
       </c>
       <c r="R54" t="n">
-        <v>644507</v>
+        <v>549228</v>
       </c>
       <c r="S54" t="n">
-        <v>849507</v>
+        <v>1003224</v>
       </c>
       <c r="T54" t="n">
-        <v>1762369</v>
+        <v>4383152</v>
       </c>
       <c r="U54" t="n">
         <v>0</v>
@@ -7829,16 +7829,16 @@
         <v>0</v>
       </c>
       <c r="Y54" t="n">
-        <v>-2000</v>
+        <v>521569</v>
       </c>
       <c r="Z54" t="n">
-        <v>98445</v>
+        <v>2396118</v>
       </c>
       <c r="AA54" t="n">
-        <v>118440</v>
+        <v>3292924</v>
       </c>
       <c r="AB54" t="n">
-        <v>237130</v>
+        <v>3745122</v>
       </c>
       <c r="AC54" t="n">
         <v>26</v>
@@ -7887,12 +7887,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2542.TW</t>
+          <t>6669.TW</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>興富發</t>
+          <t>緯穎</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -7901,28 +7901,28 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>43.3</v>
+        <v>4685</v>
       </c>
       <c r="E55" t="n">
-        <v>43.36</v>
+        <v>4884</v>
       </c>
       <c r="F55" t="n">
-        <v>43.61</v>
+        <v>4952</v>
       </c>
       <c r="G55" t="n">
-        <v>43.3</v>
+        <v>4859.75</v>
       </c>
       <c r="H55" t="n">
-        <v>14382651</v>
+        <v>1414812</v>
       </c>
       <c r="I55" t="n">
-        <v>9716324</v>
+        <v>1141671</v>
       </c>
       <c r="J55" t="n">
-        <v>45</v>
+        <v>5325</v>
       </c>
       <c r="K55" t="n">
-        <v>41.95</v>
+        <v>4250</v>
       </c>
       <c r="L55" t="inlineStr">
         <is>
@@ -7930,64 +7930,64 @@
         </is>
       </c>
       <c r="M55" t="n">
-        <v>308821</v>
+        <v>243498</v>
       </c>
       <c r="N55" t="n">
-        <v>3957796</v>
+        <v>150139</v>
       </c>
       <c r="O55" t="n">
-        <v>4024899</v>
+        <v>384451</v>
       </c>
       <c r="P55" t="n">
-        <v>11372260</v>
+        <v>960278</v>
       </c>
       <c r="Q55" t="n">
-        <v>-7047630</v>
+        <v>181116</v>
       </c>
       <c r="R55" t="n">
-        <v>-10674601</v>
+        <v>198830</v>
       </c>
       <c r="S55" t="n">
-        <v>-12185803</v>
+        <v>268750</v>
       </c>
       <c r="T55" t="n">
-        <v>-6728898</v>
+        <v>-429219</v>
       </c>
       <c r="U55" t="n">
-        <v>7357000</v>
+        <v>29573</v>
       </c>
       <c r="V55" t="n">
-        <v>14531000</v>
+        <v>-25854</v>
       </c>
       <c r="W55" t="n">
-        <v>16214000</v>
+        <v>64388</v>
       </c>
       <c r="X55" t="n">
-        <v>18150000</v>
+        <v>1385186</v>
       </c>
       <c r="Y55" t="n">
-        <v>-549</v>
+        <v>32809</v>
       </c>
       <c r="Z55" t="n">
-        <v>101397</v>
+        <v>-22837</v>
       </c>
       <c r="AA55" t="n">
-        <v>-3298</v>
+        <v>51313</v>
       </c>
       <c r="AB55" t="n">
-        <v>-48842</v>
+        <v>4311</v>
       </c>
       <c r="AC55" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AD55" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AE55" t="n">
-        <v>5</v>
+        <v>-10</v>
       </c>
       <c r="AF55" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="AG55" t="n">
         <v>0</v>
@@ -8007,29 +8007,29 @@
       </c>
       <c r="AM55" t="inlineStr">
         <is>
-          <t>跌破5日線、黃金交叉、量能溫和放大、接近20日低點</t>
+          <t>跌破5日線、量能溫和放大</t>
         </is>
       </c>
       <c r="AN55" t="inlineStr">
         <is>
-          <t>法人連續偏買、5日法人明顯買超、投信買外資賣</t>
+          <t>法人連續偏買、5日法人買超、外資投信同步買超</t>
         </is>
       </c>
       <c r="AO55" t="inlineStr">
         <is>
-          <t>整理觀察：跌破5日線、黃金交叉、量能溫和放大、接近20日低點、法人連續偏買、5日法人明顯買超、投信買外資賣。多空訊號混合，建議降低追價衝動。</t>
+          <t>整理觀察：跌破5日線、量能溫和放大、法人連續偏買、5日法人買超、外資投信同步買超。多空訊號混合，建議降低追價衝動。</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>6669.TW</t>
+          <t>1234.TW</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>緯穎</t>
+          <t>黑松</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -8038,28 +8038,28 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>4685</v>
+        <v>34</v>
       </c>
       <c r="E56" t="n">
-        <v>4884</v>
+        <v>33.73</v>
       </c>
       <c r="F56" t="n">
-        <v>4952</v>
+        <v>33.49</v>
       </c>
       <c r="G56" t="n">
-        <v>4859.75</v>
+        <v>33.82</v>
       </c>
       <c r="H56" t="n">
-        <v>1414812</v>
+        <v>170809</v>
       </c>
       <c r="I56" t="n">
-        <v>1141671</v>
+        <v>189193</v>
       </c>
       <c r="J56" t="n">
-        <v>5325</v>
+        <v>35.5</v>
       </c>
       <c r="K56" t="n">
-        <v>4250</v>
+        <v>33</v>
       </c>
       <c r="L56" t="inlineStr">
         <is>
@@ -8067,52 +8067,52 @@
         </is>
       </c>
       <c r="M56" t="n">
-        <v>243498</v>
+        <v>135700</v>
       </c>
       <c r="N56" t="n">
-        <v>150139</v>
+        <v>217222</v>
       </c>
       <c r="O56" t="n">
-        <v>384451</v>
+        <v>418609</v>
       </c>
       <c r="P56" t="n">
-        <v>960278</v>
+        <v>527843</v>
       </c>
       <c r="Q56" t="n">
-        <v>181116</v>
+        <v>129700</v>
       </c>
       <c r="R56" t="n">
-        <v>198830</v>
+        <v>205222</v>
       </c>
       <c r="S56" t="n">
-        <v>268750</v>
+        <v>392609</v>
       </c>
       <c r="T56" t="n">
-        <v>-429219</v>
+        <v>519231</v>
       </c>
       <c r="U56" t="n">
-        <v>29573</v>
+        <v>0</v>
       </c>
       <c r="V56" t="n">
-        <v>-25854</v>
+        <v>0</v>
       </c>
       <c r="W56" t="n">
-        <v>64388</v>
+        <v>0</v>
       </c>
       <c r="X56" t="n">
-        <v>1385186</v>
+        <v>0</v>
       </c>
       <c r="Y56" t="n">
-        <v>32809</v>
+        <v>6000</v>
       </c>
       <c r="Z56" t="n">
-        <v>-22837</v>
+        <v>12000</v>
       </c>
       <c r="AA56" t="n">
-        <v>51313</v>
+        <v>26000</v>
       </c>
       <c r="AB56" t="n">
-        <v>4311</v>
+        <v>8612</v>
       </c>
       <c r="AC56" t="n">
         <v>24</v>
@@ -8121,10 +8121,10 @@
         <v>24</v>
       </c>
       <c r="AE56" t="n">
-        <v>-10</v>
+        <v>10</v>
       </c>
       <c r="AF56" t="n">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="AG56" t="n">
         <v>0</v>
@@ -8144,17 +8144,17 @@
       </c>
       <c r="AM56" t="inlineStr">
         <is>
-          <t>跌破5日線、量能溫和放大</t>
+          <t>站上5日線、量能未放大、接近20日低點</t>
         </is>
       </c>
       <c r="AN56" t="inlineStr">
         <is>
-          <t>法人連續偏買、5日法人買超、外資投信同步買超</t>
+          <t>法人連續偏買、5日法人買超</t>
         </is>
       </c>
       <c r="AO56" t="inlineStr">
         <is>
-          <t>整理觀察：跌破5日線、量能溫和放大、法人連續偏買、5日法人買超、外資投信同步買超。多空訊號混合，建議降低追價衝動。</t>
+          <t>整理觀察：站上5日線、量能未放大、接近20日低點、法人連續偏買、5日法人買超。多空訊號混合，建議降低追價衝動。</t>
         </is>
       </c>
     </row>
@@ -8435,12 +8435,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>1234.TW</t>
+          <t>8028.TW</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>黑松</t>
+          <t>昇陽半導體</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -8449,28 +8449,28 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>34</v>
+        <v>300</v>
       </c>
       <c r="E59" t="n">
-        <v>33.73</v>
+        <v>315</v>
       </c>
       <c r="F59" t="n">
-        <v>33.49</v>
+        <v>313.6</v>
       </c>
       <c r="G59" t="n">
-        <v>33.82</v>
+        <v>311.9</v>
       </c>
       <c r="H59" t="n">
-        <v>170809</v>
+        <v>9537577</v>
       </c>
       <c r="I59" t="n">
-        <v>189193</v>
+        <v>10678129</v>
       </c>
       <c r="J59" t="n">
-        <v>35.5</v>
+        <v>364</v>
       </c>
       <c r="K59" t="n">
-        <v>33</v>
+        <v>276</v>
       </c>
       <c r="L59" t="inlineStr">
         <is>
@@ -8478,61 +8478,61 @@
         </is>
       </c>
       <c r="M59" t="n">
-        <v>135700</v>
+        <v>-398183</v>
       </c>
       <c r="N59" t="n">
-        <v>217222</v>
+        <v>6096521</v>
       </c>
       <c r="O59" t="n">
-        <v>418609</v>
+        <v>6949822</v>
       </c>
       <c r="P59" t="n">
-        <v>527843</v>
+        <v>6806680</v>
       </c>
       <c r="Q59" t="n">
-        <v>129700</v>
+        <v>-393511</v>
       </c>
       <c r="R59" t="n">
-        <v>205222</v>
+        <v>5739319</v>
       </c>
       <c r="S59" t="n">
-        <v>392609</v>
+        <v>6535054</v>
       </c>
       <c r="T59" t="n">
-        <v>519231</v>
+        <v>7556228</v>
       </c>
       <c r="U59" t="n">
         <v>0</v>
       </c>
       <c r="V59" t="n">
-        <v>0</v>
+        <v>537000</v>
       </c>
       <c r="W59" t="n">
-        <v>0</v>
+        <v>566000</v>
       </c>
       <c r="X59" t="n">
-        <v>0</v>
+        <v>-343100</v>
       </c>
       <c r="Y59" t="n">
-        <v>6000</v>
+        <v>-4672</v>
       </c>
       <c r="Z59" t="n">
-        <v>12000</v>
+        <v>-179798</v>
       </c>
       <c r="AA59" t="n">
-        <v>26000</v>
+        <v>-151232</v>
       </c>
       <c r="AB59" t="n">
-        <v>8612</v>
+        <v>-406448</v>
       </c>
       <c r="AC59" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AD59" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AE59" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="AF59" t="n">
         <v>50</v>
@@ -8555,29 +8555,29 @@
       </c>
       <c r="AM59" t="inlineStr">
         <is>
-          <t>站上5日線、量能未放大、接近20日低點</t>
+          <t>跌破5日線、多頭排列、量能未放大</t>
         </is>
       </c>
       <c r="AN59" t="inlineStr">
         <is>
-          <t>法人連續偏買、5日法人買超</t>
+          <t>5日法人明顯買超、外資投信同步買超</t>
         </is>
       </c>
       <c r="AO59" t="inlineStr">
         <is>
-          <t>整理觀察：站上5日線、量能未放大、接近20日低點、法人連續偏買、5日法人買超。多空訊號混合，建議降低追價衝動。</t>
+          <t>整理觀察：跌破5日線、多頭排列、量能未放大、5日法人明顯買超、外資投信同步買超。多空訊號混合，建議降低追價衝動。</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2707.TW</t>
+          <t>3045.TW</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>晶華</t>
+          <t>台灣大</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -8586,28 +8586,28 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>179.5</v>
+        <v>112</v>
       </c>
       <c r="E60" t="n">
-        <v>179.5</v>
+        <v>110.3</v>
       </c>
       <c r="F60" t="n">
-        <v>179.9</v>
+        <v>111.65</v>
       </c>
       <c r="G60" t="n">
-        <v>179.5</v>
+        <v>114.97</v>
       </c>
       <c r="H60" t="n">
-        <v>115746</v>
+        <v>18734382</v>
       </c>
       <c r="I60" t="n">
-        <v>135679</v>
+        <v>19121741</v>
       </c>
       <c r="J60" t="n">
-        <v>183</v>
+        <v>120.5</v>
       </c>
       <c r="K60" t="n">
-        <v>177</v>
+        <v>106</v>
       </c>
       <c r="L60" t="inlineStr">
         <is>
@@ -8615,52 +8615,52 @@
         </is>
       </c>
       <c r="M60" t="n">
-        <v>51000</v>
+        <v>5066246</v>
       </c>
       <c r="N60" t="n">
-        <v>154821</v>
+        <v>25526468</v>
       </c>
       <c r="O60" t="n">
-        <v>239753</v>
+        <v>36058104</v>
       </c>
       <c r="P60" t="n">
-        <v>534855</v>
+        <v>59951498</v>
       </c>
       <c r="Q60" t="n">
-        <v>47000</v>
+        <v>4798233</v>
       </c>
       <c r="R60" t="n">
-        <v>145063</v>
+        <v>31892868</v>
       </c>
       <c r="S60" t="n">
-        <v>231995</v>
+        <v>41842315</v>
       </c>
       <c r="T60" t="n">
-        <v>530097</v>
+        <v>56675536</v>
       </c>
       <c r="U60" t="n">
-        <v>0</v>
+        <v>-759397</v>
       </c>
       <c r="V60" t="n">
-        <v>4000</v>
+        <v>-8914208</v>
       </c>
       <c r="W60" t="n">
-        <v>3000</v>
+        <v>-9061118</v>
       </c>
       <c r="X60" t="n">
-        <v>2000</v>
+        <v>1493105</v>
       </c>
       <c r="Y60" t="n">
-        <v>4000</v>
+        <v>1027410</v>
       </c>
       <c r="Z60" t="n">
-        <v>5758</v>
+        <v>2547808</v>
       </c>
       <c r="AA60" t="n">
-        <v>4758</v>
+        <v>3276907</v>
       </c>
       <c r="AB60" t="n">
-        <v>2758</v>
+        <v>1782857</v>
       </c>
       <c r="AC60" t="n">
         <v>22</v>
@@ -8669,10 +8669,10 @@
         <v>22</v>
       </c>
       <c r="AE60" t="n">
-        <v>-15</v>
+        <v>-5</v>
       </c>
       <c r="AF60" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="AG60" t="n">
         <v>0</v>
@@ -8692,17 +8692,17 @@
       </c>
       <c r="AM60" t="inlineStr">
         <is>
-          <t>跌破5日線、量能未放大、接近20日高點、接近20日低點</t>
+          <t>站上5日線、空頭排列、量能未放大</t>
         </is>
       </c>
       <c r="AN60" t="inlineStr">
         <is>
-          <t>法人連續偏買、5日法人買超、外資投信同步買超</t>
+          <t>法人連續偏買、5日法人明顯買超、外資買投信賣</t>
         </is>
       </c>
       <c r="AO60" t="inlineStr">
         <is>
-          <t>整理觀察：跌破5日線、量能未放大、接近20日高點、接近20日低點、法人連續偏買、5日法人買超、外資投信同步買超。多空訊號混合，建議降低追價衝動。</t>
+          <t>整理觀察：站上5日線、空頭排列、量能未放大、法人連續偏買、5日法人明顯買超、外資買投信賣。多空訊號混合，建議降低追價衝動。</t>
         </is>
       </c>
     </row>
@@ -9120,12 +9120,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>3045.TW</t>
+          <t>2707.TW</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>台灣大</t>
+          <t>晶華</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -9134,28 +9134,28 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>112</v>
+        <v>179.5</v>
       </c>
       <c r="E64" t="n">
-        <v>110.3</v>
+        <v>179.5</v>
       </c>
       <c r="F64" t="n">
-        <v>111.65</v>
+        <v>179.9</v>
       </c>
       <c r="G64" t="n">
-        <v>114.97</v>
+        <v>179.5</v>
       </c>
       <c r="H64" t="n">
-        <v>18734382</v>
+        <v>115746</v>
       </c>
       <c r="I64" t="n">
-        <v>19121741</v>
+        <v>135679</v>
       </c>
       <c r="J64" t="n">
-        <v>120.5</v>
+        <v>183</v>
       </c>
       <c r="K64" t="n">
-        <v>106</v>
+        <v>177</v>
       </c>
       <c r="L64" t="inlineStr">
         <is>
@@ -9163,52 +9163,52 @@
         </is>
       </c>
       <c r="M64" t="n">
-        <v>5066246</v>
+        <v>51000</v>
       </c>
       <c r="N64" t="n">
-        <v>25526468</v>
+        <v>154821</v>
       </c>
       <c r="O64" t="n">
-        <v>36058104</v>
+        <v>239753</v>
       </c>
       <c r="P64" t="n">
-        <v>59951498</v>
+        <v>534855</v>
       </c>
       <c r="Q64" t="n">
-        <v>4798233</v>
+        <v>47000</v>
       </c>
       <c r="R64" t="n">
-        <v>31892868</v>
+        <v>145063</v>
       </c>
       <c r="S64" t="n">
-        <v>41842315</v>
+        <v>231995</v>
       </c>
       <c r="T64" t="n">
-        <v>56675536</v>
+        <v>530097</v>
       </c>
       <c r="U64" t="n">
-        <v>-759397</v>
+        <v>0</v>
       </c>
       <c r="V64" t="n">
-        <v>-8914208</v>
+        <v>4000</v>
       </c>
       <c r="W64" t="n">
-        <v>-9061118</v>
+        <v>3000</v>
       </c>
       <c r="X64" t="n">
-        <v>1493105</v>
+        <v>2000</v>
       </c>
       <c r="Y64" t="n">
-        <v>1027410</v>
+        <v>4000</v>
       </c>
       <c r="Z64" t="n">
-        <v>2547808</v>
+        <v>5758</v>
       </c>
       <c r="AA64" t="n">
-        <v>3276907</v>
+        <v>4758</v>
       </c>
       <c r="AB64" t="n">
-        <v>1782857</v>
+        <v>2758</v>
       </c>
       <c r="AC64" t="n">
         <v>22</v>
@@ -9217,10 +9217,10 @@
         <v>22</v>
       </c>
       <c r="AE64" t="n">
-        <v>-5</v>
+        <v>-15</v>
       </c>
       <c r="AF64" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="AG64" t="n">
         <v>0</v>
@@ -9240,17 +9240,17 @@
       </c>
       <c r="AM64" t="inlineStr">
         <is>
-          <t>站上5日線、空頭排列、量能未放大</t>
+          <t>跌破5日線、量能未放大、接近20日高點、接近20日低點</t>
         </is>
       </c>
       <c r="AN64" t="inlineStr">
         <is>
-          <t>法人連續偏買、5日法人明顯買超、外資買投信賣</t>
+          <t>法人連續偏買、5日法人買超、外資投信同步買超</t>
         </is>
       </c>
       <c r="AO64" t="inlineStr">
         <is>
-          <t>整理觀察：站上5日線、空頭排列、量能未放大、法人連續偏買、5日法人明顯買超、外資買投信賣。多空訊號混合，建議降低追價衝動。</t>
+          <t>整理觀察：跌破5日線、量能未放大、接近20日高點、接近20日低點、法人連續偏買、5日法人買超、外資投信同步買超。多空訊號混合，建議降低追價衝動。</t>
         </is>
       </c>
     </row>
@@ -9531,12 +9531,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>8028.TW</t>
+          <t>3231.TW</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>昇陽半導體</t>
+          <t>緯創</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -9545,28 +9545,28 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>300</v>
+        <v>143.5</v>
       </c>
       <c r="E67" t="n">
-        <v>315</v>
+        <v>143.4</v>
       </c>
       <c r="F67" t="n">
-        <v>313.6</v>
+        <v>146.5</v>
       </c>
       <c r="G67" t="n">
-        <v>311.9</v>
+        <v>152.32</v>
       </c>
       <c r="H67" t="n">
-        <v>9537577</v>
+        <v>51717481</v>
       </c>
       <c r="I67" t="n">
-        <v>10678129</v>
+        <v>35013897</v>
       </c>
       <c r="J67" t="n">
-        <v>364</v>
+        <v>166</v>
       </c>
       <c r="K67" t="n">
-        <v>276</v>
+        <v>139</v>
       </c>
       <c r="L67" t="inlineStr">
         <is>
@@ -9574,52 +9574,52 @@
         </is>
       </c>
       <c r="M67" t="n">
-        <v>-398183</v>
+        <v>11945523</v>
       </c>
       <c r="N67" t="n">
-        <v>6096521</v>
+        <v>10573698</v>
       </c>
       <c r="O67" t="n">
-        <v>6949822</v>
+        <v>16489013</v>
       </c>
       <c r="P67" t="n">
-        <v>6806680</v>
+        <v>-15218980</v>
       </c>
       <c r="Q67" t="n">
-        <v>-393511</v>
+        <v>11142193</v>
       </c>
       <c r="R67" t="n">
-        <v>5739319</v>
+        <v>21515813</v>
       </c>
       <c r="S67" t="n">
-        <v>6535054</v>
+        <v>25869313</v>
       </c>
       <c r="T67" t="n">
-        <v>7556228</v>
+        <v>-4147962</v>
       </c>
       <c r="U67" t="n">
-        <v>0</v>
+        <v>-1380751</v>
       </c>
       <c r="V67" t="n">
-        <v>537000</v>
+        <v>-13240898</v>
       </c>
       <c r="W67" t="n">
-        <v>566000</v>
+        <v>-13436453</v>
       </c>
       <c r="X67" t="n">
-        <v>-343100</v>
+        <v>-6965930</v>
       </c>
       <c r="Y67" t="n">
-        <v>-4672</v>
+        <v>2184081</v>
       </c>
       <c r="Z67" t="n">
-        <v>-179798</v>
+        <v>2298783</v>
       </c>
       <c r="AA67" t="n">
-        <v>-151232</v>
+        <v>4056153</v>
       </c>
       <c r="AB67" t="n">
-        <v>-406448</v>
+        <v>-4105088</v>
       </c>
       <c r="AC67" t="n">
         <v>22</v>
@@ -9628,10 +9628,10 @@
         <v>22</v>
       </c>
       <c r="AE67" t="n">
-        <v>5</v>
+        <v>-5</v>
       </c>
       <c r="AF67" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="AG67" t="n">
         <v>0</v>
@@ -9651,29 +9651,29 @@
       </c>
       <c r="AM67" t="inlineStr">
         <is>
-          <t>跌破5日線、多頭排列、量能未放大</t>
+          <t>站上5日線、空頭排列、量能溫和放大、接近20日低點</t>
         </is>
       </c>
       <c r="AN67" t="inlineStr">
         <is>
-          <t>5日法人明顯買超、外資投信同步買超</t>
+          <t>法人連續偏買、5日法人明顯買超、外資買投信賣</t>
         </is>
       </c>
       <c r="AO67" t="inlineStr">
         <is>
-          <t>整理觀察：跌破5日線、多頭排列、量能未放大、5日法人明顯買超、外資投信同步買超。多空訊號混合，建議降低追價衝動。</t>
+          <t>整理觀察：站上5日線、空頭排列、量能溫和放大、接近20日低點、法人連續偏買、5日法人明顯買超、外資買投信賣。多空訊號混合，建議降低追價衝動。</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>3231.TW</t>
+          <t>2881.TW</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>富邦金</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -9682,28 +9682,28 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>143.5</v>
+        <v>123.5</v>
       </c>
       <c r="E68" t="n">
-        <v>143.4</v>
+        <v>125.3</v>
       </c>
       <c r="F68" t="n">
-        <v>146.5</v>
+        <v>124.85</v>
       </c>
       <c r="G68" t="n">
-        <v>152.32</v>
+        <v>127.5</v>
       </c>
       <c r="H68" t="n">
-        <v>51717481</v>
+        <v>26626575</v>
       </c>
       <c r="I68" t="n">
-        <v>35013897</v>
+        <v>28186357</v>
       </c>
       <c r="J68" t="n">
-        <v>166</v>
+        <v>141</v>
       </c>
       <c r="K68" t="n">
-        <v>139</v>
+        <v>118</v>
       </c>
       <c r="L68" t="inlineStr">
         <is>
@@ -9711,64 +9711,64 @@
         </is>
       </c>
       <c r="M68" t="n">
-        <v>11945523</v>
+        <v>5673121</v>
       </c>
       <c r="N68" t="n">
-        <v>10573698</v>
+        <v>11340536</v>
       </c>
       <c r="O68" t="n">
-        <v>16489013</v>
+        <v>18981986</v>
       </c>
       <c r="P68" t="n">
-        <v>-15218980</v>
+        <v>22290184</v>
       </c>
       <c r="Q68" t="n">
-        <v>11142193</v>
+        <v>-1554649</v>
       </c>
       <c r="R68" t="n">
-        <v>21515813</v>
+        <v>-300472</v>
       </c>
       <c r="S68" t="n">
-        <v>25869313</v>
+        <v>6343340</v>
       </c>
       <c r="T68" t="n">
-        <v>-4147962</v>
+        <v>14926904</v>
       </c>
       <c r="U68" t="n">
-        <v>-1380751</v>
+        <v>5882895</v>
       </c>
       <c r="V68" t="n">
-        <v>-13240898</v>
+        <v>8397263</v>
       </c>
       <c r="W68" t="n">
-        <v>-13436453</v>
+        <v>8048467</v>
       </c>
       <c r="X68" t="n">
-        <v>-6965930</v>
+        <v>3115111</v>
       </c>
       <c r="Y68" t="n">
-        <v>2184081</v>
+        <v>1344875</v>
       </c>
       <c r="Z68" t="n">
-        <v>2298783</v>
+        <v>3243745</v>
       </c>
       <c r="AA68" t="n">
-        <v>4056153</v>
+        <v>4590179</v>
       </c>
       <c r="AB68" t="n">
-        <v>-4105088</v>
+        <v>4248169</v>
       </c>
       <c r="AC68" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AD68" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AE68" t="n">
-        <v>-5</v>
+        <v>-30</v>
       </c>
       <c r="AF68" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="AG68" t="n">
         <v>0</v>
@@ -9788,29 +9788,29 @@
       </c>
       <c r="AM68" t="inlineStr">
         <is>
-          <t>站上5日線、空頭排列、量能溫和放大、接近20日低點</t>
+          <t>跌破5日線、量能未放大、接近20日低點</t>
         </is>
       </c>
       <c r="AN68" t="inlineStr">
         <is>
-          <t>法人連續偏買、5日法人明顯買超、外資買投信賣</t>
+          <t>法人連續偏買、5日法人明顯買超、外資投信同步買超</t>
         </is>
       </c>
       <c r="AO68" t="inlineStr">
         <is>
-          <t>整理觀察：站上5日線、空頭排列、量能溫和放大、接近20日低點、法人連續偏買、5日法人明顯買超、外資買投信賣。多空訊號混合，建議降低追價衝動。</t>
+          <t>整理觀察：跌破5日線、量能未放大、接近20日低點、法人連續偏買、5日法人明顯買超、外資投信同步買超。多空訊號混合，建議降低追價衝動。</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2881.TW</t>
+          <t>2362.TW</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>富邦金</t>
+          <t>藍天</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -9819,28 +9819,28 @@
         </is>
       </c>
       <c r="D69" t="n">
-        <v>123.5</v>
+        <v>41.9</v>
       </c>
       <c r="E69" t="n">
-        <v>125.3</v>
+        <v>41.67</v>
       </c>
       <c r="F69" t="n">
-        <v>124.85</v>
+        <v>42.58</v>
       </c>
       <c r="G69" t="n">
-        <v>127.5</v>
+        <v>42.89</v>
       </c>
       <c r="H69" t="n">
-        <v>26626575</v>
+        <v>1381960</v>
       </c>
       <c r="I69" t="n">
-        <v>28186357</v>
+        <v>863840</v>
       </c>
       <c r="J69" t="n">
-        <v>141</v>
+        <v>48.3</v>
       </c>
       <c r="K69" t="n">
-        <v>118</v>
+        <v>40.4</v>
       </c>
       <c r="L69" t="inlineStr">
         <is>
@@ -9848,52 +9848,52 @@
         </is>
       </c>
       <c r="M69" t="n">
-        <v>5673121</v>
+        <v>309889</v>
       </c>
       <c r="N69" t="n">
-        <v>11340536</v>
+        <v>133211</v>
       </c>
       <c r="O69" t="n">
-        <v>18981986</v>
+        <v>185703</v>
       </c>
       <c r="P69" t="n">
-        <v>22290184</v>
+        <v>-428727</v>
       </c>
       <c r="Q69" t="n">
-        <v>-1554649</v>
+        <v>292889</v>
       </c>
       <c r="R69" t="n">
-        <v>-300472</v>
+        <v>412991</v>
       </c>
       <c r="S69" t="n">
-        <v>6343340</v>
+        <v>462363</v>
       </c>
       <c r="T69" t="n">
-        <v>14926904</v>
+        <v>-114050</v>
       </c>
       <c r="U69" t="n">
-        <v>5882895</v>
+        <v>0</v>
       </c>
       <c r="V69" t="n">
-        <v>8397263</v>
+        <v>-309000</v>
       </c>
       <c r="W69" t="n">
-        <v>8048467</v>
+        <v>-315000</v>
       </c>
       <c r="X69" t="n">
-        <v>3115111</v>
+        <v>-315000</v>
       </c>
       <c r="Y69" t="n">
-        <v>1344875</v>
+        <v>17000</v>
       </c>
       <c r="Z69" t="n">
-        <v>3243745</v>
+        <v>29220</v>
       </c>
       <c r="AA69" t="n">
-        <v>4590179</v>
+        <v>38340</v>
       </c>
       <c r="AB69" t="n">
-        <v>4248169</v>
+        <v>323</v>
       </c>
       <c r="AC69" t="n">
         <v>20</v>
@@ -9902,10 +9902,10 @@
         <v>20</v>
       </c>
       <c r="AE69" t="n">
-        <v>-30</v>
+        <v>0</v>
       </c>
       <c r="AF69" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="AG69" t="n">
         <v>0</v>
@@ -9925,17 +9925,17 @@
       </c>
       <c r="AM69" t="inlineStr">
         <is>
-          <t>跌破5日線、量能未放大、接近20日低點</t>
+          <t>站上5日線、空頭排列、成交量放大、接近20日低點</t>
         </is>
       </c>
       <c r="AN69" t="inlineStr">
         <is>
-          <t>法人連續偏買、5日法人明顯買超、外資投信同步買超</t>
+          <t>法人連續偏買、5日法人買超、外資買投信賣</t>
         </is>
       </c>
       <c r="AO69" t="inlineStr">
         <is>
-          <t>整理觀察：跌破5日線、量能未放大、接近20日低點、法人連續偏買、5日法人明顯買超、外資投信同步買超。多空訊號混合，建議降低追價衝動。</t>
+          <t>整理觀察：站上5日線、空頭排列、成交量放大、接近20日低點、法人連續偏買、5日法人買超、外資買投信賣。多空訊號混合，建議降低追價衝動。</t>
         </is>
       </c>
     </row>
@@ -9968,10 +9968,10 @@
         <v>34.12</v>
       </c>
       <c r="H70" t="n">
-        <v>145907830</v>
+        <v>146407830</v>
       </c>
       <c r="I70" t="n">
-        <v>94592251</v>
+        <v>94692251</v>
       </c>
       <c r="J70" t="n">
         <v>37.75</v>
@@ -10079,12 +10079,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2362.TW</t>
+          <t>4967.TW</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>藍天</t>
+          <t>十銓</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -10093,28 +10093,28 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>41.9</v>
+        <v>208.5</v>
       </c>
       <c r="E71" t="n">
-        <v>41.67</v>
+        <v>219.6</v>
       </c>
       <c r="F71" t="n">
-        <v>42.58</v>
+        <v>230.4</v>
       </c>
       <c r="G71" t="n">
-        <v>42.89</v>
+        <v>248.68</v>
       </c>
       <c r="H71" t="n">
-        <v>1381960</v>
+        <v>2764713</v>
       </c>
       <c r="I71" t="n">
-        <v>863840</v>
+        <v>2373928</v>
       </c>
       <c r="J71" t="n">
-        <v>48.3</v>
+        <v>290</v>
       </c>
       <c r="K71" t="n">
-        <v>40.4</v>
+        <v>195.5</v>
       </c>
       <c r="L71" t="inlineStr">
         <is>
@@ -10122,64 +10122,64 @@
         </is>
       </c>
       <c r="M71" t="n">
-        <v>309889</v>
+        <v>463003</v>
       </c>
       <c r="N71" t="n">
-        <v>133211</v>
+        <v>843085</v>
       </c>
       <c r="O71" t="n">
-        <v>185703</v>
+        <v>1334982</v>
       </c>
       <c r="P71" t="n">
-        <v>-428727</v>
+        <v>545403</v>
       </c>
       <c r="Q71" t="n">
-        <v>292889</v>
+        <v>483478</v>
       </c>
       <c r="R71" t="n">
-        <v>412991</v>
+        <v>924978</v>
       </c>
       <c r="S71" t="n">
-        <v>462363</v>
+        <v>1485299</v>
       </c>
       <c r="T71" t="n">
-        <v>-114050</v>
+        <v>483640</v>
       </c>
       <c r="U71" t="n">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="V71" t="n">
-        <v>-309000</v>
+        <v>26000</v>
       </c>
       <c r="W71" t="n">
-        <v>-315000</v>
+        <v>26000</v>
       </c>
       <c r="X71" t="n">
-        <v>-315000</v>
+        <v>596000</v>
       </c>
       <c r="Y71" t="n">
-        <v>17000</v>
+        <v>-22475</v>
       </c>
       <c r="Z71" t="n">
-        <v>29220</v>
+        <v>-107893</v>
       </c>
       <c r="AA71" t="n">
-        <v>38340</v>
+        <v>-176317</v>
       </c>
       <c r="AB71" t="n">
-        <v>323</v>
+        <v>-534237</v>
       </c>
       <c r="AC71" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AD71" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AE71" t="n">
-        <v>0</v>
+        <v>-35</v>
       </c>
       <c r="AF71" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="AG71" t="n">
         <v>0</v>
@@ -10189,27 +10189,27 @@
       <c r="AJ71" t="inlineStr"/>
       <c r="AK71" t="inlineStr">
         <is>
-          <t>⚠️整理</t>
+          <t>❌避開</t>
         </is>
       </c>
       <c r="AL71" t="inlineStr">
         <is>
-          <t>整理觀察</t>
+          <t>觀望</t>
         </is>
       </c>
       <c r="AM71" t="inlineStr">
         <is>
-          <t>站上5日線、空頭排列、成交量放大、接近20日低點</t>
+          <t>跌破5日線、空頭排列、量能溫和放大</t>
         </is>
       </c>
       <c r="AN71" t="inlineStr">
         <is>
-          <t>法人連續偏買、5日法人買超、外資買投信賣</t>
+          <t>法人連續偏買、5日法人明顯買超、外資投信同步買超</t>
         </is>
       </c>
       <c r="AO71" t="inlineStr">
         <is>
-          <t>整理觀察：站上5日線、空頭排列、成交量放大、接近20日低點、法人連續偏買、5日法人買超、外資買投信賣。多空訊號混合，建議降低追價衝動。</t>
+          <t>風險偏高：跌破5日線、空頭排列、量能溫和放大、法人連續偏買、5日法人明顯買超、外資投信同步買超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
@@ -10353,12 +10353,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>4967.TW</t>
+          <t>6213.TW</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>十銓</t>
+          <t>聯茂</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -10367,28 +10367,28 @@
         </is>
       </c>
       <c r="D73" t="n">
-        <v>208.5</v>
+        <v>322.5</v>
       </c>
       <c r="E73" t="n">
-        <v>219.6</v>
+        <v>330</v>
       </c>
       <c r="F73" t="n">
-        <v>230.4</v>
+        <v>356.3</v>
       </c>
       <c r="G73" t="n">
-        <v>248.68</v>
+        <v>348.7</v>
       </c>
       <c r="H73" t="n">
-        <v>2764713</v>
+        <v>36321779</v>
       </c>
       <c r="I73" t="n">
-        <v>2373928</v>
+        <v>23187325</v>
       </c>
       <c r="J73" t="n">
-        <v>290</v>
+        <v>424.5</v>
       </c>
       <c r="K73" t="n">
-        <v>195.5</v>
+        <v>281</v>
       </c>
       <c r="L73" t="inlineStr">
         <is>
@@ -10396,52 +10396,52 @@
         </is>
       </c>
       <c r="M73" t="n">
-        <v>463003</v>
+        <v>-2768461</v>
       </c>
       <c r="N73" t="n">
-        <v>843085</v>
+        <v>1445710</v>
       </c>
       <c r="O73" t="n">
-        <v>1334982</v>
+        <v>1464418</v>
       </c>
       <c r="P73" t="n">
-        <v>545403</v>
+        <v>-8231515</v>
       </c>
       <c r="Q73" t="n">
-        <v>483478</v>
+        <v>-2790050</v>
       </c>
       <c r="R73" t="n">
-        <v>924978</v>
+        <v>128847</v>
       </c>
       <c r="S73" t="n">
-        <v>1485299</v>
+        <v>864077</v>
       </c>
       <c r="T73" t="n">
-        <v>483640</v>
+        <v>-12834528</v>
       </c>
       <c r="U73" t="n">
-        <v>2000</v>
+        <v>117000</v>
       </c>
       <c r="V73" t="n">
-        <v>26000</v>
+        <v>1734000</v>
       </c>
       <c r="W73" t="n">
-        <v>26000</v>
+        <v>1846000</v>
       </c>
       <c r="X73" t="n">
-        <v>596000</v>
+        <v>5949900</v>
       </c>
       <c r="Y73" t="n">
-        <v>-22475</v>
+        <v>-95411</v>
       </c>
       <c r="Z73" t="n">
-        <v>-107893</v>
+        <v>-417137</v>
       </c>
       <c r="AA73" t="n">
-        <v>-176317</v>
+        <v>-1245659</v>
       </c>
       <c r="AB73" t="n">
-        <v>-534237</v>
+        <v>-1346887</v>
       </c>
       <c r="AC73" t="n">
         <v>18</v>
@@ -10450,10 +10450,10 @@
         <v>18</v>
       </c>
       <c r="AE73" t="n">
-        <v>-35</v>
+        <v>-5</v>
       </c>
       <c r="AF73" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="AG73" t="n">
         <v>0</v>
@@ -10473,29 +10473,29 @@
       </c>
       <c r="AM73" t="inlineStr">
         <is>
-          <t>跌破5日線、空頭排列、量能溫和放大</t>
+          <t>跌破5日線、成交量放大</t>
         </is>
       </c>
       <c r="AN73" t="inlineStr">
         <is>
-          <t>法人連續偏買、5日法人明顯買超、外資投信同步買超</t>
+          <t>5日法人明顯買超、外資投信同步買超</t>
         </is>
       </c>
       <c r="AO73" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、空頭排列、量能溫和放大、法人連續偏買、5日法人明顯買超、外資投信同步買超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、成交量放大、5日法人明顯買超、外資投信同步買超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>6213.TW</t>
+          <t>2227.TW</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>聯茂</t>
+          <t>裕日車</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -10504,28 +10504,28 @@
         </is>
       </c>
       <c r="D74" t="n">
-        <v>322.5</v>
+        <v>49.8</v>
       </c>
       <c r="E74" t="n">
-        <v>330</v>
+        <v>50.09</v>
       </c>
       <c r="F74" t="n">
-        <v>356.3</v>
+        <v>49.92</v>
       </c>
       <c r="G74" t="n">
-        <v>348.7</v>
+        <v>49.65</v>
       </c>
       <c r="H74" t="n">
-        <v>36321779</v>
+        <v>64127</v>
       </c>
       <c r="I74" t="n">
-        <v>23187325</v>
+        <v>65871</v>
       </c>
       <c r="J74" t="n">
-        <v>424.5</v>
+        <v>51.5</v>
       </c>
       <c r="K74" t="n">
-        <v>281</v>
+        <v>48.1</v>
       </c>
       <c r="L74" t="inlineStr">
         <is>
@@ -10533,52 +10533,52 @@
         </is>
       </c>
       <c r="M74" t="n">
-        <v>-2768461</v>
+        <v>44000</v>
       </c>
       <c r="N74" t="n">
-        <v>1445710</v>
+        <v>77000</v>
       </c>
       <c r="O74" t="n">
-        <v>1464418</v>
+        <v>135000</v>
       </c>
       <c r="P74" t="n">
-        <v>-8231515</v>
+        <v>114000</v>
       </c>
       <c r="Q74" t="n">
-        <v>-2790050</v>
+        <v>38000</v>
       </c>
       <c r="R74" t="n">
-        <v>128847</v>
+        <v>67000</v>
       </c>
       <c r="S74" t="n">
-        <v>864077</v>
+        <v>123000</v>
       </c>
       <c r="T74" t="n">
-        <v>-12834528</v>
+        <v>102000</v>
       </c>
       <c r="U74" t="n">
-        <v>117000</v>
+        <v>0</v>
       </c>
       <c r="V74" t="n">
-        <v>1734000</v>
+        <v>0</v>
       </c>
       <c r="W74" t="n">
-        <v>1846000</v>
+        <v>0</v>
       </c>
       <c r="X74" t="n">
-        <v>5949900</v>
+        <v>0</v>
       </c>
       <c r="Y74" t="n">
-        <v>-95411</v>
+        <v>6000</v>
       </c>
       <c r="Z74" t="n">
-        <v>-417137</v>
+        <v>10000</v>
       </c>
       <c r="AA74" t="n">
-        <v>-1245659</v>
+        <v>12000</v>
       </c>
       <c r="AB74" t="n">
-        <v>-1346887</v>
+        <v>12000</v>
       </c>
       <c r="AC74" t="n">
         <v>18</v>
@@ -10610,29 +10610,29 @@
       </c>
       <c r="AM74" t="inlineStr">
         <is>
-          <t>跌破5日線、成交量放大</t>
+          <t>跌破5日線、多頭排列、量能未放大、接近20日低點</t>
         </is>
       </c>
       <c r="AN74" t="inlineStr">
         <is>
-          <t>5日法人明顯買超、外資投信同步買超</t>
+          <t>法人連續偏買、5日法人買超</t>
         </is>
       </c>
       <c r="AO74" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、成交量放大、5日法人明顯買超、外資投信同步買超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、多頭排列、量能未放大、接近20日低點、法人連續偏買、5日法人買超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2227.TW</t>
+          <t>2006.TW</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>裕日車</t>
+          <t>東和鋼鐵</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -10641,28 +10641,28 @@
         </is>
       </c>
       <c r="D75" t="n">
-        <v>49.8</v>
+        <v>70</v>
       </c>
       <c r="E75" t="n">
-        <v>50.09</v>
+        <v>70.92</v>
       </c>
       <c r="F75" t="n">
-        <v>49.92</v>
+        <v>70.13</v>
       </c>
       <c r="G75" t="n">
-        <v>49.65</v>
+        <v>69.7</v>
       </c>
       <c r="H75" t="n">
-        <v>64127</v>
+        <v>3116691</v>
       </c>
       <c r="I75" t="n">
-        <v>65871</v>
+        <v>3162982</v>
       </c>
       <c r="J75" t="n">
-        <v>51.5</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="K75" t="n">
-        <v>48.1</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="L75" t="inlineStr">
         <is>
@@ -10670,52 +10670,52 @@
         </is>
       </c>
       <c r="M75" t="n">
-        <v>44000</v>
+        <v>-681959</v>
       </c>
       <c r="N75" t="n">
-        <v>77000</v>
+        <v>3110425</v>
       </c>
       <c r="O75" t="n">
-        <v>135000</v>
+        <v>5970654</v>
       </c>
       <c r="P75" t="n">
-        <v>114000</v>
+        <v>7454068</v>
       </c>
       <c r="Q75" t="n">
-        <v>38000</v>
+        <v>-1272917</v>
       </c>
       <c r="R75" t="n">
-        <v>67000</v>
+        <v>2163363</v>
       </c>
       <c r="S75" t="n">
-        <v>123000</v>
+        <v>4570662</v>
       </c>
       <c r="T75" t="n">
-        <v>102000</v>
+        <v>5108810</v>
       </c>
       <c r="U75" t="n">
-        <v>0</v>
+        <v>609558</v>
       </c>
       <c r="V75" t="n">
-        <v>0</v>
+        <v>971965</v>
       </c>
       <c r="W75" t="n">
-        <v>0</v>
+        <v>1375965</v>
       </c>
       <c r="X75" t="n">
-        <v>0</v>
+        <v>2335918</v>
       </c>
       <c r="Y75" t="n">
-        <v>6000</v>
+        <v>-18600</v>
       </c>
       <c r="Z75" t="n">
-        <v>10000</v>
+        <v>-24903</v>
       </c>
       <c r="AA75" t="n">
-        <v>12000</v>
+        <v>24027</v>
       </c>
       <c r="AB75" t="n">
-        <v>12000</v>
+        <v>9340</v>
       </c>
       <c r="AC75" t="n">
         <v>18</v>
@@ -10752,12 +10752,12 @@
       </c>
       <c r="AN75" t="inlineStr">
         <is>
-          <t>法人連續偏買、5日法人買超</t>
+          <t>5日法人明顯買超、外資投信同步買超</t>
         </is>
       </c>
       <c r="AO75" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、多頭排列、量能未放大、接近20日低點、法人連續偏買、5日法人買超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、多頭排列、量能未放大、接近20日低點、5日法人明顯買超、外資投信同步買超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
@@ -11586,12 +11586,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2006.TW</t>
+          <t>2610.TW</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>東和鋼鐵</t>
+          <t>華航</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -11600,28 +11600,28 @@
         </is>
       </c>
       <c r="D82" t="n">
-        <v>70</v>
+        <v>20.95</v>
       </c>
       <c r="E82" t="n">
-        <v>70.92</v>
+        <v>20.84</v>
       </c>
       <c r="F82" t="n">
-        <v>70.13</v>
+        <v>21.31</v>
       </c>
       <c r="G82" t="n">
-        <v>69.7</v>
+        <v>22.13</v>
       </c>
       <c r="H82" t="n">
-        <v>3116691</v>
+        <v>36809973</v>
       </c>
       <c r="I82" t="n">
-        <v>3162982</v>
+        <v>42006567</v>
       </c>
       <c r="J82" t="n">
-        <v>72.59999999999999</v>
+        <v>24.75</v>
       </c>
       <c r="K82" t="n">
-        <v>67.09999999999999</v>
+        <v>20.1</v>
       </c>
       <c r="L82" t="inlineStr">
         <is>
@@ -11629,52 +11629,52 @@
         </is>
       </c>
       <c r="M82" t="n">
-        <v>-681959</v>
+        <v>7409917</v>
       </c>
       <c r="N82" t="n">
-        <v>3110425</v>
+        <v>16616990</v>
       </c>
       <c r="O82" t="n">
-        <v>5970654</v>
+        <v>16028265</v>
       </c>
       <c r="P82" t="n">
-        <v>7454068</v>
+        <v>28255752</v>
       </c>
       <c r="Q82" t="n">
-        <v>-1272917</v>
+        <v>1435561</v>
       </c>
       <c r="R82" t="n">
-        <v>2163363</v>
+        <v>17041423</v>
       </c>
       <c r="S82" t="n">
-        <v>4570662</v>
+        <v>46509284</v>
       </c>
       <c r="T82" t="n">
-        <v>5108810</v>
+        <v>55652435</v>
       </c>
       <c r="U82" t="n">
-        <v>609558</v>
+        <v>6164000</v>
       </c>
       <c r="V82" t="n">
-        <v>971965</v>
+        <v>217825</v>
       </c>
       <c r="W82" t="n">
-        <v>1375965</v>
+        <v>-29199625</v>
       </c>
       <c r="X82" t="n">
-        <v>2335918</v>
+        <v>-24572118</v>
       </c>
       <c r="Y82" t="n">
-        <v>-18600</v>
+        <v>-189644</v>
       </c>
       <c r="Z82" t="n">
-        <v>-24903</v>
+        <v>-642258</v>
       </c>
       <c r="AA82" t="n">
-        <v>24027</v>
+        <v>-1281394</v>
       </c>
       <c r="AB82" t="n">
-        <v>9340</v>
+        <v>-2824565</v>
       </c>
       <c r="AC82" t="n">
         <v>18</v>
@@ -11683,10 +11683,10 @@
         <v>18</v>
       </c>
       <c r="AE82" t="n">
-        <v>-5</v>
+        <v>-15</v>
       </c>
       <c r="AF82" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="AG82" t="n">
         <v>0</v>
@@ -11706,17 +11706,17 @@
       </c>
       <c r="AM82" t="inlineStr">
         <is>
-          <t>跌破5日線、多頭排列、量能未放大、接近20日低點</t>
+          <t>站上5日線、空頭排列、量能未放大、接近20日低點</t>
         </is>
       </c>
       <c r="AN82" t="inlineStr">
         <is>
-          <t>5日法人明顯買超、外資投信同步買超</t>
+          <t>法人連續偏買、5日法人明顯買超、外資買投信賣</t>
         </is>
       </c>
       <c r="AO82" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、多頭排列、量能未放大、接近20日低點、5日法人明顯買超、外資投信同步買超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、空頭排列、量能未放大、接近20日低點、法人連續偏買、5日法人明顯買超、外資買投信賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
@@ -22298,10 +22298,10 @@
         <v>68.53</v>
       </c>
       <c r="H160" t="n">
-        <v>69548055</v>
+        <v>69848055</v>
       </c>
       <c r="I160" t="n">
-        <v>73216178</v>
+        <v>73276178</v>
       </c>
       <c r="J160" t="n">
         <v>73.59999999999999</v>
@@ -32022,7 +32022,7 @@
         <v>47.52</v>
       </c>
       <c r="G231" t="n">
-        <v>48.04</v>
+        <v>48.81</v>
       </c>
       <c r="H231" t="n">
         <v>588000</v>
@@ -32031,7 +32031,7 @@
         <v>364000</v>
       </c>
       <c r="J231" t="n">
-        <v>51.7</v>
+        <v>54.9</v>
       </c>
       <c r="K231" t="n">
         <v>43.5</v>
@@ -32707,7 +32707,7 @@
         <v>916.3</v>
       </c>
       <c r="G236" t="n">
-        <v>969.9</v>
+        <v>968.65</v>
       </c>
       <c r="H236" t="n">
         <v>2399000</v>
@@ -32716,7 +32716,7 @@
         <v>2291000</v>
       </c>
       <c r="J236" t="n">
-        <v>1080</v>
+        <v>1105</v>
       </c>
       <c r="K236" t="n">
         <v>819</v>
@@ -40493,12 +40493,12 @@
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>1710.TW</t>
+          <t>6285.TW</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>東聯</t>
+          <t>啟碁</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
@@ -40507,28 +40507,28 @@
         </is>
       </c>
       <c r="D293" t="n">
-        <v>15.45</v>
+        <v>235</v>
       </c>
       <c r="E293" t="n">
-        <v>16.14</v>
+        <v>248.2</v>
       </c>
       <c r="F293" t="n">
-        <v>16.65</v>
+        <v>251.4</v>
       </c>
       <c r="G293" t="n">
-        <v>16.18</v>
+        <v>252.2</v>
       </c>
       <c r="H293" t="n">
-        <v>8337541</v>
+        <v>8934026</v>
       </c>
       <c r="I293" t="n">
-        <v>13366340</v>
+        <v>9668377</v>
       </c>
       <c r="J293" t="n">
-        <v>20.15</v>
+        <v>277.5</v>
       </c>
       <c r="K293" t="n">
-        <v>13.35</v>
+        <v>220.5</v>
       </c>
       <c r="L293" t="inlineStr">
         <is>
@@ -40536,52 +40536,52 @@
         </is>
       </c>
       <c r="M293" t="n">
-        <v>-1837278</v>
+        <v>669973</v>
       </c>
       <c r="N293" t="n">
-        <v>-7475077</v>
+        <v>-2062095</v>
       </c>
       <c r="O293" t="n">
-        <v>-8847914</v>
+        <v>-958406</v>
       </c>
       <c r="P293" t="n">
-        <v>-3649231</v>
+        <v>-1546864</v>
       </c>
       <c r="Q293" t="n">
-        <v>-1855651</v>
+        <v>380351</v>
       </c>
       <c r="R293" t="n">
-        <v>-7351827</v>
+        <v>-2215059</v>
       </c>
       <c r="S293" t="n">
-        <v>-8319759</v>
+        <v>-1555774</v>
       </c>
       <c r="T293" t="n">
-        <v>-2436713</v>
+        <v>297436</v>
       </c>
       <c r="U293" t="n">
-        <v>0</v>
+        <v>8000</v>
       </c>
       <c r="V293" t="n">
-        <v>0</v>
+        <v>86000</v>
       </c>
       <c r="W293" t="n">
-        <v>0</v>
+        <v>287000</v>
       </c>
       <c r="X293" t="n">
-        <v>0</v>
+        <v>-2232100</v>
       </c>
       <c r="Y293" t="n">
-        <v>18373</v>
+        <v>281622</v>
       </c>
       <c r="Z293" t="n">
-        <v>-123250</v>
+        <v>66964</v>
       </c>
       <c r="AA293" t="n">
-        <v>-528155</v>
+        <v>310368</v>
       </c>
       <c r="AB293" t="n">
-        <v>-1212518</v>
+        <v>387800</v>
       </c>
       <c r="AC293" t="n">
         <v>-30</v>
@@ -40590,10 +40590,10 @@
         <v>-30</v>
       </c>
       <c r="AE293" t="n">
-        <v>-20</v>
+        <v>-45</v>
       </c>
       <c r="AF293" t="n">
-        <v>-55</v>
+        <v>-30</v>
       </c>
       <c r="AG293" t="n">
         <v>0</v>
@@ -40613,17 +40613,17 @@
       </c>
       <c r="AM293" t="inlineStr">
         <is>
-          <t>跌破5日線、量能未放大</t>
+          <t>跌破5日線、空頭排列、量能未放大</t>
         </is>
       </c>
       <c r="AN293" t="inlineStr">
         <is>
-          <t>法人連續偏賣、5日法人明顯賣超</t>
+          <t>5日法人明顯賣超、投信買外資賣</t>
         </is>
       </c>
       <c r="AO293" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、量能未放大、法人連續偏賣、5日法人明顯賣超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、空頭排列、量能未放大、5日法人明顯賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
@@ -40767,12 +40767,12 @@
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>2617.TW</t>
+          <t>2330.TW</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>台航</t>
+          <t>台積電</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
@@ -40781,28 +40781,28 @@
         </is>
       </c>
       <c r="D295" t="n">
-        <v>28.65</v>
+        <v>2320</v>
       </c>
       <c r="E295" t="n">
-        <v>29.01</v>
+        <v>2388</v>
       </c>
       <c r="F295" t="n">
-        <v>29.74</v>
+        <v>2416</v>
       </c>
       <c r="G295" t="n">
-        <v>29.78</v>
+        <v>2423.75</v>
       </c>
       <c r="H295" t="n">
-        <v>963587</v>
+        <v>55790346</v>
       </c>
       <c r="I295" t="n">
-        <v>972800</v>
+        <v>52042848</v>
       </c>
       <c r="J295" t="n">
-        <v>31.05</v>
+        <v>2535</v>
       </c>
       <c r="K295" t="n">
-        <v>28.3</v>
+        <v>2290</v>
       </c>
       <c r="L295" t="inlineStr">
         <is>
@@ -40810,52 +40810,52 @@
         </is>
       </c>
       <c r="M295" t="n">
-        <v>87283</v>
+        <v>4001126</v>
       </c>
       <c r="N295" t="n">
-        <v>-160821</v>
+        <v>-38559952</v>
       </c>
       <c r="O295" t="n">
-        <v>-471061</v>
+        <v>-50133184</v>
       </c>
       <c r="P295" t="n">
-        <v>-15560</v>
+        <v>-65954606</v>
       </c>
       <c r="Q295" t="n">
-        <v>458504</v>
+        <v>-1672128</v>
       </c>
       <c r="R295" t="n">
-        <v>207866</v>
+        <v>-50070828</v>
       </c>
       <c r="S295" t="n">
-        <v>-132904</v>
+        <v>-65914318</v>
       </c>
       <c r="T295" t="n">
-        <v>342274</v>
+        <v>-85020780</v>
       </c>
       <c r="U295" t="n">
-        <v>0</v>
+        <v>1047417</v>
       </c>
       <c r="V295" t="n">
-        <v>0</v>
+        <v>3064311</v>
       </c>
       <c r="W295" t="n">
-        <v>0</v>
+        <v>4308949</v>
       </c>
       <c r="X295" t="n">
-        <v>0</v>
+        <v>6530891</v>
       </c>
       <c r="Y295" t="n">
-        <v>-371221</v>
+        <v>4625837</v>
       </c>
       <c r="Z295" t="n">
-        <v>-368687</v>
+        <v>8446565</v>
       </c>
       <c r="AA295" t="n">
-        <v>-338157</v>
+        <v>11472185</v>
       </c>
       <c r="AB295" t="n">
-        <v>-357834</v>
+        <v>12535283</v>
       </c>
       <c r="AC295" t="n">
         <v>-30</v>
@@ -40864,10 +40864,10 @@
         <v>-30</v>
       </c>
       <c r="AE295" t="n">
-        <v>-55</v>
+        <v>-45</v>
       </c>
       <c r="AF295" t="n">
-        <v>-20</v>
+        <v>-30</v>
       </c>
       <c r="AG295" t="n">
         <v>0</v>
@@ -40887,29 +40887,29 @@
       </c>
       <c r="AM295" t="inlineStr">
         <is>
-          <t>跌破5日線、空頭排列、量能未放大、接近20日低點</t>
+          <t>跌破5日線、空頭排列、量能溫和放大、接近20日低點</t>
         </is>
       </c>
       <c r="AN295" t="inlineStr">
         <is>
-          <t>5日法人賣超</t>
+          <t>5日法人明顯賣超、投信買外資賣</t>
         </is>
       </c>
       <c r="AO295" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、空頭排列、量能未放大、接近20日低點、5日法人賣超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、空頭排列、量能溫和放大、接近20日低點、5日法人明顯賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>6285.TW</t>
+          <t>2617.TW</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>啟碁</t>
+          <t>台航</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
@@ -40918,28 +40918,28 @@
         </is>
       </c>
       <c r="D296" t="n">
-        <v>235</v>
+        <v>28.65</v>
       </c>
       <c r="E296" t="n">
-        <v>248.2</v>
+        <v>29.01</v>
       </c>
       <c r="F296" t="n">
-        <v>251.4</v>
+        <v>29.74</v>
       </c>
       <c r="G296" t="n">
-        <v>252.2</v>
+        <v>29.78</v>
       </c>
       <c r="H296" t="n">
-        <v>8934026</v>
+        <v>963587</v>
       </c>
       <c r="I296" t="n">
-        <v>9668377</v>
+        <v>972800</v>
       </c>
       <c r="J296" t="n">
-        <v>277.5</v>
+        <v>31.05</v>
       </c>
       <c r="K296" t="n">
-        <v>220.5</v>
+        <v>28.3</v>
       </c>
       <c r="L296" t="inlineStr">
         <is>
@@ -40947,52 +40947,52 @@
         </is>
       </c>
       <c r="M296" t="n">
-        <v>669973</v>
+        <v>87283</v>
       </c>
       <c r="N296" t="n">
-        <v>-2062095</v>
+        <v>-160821</v>
       </c>
       <c r="O296" t="n">
-        <v>-958406</v>
+        <v>-471061</v>
       </c>
       <c r="P296" t="n">
-        <v>-1546864</v>
+        <v>-15560</v>
       </c>
       <c r="Q296" t="n">
-        <v>380351</v>
+        <v>458504</v>
       </c>
       <c r="R296" t="n">
-        <v>-2215059</v>
+        <v>207866</v>
       </c>
       <c r="S296" t="n">
-        <v>-1555774</v>
+        <v>-132904</v>
       </c>
       <c r="T296" t="n">
-        <v>297436</v>
+        <v>342274</v>
       </c>
       <c r="U296" t="n">
-        <v>8000</v>
+        <v>0</v>
       </c>
       <c r="V296" t="n">
-        <v>86000</v>
+        <v>0</v>
       </c>
       <c r="W296" t="n">
-        <v>287000</v>
+        <v>0</v>
       </c>
       <c r="X296" t="n">
-        <v>-2232100</v>
+        <v>0</v>
       </c>
       <c r="Y296" t="n">
-        <v>281622</v>
+        <v>-371221</v>
       </c>
       <c r="Z296" t="n">
-        <v>66964</v>
+        <v>-368687</v>
       </c>
       <c r="AA296" t="n">
-        <v>310368</v>
+        <v>-338157</v>
       </c>
       <c r="AB296" t="n">
-        <v>387800</v>
+        <v>-357834</v>
       </c>
       <c r="AC296" t="n">
         <v>-30</v>
@@ -41001,10 +41001,10 @@
         <v>-30</v>
       </c>
       <c r="AE296" t="n">
-        <v>-45</v>
+        <v>-55</v>
       </c>
       <c r="AF296" t="n">
-        <v>-30</v>
+        <v>-20</v>
       </c>
       <c r="AG296" t="n">
         <v>0</v>
@@ -41024,17 +41024,17 @@
       </c>
       <c r="AM296" t="inlineStr">
         <is>
-          <t>跌破5日線、空頭排列、量能未放大</t>
+          <t>跌破5日線、空頭排列、量能未放大、接近20日低點</t>
         </is>
       </c>
       <c r="AN296" t="inlineStr">
         <is>
-          <t>5日法人明顯賣超、投信買外資賣</t>
+          <t>5日法人賣超</t>
         </is>
       </c>
       <c r="AO296" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、空頭排列、量能未放大、5日法人明顯賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、空頭排列、量能未放大、接近20日低點、5日法人賣超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
@@ -41589,12 +41589,12 @@
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>3035.TW</t>
+          <t>1710.TW</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>智原</t>
+          <t>東聯</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
@@ -41603,28 +41603,28 @@
         </is>
       </c>
       <c r="D301" t="n">
-        <v>182.5</v>
+        <v>15.45</v>
       </c>
       <c r="E301" t="n">
-        <v>196.8</v>
+        <v>16.14</v>
       </c>
       <c r="F301" t="n">
-        <v>203.9</v>
+        <v>16.65</v>
       </c>
       <c r="G301" t="n">
-        <v>212.38</v>
+        <v>16.18</v>
       </c>
       <c r="H301" t="n">
-        <v>5623259</v>
+        <v>8337541</v>
       </c>
       <c r="I301" t="n">
-        <v>5875817</v>
+        <v>13366340</v>
       </c>
       <c r="J301" t="n">
-        <v>245</v>
+        <v>20.15</v>
       </c>
       <c r="K301" t="n">
-        <v>172</v>
+        <v>13.35</v>
       </c>
       <c r="L301" t="inlineStr">
         <is>
@@ -41632,52 +41632,52 @@
         </is>
       </c>
       <c r="M301" t="n">
-        <v>581546</v>
+        <v>-1837278</v>
       </c>
       <c r="N301" t="n">
-        <v>-955794</v>
+        <v>-7475077</v>
       </c>
       <c r="O301" t="n">
-        <v>-2011969</v>
+        <v>-8847914</v>
       </c>
       <c r="P301" t="n">
-        <v>-739017</v>
+        <v>-3649231</v>
       </c>
       <c r="Q301" t="n">
-        <v>641025</v>
+        <v>-1855651</v>
       </c>
       <c r="R301" t="n">
-        <v>-566798</v>
+        <v>-7351827</v>
       </c>
       <c r="S301" t="n">
-        <v>-1545708</v>
+        <v>-8319759</v>
       </c>
       <c r="T301" t="n">
-        <v>-181958</v>
+        <v>-2436713</v>
       </c>
       <c r="U301" t="n">
         <v>0</v>
       </c>
       <c r="V301" t="n">
-        <v>125000</v>
+        <v>0</v>
       </c>
       <c r="W301" t="n">
-        <v>125000</v>
+        <v>0</v>
       </c>
       <c r="X301" t="n">
-        <v>127200</v>
+        <v>0</v>
       </c>
       <c r="Y301" t="n">
-        <v>-59479</v>
+        <v>18373</v>
       </c>
       <c r="Z301" t="n">
-        <v>-513996</v>
+        <v>-123250</v>
       </c>
       <c r="AA301" t="n">
-        <v>-591261</v>
+        <v>-528155</v>
       </c>
       <c r="AB301" t="n">
-        <v>-684259</v>
+        <v>-1212518</v>
       </c>
       <c r="AC301" t="n">
         <v>-30</v>
@@ -41686,10 +41686,10 @@
         <v>-30</v>
       </c>
       <c r="AE301" t="n">
-        <v>-45</v>
+        <v>-20</v>
       </c>
       <c r="AF301" t="n">
-        <v>-30</v>
+        <v>-55</v>
       </c>
       <c r="AG301" t="n">
         <v>0</v>
@@ -41709,29 +41709,29 @@
       </c>
       <c r="AM301" t="inlineStr">
         <is>
-          <t>跌破5日線、空頭排列、量能未放大</t>
+          <t>跌破5日線、量能未放大</t>
         </is>
       </c>
       <c r="AN301" t="inlineStr">
         <is>
-          <t>5日法人明顯賣超、投信買外資賣</t>
+          <t>法人連續偏賣、5日法人明顯賣超</t>
         </is>
       </c>
       <c r="AO301" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、空頭排列、量能未放大、5日法人明顯賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、量能未放大、法人連續偏賣、5日法人明顯賣超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>2314.TW</t>
+          <t>3035.TW</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>台揚</t>
+          <t>智原</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
@@ -41740,28 +41740,28 @@
         </is>
       </c>
       <c r="D302" t="n">
-        <v>12.45</v>
+        <v>182.5</v>
       </c>
       <c r="E302" t="n">
-        <v>13.05</v>
+        <v>196.8</v>
       </c>
       <c r="F302" t="n">
-        <v>13.38</v>
+        <v>203.9</v>
       </c>
       <c r="G302" t="n">
-        <v>13.86</v>
+        <v>212.38</v>
       </c>
       <c r="H302" t="n">
-        <v>120717</v>
+        <v>5623259</v>
       </c>
       <c r="I302" t="n">
-        <v>106231</v>
+        <v>5875817</v>
       </c>
       <c r="J302" t="n">
-        <v>15.75</v>
+        <v>245</v>
       </c>
       <c r="K302" t="n">
-        <v>12.4</v>
+        <v>172</v>
       </c>
       <c r="L302" t="inlineStr">
         <is>
@@ -41769,64 +41769,64 @@
         </is>
       </c>
       <c r="M302" t="n">
-        <v>-16000</v>
+        <v>581546</v>
       </c>
       <c r="N302" t="n">
-        <v>-34000</v>
+        <v>-955794</v>
       </c>
       <c r="O302" t="n">
-        <v>-58000</v>
+        <v>-2011969</v>
       </c>
       <c r="P302" t="n">
-        <v>-133000</v>
+        <v>-739017</v>
       </c>
       <c r="Q302" t="n">
-        <v>-16000</v>
+        <v>641025</v>
       </c>
       <c r="R302" t="n">
-        <v>-34000</v>
+        <v>-566798</v>
       </c>
       <c r="S302" t="n">
-        <v>-58000</v>
+        <v>-1545708</v>
       </c>
       <c r="T302" t="n">
-        <v>-133000</v>
+        <v>-181958</v>
       </c>
       <c r="U302" t="n">
         <v>0</v>
       </c>
       <c r="V302" t="n">
-        <v>0</v>
+        <v>125000</v>
       </c>
       <c r="W302" t="n">
-        <v>0</v>
+        <v>125000</v>
       </c>
       <c r="X302" t="n">
-        <v>0</v>
+        <v>127200</v>
       </c>
       <c r="Y302" t="n">
-        <v>0</v>
+        <v>-59479</v>
       </c>
       <c r="Z302" t="n">
-        <v>0</v>
+        <v>-513996</v>
       </c>
       <c r="AA302" t="n">
-        <v>0</v>
+        <v>-591261</v>
       </c>
       <c r="AB302" t="n">
-        <v>0</v>
+        <v>-684259</v>
       </c>
       <c r="AC302" t="n">
-        <v>-32</v>
+        <v>-30</v>
       </c>
       <c r="AD302" t="n">
-        <v>-32</v>
+        <v>-30</v>
       </c>
       <c r="AE302" t="n">
         <v>-45</v>
       </c>
       <c r="AF302" t="n">
-        <v>-35</v>
+        <v>-30</v>
       </c>
       <c r="AG302" t="n">
         <v>0</v>
@@ -41846,29 +41846,29 @@
       </c>
       <c r="AM302" t="inlineStr">
         <is>
-          <t>跌破5日線、空頭排列、量能溫和放大、接近20日低點</t>
+          <t>跌破5日線、空頭排列、量能未放大</t>
         </is>
       </c>
       <c r="AN302" t="inlineStr">
         <is>
-          <t>法人連續偏賣、5日法人小幅賣超</t>
+          <t>5日法人明顯賣超、投信買外資賣</t>
         </is>
       </c>
       <c r="AO302" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、空頭排列、量能溫和放大、接近20日低點、法人連續偏賣、5日法人小幅賣超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、空頭排列、量能未放大、5日法人明顯賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>2535.TW</t>
+          <t>2515.TW</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>達欣工</t>
+          <t>中工</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
@@ -41877,28 +41877,28 @@
         </is>
       </c>
       <c r="D303" t="n">
-        <v>86</v>
+        <v>12.2</v>
       </c>
       <c r="E303" t="n">
-        <v>87.52</v>
+        <v>12.94</v>
       </c>
       <c r="F303" t="n">
-        <v>88.04000000000001</v>
+        <v>13.45</v>
       </c>
       <c r="G303" t="n">
-        <v>90.25</v>
+        <v>13.39</v>
       </c>
       <c r="H303" t="n">
-        <v>297832</v>
+        <v>7629024</v>
       </c>
       <c r="I303" t="n">
-        <v>287642</v>
+        <v>12243597</v>
       </c>
       <c r="J303" t="n">
-        <v>96.3</v>
+        <v>15.3</v>
       </c>
       <c r="K303" t="n">
-        <v>85</v>
+        <v>12.05</v>
       </c>
       <c r="L303" t="inlineStr">
         <is>
@@ -41906,52 +41906,52 @@
         </is>
       </c>
       <c r="M303" t="n">
-        <v>-31487</v>
+        <v>107188</v>
       </c>
       <c r="N303" t="n">
-        <v>-2340</v>
+        <v>-14194071</v>
       </c>
       <c r="O303" t="n">
-        <v>-78047</v>
+        <v>-12534669</v>
       </c>
       <c r="P303" t="n">
-        <v>-291141</v>
+        <v>-16314308</v>
       </c>
       <c r="Q303" t="n">
-        <v>-42965</v>
+        <v>128865</v>
       </c>
       <c r="R303" t="n">
-        <v>-43332</v>
+        <v>-12006727</v>
       </c>
       <c r="S303" t="n">
-        <v>-130442</v>
+        <v>-11316959</v>
       </c>
       <c r="T303" t="n">
-        <v>-267999</v>
+        <v>-15132052</v>
       </c>
       <c r="U303" t="n">
-        <v>0</v>
+        <v>-3000</v>
       </c>
       <c r="V303" t="n">
-        <v>7000</v>
+        <v>-803000</v>
       </c>
       <c r="W303" t="n">
-        <v>3000</v>
+        <v>-827258</v>
       </c>
       <c r="X303" t="n">
-        <v>2000</v>
+        <v>-837258</v>
       </c>
       <c r="Y303" t="n">
-        <v>11478</v>
+        <v>-18677</v>
       </c>
       <c r="Z303" t="n">
-        <v>33992</v>
+        <v>-1384344</v>
       </c>
       <c r="AA303" t="n">
-        <v>49395</v>
+        <v>-390452</v>
       </c>
       <c r="AB303" t="n">
-        <v>-25142</v>
+        <v>-344998</v>
       </c>
       <c r="AC303" t="n">
         <v>-32</v>
@@ -41960,10 +41960,10 @@
         <v>-32</v>
       </c>
       <c r="AE303" t="n">
-        <v>-45</v>
+        <v>-30</v>
       </c>
       <c r="AF303" t="n">
-        <v>-35</v>
+        <v>-50</v>
       </c>
       <c r="AG303" t="n">
         <v>0</v>
@@ -41983,29 +41983,29 @@
       </c>
       <c r="AM303" t="inlineStr">
         <is>
-          <t>跌破5日線、空頭排列、量能溫和放大、接近20日低點</t>
+          <t>跌破5日線、量能未放大、接近20日低點</t>
         </is>
       </c>
       <c r="AN303" t="inlineStr">
         <is>
-          <t>法人連續偏賣、5日法人小幅賣超、投信買外資賣</t>
+          <t>5日法人明顯賣超、外資投信同步賣超</t>
         </is>
       </c>
       <c r="AO303" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、空頭排列、量能溫和放大、接近20日低點、法人連續偏賣、5日法人小幅賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、量能未放大、接近20日低點、5日法人明顯賣超、外資投信同步賣超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>2515.TW</t>
+          <t>2535.TW</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>中工</t>
+          <t>達欣工</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
@@ -42014,28 +42014,28 @@
         </is>
       </c>
       <c r="D304" t="n">
-        <v>12.2</v>
+        <v>86</v>
       </c>
       <c r="E304" t="n">
-        <v>12.94</v>
+        <v>87.52</v>
       </c>
       <c r="F304" t="n">
-        <v>13.45</v>
+        <v>88.04000000000001</v>
       </c>
       <c r="G304" t="n">
-        <v>13.39</v>
+        <v>90.25</v>
       </c>
       <c r="H304" t="n">
-        <v>7629024</v>
+        <v>297832</v>
       </c>
       <c r="I304" t="n">
-        <v>12243597</v>
+        <v>287642</v>
       </c>
       <c r="J304" t="n">
-        <v>15.3</v>
+        <v>96.3</v>
       </c>
       <c r="K304" t="n">
-        <v>12.05</v>
+        <v>85</v>
       </c>
       <c r="L304" t="inlineStr">
         <is>
@@ -42043,52 +42043,52 @@
         </is>
       </c>
       <c r="M304" t="n">
-        <v>107188</v>
+        <v>-31487</v>
       </c>
       <c r="N304" t="n">
-        <v>-14194071</v>
+        <v>-2340</v>
       </c>
       <c r="O304" t="n">
-        <v>-12534669</v>
+        <v>-78047</v>
       </c>
       <c r="P304" t="n">
-        <v>-16314308</v>
+        <v>-291141</v>
       </c>
       <c r="Q304" t="n">
-        <v>128865</v>
+        <v>-42965</v>
       </c>
       <c r="R304" t="n">
-        <v>-12006727</v>
+        <v>-43332</v>
       </c>
       <c r="S304" t="n">
-        <v>-11316959</v>
+        <v>-130442</v>
       </c>
       <c r="T304" t="n">
-        <v>-15132052</v>
+        <v>-267999</v>
       </c>
       <c r="U304" t="n">
-        <v>-3000</v>
+        <v>0</v>
       </c>
       <c r="V304" t="n">
-        <v>-803000</v>
+        <v>7000</v>
       </c>
       <c r="W304" t="n">
-        <v>-827258</v>
+        <v>3000</v>
       </c>
       <c r="X304" t="n">
-        <v>-837258</v>
+        <v>2000</v>
       </c>
       <c r="Y304" t="n">
-        <v>-18677</v>
+        <v>11478</v>
       </c>
       <c r="Z304" t="n">
-        <v>-1384344</v>
+        <v>33992</v>
       </c>
       <c r="AA304" t="n">
-        <v>-390452</v>
+        <v>49395</v>
       </c>
       <c r="AB304" t="n">
-        <v>-344998</v>
+        <v>-25142</v>
       </c>
       <c r="AC304" t="n">
         <v>-32</v>
@@ -42097,10 +42097,10 @@
         <v>-32</v>
       </c>
       <c r="AE304" t="n">
-        <v>-30</v>
+        <v>-45</v>
       </c>
       <c r="AF304" t="n">
-        <v>-50</v>
+        <v>-35</v>
       </c>
       <c r="AG304" t="n">
         <v>0</v>
@@ -42120,17 +42120,17 @@
       </c>
       <c r="AM304" t="inlineStr">
         <is>
-          <t>跌破5日線、量能未放大、接近20日低點</t>
+          <t>跌破5日線、空頭排列、量能溫和放大、接近20日低點</t>
         </is>
       </c>
       <c r="AN304" t="inlineStr">
         <is>
-          <t>5日法人明顯賣超、外資投信同步賣超</t>
+          <t>法人連續偏賣、5日法人小幅賣超、投信買外資賣</t>
         </is>
       </c>
       <c r="AO304" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、量能未放大、接近20日低點、5日法人明顯賣超、外資投信同步賣超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、空頭排列、量能溫和放大、接近20日低點、法人連續偏賣、5日法人小幅賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
@@ -42163,10 +42163,10 @@
         <v>2081.25</v>
       </c>
       <c r="H305" t="n">
-        <v>1128929</v>
+        <v>1139929</v>
       </c>
       <c r="I305" t="n">
-        <v>1056414</v>
+        <v>1058614</v>
       </c>
       <c r="J305" t="n">
         <v>2350</v>
@@ -42274,12 +42274,12 @@
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>3014.TW</t>
+          <t>2314.TW</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>聯陽</t>
+          <t>台揚</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
@@ -42288,28 +42288,28 @@
         </is>
       </c>
       <c r="D306" t="n">
-        <v>124</v>
+        <v>12.45</v>
       </c>
       <c r="E306" t="n">
-        <v>130</v>
+        <v>13.05</v>
       </c>
       <c r="F306" t="n">
-        <v>139.2</v>
+        <v>13.38</v>
       </c>
       <c r="G306" t="n">
-        <v>150.22</v>
+        <v>13.86</v>
       </c>
       <c r="H306" t="n">
-        <v>1381874</v>
+        <v>120717</v>
       </c>
       <c r="I306" t="n">
-        <v>1735392</v>
+        <v>106231</v>
       </c>
       <c r="J306" t="n">
-        <v>171</v>
+        <v>15.75</v>
       </c>
       <c r="K306" t="n">
-        <v>121</v>
+        <v>12.4</v>
       </c>
       <c r="L306" t="inlineStr">
         <is>
@@ -42317,64 +42317,64 @@
         </is>
       </c>
       <c r="M306" t="n">
-        <v>88252</v>
+        <v>-16000</v>
       </c>
       <c r="N306" t="n">
-        <v>-229158</v>
+        <v>-34000</v>
       </c>
       <c r="O306" t="n">
-        <v>-1254874</v>
+        <v>-58000</v>
       </c>
       <c r="P306" t="n">
-        <v>-2660888</v>
+        <v>-133000</v>
       </c>
       <c r="Q306" t="n">
-        <v>104000</v>
+        <v>-16000</v>
       </c>
       <c r="R306" t="n">
-        <v>-424841</v>
+        <v>-34000</v>
       </c>
       <c r="S306" t="n">
-        <v>-1617942</v>
+        <v>-58000</v>
       </c>
       <c r="T306" t="n">
-        <v>-3192191</v>
+        <v>-133000</v>
       </c>
       <c r="U306" t="n">
-        <v>-10390</v>
+        <v>0</v>
       </c>
       <c r="V306" t="n">
-        <v>206610</v>
+        <v>0</v>
       </c>
       <c r="W306" t="n">
-        <v>363610</v>
+        <v>0</v>
       </c>
       <c r="X306" t="n">
-        <v>788108</v>
+        <v>0</v>
       </c>
       <c r="Y306" t="n">
-        <v>-5358</v>
+        <v>0</v>
       </c>
       <c r="Z306" t="n">
-        <v>-10927</v>
+        <v>0</v>
       </c>
       <c r="AA306" t="n">
-        <v>-542</v>
+        <v>0</v>
       </c>
       <c r="AB306" t="n">
-        <v>-256805</v>
+        <v>0</v>
       </c>
       <c r="AC306" t="n">
-        <v>-34</v>
+        <v>-32</v>
       </c>
       <c r="AD306" t="n">
-        <v>-34</v>
+        <v>-32</v>
       </c>
       <c r="AE306" t="n">
-        <v>-55</v>
+        <v>-45</v>
       </c>
       <c r="AF306" t="n">
-        <v>-30</v>
+        <v>-35</v>
       </c>
       <c r="AG306" t="n">
         <v>0</v>
@@ -42394,17 +42394,17 @@
       </c>
       <c r="AM306" t="inlineStr">
         <is>
-          <t>跌破5日線、空頭排列、量能未放大、接近20日低點</t>
+          <t>跌破5日線、空頭排列、量能溫和放大、接近20日低點</t>
         </is>
       </c>
       <c r="AN306" t="inlineStr">
         <is>
-          <t>5日法人明顯賣超、投信買外資賣</t>
+          <t>法人連續偏賣、5日法人小幅賣超</t>
         </is>
       </c>
       <c r="AO306" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、空頭排列、量能未放大、接近20日低點、5日法人明顯賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、空頭排列、量能溫和放大、接近20日低點、法人連續偏賣、5日法人小幅賣超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
@@ -43370,12 +43370,12 @@
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>3062.TW</t>
+          <t>3014.TW</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>建漢</t>
+          <t>聯陽</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
@@ -43384,28 +43384,28 @@
         </is>
       </c>
       <c r="D314" t="n">
-        <v>20.85</v>
+        <v>124</v>
       </c>
       <c r="E314" t="n">
-        <v>22.32</v>
+        <v>130</v>
       </c>
       <c r="F314" t="n">
-        <v>23.21</v>
+        <v>139.2</v>
       </c>
       <c r="G314" t="n">
-        <v>24.05</v>
+        <v>150.22</v>
       </c>
       <c r="H314" t="n">
-        <v>2586508</v>
+        <v>1381874</v>
       </c>
       <c r="I314" t="n">
-        <v>2632591</v>
+        <v>1735392</v>
       </c>
       <c r="J314" t="n">
-        <v>26.3</v>
+        <v>171</v>
       </c>
       <c r="K314" t="n">
-        <v>20.4</v>
+        <v>121</v>
       </c>
       <c r="L314" t="inlineStr">
         <is>
@@ -43413,52 +43413,52 @@
         </is>
       </c>
       <c r="M314" t="n">
-        <v>320487</v>
+        <v>88252</v>
       </c>
       <c r="N314" t="n">
-        <v>-749999</v>
+        <v>-229158</v>
       </c>
       <c r="O314" t="n">
-        <v>-1496210</v>
+        <v>-1254874</v>
       </c>
       <c r="P314" t="n">
-        <v>-3707876</v>
+        <v>-2660888</v>
       </c>
       <c r="Q314" t="n">
-        <v>346816</v>
+        <v>104000</v>
       </c>
       <c r="R314" t="n">
-        <v>-677684</v>
+        <v>-424841</v>
       </c>
       <c r="S314" t="n">
-        <v>-1333234</v>
+        <v>-1617942</v>
       </c>
       <c r="T314" t="n">
-        <v>-3425232</v>
+        <v>-3192191</v>
       </c>
       <c r="U314" t="n">
-        <v>0</v>
+        <v>-10390</v>
       </c>
       <c r="V314" t="n">
-        <v>0</v>
+        <v>206610</v>
       </c>
       <c r="W314" t="n">
-        <v>0</v>
+        <v>363610</v>
       </c>
       <c r="X314" t="n">
-        <v>0</v>
+        <v>788108</v>
       </c>
       <c r="Y314" t="n">
-        <v>-26329</v>
+        <v>-5358</v>
       </c>
       <c r="Z314" t="n">
-        <v>-72315</v>
+        <v>-10927</v>
       </c>
       <c r="AA314" t="n">
-        <v>-162976</v>
+        <v>-542</v>
       </c>
       <c r="AB314" t="n">
-        <v>-282644</v>
+        <v>-256805</v>
       </c>
       <c r="AC314" t="n">
         <v>-34</v>
@@ -43495,12 +43495,12 @@
       </c>
       <c r="AN314" t="inlineStr">
         <is>
-          <t>5日法人明顯賣超</t>
+          <t>5日法人明顯賣超、投信買外資賣</t>
         </is>
       </c>
       <c r="AO314" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、空頭排列、量能未放大、接近20日低點、5日法人明顯賣超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、空頭排列、量能未放大、接近20日低點、5日法人明顯賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
@@ -43918,12 +43918,12 @@
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>2330.TW</t>
+          <t>3062.TW</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>台積電</t>
+          <t>建漢</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
@@ -43932,28 +43932,28 @@
         </is>
       </c>
       <c r="D318" t="n">
-        <v>2320</v>
+        <v>20.85</v>
       </c>
       <c r="E318" t="n">
-        <v>2388</v>
+        <v>22.32</v>
       </c>
       <c r="F318" t="n">
-        <v>2416</v>
+        <v>23.21</v>
       </c>
       <c r="G318" t="n">
-        <v>2423.75</v>
+        <v>24.05</v>
       </c>
       <c r="H318" t="n">
-        <v>48542346</v>
+        <v>2586508</v>
       </c>
       <c r="I318" t="n">
-        <v>50593248</v>
+        <v>2632591</v>
       </c>
       <c r="J318" t="n">
-        <v>2535</v>
+        <v>26.3</v>
       </c>
       <c r="K318" t="n">
-        <v>2290</v>
+        <v>20.4</v>
       </c>
       <c r="L318" t="inlineStr">
         <is>
@@ -43961,52 +43961,52 @@
         </is>
       </c>
       <c r="M318" t="n">
-        <v>4001126</v>
+        <v>320487</v>
       </c>
       <c r="N318" t="n">
-        <v>-38559952</v>
+        <v>-749999</v>
       </c>
       <c r="O318" t="n">
-        <v>-50133184</v>
+        <v>-1496210</v>
       </c>
       <c r="P318" t="n">
-        <v>-65954606</v>
+        <v>-3707876</v>
       </c>
       <c r="Q318" t="n">
-        <v>-1672128</v>
+        <v>346816</v>
       </c>
       <c r="R318" t="n">
-        <v>-50070828</v>
+        <v>-677684</v>
       </c>
       <c r="S318" t="n">
-        <v>-65914318</v>
+        <v>-1333234</v>
       </c>
       <c r="T318" t="n">
-        <v>-85020780</v>
+        <v>-3425232</v>
       </c>
       <c r="U318" t="n">
-        <v>1047417</v>
+        <v>0</v>
       </c>
       <c r="V318" t="n">
-        <v>3064311</v>
+        <v>0</v>
       </c>
       <c r="W318" t="n">
-        <v>4308949</v>
+        <v>0</v>
       </c>
       <c r="X318" t="n">
-        <v>6530891</v>
+        <v>0</v>
       </c>
       <c r="Y318" t="n">
-        <v>4625837</v>
+        <v>-26329</v>
       </c>
       <c r="Z318" t="n">
-        <v>8446565</v>
+        <v>-72315</v>
       </c>
       <c r="AA318" t="n">
-        <v>11472185</v>
+        <v>-162976</v>
       </c>
       <c r="AB318" t="n">
-        <v>12535283</v>
+        <v>-282644</v>
       </c>
       <c r="AC318" t="n">
         <v>-34</v>
@@ -44043,12 +44043,12 @@
       </c>
       <c r="AN318" t="inlineStr">
         <is>
-          <t>5日法人明顯賣超、投信買外資賣</t>
+          <t>5日法人明顯賣超</t>
         </is>
       </c>
       <c r="AO318" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、空頭排列、量能未放大、接近20日低點、5日法人明顯賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、空頭排列、量能未放大、接近20日低點、5日法人明顯賣超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
@@ -44081,10 +44081,10 @@
         <v>928.65</v>
       </c>
       <c r="H319" t="n">
-        <v>30088875</v>
+        <v>30661875</v>
       </c>
       <c r="I319" t="n">
-        <v>30852804</v>
+        <v>30967404</v>
       </c>
       <c r="J319" t="n">
         <v>1115</v>
@@ -44766,10 +44766,10 @@
         <v>2397.25</v>
       </c>
       <c r="H324" t="n">
-        <v>4355999</v>
+        <v>4416999</v>
       </c>
       <c r="I324" t="n">
-        <v>4129229</v>
+        <v>4141429</v>
       </c>
       <c r="J324" t="n">
         <v>2790</v>
@@ -45177,10 +45177,10 @@
         <v>4010.75</v>
       </c>
       <c r="H327" t="n">
-        <v>9200986</v>
+        <v>9227986</v>
       </c>
       <c r="I327" t="n">
-        <v>9194247</v>
+        <v>9199647</v>
       </c>
       <c r="J327" t="n">
         <v>4785</v>
@@ -49972,10 +49972,10 @@
         <v>944.65</v>
       </c>
       <c r="H362" t="n">
-        <v>32447060</v>
+        <v>39385060</v>
       </c>
       <c r="I362" t="n">
-        <v>51589844</v>
+        <v>52977444</v>
       </c>
       <c r="J362" t="n">
         <v>1220</v>

--- a/output/universe_analysis_result.xlsx
+++ b/output/universe_analysis_result.xlsx
@@ -13253,7 +13253,7 @@
         <v>33.09</v>
       </c>
       <c r="G94" t="n">
-        <v>34.09</v>
+        <v>34.77</v>
       </c>
       <c r="H94" t="n">
         <v>27797662</v>
@@ -13262,7 +13262,7 @@
         <v>21031572</v>
       </c>
       <c r="J94" t="n">
-        <v>38.55</v>
+        <v>41.05</v>
       </c>
       <c r="K94" t="n">
         <v>28.85</v>
@@ -18322,7 +18322,7 @@
         <v>63.58</v>
       </c>
       <c r="G131" t="n">
-        <v>62.48</v>
+        <v>62.88</v>
       </c>
       <c r="H131" t="n">
         <v>4608557</v>
@@ -18334,7 +18334,7 @@
         <v>65.09999999999999</v>
       </c>
       <c r="K131" t="n">
-        <v>59</v>
+        <v>59.4</v>
       </c>
       <c r="L131" t="inlineStr">
         <is>
@@ -25286,12 +25286,12 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>4931.TWO</t>
+          <t>5530.TWO</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>新盛力</t>
+          <t>龍巖</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -25300,28 +25300,28 @@
         </is>
       </c>
       <c r="D182" t="n">
-        <v>215</v>
+        <v>48.4</v>
       </c>
       <c r="E182" t="n">
-        <v>209.3</v>
+        <v>48.5</v>
       </c>
       <c r="F182" t="n">
-        <v>225.55</v>
+        <v>48.59</v>
       </c>
       <c r="G182" t="n">
-        <v>234.55</v>
+        <v>48.47</v>
       </c>
       <c r="H182" t="n">
-        <v>3520000</v>
+        <v>273000</v>
       </c>
       <c r="I182" t="n">
-        <v>3282200</v>
+        <v>367800</v>
       </c>
       <c r="J182" t="n">
-        <v>275</v>
+        <v>50.4</v>
       </c>
       <c r="K182" t="n">
-        <v>181.5</v>
+        <v>45.95</v>
       </c>
       <c r="L182" t="inlineStr">
         <is>
@@ -25406,7 +25406,7 @@
       </c>
       <c r="AM182" t="inlineStr">
         <is>
-          <t>站上5日線、空頭排列、量能溫和放大</t>
+          <t>跌破5日線、黃金交叉、量能未放大</t>
         </is>
       </c>
       <c r="AN182" t="inlineStr">
@@ -25416,7 +25416,7 @@
       </c>
       <c r="AO182" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、空頭排列、量能溫和放大、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、黃金交叉、量能未放大、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
@@ -27478,12 +27478,12 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>2543.TW</t>
+          <t>4931.TWO</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>皇昌</t>
+          <t>新盛力</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -27492,28 +27492,28 @@
         </is>
       </c>
       <c r="D198" t="n">
-        <v>39</v>
+        <v>215</v>
       </c>
       <c r="E198" t="n">
-        <v>39.1</v>
+        <v>209.3</v>
       </c>
       <c r="F198" t="n">
-        <v>39.1</v>
+        <v>225.55</v>
       </c>
       <c r="G198" t="n">
-        <v>38.95</v>
+        <v>234.55</v>
       </c>
       <c r="H198" t="n">
-        <v>1053872</v>
+        <v>3520000</v>
       </c>
       <c r="I198" t="n">
-        <v>1435625</v>
+        <v>3282200</v>
       </c>
       <c r="J198" t="n">
-        <v>41</v>
+        <v>275</v>
       </c>
       <c r="K198" t="n">
-        <v>37.75</v>
+        <v>181.5</v>
       </c>
       <c r="L198" t="inlineStr">
         <is>
@@ -27521,64 +27521,64 @@
         </is>
       </c>
       <c r="M198" t="n">
-        <v>-519271</v>
+        <v>0</v>
       </c>
       <c r="N198" t="n">
-        <v>449003</v>
+        <v>0</v>
       </c>
       <c r="O198" t="n">
-        <v>666261</v>
+        <v>0</v>
       </c>
       <c r="P198" t="n">
-        <v>1584458</v>
+        <v>0</v>
       </c>
       <c r="Q198" t="n">
-        <v>-499000</v>
+        <v>0</v>
       </c>
       <c r="R198" t="n">
-        <v>459991</v>
+        <v>0</v>
       </c>
       <c r="S198" t="n">
-        <v>657611</v>
+        <v>0</v>
       </c>
       <c r="T198" t="n">
-        <v>1589223</v>
+        <v>0</v>
       </c>
       <c r="U198" t="n">
         <v>0</v>
       </c>
       <c r="V198" t="n">
-        <v>-1000</v>
+        <v>0</v>
       </c>
       <c r="W198" t="n">
-        <v>-2000</v>
+        <v>0</v>
       </c>
       <c r="X198" t="n">
-        <v>-4000</v>
+        <v>0</v>
       </c>
       <c r="Y198" t="n">
-        <v>-20271</v>
+        <v>0</v>
       </c>
       <c r="Z198" t="n">
-        <v>-9988</v>
+        <v>0</v>
       </c>
       <c r="AA198" t="n">
-        <v>10650</v>
+        <v>0</v>
       </c>
       <c r="AB198" t="n">
-        <v>-765</v>
+        <v>0</v>
       </c>
       <c r="AC198" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD198" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AE198" t="n">
-        <v>-30</v>
+        <v>5</v>
       </c>
       <c r="AF198" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="AG198" t="n">
         <v>0</v>
@@ -27598,29 +27598,29 @@
       </c>
       <c r="AM198" t="inlineStr">
         <is>
-          <t>跌破5日線、量能未放大、接近20日低點</t>
+          <t>站上5日線、空頭排列、量能溫和放大</t>
         </is>
       </c>
       <c r="AN198" t="inlineStr">
         <is>
-          <t>5日法人明顯買超、外資買投信賣</t>
+          <t>籌碼中性</t>
         </is>
       </c>
       <c r="AO198" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、量能未放大、接近20日低點、5日法人明顯買超、外資買投信賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、空頭排列、量能溫和放大、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>2903.TW</t>
+          <t>2543.TW</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>遠百</t>
+          <t>皇昌</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -27629,28 +27629,28 @@
         </is>
       </c>
       <c r="D199" t="n">
-        <v>22.1</v>
+        <v>39</v>
       </c>
       <c r="E199" t="n">
-        <v>22.33</v>
+        <v>39.1</v>
       </c>
       <c r="F199" t="n">
-        <v>22.21</v>
+        <v>39.1</v>
       </c>
       <c r="G199" t="n">
-        <v>22.46</v>
+        <v>38.95</v>
       </c>
       <c r="H199" t="n">
-        <v>2134904</v>
+        <v>1053872</v>
       </c>
       <c r="I199" t="n">
-        <v>2276463</v>
+        <v>1435625</v>
       </c>
       <c r="J199" t="n">
-        <v>23.8</v>
+        <v>41</v>
       </c>
       <c r="K199" t="n">
-        <v>21.55</v>
+        <v>37.75</v>
       </c>
       <c r="L199" t="inlineStr">
         <is>
@@ -27658,52 +27658,52 @@
         </is>
       </c>
       <c r="M199" t="n">
-        <v>-1198261</v>
+        <v>-519271</v>
       </c>
       <c r="N199" t="n">
-        <v>-92681</v>
+        <v>449003</v>
       </c>
       <c r="O199" t="n">
-        <v>2383398</v>
+        <v>666261</v>
       </c>
       <c r="P199" t="n">
-        <v>2787598</v>
+        <v>1584458</v>
       </c>
       <c r="Q199" t="n">
-        <v>-759000</v>
+        <v>-499000</v>
       </c>
       <c r="R199" t="n">
-        <v>309580</v>
+        <v>459991</v>
       </c>
       <c r="S199" t="n">
-        <v>2781659</v>
+        <v>657611</v>
       </c>
       <c r="T199" t="n">
-        <v>3579275</v>
+        <v>1589223</v>
       </c>
       <c r="U199" t="n">
         <v>0</v>
       </c>
       <c r="V199" t="n">
+        <v>-1000</v>
+      </c>
+      <c r="W199" t="n">
         <v>-2000</v>
       </c>
-      <c r="W199" t="n">
-        <v>-6000</v>
-      </c>
       <c r="X199" t="n">
-        <v>-16000</v>
+        <v>-4000</v>
       </c>
       <c r="Y199" t="n">
-        <v>-439261</v>
+        <v>-20271</v>
       </c>
       <c r="Z199" t="n">
-        <v>-400261</v>
+        <v>-9988</v>
       </c>
       <c r="AA199" t="n">
-        <v>-392261</v>
+        <v>10650</v>
       </c>
       <c r="AB199" t="n">
-        <v>-775677</v>
+        <v>-765</v>
       </c>
       <c r="AC199" t="n">
         <v>0</v>
@@ -27752,12 +27752,12 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>2608.TW</t>
+          <t>9904.TW</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>嘉里大榮</t>
+          <t>寶成</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -27766,28 +27766,28 @@
         </is>
       </c>
       <c r="D200" t="n">
-        <v>29.1</v>
+        <v>24.25</v>
       </c>
       <c r="E200" t="n">
-        <v>29.29</v>
+        <v>24.44</v>
       </c>
       <c r="F200" t="n">
-        <v>29.31</v>
+        <v>24.34</v>
       </c>
       <c r="G200" t="n">
-        <v>29.14</v>
+        <v>24.68</v>
       </c>
       <c r="H200" t="n">
-        <v>170739</v>
+        <v>21266835</v>
       </c>
       <c r="I200" t="n">
-        <v>254372</v>
+        <v>29651675</v>
       </c>
       <c r="J200" t="n">
-        <v>29.7</v>
+        <v>26.2</v>
       </c>
       <c r="K200" t="n">
-        <v>28.6</v>
+        <v>23.8</v>
       </c>
       <c r="L200" t="inlineStr">
         <is>
@@ -27795,52 +27795,52 @@
         </is>
       </c>
       <c r="M200" t="n">
-        <v>-16100</v>
+        <v>-5604465</v>
       </c>
       <c r="N200" t="n">
-        <v>200432</v>
+        <v>-12138312</v>
       </c>
       <c r="O200" t="n">
-        <v>541514</v>
+        <v>12581146</v>
       </c>
       <c r="P200" t="n">
-        <v>684876</v>
+        <v>4796142</v>
       </c>
       <c r="Q200" t="n">
-        <v>9900</v>
+        <v>-2496180</v>
       </c>
       <c r="R200" t="n">
-        <v>214432</v>
+        <v>-3105680</v>
       </c>
       <c r="S200" t="n">
-        <v>531514</v>
+        <v>25969860</v>
       </c>
       <c r="T200" t="n">
-        <v>679395</v>
+        <v>17514827</v>
       </c>
       <c r="U200" t="n">
-        <v>0</v>
+        <v>-3103399</v>
       </c>
       <c r="V200" t="n">
-        <v>0</v>
+        <v>-9333268</v>
       </c>
       <c r="W200" t="n">
-        <v>0</v>
+        <v>-14846357</v>
       </c>
       <c r="X200" t="n">
-        <v>0</v>
+        <v>-14714968</v>
       </c>
       <c r="Y200" t="n">
-        <v>-26000</v>
+        <v>-4886</v>
       </c>
       <c r="Z200" t="n">
-        <v>-14000</v>
+        <v>300636</v>
       </c>
       <c r="AA200" t="n">
-        <v>10000</v>
+        <v>1457643</v>
       </c>
       <c r="AB200" t="n">
-        <v>5481</v>
+        <v>1996283</v>
       </c>
       <c r="AC200" t="n">
         <v>0</v>
@@ -27877,12 +27877,12 @@
       </c>
       <c r="AN200" t="inlineStr">
         <is>
-          <t>5日法人明顯買超</t>
+          <t>5日法人明顯買超、外資買投信賣</t>
         </is>
       </c>
       <c r="AO200" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、量能未放大、接近20日低點、5日法人明顯買超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、量能未放大、接近20日低點、5日法人明顯買超、外資買投信賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
@@ -28163,12 +28163,12 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>9904.TW</t>
+          <t>2903.TW</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>寶成</t>
+          <t>遠百</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -28177,28 +28177,28 @@
         </is>
       </c>
       <c r="D203" t="n">
-        <v>24.25</v>
+        <v>22.1</v>
       </c>
       <c r="E203" t="n">
-        <v>24.44</v>
+        <v>22.33</v>
       </c>
       <c r="F203" t="n">
-        <v>24.34</v>
+        <v>22.21</v>
       </c>
       <c r="G203" t="n">
-        <v>24.68</v>
+        <v>22.46</v>
       </c>
       <c r="H203" t="n">
-        <v>21266835</v>
+        <v>2134904</v>
       </c>
       <c r="I203" t="n">
-        <v>29651675</v>
+        <v>2276463</v>
       </c>
       <c r="J203" t="n">
-        <v>26.2</v>
+        <v>23.8</v>
       </c>
       <c r="K203" t="n">
-        <v>23.8</v>
+        <v>21.55</v>
       </c>
       <c r="L203" t="inlineStr">
         <is>
@@ -28206,52 +28206,52 @@
         </is>
       </c>
       <c r="M203" t="n">
-        <v>-5604465</v>
+        <v>-1198261</v>
       </c>
       <c r="N203" t="n">
-        <v>-12138312</v>
+        <v>-92681</v>
       </c>
       <c r="O203" t="n">
-        <v>12581146</v>
+        <v>2383398</v>
       </c>
       <c r="P203" t="n">
-        <v>4796142</v>
+        <v>2787598</v>
       </c>
       <c r="Q203" t="n">
-        <v>-2496180</v>
+        <v>-759000</v>
       </c>
       <c r="R203" t="n">
-        <v>-3105680</v>
+        <v>309580</v>
       </c>
       <c r="S203" t="n">
-        <v>25969860</v>
+        <v>2781659</v>
       </c>
       <c r="T203" t="n">
-        <v>17514827</v>
+        <v>3579275</v>
       </c>
       <c r="U203" t="n">
-        <v>-3103399</v>
+        <v>0</v>
       </c>
       <c r="V203" t="n">
-        <v>-9333268</v>
+        <v>-2000</v>
       </c>
       <c r="W203" t="n">
-        <v>-14846357</v>
+        <v>-6000</v>
       </c>
       <c r="X203" t="n">
-        <v>-14714968</v>
+        <v>-16000</v>
       </c>
       <c r="Y203" t="n">
-        <v>-4886</v>
+        <v>-439261</v>
       </c>
       <c r="Z203" t="n">
-        <v>300636</v>
+        <v>-400261</v>
       </c>
       <c r="AA203" t="n">
-        <v>1457643</v>
+        <v>-392261</v>
       </c>
       <c r="AB203" t="n">
-        <v>1996283</v>
+        <v>-775677</v>
       </c>
       <c r="AC203" t="n">
         <v>0</v>
@@ -28300,12 +28300,12 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>2395.TW</t>
+          <t>2608.TW</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>研華</t>
+          <t>嘉里大榮</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
@@ -28314,96 +28314,96 @@
         </is>
       </c>
       <c r="D204" t="n">
-        <v>596</v>
+        <v>29.1</v>
       </c>
       <c r="E204" t="n">
-        <v>544.4</v>
+        <v>29.29</v>
       </c>
       <c r="F204" t="n">
-        <v>540.6</v>
+        <v>29.31</v>
       </c>
       <c r="G204" t="n">
-        <v>516.25</v>
+        <v>29.14</v>
       </c>
       <c r="H204" t="n">
-        <v>9512024</v>
+        <v>170739</v>
       </c>
       <c r="I204" t="n">
-        <v>4514156</v>
+        <v>254372</v>
       </c>
       <c r="J204" t="n">
-        <v>618</v>
+        <v>29.7</v>
       </c>
       <c r="K204" t="n">
-        <v>453</v>
+        <v>28.6</v>
       </c>
       <c r="L204" t="inlineStr">
         <is>
-          <t>帶量突破20日高點</t>
+          <t>無明顯異常</t>
         </is>
       </c>
       <c r="M204" t="n">
-        <v>-751632</v>
+        <v>-16100</v>
       </c>
       <c r="N204" t="n">
-        <v>-1325837</v>
+        <v>200432</v>
       </c>
       <c r="O204" t="n">
-        <v>-1171592</v>
+        <v>541514</v>
       </c>
       <c r="P204" t="n">
-        <v>10683</v>
+        <v>684876</v>
       </c>
       <c r="Q204" t="n">
-        <v>-1405730</v>
+        <v>9900</v>
       </c>
       <c r="R204" t="n">
-        <v>-2769237</v>
+        <v>214432</v>
       </c>
       <c r="S204" t="n">
-        <v>-3321450</v>
+        <v>531514</v>
       </c>
       <c r="T204" t="n">
-        <v>-2535733</v>
+        <v>679395</v>
       </c>
       <c r="U204" t="n">
-        <v>528662</v>
+        <v>0</v>
       </c>
       <c r="V204" t="n">
-        <v>1114746</v>
+        <v>0</v>
       </c>
       <c r="W204" t="n">
-        <v>1860549</v>
+        <v>0</v>
       </c>
       <c r="X204" t="n">
-        <v>1978373</v>
+        <v>0</v>
       </c>
       <c r="Y204" t="n">
-        <v>125436</v>
+        <v>-26000</v>
       </c>
       <c r="Z204" t="n">
-        <v>328654</v>
+        <v>-14000</v>
       </c>
       <c r="AA204" t="n">
-        <v>289309</v>
+        <v>10000</v>
       </c>
       <c r="AB204" t="n">
-        <v>568043</v>
+        <v>5481</v>
       </c>
       <c r="AC204" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AD204" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AE204" t="n">
-        <v>65</v>
+        <v>-30</v>
       </c>
       <c r="AF204" t="n">
-        <v>-80</v>
+        <v>30</v>
       </c>
       <c r="AG204" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="AH204" t="inlineStr"/>
       <c r="AI204" t="inlineStr"/>
@@ -28420,29 +28420,29 @@
       </c>
       <c r="AM204" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、爆量、帶量突破20日高點</t>
+          <t>跌破5日線、量能未放大、接近20日低點</t>
         </is>
       </c>
       <c r="AN204" t="inlineStr">
         <is>
-          <t>法人連續偏賣、中期買超轉短線賣壓、5日法人明顯賣超、投信買外資賣</t>
+          <t>5日法人明顯買超</t>
         </is>
       </c>
       <c r="AO204" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、多頭排列、爆量、帶量突破20日高點、法人連續偏賣、中期買超轉短線賣壓、5日法人明顯賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、量能未放大、接近20日低點、5日法人明顯買超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>4908.TWO</t>
+          <t>2395.TW</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>前鼎</t>
+          <t>研華</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
@@ -28451,96 +28451,96 @@
         </is>
       </c>
       <c r="D205" t="n">
-        <v>144.5</v>
+        <v>596</v>
       </c>
       <c r="E205" t="n">
-        <v>141.4</v>
+        <v>544.4</v>
       </c>
       <c r="F205" t="n">
-        <v>151</v>
+        <v>540.6</v>
       </c>
       <c r="G205" t="n">
-        <v>166.45</v>
+        <v>516.25</v>
       </c>
       <c r="H205" t="n">
-        <v>1158000</v>
+        <v>9512024</v>
       </c>
       <c r="I205" t="n">
-        <v>1189400</v>
+        <v>4514156</v>
       </c>
       <c r="J205" t="n">
-        <v>212.5</v>
+        <v>618</v>
       </c>
       <c r="K205" t="n">
-        <v>124.5</v>
+        <v>453</v>
       </c>
       <c r="L205" t="inlineStr">
         <is>
-          <t>無明顯異常</t>
+          <t>帶量突破20日高點</t>
         </is>
       </c>
       <c r="M205" t="n">
-        <v>0</v>
+        <v>-751632</v>
       </c>
       <c r="N205" t="n">
-        <v>0</v>
+        <v>-1325837</v>
       </c>
       <c r="O205" t="n">
-        <v>0</v>
+        <v>-1171592</v>
       </c>
       <c r="P205" t="n">
-        <v>0</v>
+        <v>10683</v>
       </c>
       <c r="Q205" t="n">
-        <v>0</v>
+        <v>-1405730</v>
       </c>
       <c r="R205" t="n">
-        <v>0</v>
+        <v>-2769237</v>
       </c>
       <c r="S205" t="n">
-        <v>0</v>
+        <v>-3321450</v>
       </c>
       <c r="T205" t="n">
-        <v>0</v>
+        <v>-2535733</v>
       </c>
       <c r="U205" t="n">
-        <v>0</v>
+        <v>528662</v>
       </c>
       <c r="V205" t="n">
-        <v>0</v>
+        <v>1114746</v>
       </c>
       <c r="W205" t="n">
-        <v>0</v>
+        <v>1860549</v>
       </c>
       <c r="X205" t="n">
-        <v>0</v>
+        <v>1978373</v>
       </c>
       <c r="Y205" t="n">
-        <v>0</v>
+        <v>125436</v>
       </c>
       <c r="Z205" t="n">
-        <v>0</v>
+        <v>328654</v>
       </c>
       <c r="AA205" t="n">
-        <v>0</v>
+        <v>289309</v>
       </c>
       <c r="AB205" t="n">
-        <v>0</v>
+        <v>568043</v>
       </c>
       <c r="AC205" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="AD205" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="AE205" t="n">
-        <v>-5</v>
+        <v>65</v>
       </c>
       <c r="AF205" t="n">
-        <v>0</v>
+        <v>-80</v>
       </c>
       <c r="AG205" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AH205" t="inlineStr"/>
       <c r="AI205" t="inlineStr"/>
@@ -28557,29 +28557,29 @@
       </c>
       <c r="AM205" t="inlineStr">
         <is>
-          <t>站上5日線、空頭排列、量能未放大</t>
+          <t>站上5日線、多頭排列、爆量、帶量突破20日高點</t>
         </is>
       </c>
       <c r="AN205" t="inlineStr">
         <is>
-          <t>籌碼中性</t>
+          <t>法人連續偏賣、中期買超轉短線賣壓、5日法人明顯賣超、投信買外資賣</t>
         </is>
       </c>
       <c r="AO205" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、空頭排列、量能未放大、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、多頭排列、爆量、帶量突破20日高點、法人連續偏賣、中期買超轉短線賣壓、5日法人明顯賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>8299.TWO</t>
+          <t>3260.TWO</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>群聯</t>
+          <t>威剛</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
@@ -28588,28 +28588,28 @@
         </is>
       </c>
       <c r="D206" t="n">
-        <v>1915</v>
+        <v>379.5</v>
       </c>
       <c r="E206" t="n">
-        <v>1854</v>
+        <v>372.7</v>
       </c>
       <c r="F206" t="n">
-        <v>1995.5</v>
+        <v>389.35</v>
       </c>
       <c r="G206" t="n">
-        <v>2160.25</v>
+        <v>397.73</v>
       </c>
       <c r="H206" t="n">
-        <v>4333000</v>
+        <v>6356000</v>
       </c>
       <c r="I206" t="n">
-        <v>4928000</v>
+        <v>7207400</v>
       </c>
       <c r="J206" t="n">
-        <v>2640</v>
+        <v>423</v>
       </c>
       <c r="K206" t="n">
-        <v>1685</v>
+        <v>334</v>
       </c>
       <c r="L206" t="inlineStr">
         <is>
@@ -28711,12 +28711,12 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>3260.TWO</t>
+          <t>6409.TW</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>威剛</t>
+          <t>旭隼</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
@@ -28725,28 +28725,28 @@
         </is>
       </c>
       <c r="D207" t="n">
-        <v>379.5</v>
+        <v>998</v>
       </c>
       <c r="E207" t="n">
-        <v>372.7</v>
+        <v>992.4</v>
       </c>
       <c r="F207" t="n">
-        <v>389.35</v>
+        <v>1042.2</v>
       </c>
       <c r="G207" t="n">
-        <v>397.73</v>
+        <v>1073.1</v>
       </c>
       <c r="H207" t="n">
-        <v>6356000</v>
+        <v>597756</v>
       </c>
       <c r="I207" t="n">
-        <v>7207400</v>
+        <v>643106</v>
       </c>
       <c r="J207" t="n">
-        <v>423</v>
+        <v>1380</v>
       </c>
       <c r="K207" t="n">
-        <v>334</v>
+        <v>907</v>
       </c>
       <c r="L207" t="inlineStr">
         <is>
@@ -28754,52 +28754,52 @@
         </is>
       </c>
       <c r="M207" t="n">
-        <v>0</v>
+        <v>-35891</v>
       </c>
       <c r="N207" t="n">
-        <v>0</v>
+        <v>-133829</v>
       </c>
       <c r="O207" t="n">
-        <v>0</v>
+        <v>12087</v>
       </c>
       <c r="P207" t="n">
-        <v>0</v>
+        <v>-935018</v>
       </c>
       <c r="Q207" t="n">
-        <v>0</v>
+        <v>-100938</v>
       </c>
       <c r="R207" t="n">
-        <v>0</v>
+        <v>-456448</v>
       </c>
       <c r="S207" t="n">
-        <v>0</v>
+        <v>-357251</v>
       </c>
       <c r="T207" t="n">
-        <v>0</v>
+        <v>-1389947</v>
       </c>
       <c r="U207" t="n">
-        <v>0</v>
+        <v>59914</v>
       </c>
       <c r="V207" t="n">
-        <v>0</v>
+        <v>326450</v>
       </c>
       <c r="W207" t="n">
-        <v>0</v>
+        <v>413978</v>
       </c>
       <c r="X207" t="n">
-        <v>0</v>
+        <v>504775</v>
       </c>
       <c r="Y207" t="n">
-        <v>0</v>
+        <v>5133</v>
       </c>
       <c r="Z207" t="n">
-        <v>0</v>
+        <v>-3831</v>
       </c>
       <c r="AA207" t="n">
-        <v>0</v>
+        <v>-44640</v>
       </c>
       <c r="AB207" t="n">
-        <v>0</v>
+        <v>-49846</v>
       </c>
       <c r="AC207" t="n">
         <v>-2</v>
@@ -28836,12 +28836,12 @@
       </c>
       <c r="AN207" t="inlineStr">
         <is>
-          <t>籌碼中性</t>
+          <t>籌碼中性、投信買外資賣</t>
         </is>
       </c>
       <c r="AO207" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、空頭排列、量能未放大、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、空頭排列、量能未放大、籌碼中性、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
@@ -28985,12 +28985,12 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>6147.TWO</t>
+          <t>4908.TWO</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>頎邦</t>
+          <t>前鼎</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
@@ -28999,28 +28999,28 @@
         </is>
       </c>
       <c r="D209" t="n">
-        <v>190</v>
+        <v>144.5</v>
       </c>
       <c r="E209" t="n">
-        <v>180.7</v>
+        <v>141.4</v>
       </c>
       <c r="F209" t="n">
-        <v>190.85</v>
+        <v>151</v>
       </c>
       <c r="G209" t="n">
-        <v>205</v>
+        <v>166.45</v>
       </c>
       <c r="H209" t="n">
-        <v>23213000</v>
+        <v>1158000</v>
       </c>
       <c r="I209" t="n">
-        <v>24726800</v>
+        <v>1189400</v>
       </c>
       <c r="J209" t="n">
-        <v>258.5</v>
+        <v>212.5</v>
       </c>
       <c r="K209" t="n">
-        <v>161</v>
+        <v>124.5</v>
       </c>
       <c r="L209" t="inlineStr">
         <is>
@@ -29122,12 +29122,12 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>6409.TW</t>
+          <t>3324.TWO</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>旭隼</t>
+          <t>雙鴻</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
@@ -29136,28 +29136,28 @@
         </is>
       </c>
       <c r="D210" t="n">
-        <v>998</v>
+        <v>908</v>
       </c>
       <c r="E210" t="n">
-        <v>992.4</v>
+        <v>901.4</v>
       </c>
       <c r="F210" t="n">
-        <v>1042.2</v>
+        <v>901.7</v>
       </c>
       <c r="G210" t="n">
-        <v>1073.1</v>
+        <v>955.35</v>
       </c>
       <c r="H210" t="n">
-        <v>597756</v>
+        <v>1921000</v>
       </c>
       <c r="I210" t="n">
-        <v>643106</v>
+        <v>2363800</v>
       </c>
       <c r="J210" t="n">
-        <v>1380</v>
+        <v>1075</v>
       </c>
       <c r="K210" t="n">
-        <v>907</v>
+        <v>819</v>
       </c>
       <c r="L210" t="inlineStr">
         <is>
@@ -29165,52 +29165,52 @@
         </is>
       </c>
       <c r="M210" t="n">
-        <v>-35891</v>
+        <v>0</v>
       </c>
       <c r="N210" t="n">
-        <v>-133829</v>
+        <v>0</v>
       </c>
       <c r="O210" t="n">
-        <v>12087</v>
+        <v>0</v>
       </c>
       <c r="P210" t="n">
-        <v>-935018</v>
+        <v>0</v>
       </c>
       <c r="Q210" t="n">
-        <v>-100938</v>
+        <v>0</v>
       </c>
       <c r="R210" t="n">
-        <v>-456448</v>
+        <v>0</v>
       </c>
       <c r="S210" t="n">
-        <v>-357251</v>
+        <v>0</v>
       </c>
       <c r="T210" t="n">
-        <v>-1389947</v>
+        <v>0</v>
       </c>
       <c r="U210" t="n">
-        <v>59914</v>
+        <v>0</v>
       </c>
       <c r="V210" t="n">
-        <v>326450</v>
+        <v>0</v>
       </c>
       <c r="W210" t="n">
-        <v>413978</v>
+        <v>0</v>
       </c>
       <c r="X210" t="n">
-        <v>504775</v>
+        <v>0</v>
       </c>
       <c r="Y210" t="n">
-        <v>5133</v>
+        <v>0</v>
       </c>
       <c r="Z210" t="n">
-        <v>-3831</v>
+        <v>0</v>
       </c>
       <c r="AA210" t="n">
-        <v>-44640</v>
+        <v>0</v>
       </c>
       <c r="AB210" t="n">
-        <v>-49846</v>
+        <v>0</v>
       </c>
       <c r="AC210" t="n">
         <v>-2</v>
@@ -29247,12 +29247,12 @@
       </c>
       <c r="AN210" t="inlineStr">
         <is>
-          <t>籌碼中性、投信買外資賣</t>
+          <t>籌碼中性</t>
         </is>
       </c>
       <c r="AO210" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、空頭排列、量能未放大、籌碼中性、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、空頭排列、量能未放大、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
@@ -30081,12 +30081,12 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>2501.TW</t>
+          <t>6147.TWO</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>國建</t>
+          <t>頎邦</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
@@ -30095,28 +30095,28 @@
         </is>
       </c>
       <c r="D217" t="n">
-        <v>22.3</v>
+        <v>190</v>
       </c>
       <c r="E217" t="n">
-        <v>22.46</v>
+        <v>180.7</v>
       </c>
       <c r="F217" t="n">
-        <v>22.76</v>
+        <v>190.85</v>
       </c>
       <c r="G217" t="n">
-        <v>23.54</v>
+        <v>205</v>
       </c>
       <c r="H217" t="n">
-        <v>1112648</v>
+        <v>23213000</v>
       </c>
       <c r="I217" t="n">
-        <v>1845615</v>
+        <v>24726800</v>
       </c>
       <c r="J217" t="n">
-        <v>24.9</v>
+        <v>258.5</v>
       </c>
       <c r="K217" t="n">
-        <v>21.5</v>
+        <v>161</v>
       </c>
       <c r="L217" t="inlineStr">
         <is>
@@ -30124,52 +30124,52 @@
         </is>
       </c>
       <c r="M217" t="n">
-        <v>-187197</v>
+        <v>0</v>
       </c>
       <c r="N217" t="n">
-        <v>-70172</v>
+        <v>0</v>
       </c>
       <c r="O217" t="n">
-        <v>1892725</v>
+        <v>0</v>
       </c>
       <c r="P217" t="n">
-        <v>-3669193</v>
+        <v>0</v>
       </c>
       <c r="Q217" t="n">
-        <v>-163000</v>
+        <v>0</v>
       </c>
       <c r="R217" t="n">
-        <v>-116049</v>
+        <v>0</v>
       </c>
       <c r="S217" t="n">
-        <v>1512844</v>
+        <v>0</v>
       </c>
       <c r="T217" t="n">
-        <v>-3796664</v>
+        <v>0</v>
       </c>
       <c r="U217" t="n">
-        <v>20000</v>
+        <v>0</v>
       </c>
       <c r="V217" t="n">
-        <v>45000</v>
+        <v>0</v>
       </c>
       <c r="W217" t="n">
-        <v>378000</v>
+        <v>0</v>
       </c>
       <c r="X217" t="n">
-        <v>566000</v>
+        <v>0</v>
       </c>
       <c r="Y217" t="n">
-        <v>-44197</v>
+        <v>0</v>
       </c>
       <c r="Z217" t="n">
-        <v>877</v>
+        <v>0</v>
       </c>
       <c r="AA217" t="n">
-        <v>1881</v>
+        <v>0</v>
       </c>
       <c r="AB217" t="n">
-        <v>-438529</v>
+        <v>0</v>
       </c>
       <c r="AC217" t="n">
         <v>-2</v>
@@ -30178,10 +30178,10 @@
         <v>-2</v>
       </c>
       <c r="AE217" t="n">
-        <v>-55</v>
+        <v>-5</v>
       </c>
       <c r="AF217" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="AG217" t="n">
         <v>0</v>
@@ -30201,29 +30201,29 @@
       </c>
       <c r="AM217" t="inlineStr">
         <is>
-          <t>跌破5日線、空頭排列、量能未放大、接近20日低點</t>
+          <t>站上5日線、空頭排列、量能未放大</t>
         </is>
       </c>
       <c r="AN217" t="inlineStr">
         <is>
-          <t>5日法人明顯買超、外資投信同步買超</t>
+          <t>籌碼中性</t>
         </is>
       </c>
       <c r="AO217" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、空頭排列、量能未放大、接近20日低點、5日法人明顯買超、外資投信同步買超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、空頭排列、量能未放大、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>3324.TWO</t>
+          <t>2501.TW</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>雙鴻</t>
+          <t>國建</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
@@ -30232,28 +30232,28 @@
         </is>
       </c>
       <c r="D218" t="n">
-        <v>908</v>
+        <v>22.3</v>
       </c>
       <c r="E218" t="n">
-        <v>901.4</v>
+        <v>22.46</v>
       </c>
       <c r="F218" t="n">
-        <v>901.7</v>
+        <v>22.76</v>
       </c>
       <c r="G218" t="n">
-        <v>955.35</v>
+        <v>23.54</v>
       </c>
       <c r="H218" t="n">
-        <v>1921000</v>
+        <v>1112648</v>
       </c>
       <c r="I218" t="n">
-        <v>2363800</v>
+        <v>1845615</v>
       </c>
       <c r="J218" t="n">
-        <v>1075</v>
+        <v>24.9</v>
       </c>
       <c r="K218" t="n">
-        <v>819</v>
+        <v>21.5</v>
       </c>
       <c r="L218" t="inlineStr">
         <is>
@@ -30261,52 +30261,52 @@
         </is>
       </c>
       <c r="M218" t="n">
-        <v>0</v>
+        <v>-187197</v>
       </c>
       <c r="N218" t="n">
-        <v>0</v>
+        <v>-70172</v>
       </c>
       <c r="O218" t="n">
-        <v>0</v>
+        <v>1892725</v>
       </c>
       <c r="P218" t="n">
-        <v>0</v>
+        <v>-3669193</v>
       </c>
       <c r="Q218" t="n">
-        <v>0</v>
+        <v>-163000</v>
       </c>
       <c r="R218" t="n">
-        <v>0</v>
+        <v>-116049</v>
       </c>
       <c r="S218" t="n">
-        <v>0</v>
+        <v>1512844</v>
       </c>
       <c r="T218" t="n">
-        <v>0</v>
+        <v>-3796664</v>
       </c>
       <c r="U218" t="n">
-        <v>0</v>
+        <v>20000</v>
       </c>
       <c r="V218" t="n">
-        <v>0</v>
+        <v>45000</v>
       </c>
       <c r="W218" t="n">
-        <v>0</v>
+        <v>378000</v>
       </c>
       <c r="X218" t="n">
-        <v>0</v>
+        <v>566000</v>
       </c>
       <c r="Y218" t="n">
-        <v>0</v>
+        <v>-44197</v>
       </c>
       <c r="Z218" t="n">
-        <v>0</v>
+        <v>877</v>
       </c>
       <c r="AA218" t="n">
-        <v>0</v>
+        <v>1881</v>
       </c>
       <c r="AB218" t="n">
-        <v>0</v>
+        <v>-438529</v>
       </c>
       <c r="AC218" t="n">
         <v>-2</v>
@@ -30315,10 +30315,10 @@
         <v>-2</v>
       </c>
       <c r="AE218" t="n">
-        <v>-5</v>
+        <v>-55</v>
       </c>
       <c r="AF218" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AG218" t="n">
         <v>0</v>
@@ -30338,17 +30338,17 @@
       </c>
       <c r="AM218" t="inlineStr">
         <is>
-          <t>站上5日線、空頭排列、量能未放大</t>
+          <t>跌破5日線、空頭排列、量能未放大、接近20日低點</t>
         </is>
       </c>
       <c r="AN218" t="inlineStr">
         <is>
-          <t>籌碼中性</t>
+          <t>5日法人明顯買超、外資投信同步買超</t>
         </is>
       </c>
       <c r="AO218" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、空頭排列、量能未放大、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、空頭排列、量能未放大、接近20日低點、5日法人明顯買超、外資投信同步買超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
@@ -31040,12 +31040,12 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>3680.TWO</t>
+          <t>8299.TWO</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>家登</t>
+          <t>群聯</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
@@ -31054,28 +31054,28 @@
         </is>
       </c>
       <c r="D224" t="n">
-        <v>494</v>
+        <v>1915</v>
       </c>
       <c r="E224" t="n">
-        <v>478.6</v>
+        <v>1854</v>
       </c>
       <c r="F224" t="n">
-        <v>494.35</v>
+        <v>1995.5</v>
       </c>
       <c r="G224" t="n">
-        <v>506.85</v>
+        <v>2160.25</v>
       </c>
       <c r="H224" t="n">
-        <v>2510000</v>
+        <v>4333000</v>
       </c>
       <c r="I224" t="n">
-        <v>2931400</v>
+        <v>4928000</v>
       </c>
       <c r="J224" t="n">
-        <v>558</v>
+        <v>2640</v>
       </c>
       <c r="K224" t="n">
-        <v>423</v>
+        <v>1685</v>
       </c>
       <c r="L224" t="inlineStr">
         <is>
@@ -31177,12 +31177,12 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>4123.TWO</t>
+          <t>3680.TWO</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>晟德</t>
+          <t>家登</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
@@ -31191,28 +31191,28 @@
         </is>
       </c>
       <c r="D225" t="n">
-        <v>38.35</v>
+        <v>494</v>
       </c>
       <c r="E225" t="n">
-        <v>37.78</v>
+        <v>478.6</v>
       </c>
       <c r="F225" t="n">
-        <v>38.07</v>
+        <v>494.35</v>
       </c>
       <c r="G225" t="n">
-        <v>38.28</v>
+        <v>506.85</v>
       </c>
       <c r="H225" t="n">
-        <v>1846000</v>
+        <v>2510000</v>
       </c>
       <c r="I225" t="n">
-        <v>1752400</v>
+        <v>2931400</v>
       </c>
       <c r="J225" t="n">
-        <v>40.55</v>
+        <v>558</v>
       </c>
       <c r="K225" t="n">
-        <v>36.6</v>
+        <v>423</v>
       </c>
       <c r="L225" t="inlineStr">
         <is>
@@ -31297,7 +31297,7 @@
       </c>
       <c r="AM225" t="inlineStr">
         <is>
-          <t>站上5日線、空頭排列、量能溫和放大、接近20日低點</t>
+          <t>站上5日線、空頭排列、量能未放大</t>
         </is>
       </c>
       <c r="AN225" t="inlineStr">
@@ -31307,19 +31307,19 @@
       </c>
       <c r="AO225" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、空頭排列、量能溫和放大、接近20日低點、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、空頭排列、量能未放大、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>6488.TWO</t>
+          <t>4123.TWO</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>環球晶</t>
+          <t>晟德</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
@@ -31328,28 +31328,28 @@
         </is>
       </c>
       <c r="D226" t="n">
-        <v>1240</v>
+        <v>38.35</v>
       </c>
       <c r="E226" t="n">
-        <v>1264</v>
+        <v>37.78</v>
       </c>
       <c r="F226" t="n">
-        <v>1338</v>
+        <v>38.07</v>
       </c>
       <c r="G226" t="n">
-        <v>1217.3</v>
+        <v>38.28</v>
       </c>
       <c r="H226" t="n">
-        <v>11636000</v>
+        <v>1846000</v>
       </c>
       <c r="I226" t="n">
-        <v>10973800</v>
+        <v>1752400</v>
       </c>
       <c r="J226" t="n">
-        <v>1600</v>
+        <v>40.55</v>
       </c>
       <c r="K226" t="n">
-        <v>866</v>
+        <v>36.6</v>
       </c>
       <c r="L226" t="inlineStr">
         <is>
@@ -31405,13 +31405,13 @@
         <v>0</v>
       </c>
       <c r="AC226" t="n">
-        <v>-4</v>
+        <v>-2</v>
       </c>
       <c r="AD226" t="n">
-        <v>-4</v>
+        <v>-2</v>
       </c>
       <c r="AE226" t="n">
-        <v>-10</v>
+        <v>-5</v>
       </c>
       <c r="AF226" t="n">
         <v>0</v>
@@ -31434,7 +31434,7 @@
       </c>
       <c r="AM226" t="inlineStr">
         <is>
-          <t>跌破5日線、量能溫和放大</t>
+          <t>站上5日線、空頭排列、量能溫和放大、接近20日低點</t>
         </is>
       </c>
       <c r="AN226" t="inlineStr">
@@ -31444,19 +31444,19 @@
       </c>
       <c r="AO226" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、量能溫和放大、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、空頭排列、量能溫和放大、接近20日低點、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>1301.TW</t>
+          <t>6488.TWO</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>台塑</t>
+          <t>環球晶</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
@@ -31465,28 +31465,28 @@
         </is>
       </c>
       <c r="D227" t="n">
-        <v>63.5</v>
+        <v>1240</v>
       </c>
       <c r="E227" t="n">
-        <v>63.1</v>
+        <v>1264</v>
       </c>
       <c r="F227" t="n">
-        <v>61.78</v>
+        <v>1338</v>
       </c>
       <c r="G227" t="n">
-        <v>59.2</v>
+        <v>1217.3</v>
       </c>
       <c r="H227" t="n">
-        <v>61438338</v>
+        <v>11636000</v>
       </c>
       <c r="I227" t="n">
-        <v>72907964</v>
+        <v>10973800</v>
       </c>
       <c r="J227" t="n">
-        <v>68.59999999999999</v>
+        <v>1600</v>
       </c>
       <c r="K227" t="n">
-        <v>48.15</v>
+        <v>866</v>
       </c>
       <c r="L227" t="inlineStr">
         <is>
@@ -31494,52 +31494,52 @@
         </is>
       </c>
       <c r="M227" t="n">
-        <v>10038023</v>
+        <v>0</v>
       </c>
       <c r="N227" t="n">
-        <v>-1917762</v>
+        <v>0</v>
       </c>
       <c r="O227" t="n">
-        <v>-5272270</v>
+        <v>0</v>
       </c>
       <c r="P227" t="n">
-        <v>24491334</v>
+        <v>0</v>
       </c>
       <c r="Q227" t="n">
-        <v>10118099</v>
+        <v>0</v>
       </c>
       <c r="R227" t="n">
-        <v>-2673676</v>
+        <v>0</v>
       </c>
       <c r="S227" t="n">
-        <v>-5857406</v>
+        <v>0</v>
       </c>
       <c r="T227" t="n">
-        <v>21546112</v>
+        <v>0</v>
       </c>
       <c r="U227" t="n">
-        <v>330000</v>
+        <v>0</v>
       </c>
       <c r="V227" t="n">
-        <v>673900</v>
+        <v>0</v>
       </c>
       <c r="W227" t="n">
-        <v>659900</v>
+        <v>0</v>
       </c>
       <c r="X227" t="n">
-        <v>642900</v>
+        <v>0</v>
       </c>
       <c r="Y227" t="n">
-        <v>-410076</v>
+        <v>0</v>
       </c>
       <c r="Z227" t="n">
-        <v>82014</v>
+        <v>0</v>
       </c>
       <c r="AA227" t="n">
-        <v>-74764</v>
+        <v>0</v>
       </c>
       <c r="AB227" t="n">
-        <v>2302322</v>
+        <v>0</v>
       </c>
       <c r="AC227" t="n">
         <v>-4</v>
@@ -31548,10 +31548,10 @@
         <v>-4</v>
       </c>
       <c r="AE227" t="n">
-        <v>45</v>
+        <v>-10</v>
       </c>
       <c r="AF227" t="n">
-        <v>-55</v>
+        <v>0</v>
       </c>
       <c r="AG227" t="n">
         <v>0</v>
@@ -31571,17 +31571,17 @@
       </c>
       <c r="AM227" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、量能未放大</t>
+          <t>跌破5日線、量能溫和放大</t>
         </is>
       </c>
       <c r="AN227" t="inlineStr">
         <is>
-          <t>中期買超轉短線賣壓、5日法人明顯賣超、投信買外資賣</t>
+          <t>籌碼中性</t>
         </is>
       </c>
       <c r="AO227" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、多頭排列、量能未放大、中期買超轉短線賣壓、5日法人明顯賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、量能溫和放大、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
@@ -31862,42 +31862,42 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>2369.TW</t>
+          <t>00923.TW</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>菱生</t>
+          <t>群益台ESG低碳50</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>個股</t>
+          <t>ETF</t>
         </is>
       </c>
       <c r="D230" t="n">
-        <v>36.45</v>
+        <v>41.08</v>
       </c>
       <c r="E230" t="n">
-        <v>35.9</v>
+        <v>40.22</v>
       </c>
       <c r="F230" t="n">
-        <v>38.5</v>
+        <v>41</v>
       </c>
       <c r="G230" t="n">
-        <v>39.62</v>
+        <v>41.9</v>
       </c>
       <c r="H230" t="n">
-        <v>18804611</v>
+        <v>5247693</v>
       </c>
       <c r="I230" t="n">
-        <v>13827451</v>
+        <v>4901301</v>
       </c>
       <c r="J230" t="n">
-        <v>45.7</v>
+        <v>43.92</v>
       </c>
       <c r="K230" t="n">
-        <v>32.4</v>
+        <v>38.33</v>
       </c>
       <c r="L230" t="inlineStr">
         <is>
@@ -31905,28 +31905,28 @@
         </is>
       </c>
       <c r="M230" t="n">
-        <v>1863313</v>
+        <v>215974</v>
       </c>
       <c r="N230" t="n">
-        <v>141985</v>
+        <v>97867</v>
       </c>
       <c r="O230" t="n">
-        <v>-6972509</v>
+        <v>-3680090</v>
       </c>
       <c r="P230" t="n">
-        <v>-14135863</v>
+        <v>-4364833</v>
       </c>
       <c r="Q230" t="n">
-        <v>1761511</v>
+        <v>-1460990</v>
       </c>
       <c r="R230" t="n">
-        <v>573749</v>
+        <v>-1095200</v>
       </c>
       <c r="S230" t="n">
-        <v>-6091206</v>
+        <v>-1944595</v>
       </c>
       <c r="T230" t="n">
-        <v>-13487228</v>
+        <v>-2008420</v>
       </c>
       <c r="U230" t="n">
         <v>0</v>
@@ -31941,16 +31941,16 @@
         <v>0</v>
       </c>
       <c r="Y230" t="n">
-        <v>101802</v>
+        <v>1676964</v>
       </c>
       <c r="Z230" t="n">
-        <v>-431764</v>
+        <v>1193067</v>
       </c>
       <c r="AA230" t="n">
-        <v>-881303</v>
+        <v>-1735495</v>
       </c>
       <c r="AB230" t="n">
-        <v>-648635</v>
+        <v>-2356413</v>
       </c>
       <c r="AC230" t="n">
         <v>-4</v>
@@ -31999,42 +31999,42 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>00923.TW</t>
+          <t>3673.TW</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>群益台ESG低碳50</t>
+          <t>TPK-KY</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>ETF</t>
+          <t>個股</t>
         </is>
       </c>
       <c r="D231" t="n">
-        <v>41.08</v>
+        <v>65.3</v>
       </c>
       <c r="E231" t="n">
-        <v>40.22</v>
+        <v>65.68000000000001</v>
       </c>
       <c r="F231" t="n">
-        <v>41</v>
+        <v>70.87</v>
       </c>
       <c r="G231" t="n">
-        <v>41.9</v>
+        <v>75.36</v>
       </c>
       <c r="H231" t="n">
-        <v>5247693</v>
+        <v>5526555</v>
       </c>
       <c r="I231" t="n">
-        <v>4901301</v>
+        <v>6146595</v>
       </c>
       <c r="J231" t="n">
-        <v>43.92</v>
+        <v>88.8</v>
       </c>
       <c r="K231" t="n">
-        <v>38.33</v>
+        <v>60</v>
       </c>
       <c r="L231" t="inlineStr">
         <is>
@@ -32042,52 +32042,52 @@
         </is>
       </c>
       <c r="M231" t="n">
-        <v>215974</v>
+        <v>-4511</v>
       </c>
       <c r="N231" t="n">
-        <v>97867</v>
+        <v>271807</v>
       </c>
       <c r="O231" t="n">
-        <v>-3680090</v>
+        <v>-36517</v>
       </c>
       <c r="P231" t="n">
-        <v>-4364833</v>
+        <v>-1107081</v>
       </c>
       <c r="Q231" t="n">
-        <v>-1460990</v>
+        <v>-7381</v>
       </c>
       <c r="R231" t="n">
-        <v>-1095200</v>
+        <v>441285</v>
       </c>
       <c r="S231" t="n">
-        <v>-1944595</v>
+        <v>397612</v>
       </c>
       <c r="T231" t="n">
-        <v>-2008420</v>
+        <v>-691145</v>
       </c>
       <c r="U231" t="n">
         <v>0</v>
       </c>
       <c r="V231" t="n">
-        <v>0</v>
+        <v>8000</v>
       </c>
       <c r="W231" t="n">
-        <v>0</v>
+        <v>125000</v>
       </c>
       <c r="X231" t="n">
-        <v>0</v>
+        <v>125000</v>
       </c>
       <c r="Y231" t="n">
-        <v>1676964</v>
+        <v>2870</v>
       </c>
       <c r="Z231" t="n">
-        <v>1193067</v>
+        <v>-177478</v>
       </c>
       <c r="AA231" t="n">
-        <v>-1735495</v>
+        <v>-559129</v>
       </c>
       <c r="AB231" t="n">
-        <v>-2356413</v>
+        <v>-540936</v>
       </c>
       <c r="AC231" t="n">
         <v>-4</v>
@@ -32096,10 +32096,10 @@
         <v>-4</v>
       </c>
       <c r="AE231" t="n">
-        <v>5</v>
+        <v>-45</v>
       </c>
       <c r="AF231" t="n">
-        <v>-15</v>
+        <v>35</v>
       </c>
       <c r="AG231" t="n">
         <v>0</v>
@@ -32119,29 +32119,29 @@
       </c>
       <c r="AM231" t="inlineStr">
         <is>
-          <t>站上5日線、空頭排列、量能溫和放大</t>
+          <t>跌破5日線、空頭排列、量能未放大</t>
         </is>
       </c>
       <c r="AN231" t="inlineStr">
         <is>
-          <t>短線籌碼止穩、5日法人明顯賣超</t>
+          <t>短線籌碼止穩、外資投信同步買超</t>
         </is>
       </c>
       <c r="AO231" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、空頭排列、量能溫和放大、短線籌碼止穩、5日法人明顯賣超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、空頭排列、量能未放大、短線籌碼止穩、外資投信同步買超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>3673.TW</t>
+          <t>3661.TW</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>TPK-KY</t>
+          <t>世芯-KY</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
@@ -32150,28 +32150,28 @@
         </is>
       </c>
       <c r="D232" t="n">
-        <v>65.3</v>
+        <v>3590</v>
       </c>
       <c r="E232" t="n">
-        <v>65.68000000000001</v>
+        <v>3539</v>
       </c>
       <c r="F232" t="n">
-        <v>70.87</v>
+        <v>3756.5</v>
       </c>
       <c r="G232" t="n">
-        <v>75.36</v>
+        <v>4020.25</v>
       </c>
       <c r="H232" t="n">
-        <v>5526555</v>
+        <v>1558375</v>
       </c>
       <c r="I232" t="n">
-        <v>6146595</v>
+        <v>1759675</v>
       </c>
       <c r="J232" t="n">
-        <v>88.8</v>
+        <v>4895</v>
       </c>
       <c r="K232" t="n">
-        <v>60</v>
+        <v>3245</v>
       </c>
       <c r="L232" t="inlineStr">
         <is>
@@ -32179,52 +32179,52 @@
         </is>
       </c>
       <c r="M232" t="n">
-        <v>-4511</v>
+        <v>24293</v>
       </c>
       <c r="N232" t="n">
-        <v>271807</v>
+        <v>136905</v>
       </c>
       <c r="O232" t="n">
-        <v>-36517</v>
+        <v>-162622</v>
       </c>
       <c r="P232" t="n">
-        <v>-1107081</v>
+        <v>-1348378</v>
       </c>
       <c r="Q232" t="n">
-        <v>-7381</v>
+        <v>28352</v>
       </c>
       <c r="R232" t="n">
-        <v>441285</v>
+        <v>107903</v>
       </c>
       <c r="S232" t="n">
-        <v>397612</v>
+        <v>-167318</v>
       </c>
       <c r="T232" t="n">
-        <v>-691145</v>
+        <v>-1052747</v>
       </c>
       <c r="U232" t="n">
-        <v>0</v>
+        <v>-58</v>
       </c>
       <c r="V232" t="n">
-        <v>8000</v>
+        <v>25556</v>
       </c>
       <c r="W232" t="n">
-        <v>125000</v>
+        <v>43693</v>
       </c>
       <c r="X232" t="n">
-        <v>125000</v>
+        <v>-159659</v>
       </c>
       <c r="Y232" t="n">
-        <v>2870</v>
+        <v>-4001</v>
       </c>
       <c r="Z232" t="n">
-        <v>-177478</v>
+        <v>3446</v>
       </c>
       <c r="AA232" t="n">
-        <v>-559129</v>
+        <v>-38997</v>
       </c>
       <c r="AB232" t="n">
-        <v>-540936</v>
+        <v>-135972</v>
       </c>
       <c r="AC232" t="n">
         <v>-4</v>
@@ -32233,10 +32233,10 @@
         <v>-4</v>
       </c>
       <c r="AE232" t="n">
-        <v>-45</v>
+        <v>-5</v>
       </c>
       <c r="AF232" t="n">
-        <v>35</v>
+        <v>-5</v>
       </c>
       <c r="AG232" t="n">
         <v>0</v>
@@ -32256,17 +32256,17 @@
       </c>
       <c r="AM232" t="inlineStr">
         <is>
-          <t>跌破5日線、空頭排列、量能未放大</t>
+          <t>站上5日線、空頭排列、量能未放大</t>
         </is>
       </c>
       <c r="AN232" t="inlineStr">
         <is>
-          <t>短線籌碼止穩、外資投信同步買超</t>
+          <t>短線籌碼止穩、5日法人賣超、投信買外資賣</t>
         </is>
       </c>
       <c r="AO232" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、空頭排列、量能未放大、短線籌碼止穩、外資投信同步買超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、空頭排列、量能未放大、短線籌碼止穩、5日法人賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
@@ -32547,12 +32547,12 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>3661.TW</t>
+          <t>1301.TW</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>世芯-KY</t>
+          <t>台塑</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
@@ -32561,28 +32561,28 @@
         </is>
       </c>
       <c r="D235" t="n">
-        <v>3590</v>
+        <v>63.5</v>
       </c>
       <c r="E235" t="n">
-        <v>3539</v>
+        <v>63.1</v>
       </c>
       <c r="F235" t="n">
-        <v>3756.5</v>
+        <v>61.78</v>
       </c>
       <c r="G235" t="n">
-        <v>4020.25</v>
+        <v>59.2</v>
       </c>
       <c r="H235" t="n">
-        <v>1558375</v>
+        <v>61438338</v>
       </c>
       <c r="I235" t="n">
-        <v>1759675</v>
+        <v>72907964</v>
       </c>
       <c r="J235" t="n">
-        <v>4895</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="K235" t="n">
-        <v>3245</v>
+        <v>48.15</v>
       </c>
       <c r="L235" t="inlineStr">
         <is>
@@ -32590,52 +32590,52 @@
         </is>
       </c>
       <c r="M235" t="n">
-        <v>24293</v>
+        <v>10038023</v>
       </c>
       <c r="N235" t="n">
-        <v>136905</v>
+        <v>-1917762</v>
       </c>
       <c r="O235" t="n">
-        <v>-162622</v>
+        <v>-5272270</v>
       </c>
       <c r="P235" t="n">
-        <v>-1348378</v>
+        <v>24491334</v>
       </c>
       <c r="Q235" t="n">
-        <v>28352</v>
+        <v>10118099</v>
       </c>
       <c r="R235" t="n">
-        <v>107903</v>
+        <v>-2673676</v>
       </c>
       <c r="S235" t="n">
-        <v>-167318</v>
+        <v>-5857406</v>
       </c>
       <c r="T235" t="n">
-        <v>-1052747</v>
+        <v>21546112</v>
       </c>
       <c r="U235" t="n">
-        <v>-58</v>
+        <v>330000</v>
       </c>
       <c r="V235" t="n">
-        <v>25556</v>
+        <v>673900</v>
       </c>
       <c r="W235" t="n">
-        <v>43693</v>
+        <v>659900</v>
       </c>
       <c r="X235" t="n">
-        <v>-159659</v>
+        <v>642900</v>
       </c>
       <c r="Y235" t="n">
-        <v>-4001</v>
+        <v>-410076</v>
       </c>
       <c r="Z235" t="n">
-        <v>3446</v>
+        <v>82014</v>
       </c>
       <c r="AA235" t="n">
-        <v>-38997</v>
+        <v>-74764</v>
       </c>
       <c r="AB235" t="n">
-        <v>-135972</v>
+        <v>2302322</v>
       </c>
       <c r="AC235" t="n">
         <v>-4</v>
@@ -32644,10 +32644,10 @@
         <v>-4</v>
       </c>
       <c r="AE235" t="n">
-        <v>-5</v>
+        <v>45</v>
       </c>
       <c r="AF235" t="n">
-        <v>-5</v>
+        <v>-55</v>
       </c>
       <c r="AG235" t="n">
         <v>0</v>
@@ -32667,29 +32667,29 @@
       </c>
       <c r="AM235" t="inlineStr">
         <is>
-          <t>站上5日線、空頭排列、量能未放大</t>
+          <t>站上5日線、多頭排列、量能未放大</t>
         </is>
       </c>
       <c r="AN235" t="inlineStr">
         <is>
-          <t>短線籌碼止穩、5日法人賣超、投信買外資賣</t>
+          <t>中期買超轉短線賣壓、5日法人明顯賣超、投信買外資賣</t>
         </is>
       </c>
       <c r="AO235" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、空頭排列、量能未放大、短線籌碼止穩、5日法人賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、多頭排列、量能未放大、中期買超轉短線賣壓、5日法人明顯賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>8039.TW</t>
+          <t>2369.TW</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>台虹</t>
+          <t>菱生</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
@@ -32698,28 +32698,28 @@
         </is>
       </c>
       <c r="D236" t="n">
-        <v>233</v>
+        <v>36.45</v>
       </c>
       <c r="E236" t="n">
-        <v>206</v>
+        <v>35.9</v>
       </c>
       <c r="F236" t="n">
-        <v>186</v>
+        <v>38.5</v>
       </c>
       <c r="G236" t="n">
-        <v>165.53</v>
+        <v>39.62</v>
       </c>
       <c r="H236" t="n">
-        <v>27683012</v>
+        <v>18804611</v>
       </c>
       <c r="I236" t="n">
-        <v>33357682</v>
+        <v>13827451</v>
       </c>
       <c r="J236" t="n">
-        <v>233</v>
+        <v>45.7</v>
       </c>
       <c r="K236" t="n">
-        <v>135.5</v>
+        <v>32.4</v>
       </c>
       <c r="L236" t="inlineStr">
         <is>
@@ -32727,52 +32727,52 @@
         </is>
       </c>
       <c r="M236" t="n">
-        <v>-1643294</v>
+        <v>1863313</v>
       </c>
       <c r="N236" t="n">
-        <v>-6628326</v>
+        <v>141985</v>
       </c>
       <c r="O236" t="n">
-        <v>-3619445</v>
+        <v>-6972509</v>
       </c>
       <c r="P236" t="n">
-        <v>12414833</v>
+        <v>-14135863</v>
       </c>
       <c r="Q236" t="n">
-        <v>-1629232</v>
+        <v>1761511</v>
       </c>
       <c r="R236" t="n">
-        <v>-7418726</v>
+        <v>573749</v>
       </c>
       <c r="S236" t="n">
-        <v>-7111485</v>
+        <v>-6091206</v>
       </c>
       <c r="T236" t="n">
-        <v>7400926</v>
+        <v>-13487228</v>
       </c>
       <c r="U236" t="n">
-        <v>7000</v>
+        <v>0</v>
       </c>
       <c r="V236" t="n">
-        <v>67000</v>
+        <v>0</v>
       </c>
       <c r="W236" t="n">
-        <v>2033000</v>
+        <v>0</v>
       </c>
       <c r="X236" t="n">
-        <v>3086000</v>
+        <v>0</v>
       </c>
       <c r="Y236" t="n">
-        <v>-21062</v>
+        <v>101802</v>
       </c>
       <c r="Z236" t="n">
-        <v>723400</v>
+        <v>-431764</v>
       </c>
       <c r="AA236" t="n">
-        <v>1459040</v>
+        <v>-881303</v>
       </c>
       <c r="AB236" t="n">
-        <v>1927907</v>
+        <v>-648635</v>
       </c>
       <c r="AC236" t="n">
         <v>-4</v>
@@ -32781,10 +32781,10 @@
         <v>-4</v>
       </c>
       <c r="AE236" t="n">
-        <v>70</v>
+        <v>5</v>
       </c>
       <c r="AF236" t="n">
-        <v>-80</v>
+        <v>-15</v>
       </c>
       <c r="AG236" t="n">
         <v>0</v>
@@ -32804,17 +32804,17 @@
       </c>
       <c r="AM236" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、量能未放大、突破20日高點</t>
+          <t>站上5日線、空頭排列、量能溫和放大</t>
         </is>
       </c>
       <c r="AN236" t="inlineStr">
         <is>
-          <t>法人連續偏賣、中期買超轉短線賣壓、5日法人明顯賣超、投信買外資賣</t>
+          <t>短線籌碼止穩、5日法人明顯賣超</t>
         </is>
       </c>
       <c r="AO236" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、多頭排列、量能未放大、突破20日高點、法人連續偏賣、中期買超轉短線賣壓、5日法人明顯賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、空頭排列、量能溫和放大、短線籌碼止穩、5日法人明顯賣超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
@@ -32958,12 +32958,12 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>2355.TW</t>
+          <t>8039.TW</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>敬鵬</t>
+          <t>台虹</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
@@ -32972,28 +32972,28 @@
         </is>
       </c>
       <c r="D238" t="n">
-        <v>43.25</v>
+        <v>233</v>
       </c>
       <c r="E238" t="n">
-        <v>43.67</v>
+        <v>206</v>
       </c>
       <c r="F238" t="n">
-        <v>46.42</v>
+        <v>186</v>
       </c>
       <c r="G238" t="n">
-        <v>49.8</v>
+        <v>165.53</v>
       </c>
       <c r="H238" t="n">
-        <v>3050389</v>
+        <v>27683012</v>
       </c>
       <c r="I238" t="n">
-        <v>4530787</v>
+        <v>33357682</v>
       </c>
       <c r="J238" t="n">
-        <v>57.4</v>
+        <v>233</v>
       </c>
       <c r="K238" t="n">
-        <v>40.25</v>
+        <v>135.5</v>
       </c>
       <c r="L238" t="inlineStr">
         <is>
@@ -33001,64 +33001,64 @@
         </is>
       </c>
       <c r="M238" t="n">
-        <v>-432343</v>
+        <v>-1643294</v>
       </c>
       <c r="N238" t="n">
-        <v>750313</v>
+        <v>-6628326</v>
       </c>
       <c r="O238" t="n">
-        <v>1072441</v>
+        <v>-3619445</v>
       </c>
       <c r="P238" t="n">
-        <v>3324494</v>
+        <v>12414833</v>
       </c>
       <c r="Q238" t="n">
-        <v>-341870</v>
+        <v>-1629232</v>
       </c>
       <c r="R238" t="n">
-        <v>1101629</v>
+        <v>-7418726</v>
       </c>
       <c r="S238" t="n">
-        <v>1978834</v>
+        <v>-7111485</v>
       </c>
       <c r="T238" t="n">
-        <v>4610717</v>
+        <v>7400926</v>
       </c>
       <c r="U238" t="n">
-        <v>-116000</v>
+        <v>7000</v>
       </c>
       <c r="V238" t="n">
-        <v>-275000</v>
+        <v>67000</v>
       </c>
       <c r="W238" t="n">
-        <v>-479000</v>
+        <v>2033000</v>
       </c>
       <c r="X238" t="n">
-        <v>-483000</v>
+        <v>3086000</v>
       </c>
       <c r="Y238" t="n">
-        <v>25527</v>
+        <v>-21062</v>
       </c>
       <c r="Z238" t="n">
-        <v>-76316</v>
+        <v>723400</v>
       </c>
       <c r="AA238" t="n">
-        <v>-427393</v>
+        <v>1459040</v>
       </c>
       <c r="AB238" t="n">
-        <v>-803223</v>
+        <v>1927907</v>
       </c>
       <c r="AC238" t="n">
-        <v>-6</v>
+        <v>-4</v>
       </c>
       <c r="AD238" t="n">
-        <v>-6</v>
+        <v>-4</v>
       </c>
       <c r="AE238" t="n">
-        <v>-45</v>
+        <v>70</v>
       </c>
       <c r="AF238" t="n">
-        <v>30</v>
+        <v>-80</v>
       </c>
       <c r="AG238" t="n">
         <v>0</v>
@@ -33078,29 +33078,29 @@
       </c>
       <c r="AM238" t="inlineStr">
         <is>
-          <t>跌破5日線、空頭排列、量能未放大</t>
+          <t>站上5日線、多頭排列、量能未放大、突破20日高點</t>
         </is>
       </c>
       <c r="AN238" t="inlineStr">
         <is>
-          <t>5日法人明顯買超、外資買投信賣</t>
+          <t>法人連續偏賣、中期買超轉短線賣壓、5日法人明顯賣超、投信買外資賣</t>
         </is>
       </c>
       <c r="AO238" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、空頭排列、量能未放大、5日法人明顯買超、外資買投信賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、多頭排列、量能未放大、突破20日高點、法人連續偏賣、中期買超轉短線賣壓、5日法人明顯賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>6116.TW</t>
+          <t>2355.TW</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>彩晶</t>
+          <t>敬鵬</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
@@ -33109,28 +33109,28 @@
         </is>
       </c>
       <c r="D239" t="n">
-        <v>14.65</v>
+        <v>43.25</v>
       </c>
       <c r="E239" t="n">
-        <v>14.91</v>
+        <v>43.67</v>
       </c>
       <c r="F239" t="n">
-        <v>15.8</v>
+        <v>46.42</v>
       </c>
       <c r="G239" t="n">
-        <v>17.22</v>
+        <v>49.8</v>
       </c>
       <c r="H239" t="n">
-        <v>23243708</v>
+        <v>3050389</v>
       </c>
       <c r="I239" t="n">
-        <v>28609418</v>
+        <v>4530787</v>
       </c>
       <c r="J239" t="n">
-        <v>20.9</v>
+        <v>57.4</v>
       </c>
       <c r="K239" t="n">
-        <v>13.85</v>
+        <v>40.25</v>
       </c>
       <c r="L239" t="inlineStr">
         <is>
@@ -33138,52 +33138,52 @@
         </is>
       </c>
       <c r="M239" t="n">
-        <v>-2759187</v>
+        <v>-432343</v>
       </c>
       <c r="N239" t="n">
-        <v>2447055</v>
+        <v>750313</v>
       </c>
       <c r="O239" t="n">
-        <v>5419137</v>
+        <v>1072441</v>
       </c>
       <c r="P239" t="n">
-        <v>10632908</v>
+        <v>3324494</v>
       </c>
       <c r="Q239" t="n">
-        <v>-2583427</v>
+        <v>-341870</v>
       </c>
       <c r="R239" t="n">
-        <v>2801619</v>
+        <v>1101629</v>
       </c>
       <c r="S239" t="n">
-        <v>5820549</v>
+        <v>1978834</v>
       </c>
       <c r="T239" t="n">
-        <v>13936198</v>
+        <v>4610717</v>
       </c>
       <c r="U239" t="n">
-        <v>0</v>
+        <v>-116000</v>
       </c>
       <c r="V239" t="n">
-        <v>0</v>
+        <v>-275000</v>
       </c>
       <c r="W239" t="n">
-        <v>0</v>
+        <v>-479000</v>
       </c>
       <c r="X239" t="n">
-        <v>0</v>
+        <v>-483000</v>
       </c>
       <c r="Y239" t="n">
-        <v>-175760</v>
+        <v>25527</v>
       </c>
       <c r="Z239" t="n">
-        <v>-354564</v>
+        <v>-76316</v>
       </c>
       <c r="AA239" t="n">
-        <v>-401412</v>
+        <v>-427393</v>
       </c>
       <c r="AB239" t="n">
-        <v>-3303290</v>
+        <v>-803223</v>
       </c>
       <c r="AC239" t="n">
         <v>-6</v>
@@ -33220,12 +33220,12 @@
       </c>
       <c r="AN239" t="inlineStr">
         <is>
-          <t>5日法人明顯買超</t>
+          <t>5日法人明顯買超、外資買投信賣</t>
         </is>
       </c>
       <c r="AO239" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、空頭排列、量能未放大、5日法人明顯買超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、空頭排列、量能未放大、5日法人明顯買超、外資買投信賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
@@ -33643,12 +33643,12 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>2345.TW</t>
+          <t>6116.TW</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>智邦</t>
+          <t>彩晶</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
@@ -33657,28 +33657,28 @@
         </is>
       </c>
       <c r="D243" t="n">
-        <v>2285</v>
+        <v>14.65</v>
       </c>
       <c r="E243" t="n">
-        <v>2201</v>
+        <v>14.91</v>
       </c>
       <c r="F243" t="n">
-        <v>2291.5</v>
+        <v>15.8</v>
       </c>
       <c r="G243" t="n">
-        <v>2406.5</v>
+        <v>17.22</v>
       </c>
       <c r="H243" t="n">
-        <v>3027115</v>
+        <v>23243708</v>
       </c>
       <c r="I243" t="n">
-        <v>2788692</v>
+        <v>28609418</v>
       </c>
       <c r="J243" t="n">
-        <v>2825</v>
+        <v>20.9</v>
       </c>
       <c r="K243" t="n">
-        <v>2000</v>
+        <v>13.85</v>
       </c>
       <c r="L243" t="inlineStr">
         <is>
@@ -33686,52 +33686,52 @@
         </is>
       </c>
       <c r="M243" t="n">
-        <v>7136</v>
+        <v>-2759187</v>
       </c>
       <c r="N243" t="n">
-        <v>-83167</v>
+        <v>2447055</v>
       </c>
       <c r="O243" t="n">
-        <v>-346671</v>
+        <v>5419137</v>
       </c>
       <c r="P243" t="n">
-        <v>-1328732</v>
+        <v>10632908</v>
       </c>
       <c r="Q243" t="n">
-        <v>-194448</v>
+        <v>-2583427</v>
       </c>
       <c r="R243" t="n">
-        <v>-993354</v>
+        <v>2801619</v>
       </c>
       <c r="S243" t="n">
-        <v>-1549622</v>
+        <v>5820549</v>
       </c>
       <c r="T243" t="n">
-        <v>-2428940</v>
+        <v>13936198</v>
       </c>
       <c r="U243" t="n">
-        <v>232637</v>
+        <v>0</v>
       </c>
       <c r="V243" t="n">
-        <v>844128</v>
+        <v>0</v>
       </c>
       <c r="W243" t="n">
-        <v>1051449</v>
+        <v>0</v>
       </c>
       <c r="X243" t="n">
-        <v>1269574</v>
+        <v>0</v>
       </c>
       <c r="Y243" t="n">
-        <v>-31053</v>
+        <v>-175760</v>
       </c>
       <c r="Z243" t="n">
-        <v>66059</v>
+        <v>-354564</v>
       </c>
       <c r="AA243" t="n">
-        <v>151502</v>
+        <v>-401412</v>
       </c>
       <c r="AB243" t="n">
-        <v>-169366</v>
+        <v>-3303290</v>
       </c>
       <c r="AC243" t="n">
         <v>-6</v>
@@ -33740,10 +33740,10 @@
         <v>-6</v>
       </c>
       <c r="AE243" t="n">
-        <v>5</v>
+        <v>-45</v>
       </c>
       <c r="AF243" t="n">
-        <v>-20</v>
+        <v>30</v>
       </c>
       <c r="AG243" t="n">
         <v>0</v>
@@ -33763,17 +33763,17 @@
       </c>
       <c r="AM243" t="inlineStr">
         <is>
-          <t>站上5日線、空頭排列、量能溫和放大</t>
+          <t>跌破5日線、空頭排列、量能未放大</t>
         </is>
       </c>
       <c r="AN243" t="inlineStr">
         <is>
-          <t>5日法人賣超、投信買外資賣</t>
+          <t>5日法人明顯買超</t>
         </is>
       </c>
       <c r="AO243" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、空頭排列、量能溫和放大、5日法人賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、空頭排列、量能未放大、5日法人明顯買超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
@@ -34054,12 +34054,12 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>3552.TWO</t>
+          <t>2345.TW</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>同致</t>
+          <t>智邦</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
@@ -34068,28 +34068,28 @@
         </is>
       </c>
       <c r="D246" t="n">
-        <v>46.15</v>
+        <v>2285</v>
       </c>
       <c r="E246" t="n">
-        <v>45.47</v>
+        <v>2201</v>
       </c>
       <c r="F246" t="n">
-        <v>46.13</v>
+        <v>2291.5</v>
       </c>
       <c r="G246" t="n">
-        <v>47.27</v>
+        <v>2406.5</v>
       </c>
       <c r="H246" t="n">
-        <v>80000</v>
+        <v>3027115</v>
       </c>
       <c r="I246" t="n">
-        <v>115400</v>
+        <v>2788692</v>
       </c>
       <c r="J246" t="n">
-        <v>51.7</v>
+        <v>2825</v>
       </c>
       <c r="K246" t="n">
-        <v>44</v>
+        <v>2000</v>
       </c>
       <c r="L246" t="inlineStr">
         <is>
@@ -34097,52 +34097,52 @@
         </is>
       </c>
       <c r="M246" t="n">
-        <v>0</v>
+        <v>7136</v>
       </c>
       <c r="N246" t="n">
-        <v>0</v>
+        <v>-83167</v>
       </c>
       <c r="O246" t="n">
-        <v>0</v>
+        <v>-346671</v>
       </c>
       <c r="P246" t="n">
-        <v>0</v>
+        <v>-1328732</v>
       </c>
       <c r="Q246" t="n">
-        <v>0</v>
+        <v>-194448</v>
       </c>
       <c r="R246" t="n">
-        <v>0</v>
+        <v>-993354</v>
       </c>
       <c r="S246" t="n">
-        <v>0</v>
+        <v>-1549622</v>
       </c>
       <c r="T246" t="n">
-        <v>0</v>
+        <v>-2428940</v>
       </c>
       <c r="U246" t="n">
-        <v>0</v>
+        <v>232637</v>
       </c>
       <c r="V246" t="n">
-        <v>0</v>
+        <v>844128</v>
       </c>
       <c r="W246" t="n">
-        <v>0</v>
+        <v>1051449</v>
       </c>
       <c r="X246" t="n">
-        <v>0</v>
+        <v>1269574</v>
       </c>
       <c r="Y246" t="n">
-        <v>0</v>
+        <v>-31053</v>
       </c>
       <c r="Z246" t="n">
-        <v>0</v>
+        <v>66059</v>
       </c>
       <c r="AA246" t="n">
-        <v>0</v>
+        <v>151502</v>
       </c>
       <c r="AB246" t="n">
-        <v>0</v>
+        <v>-169366</v>
       </c>
       <c r="AC246" t="n">
         <v>-6</v>
@@ -34151,10 +34151,10 @@
         <v>-6</v>
       </c>
       <c r="AE246" t="n">
-        <v>-15</v>
+        <v>5</v>
       </c>
       <c r="AF246" t="n">
-        <v>0</v>
+        <v>-20</v>
       </c>
       <c r="AG246" t="n">
         <v>0</v>
@@ -34174,17 +34174,17 @@
       </c>
       <c r="AM246" t="inlineStr">
         <is>
-          <t>站上5日線、空頭排列、量能未放大、接近20日低點</t>
+          <t>站上5日線、空頭排列、量能溫和放大</t>
         </is>
       </c>
       <c r="AN246" t="inlineStr">
         <is>
-          <t>籌碼中性</t>
+          <t>5日法人賣超、投信買外資賣</t>
         </is>
       </c>
       <c r="AO246" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、空頭排列、量能未放大、接近20日低點、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、空頭排列、量能溫和放大、5日法人賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
@@ -34465,12 +34465,12 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>3711.TW</t>
+          <t>3552.TWO</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>同致</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
@@ -34479,28 +34479,28 @@
         </is>
       </c>
       <c r="D249" t="n">
-        <v>656</v>
+        <v>46.15</v>
       </c>
       <c r="E249" t="n">
-        <v>636.4</v>
+        <v>45.47</v>
       </c>
       <c r="F249" t="n">
-        <v>647.8</v>
+        <v>46.13</v>
       </c>
       <c r="G249" t="n">
-        <v>657.65</v>
+        <v>47.27</v>
       </c>
       <c r="H249" t="n">
-        <v>22726328</v>
+        <v>80000</v>
       </c>
       <c r="I249" t="n">
-        <v>23727962</v>
+        <v>115400</v>
       </c>
       <c r="J249" t="n">
-        <v>729</v>
+        <v>51.7</v>
       </c>
       <c r="K249" t="n">
-        <v>577</v>
+        <v>44</v>
       </c>
       <c r="L249" t="inlineStr">
         <is>
@@ -34508,64 +34508,64 @@
         </is>
       </c>
       <c r="M249" t="n">
-        <v>2134871</v>
+        <v>0</v>
       </c>
       <c r="N249" t="n">
-        <v>2221698</v>
+        <v>0</v>
       </c>
       <c r="O249" t="n">
-        <v>-9489719</v>
+        <v>0</v>
       </c>
       <c r="P249" t="n">
-        <v>-8790069</v>
+        <v>0</v>
       </c>
       <c r="Q249" t="n">
-        <v>1119419</v>
+        <v>0</v>
       </c>
       <c r="R249" t="n">
-        <v>-3815793</v>
+        <v>0</v>
       </c>
       <c r="S249" t="n">
-        <v>-16574880</v>
+        <v>0</v>
       </c>
       <c r="T249" t="n">
-        <v>-23914767</v>
+        <v>0</v>
       </c>
       <c r="U249" t="n">
-        <v>1475018</v>
+        <v>0</v>
       </c>
       <c r="V249" t="n">
-        <v>4432509</v>
+        <v>0</v>
       </c>
       <c r="W249" t="n">
-        <v>5648989</v>
+        <v>0</v>
       </c>
       <c r="X249" t="n">
-        <v>12571578</v>
+        <v>0</v>
       </c>
       <c r="Y249" t="n">
-        <v>-459566</v>
+        <v>0</v>
       </c>
       <c r="Z249" t="n">
-        <v>1604982</v>
+        <v>0</v>
       </c>
       <c r="AA249" t="n">
-        <v>1436172</v>
+        <v>0</v>
       </c>
       <c r="AB249" t="n">
-        <v>2553120</v>
+        <v>0</v>
       </c>
       <c r="AC249" t="n">
-        <v>-8</v>
+        <v>-6</v>
       </c>
       <c r="AD249" t="n">
-        <v>-8</v>
+        <v>-6</v>
       </c>
       <c r="AE249" t="n">
-        <v>-5</v>
+        <v>-15</v>
       </c>
       <c r="AF249" t="n">
-        <v>-15</v>
+        <v>0</v>
       </c>
       <c r="AG249" t="n">
         <v>0</v>
@@ -34585,17 +34585,17 @@
       </c>
       <c r="AM249" t="inlineStr">
         <is>
-          <t>站上5日線、空頭排列、量能未放大</t>
+          <t>站上5日線、空頭排列、量能未放大、接近20日低點</t>
         </is>
       </c>
       <c r="AN249" t="inlineStr">
         <is>
-          <t>短線籌碼止穩、5日法人明顯賣超、投信買外資賣</t>
+          <t>籌碼中性</t>
         </is>
       </c>
       <c r="AO249" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、空頭排列、量能未放大、短線籌碼止穩、5日法人明顯賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、空頭排列、量能未放大、接近20日低點、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
@@ -34739,42 +34739,42 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>00692.TW</t>
+          <t>3711.TW</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>富邦公司治理</t>
+          <t>日月光投控</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>ETF</t>
+          <t>個股</t>
         </is>
       </c>
       <c r="D251" t="n">
-        <v>89.05</v>
+        <v>656</v>
       </c>
       <c r="E251" t="n">
-        <v>87.44</v>
+        <v>636.4</v>
       </c>
       <c r="F251" t="n">
-        <v>89.55</v>
+        <v>647.8</v>
       </c>
       <c r="G251" t="n">
-        <v>90.98</v>
+        <v>657.65</v>
       </c>
       <c r="H251" t="n">
-        <v>821748</v>
+        <v>22726328</v>
       </c>
       <c r="I251" t="n">
-        <v>2014838</v>
+        <v>23727962</v>
       </c>
       <c r="J251" t="n">
-        <v>94.55</v>
+        <v>729</v>
       </c>
       <c r="K251" t="n">
-        <v>84</v>
+        <v>577</v>
       </c>
       <c r="L251" t="inlineStr">
         <is>
@@ -34782,52 +34782,52 @@
         </is>
       </c>
       <c r="M251" t="n">
-        <v>241412</v>
+        <v>2134871</v>
       </c>
       <c r="N251" t="n">
-        <v>1089074</v>
+        <v>2221698</v>
       </c>
       <c r="O251" t="n">
-        <v>-938495</v>
+        <v>-9489719</v>
       </c>
       <c r="P251" t="n">
-        <v>-941789</v>
+        <v>-8790069</v>
       </c>
       <c r="Q251" t="n">
-        <v>51000</v>
+        <v>1119419</v>
       </c>
       <c r="R251" t="n">
-        <v>349769</v>
+        <v>-3815793</v>
       </c>
       <c r="S251" t="n">
-        <v>360868</v>
+        <v>-16574880</v>
       </c>
       <c r="T251" t="n">
-        <v>172761</v>
+        <v>-23914767</v>
       </c>
       <c r="U251" t="n">
-        <v>0</v>
+        <v>1475018</v>
       </c>
       <c r="V251" t="n">
-        <v>0</v>
+        <v>4432509</v>
       </c>
       <c r="W251" t="n">
-        <v>0</v>
+        <v>5648989</v>
       </c>
       <c r="X251" t="n">
-        <v>0</v>
+        <v>12571578</v>
       </c>
       <c r="Y251" t="n">
-        <v>190412</v>
+        <v>-459566</v>
       </c>
       <c r="Z251" t="n">
-        <v>739305</v>
+        <v>1604982</v>
       </c>
       <c r="AA251" t="n">
-        <v>-1299363</v>
+        <v>1436172</v>
       </c>
       <c r="AB251" t="n">
-        <v>-1114550</v>
+        <v>2553120</v>
       </c>
       <c r="AC251" t="n">
         <v>-8</v>
@@ -34864,12 +34864,12 @@
       </c>
       <c r="AN251" t="inlineStr">
         <is>
-          <t>短線籌碼止穩、5日法人明顯賣超</t>
+          <t>短線籌碼止穩、5日法人明顯賣超、投信買外資賣</t>
         </is>
       </c>
       <c r="AO251" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、空頭排列、量能未放大、短線籌碼止穩、5日法人明顯賣超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、空頭排列、量能未放大、短線籌碼止穩、5日法人明顯賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
@@ -35150,42 +35150,42 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>5530.TWO</t>
+          <t>00927.TW</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>龍巖</t>
+          <t>群益半導體收益</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>個股</t>
+          <t>ETF</t>
         </is>
       </c>
       <c r="D254" t="n">
-        <v>48.4</v>
+        <v>37.2</v>
       </c>
       <c r="E254" t="n">
-        <v>48.5</v>
+        <v>36.44</v>
       </c>
       <c r="F254" t="n">
-        <v>48.59</v>
+        <v>38.73</v>
       </c>
       <c r="G254" t="n">
-        <v>48.23</v>
+        <v>40.25</v>
       </c>
       <c r="H254" t="n">
-        <v>273000</v>
+        <v>18905022</v>
       </c>
       <c r="I254" t="n">
-        <v>367800</v>
+        <v>37126664</v>
       </c>
       <c r="J254" t="n">
-        <v>50.4</v>
+        <v>43.55</v>
       </c>
       <c r="K254" t="n">
-        <v>45.95</v>
+        <v>34.02</v>
       </c>
       <c r="L254" t="inlineStr">
         <is>
@@ -35193,28 +35193,28 @@
         </is>
       </c>
       <c r="M254" t="n">
-        <v>0</v>
+        <v>2324388</v>
       </c>
       <c r="N254" t="n">
-        <v>0</v>
+        <v>9113820</v>
       </c>
       <c r="O254" t="n">
-        <v>0</v>
+        <v>-26485554</v>
       </c>
       <c r="P254" t="n">
-        <v>0</v>
+        <v>-207530190</v>
       </c>
       <c r="Q254" t="n">
-        <v>0</v>
+        <v>2094013</v>
       </c>
       <c r="R254" t="n">
-        <v>0</v>
+        <v>9574378</v>
       </c>
       <c r="S254" t="n">
-        <v>0</v>
+        <v>3582981</v>
       </c>
       <c r="T254" t="n">
-        <v>0</v>
+        <v>2689748</v>
       </c>
       <c r="U254" t="n">
         <v>0</v>
@@ -35226,19 +35226,19 @@
         <v>0</v>
       </c>
       <c r="X254" t="n">
-        <v>0</v>
+        <v>230000</v>
       </c>
       <c r="Y254" t="n">
-        <v>0</v>
+        <v>230375</v>
       </c>
       <c r="Z254" t="n">
-        <v>0</v>
+        <v>-460558</v>
       </c>
       <c r="AA254" t="n">
-        <v>0</v>
+        <v>-30068535</v>
       </c>
       <c r="AB254" t="n">
-        <v>0</v>
+        <v>-210449938</v>
       </c>
       <c r="AC254" t="n">
         <v>-8</v>
@@ -35247,10 +35247,10 @@
         <v>-8</v>
       </c>
       <c r="AE254" t="n">
-        <v>-20</v>
+        <v>-5</v>
       </c>
       <c r="AF254" t="n">
-        <v>0</v>
+        <v>-15</v>
       </c>
       <c r="AG254" t="n">
         <v>0</v>
@@ -35270,17 +35270,17 @@
       </c>
       <c r="AM254" t="inlineStr">
         <is>
-          <t>跌破5日線、量能未放大</t>
+          <t>站上5日線、空頭排列、量能未放大</t>
         </is>
       </c>
       <c r="AN254" t="inlineStr">
         <is>
-          <t>籌碼中性</t>
+          <t>短線籌碼止穩、5日法人明顯賣超</t>
         </is>
       </c>
       <c r="AO254" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、量能未放大、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、空頭排列、量能未放大、短線籌碼止穩、5日法人明顯賣超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
@@ -35698,12 +35698,12 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>00927.TW</t>
+          <t>00692.TW</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>群益半導體收益</t>
+          <t>富邦公司治理</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
@@ -35712,28 +35712,28 @@
         </is>
       </c>
       <c r="D258" t="n">
-        <v>37.2</v>
+        <v>89.05</v>
       </c>
       <c r="E258" t="n">
-        <v>36.44</v>
+        <v>87.44</v>
       </c>
       <c r="F258" t="n">
-        <v>38.73</v>
+        <v>89.55</v>
       </c>
       <c r="G258" t="n">
-        <v>40.25</v>
+        <v>90.98</v>
       </c>
       <c r="H258" t="n">
-        <v>18905022</v>
+        <v>821748</v>
       </c>
       <c r="I258" t="n">
-        <v>37126664</v>
+        <v>2014838</v>
       </c>
       <c r="J258" t="n">
-        <v>43.55</v>
+        <v>94.55</v>
       </c>
       <c r="K258" t="n">
-        <v>34.02</v>
+        <v>84</v>
       </c>
       <c r="L258" t="inlineStr">
         <is>
@@ -35741,28 +35741,28 @@
         </is>
       </c>
       <c r="M258" t="n">
-        <v>2324388</v>
+        <v>241412</v>
       </c>
       <c r="N258" t="n">
-        <v>9113820</v>
+        <v>1089074</v>
       </c>
       <c r="O258" t="n">
-        <v>-26485554</v>
+        <v>-938495</v>
       </c>
       <c r="P258" t="n">
-        <v>-207530190</v>
+        <v>-941789</v>
       </c>
       <c r="Q258" t="n">
-        <v>2094013</v>
+        <v>51000</v>
       </c>
       <c r="R258" t="n">
-        <v>9574378</v>
+        <v>349769</v>
       </c>
       <c r="S258" t="n">
-        <v>3582981</v>
+        <v>360868</v>
       </c>
       <c r="T258" t="n">
-        <v>2689748</v>
+        <v>172761</v>
       </c>
       <c r="U258" t="n">
         <v>0</v>
@@ -35774,19 +35774,19 @@
         <v>0</v>
       </c>
       <c r="X258" t="n">
-        <v>230000</v>
+        <v>0</v>
       </c>
       <c r="Y258" t="n">
-        <v>230375</v>
+        <v>190412</v>
       </c>
       <c r="Z258" t="n">
-        <v>-460558</v>
+        <v>739305</v>
       </c>
       <c r="AA258" t="n">
-        <v>-30068535</v>
+        <v>-1299363</v>
       </c>
       <c r="AB258" t="n">
-        <v>-210449938</v>
+        <v>-1114550</v>
       </c>
       <c r="AC258" t="n">
         <v>-8</v>

--- a/output/universe_analysis_result.xlsx
+++ b/output/universe_analysis_result.xlsx
@@ -31040,12 +31040,12 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>2401.TW</t>
+          <t>2395.TW</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>凌陽</t>
+          <t>研華</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
@@ -31054,28 +31054,28 @@
         </is>
       </c>
       <c r="D224" t="n">
-        <v>28.2</v>
+        <v>600</v>
       </c>
       <c r="E224" t="n">
-        <v>27.9</v>
+        <v>558.4</v>
       </c>
       <c r="F224" t="n">
-        <v>29.68</v>
+        <v>546</v>
       </c>
       <c r="G224" t="n">
-        <v>31.07</v>
+        <v>522.58</v>
       </c>
       <c r="H224" t="n">
-        <v>6729552</v>
+        <v>3860896</v>
       </c>
       <c r="I224" t="n">
-        <v>6216693</v>
+        <v>4829073</v>
       </c>
       <c r="J224" t="n">
-        <v>35.65</v>
+        <v>618</v>
       </c>
       <c r="K224" t="n">
-        <v>25.3</v>
+        <v>453</v>
       </c>
       <c r="L224" t="inlineStr">
         <is>
@@ -31083,52 +31083,52 @@
         </is>
       </c>
       <c r="M224" t="n">
-        <v>-2940120</v>
+        <v>-542853</v>
       </c>
       <c r="N224" t="n">
-        <v>419415</v>
+        <v>-1782926</v>
       </c>
       <c r="O224" t="n">
-        <v>-1169001</v>
+        <v>-1741207</v>
       </c>
       <c r="P224" t="n">
-        <v>-2279981</v>
+        <v>-691224</v>
       </c>
       <c r="Q224" t="n">
-        <v>-2727747</v>
+        <v>-956752</v>
       </c>
       <c r="R224" t="n">
-        <v>412534</v>
+        <v>-3143446</v>
       </c>
       <c r="S224" t="n">
-        <v>-697126</v>
+        <v>-4066985</v>
       </c>
       <c r="T224" t="n">
-        <v>-1096206</v>
+        <v>-3546309</v>
       </c>
       <c r="U224" t="n">
-        <v>0</v>
+        <v>365915</v>
       </c>
       <c r="V224" t="n">
-        <v>0</v>
+        <v>1081577</v>
       </c>
       <c r="W224" t="n">
-        <v>15000</v>
+        <v>1971832</v>
       </c>
       <c r="X224" t="n">
-        <v>20000</v>
+        <v>2344288</v>
       </c>
       <c r="Y224" t="n">
-        <v>-212373</v>
+        <v>47984</v>
       </c>
       <c r="Z224" t="n">
-        <v>6881</v>
+        <v>278943</v>
       </c>
       <c r="AA224" t="n">
-        <v>-486875</v>
+        <v>353946</v>
       </c>
       <c r="AB224" t="n">
-        <v>-1203775</v>
+        <v>510797</v>
       </c>
       <c r="AC224" t="n">
         <v>-4</v>
@@ -31137,10 +31137,10 @@
         <v>-4</v>
       </c>
       <c r="AE224" t="n">
-        <v>5</v>
+        <v>45</v>
       </c>
       <c r="AF224" t="n">
-        <v>-15</v>
+        <v>-55</v>
       </c>
       <c r="AG224" t="n">
         <v>0</v>
@@ -31160,17 +31160,17 @@
       </c>
       <c r="AM224" t="inlineStr">
         <is>
-          <t>站上5日線、空頭排列、量能溫和放大</t>
+          <t>站上5日線、多頭排列、量能未放大</t>
         </is>
       </c>
       <c r="AN224" t="inlineStr">
         <is>
-          <t>短線籌碼止穩、5日法人明顯賣超、投信買外資賣</t>
+          <t>法人連續偏賣、5日法人明顯賣超、投信買外資賣</t>
         </is>
       </c>
       <c r="AO224" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、空頭排列、量能溫和放大、短線籌碼止穩、5日法人明顯賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、多頭排列、量能未放大、法人連續偏賣、5日法人明顯賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
@@ -31314,12 +31314,12 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>6182.TWO</t>
+          <t>2401.TW</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>合晶</t>
+          <t>凌陽</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
@@ -31328,28 +31328,28 @@
         </is>
       </c>
       <c r="D226" t="n">
-        <v>126.5</v>
+        <v>28.2</v>
       </c>
       <c r="E226" t="n">
-        <v>134</v>
+        <v>27.9</v>
       </c>
       <c r="F226" t="n">
-        <v>156.4</v>
+        <v>29.68</v>
       </c>
       <c r="G226" t="n">
-        <v>147.57</v>
+        <v>31.07</v>
       </c>
       <c r="H226" t="n">
-        <v>127168000</v>
+        <v>6729552</v>
       </c>
       <c r="I226" t="n">
-        <v>109015400</v>
+        <v>6216693</v>
       </c>
       <c r="J226" t="n">
-        <v>194.5</v>
+        <v>35.65</v>
       </c>
       <c r="K226" t="n">
-        <v>109.5</v>
+        <v>25.3</v>
       </c>
       <c r="L226" t="inlineStr">
         <is>
@@ -31357,28 +31357,28 @@
         </is>
       </c>
       <c r="M226" t="n">
-        <v>0</v>
+        <v>-2940120</v>
       </c>
       <c r="N226" t="n">
-        <v>0</v>
+        <v>419415</v>
       </c>
       <c r="O226" t="n">
-        <v>0</v>
+        <v>-1169001</v>
       </c>
       <c r="P226" t="n">
-        <v>0</v>
+        <v>-2279981</v>
       </c>
       <c r="Q226" t="n">
-        <v>0</v>
+        <v>-2727747</v>
       </c>
       <c r="R226" t="n">
-        <v>0</v>
+        <v>412534</v>
       </c>
       <c r="S226" t="n">
-        <v>0</v>
+        <v>-697126</v>
       </c>
       <c r="T226" t="n">
-        <v>0</v>
+        <v>-1096206</v>
       </c>
       <c r="U226" t="n">
         <v>0</v>
@@ -31387,22 +31387,22 @@
         <v>0</v>
       </c>
       <c r="W226" t="n">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="X226" t="n">
-        <v>0</v>
+        <v>20000</v>
       </c>
       <c r="Y226" t="n">
-        <v>0</v>
+        <v>-212373</v>
       </c>
       <c r="Z226" t="n">
-        <v>0</v>
+        <v>6881</v>
       </c>
       <c r="AA226" t="n">
-        <v>0</v>
+        <v>-486875</v>
       </c>
       <c r="AB226" t="n">
-        <v>0</v>
+        <v>-1203775</v>
       </c>
       <c r="AC226" t="n">
         <v>-4</v>
@@ -31411,10 +31411,10 @@
         <v>-4</v>
       </c>
       <c r="AE226" t="n">
-        <v>-10</v>
+        <v>5</v>
       </c>
       <c r="AF226" t="n">
-        <v>0</v>
+        <v>-15</v>
       </c>
       <c r="AG226" t="n">
         <v>0</v>
@@ -31434,17 +31434,17 @@
       </c>
       <c r="AM226" t="inlineStr">
         <is>
-          <t>跌破5日線、量能溫和放大</t>
+          <t>站上5日線、空頭排列、量能溫和放大</t>
         </is>
       </c>
       <c r="AN226" t="inlineStr">
         <is>
-          <t>籌碼中性</t>
+          <t>短線籌碼止穩、5日法人明顯賣超、投信買外資賣</t>
         </is>
       </c>
       <c r="AO226" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、量能溫和放大、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、空頭排列、量能溫和放大、短線籌碼止穩、5日法人明顯賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
@@ -31862,12 +31862,12 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>2908.TW</t>
+          <t>6182.TWO</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>特力</t>
+          <t>合晶</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
@@ -31876,28 +31876,28 @@
         </is>
       </c>
       <c r="D230" t="n">
-        <v>21.55</v>
+        <v>126.5</v>
       </c>
       <c r="E230" t="n">
-        <v>21.78</v>
+        <v>134</v>
       </c>
       <c r="F230" t="n">
-        <v>21.81</v>
+        <v>156.4</v>
       </c>
       <c r="G230" t="n">
-        <v>21.59</v>
+        <v>147.57</v>
       </c>
       <c r="H230" t="n">
-        <v>121724</v>
+        <v>127168000</v>
       </c>
       <c r="I230" t="n">
-        <v>189905</v>
+        <v>109015400</v>
       </c>
       <c r="J230" t="n">
-        <v>22.15</v>
+        <v>194.5</v>
       </c>
       <c r="K230" t="n">
-        <v>20.95</v>
+        <v>109.5</v>
       </c>
       <c r="L230" t="inlineStr">
         <is>
@@ -31905,28 +31905,28 @@
         </is>
       </c>
       <c r="M230" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="N230" t="n">
-        <v>-88000</v>
+        <v>0</v>
       </c>
       <c r="O230" t="n">
-        <v>135156</v>
+        <v>0</v>
       </c>
       <c r="P230" t="n">
-        <v>530162</v>
+        <v>0</v>
       </c>
       <c r="Q230" t="n">
-        <v>-3000</v>
+        <v>0</v>
       </c>
       <c r="R230" t="n">
-        <v>-131000</v>
+        <v>0</v>
       </c>
       <c r="S230" t="n">
-        <v>62156</v>
+        <v>0</v>
       </c>
       <c r="T230" t="n">
-        <v>452162</v>
+        <v>0</v>
       </c>
       <c r="U230" t="n">
         <v>0</v>
@@ -31941,16 +31941,16 @@
         <v>0</v>
       </c>
       <c r="Y230" t="n">
-        <v>4000</v>
+        <v>0</v>
       </c>
       <c r="Z230" t="n">
-        <v>43000</v>
+        <v>0</v>
       </c>
       <c r="AA230" t="n">
-        <v>73000</v>
+        <v>0</v>
       </c>
       <c r="AB230" t="n">
-        <v>78000</v>
+        <v>0</v>
       </c>
       <c r="AC230" t="n">
         <v>-4</v>
@@ -31959,10 +31959,10 @@
         <v>-4</v>
       </c>
       <c r="AE230" t="n">
-        <v>-30</v>
+        <v>-10</v>
       </c>
       <c r="AF230" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AG230" t="n">
         <v>0</v>
@@ -31982,29 +31982,29 @@
       </c>
       <c r="AM230" t="inlineStr">
         <is>
-          <t>跌破5日線、量能未放大、接近20日低點</t>
+          <t>跌破5日線、量能溫和放大</t>
         </is>
       </c>
       <c r="AN230" t="inlineStr">
         <is>
-          <t>5日法人買超</t>
+          <t>籌碼中性</t>
         </is>
       </c>
       <c r="AO230" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、量能未放大、接近20日低點、5日法人買超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、量能溫和放大、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>2395.TW</t>
+          <t>6278.TW</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>研華</t>
+          <t>台表科</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
@@ -32013,28 +32013,28 @@
         </is>
       </c>
       <c r="D231" t="n">
-        <v>600</v>
+        <v>213</v>
       </c>
       <c r="E231" t="n">
-        <v>558.4</v>
+        <v>200.8</v>
       </c>
       <c r="F231" t="n">
-        <v>546</v>
+        <v>203.25</v>
       </c>
       <c r="G231" t="n">
-        <v>522.58</v>
+        <v>203.88</v>
       </c>
       <c r="H231" t="n">
-        <v>3860896</v>
+        <v>12819719</v>
       </c>
       <c r="I231" t="n">
-        <v>4829073</v>
+        <v>7812777</v>
       </c>
       <c r="J231" t="n">
-        <v>618</v>
+        <v>230.5</v>
       </c>
       <c r="K231" t="n">
-        <v>453</v>
+        <v>186</v>
       </c>
       <c r="L231" t="inlineStr">
         <is>
@@ -32042,52 +32042,52 @@
         </is>
       </c>
       <c r="M231" t="n">
-        <v>-542853</v>
+        <v>136981</v>
       </c>
       <c r="N231" t="n">
-        <v>-1782926</v>
+        <v>-1416719</v>
       </c>
       <c r="O231" t="n">
-        <v>-1741207</v>
+        <v>-186060</v>
       </c>
       <c r="P231" t="n">
-        <v>-691224</v>
+        <v>-6236332</v>
       </c>
       <c r="Q231" t="n">
-        <v>-956752</v>
+        <v>56604</v>
       </c>
       <c r="R231" t="n">
-        <v>-3143446</v>
+        <v>-1452202</v>
       </c>
       <c r="S231" t="n">
-        <v>-4066985</v>
+        <v>421192</v>
       </c>
       <c r="T231" t="n">
-        <v>-3546309</v>
+        <v>-1867623</v>
       </c>
       <c r="U231" t="n">
-        <v>365915</v>
+        <v>72000</v>
       </c>
       <c r="V231" t="n">
-        <v>1081577</v>
+        <v>78000</v>
       </c>
       <c r="W231" t="n">
-        <v>1971832</v>
+        <v>-438000</v>
       </c>
       <c r="X231" t="n">
-        <v>2344288</v>
+        <v>-3336000</v>
       </c>
       <c r="Y231" t="n">
-        <v>47984</v>
+        <v>8377</v>
       </c>
       <c r="Z231" t="n">
-        <v>278943</v>
+        <v>-42517</v>
       </c>
       <c r="AA231" t="n">
-        <v>353946</v>
+        <v>-169252</v>
       </c>
       <c r="AB231" t="n">
-        <v>510797</v>
+        <v>-1032709</v>
       </c>
       <c r="AC231" t="n">
         <v>-4</v>
@@ -32096,10 +32096,10 @@
         <v>-4</v>
       </c>
       <c r="AE231" t="n">
-        <v>45</v>
+        <v>10</v>
       </c>
       <c r="AF231" t="n">
-        <v>-55</v>
+        <v>-20</v>
       </c>
       <c r="AG231" t="n">
         <v>0</v>
@@ -32119,29 +32119,29 @@
       </c>
       <c r="AM231" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、量能未放大</t>
+          <t>站上5日線、空頭排列、成交量放大</t>
         </is>
       </c>
       <c r="AN231" t="inlineStr">
         <is>
-          <t>法人連續偏賣、5日法人明顯賣超、投信買外資賣</t>
+          <t>5日法人賣超、外資買投信賣</t>
         </is>
       </c>
       <c r="AO231" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、多頭排列、量能未放大、法人連續偏賣、5日法人明顯賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、空頭排列、成交量放大、5日法人賣超、外資買投信賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>2355.TW</t>
+          <t>2908.TW</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>敬鵬</t>
+          <t>特力</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
@@ -32150,28 +32150,28 @@
         </is>
       </c>
       <c r="D232" t="n">
-        <v>42.9</v>
+        <v>21.55</v>
       </c>
       <c r="E232" t="n">
-        <v>42.93</v>
+        <v>21.78</v>
       </c>
       <c r="F232" t="n">
-        <v>45.59</v>
+        <v>21.81</v>
       </c>
       <c r="G232" t="n">
-        <v>49.14</v>
+        <v>21.59</v>
       </c>
       <c r="H232" t="n">
-        <v>2551698</v>
+        <v>121724</v>
       </c>
       <c r="I232" t="n">
-        <v>4307409</v>
+        <v>189905</v>
       </c>
       <c r="J232" t="n">
-        <v>56.4</v>
+        <v>22.15</v>
       </c>
       <c r="K232" t="n">
-        <v>40.25</v>
+        <v>20.95</v>
       </c>
       <c r="L232" t="inlineStr">
         <is>
@@ -32179,64 +32179,64 @@
         </is>
       </c>
       <c r="M232" t="n">
-        <v>-378536</v>
+        <v>1000</v>
       </c>
       <c r="N232" t="n">
-        <v>-251690</v>
+        <v>-88000</v>
       </c>
       <c r="O232" t="n">
-        <v>842677</v>
+        <v>135156</v>
       </c>
       <c r="P232" t="n">
-        <v>2472640</v>
+        <v>530162</v>
       </c>
       <c r="Q232" t="n">
-        <v>-203776</v>
+        <v>-3000</v>
       </c>
       <c r="R232" t="n">
-        <v>130730</v>
+        <v>-131000</v>
       </c>
       <c r="S232" t="n">
-        <v>1847095</v>
+        <v>62156</v>
       </c>
       <c r="T232" t="n">
-        <v>3914454</v>
+        <v>452162</v>
       </c>
       <c r="U232" t="n">
-        <v>-115000</v>
+        <v>0</v>
       </c>
       <c r="V232" t="n">
-        <v>-346000</v>
+        <v>0</v>
       </c>
       <c r="W232" t="n">
-        <v>-578000</v>
+        <v>0</v>
       </c>
       <c r="X232" t="n">
-        <v>-598000</v>
+        <v>0</v>
       </c>
       <c r="Y232" t="n">
-        <v>-59760</v>
+        <v>4000</v>
       </c>
       <c r="Z232" t="n">
-        <v>-36420</v>
+        <v>43000</v>
       </c>
       <c r="AA232" t="n">
-        <v>-426418</v>
+        <v>73000</v>
       </c>
       <c r="AB232" t="n">
-        <v>-843814</v>
+        <v>78000</v>
       </c>
       <c r="AC232" t="n">
-        <v>-6</v>
+        <v>-4</v>
       </c>
       <c r="AD232" t="n">
-        <v>-6</v>
+        <v>-4</v>
       </c>
       <c r="AE232" t="n">
-        <v>-45</v>
+        <v>-30</v>
       </c>
       <c r="AF232" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="AG232" t="n">
         <v>0</v>
@@ -32256,17 +32256,17 @@
       </c>
       <c r="AM232" t="inlineStr">
         <is>
-          <t>跌破5日線、空頭排列、量能未放大</t>
+          <t>跌破5日線、量能未放大、接近20日低點</t>
         </is>
       </c>
       <c r="AN232" t="inlineStr">
         <is>
-          <t>5日法人明顯買超、外資買投信賣</t>
+          <t>5日法人買超</t>
         </is>
       </c>
       <c r="AO232" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、空頭排列、量能未放大、5日法人明顯買超、外資買投信賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、量能未放大、接近20日低點、5日法人買超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
@@ -33369,12 +33369,12 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>2890.TW</t>
+          <t>1229.TW</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>永豐金</t>
+          <t>聯華</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
@@ -33383,81 +33383,81 @@
         </is>
       </c>
       <c r="D241" t="n">
-        <v>38.2</v>
+        <v>42.5</v>
       </c>
       <c r="E241" t="n">
+        <v>40.85</v>
+      </c>
+      <c r="F241" t="n">
+        <v>40.66</v>
+      </c>
+      <c r="G241" t="n">
+        <v>41.72</v>
+      </c>
+      <c r="H241" t="n">
+        <v>9105810</v>
+      </c>
+      <c r="I241" t="n">
+        <v>4247248</v>
+      </c>
+      <c r="J241" t="n">
+        <v>44.2</v>
+      </c>
+      <c r="K241" t="n">
         <v>39.7</v>
       </c>
-      <c r="F241" t="n">
-        <v>39.86</v>
-      </c>
-      <c r="G241" t="n">
-        <v>40.02</v>
-      </c>
-      <c r="H241" t="n">
-        <v>75842535</v>
-      </c>
-      <c r="I241" t="n">
-        <v>61979308</v>
-      </c>
-      <c r="J241" t="n">
-        <v>42.3</v>
-      </c>
-      <c r="K241" t="n">
-        <v>37.6</v>
-      </c>
       <c r="L241" t="inlineStr">
         <is>
           <t>無明顯異常</t>
         </is>
       </c>
       <c r="M241" t="n">
-        <v>-4278391</v>
+        <v>377927</v>
       </c>
       <c r="N241" t="n">
-        <v>3213534</v>
+        <v>-1550324</v>
       </c>
       <c r="O241" t="n">
-        <v>8277961</v>
+        <v>-846671</v>
       </c>
       <c r="P241" t="n">
-        <v>20336139</v>
+        <v>438920</v>
       </c>
       <c r="Q241" t="n">
-        <v>-3283107</v>
+        <v>378064</v>
       </c>
       <c r="R241" t="n">
-        <v>-13565282</v>
+        <v>-1430187</v>
       </c>
       <c r="S241" t="n">
-        <v>-44355647</v>
+        <v>-1601981</v>
       </c>
       <c r="T241" t="n">
-        <v>-34673389</v>
+        <v>-432002</v>
       </c>
       <c r="U241" t="n">
-        <v>6667503</v>
+        <v>0</v>
       </c>
       <c r="V241" t="n">
-        <v>24925096</v>
+        <v>5000</v>
       </c>
       <c r="W241" t="n">
-        <v>45964384</v>
+        <v>879000</v>
       </c>
       <c r="X241" t="n">
-        <v>39627024</v>
+        <v>929000</v>
       </c>
       <c r="Y241" t="n">
-        <v>-7662787</v>
+        <v>-137</v>
       </c>
       <c r="Z241" t="n">
-        <v>-8146280</v>
+        <v>-125137</v>
       </c>
       <c r="AA241" t="n">
-        <v>6669224</v>
+        <v>-123690</v>
       </c>
       <c r="AB241" t="n">
-        <v>15382504</v>
+        <v>-58078</v>
       </c>
       <c r="AC241" t="n">
         <v>-6</v>
@@ -33466,10 +33466,10 @@
         <v>-6</v>
       </c>
       <c r="AE241" t="n">
-        <v>-45</v>
+        <v>40</v>
       </c>
       <c r="AF241" t="n">
-        <v>30</v>
+        <v>-55</v>
       </c>
       <c r="AG241" t="n">
         <v>0</v>
@@ -33489,17 +33489,17 @@
       </c>
       <c r="AM241" t="inlineStr">
         <is>
-          <t>跌破5日線、空頭排列、量能溫和放大、接近20日低點</t>
+          <t>站上5日線、爆量</t>
         </is>
       </c>
       <c r="AN241" t="inlineStr">
         <is>
-          <t>5日法人明顯買超、投信買外資賣</t>
+          <t>中期買超轉短線賣壓、5日法人明顯賣超、投信買外資賣</t>
         </is>
       </c>
       <c r="AO241" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、空頭排列、量能溫和放大、接近20日低點、5日法人明顯買超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、爆量、中期買超轉短線賣壓、5日法人明顯賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
@@ -33643,12 +33643,12 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>1229.TW</t>
+          <t>1304.TW</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>聯華</t>
+          <t>台聚</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
@@ -33657,28 +33657,28 @@
         </is>
       </c>
       <c r="D243" t="n">
-        <v>42.5</v>
+        <v>13.45</v>
       </c>
       <c r="E243" t="n">
-        <v>40.85</v>
+        <v>13.22</v>
       </c>
       <c r="F243" t="n">
-        <v>40.66</v>
+        <v>13.44</v>
       </c>
       <c r="G243" t="n">
-        <v>41.72</v>
+        <v>13.68</v>
       </c>
       <c r="H243" t="n">
-        <v>9105810</v>
+        <v>11334246</v>
       </c>
       <c r="I243" t="n">
-        <v>4247248</v>
+        <v>6999002</v>
       </c>
       <c r="J243" t="n">
-        <v>44.2</v>
+        <v>15.8</v>
       </c>
       <c r="K243" t="n">
-        <v>39.7</v>
+        <v>12.85</v>
       </c>
       <c r="L243" t="inlineStr">
         <is>
@@ -33686,52 +33686,52 @@
         </is>
       </c>
       <c r="M243" t="n">
-        <v>377927</v>
+        <v>-1882568</v>
       </c>
       <c r="N243" t="n">
-        <v>-1550324</v>
+        <v>969172</v>
       </c>
       <c r="O243" t="n">
-        <v>-846671</v>
+        <v>-1356962</v>
       </c>
       <c r="P243" t="n">
-        <v>438920</v>
+        <v>-2940233</v>
       </c>
       <c r="Q243" t="n">
-        <v>378064</v>
+        <v>-2090000</v>
       </c>
       <c r="R243" t="n">
-        <v>-1430187</v>
+        <v>450633</v>
       </c>
       <c r="S243" t="n">
-        <v>-1601981</v>
+        <v>-1903467</v>
       </c>
       <c r="T243" t="n">
-        <v>-432002</v>
+        <v>-3515329</v>
       </c>
       <c r="U243" t="n">
         <v>0</v>
       </c>
       <c r="V243" t="n">
-        <v>5000</v>
+        <v>0</v>
       </c>
       <c r="W243" t="n">
-        <v>879000</v>
+        <v>0</v>
       </c>
       <c r="X243" t="n">
-        <v>929000</v>
+        <v>0</v>
       </c>
       <c r="Y243" t="n">
-        <v>-137</v>
+        <v>207432</v>
       </c>
       <c r="Z243" t="n">
-        <v>-125137</v>
+        <v>518539</v>
       </c>
       <c r="AA243" t="n">
-        <v>-123690</v>
+        <v>546505</v>
       </c>
       <c r="AB243" t="n">
-        <v>-58078</v>
+        <v>575096</v>
       </c>
       <c r="AC243" t="n">
         <v>-6</v>
@@ -33740,10 +33740,10 @@
         <v>-6</v>
       </c>
       <c r="AE243" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="AF243" t="n">
-        <v>-55</v>
+        <v>-15</v>
       </c>
       <c r="AG243" t="n">
         <v>0</v>
@@ -33763,29 +33763,29 @@
       </c>
       <c r="AM243" t="inlineStr">
         <is>
-          <t>站上5日線、爆量</t>
+          <t>站上5日線、空頭排列、成交量放大、接近20日低點</t>
         </is>
       </c>
       <c r="AN243" t="inlineStr">
         <is>
-          <t>中期買超轉短線賣壓、5日法人明顯賣超、投信買外資賣</t>
+          <t>短線籌碼止穩、5日法人明顯賣超</t>
         </is>
       </c>
       <c r="AO243" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、爆量、中期買超轉短線賣壓、5日法人明顯賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、空頭排列、成交量放大、接近20日低點、短線籌碼止穩、5日法人明顯賣超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>1304.TW</t>
+          <t>2355.TW</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>台聚</t>
+          <t>敬鵬</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
@@ -33794,28 +33794,28 @@
         </is>
       </c>
       <c r="D244" t="n">
-        <v>13.45</v>
+        <v>42.9</v>
       </c>
       <c r="E244" t="n">
-        <v>13.22</v>
+        <v>42.93</v>
       </c>
       <c r="F244" t="n">
-        <v>13.44</v>
+        <v>45.59</v>
       </c>
       <c r="G244" t="n">
-        <v>13.68</v>
+        <v>49.14</v>
       </c>
       <c r="H244" t="n">
-        <v>11334246</v>
+        <v>2551698</v>
       </c>
       <c r="I244" t="n">
-        <v>6999002</v>
+        <v>4307409</v>
       </c>
       <c r="J244" t="n">
-        <v>15.8</v>
+        <v>56.4</v>
       </c>
       <c r="K244" t="n">
-        <v>12.85</v>
+        <v>40.25</v>
       </c>
       <c r="L244" t="inlineStr">
         <is>
@@ -33823,52 +33823,52 @@
         </is>
       </c>
       <c r="M244" t="n">
-        <v>-1882568</v>
+        <v>-378536</v>
       </c>
       <c r="N244" t="n">
-        <v>969172</v>
+        <v>-251690</v>
       </c>
       <c r="O244" t="n">
-        <v>-1356962</v>
+        <v>842677</v>
       </c>
       <c r="P244" t="n">
-        <v>-2940233</v>
+        <v>2472640</v>
       </c>
       <c r="Q244" t="n">
-        <v>-2090000</v>
+        <v>-203776</v>
       </c>
       <c r="R244" t="n">
-        <v>450633</v>
+        <v>130730</v>
       </c>
       <c r="S244" t="n">
-        <v>-1903467</v>
+        <v>1847095</v>
       </c>
       <c r="T244" t="n">
-        <v>-3515329</v>
+        <v>3914454</v>
       </c>
       <c r="U244" t="n">
-        <v>0</v>
+        <v>-115000</v>
       </c>
       <c r="V244" t="n">
-        <v>0</v>
+        <v>-346000</v>
       </c>
       <c r="W244" t="n">
-        <v>0</v>
+        <v>-578000</v>
       </c>
       <c r="X244" t="n">
-        <v>0</v>
+        <v>-598000</v>
       </c>
       <c r="Y244" t="n">
-        <v>207432</v>
+        <v>-59760</v>
       </c>
       <c r="Z244" t="n">
-        <v>518539</v>
+        <v>-36420</v>
       </c>
       <c r="AA244" t="n">
-        <v>546505</v>
+        <v>-426418</v>
       </c>
       <c r="AB244" t="n">
-        <v>575096</v>
+        <v>-843814</v>
       </c>
       <c r="AC244" t="n">
         <v>-6</v>
@@ -33877,10 +33877,10 @@
         <v>-6</v>
       </c>
       <c r="AE244" t="n">
-        <v>0</v>
+        <v>-45</v>
       </c>
       <c r="AF244" t="n">
-        <v>-15</v>
+        <v>30</v>
       </c>
       <c r="AG244" t="n">
         <v>0</v>
@@ -33900,29 +33900,29 @@
       </c>
       <c r="AM244" t="inlineStr">
         <is>
-          <t>站上5日線、空頭排列、成交量放大、接近20日低點</t>
+          <t>跌破5日線、空頭排列、量能未放大</t>
         </is>
       </c>
       <c r="AN244" t="inlineStr">
         <is>
-          <t>短線籌碼止穩、5日法人明顯賣超</t>
+          <t>5日法人明顯買超、外資買投信賣</t>
         </is>
       </c>
       <c r="AO244" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、空頭排列、成交量放大、接近20日低點、短線籌碼止穩、5日法人明顯賣超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、空頭排列、量能未放大、5日法人明顯買超、外資買投信賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>3042.TW</t>
+          <t>2890.TW</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>晶技</t>
+          <t>永豐金</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
@@ -33931,28 +33931,28 @@
         </is>
       </c>
       <c r="D245" t="n">
-        <v>164.5</v>
+        <v>38.2</v>
       </c>
       <c r="E245" t="n">
-        <v>165.4</v>
+        <v>39.7</v>
       </c>
       <c r="F245" t="n">
-        <v>178.15</v>
+        <v>39.86</v>
       </c>
       <c r="G245" t="n">
-        <v>192.82</v>
+        <v>40.02</v>
       </c>
       <c r="H245" t="n">
-        <v>7564470</v>
+        <v>75842535</v>
       </c>
       <c r="I245" t="n">
-        <v>11745473</v>
+        <v>61979308</v>
       </c>
       <c r="J245" t="n">
-        <v>250</v>
+        <v>42.3</v>
       </c>
       <c r="K245" t="n">
-        <v>153.5</v>
+        <v>37.6</v>
       </c>
       <c r="L245" t="inlineStr">
         <is>
@@ -33960,52 +33960,52 @@
         </is>
       </c>
       <c r="M245" t="n">
-        <v>364457</v>
+        <v>-4278391</v>
       </c>
       <c r="N245" t="n">
-        <v>-3586934</v>
+        <v>3213534</v>
       </c>
       <c r="O245" t="n">
-        <v>3607629</v>
+        <v>8277961</v>
       </c>
       <c r="P245" t="n">
-        <v>-463875</v>
+        <v>20336139</v>
       </c>
       <c r="Q245" t="n">
-        <v>1938836</v>
+        <v>-3283107</v>
       </c>
       <c r="R245" t="n">
-        <v>-1866213</v>
+        <v>-13565282</v>
       </c>
       <c r="S245" t="n">
-        <v>6025260</v>
+        <v>-44355647</v>
       </c>
       <c r="T245" t="n">
-        <v>4334054</v>
+        <v>-34673389</v>
       </c>
       <c r="U245" t="n">
-        <v>-1578000</v>
+        <v>6667503</v>
       </c>
       <c r="V245" t="n">
-        <v>-2199000</v>
+        <v>24925096</v>
       </c>
       <c r="W245" t="n">
-        <v>-2495000</v>
+        <v>45964384</v>
       </c>
       <c r="X245" t="n">
-        <v>-2604000</v>
+        <v>39627024</v>
       </c>
       <c r="Y245" t="n">
-        <v>3621</v>
+        <v>-7662787</v>
       </c>
       <c r="Z245" t="n">
-        <v>478279</v>
+        <v>-8146280</v>
       </c>
       <c r="AA245" t="n">
-        <v>77369</v>
+        <v>6669224</v>
       </c>
       <c r="AB245" t="n">
-        <v>-2193929</v>
+        <v>15382504</v>
       </c>
       <c r="AC245" t="n">
         <v>-6</v>
@@ -34037,59 +34037,59 @@
       </c>
       <c r="AM245" t="inlineStr">
         <is>
-          <t>跌破5日線、空頭排列、量能未放大</t>
+          <t>跌破5日線、空頭排列、量能溫和放大、接近20日低點</t>
         </is>
       </c>
       <c r="AN245" t="inlineStr">
         <is>
-          <t>5日法人明顯買超、外資買投信賣</t>
+          <t>5日法人明顯買超、投信買外資賣</t>
         </is>
       </c>
       <c r="AO245" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、空頭排列、量能未放大、5日法人明顯買超、外資買投信賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、空頭排列、量能溫和放大、接近20日低點、5日法人明顯買超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>00935.TW</t>
+          <t>3042.TW</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>野村臺灣新科技50</t>
+          <t>晶技</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>ETF</t>
+          <t>個股</t>
         </is>
       </c>
       <c r="D246" t="n">
-        <v>56.9</v>
+        <v>164.5</v>
       </c>
       <c r="E246" t="n">
-        <v>54.98</v>
+        <v>165.4</v>
       </c>
       <c r="F246" t="n">
-        <v>56.52</v>
+        <v>178.15</v>
       </c>
       <c r="G246" t="n">
-        <v>58.73</v>
+        <v>192.82</v>
       </c>
       <c r="H246" t="n">
-        <v>11171553</v>
+        <v>7564470</v>
       </c>
       <c r="I246" t="n">
-        <v>18797996</v>
+        <v>11745473</v>
       </c>
       <c r="J246" t="n">
-        <v>63.7</v>
+        <v>250</v>
       </c>
       <c r="K246" t="n">
-        <v>51.4</v>
+        <v>153.5</v>
       </c>
       <c r="L246" t="inlineStr">
         <is>
@@ -34097,64 +34097,64 @@
         </is>
       </c>
       <c r="M246" t="n">
-        <v>5357735</v>
+        <v>364457</v>
       </c>
       <c r="N246" t="n">
-        <v>4269758</v>
+        <v>-3586934</v>
       </c>
       <c r="O246" t="n">
-        <v>-14894555</v>
+        <v>3607629</v>
       </c>
       <c r="P246" t="n">
-        <v>-33717237</v>
+        <v>-463875</v>
       </c>
       <c r="Q246" t="n">
-        <v>1616320</v>
+        <v>1938836</v>
       </c>
       <c r="R246" t="n">
-        <v>4784163</v>
+        <v>-1866213</v>
       </c>
       <c r="S246" t="n">
-        <v>-4159954</v>
+        <v>6025260</v>
       </c>
       <c r="T246" t="n">
-        <v>-11629055</v>
+        <v>4334054</v>
       </c>
       <c r="U246" t="n">
-        <v>470000</v>
+        <v>-1578000</v>
       </c>
       <c r="V246" t="n">
-        <v>1388000</v>
+        <v>-2199000</v>
       </c>
       <c r="W246" t="n">
-        <v>1530000</v>
+        <v>-2495000</v>
       </c>
       <c r="X246" t="n">
-        <v>3169000</v>
+        <v>-2604000</v>
       </c>
       <c r="Y246" t="n">
-        <v>3271415</v>
+        <v>3621</v>
       </c>
       <c r="Z246" t="n">
-        <v>-1902405</v>
+        <v>478279</v>
       </c>
       <c r="AA246" t="n">
-        <v>-12264601</v>
+        <v>77369</v>
       </c>
       <c r="AB246" t="n">
-        <v>-25257182</v>
+        <v>-2193929</v>
       </c>
       <c r="AC246" t="n">
-        <v>-8</v>
+        <v>-6</v>
       </c>
       <c r="AD246" t="n">
-        <v>-8</v>
+        <v>-6</v>
       </c>
       <c r="AE246" t="n">
-        <v>-5</v>
+        <v>-45</v>
       </c>
       <c r="AF246" t="n">
-        <v>-15</v>
+        <v>30</v>
       </c>
       <c r="AG246" t="n">
         <v>0</v>
@@ -34174,29 +34174,29 @@
       </c>
       <c r="AM246" t="inlineStr">
         <is>
-          <t>站上5日線、空頭排列、量能未放大</t>
+          <t>跌破5日線、空頭排列、量能未放大</t>
         </is>
       </c>
       <c r="AN246" t="inlineStr">
         <is>
-          <t>短線籌碼止穩、5日法人明顯賣超、投信買外資賣</t>
+          <t>5日法人明顯買超、外資買投信賣</t>
         </is>
       </c>
       <c r="AO246" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、空頭排列、量能未放大、短線籌碼止穩、5日法人明顯賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、空頭排列、量能未放大、5日法人明顯買超、外資買投信賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>2436.TW</t>
+          <t>5371.TWO</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>偉詮電</t>
+          <t>中光電</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
@@ -34205,28 +34205,28 @@
         </is>
       </c>
       <c r="D247" t="n">
-        <v>60.2</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="E247" t="n">
-        <v>59.08</v>
+        <v>84.58</v>
       </c>
       <c r="F247" t="n">
-        <v>61.35</v>
+        <v>89.02</v>
       </c>
       <c r="G247" t="n">
-        <v>67.12</v>
+        <v>88.01000000000001</v>
       </c>
       <c r="H247" t="n">
-        <v>1962581</v>
+        <v>17459000</v>
       </c>
       <c r="I247" t="n">
-        <v>2812006</v>
+        <v>32166400</v>
       </c>
       <c r="J247" t="n">
-        <v>79.3</v>
+        <v>104</v>
       </c>
       <c r="K247" t="n">
-        <v>54.7</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="L247" t="inlineStr">
         <is>
@@ -34234,28 +34234,28 @@
         </is>
       </c>
       <c r="M247" t="n">
-        <v>-344330</v>
+        <v>0</v>
       </c>
       <c r="N247" t="n">
-        <v>272811</v>
+        <v>0</v>
       </c>
       <c r="O247" t="n">
-        <v>-1680055</v>
+        <v>0</v>
       </c>
       <c r="P247" t="n">
-        <v>-5498871</v>
+        <v>0</v>
       </c>
       <c r="Q247" t="n">
-        <v>-323000</v>
+        <v>0</v>
       </c>
       <c r="R247" t="n">
-        <v>289409</v>
+        <v>0</v>
       </c>
       <c r="S247" t="n">
-        <v>-1554102</v>
+        <v>0</v>
       </c>
       <c r="T247" t="n">
-        <v>-5000260</v>
+        <v>0</v>
       </c>
       <c r="U247" t="n">
         <v>0</v>
@@ -34264,22 +34264,22 @@
         <v>0</v>
       </c>
       <c r="W247" t="n">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="X247" t="n">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="Y247" t="n">
-        <v>-21330</v>
+        <v>0</v>
       </c>
       <c r="Z247" t="n">
-        <v>-16598</v>
+        <v>0</v>
       </c>
       <c r="AA247" t="n">
-        <v>-127953</v>
+        <v>0</v>
       </c>
       <c r="AB247" t="n">
-        <v>-500611</v>
+        <v>0</v>
       </c>
       <c r="AC247" t="n">
         <v>-8</v>
@@ -34288,10 +34288,10 @@
         <v>-8</v>
       </c>
       <c r="AE247" t="n">
-        <v>-5</v>
+        <v>-20</v>
       </c>
       <c r="AF247" t="n">
-        <v>-15</v>
+        <v>0</v>
       </c>
       <c r="AG247" t="n">
         <v>0</v>
@@ -34311,29 +34311,29 @@
       </c>
       <c r="AM247" t="inlineStr">
         <is>
-          <t>站上5日線、空頭排列、量能未放大</t>
+          <t>跌破5日線、量能未放大</t>
         </is>
       </c>
       <c r="AN247" t="inlineStr">
         <is>
-          <t>短線籌碼止穩、5日法人明顯賣超、投信買外資賣</t>
+          <t>籌碼中性</t>
         </is>
       </c>
       <c r="AO247" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、空頭排列、量能未放大、短線籌碼止穩、5日法人明顯賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、量能未放大、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>00927.TW</t>
+          <t>00935.TW</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>群益半導體收益</t>
+          <t>野村臺灣新科技50</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
@@ -34342,28 +34342,28 @@
         </is>
       </c>
       <c r="D248" t="n">
-        <v>36.94</v>
+        <v>56.9</v>
       </c>
       <c r="E248" t="n">
-        <v>36.09</v>
+        <v>54.98</v>
       </c>
       <c r="F248" t="n">
-        <v>38.31</v>
+        <v>56.52</v>
       </c>
       <c r="G248" t="n">
-        <v>39.99</v>
+        <v>58.73</v>
       </c>
       <c r="H248" t="n">
-        <v>12824606</v>
+        <v>11171553</v>
       </c>
       <c r="I248" t="n">
-        <v>31736591</v>
+        <v>18797996</v>
       </c>
       <c r="J248" t="n">
-        <v>43.55</v>
+        <v>63.7</v>
       </c>
       <c r="K248" t="n">
-        <v>34.02</v>
+        <v>51.4</v>
       </c>
       <c r="L248" t="inlineStr">
         <is>
@@ -34371,52 +34371,52 @@
         </is>
       </c>
       <c r="M248" t="n">
-        <v>-807556</v>
+        <v>5357735</v>
       </c>
       <c r="N248" t="n">
-        <v>2155976</v>
+        <v>4269758</v>
       </c>
       <c r="O248" t="n">
-        <v>-7448253</v>
+        <v>-14894555</v>
       </c>
       <c r="P248" t="n">
-        <v>-184471028</v>
+        <v>-33717237</v>
       </c>
       <c r="Q248" t="n">
-        <v>178050</v>
+        <v>1616320</v>
       </c>
       <c r="R248" t="n">
-        <v>5700063</v>
+        <v>4784163</v>
       </c>
       <c r="S248" t="n">
-        <v>5021481</v>
+        <v>-4159954</v>
       </c>
       <c r="T248" t="n">
-        <v>2523678</v>
+        <v>-11629055</v>
       </c>
       <c r="U248" t="n">
-        <v>0</v>
+        <v>470000</v>
       </c>
       <c r="V248" t="n">
-        <v>0</v>
+        <v>1388000</v>
       </c>
       <c r="W248" t="n">
-        <v>0</v>
+        <v>1530000</v>
       </c>
       <c r="X248" t="n">
-        <v>230000</v>
+        <v>3169000</v>
       </c>
       <c r="Y248" t="n">
-        <v>-985606</v>
+        <v>3271415</v>
       </c>
       <c r="Z248" t="n">
-        <v>-3544087</v>
+        <v>-1902405</v>
       </c>
       <c r="AA248" t="n">
-        <v>-12469734</v>
+        <v>-12264601</v>
       </c>
       <c r="AB248" t="n">
-        <v>-187224706</v>
+        <v>-25257182</v>
       </c>
       <c r="AC248" t="n">
         <v>-8</v>
@@ -34453,12 +34453,12 @@
       </c>
       <c r="AN248" t="inlineStr">
         <is>
-          <t>短線籌碼止穩、5日法人明顯賣超</t>
+          <t>短線籌碼止穩、5日法人明顯賣超、投信買外資賣</t>
         </is>
       </c>
       <c r="AO248" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、空頭排列、量能未放大、短線籌碼止穩、5日法人明顯賣超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、空頭排列、量能未放大、短線籌碼止穩、5日法人明顯賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
@@ -35561,12 +35561,12 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>2323.TW</t>
+          <t>2436.TW</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>中環</t>
+          <t>偉詮電</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
@@ -35575,28 +35575,28 @@
         </is>
       </c>
       <c r="D257" t="n">
-        <v>10.6</v>
+        <v>60.2</v>
       </c>
       <c r="E257" t="n">
-        <v>10.44</v>
+        <v>59.08</v>
       </c>
       <c r="F257" t="n">
-        <v>10.69</v>
+        <v>61.35</v>
       </c>
       <c r="G257" t="n">
-        <v>11.05</v>
+        <v>67.12</v>
       </c>
       <c r="H257" t="n">
-        <v>2620926</v>
+        <v>1962581</v>
       </c>
       <c r="I257" t="n">
-        <v>6282801</v>
+        <v>2812006</v>
       </c>
       <c r="J257" t="n">
-        <v>12.2</v>
+        <v>79.3</v>
       </c>
       <c r="K257" t="n">
-        <v>9.98</v>
+        <v>54.7</v>
       </c>
       <c r="L257" t="inlineStr">
         <is>
@@ -35604,28 +35604,28 @@
         </is>
       </c>
       <c r="M257" t="n">
-        <v>-253356</v>
+        <v>-344330</v>
       </c>
       <c r="N257" t="n">
-        <v>2122311</v>
+        <v>272811</v>
       </c>
       <c r="O257" t="n">
-        <v>-7353485</v>
+        <v>-1680055</v>
       </c>
       <c r="P257" t="n">
-        <v>-12690374</v>
+        <v>-5498871</v>
       </c>
       <c r="Q257" t="n">
-        <v>-188055</v>
+        <v>-323000</v>
       </c>
       <c r="R257" t="n">
-        <v>2274612</v>
+        <v>289409</v>
       </c>
       <c r="S257" t="n">
-        <v>-6544000</v>
+        <v>-1554102</v>
       </c>
       <c r="T257" t="n">
-        <v>-10808505</v>
+        <v>-5000260</v>
       </c>
       <c r="U257" t="n">
         <v>0</v>
@@ -35634,22 +35634,22 @@
         <v>0</v>
       </c>
       <c r="W257" t="n">
-        <v>111000</v>
+        <v>2000</v>
       </c>
       <c r="X257" t="n">
-        <v>11000</v>
+        <v>2000</v>
       </c>
       <c r="Y257" t="n">
-        <v>-65301</v>
+        <v>-21330</v>
       </c>
       <c r="Z257" t="n">
-        <v>-152301</v>
+        <v>-16598</v>
       </c>
       <c r="AA257" t="n">
-        <v>-920485</v>
+        <v>-127953</v>
       </c>
       <c r="AB257" t="n">
-        <v>-1892869</v>
+        <v>-500611</v>
       </c>
       <c r="AC257" t="n">
         <v>-8</v>
@@ -36109,12 +36109,12 @@
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>3019.TW</t>
+          <t>2323.TW</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>亞光</t>
+          <t>中環</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
@@ -36123,28 +36123,28 @@
         </is>
       </c>
       <c r="D261" t="n">
-        <v>136.5</v>
+        <v>10.6</v>
       </c>
       <c r="E261" t="n">
-        <v>134.6</v>
+        <v>10.44</v>
       </c>
       <c r="F261" t="n">
-        <v>139.35</v>
+        <v>10.69</v>
       </c>
       <c r="G261" t="n">
-        <v>142.28</v>
+        <v>11.05</v>
       </c>
       <c r="H261" t="n">
-        <v>2144408</v>
+        <v>2620926</v>
       </c>
       <c r="I261" t="n">
-        <v>3070049</v>
+        <v>6282801</v>
       </c>
       <c r="J261" t="n">
-        <v>159.5</v>
+        <v>12.2</v>
       </c>
       <c r="K261" t="n">
-        <v>124.5</v>
+        <v>9.98</v>
       </c>
       <c r="L261" t="inlineStr">
         <is>
@@ -36152,28 +36152,28 @@
         </is>
       </c>
       <c r="M261" t="n">
-        <v>-307708</v>
+        <v>-253356</v>
       </c>
       <c r="N261" t="n">
-        <v>613973</v>
+        <v>2122311</v>
       </c>
       <c r="O261" t="n">
-        <v>-1808168</v>
+        <v>-7353485</v>
       </c>
       <c r="P261" t="n">
-        <v>-2429397</v>
+        <v>-12690374</v>
       </c>
       <c r="Q261" t="n">
-        <v>-279006</v>
+        <v>-188055</v>
       </c>
       <c r="R261" t="n">
-        <v>592580</v>
+        <v>2274612</v>
       </c>
       <c r="S261" t="n">
-        <v>-1227951</v>
+        <v>-6544000</v>
       </c>
       <c r="T261" t="n">
-        <v>-2356947</v>
+        <v>-10808505</v>
       </c>
       <c r="U261" t="n">
         <v>0</v>
@@ -36182,22 +36182,22 @@
         <v>0</v>
       </c>
       <c r="W261" t="n">
-        <v>0</v>
+        <v>111000</v>
       </c>
       <c r="X261" t="n">
-        <v>0</v>
+        <v>11000</v>
       </c>
       <c r="Y261" t="n">
-        <v>-28702</v>
+        <v>-65301</v>
       </c>
       <c r="Z261" t="n">
-        <v>21393</v>
+        <v>-152301</v>
       </c>
       <c r="AA261" t="n">
-        <v>-580217</v>
+        <v>-920485</v>
       </c>
       <c r="AB261" t="n">
-        <v>-72450</v>
+        <v>-1892869</v>
       </c>
       <c r="AC261" t="n">
         <v>-8</v>
@@ -36234,12 +36234,12 @@
       </c>
       <c r="AN261" t="inlineStr">
         <is>
-          <t>短線籌碼止穩、5日法人明顯賣超</t>
+          <t>短線籌碼止穩、5日法人明顯賣超、投信買外資賣</t>
         </is>
       </c>
       <c r="AO261" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、空頭排列、量能未放大、短線籌碼止穩、5日法人明顯賣超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、空頭排列、量能未放大、短線籌碼止穩、5日法人明顯賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
@@ -36520,12 +36520,12 @@
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>00403A.TW</t>
+          <t>00927.TW</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>主動統一升級50</t>
+          <t>群益半導體收益</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
@@ -36534,28 +36534,28 @@
         </is>
       </c>
       <c r="D264" t="n">
-        <v>9.970000000000001</v>
+        <v>36.94</v>
       </c>
       <c r="E264" t="n">
-        <v>9.699999999999999</v>
+        <v>36.09</v>
       </c>
       <c r="F264" t="n">
-        <v>10.02</v>
+        <v>38.31</v>
       </c>
       <c r="G264" t="n">
-        <v>10.43</v>
+        <v>39.99</v>
       </c>
       <c r="H264" t="n">
-        <v>164301751</v>
+        <v>12824606</v>
       </c>
       <c r="I264" t="n">
-        <v>502701016</v>
+        <v>31736591</v>
       </c>
       <c r="J264" t="n">
-        <v>11.29</v>
+        <v>43.55</v>
       </c>
       <c r="K264" t="n">
-        <v>9.130000000000001</v>
+        <v>34.02</v>
       </c>
       <c r="L264" t="inlineStr">
         <is>
@@ -36563,28 +36563,28 @@
         </is>
       </c>
       <c r="M264" t="n">
-        <v>25760459</v>
+        <v>-807556</v>
       </c>
       <c r="N264" t="n">
-        <v>201798751</v>
+        <v>2155976</v>
       </c>
       <c r="O264" t="n">
-        <v>-997245738</v>
+        <v>-7448253</v>
       </c>
       <c r="P264" t="n">
-        <v>-1288172155</v>
+        <v>-184471028</v>
       </c>
       <c r="Q264" t="n">
-        <v>6112368</v>
+        <v>178050</v>
       </c>
       <c r="R264" t="n">
-        <v>170833262</v>
+        <v>5700063</v>
       </c>
       <c r="S264" t="n">
-        <v>-363121665</v>
+        <v>5021481</v>
       </c>
       <c r="T264" t="n">
-        <v>-490287020</v>
+        <v>2523678</v>
       </c>
       <c r="U264" t="n">
         <v>0</v>
@@ -36596,19 +36596,19 @@
         <v>0</v>
       </c>
       <c r="X264" t="n">
-        <v>0</v>
+        <v>230000</v>
       </c>
       <c r="Y264" t="n">
-        <v>19648091</v>
+        <v>-985606</v>
       </c>
       <c r="Z264" t="n">
-        <v>30965489</v>
+        <v>-3544087</v>
       </c>
       <c r="AA264" t="n">
-        <v>-634124073</v>
+        <v>-12469734</v>
       </c>
       <c r="AB264" t="n">
-        <v>-797885135</v>
+        <v>-187224706</v>
       </c>
       <c r="AC264" t="n">
         <v>-8</v>
@@ -36657,42 +36657,42 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>1605.TW</t>
+          <t>00403A.TW</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>華新</t>
+          <t>主動統一升級50</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>個股</t>
+          <t>ETF</t>
         </is>
       </c>
       <c r="D265" t="n">
-        <v>33.65</v>
+        <v>9.970000000000001</v>
       </c>
       <c r="E265" t="n">
-        <v>32.9</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="F265" t="n">
-        <v>33.58</v>
+        <v>10.02</v>
       </c>
       <c r="G265" t="n">
-        <v>34.77</v>
+        <v>10.43</v>
       </c>
       <c r="H265" t="n">
-        <v>15343771</v>
+        <v>164301751</v>
       </c>
       <c r="I265" t="n">
-        <v>19561660</v>
+        <v>502701016</v>
       </c>
       <c r="J265" t="n">
-        <v>39.7</v>
+        <v>11.29</v>
       </c>
       <c r="K265" t="n">
-        <v>31.1</v>
+        <v>9.130000000000001</v>
       </c>
       <c r="L265" t="inlineStr">
         <is>
@@ -36700,52 +36700,52 @@
         </is>
       </c>
       <c r="M265" t="n">
-        <v>2237021</v>
+        <v>25760459</v>
       </c>
       <c r="N265" t="n">
-        <v>7401788</v>
+        <v>201798751</v>
       </c>
       <c r="O265" t="n">
-        <v>-2159626</v>
+        <v>-997245738</v>
       </c>
       <c r="P265" t="n">
-        <v>-7890215</v>
+        <v>-1288172155</v>
       </c>
       <c r="Q265" t="n">
-        <v>2313742</v>
+        <v>6112368</v>
       </c>
       <c r="R265" t="n">
-        <v>7240739</v>
+        <v>170833262</v>
       </c>
       <c r="S265" t="n">
-        <v>-1333124</v>
+        <v>-363121665</v>
       </c>
       <c r="T265" t="n">
-        <v>-7289780</v>
+        <v>-490287020</v>
       </c>
       <c r="U265" t="n">
-        <v>-247</v>
+        <v>0</v>
       </c>
       <c r="V265" t="n">
-        <v>-21296</v>
+        <v>0</v>
       </c>
       <c r="W265" t="n">
-        <v>9388</v>
+        <v>0</v>
       </c>
       <c r="X265" t="n">
-        <v>-17630</v>
+        <v>0</v>
       </c>
       <c r="Y265" t="n">
-        <v>-76474</v>
+        <v>19648091</v>
       </c>
       <c r="Z265" t="n">
-        <v>182345</v>
+        <v>30965489</v>
       </c>
       <c r="AA265" t="n">
-        <v>-835890</v>
+        <v>-634124073</v>
       </c>
       <c r="AB265" t="n">
-        <v>-582805</v>
+        <v>-797885135</v>
       </c>
       <c r="AC265" t="n">
         <v>-8</v>
@@ -36782,12 +36782,12 @@
       </c>
       <c r="AN265" t="inlineStr">
         <is>
-          <t>短線籌碼止穩、5日法人明顯賣超、投信買外資賣</t>
+          <t>短線籌碼止穩、5日法人明顯賣超</t>
         </is>
       </c>
       <c r="AO265" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、空頭排列、量能未放大、短線籌碼止穩、5日法人明顯賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、空頭排列、量能未放大、短線籌碼止穩、5日法人明顯賣超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
@@ -36931,12 +36931,12 @@
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>5371.TWO</t>
+          <t>1605.TW</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>中光電</t>
+          <t>華新</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
@@ -36945,28 +36945,28 @@
         </is>
       </c>
       <c r="D267" t="n">
-        <v>82.09999999999999</v>
+        <v>33.65</v>
       </c>
       <c r="E267" t="n">
-        <v>84.58</v>
+        <v>32.9</v>
       </c>
       <c r="F267" t="n">
-        <v>89.02</v>
+        <v>33.58</v>
       </c>
       <c r="G267" t="n">
-        <v>88.01000000000001</v>
+        <v>34.77</v>
       </c>
       <c r="H267" t="n">
-        <v>17459000</v>
+        <v>15343771</v>
       </c>
       <c r="I267" t="n">
-        <v>32166400</v>
+        <v>19561660</v>
       </c>
       <c r="J267" t="n">
-        <v>104</v>
+        <v>39.7</v>
       </c>
       <c r="K267" t="n">
-        <v>71.90000000000001</v>
+        <v>31.1</v>
       </c>
       <c r="L267" t="inlineStr">
         <is>
@@ -36974,52 +36974,52 @@
         </is>
       </c>
       <c r="M267" t="n">
-        <v>0</v>
+        <v>2237021</v>
       </c>
       <c r="N267" t="n">
-        <v>0</v>
+        <v>7401788</v>
       </c>
       <c r="O267" t="n">
-        <v>0</v>
+        <v>-2159626</v>
       </c>
       <c r="P267" t="n">
-        <v>0</v>
+        <v>-7890215</v>
       </c>
       <c r="Q267" t="n">
-        <v>0</v>
+        <v>2313742</v>
       </c>
       <c r="R267" t="n">
-        <v>0</v>
+        <v>7240739</v>
       </c>
       <c r="S267" t="n">
-        <v>0</v>
+        <v>-1333124</v>
       </c>
       <c r="T267" t="n">
-        <v>0</v>
+        <v>-7289780</v>
       </c>
       <c r="U267" t="n">
-        <v>0</v>
+        <v>-247</v>
       </c>
       <c r="V267" t="n">
-        <v>0</v>
+        <v>-21296</v>
       </c>
       <c r="W267" t="n">
-        <v>0</v>
+        <v>9388</v>
       </c>
       <c r="X267" t="n">
-        <v>0</v>
+        <v>-17630</v>
       </c>
       <c r="Y267" t="n">
-        <v>0</v>
+        <v>-76474</v>
       </c>
       <c r="Z267" t="n">
-        <v>0</v>
+        <v>182345</v>
       </c>
       <c r="AA267" t="n">
-        <v>0</v>
+        <v>-835890</v>
       </c>
       <c r="AB267" t="n">
-        <v>0</v>
+        <v>-582805</v>
       </c>
       <c r="AC267" t="n">
         <v>-8</v>
@@ -37028,10 +37028,10 @@
         <v>-8</v>
       </c>
       <c r="AE267" t="n">
-        <v>-20</v>
+        <v>-5</v>
       </c>
       <c r="AF267" t="n">
-        <v>0</v>
+        <v>-15</v>
       </c>
       <c r="AG267" t="n">
         <v>0</v>
@@ -37051,29 +37051,29 @@
       </c>
       <c r="AM267" t="inlineStr">
         <is>
-          <t>跌破5日線、量能未放大</t>
+          <t>站上5日線、空頭排列、量能未放大</t>
         </is>
       </c>
       <c r="AN267" t="inlineStr">
         <is>
-          <t>籌碼中性</t>
+          <t>短線籌碼止穩、5日法人明顯賣超、投信買外資賣</t>
         </is>
       </c>
       <c r="AO267" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、量能未放大、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、空頭排列、量能未放大、短線籌碼止穩、5日法人明顯賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>2108.TW</t>
+          <t>3019.TW</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>南帝</t>
+          <t>亞光</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
@@ -37082,28 +37082,28 @@
         </is>
       </c>
       <c r="D268" t="n">
-        <v>28.85</v>
+        <v>136.5</v>
       </c>
       <c r="E268" t="n">
-        <v>28.09</v>
+        <v>134.6</v>
       </c>
       <c r="F268" t="n">
-        <v>28.32</v>
+        <v>139.35</v>
       </c>
       <c r="G268" t="n">
-        <v>28.37</v>
+        <v>142.28</v>
       </c>
       <c r="H268" t="n">
-        <v>714394</v>
+        <v>2144408</v>
       </c>
       <c r="I268" t="n">
-        <v>726024</v>
+        <v>3070049</v>
       </c>
       <c r="J268" t="n">
-        <v>30.6</v>
+        <v>159.5</v>
       </c>
       <c r="K268" t="n">
-        <v>26.9</v>
+        <v>124.5</v>
       </c>
       <c r="L268" t="inlineStr">
         <is>
@@ -37111,28 +37111,28 @@
         </is>
       </c>
       <c r="M268" t="n">
-        <v>200384</v>
+        <v>-307708</v>
       </c>
       <c r="N268" t="n">
-        <v>170186</v>
+        <v>613973</v>
       </c>
       <c r="O268" t="n">
-        <v>-263696</v>
+        <v>-1808168</v>
       </c>
       <c r="P268" t="n">
-        <v>164317</v>
+        <v>-2429397</v>
       </c>
       <c r="Q268" t="n">
-        <v>194150</v>
+        <v>-279006</v>
       </c>
       <c r="R268" t="n">
-        <v>178167</v>
+        <v>592580</v>
       </c>
       <c r="S268" t="n">
-        <v>-430225</v>
+        <v>-1227951</v>
       </c>
       <c r="T268" t="n">
-        <v>-16532</v>
+        <v>-2356947</v>
       </c>
       <c r="U268" t="n">
         <v>0</v>
@@ -37141,34 +37141,34 @@
         <v>0</v>
       </c>
       <c r="W268" t="n">
-        <v>152000</v>
+        <v>0</v>
       </c>
       <c r="X268" t="n">
-        <v>152000</v>
+        <v>0</v>
       </c>
       <c r="Y268" t="n">
-        <v>6234</v>
+        <v>-28702</v>
       </c>
       <c r="Z268" t="n">
-        <v>-7981</v>
+        <v>21393</v>
       </c>
       <c r="AA268" t="n">
-        <v>14529</v>
+        <v>-580217</v>
       </c>
       <c r="AB268" t="n">
-        <v>28849</v>
+        <v>-72450</v>
       </c>
       <c r="AC268" t="n">
-        <v>-10</v>
+        <v>-8</v>
       </c>
       <c r="AD268" t="n">
-        <v>-10</v>
+        <v>-8</v>
       </c>
       <c r="AE268" t="n">
         <v>-5</v>
       </c>
       <c r="AF268" t="n">
-        <v>-20</v>
+        <v>-15</v>
       </c>
       <c r="AG268" t="n">
         <v>0</v>
@@ -37193,12 +37193,12 @@
       </c>
       <c r="AN268" t="inlineStr">
         <is>
-          <t>5日法人賣超、投信買外資賣</t>
+          <t>短線籌碼止穩、5日法人明顯賣超</t>
         </is>
       </c>
       <c r="AO268" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、空頭排列、量能未放大、5日法人賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、空頭排列、量能未放大、短線籌碼止穩、5日法人明顯賣超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
@@ -37342,12 +37342,12 @@
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>6278.TW</t>
+          <t>2108.TW</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>台表科</t>
+          <t>南帝</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
@@ -37356,28 +37356,28 @@
         </is>
       </c>
       <c r="D270" t="n">
-        <v>166</v>
+        <v>28.85</v>
       </c>
       <c r="E270" t="n">
-        <v>164.4</v>
+        <v>28.09</v>
       </c>
       <c r="F270" t="n">
-        <v>172.9</v>
+        <v>28.32</v>
       </c>
       <c r="G270" t="n">
-        <v>188.25</v>
+        <v>28.37</v>
       </c>
       <c r="H270" t="n">
-        <v>2064537</v>
+        <v>714394</v>
       </c>
       <c r="I270" t="n">
-        <v>3976756</v>
+        <v>726024</v>
       </c>
       <c r="J270" t="n">
-        <v>221</v>
+        <v>30.6</v>
       </c>
       <c r="K270" t="n">
-        <v>153.5</v>
+        <v>26.9</v>
       </c>
       <c r="L270" t="inlineStr">
         <is>
@@ -37385,52 +37385,52 @@
         </is>
       </c>
       <c r="M270" t="n">
-        <v>136981</v>
+        <v>200384</v>
       </c>
       <c r="N270" t="n">
-        <v>-1416719</v>
+        <v>170186</v>
       </c>
       <c r="O270" t="n">
-        <v>-186060</v>
+        <v>-263696</v>
       </c>
       <c r="P270" t="n">
-        <v>-6236332</v>
+        <v>164317</v>
       </c>
       <c r="Q270" t="n">
-        <v>56604</v>
+        <v>194150</v>
       </c>
       <c r="R270" t="n">
-        <v>-1452202</v>
+        <v>178167</v>
       </c>
       <c r="S270" t="n">
-        <v>421192</v>
+        <v>-430225</v>
       </c>
       <c r="T270" t="n">
-        <v>-1867623</v>
+        <v>-16532</v>
       </c>
       <c r="U270" t="n">
-        <v>72000</v>
+        <v>0</v>
       </c>
       <c r="V270" t="n">
-        <v>78000</v>
+        <v>0</v>
       </c>
       <c r="W270" t="n">
-        <v>-438000</v>
+        <v>152000</v>
       </c>
       <c r="X270" t="n">
-        <v>-3336000</v>
+        <v>152000</v>
       </c>
       <c r="Y270" t="n">
-        <v>8377</v>
+        <v>6234</v>
       </c>
       <c r="Z270" t="n">
-        <v>-42517</v>
+        <v>-7981</v>
       </c>
       <c r="AA270" t="n">
-        <v>-169252</v>
+        <v>14529</v>
       </c>
       <c r="AB270" t="n">
-        <v>-1032709</v>
+        <v>28849</v>
       </c>
       <c r="AC270" t="n">
         <v>-10</v>
@@ -37467,12 +37467,12 @@
       </c>
       <c r="AN270" t="inlineStr">
         <is>
-          <t>5日法人賣超、外資買投信賣</t>
+          <t>5日法人賣超、投信買外資賣</t>
         </is>
       </c>
       <c r="AO270" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、空頭排列、量能未放大、5日法人賣超、外資買投信賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、空頭排列、量能未放大、5日法人賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>

--- a/output/universe_analysis_result.xlsx
+++ b/output/universe_analysis_result.xlsx
@@ -26245,12 +26245,12 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>2498.TW</t>
+          <t>4147.TWO</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>宏達電</t>
+          <t>中裕</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -26259,28 +26259,28 @@
         </is>
       </c>
       <c r="D189" t="n">
-        <v>41.6</v>
+        <v>58.9</v>
       </c>
       <c r="E189" t="n">
-        <v>41.79</v>
+        <v>58.68</v>
       </c>
       <c r="F189" t="n">
-        <v>42.23</v>
+        <v>60.77</v>
       </c>
       <c r="G189" t="n">
-        <v>43.27</v>
+        <v>64.17</v>
       </c>
       <c r="H189" t="n">
-        <v>3249275</v>
+        <v>553000</v>
       </c>
       <c r="I189" t="n">
-        <v>3715775</v>
+        <v>848400</v>
       </c>
       <c r="J189" t="n">
-        <v>47.2</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="K189" t="n">
-        <v>39.85</v>
+        <v>57.8</v>
       </c>
       <c r="L189" t="inlineStr">
         <is>
@@ -26288,28 +26288,28 @@
         </is>
       </c>
       <c r="M189" t="n">
-        <v>-483893</v>
+        <v>0</v>
       </c>
       <c r="N189" t="n">
-        <v>-744420</v>
+        <v>0</v>
       </c>
       <c r="O189" t="n">
-        <v>327102</v>
+        <v>0</v>
       </c>
       <c r="P189" t="n">
-        <v>-1228405</v>
+        <v>0</v>
       </c>
       <c r="Q189" t="n">
-        <v>-380294</v>
+        <v>0</v>
       </c>
       <c r="R189" t="n">
-        <v>-710328</v>
+        <v>0</v>
       </c>
       <c r="S189" t="n">
-        <v>384317</v>
+        <v>0</v>
       </c>
       <c r="T189" t="n">
-        <v>-662138</v>
+        <v>0</v>
       </c>
       <c r="U189" t="n">
         <v>0</v>
@@ -26318,22 +26318,22 @@
         <v>0</v>
       </c>
       <c r="W189" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="X189" t="n">
-        <v>-15000</v>
+        <v>0</v>
       </c>
       <c r="Y189" t="n">
-        <v>-103599</v>
+        <v>0</v>
       </c>
       <c r="Z189" t="n">
-        <v>-34092</v>
+        <v>0</v>
       </c>
       <c r="AA189" t="n">
-        <v>-58215</v>
+        <v>0</v>
       </c>
       <c r="AB189" t="n">
-        <v>-551267</v>
+        <v>0</v>
       </c>
       <c r="AC189" t="n">
         <v>-6</v>
@@ -26342,10 +26342,10 @@
         <v>-6</v>
       </c>
       <c r="AE189" t="n">
-        <v>-55</v>
+        <v>-15</v>
       </c>
       <c r="AF189" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="AG189" t="n">
         <v>0</v>
@@ -26365,29 +26365,29 @@
       </c>
       <c r="AM189" t="inlineStr">
         <is>
-          <t>跌破5日線、空頭排列、量能未放大、接近20日低點</t>
+          <t>站上5日線、空頭排列、量能未放大、接近20日低點</t>
         </is>
       </c>
       <c r="AN189" t="inlineStr">
         <is>
-          <t>5日法人買超、外資投信同步買超</t>
+          <t>籌碼中性</t>
         </is>
       </c>
       <c r="AO189" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、空頭排列、量能未放大、接近20日低點、5日法人買超、外資投信同步買超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、空頭排列、量能未放大、接近20日低點、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>9105.TW</t>
+          <t>2498.TW</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>泰金寶-DR</t>
+          <t>宏達電</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -26396,28 +26396,28 @@
         </is>
       </c>
       <c r="D190" t="n">
-        <v>8.390000000000001</v>
+        <v>41.6</v>
       </c>
       <c r="E190" t="n">
-        <v>8.59</v>
+        <v>41.79</v>
       </c>
       <c r="F190" t="n">
-        <v>8.630000000000001</v>
+        <v>42.23</v>
       </c>
       <c r="G190" t="n">
-        <v>8.869999999999999</v>
+        <v>43.27</v>
       </c>
       <c r="H190" t="n">
-        <v>17499331</v>
+        <v>3249275</v>
       </c>
       <c r="I190" t="n">
-        <v>19152640</v>
+        <v>3715775</v>
       </c>
       <c r="J190" t="n">
-        <v>10.15</v>
+        <v>47.2</v>
       </c>
       <c r="K190" t="n">
-        <v>7.91</v>
+        <v>39.85</v>
       </c>
       <c r="L190" t="inlineStr">
         <is>
@@ -26425,28 +26425,28 @@
         </is>
       </c>
       <c r="M190" t="n">
-        <v>1154289</v>
+        <v>-483893</v>
       </c>
       <c r="N190" t="n">
-        <v>-1690722</v>
+        <v>-744420</v>
       </c>
       <c r="O190" t="n">
-        <v>1011512</v>
+        <v>327102</v>
       </c>
       <c r="P190" t="n">
-        <v>10792354</v>
+        <v>-1228405</v>
       </c>
       <c r="Q190" t="n">
-        <v>2789000</v>
+        <v>-380294</v>
       </c>
       <c r="R190" t="n">
-        <v>-117000</v>
+        <v>-710328</v>
       </c>
       <c r="S190" t="n">
-        <v>1787100</v>
+        <v>384317</v>
       </c>
       <c r="T190" t="n">
-        <v>11877700</v>
+        <v>-662138</v>
       </c>
       <c r="U190" t="n">
         <v>0</v>
@@ -26455,22 +26455,22 @@
         <v>0</v>
       </c>
       <c r="W190" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="X190" t="n">
-        <v>0</v>
+        <v>-15000</v>
       </c>
       <c r="Y190" t="n">
-        <v>-1634711</v>
+        <v>-103599</v>
       </c>
       <c r="Z190" t="n">
-        <v>-1573722</v>
+        <v>-34092</v>
       </c>
       <c r="AA190" t="n">
-        <v>-775588</v>
+        <v>-58215</v>
       </c>
       <c r="AB190" t="n">
-        <v>-1085346</v>
+        <v>-551267</v>
       </c>
       <c r="AC190" t="n">
         <v>-6</v>
@@ -26479,10 +26479,10 @@
         <v>-6</v>
       </c>
       <c r="AE190" t="n">
-        <v>-45</v>
+        <v>-55</v>
       </c>
       <c r="AF190" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="AG190" t="n">
         <v>0</v>
@@ -26502,29 +26502,29 @@
       </c>
       <c r="AM190" t="inlineStr">
         <is>
-          <t>跌破5日線、空頭排列、量能未放大</t>
+          <t>跌破5日線、空頭排列、量能未放大、接近20日低點</t>
         </is>
       </c>
       <c r="AN190" t="inlineStr">
         <is>
-          <t>5日法人明顯買超</t>
+          <t>5日法人買超、外資投信同步買超</t>
         </is>
       </c>
       <c r="AO190" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、空頭排列、量能未放大、5日法人明顯買超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、空頭排列、量能未放大、接近20日低點、5日法人買超、外資投信同步買超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>5530.TWO</t>
+          <t>3008.TW</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>龍巖</t>
+          <t>大立光</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -26533,28 +26533,28 @@
         </is>
       </c>
       <c r="D191" t="n">
-        <v>48.3</v>
+        <v>4090</v>
       </c>
       <c r="E191" t="n">
-        <v>47.82</v>
+        <v>4027</v>
       </c>
       <c r="F191" t="n">
-        <v>48.55</v>
+        <v>4058.5</v>
       </c>
       <c r="G191" t="n">
-        <v>49.65</v>
+        <v>4119</v>
       </c>
       <c r="H191" t="n">
-        <v>394000</v>
+        <v>2213868</v>
       </c>
       <c r="I191" t="n">
-        <v>443400</v>
+        <v>1864092</v>
       </c>
       <c r="J191" t="n">
-        <v>58.3</v>
+        <v>4730</v>
       </c>
       <c r="K191" t="n">
-        <v>46.8</v>
+        <v>3795</v>
       </c>
       <c r="L191" t="inlineStr">
         <is>
@@ -26562,52 +26562,52 @@
         </is>
       </c>
       <c r="M191" t="n">
-        <v>0</v>
+        <v>44229</v>
       </c>
       <c r="N191" t="n">
-        <v>0</v>
+        <v>-109458</v>
       </c>
       <c r="O191" t="n">
-        <v>0</v>
+        <v>-434741</v>
       </c>
       <c r="P191" t="n">
-        <v>0</v>
+        <v>-1343676</v>
       </c>
       <c r="Q191" t="n">
-        <v>0</v>
+        <v>-317080</v>
       </c>
       <c r="R191" t="n">
-        <v>0</v>
+        <v>-441418</v>
       </c>
       <c r="S191" t="n">
-        <v>0</v>
+        <v>-1146068</v>
       </c>
       <c r="T191" t="n">
-        <v>0</v>
+        <v>-2731651</v>
       </c>
       <c r="U191" t="n">
-        <v>0</v>
+        <v>421000</v>
       </c>
       <c r="V191" t="n">
-        <v>0</v>
+        <v>495028</v>
       </c>
       <c r="W191" t="n">
-        <v>0</v>
+        <v>884959</v>
       </c>
       <c r="X191" t="n">
-        <v>0</v>
+        <v>1602214</v>
       </c>
       <c r="Y191" t="n">
-        <v>0</v>
+        <v>-59691</v>
       </c>
       <c r="Z191" t="n">
-        <v>0</v>
+        <v>-163068</v>
       </c>
       <c r="AA191" t="n">
-        <v>0</v>
+        <v>-173632</v>
       </c>
       <c r="AB191" t="n">
-        <v>0</v>
+        <v>-214239</v>
       </c>
       <c r="AC191" t="n">
         <v>-6</v>
@@ -26616,10 +26616,10 @@
         <v>-6</v>
       </c>
       <c r="AE191" t="n">
-        <v>-15</v>
+        <v>5</v>
       </c>
       <c r="AF191" t="n">
-        <v>0</v>
+        <v>-20</v>
       </c>
       <c r="AG191" t="n">
         <v>0</v>
@@ -26639,29 +26639,29 @@
       </c>
       <c r="AM191" t="inlineStr">
         <is>
-          <t>站上5日線、空頭排列、量能未放大、接近20日低點</t>
+          <t>站上5日線、空頭排列、量能溫和放大</t>
         </is>
       </c>
       <c r="AN191" t="inlineStr">
         <is>
-          <t>籌碼中性</t>
+          <t>5日法人賣超、投信買外資賣</t>
         </is>
       </c>
       <c r="AO191" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、空頭排列、量能未放大、接近20日低點、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、空頭排列、量能溫和放大、5日法人賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>3008.TW</t>
+          <t>9105.TW</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>大立光</t>
+          <t>泰金寶-DR</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -26670,28 +26670,28 @@
         </is>
       </c>
       <c r="D192" t="n">
-        <v>4090</v>
+        <v>8.390000000000001</v>
       </c>
       <c r="E192" t="n">
-        <v>4027</v>
+        <v>8.59</v>
       </c>
       <c r="F192" t="n">
-        <v>4058.5</v>
+        <v>8.630000000000001</v>
       </c>
       <c r="G192" t="n">
-        <v>4119</v>
+        <v>8.869999999999999</v>
       </c>
       <c r="H192" t="n">
-        <v>2213868</v>
+        <v>17499331</v>
       </c>
       <c r="I192" t="n">
-        <v>1864092</v>
+        <v>19152640</v>
       </c>
       <c r="J192" t="n">
-        <v>4730</v>
+        <v>10.15</v>
       </c>
       <c r="K192" t="n">
-        <v>3795</v>
+        <v>7.91</v>
       </c>
       <c r="L192" t="inlineStr">
         <is>
@@ -26699,52 +26699,52 @@
         </is>
       </c>
       <c r="M192" t="n">
-        <v>44229</v>
+        <v>1154289</v>
       </c>
       <c r="N192" t="n">
-        <v>-109458</v>
+        <v>-1690722</v>
       </c>
       <c r="O192" t="n">
-        <v>-434741</v>
+        <v>1011512</v>
       </c>
       <c r="P192" t="n">
-        <v>-1343676</v>
+        <v>10792354</v>
       </c>
       <c r="Q192" t="n">
-        <v>-317080</v>
+        <v>2789000</v>
       </c>
       <c r="R192" t="n">
-        <v>-441418</v>
+        <v>-117000</v>
       </c>
       <c r="S192" t="n">
-        <v>-1146068</v>
+        <v>1787100</v>
       </c>
       <c r="T192" t="n">
-        <v>-2731651</v>
+        <v>11877700</v>
       </c>
       <c r="U192" t="n">
-        <v>421000</v>
+        <v>0</v>
       </c>
       <c r="V192" t="n">
-        <v>495028</v>
+        <v>0</v>
       </c>
       <c r="W192" t="n">
-        <v>884959</v>
+        <v>0</v>
       </c>
       <c r="X192" t="n">
-        <v>1602214</v>
+        <v>0</v>
       </c>
       <c r="Y192" t="n">
-        <v>-59691</v>
+        <v>-1634711</v>
       </c>
       <c r="Z192" t="n">
-        <v>-163068</v>
+        <v>-1573722</v>
       </c>
       <c r="AA192" t="n">
-        <v>-173632</v>
+        <v>-775588</v>
       </c>
       <c r="AB192" t="n">
-        <v>-214239</v>
+        <v>-1085346</v>
       </c>
       <c r="AC192" t="n">
         <v>-6</v>
@@ -26753,10 +26753,10 @@
         <v>-6</v>
       </c>
       <c r="AE192" t="n">
-        <v>5</v>
+        <v>-45</v>
       </c>
       <c r="AF192" t="n">
-        <v>-20</v>
+        <v>30</v>
       </c>
       <c r="AG192" t="n">
         <v>0</v>
@@ -26776,17 +26776,17 @@
       </c>
       <c r="AM192" t="inlineStr">
         <is>
-          <t>站上5日線、空頭排列、量能溫和放大</t>
+          <t>跌破5日線、空頭排列、量能未放大</t>
         </is>
       </c>
       <c r="AN192" t="inlineStr">
         <is>
-          <t>5日法人賣超、投信買外資賣</t>
+          <t>5日法人明顯買超</t>
         </is>
       </c>
       <c r="AO192" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、空頭排列、量能溫和放大、5日法人賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、空頭排列、量能未放大、5日法人明顯買超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
@@ -27341,12 +27341,12 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>4147.TWO</t>
+          <t>3443.TW</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>中裕</t>
+          <t>創意</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -27355,28 +27355,28 @@
         </is>
       </c>
       <c r="D197" t="n">
-        <v>58.9</v>
+        <v>4050</v>
       </c>
       <c r="E197" t="n">
-        <v>58.68</v>
+        <v>4197</v>
       </c>
       <c r="F197" t="n">
-        <v>60.77</v>
+        <v>4089</v>
       </c>
       <c r="G197" t="n">
-        <v>64.17</v>
+        <v>4383.25</v>
       </c>
       <c r="H197" t="n">
-        <v>553000</v>
+        <v>1820157</v>
       </c>
       <c r="I197" t="n">
-        <v>848400</v>
+        <v>1798789</v>
       </c>
       <c r="J197" t="n">
-        <v>75.40000000000001</v>
+        <v>5345</v>
       </c>
       <c r="K197" t="n">
-        <v>57.8</v>
+        <v>3535</v>
       </c>
       <c r="L197" t="inlineStr">
         <is>
@@ -27384,52 +27384,52 @@
         </is>
       </c>
       <c r="M197" t="n">
-        <v>0</v>
+        <v>78042</v>
       </c>
       <c r="N197" t="n">
-        <v>0</v>
+        <v>172231</v>
       </c>
       <c r="O197" t="n">
-        <v>0</v>
+        <v>-334656</v>
       </c>
       <c r="P197" t="n">
-        <v>0</v>
+        <v>-509954</v>
       </c>
       <c r="Q197" t="n">
-        <v>0</v>
+        <v>184396</v>
       </c>
       <c r="R197" t="n">
-        <v>0</v>
+        <v>52382</v>
       </c>
       <c r="S197" t="n">
-        <v>0</v>
+        <v>-791333</v>
       </c>
       <c r="T197" t="n">
-        <v>0</v>
+        <v>-378243</v>
       </c>
       <c r="U197" t="n">
-        <v>0</v>
+        <v>-156386</v>
       </c>
       <c r="V197" t="n">
-        <v>0</v>
+        <v>-20127</v>
       </c>
       <c r="W197" t="n">
-        <v>0</v>
+        <v>348181</v>
       </c>
       <c r="X197" t="n">
-        <v>0</v>
+        <v>-106191</v>
       </c>
       <c r="Y197" t="n">
-        <v>0</v>
+        <v>50032</v>
       </c>
       <c r="Z197" t="n">
-        <v>0</v>
+        <v>139976</v>
       </c>
       <c r="AA197" t="n">
-        <v>0</v>
+        <v>108496</v>
       </c>
       <c r="AB197" t="n">
-        <v>0</v>
+        <v>-25520</v>
       </c>
       <c r="AC197" t="n">
         <v>-6</v>
@@ -27438,10 +27438,10 @@
         <v>-6</v>
       </c>
       <c r="AE197" t="n">
-        <v>-15</v>
+        <v>-10</v>
       </c>
       <c r="AF197" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="AG197" t="n">
         <v>0</v>
@@ -27461,17 +27461,17 @@
       </c>
       <c r="AM197" t="inlineStr">
         <is>
-          <t>站上5日線、空頭排列、量能未放大、接近20日低點</t>
+          <t>跌破5日線、量能溫和放大</t>
         </is>
       </c>
       <c r="AN197" t="inlineStr">
         <is>
-          <t>籌碼中性</t>
+          <t>短線籌碼止穩、5日法人賣超、投信買外資賣</t>
         </is>
       </c>
       <c r="AO197" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、空頭排列、量能未放大、接近20日低點、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、量能溫和放大、短線籌碼止穩、5日法人賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
@@ -27615,12 +27615,12 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>3443.TW</t>
+          <t>3030.TW</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>創意</t>
+          <t>德律</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -27629,28 +27629,28 @@
         </is>
       </c>
       <c r="D199" t="n">
-        <v>4050</v>
+        <v>296.5</v>
       </c>
       <c r="E199" t="n">
-        <v>4197</v>
+        <v>295.1</v>
       </c>
       <c r="F199" t="n">
-        <v>4089</v>
+        <v>295</v>
       </c>
       <c r="G199" t="n">
-        <v>4383.25</v>
+        <v>305.07</v>
       </c>
       <c r="H199" t="n">
-        <v>1820157</v>
+        <v>1198605</v>
       </c>
       <c r="I199" t="n">
-        <v>1798789</v>
+        <v>1145119</v>
       </c>
       <c r="J199" t="n">
-        <v>5345</v>
+        <v>360</v>
       </c>
       <c r="K199" t="n">
-        <v>3535</v>
+        <v>270.5</v>
       </c>
       <c r="L199" t="inlineStr">
         <is>
@@ -27658,52 +27658,52 @@
         </is>
       </c>
       <c r="M199" t="n">
-        <v>78042</v>
+        <v>-208616</v>
       </c>
       <c r="N199" t="n">
-        <v>172231</v>
+        <v>-417679</v>
       </c>
       <c r="O199" t="n">
-        <v>-334656</v>
+        <v>-347472</v>
       </c>
       <c r="P199" t="n">
-        <v>-509954</v>
+        <v>-1236685</v>
       </c>
       <c r="Q199" t="n">
-        <v>184396</v>
+        <v>-190043</v>
       </c>
       <c r="R199" t="n">
-        <v>52382</v>
+        <v>-361982</v>
       </c>
       <c r="S199" t="n">
-        <v>-791333</v>
+        <v>-323219</v>
       </c>
       <c r="T199" t="n">
-        <v>-378243</v>
+        <v>-1200263</v>
       </c>
       <c r="U199" t="n">
-        <v>-156386</v>
+        <v>0</v>
       </c>
       <c r="V199" t="n">
-        <v>-20127</v>
+        <v>2000</v>
       </c>
       <c r="W199" t="n">
-        <v>348181</v>
+        <v>4000</v>
       </c>
       <c r="X199" t="n">
-        <v>-106191</v>
+        <v>10000</v>
       </c>
       <c r="Y199" t="n">
-        <v>50032</v>
+        <v>-18573</v>
       </c>
       <c r="Z199" t="n">
-        <v>139976</v>
+        <v>-57697</v>
       </c>
       <c r="AA199" t="n">
-        <v>108496</v>
+        <v>-28253</v>
       </c>
       <c r="AB199" t="n">
-        <v>-25520</v>
+        <v>-46422</v>
       </c>
       <c r="AC199" t="n">
         <v>-6</v>
@@ -27712,10 +27712,10 @@
         <v>-6</v>
       </c>
       <c r="AE199" t="n">
-        <v>-10</v>
+        <v>30</v>
       </c>
       <c r="AF199" t="n">
-        <v>-5</v>
+        <v>-45</v>
       </c>
       <c r="AG199" t="n">
         <v>0</v>
@@ -27735,29 +27735,29 @@
       </c>
       <c r="AM199" t="inlineStr">
         <is>
-          <t>跌破5日線、量能溫和放大</t>
+          <t>站上5日線、量能溫和放大</t>
         </is>
       </c>
       <c r="AN199" t="inlineStr">
         <is>
-          <t>短線籌碼止穩、5日法人賣超、投信買外資賣</t>
+          <t>法人連續偏賣、5日法人賣超、投信買外資賣</t>
         </is>
       </c>
       <c r="AO199" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、量能溫和放大、短線籌碼止穩、5日法人賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、量能溫和放大、法人連續偏賣、5日法人賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>3030.TW</t>
+          <t>6488.TWO</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>德律</t>
+          <t>環球晶</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -27766,28 +27766,28 @@
         </is>
       </c>
       <c r="D200" t="n">
-        <v>296.5</v>
+        <v>1065</v>
       </c>
       <c r="E200" t="n">
-        <v>295.1</v>
+        <v>1132</v>
       </c>
       <c r="F200" t="n">
-        <v>295</v>
+        <v>1253</v>
       </c>
       <c r="G200" t="n">
-        <v>305.07</v>
+        <v>1231</v>
       </c>
       <c r="H200" t="n">
-        <v>1198605</v>
+        <v>5780000</v>
       </c>
       <c r="I200" t="n">
-        <v>1145119</v>
+        <v>10288200</v>
       </c>
       <c r="J200" t="n">
-        <v>360</v>
+        <v>1600</v>
       </c>
       <c r="K200" t="n">
-        <v>270.5</v>
+        <v>866</v>
       </c>
       <c r="L200" t="inlineStr">
         <is>
@@ -27795,64 +27795,64 @@
         </is>
       </c>
       <c r="M200" t="n">
-        <v>-208616</v>
+        <v>0</v>
       </c>
       <c r="N200" t="n">
-        <v>-417679</v>
+        <v>0</v>
       </c>
       <c r="O200" t="n">
-        <v>-347472</v>
+        <v>0</v>
       </c>
       <c r="P200" t="n">
-        <v>-1236685</v>
+        <v>0</v>
       </c>
       <c r="Q200" t="n">
-        <v>-190043</v>
+        <v>0</v>
       </c>
       <c r="R200" t="n">
-        <v>-361982</v>
+        <v>0</v>
       </c>
       <c r="S200" t="n">
-        <v>-323219</v>
+        <v>0</v>
       </c>
       <c r="T200" t="n">
-        <v>-1200263</v>
+        <v>0</v>
       </c>
       <c r="U200" t="n">
         <v>0</v>
       </c>
       <c r="V200" t="n">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="W200" t="n">
-        <v>4000</v>
+        <v>0</v>
       </c>
       <c r="X200" t="n">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="Y200" t="n">
-        <v>-18573</v>
+        <v>0</v>
       </c>
       <c r="Z200" t="n">
-        <v>-57697</v>
+        <v>0</v>
       </c>
       <c r="AA200" t="n">
-        <v>-28253</v>
+        <v>0</v>
       </c>
       <c r="AB200" t="n">
-        <v>-46422</v>
+        <v>0</v>
       </c>
       <c r="AC200" t="n">
-        <v>-6</v>
+        <v>-8</v>
       </c>
       <c r="AD200" t="n">
-        <v>-6</v>
+        <v>-8</v>
       </c>
       <c r="AE200" t="n">
-        <v>30</v>
+        <v>-20</v>
       </c>
       <c r="AF200" t="n">
-        <v>-45</v>
+        <v>0</v>
       </c>
       <c r="AG200" t="n">
         <v>0</v>
@@ -27872,17 +27872,17 @@
       </c>
       <c r="AM200" t="inlineStr">
         <is>
-          <t>站上5日線、量能溫和放大</t>
+          <t>跌破5日線、量能未放大</t>
         </is>
       </c>
       <c r="AN200" t="inlineStr">
         <is>
-          <t>法人連續偏賣、5日法人賣超、投信買外資賣</t>
+          <t>籌碼中性</t>
         </is>
       </c>
       <c r="AO200" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、量能溫和放大、法人連續偏賣、5日法人賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、量能未放大、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
@@ -28437,12 +28437,12 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>6488.TWO</t>
+          <t>5530.TWO</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>環球晶</t>
+          <t>龍巖</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
@@ -28451,28 +28451,28 @@
         </is>
       </c>
       <c r="D205" t="n">
-        <v>1065</v>
+        <v>48.35</v>
       </c>
       <c r="E205" t="n">
-        <v>1132</v>
+        <v>48.57</v>
       </c>
       <c r="F205" t="n">
-        <v>1253</v>
+        <v>48.36</v>
       </c>
       <c r="G205" t="n">
-        <v>1231</v>
+        <v>48.56</v>
       </c>
       <c r="H205" t="n">
-        <v>5780000</v>
+        <v>191000</v>
       </c>
       <c r="I205" t="n">
-        <v>10288200</v>
+        <v>315200</v>
       </c>
       <c r="J205" t="n">
-        <v>1600</v>
+        <v>50.4</v>
       </c>
       <c r="K205" t="n">
-        <v>866</v>
+        <v>45.95</v>
       </c>
       <c r="L205" t="inlineStr">
         <is>

--- a/output/universe_analysis_result.xlsx
+++ b/output/universe_analysis_result.xlsx
@@ -2296,10 +2296,10 @@
         <v>21.59</v>
       </c>
       <c r="H14" t="n">
-        <v>103306108</v>
+        <v>108306108</v>
       </c>
       <c r="I14" t="n">
-        <v>47084393</v>
+        <v>48084393</v>
       </c>
       <c r="J14" t="n">
         <v>23.7</v>
@@ -6406,10 +6406,10 @@
         <v>708.15</v>
       </c>
       <c r="H44" t="n">
-        <v>3742159</v>
+        <v>3774159</v>
       </c>
       <c r="I44" t="n">
-        <v>3949675</v>
+        <v>3956075</v>
       </c>
       <c r="J44" t="n">
         <v>780</v>
@@ -17640,10 +17640,10 @@
         <v>65.91</v>
       </c>
       <c r="H126" t="n">
-        <v>36045128</v>
+        <v>36615128</v>
       </c>
       <c r="I126" t="n">
-        <v>28815543</v>
+        <v>28929543</v>
       </c>
       <c r="J126" t="n">
         <v>72.3</v>
@@ -17914,10 +17914,10 @@
         <v>1074.85</v>
       </c>
       <c r="H128" t="n">
-        <v>417911</v>
+        <v>574911</v>
       </c>
       <c r="I128" t="n">
-        <v>613889</v>
+        <v>645289</v>
       </c>
       <c r="J128" t="n">
         <v>1380</v>
@@ -23120,10 +23120,10 @@
         <v>537.88</v>
       </c>
       <c r="H166" t="n">
-        <v>3343170</v>
+        <v>3455170</v>
       </c>
       <c r="I166" t="n">
-        <v>4967955</v>
+        <v>4990355</v>
       </c>
       <c r="J166" t="n">
         <v>618</v>
@@ -29148,10 +29148,10 @@
         <v>2374</v>
       </c>
       <c r="H210" t="n">
-        <v>2673586</v>
+        <v>2796586</v>
       </c>
       <c r="I210" t="n">
-        <v>2259334</v>
+        <v>2283934</v>
       </c>
       <c r="J210" t="n">
         <v>2825</v>
@@ -31477,10 +31477,10 @@
         <v>66.28</v>
       </c>
       <c r="H227" t="n">
-        <v>36667126</v>
+        <v>40111126</v>
       </c>
       <c r="I227" t="n">
-        <v>30231399</v>
+        <v>30920199</v>
       </c>
       <c r="J227" t="n">
         <v>72.2</v>
@@ -32025,10 +32025,10 @@
         <v>765.55</v>
       </c>
       <c r="H231" t="n">
-        <v>3301938</v>
+        <v>3474938</v>
       </c>
       <c r="I231" t="n">
-        <v>3843437</v>
+        <v>3878037</v>
       </c>
       <c r="J231" t="n">
         <v>862</v>
@@ -32299,10 +32299,10 @@
         <v>2019.5</v>
       </c>
       <c r="H233" t="n">
-        <v>3130014</v>
+        <v>3354014</v>
       </c>
       <c r="I233" t="n">
-        <v>2780519</v>
+        <v>2825319</v>
       </c>
       <c r="J233" t="n">
         <v>2325</v>
@@ -35313,10 +35313,10 @@
         <v>213.43</v>
       </c>
       <c r="H255" t="n">
-        <v>22260564</v>
+        <v>22352564</v>
       </c>
       <c r="I255" t="n">
-        <v>17947182</v>
+        <v>17965582</v>
       </c>
       <c r="J255" t="n">
         <v>233.5</v>
@@ -37505,10 +37505,10 @@
         <v>353.62</v>
       </c>
       <c r="H271" t="n">
-        <v>20382771</v>
+        <v>20455771</v>
       </c>
       <c r="I271" t="n">
-        <v>19949453</v>
+        <v>19964053</v>
       </c>
       <c r="J271" t="n">
         <v>393</v>
@@ -41478,10 +41478,10 @@
         <v>557.42</v>
       </c>
       <c r="H300" t="n">
-        <v>28084435</v>
+        <v>28467435</v>
       </c>
       <c r="I300" t="n">
-        <v>37934024</v>
+        <v>38010624</v>
       </c>
       <c r="J300" t="n">
         <v>659</v>
@@ -42163,10 +42163,10 @@
         <v>1866.75</v>
       </c>
       <c r="H305" t="n">
-        <v>16445645</v>
+        <v>16516645</v>
       </c>
       <c r="I305" t="n">
-        <v>10262368</v>
+        <v>10276568</v>
       </c>
       <c r="J305" t="n">
         <v>2135</v>
@@ -44355,10 +44355,10 @@
         <v>3848.5</v>
       </c>
       <c r="H321" t="n">
-        <v>11843794</v>
+        <v>11958794</v>
       </c>
       <c r="I321" t="n">
-        <v>10447896</v>
+        <v>10470896</v>
       </c>
       <c r="J321" t="n">
         <v>4380</v>
@@ -45451,10 +45451,10 @@
         <v>2409</v>
       </c>
       <c r="H329" t="n">
-        <v>44201317</v>
+        <v>45333029</v>
       </c>
       <c r="I329" t="n">
-        <v>31521181</v>
+        <v>31747524</v>
       </c>
       <c r="J329" t="n">
         <v>2505</v>
@@ -49972,10 +49972,10 @@
         <v>823.85</v>
       </c>
       <c r="H362" t="n">
-        <v>34451662</v>
+        <v>35712662</v>
       </c>
       <c r="I362" t="n">
-        <v>53619560</v>
+        <v>53871760</v>
       </c>
       <c r="J362" t="n">
         <v>1220</v>
@@ -54630,10 +54630,10 @@
         <v>2010.5</v>
       </c>
       <c r="H396" t="n">
-        <v>678164</v>
+        <v>742164</v>
       </c>
       <c r="I396" t="n">
-        <v>740434</v>
+        <v>753234</v>
       </c>
       <c r="J396" t="n">
         <v>2320</v>

--- a/output/universe_analysis_result.xlsx
+++ b/output/universe_analysis_result.xlsx
@@ -12571,10 +12571,10 @@
         <v>6313</v>
       </c>
       <c r="H89" t="n">
-        <v>1572115</v>
+        <v>1628115</v>
       </c>
       <c r="I89" t="n">
-        <v>900013</v>
+        <v>911213</v>
       </c>
       <c r="J89" t="n">
         <v>7080</v>
@@ -13393,10 +13393,10 @@
         <v>5139</v>
       </c>
       <c r="H95" t="n">
-        <v>2273686</v>
+        <v>2283686</v>
       </c>
       <c r="I95" t="n">
-        <v>2380774</v>
+        <v>2382774</v>
       </c>
       <c r="J95" t="n">
         <v>5835</v>
@@ -14489,10 +14489,10 @@
         <v>755.55</v>
       </c>
       <c r="H103" t="n">
-        <v>5833385</v>
+        <v>5860385</v>
       </c>
       <c r="I103" t="n">
-        <v>4586904</v>
+        <v>4592304</v>
       </c>
       <c r="J103" t="n">
         <v>848</v>
@@ -18188,10 +18188,10 @@
         <v>491.57</v>
       </c>
       <c r="H130" t="n">
-        <v>6127777</v>
+        <v>6257777</v>
       </c>
       <c r="I130" t="n">
-        <v>4957762</v>
+        <v>4983762</v>
       </c>
       <c r="J130" t="n">
         <v>645</v>
@@ -21476,10 +21476,10 @@
         <v>4188.5</v>
       </c>
       <c r="H154" t="n">
-        <v>2922508</v>
+        <v>3078508</v>
       </c>
       <c r="I154" t="n">
-        <v>2288885</v>
+        <v>2320085</v>
       </c>
       <c r="J154" t="n">
         <v>5345</v>
@@ -22709,10 +22709,10 @@
         <v>143.62</v>
       </c>
       <c r="H163" t="n">
-        <v>376078814</v>
+        <v>376328814</v>
       </c>
       <c r="I163" t="n">
-        <v>234353666</v>
+        <v>234403666</v>
       </c>
       <c r="J163" t="n">
         <v>171.5</v>
@@ -25723,10 +25723,10 @@
         <v>534.8</v>
       </c>
       <c r="H185" t="n">
-        <v>63762972</v>
+        <v>64944972</v>
       </c>
       <c r="I185" t="n">
-        <v>40701125</v>
+        <v>40937525</v>
       </c>
       <c r="J185" t="n">
         <v>656</v>
@@ -28711,12 +28711,12 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>2355.TW</t>
+          <t>2342.TW</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>敬鵬</t>
+          <t>茂矽</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
@@ -28725,28 +28725,28 @@
         </is>
       </c>
       <c r="D207" t="n">
-        <v>34.5</v>
+        <v>29.95</v>
       </c>
       <c r="E207" t="n">
-        <v>38.06</v>
+        <v>34.82</v>
       </c>
       <c r="F207" t="n">
-        <v>40.49</v>
+        <v>38.18</v>
       </c>
       <c r="G207" t="n">
-        <v>45.37</v>
+        <v>45.16</v>
       </c>
       <c r="H207" t="n">
-        <v>4524096</v>
+        <v>2804247</v>
       </c>
       <c r="I207" t="n">
-        <v>4500855</v>
+        <v>2707135</v>
       </c>
       <c r="J207" t="n">
-        <v>54.2</v>
+        <v>60.7</v>
       </c>
       <c r="K207" t="n">
-        <v>34.3</v>
+        <v>29.45</v>
       </c>
       <c r="L207" t="inlineStr">
         <is>
@@ -28754,28 +28754,28 @@
         </is>
       </c>
       <c r="M207" t="n">
-        <v>-739598</v>
+        <v>-308600</v>
       </c>
       <c r="N207" t="n">
-        <v>382201</v>
+        <v>555367</v>
       </c>
       <c r="O207" t="n">
-        <v>480952</v>
+        <v>286817</v>
       </c>
       <c r="P207" t="n">
-        <v>1323629</v>
+        <v>153061</v>
       </c>
       <c r="Q207" t="n">
-        <v>-671972</v>
+        <v>-246241</v>
       </c>
       <c r="R207" t="n">
-        <v>693513</v>
+        <v>551466</v>
       </c>
       <c r="S207" t="n">
-        <v>877386</v>
+        <v>281710</v>
       </c>
       <c r="T207" t="n">
-        <v>2724481</v>
+        <v>124495</v>
       </c>
       <c r="U207" t="n">
         <v>0</v>
@@ -28787,19 +28787,19 @@
         <v>0</v>
       </c>
       <c r="X207" t="n">
-        <v>-578000</v>
+        <v>0</v>
       </c>
       <c r="Y207" t="n">
-        <v>-67626</v>
+        <v>-62359</v>
       </c>
       <c r="Z207" t="n">
-        <v>-311312</v>
+        <v>3901</v>
       </c>
       <c r="AA207" t="n">
-        <v>-396434</v>
+        <v>5107</v>
       </c>
       <c r="AB207" t="n">
-        <v>-822852</v>
+        <v>28566</v>
       </c>
       <c r="AC207" t="n">
         <v>-10</v>
@@ -28985,12 +28985,12 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>2342.TW</t>
+          <t>2355.TW</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>茂矽</t>
+          <t>敬鵬</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
@@ -28999,28 +28999,28 @@
         </is>
       </c>
       <c r="D209" t="n">
-        <v>29.95</v>
+        <v>34.5</v>
       </c>
       <c r="E209" t="n">
-        <v>34.82</v>
+        <v>38.06</v>
       </c>
       <c r="F209" t="n">
-        <v>38.18</v>
+        <v>40.49</v>
       </c>
       <c r="G209" t="n">
-        <v>45.16</v>
+        <v>45.37</v>
       </c>
       <c r="H209" t="n">
-        <v>2804247</v>
+        <v>4524096</v>
       </c>
       <c r="I209" t="n">
-        <v>2707135</v>
+        <v>4500855</v>
       </c>
       <c r="J209" t="n">
-        <v>60.7</v>
+        <v>54.2</v>
       </c>
       <c r="K209" t="n">
-        <v>29.45</v>
+        <v>34.3</v>
       </c>
       <c r="L209" t="inlineStr">
         <is>
@@ -29028,28 +29028,28 @@
         </is>
       </c>
       <c r="M209" t="n">
-        <v>-308600</v>
+        <v>-739598</v>
       </c>
       <c r="N209" t="n">
-        <v>555367</v>
+        <v>382201</v>
       </c>
       <c r="O209" t="n">
-        <v>286817</v>
+        <v>480952</v>
       </c>
       <c r="P209" t="n">
-        <v>153061</v>
+        <v>1323629</v>
       </c>
       <c r="Q209" t="n">
-        <v>-246241</v>
+        <v>-671972</v>
       </c>
       <c r="R209" t="n">
-        <v>551466</v>
+        <v>693513</v>
       </c>
       <c r="S209" t="n">
-        <v>281710</v>
+        <v>877386</v>
       </c>
       <c r="T209" t="n">
-        <v>124495</v>
+        <v>2724481</v>
       </c>
       <c r="U209" t="n">
         <v>0</v>
@@ -29061,19 +29061,19 @@
         <v>0</v>
       </c>
       <c r="X209" t="n">
-        <v>0</v>
+        <v>-578000</v>
       </c>
       <c r="Y209" t="n">
-        <v>-62359</v>
+        <v>-67626</v>
       </c>
       <c r="Z209" t="n">
-        <v>3901</v>
+        <v>-311312</v>
       </c>
       <c r="AA209" t="n">
-        <v>5107</v>
+        <v>-396434</v>
       </c>
       <c r="AB209" t="n">
-        <v>28566</v>
+        <v>-822852</v>
       </c>
       <c r="AC209" t="n">
         <v>-10</v>
@@ -29122,12 +29122,12 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>4903.TWO</t>
+          <t>3036.TW</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>聯光通</t>
+          <t>文曄</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
@@ -29136,28 +29136,28 @@
         </is>
       </c>
       <c r="D210" t="n">
-        <v>32.05</v>
+        <v>183.5</v>
       </c>
       <c r="E210" t="n">
-        <v>36.61</v>
+        <v>193.5</v>
       </c>
       <c r="F210" t="n">
-        <v>35.94</v>
+        <v>194.4</v>
       </c>
       <c r="G210" t="n">
-        <v>37.78</v>
+        <v>202.43</v>
       </c>
       <c r="H210" t="n">
-        <v>1426000</v>
+        <v>10202197</v>
       </c>
       <c r="I210" t="n">
-        <v>3622200</v>
+        <v>8521179</v>
       </c>
       <c r="J210" t="n">
-        <v>42.55</v>
+        <v>223.5</v>
       </c>
       <c r="K210" t="n">
-        <v>31.8</v>
+        <v>180</v>
       </c>
       <c r="L210" t="inlineStr">
         <is>
@@ -29165,64 +29165,64 @@
         </is>
       </c>
       <c r="M210" t="n">
-        <v>0</v>
+        <v>-1032305</v>
       </c>
       <c r="N210" t="n">
-        <v>0</v>
+        <v>419316</v>
       </c>
       <c r="O210" t="n">
-        <v>0</v>
+        <v>256443</v>
       </c>
       <c r="P210" t="n">
-        <v>0</v>
+        <v>-827509</v>
       </c>
       <c r="Q210" t="n">
-        <v>0</v>
+        <v>-1039233</v>
       </c>
       <c r="R210" t="n">
-        <v>0</v>
+        <v>-8161</v>
       </c>
       <c r="S210" t="n">
-        <v>0</v>
+        <v>-40702</v>
       </c>
       <c r="T210" t="n">
-        <v>0</v>
+        <v>4079479</v>
       </c>
       <c r="U210" t="n">
-        <v>0</v>
+        <v>3245</v>
       </c>
       <c r="V210" t="n">
-        <v>0</v>
+        <v>181089</v>
       </c>
       <c r="W210" t="n">
-        <v>0</v>
+        <v>395971</v>
       </c>
       <c r="X210" t="n">
-        <v>0</v>
+        <v>-5251094</v>
       </c>
       <c r="Y210" t="n">
-        <v>0</v>
+        <v>3683</v>
       </c>
       <c r="Z210" t="n">
-        <v>0</v>
+        <v>246388</v>
       </c>
       <c r="AA210" t="n">
-        <v>0</v>
+        <v>-98826</v>
       </c>
       <c r="AB210" t="n">
-        <v>0</v>
+        <v>344106</v>
       </c>
       <c r="AC210" t="n">
-        <v>-12</v>
+        <v>-10</v>
       </c>
       <c r="AD210" t="n">
-        <v>-12</v>
+        <v>-10</v>
       </c>
       <c r="AE210" t="n">
-        <v>-30</v>
+        <v>-45</v>
       </c>
       <c r="AF210" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AG210" t="n">
         <v>0</v>
@@ -29242,29 +29242,29 @@
       </c>
       <c r="AM210" t="inlineStr">
         <is>
-          <t>跌破5日線、量能未放大、接近20日低點</t>
+          <t>跌破5日線、空頭排列、量能溫和放大、接近20日低點</t>
         </is>
       </c>
       <c r="AN210" t="inlineStr">
         <is>
-          <t>籌碼中性</t>
+          <t>5日法人買超、投信買外資賣</t>
         </is>
       </c>
       <c r="AO210" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、量能未放大、接近20日低點、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、空頭排列、量能溫和放大、接近20日低點、5日法人買超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>3057.TW</t>
+          <t>5347.TWO</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>喬鼎</t>
+          <t>世界</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
@@ -29273,28 +29273,28 @@
         </is>
       </c>
       <c r="D211" t="n">
-        <v>13.5</v>
+        <v>138</v>
       </c>
       <c r="E211" t="n">
-        <v>14.69</v>
+        <v>146.5</v>
       </c>
       <c r="F211" t="n">
-        <v>15.36</v>
+        <v>154.9</v>
       </c>
       <c r="G211" t="n">
-        <v>16.79</v>
+        <v>168.82</v>
       </c>
       <c r="H211" t="n">
-        <v>261848</v>
+        <v>39010000</v>
       </c>
       <c r="I211" t="n">
-        <v>191918</v>
+        <v>23499800</v>
       </c>
       <c r="J211" t="n">
-        <v>20.1</v>
+        <v>201.5</v>
       </c>
       <c r="K211" t="n">
-        <v>13.2</v>
+        <v>131</v>
       </c>
       <c r="L211" t="inlineStr">
         <is>
@@ -29302,28 +29302,28 @@
         </is>
       </c>
       <c r="M211" t="n">
-        <v>-11000</v>
+        <v>0</v>
       </c>
       <c r="N211" t="n">
-        <v>10100</v>
+        <v>0</v>
       </c>
       <c r="O211" t="n">
-        <v>-23900</v>
+        <v>0</v>
       </c>
       <c r="P211" t="n">
-        <v>-37900</v>
+        <v>0</v>
       </c>
       <c r="Q211" t="n">
-        <v>-10000</v>
+        <v>0</v>
       </c>
       <c r="R211" t="n">
-        <v>9100</v>
+        <v>0</v>
       </c>
       <c r="S211" t="n">
-        <v>-24900</v>
+        <v>0</v>
       </c>
       <c r="T211" t="n">
-        <v>-35900</v>
+        <v>0</v>
       </c>
       <c r="U211" t="n">
         <v>0</v>
@@ -29338,16 +29338,16 @@
         <v>0</v>
       </c>
       <c r="Y211" t="n">
-        <v>-1000</v>
+        <v>0</v>
       </c>
       <c r="Z211" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AA211" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AB211" t="n">
-        <v>-2000</v>
+        <v>0</v>
       </c>
       <c r="AC211" t="n">
         <v>-12</v>
@@ -29356,10 +29356,10 @@
         <v>-12</v>
       </c>
       <c r="AE211" t="n">
-        <v>-45</v>
+        <v>-30</v>
       </c>
       <c r="AF211" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="AG211" t="n">
         <v>0</v>
@@ -29379,17 +29379,17 @@
       </c>
       <c r="AM211" t="inlineStr">
         <is>
-          <t>跌破5日線、空頭排列、量能溫和放大、接近20日低點</t>
+          <t>跌破5日線、空頭排列、成交量放大</t>
         </is>
       </c>
       <c r="AN211" t="inlineStr">
         <is>
-          <t>短線籌碼止穩</t>
+          <t>籌碼中性</t>
         </is>
       </c>
       <c r="AO211" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、空頭排列、量能溫和放大、接近20日低點、短線籌碼止穩。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、空頭排列、成交量放大、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
@@ -29670,12 +29670,12 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>5347.TWO</t>
+          <t>4903.TWO</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>世界</t>
+          <t>聯光通</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
@@ -29684,28 +29684,28 @@
         </is>
       </c>
       <c r="D214" t="n">
-        <v>138</v>
+        <v>32.05</v>
       </c>
       <c r="E214" t="n">
-        <v>146.5</v>
+        <v>36.61</v>
       </c>
       <c r="F214" t="n">
-        <v>154.9</v>
+        <v>35.94</v>
       </c>
       <c r="G214" t="n">
-        <v>168.82</v>
+        <v>37.78</v>
       </c>
       <c r="H214" t="n">
-        <v>39010000</v>
+        <v>1426000</v>
       </c>
       <c r="I214" t="n">
-        <v>23499800</v>
+        <v>3622200</v>
       </c>
       <c r="J214" t="n">
-        <v>201.5</v>
+        <v>42.55</v>
       </c>
       <c r="K214" t="n">
-        <v>131</v>
+        <v>31.8</v>
       </c>
       <c r="L214" t="inlineStr">
         <is>
@@ -29790,7 +29790,7 @@
       </c>
       <c r="AM214" t="inlineStr">
         <is>
-          <t>跌破5日線、空頭排列、成交量放大</t>
+          <t>跌破5日線、量能未放大、接近20日低點</t>
         </is>
       </c>
       <c r="AN214" t="inlineStr">
@@ -29800,19 +29800,19 @@
       </c>
       <c r="AO214" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、空頭排列、成交量放大、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、量能未放大、接近20日低點、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>3529.TWO</t>
+          <t>3057.TW</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>力旺</t>
+          <t>喬鼎</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
@@ -29821,28 +29821,28 @@
         </is>
       </c>
       <c r="D215" t="n">
-        <v>2290</v>
+        <v>13.5</v>
       </c>
       <c r="E215" t="n">
-        <v>2295</v>
+        <v>14.69</v>
       </c>
       <c r="F215" t="n">
-        <v>2359.5</v>
+        <v>15.36</v>
       </c>
       <c r="G215" t="n">
-        <v>2509.75</v>
+        <v>16.79</v>
       </c>
       <c r="H215" t="n">
-        <v>1004000</v>
+        <v>261848</v>
       </c>
       <c r="I215" t="n">
-        <v>755400</v>
+        <v>191918</v>
       </c>
       <c r="J215" t="n">
-        <v>3085</v>
+        <v>20.1</v>
       </c>
       <c r="K215" t="n">
-        <v>1995</v>
+        <v>13.2</v>
       </c>
       <c r="L215" t="inlineStr">
         <is>
@@ -29850,28 +29850,28 @@
         </is>
       </c>
       <c r="M215" t="n">
-        <v>0</v>
+        <v>-11000</v>
       </c>
       <c r="N215" t="n">
-        <v>0</v>
+        <v>10100</v>
       </c>
       <c r="O215" t="n">
-        <v>0</v>
+        <v>-23900</v>
       </c>
       <c r="P215" t="n">
-        <v>0</v>
+        <v>-37900</v>
       </c>
       <c r="Q215" t="n">
-        <v>0</v>
+        <v>-10000</v>
       </c>
       <c r="R215" t="n">
-        <v>0</v>
+        <v>9100</v>
       </c>
       <c r="S215" t="n">
-        <v>0</v>
+        <v>-24900</v>
       </c>
       <c r="T215" t="n">
-        <v>0</v>
+        <v>-35900</v>
       </c>
       <c r="U215" t="n">
         <v>0</v>
@@ -29886,28 +29886,28 @@
         <v>0</v>
       </c>
       <c r="Y215" t="n">
-        <v>0</v>
+        <v>-1000</v>
       </c>
       <c r="Z215" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA215" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB215" t="n">
-        <v>0</v>
+        <v>-2000</v>
       </c>
       <c r="AC215" t="n">
-        <v>-14</v>
+        <v>-12</v>
       </c>
       <c r="AD215" t="n">
-        <v>-14</v>
+        <v>-12</v>
       </c>
       <c r="AE215" t="n">
-        <v>-35</v>
+        <v>-45</v>
       </c>
       <c r="AF215" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AG215" t="n">
         <v>0</v>
@@ -29927,29 +29927,29 @@
       </c>
       <c r="AM215" t="inlineStr">
         <is>
-          <t>跌破5日線、空頭排列、量能溫和放大</t>
+          <t>跌破5日線、空頭排列、量能溫和放大、接近20日低點</t>
         </is>
       </c>
       <c r="AN215" t="inlineStr">
         <is>
-          <t>籌碼中性</t>
+          <t>短線籌碼止穩</t>
         </is>
       </c>
       <c r="AO215" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、空頭排列、量能溫和放大、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、空頭排列、量能溫和放大、接近20日低點、短線籌碼止穩。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>1789.TW</t>
+          <t>3529.TWO</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>神隆</t>
+          <t>力旺</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
@@ -29958,28 +29958,28 @@
         </is>
       </c>
       <c r="D216" t="n">
-        <v>19.1</v>
+        <v>2290</v>
       </c>
       <c r="E216" t="n">
-        <v>19.41</v>
+        <v>2295</v>
       </c>
       <c r="F216" t="n">
-        <v>19.65</v>
+        <v>2359.5</v>
       </c>
       <c r="G216" t="n">
-        <v>20.12</v>
+        <v>2509.75</v>
       </c>
       <c r="H216" t="n">
-        <v>611772</v>
+        <v>1004000</v>
       </c>
       <c r="I216" t="n">
-        <v>712048</v>
+        <v>755400</v>
       </c>
       <c r="J216" t="n">
-        <v>21.35</v>
+        <v>3085</v>
       </c>
       <c r="K216" t="n">
-        <v>19</v>
+        <v>1995</v>
       </c>
       <c r="L216" t="inlineStr">
         <is>
@@ -29987,28 +29987,28 @@
         </is>
       </c>
       <c r="M216" t="n">
-        <v>-39520</v>
+        <v>0</v>
       </c>
       <c r="N216" t="n">
-        <v>255036</v>
+        <v>0</v>
       </c>
       <c r="O216" t="n">
-        <v>193582</v>
+        <v>0</v>
       </c>
       <c r="P216" t="n">
-        <v>-121118</v>
+        <v>0</v>
       </c>
       <c r="Q216" t="n">
-        <v>-11520</v>
+        <v>0</v>
       </c>
       <c r="R216" t="n">
-        <v>247864</v>
+        <v>0</v>
       </c>
       <c r="S216" t="n">
-        <v>174864</v>
+        <v>0</v>
       </c>
       <c r="T216" t="n">
-        <v>-103704</v>
+        <v>0</v>
       </c>
       <c r="U216" t="n">
         <v>0</v>
@@ -30023,16 +30023,16 @@
         <v>0</v>
       </c>
       <c r="Y216" t="n">
-        <v>-28000</v>
+        <v>0</v>
       </c>
       <c r="Z216" t="n">
-        <v>7172</v>
+        <v>0</v>
       </c>
       <c r="AA216" t="n">
-        <v>18718</v>
+        <v>0</v>
       </c>
       <c r="AB216" t="n">
-        <v>-17414</v>
+        <v>0</v>
       </c>
       <c r="AC216" t="n">
         <v>-14</v>
@@ -30041,10 +30041,10 @@
         <v>-14</v>
       </c>
       <c r="AE216" t="n">
-        <v>-55</v>
+        <v>-35</v>
       </c>
       <c r="AF216" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AG216" t="n">
         <v>0</v>
@@ -30064,29 +30064,29 @@
       </c>
       <c r="AM216" t="inlineStr">
         <is>
-          <t>跌破5日線、空頭排列、量能未放大、接近20日低點</t>
+          <t>跌破5日線、空頭排列、量能溫和放大</t>
         </is>
       </c>
       <c r="AN216" t="inlineStr">
         <is>
-          <t>5日法人買超</t>
+          <t>籌碼中性</t>
         </is>
       </c>
       <c r="AO216" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、空頭排列、量能未放大、接近20日低點、5日法人買超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、空頭排列、量能溫和放大、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>3059.TW</t>
+          <t>1789.TW</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>華晶科</t>
+          <t>神隆</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
@@ -30095,28 +30095,28 @@
         </is>
       </c>
       <c r="D217" t="n">
-        <v>36.25</v>
+        <v>19.1</v>
       </c>
       <c r="E217" t="n">
-        <v>38.49</v>
+        <v>19.41</v>
       </c>
       <c r="F217" t="n">
-        <v>39.8</v>
+        <v>19.65</v>
       </c>
       <c r="G217" t="n">
-        <v>43.43</v>
+        <v>20.12</v>
       </c>
       <c r="H217" t="n">
-        <v>2076444</v>
+        <v>611772</v>
       </c>
       <c r="I217" t="n">
-        <v>2184949</v>
+        <v>712048</v>
       </c>
       <c r="J217" t="n">
-        <v>52.8</v>
+        <v>21.35</v>
       </c>
       <c r="K217" t="n">
-        <v>36.15</v>
+        <v>19</v>
       </c>
       <c r="L217" t="inlineStr">
         <is>
@@ -30124,28 +30124,28 @@
         </is>
       </c>
       <c r="M217" t="n">
-        <v>-63289</v>
+        <v>-39520</v>
       </c>
       <c r="N217" t="n">
-        <v>334491</v>
+        <v>255036</v>
       </c>
       <c r="O217" t="n">
-        <v>413124</v>
+        <v>193582</v>
       </c>
       <c r="P217" t="n">
-        <v>1209608</v>
+        <v>-121118</v>
       </c>
       <c r="Q217" t="n">
-        <v>-24056</v>
+        <v>-11520</v>
       </c>
       <c r="R217" t="n">
-        <v>501958</v>
+        <v>247864</v>
       </c>
       <c r="S217" t="n">
-        <v>622534</v>
+        <v>174864</v>
       </c>
       <c r="T217" t="n">
-        <v>1809362</v>
+        <v>-103704</v>
       </c>
       <c r="U217" t="n">
         <v>0</v>
@@ -30160,16 +30160,16 @@
         <v>0</v>
       </c>
       <c r="Y217" t="n">
-        <v>-39233</v>
+        <v>-28000</v>
       </c>
       <c r="Z217" t="n">
-        <v>-167467</v>
+        <v>7172</v>
       </c>
       <c r="AA217" t="n">
-        <v>-209410</v>
+        <v>18718</v>
       </c>
       <c r="AB217" t="n">
-        <v>-599754</v>
+        <v>-17414</v>
       </c>
       <c r="AC217" t="n">
         <v>-14</v>
@@ -30355,12 +30355,12 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>3036.TW</t>
+          <t>3059.TW</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>文曄</t>
+          <t>華晶科</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
@@ -30369,28 +30369,28 @@
         </is>
       </c>
       <c r="D219" t="n">
-        <v>183.5</v>
+        <v>36.25</v>
       </c>
       <c r="E219" t="n">
-        <v>193.5</v>
+        <v>38.49</v>
       </c>
       <c r="F219" t="n">
-        <v>194.4</v>
+        <v>39.8</v>
       </c>
       <c r="G219" t="n">
-        <v>202.43</v>
+        <v>43.43</v>
       </c>
       <c r="H219" t="n">
-        <v>5523197</v>
+        <v>2076444</v>
       </c>
       <c r="I219" t="n">
-        <v>7585379</v>
+        <v>2184949</v>
       </c>
       <c r="J219" t="n">
-        <v>223.5</v>
+        <v>52.8</v>
       </c>
       <c r="K219" t="n">
-        <v>180</v>
+        <v>36.15</v>
       </c>
       <c r="L219" t="inlineStr">
         <is>
@@ -30398,52 +30398,52 @@
         </is>
       </c>
       <c r="M219" t="n">
-        <v>-1032305</v>
+        <v>-63289</v>
       </c>
       <c r="N219" t="n">
-        <v>419316</v>
+        <v>334491</v>
       </c>
       <c r="O219" t="n">
-        <v>256443</v>
+        <v>413124</v>
       </c>
       <c r="P219" t="n">
-        <v>-827509</v>
+        <v>1209608</v>
       </c>
       <c r="Q219" t="n">
-        <v>-1039233</v>
+        <v>-24056</v>
       </c>
       <c r="R219" t="n">
-        <v>-8161</v>
+        <v>501958</v>
       </c>
       <c r="S219" t="n">
-        <v>-40702</v>
+        <v>622534</v>
       </c>
       <c r="T219" t="n">
-        <v>4079479</v>
+        <v>1809362</v>
       </c>
       <c r="U219" t="n">
-        <v>3245</v>
+        <v>0</v>
       </c>
       <c r="V219" t="n">
-        <v>181089</v>
+        <v>0</v>
       </c>
       <c r="W219" t="n">
-        <v>395971</v>
+        <v>0</v>
       </c>
       <c r="X219" t="n">
-        <v>-5251094</v>
+        <v>0</v>
       </c>
       <c r="Y219" t="n">
-        <v>3683</v>
+        <v>-39233</v>
       </c>
       <c r="Z219" t="n">
-        <v>246388</v>
+        <v>-167467</v>
       </c>
       <c r="AA219" t="n">
-        <v>-98826</v>
+        <v>-209410</v>
       </c>
       <c r="AB219" t="n">
-        <v>344106</v>
+        <v>-599754</v>
       </c>
       <c r="AC219" t="n">
         <v>-14</v>
@@ -30480,12 +30480,12 @@
       </c>
       <c r="AN219" t="inlineStr">
         <is>
-          <t>5日法人買超、投信買外資賣</t>
+          <t>5日法人買超</t>
         </is>
       </c>
       <c r="AO219" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、空頭排列、量能未放大、接近20日低點、5日法人買超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、空頭排列、量能未放大、接近20日低點、5日法人買超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
@@ -37642,10 +37642,10 @@
         <v>290.2</v>
       </c>
       <c r="H272" t="n">
-        <v>37702844</v>
+        <v>37892844</v>
       </c>
       <c r="I272" t="n">
-        <v>23556800</v>
+        <v>23594800</v>
       </c>
       <c r="J272" t="n">
         <v>367.5</v>
@@ -40656,10 +40656,10 @@
         <v>4977</v>
       </c>
       <c r="H294" t="n">
-        <v>5227758</v>
+        <v>5459758</v>
       </c>
       <c r="I294" t="n">
-        <v>2904540</v>
+        <v>2950940</v>
       </c>
       <c r="J294" t="n">
         <v>6250</v>
@@ -41752,10 +41752,10 @@
         <v>162.72</v>
       </c>
       <c r="H302" t="n">
-        <v>208317971</v>
+        <v>211417971</v>
       </c>
       <c r="I302" t="n">
-        <v>121866744</v>
+        <v>122486744</v>
       </c>
       <c r="J302" t="n">
         <v>200</v>
@@ -43396,10 +43396,10 @@
         <v>241.03</v>
       </c>
       <c r="H314" t="n">
-        <v>77049664</v>
+        <v>77132664</v>
       </c>
       <c r="I314" t="n">
-        <v>56890068</v>
+        <v>56906668</v>
       </c>
       <c r="J314" t="n">
         <v>259.5</v>
@@ -43807,10 +43807,10 @@
         <v>2383.5</v>
       </c>
       <c r="H317" t="n">
-        <v>47256177</v>
+        <v>51372177</v>
       </c>
       <c r="I317" t="n">
-        <v>42895774</v>
+        <v>43718974</v>
       </c>
       <c r="J317" t="n">
         <v>2500</v>
@@ -45314,10 +45314,10 @@
         <v>346.05</v>
       </c>
       <c r="H328" t="n">
-        <v>58851779</v>
+        <v>60476779</v>
       </c>
       <c r="I328" t="n">
-        <v>27798410</v>
+        <v>28123410</v>
       </c>
       <c r="J328" t="n">
         <v>393</v>
@@ -47232,10 +47232,10 @@
         <v>740.75</v>
       </c>
       <c r="H342" t="n">
-        <v>30070261</v>
+        <v>30600261</v>
       </c>
       <c r="I342" t="n">
-        <v>18187111</v>
+        <v>18293111</v>
       </c>
       <c r="J342" t="n">
         <v>859</v>
@@ -48054,10 +48054,10 @@
         <v>632.25</v>
       </c>
       <c r="H348" t="n">
-        <v>30767999</v>
+        <v>31004999</v>
       </c>
       <c r="I348" t="n">
-        <v>23364877</v>
+        <v>23412277</v>
       </c>
       <c r="J348" t="n">
         <v>729</v>
@@ -50520,10 +50520,10 @@
         <v>1985.25</v>
       </c>
       <c r="H366" t="n">
-        <v>5130465</v>
+        <v>5148465</v>
       </c>
       <c r="I366" t="n">
-        <v>3319786</v>
+        <v>3323386</v>
       </c>
       <c r="J366" t="n">
         <v>2300</v>
@@ -51205,10 +51205,10 @@
         <v>3738.75</v>
       </c>
       <c r="H371" t="n">
-        <v>14088689</v>
+        <v>14125689</v>
       </c>
       <c r="I371" t="n">
-        <v>12067198</v>
+        <v>12074598</v>
       </c>
       <c r="J371" t="n">
         <v>4380</v>

--- a/output/universe_analysis_result.xlsx
+++ b/output/universe_analysis_result.xlsx
@@ -926,10 +926,10 @@
         <v>71.11</v>
       </c>
       <c r="H4" t="n">
-        <v>8057548</v>
+        <v>11141548</v>
       </c>
       <c r="I4" t="n">
-        <v>3781271</v>
+        <v>4398071</v>
       </c>
       <c r="J4" t="n">
         <v>74.8</v>
@@ -1611,10 +1611,10 @@
         <v>34.14</v>
       </c>
       <c r="H9" t="n">
-        <v>60735905</v>
+        <v>65838905</v>
       </c>
       <c r="I9" t="n">
-        <v>51036183</v>
+        <v>52056783</v>
       </c>
       <c r="J9" t="n">
         <v>36.9</v>
@@ -2022,10 +2022,10 @@
         <v>125.42</v>
       </c>
       <c r="H12" t="n">
-        <v>32837894</v>
+        <v>32956894</v>
       </c>
       <c r="I12" t="n">
-        <v>24828665</v>
+        <v>24852465</v>
       </c>
       <c r="J12" t="n">
         <v>131</v>
@@ -2981,10 +2981,10 @@
         <v>87.83</v>
       </c>
       <c r="H19" t="n">
-        <v>11836095</v>
+        <v>12415095</v>
       </c>
       <c r="I19" t="n">
-        <v>4837219</v>
+        <v>4953019</v>
       </c>
       <c r="J19" t="n">
         <v>98.3</v>
@@ -3229,12 +3229,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>1907.TW</t>
+          <t>2618.TW</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>永豐餘</t>
+          <t>長榮航</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -3243,28 +3243,28 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>29.05</v>
+        <v>43.3</v>
       </c>
       <c r="E21" t="n">
-        <v>28.54</v>
+        <v>42.24</v>
       </c>
       <c r="F21" t="n">
-        <v>28.29</v>
+        <v>41.84</v>
       </c>
       <c r="G21" t="n">
-        <v>28.2</v>
+        <v>41.72</v>
       </c>
       <c r="H21" t="n">
-        <v>4385328</v>
+        <v>70267465</v>
       </c>
       <c r="I21" t="n">
-        <v>2575244</v>
+        <v>58285117</v>
       </c>
       <c r="J21" t="n">
-        <v>29.7</v>
+        <v>44.3</v>
       </c>
       <c r="K21" t="n">
-        <v>26.9</v>
+        <v>38.75</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
@@ -3272,52 +3272,52 @@
         </is>
       </c>
       <c r="M21" t="n">
-        <v>583256</v>
+        <v>42747309</v>
       </c>
       <c r="N21" t="n">
-        <v>3441822</v>
+        <v>84557583</v>
       </c>
       <c r="O21" t="n">
-        <v>4561789</v>
+        <v>141645747</v>
       </c>
       <c r="P21" t="n">
-        <v>4272437</v>
+        <v>192565620</v>
       </c>
       <c r="Q21" t="n">
-        <v>531256</v>
+        <v>40012546</v>
       </c>
       <c r="R21" t="n">
-        <v>3354742</v>
+        <v>83558902</v>
       </c>
       <c r="S21" t="n">
-        <v>4412709</v>
+        <v>136949595</v>
       </c>
       <c r="T21" t="n">
-        <v>4151350</v>
+        <v>203348182</v>
       </c>
       <c r="U21" t="n">
-        <v>6000</v>
+        <v>458000</v>
       </c>
       <c r="V21" t="n">
-        <v>33080</v>
+        <v>-2448323</v>
       </c>
       <c r="W21" t="n">
-        <v>35080</v>
+        <v>-374278</v>
       </c>
       <c r="X21" t="n">
-        <v>52087</v>
+        <v>-16190664</v>
       </c>
       <c r="Y21" t="n">
-        <v>46000</v>
+        <v>2276763</v>
       </c>
       <c r="Z21" t="n">
-        <v>54000</v>
+        <v>3447004</v>
       </c>
       <c r="AA21" t="n">
-        <v>114000</v>
+        <v>5070430</v>
       </c>
       <c r="AB21" t="n">
-        <v>69000</v>
+        <v>5408102</v>
       </c>
       <c r="AC21" t="n">
         <v>56</v>
@@ -3326,10 +3326,10 @@
         <v>56</v>
       </c>
       <c r="AE21" t="n">
+        <v>80</v>
+      </c>
+      <c r="AF21" t="n">
         <v>60</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>80</v>
       </c>
       <c r="AG21" t="n">
         <v>0</v>
@@ -3349,29 +3349,29 @@
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、成交量放大</t>
+          <t>站上5日線、多頭排列、黃金交叉、量能溫和放大</t>
         </is>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>法人連續偏買、5日法人明顯買超、外資投信同步買超</t>
+          <t>法人連續偏買、5日法人明顯買超、外資買投信賣</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>偏多觀察：站上5日線、多頭排列、成交量放大、法人連續偏買、5日法人明顯買超、外資投信同步買超。條件不差，適合等待拉回或突破確認。</t>
+          <t>偏多觀察：站上5日線、多頭排列、黃金交叉、量能溫和放大、法人連續偏買、5日法人明顯買超、外資買投信賣。條件不差，適合等待拉回或突破確認。</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2618.TW</t>
+          <t>1907.TW</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>長榮航</t>
+          <t>永豐餘</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -3380,28 +3380,28 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>43.3</v>
+        <v>29.05</v>
       </c>
       <c r="E22" t="n">
-        <v>42.24</v>
+        <v>28.54</v>
       </c>
       <c r="F22" t="n">
-        <v>41.84</v>
+        <v>28.29</v>
       </c>
       <c r="G22" t="n">
-        <v>41.72</v>
+        <v>28.2</v>
       </c>
       <c r="H22" t="n">
-        <v>69045465</v>
+        <v>4385328</v>
       </c>
       <c r="I22" t="n">
-        <v>58040717</v>
+        <v>2575244</v>
       </c>
       <c r="J22" t="n">
-        <v>44.3</v>
+        <v>29.7</v>
       </c>
       <c r="K22" t="n">
-        <v>38.75</v>
+        <v>26.9</v>
       </c>
       <c r="L22" t="inlineStr">
         <is>
@@ -3409,52 +3409,52 @@
         </is>
       </c>
       <c r="M22" t="n">
-        <v>42747309</v>
+        <v>583256</v>
       </c>
       <c r="N22" t="n">
-        <v>84557583</v>
+        <v>3441822</v>
       </c>
       <c r="O22" t="n">
-        <v>141645747</v>
+        <v>4561789</v>
       </c>
       <c r="P22" t="n">
-        <v>192565620</v>
+        <v>4272437</v>
       </c>
       <c r="Q22" t="n">
-        <v>40012546</v>
+        <v>531256</v>
       </c>
       <c r="R22" t="n">
-        <v>83558902</v>
+        <v>3354742</v>
       </c>
       <c r="S22" t="n">
-        <v>136949595</v>
+        <v>4412709</v>
       </c>
       <c r="T22" t="n">
-        <v>203348182</v>
+        <v>4151350</v>
       </c>
       <c r="U22" t="n">
-        <v>458000</v>
+        <v>6000</v>
       </c>
       <c r="V22" t="n">
-        <v>-2448323</v>
+        <v>33080</v>
       </c>
       <c r="W22" t="n">
-        <v>-374278</v>
+        <v>35080</v>
       </c>
       <c r="X22" t="n">
-        <v>-16190664</v>
+        <v>52087</v>
       </c>
       <c r="Y22" t="n">
-        <v>2276763</v>
+        <v>46000</v>
       </c>
       <c r="Z22" t="n">
-        <v>3447004</v>
+        <v>54000</v>
       </c>
       <c r="AA22" t="n">
-        <v>5070430</v>
+        <v>114000</v>
       </c>
       <c r="AB22" t="n">
-        <v>5408102</v>
+        <v>69000</v>
       </c>
       <c r="AC22" t="n">
         <v>56</v>
@@ -3463,10 +3463,10 @@
         <v>56</v>
       </c>
       <c r="AE22" t="n">
+        <v>60</v>
+      </c>
+      <c r="AF22" t="n">
         <v>80</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>60</v>
       </c>
       <c r="AG22" t="n">
         <v>0</v>
@@ -3486,29 +3486,29 @@
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、黃金交叉、量能溫和放大</t>
+          <t>站上5日線、多頭排列、成交量放大</t>
         </is>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>法人連續偏買、5日法人明顯買超、外資買投信賣</t>
+          <t>法人連續偏買、5日法人明顯買超、外資投信同步買超</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>偏多觀察：站上5日線、多頭排列、黃金交叉、量能溫和放大、法人連續偏買、5日法人明顯買超、外資買投信賣。條件不差，適合等待拉回或突破確認。</t>
+          <t>偏多觀察：站上5日線、多頭排列、成交量放大、法人連續偏買、5日法人明顯買超、外資投信同步買超。條件不差，適合等待拉回或突破確認。</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>1808.TW</t>
+          <t>1476.TW</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>潤隆</t>
+          <t>儒鴻</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -3517,96 +3517,96 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>33</v>
+        <v>346</v>
       </c>
       <c r="E23" t="n">
-        <v>32.12</v>
+        <v>343.4</v>
       </c>
       <c r="F23" t="n">
-        <v>32.08</v>
+        <v>340.3</v>
       </c>
       <c r="G23" t="n">
-        <v>31.5</v>
+        <v>337.45</v>
       </c>
       <c r="H23" t="n">
-        <v>3407617</v>
+        <v>3624076</v>
       </c>
       <c r="I23" t="n">
-        <v>1689958</v>
+        <v>2302485</v>
       </c>
       <c r="J23" t="n">
-        <v>33.85</v>
+        <v>357.5</v>
       </c>
       <c r="K23" t="n">
-        <v>29.65</v>
+        <v>315</v>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>帶量突破20日高點</t>
+          <t>無明顯異常</t>
         </is>
       </c>
       <c r="M23" t="n">
-        <v>1018740</v>
+        <v>130149</v>
       </c>
       <c r="N23" t="n">
-        <v>2164107</v>
+        <v>1328162</v>
       </c>
       <c r="O23" t="n">
-        <v>2363563</v>
+        <v>1682368</v>
       </c>
       <c r="P23" t="n">
-        <v>2925079</v>
+        <v>2017868</v>
       </c>
       <c r="Q23" t="n">
-        <v>857740</v>
+        <v>127109</v>
       </c>
       <c r="R23" t="n">
-        <v>1992107</v>
+        <v>1285627</v>
       </c>
       <c r="S23" t="n">
-        <v>2201563</v>
+        <v>1637466</v>
       </c>
       <c r="T23" t="n">
-        <v>2724079</v>
+        <v>3210720</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>7544</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>13124</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>-1214961</v>
       </c>
       <c r="Y23" t="n">
-        <v>161000</v>
+        <v>2040</v>
       </c>
       <c r="Z23" t="n">
-        <v>172000</v>
+        <v>34991</v>
       </c>
       <c r="AA23" t="n">
-        <v>162000</v>
+        <v>31778</v>
       </c>
       <c r="AB23" t="n">
-        <v>201000</v>
+        <v>22109</v>
       </c>
       <c r="AC23" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="AD23" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="AE23" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AF23" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="AG23" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="AH23" t="inlineStr"/>
       <c r="AI23" t="inlineStr"/>
@@ -3623,29 +3623,29 @@
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、爆量、帶量突破20日高點</t>
+          <t>站上5日線、多頭排列、成交量放大</t>
         </is>
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>法人連續偏買、5日法人明顯買超</t>
+          <t>法人連續偏買、5日法人明顯買超、外資投信同步買超</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>偏多觀察：站上5日線、多頭排列、爆量、帶量突破20日高點、法人連續偏買、5日法人明顯買超。條件不差，適合等待拉回或突破確認。</t>
+          <t>偏多觀察：站上5日線、多頭排列、成交量放大、法人連續偏買、5日法人明顯買超、外資投信同步買超。條件不差，適合等待拉回或突破確認。</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2610.TW</t>
+          <t>1808.TW</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>華航</t>
+          <t>潤隆</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -3654,96 +3654,96 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>22.4</v>
+        <v>33</v>
       </c>
       <c r="E24" t="n">
-        <v>21.76</v>
+        <v>32.12</v>
       </c>
       <c r="F24" t="n">
-        <v>21.37</v>
+        <v>32.08</v>
       </c>
       <c r="G24" t="n">
-        <v>21.42</v>
+        <v>31.5</v>
       </c>
       <c r="H24" t="n">
-        <v>76781125</v>
+        <v>3407617</v>
       </c>
       <c r="I24" t="n">
-        <v>64229401</v>
+        <v>1689958</v>
       </c>
       <c r="J24" t="n">
-        <v>22.95</v>
+        <v>33.85</v>
       </c>
       <c r="K24" t="n">
-        <v>20.1</v>
+        <v>29.65</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>無明顯異常</t>
+          <t>帶量突破20日高點</t>
         </is>
       </c>
       <c r="M24" t="n">
-        <v>40122579</v>
+        <v>1018740</v>
       </c>
       <c r="N24" t="n">
-        <v>55293876</v>
+        <v>2164107</v>
       </c>
       <c r="O24" t="n">
-        <v>126096995</v>
+        <v>2363563</v>
       </c>
       <c r="P24" t="n">
-        <v>125044351</v>
+        <v>2925079</v>
       </c>
       <c r="Q24" t="n">
-        <v>37781188</v>
+        <v>857740</v>
       </c>
       <c r="R24" t="n">
-        <v>52878896</v>
+        <v>1992107</v>
       </c>
       <c r="S24" t="n">
-        <v>117482772</v>
+        <v>2201563</v>
       </c>
       <c r="T24" t="n">
-        <v>104023168</v>
+        <v>2724079</v>
       </c>
       <c r="U24" t="n">
-        <v>389000</v>
+        <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>910409</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>6033409</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>19184842</v>
+        <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>1952391</v>
+        <v>161000</v>
       </c>
       <c r="Z24" t="n">
-        <v>1504571</v>
+        <v>172000</v>
       </c>
       <c r="AA24" t="n">
-        <v>2580814</v>
+        <v>162000</v>
       </c>
       <c r="AB24" t="n">
-        <v>1836341</v>
+        <v>201000</v>
       </c>
       <c r="AC24" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="AD24" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="AE24" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="AF24" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AH24" t="inlineStr"/>
       <c r="AI24" t="inlineStr"/>
@@ -3760,29 +3760,29 @@
       </c>
       <c r="AM24" t="inlineStr">
         <is>
-          <t>站上5日線、黃金交叉、量能溫和放大</t>
+          <t>站上5日線、多頭排列、爆量、帶量突破20日高點</t>
         </is>
       </c>
       <c r="AN24" t="inlineStr">
         <is>
-          <t>法人連續偏買、5日法人明顯買超、外資投信同步買超</t>
+          <t>法人連續偏買、5日法人明顯買超</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>偏多觀察：站上5日線、黃金交叉、量能溫和放大、法人連續偏買、5日法人明顯買超、外資投信同步買超。條件不差，適合等待拉回或突破確認。</t>
+          <t>偏多觀察：站上5日線、多頭排列、爆量、帶量突破20日高點、法人連續偏買、5日法人明顯買超。條件不差，適合等待拉回或突破確認。</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2850.TW</t>
+          <t>2610.TW</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>新產</t>
+          <t>華航</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -3791,28 +3791,28 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>161</v>
+        <v>22.4</v>
       </c>
       <c r="E25" t="n">
-        <v>157.3</v>
+        <v>21.76</v>
       </c>
       <c r="F25" t="n">
-        <v>152.25</v>
+        <v>21.37</v>
       </c>
       <c r="G25" t="n">
-        <v>149</v>
+        <v>21.42</v>
       </c>
       <c r="H25" t="n">
-        <v>1052899</v>
+        <v>76786125</v>
       </c>
       <c r="I25" t="n">
-        <v>895161</v>
+        <v>64230401</v>
       </c>
       <c r="J25" t="n">
-        <v>164.5</v>
+        <v>22.95</v>
       </c>
       <c r="K25" t="n">
-        <v>140</v>
+        <v>20.1</v>
       </c>
       <c r="L25" t="inlineStr">
         <is>
@@ -3820,52 +3820,52 @@
         </is>
       </c>
       <c r="M25" t="n">
-        <v>465766</v>
+        <v>40122579</v>
       </c>
       <c r="N25" t="n">
-        <v>530353</v>
+        <v>55293876</v>
       </c>
       <c r="O25" t="n">
-        <v>858307</v>
+        <v>126096995</v>
       </c>
       <c r="P25" t="n">
-        <v>710518</v>
+        <v>125044351</v>
       </c>
       <c r="Q25" t="n">
-        <v>449766</v>
+        <v>37781188</v>
       </c>
       <c r="R25" t="n">
-        <v>504353</v>
+        <v>52878896</v>
       </c>
       <c r="S25" t="n">
-        <v>841307</v>
+        <v>117482772</v>
       </c>
       <c r="T25" t="n">
-        <v>709613</v>
+        <v>104023168</v>
       </c>
       <c r="U25" t="n">
-        <v>23000</v>
+        <v>389000</v>
       </c>
       <c r="V25" t="n">
-        <v>24000</v>
+        <v>910409</v>
       </c>
       <c r="W25" t="n">
-        <v>24000</v>
+        <v>6033409</v>
       </c>
       <c r="X25" t="n">
-        <v>25000</v>
+        <v>19184842</v>
       </c>
       <c r="Y25" t="n">
-        <v>-7000</v>
+        <v>1952391</v>
       </c>
       <c r="Z25" t="n">
-        <v>2000</v>
+        <v>1504571</v>
       </c>
       <c r="AA25" t="n">
-        <v>-7000</v>
+        <v>2580814</v>
       </c>
       <c r="AB25" t="n">
-        <v>-24095</v>
+        <v>1836341</v>
       </c>
       <c r="AC25" t="n">
         <v>54</v>
@@ -3897,7 +3897,7 @@
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、量能溫和放大</t>
+          <t>站上5日線、黃金交叉、量能溫和放大</t>
         </is>
       </c>
       <c r="AN25" t="inlineStr">
@@ -3907,19 +3907,19 @@
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>偏多觀察：站上5日線、多頭排列、量能溫和放大、法人連續偏買、5日法人明顯買超、外資投信同步買超。條件不差，適合等待拉回或突破確認。</t>
+          <t>偏多觀察：站上5日線、黃金交叉、量能溫和放大、法人連續偏買、5日法人明顯買超、外資投信同步買超。條件不差，適合等待拉回或突破確認。</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>1476.TW</t>
+          <t>2206.TW</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>儒鴻</t>
+          <t>三陽工業</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -3928,28 +3928,28 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>346</v>
+        <v>64.8</v>
       </c>
       <c r="E26" t="n">
-        <v>343.4</v>
+        <v>63.76</v>
       </c>
       <c r="F26" t="n">
-        <v>340.3</v>
+        <v>62.96</v>
       </c>
       <c r="G26" t="n">
-        <v>337.45</v>
+        <v>63.41</v>
       </c>
       <c r="H26" t="n">
-        <v>3225076</v>
+        <v>2224051</v>
       </c>
       <c r="I26" t="n">
-        <v>2222685</v>
+        <v>1836201</v>
       </c>
       <c r="J26" t="n">
-        <v>357.5</v>
+        <v>66.7</v>
       </c>
       <c r="K26" t="n">
-        <v>315</v>
+        <v>59.4</v>
       </c>
       <c r="L26" t="inlineStr">
         <is>
@@ -3957,52 +3957,52 @@
         </is>
       </c>
       <c r="M26" t="n">
-        <v>130149</v>
+        <v>777453</v>
       </c>
       <c r="N26" t="n">
-        <v>1328162</v>
+        <v>3290981</v>
       </c>
       <c r="O26" t="n">
-        <v>1682368</v>
+        <v>4302859</v>
       </c>
       <c r="P26" t="n">
-        <v>2017868</v>
+        <v>5010999</v>
       </c>
       <c r="Q26" t="n">
-        <v>127109</v>
+        <v>719453</v>
       </c>
       <c r="R26" t="n">
-        <v>1285627</v>
+        <v>3204981</v>
       </c>
       <c r="S26" t="n">
-        <v>1637466</v>
+        <v>4211859</v>
       </c>
       <c r="T26" t="n">
-        <v>3210720</v>
+        <v>4416999</v>
       </c>
       <c r="U26" t="n">
-        <v>1000</v>
+        <v>6000</v>
       </c>
       <c r="V26" t="n">
-        <v>7544</v>
+        <v>18000</v>
       </c>
       <c r="W26" t="n">
-        <v>13124</v>
+        <v>19000</v>
       </c>
       <c r="X26" t="n">
-        <v>-1214961</v>
+        <v>440000</v>
       </c>
       <c r="Y26" t="n">
-        <v>2040</v>
+        <v>52000</v>
       </c>
       <c r="Z26" t="n">
-        <v>34991</v>
+        <v>68000</v>
       </c>
       <c r="AA26" t="n">
-        <v>31778</v>
+        <v>72000</v>
       </c>
       <c r="AB26" t="n">
-        <v>22109</v>
+        <v>154000</v>
       </c>
       <c r="AC26" t="n">
         <v>54</v>
@@ -4034,7 +4034,7 @@
       </c>
       <c r="AM26" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、量能溫和放大</t>
+          <t>站上5日線、黃金交叉、量能溫和放大</t>
         </is>
       </c>
       <c r="AN26" t="inlineStr">
@@ -4044,19 +4044,19 @@
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>偏多觀察：站上5日線、多頭排列、量能溫和放大、法人連續偏買、5日法人明顯買超、外資投信同步買超。條件不差，適合等待拉回或突破確認。</t>
+          <t>偏多觀察：站上5日線、黃金交叉、量能溫和放大、法人連續偏買、5日法人明顯買超、外資投信同步買超。條件不差，適合等待拉回或突破確認。</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2207.TW</t>
+          <t>2850.TW</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>和泰車</t>
+          <t>新產</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -4065,28 +4065,28 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>558</v>
+        <v>161</v>
       </c>
       <c r="E27" t="n">
-        <v>525.2</v>
+        <v>157.3</v>
       </c>
       <c r="F27" t="n">
-        <v>508.55</v>
+        <v>152.25</v>
       </c>
       <c r="G27" t="n">
-        <v>493.85</v>
+        <v>149</v>
       </c>
       <c r="H27" t="n">
-        <v>1231859</v>
+        <v>1052899</v>
       </c>
       <c r="I27" t="n">
-        <v>1038864</v>
+        <v>895161</v>
       </c>
       <c r="J27" t="n">
-        <v>573</v>
+        <v>164.5</v>
       </c>
       <c r="K27" t="n">
-        <v>461</v>
+        <v>140</v>
       </c>
       <c r="L27" t="inlineStr">
         <is>
@@ -4094,52 +4094,52 @@
         </is>
       </c>
       <c r="M27" t="n">
-        <v>535907</v>
+        <v>465766</v>
       </c>
       <c r="N27" t="n">
-        <v>1582427</v>
+        <v>530353</v>
       </c>
       <c r="O27" t="n">
-        <v>1984699</v>
+        <v>858307</v>
       </c>
       <c r="P27" t="n">
-        <v>2122319</v>
+        <v>710518</v>
       </c>
       <c r="Q27" t="n">
-        <v>513505</v>
+        <v>449766</v>
       </c>
       <c r="R27" t="n">
-        <v>1553212</v>
+        <v>504353</v>
       </c>
       <c r="S27" t="n">
-        <v>1943484</v>
+        <v>841307</v>
       </c>
       <c r="T27" t="n">
-        <v>2030086</v>
+        <v>709613</v>
       </c>
       <c r="U27" t="n">
+        <v>23000</v>
+      </c>
+      <c r="V27" t="n">
+        <v>24000</v>
+      </c>
+      <c r="W27" t="n">
+        <v>24000</v>
+      </c>
+      <c r="X27" t="n">
+        <v>25000</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>-7000</v>
+      </c>
+      <c r="Z27" t="n">
         <v>2000</v>
       </c>
-      <c r="V27" t="n">
-        <v>6816</v>
-      </c>
-      <c r="W27" t="n">
-        <v>10816</v>
-      </c>
-      <c r="X27" t="n">
-        <v>73043</v>
-      </c>
-      <c r="Y27" t="n">
-        <v>20402</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>22399</v>
-      </c>
       <c r="AA27" t="n">
-        <v>30399</v>
+        <v>-7000</v>
       </c>
       <c r="AB27" t="n">
-        <v>19190</v>
+        <v>-24095</v>
       </c>
       <c r="AC27" t="n">
         <v>54</v>
@@ -4462,12 +4462,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2206.TW</t>
+          <t>2207.TW</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>三陽工業</t>
+          <t>和泰車</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -4476,28 +4476,28 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>64.8</v>
+        <v>558</v>
       </c>
       <c r="E30" t="n">
-        <v>63.76</v>
+        <v>525.2</v>
       </c>
       <c r="F30" t="n">
-        <v>62.96</v>
+        <v>508.55</v>
       </c>
       <c r="G30" t="n">
-        <v>63.41</v>
+        <v>493.85</v>
       </c>
       <c r="H30" t="n">
-        <v>2224051</v>
+        <v>1231859</v>
       </c>
       <c r="I30" t="n">
-        <v>1836201</v>
+        <v>1038864</v>
       </c>
       <c r="J30" t="n">
-        <v>66.7</v>
+        <v>573</v>
       </c>
       <c r="K30" t="n">
-        <v>59.4</v>
+        <v>461</v>
       </c>
       <c r="L30" t="inlineStr">
         <is>
@@ -4505,52 +4505,52 @@
         </is>
       </c>
       <c r="M30" t="n">
-        <v>777453</v>
+        <v>535907</v>
       </c>
       <c r="N30" t="n">
-        <v>3290981</v>
+        <v>1582427</v>
       </c>
       <c r="O30" t="n">
-        <v>4302859</v>
+        <v>1984699</v>
       </c>
       <c r="P30" t="n">
-        <v>5010999</v>
+        <v>2122319</v>
       </c>
       <c r="Q30" t="n">
-        <v>719453</v>
+        <v>513505</v>
       </c>
       <c r="R30" t="n">
-        <v>3204981</v>
+        <v>1553212</v>
       </c>
       <c r="S30" t="n">
-        <v>4211859</v>
+        <v>1943484</v>
       </c>
       <c r="T30" t="n">
-        <v>4416999</v>
+        <v>2030086</v>
       </c>
       <c r="U30" t="n">
-        <v>6000</v>
+        <v>2000</v>
       </c>
       <c r="V30" t="n">
-        <v>18000</v>
+        <v>6816</v>
       </c>
       <c r="W30" t="n">
-        <v>19000</v>
+        <v>10816</v>
       </c>
       <c r="X30" t="n">
-        <v>440000</v>
+        <v>73043</v>
       </c>
       <c r="Y30" t="n">
-        <v>52000</v>
+        <v>20402</v>
       </c>
       <c r="Z30" t="n">
-        <v>68000</v>
+        <v>22399</v>
       </c>
       <c r="AA30" t="n">
-        <v>72000</v>
+        <v>30399</v>
       </c>
       <c r="AB30" t="n">
-        <v>154000</v>
+        <v>19190</v>
       </c>
       <c r="AC30" t="n">
         <v>54</v>
@@ -4582,7 +4582,7 @@
       </c>
       <c r="AM30" t="inlineStr">
         <is>
-          <t>站上5日線、黃金交叉、量能溫和放大</t>
+          <t>站上5日線、多頭排列、量能溫和放大</t>
         </is>
       </c>
       <c r="AN30" t="inlineStr">
@@ -4592,7 +4592,7 @@
       </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>偏多觀察：站上5日線、黃金交叉、量能溫和放大、法人連續偏買、5日法人明顯買超、外資投信同步買超。條件不差，適合等待拉回或突破確認。</t>
+          <t>偏多觀察：站上5日線、多頭排列、量能溫和放大、法人連續偏買、5日法人明顯買超、外資投信同步買超。條件不差，適合等待拉回或突破確認。</t>
         </is>
       </c>
     </row>
@@ -5036,10 +5036,10 @@
         <v>29.94</v>
       </c>
       <c r="H34" t="n">
-        <v>88558119</v>
+        <v>89011119</v>
       </c>
       <c r="I34" t="n">
-        <v>54099929</v>
+        <v>54190529</v>
       </c>
       <c r="J34" t="n">
         <v>31.3</v>
@@ -5995,10 +5995,10 @@
         <v>65.70999999999999</v>
       </c>
       <c r="H41" t="n">
-        <v>45193974</v>
+        <v>50598974</v>
       </c>
       <c r="I41" t="n">
-        <v>37463373</v>
+        <v>38544373</v>
       </c>
       <c r="J41" t="n">
         <v>72.3</v>
@@ -6680,10 +6680,10 @@
         <v>500.15</v>
       </c>
       <c r="H46" t="n">
-        <v>7467701</v>
+        <v>7502701</v>
       </c>
       <c r="I46" t="n">
-        <v>5000024</v>
+        <v>5007024</v>
       </c>
       <c r="J46" t="n">
         <v>553</v>
@@ -8050,10 +8050,10 @@
         <v>307.57</v>
       </c>
       <c r="H56" t="n">
-        <v>5083334</v>
+        <v>5247334</v>
       </c>
       <c r="I56" t="n">
-        <v>2257019</v>
+        <v>2289819</v>
       </c>
       <c r="J56" t="n">
         <v>350</v>
@@ -8598,10 +8598,10 @@
         <v>241.6</v>
       </c>
       <c r="H60" t="n">
-        <v>98985798</v>
+        <v>99413798</v>
       </c>
       <c r="I60" t="n">
-        <v>69964913</v>
+        <v>70050513</v>
       </c>
       <c r="J60" t="n">
         <v>259.5</v>
@@ -8735,10 +8735,10 @@
         <v>112.1</v>
       </c>
       <c r="H61" t="n">
-        <v>11037466</v>
+        <v>12300466</v>
       </c>
       <c r="I61" t="n">
-        <v>8844514</v>
+        <v>9097114</v>
       </c>
       <c r="J61" t="n">
         <v>123</v>
@@ -9283,10 +9283,10 @@
         <v>34.94</v>
       </c>
       <c r="H65" t="n">
-        <v>95024582</v>
+        <v>96324582</v>
       </c>
       <c r="I65" t="n">
-        <v>71455545</v>
+        <v>71715545</v>
       </c>
       <c r="J65" t="n">
         <v>37.75</v>
@@ -9557,10 +9557,10 @@
         <v>138.28</v>
       </c>
       <c r="H67" t="n">
-        <v>21622742</v>
+        <v>23664742</v>
       </c>
       <c r="I67" t="n">
-        <v>23443205</v>
+        <v>23851605</v>
       </c>
       <c r="J67" t="n">
         <v>142.5</v>
@@ -9968,10 +9968,10 @@
         <v>134.18</v>
       </c>
       <c r="H70" t="n">
-        <v>2065333</v>
+        <v>2210333</v>
       </c>
       <c r="I70" t="n">
-        <v>1952001</v>
+        <v>1981001</v>
       </c>
       <c r="J70" t="n">
         <v>152</v>
@@ -11475,10 +11475,10 @@
         <v>101.93</v>
       </c>
       <c r="H81" t="n">
-        <v>16947166</v>
+        <v>20608166</v>
       </c>
       <c r="I81" t="n">
-        <v>14219948</v>
+        <v>14952148</v>
       </c>
       <c r="J81" t="n">
         <v>108.5</v>
@@ -12708,10 +12708,10 @@
         <v>2381.5</v>
       </c>
       <c r="H90" t="n">
-        <v>64039645</v>
+        <v>69478145</v>
       </c>
       <c r="I90" t="n">
-        <v>51564802</v>
+        <v>52652502</v>
       </c>
       <c r="J90" t="n">
         <v>2500</v>
@@ -13941,10 +13941,10 @@
         <v>34.01</v>
       </c>
       <c r="H99" t="n">
-        <v>32852302</v>
+        <v>33282302</v>
       </c>
       <c r="I99" t="n">
-        <v>14469392</v>
+        <v>14555392</v>
       </c>
       <c r="J99" t="n">
         <v>37.1</v>
@@ -18162,12 +18162,12 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>2105.TW</t>
+          <t>2608.TW</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>正新</t>
+          <t>嘉里大榮</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -18176,93 +18176,93 @@
         </is>
       </c>
       <c r="D130" t="n">
-        <v>30.45</v>
+        <v>29.1</v>
       </c>
       <c r="E130" t="n">
-        <v>30.58</v>
+        <v>29.49</v>
       </c>
       <c r="F130" t="n">
-        <v>31.21</v>
+        <v>29.36</v>
       </c>
       <c r="G130" t="n">
-        <v>31.96</v>
+        <v>29.33</v>
       </c>
       <c r="H130" t="n">
-        <v>24585466</v>
+        <v>538920</v>
       </c>
       <c r="I130" t="n">
-        <v>12413779</v>
+        <v>481930</v>
       </c>
       <c r="J130" t="n">
-        <v>34.6</v>
+        <v>30</v>
       </c>
       <c r="K130" t="n">
+        <v>28.7</v>
+      </c>
+      <c r="L130" t="inlineStr">
+        <is>
+          <t>無明顯異常</t>
+        </is>
+      </c>
+      <c r="M130" t="n">
+        <v>-250600</v>
+      </c>
+      <c r="N130" t="n">
+        <v>468862</v>
+      </c>
+      <c r="O130" t="n">
+        <v>692842</v>
+      </c>
+      <c r="P130" t="n">
+        <v>933274</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>-264600</v>
+      </c>
+      <c r="R130" t="n">
+        <v>452862</v>
+      </c>
+      <c r="S130" t="n">
+        <v>647842</v>
+      </c>
+      <c r="T130" t="n">
+        <v>895274</v>
+      </c>
+      <c r="U130" t="n">
+        <v>0</v>
+      </c>
+      <c r="V130" t="n">
+        <v>0</v>
+      </c>
+      <c r="W130" t="n">
+        <v>0</v>
+      </c>
+      <c r="X130" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>14000</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>16000</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>45000</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>38000</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>14</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>14</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>5</v>
+      </c>
+      <c r="AF130" t="n">
         <v>30</v>
-      </c>
-      <c r="L130" t="inlineStr">
-        <is>
-          <t>無明顯異常</t>
-        </is>
-      </c>
-      <c r="M130" t="n">
-        <v>3078772</v>
-      </c>
-      <c r="N130" t="n">
-        <v>3238432</v>
-      </c>
-      <c r="O130" t="n">
-        <v>2009743</v>
-      </c>
-      <c r="P130" t="n">
-        <v>-2819839</v>
-      </c>
-      <c r="Q130" t="n">
-        <v>2841494</v>
-      </c>
-      <c r="R130" t="n">
-        <v>2492511</v>
-      </c>
-      <c r="S130" t="n">
-        <v>684947</v>
-      </c>
-      <c r="T130" t="n">
-        <v>5388199</v>
-      </c>
-      <c r="U130" t="n">
-        <v>10000</v>
-      </c>
-      <c r="V130" t="n">
-        <v>64903</v>
-      </c>
-      <c r="W130" t="n">
-        <v>89903</v>
-      </c>
-      <c r="X130" t="n">
-        <v>-10420487</v>
-      </c>
-      <c r="Y130" t="n">
-        <v>227278</v>
-      </c>
-      <c r="Z130" t="n">
-        <v>681018</v>
-      </c>
-      <c r="AA130" t="n">
-        <v>1234893</v>
-      </c>
-      <c r="AB130" t="n">
-        <v>2212449</v>
-      </c>
-      <c r="AC130" t="n">
-        <v>16</v>
-      </c>
-      <c r="AD130" t="n">
-        <v>16</v>
-      </c>
-      <c r="AE130" t="n">
-        <v>-40</v>
-      </c>
-      <c r="AF130" t="n">
-        <v>80</v>
       </c>
       <c r="AG130" t="n">
         <v>0</v>
@@ -18282,17 +18282,17 @@
       </c>
       <c r="AM130" t="inlineStr">
         <is>
-          <t>跌破5日線、空頭排列、成交量放大、接近20日低點</t>
+          <t>跌破5日線、多頭排列、量能溫和放大、接近20日低點</t>
         </is>
       </c>
       <c r="AN130" t="inlineStr">
         <is>
-          <t>法人連續偏買、5日法人明顯買超、外資投信同步買超</t>
+          <t>5日法人明顯買超</t>
         </is>
       </c>
       <c r="AO130" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、空頭排列、成交量放大、接近20日低點、法人連續偏買、5日法人明顯買超、外資投信同步買超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、多頭排列、量能溫和放大、接近20日低點、5日法人明顯買超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
@@ -18573,12 +18573,12 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>2328.TW</t>
+          <t>2524.TW</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>廣宇</t>
+          <t>京城</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -18587,28 +18587,28 @@
         </is>
       </c>
       <c r="D133" t="n">
-        <v>41.15</v>
+        <v>35.8</v>
       </c>
       <c r="E133" t="n">
-        <v>41.6</v>
+        <v>35.78</v>
       </c>
       <c r="F133" t="n">
-        <v>43.85</v>
+        <v>36.08</v>
       </c>
       <c r="G133" t="n">
-        <v>46.43</v>
+        <v>36.18</v>
       </c>
       <c r="H133" t="n">
-        <v>2682207</v>
+        <v>93859</v>
       </c>
       <c r="I133" t="n">
-        <v>3274281</v>
+        <v>129711</v>
       </c>
       <c r="J133" t="n">
-        <v>52.4</v>
+        <v>38.5</v>
       </c>
       <c r="K133" t="n">
-        <v>38.65</v>
+        <v>34.1</v>
       </c>
       <c r="L133" t="inlineStr">
         <is>
@@ -18616,52 +18616,52 @@
         </is>
       </c>
       <c r="M133" t="n">
-        <v>698874</v>
+        <v>40000</v>
       </c>
       <c r="N133" t="n">
-        <v>1345986</v>
+        <v>174400</v>
       </c>
       <c r="O133" t="n">
-        <v>647886</v>
+        <v>227546</v>
       </c>
       <c r="P133" t="n">
-        <v>534532</v>
+        <v>335646</v>
       </c>
       <c r="Q133" t="n">
-        <v>506526</v>
+        <v>38000</v>
       </c>
       <c r="R133" t="n">
-        <v>1322081</v>
+        <v>180400</v>
       </c>
       <c r="S133" t="n">
-        <v>842499</v>
+        <v>235546</v>
       </c>
       <c r="T133" t="n">
-        <v>913300</v>
+        <v>332646</v>
       </c>
       <c r="U133" t="n">
         <v>0</v>
       </c>
       <c r="V133" t="n">
-        <v>6000</v>
+        <v>0</v>
       </c>
       <c r="W133" t="n">
-        <v>6000</v>
+        <v>0</v>
       </c>
       <c r="X133" t="n">
-        <v>6000</v>
+        <v>0</v>
       </c>
       <c r="Y133" t="n">
-        <v>192348</v>
+        <v>2000</v>
       </c>
       <c r="Z133" t="n">
-        <v>17905</v>
+        <v>-6000</v>
       </c>
       <c r="AA133" t="n">
-        <v>-200613</v>
+        <v>-8000</v>
       </c>
       <c r="AB133" t="n">
-        <v>-384768</v>
+        <v>3000</v>
       </c>
       <c r="AC133" t="n">
         <v>14</v>
@@ -18670,10 +18670,10 @@
         <v>14</v>
       </c>
       <c r="AE133" t="n">
-        <v>-45</v>
+        <v>-15</v>
       </c>
       <c r="AF133" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="AG133" t="n">
         <v>0</v>
@@ -18693,29 +18693,29 @@
       </c>
       <c r="AM133" t="inlineStr">
         <is>
-          <t>跌破5日線、空頭排列、量能未放大</t>
+          <t>站上5日線、空頭排列、量能未放大、接近20日低點</t>
         </is>
       </c>
       <c r="AN133" t="inlineStr">
         <is>
-          <t>法人連續偏買、5日法人明顯買超、外資投信同步買超</t>
+          <t>法人連續偏買、5日法人買超</t>
         </is>
       </c>
       <c r="AO133" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、空頭排列、量能未放大、法人連續偏買、5日法人明顯買超、外資投信同步買超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、空頭排列、量能未放大、接近20日低點、法人連續偏買、5日法人買超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>9904.TW</t>
+          <t>2105.TW</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>寶成</t>
+          <t>正新</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -18724,81 +18724,81 @@
         </is>
       </c>
       <c r="D134" t="n">
-        <v>23.95</v>
+        <v>30.45</v>
       </c>
       <c r="E134" t="n">
-        <v>24.08</v>
+        <v>30.58</v>
       </c>
       <c r="F134" t="n">
-        <v>24.21</v>
+        <v>31.21</v>
       </c>
       <c r="G134" t="n">
-        <v>24.28</v>
+        <v>31.96</v>
       </c>
       <c r="H134" t="n">
-        <v>23076885</v>
+        <v>31221466</v>
       </c>
       <c r="I134" t="n">
-        <v>20319426</v>
+        <v>13740979</v>
       </c>
       <c r="J134" t="n">
-        <v>25.45</v>
+        <v>34.6</v>
       </c>
       <c r="K134" t="n">
-        <v>23.7</v>
+        <v>30</v>
       </c>
       <c r="L134" t="inlineStr">
         <is>
-          <t>無明顯異常</t>
+          <t>爆量價未漲</t>
         </is>
       </c>
       <c r="M134" t="n">
-        <v>2241344</v>
+        <v>3078772</v>
       </c>
       <c r="N134" t="n">
-        <v>16504190</v>
+        <v>3238432</v>
       </c>
       <c r="O134" t="n">
-        <v>11296681</v>
+        <v>2009743</v>
       </c>
       <c r="P134" t="n">
-        <v>-4017280</v>
+        <v>-2819839</v>
       </c>
       <c r="Q134" t="n">
-        <v>2139983</v>
+        <v>2841494</v>
       </c>
       <c r="R134" t="n">
-        <v>16010602</v>
+        <v>2492511</v>
       </c>
       <c r="S134" t="n">
-        <v>10805202</v>
+        <v>684947</v>
       </c>
       <c r="T134" t="n">
-        <v>7587082</v>
+        <v>5388199</v>
       </c>
       <c r="U134" t="n">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="V134" t="n">
-        <v>17562</v>
+        <v>64903</v>
       </c>
       <c r="W134" t="n">
-        <v>60562</v>
+        <v>89903</v>
       </c>
       <c r="X134" t="n">
-        <v>-12294967</v>
+        <v>-10420487</v>
       </c>
       <c r="Y134" t="n">
-        <v>101361</v>
+        <v>227278</v>
       </c>
       <c r="Z134" t="n">
-        <v>476026</v>
+        <v>681018</v>
       </c>
       <c r="AA134" t="n">
-        <v>430917</v>
+        <v>1234893</v>
       </c>
       <c r="AB134" t="n">
-        <v>690605</v>
+        <v>2212449</v>
       </c>
       <c r="AC134" t="n">
         <v>14</v>
@@ -18807,13 +18807,13 @@
         <v>14</v>
       </c>
       <c r="AE134" t="n">
-        <v>-45</v>
+        <v>-35</v>
       </c>
       <c r="AF134" t="n">
         <v>80</v>
       </c>
       <c r="AG134" t="n">
-        <v>0</v>
+        <v>-20</v>
       </c>
       <c r="AH134" t="inlineStr"/>
       <c r="AI134" t="inlineStr"/>
@@ -18830,7 +18830,7 @@
       </c>
       <c r="AM134" t="inlineStr">
         <is>
-          <t>跌破5日線、空頭排列、量能溫和放大、接近20日低點</t>
+          <t>跌破5日線、空頭排列、爆量、接近20日低點、爆量價未漲</t>
         </is>
       </c>
       <c r="AN134" t="inlineStr">
@@ -18840,19 +18840,19 @@
       </c>
       <c r="AO134" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、空頭排列、量能溫和放大、接近20日低點、法人連續偏買、5日法人明顯買超、外資投信同步買超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、空頭排列、爆量、接近20日低點、爆量價未漲、法人連續偏買、5日法人明顯買超、外資投信同步買超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>2524.TW</t>
+          <t>9904.TW</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>京城</t>
+          <t>寶成</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -18861,28 +18861,28 @@
         </is>
       </c>
       <c r="D135" t="n">
-        <v>35.8</v>
+        <v>23.95</v>
       </c>
       <c r="E135" t="n">
-        <v>35.78</v>
+        <v>24.08</v>
       </c>
       <c r="F135" t="n">
-        <v>36.08</v>
+        <v>24.21</v>
       </c>
       <c r="G135" t="n">
-        <v>36.18</v>
+        <v>24.28</v>
       </c>
       <c r="H135" t="n">
-        <v>93859</v>
+        <v>23076885</v>
       </c>
       <c r="I135" t="n">
-        <v>129711</v>
+        <v>20319426</v>
       </c>
       <c r="J135" t="n">
-        <v>38.5</v>
+        <v>25.45</v>
       </c>
       <c r="K135" t="n">
-        <v>34.1</v>
+        <v>23.7</v>
       </c>
       <c r="L135" t="inlineStr">
         <is>
@@ -18890,52 +18890,52 @@
         </is>
       </c>
       <c r="M135" t="n">
-        <v>40000</v>
+        <v>2241344</v>
       </c>
       <c r="N135" t="n">
-        <v>174400</v>
+        <v>16504190</v>
       </c>
       <c r="O135" t="n">
-        <v>227546</v>
+        <v>11296681</v>
       </c>
       <c r="P135" t="n">
-        <v>335646</v>
+        <v>-4017280</v>
       </c>
       <c r="Q135" t="n">
-        <v>38000</v>
+        <v>2139983</v>
       </c>
       <c r="R135" t="n">
-        <v>180400</v>
+        <v>16010602</v>
       </c>
       <c r="S135" t="n">
-        <v>235546</v>
+        <v>10805202</v>
       </c>
       <c r="T135" t="n">
-        <v>332646</v>
+        <v>7587082</v>
       </c>
       <c r="U135" t="n">
         <v>0</v>
       </c>
       <c r="V135" t="n">
-        <v>0</v>
+        <v>17562</v>
       </c>
       <c r="W135" t="n">
-        <v>0</v>
+        <v>60562</v>
       </c>
       <c r="X135" t="n">
-        <v>0</v>
+        <v>-12294967</v>
       </c>
       <c r="Y135" t="n">
-        <v>2000</v>
+        <v>101361</v>
       </c>
       <c r="Z135" t="n">
-        <v>-6000</v>
+        <v>476026</v>
       </c>
       <c r="AA135" t="n">
-        <v>-8000</v>
+        <v>430917</v>
       </c>
       <c r="AB135" t="n">
-        <v>3000</v>
+        <v>690605</v>
       </c>
       <c r="AC135" t="n">
         <v>14</v>
@@ -18944,10 +18944,10 @@
         <v>14</v>
       </c>
       <c r="AE135" t="n">
-        <v>-15</v>
+        <v>-45</v>
       </c>
       <c r="AF135" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="AG135" t="n">
         <v>0</v>
@@ -18967,29 +18967,29 @@
       </c>
       <c r="AM135" t="inlineStr">
         <is>
-          <t>站上5日線、空頭排列、量能未放大、接近20日低點</t>
+          <t>跌破5日線、空頭排列、量能溫和放大、接近20日低點</t>
         </is>
       </c>
       <c r="AN135" t="inlineStr">
         <is>
-          <t>法人連續偏買、5日法人買超</t>
+          <t>法人連續偏買、5日法人明顯買超、外資投信同步買超</t>
         </is>
       </c>
       <c r="AO135" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、空頭排列、量能未放大、接近20日低點、法人連續偏買、5日法人買超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、空頭排列、量能溫和放大、接近20日低點、法人連續偏買、5日法人明顯買超、外資投信同步買超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>2608.TW</t>
+          <t>2328.TW</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>嘉里大榮</t>
+          <t>廣宇</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -18998,28 +18998,28 @@
         </is>
       </c>
       <c r="D136" t="n">
-        <v>29.1</v>
+        <v>41.15</v>
       </c>
       <c r="E136" t="n">
-        <v>29.49</v>
+        <v>41.6</v>
       </c>
       <c r="F136" t="n">
-        <v>29.36</v>
+        <v>43.85</v>
       </c>
       <c r="G136" t="n">
-        <v>29.33</v>
+        <v>46.43</v>
       </c>
       <c r="H136" t="n">
-        <v>538920</v>
+        <v>2682207</v>
       </c>
       <c r="I136" t="n">
-        <v>481930</v>
+        <v>3274281</v>
       </c>
       <c r="J136" t="n">
-        <v>30</v>
+        <v>52.4</v>
       </c>
       <c r="K136" t="n">
-        <v>28.7</v>
+        <v>38.65</v>
       </c>
       <c r="L136" t="inlineStr">
         <is>
@@ -19027,52 +19027,52 @@
         </is>
       </c>
       <c r="M136" t="n">
-        <v>-250600</v>
+        <v>698874</v>
       </c>
       <c r="N136" t="n">
-        <v>468862</v>
+        <v>1345986</v>
       </c>
       <c r="O136" t="n">
-        <v>692842</v>
+        <v>647886</v>
       </c>
       <c r="P136" t="n">
-        <v>933274</v>
+        <v>534532</v>
       </c>
       <c r="Q136" t="n">
-        <v>-264600</v>
+        <v>506526</v>
       </c>
       <c r="R136" t="n">
-        <v>452862</v>
+        <v>1322081</v>
       </c>
       <c r="S136" t="n">
-        <v>647842</v>
+        <v>842499</v>
       </c>
       <c r="T136" t="n">
-        <v>895274</v>
+        <v>913300</v>
       </c>
       <c r="U136" t="n">
         <v>0</v>
       </c>
       <c r="V136" t="n">
-        <v>0</v>
+        <v>6000</v>
       </c>
       <c r="W136" t="n">
-        <v>0</v>
+        <v>6000</v>
       </c>
       <c r="X136" t="n">
-        <v>0</v>
+        <v>6000</v>
       </c>
       <c r="Y136" t="n">
-        <v>14000</v>
+        <v>192348</v>
       </c>
       <c r="Z136" t="n">
-        <v>16000</v>
+        <v>17905</v>
       </c>
       <c r="AA136" t="n">
-        <v>45000</v>
+        <v>-200613</v>
       </c>
       <c r="AB136" t="n">
-        <v>38000</v>
+        <v>-384768</v>
       </c>
       <c r="AC136" t="n">
         <v>14</v>
@@ -19081,10 +19081,10 @@
         <v>14</v>
       </c>
       <c r="AE136" t="n">
-        <v>5</v>
+        <v>-45</v>
       </c>
       <c r="AF136" t="n">
-        <v>30</v>
+        <v>80</v>
       </c>
       <c r="AG136" t="n">
         <v>0</v>
@@ -19104,17 +19104,17 @@
       </c>
       <c r="AM136" t="inlineStr">
         <is>
-          <t>跌破5日線、多頭排列、量能溫和放大、接近20日低點</t>
+          <t>跌破5日線、空頭排列、量能未放大</t>
         </is>
       </c>
       <c r="AN136" t="inlineStr">
         <is>
-          <t>5日法人明顯買超</t>
+          <t>法人連續偏買、5日法人明顯買超、外資投信同步買超</t>
         </is>
       </c>
       <c r="AO136" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、多頭排列、量能溫和放大、接近20日低點、5日法人明顯買超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、空頭排列、量能未放大、法人連續偏買、5日法人明顯買超、外資投信同步買超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
@@ -19969,10 +19969,10 @@
         <v>239.18</v>
       </c>
       <c r="H143" t="n">
-        <v>6290591</v>
+        <v>6566591</v>
       </c>
       <c r="I143" t="n">
-        <v>4833961</v>
+        <v>4889161</v>
       </c>
       <c r="J143" t="n">
         <v>249</v>
@@ -22298,10 +22298,10 @@
         <v>80.95</v>
       </c>
       <c r="H160" t="n">
-        <v>2578276</v>
+        <v>2927276</v>
       </c>
       <c r="I160" t="n">
-        <v>2236024</v>
+        <v>2305824</v>
       </c>
       <c r="J160" t="n">
         <v>88</v>
@@ -26682,10 +26682,10 @@
         <v>2277.25</v>
       </c>
       <c r="H192" t="n">
-        <v>951455</v>
+        <v>1009455</v>
       </c>
       <c r="I192" t="n">
-        <v>2605636</v>
+        <v>2617236</v>
       </c>
       <c r="J192" t="n">
         <v>2825</v>
@@ -42163,10 +42163,10 @@
         <v>1804.5</v>
       </c>
       <c r="H305" t="n">
-        <v>31352334</v>
+        <v>31456334</v>
       </c>
       <c r="I305" t="n">
-        <v>20551893</v>
+        <v>20572693</v>
       </c>
       <c r="J305" t="n">
         <v>2135</v>
@@ -43396,10 +43396,10 @@
         <v>4029.25</v>
       </c>
       <c r="H314" t="n">
-        <v>2963845</v>
+        <v>2970845</v>
       </c>
       <c r="I314" t="n">
-        <v>2747276</v>
+        <v>2748676</v>
       </c>
       <c r="J314" t="n">
         <v>4485</v>
@@ -43944,10 +43944,10 @@
         <v>416.88</v>
       </c>
       <c r="H318" t="n">
-        <v>3372394</v>
+        <v>3814394</v>
       </c>
       <c r="I318" t="n">
-        <v>3152828</v>
+        <v>3241228</v>
       </c>
       <c r="J318" t="n">
         <v>525</v>
@@ -44766,10 +44766,10 @@
         <v>141.4</v>
       </c>
       <c r="H324" t="n">
-        <v>45325057</v>
+        <v>45464057</v>
       </c>
       <c r="I324" t="n">
-        <v>213014968</v>
+        <v>213042768</v>
       </c>
       <c r="J324" t="n">
         <v>171.5</v>
@@ -45314,10 +45314,10 @@
         <v>623.65</v>
       </c>
       <c r="H328" t="n">
-        <v>7506972</v>
+        <v>8045972</v>
       </c>
       <c r="I328" t="n">
-        <v>21394582</v>
+        <v>21502382</v>
       </c>
       <c r="J328" t="n">
         <v>712</v>
@@ -45987,22 +45987,22 @@
         </is>
       </c>
       <c r="D333" t="n">
-        <v>13.2</v>
+        <v>13.8</v>
       </c>
       <c r="E333" t="n">
-        <v>14.15</v>
+        <v>13.98</v>
       </c>
       <c r="F333" t="n">
-        <v>14.57</v>
+        <v>14.48</v>
       </c>
       <c r="G333" t="n">
-        <v>15.38</v>
+        <v>15.28</v>
       </c>
       <c r="H333" t="n">
-        <v>1262071</v>
+        <v>1289778</v>
       </c>
       <c r="I333" t="n">
-        <v>1101237</v>
+        <v>1245498</v>
       </c>
       <c r="J333" t="n">
         <v>17.5</v>
@@ -46410,10 +46410,10 @@
         <v>1172.5</v>
       </c>
       <c r="H336" t="n">
-        <v>4120254</v>
+        <v>4149254</v>
       </c>
       <c r="I336" t="n">
-        <v>2839150</v>
+        <v>2844950</v>
       </c>
       <c r="J336" t="n">
         <v>1395</v>
@@ -46658,12 +46658,12 @@
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>3062.TW</t>
+          <t>1590.TW</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>建漢</t>
+          <t>亞德客-KY</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
@@ -46672,28 +46672,28 @@
         </is>
       </c>
       <c r="D338" t="n">
-        <v>19.3</v>
+        <v>1325</v>
       </c>
       <c r="E338" t="n">
-        <v>19.41</v>
+        <v>1359</v>
       </c>
       <c r="F338" t="n">
-        <v>20.3</v>
+        <v>1375</v>
       </c>
       <c r="G338" t="n">
-        <v>21.96</v>
+        <v>1358.5</v>
       </c>
       <c r="H338" t="n">
-        <v>1785247</v>
+        <v>2086066</v>
       </c>
       <c r="I338" t="n">
-        <v>2482827</v>
+        <v>1337764</v>
       </c>
       <c r="J338" t="n">
-        <v>25.3</v>
+        <v>1480</v>
       </c>
       <c r="K338" t="n">
-        <v>18.15</v>
+        <v>1245</v>
       </c>
       <c r="L338" t="inlineStr">
         <is>
@@ -46701,64 +46701,64 @@
         </is>
       </c>
       <c r="M338" t="n">
-        <v>121025</v>
+        <v>-174334</v>
       </c>
       <c r="N338" t="n">
-        <v>-519711</v>
+        <v>-120447</v>
       </c>
       <c r="O338" t="n">
-        <v>-655112</v>
+        <v>-368281</v>
       </c>
       <c r="P338" t="n">
-        <v>-579935</v>
+        <v>-148334</v>
       </c>
       <c r="Q338" t="n">
-        <v>96800</v>
+        <v>-176243</v>
       </c>
       <c r="R338" t="n">
-        <v>-506242</v>
+        <v>-343172</v>
       </c>
       <c r="S338" t="n">
-        <v>-604042</v>
+        <v>-131309</v>
       </c>
       <c r="T338" t="n">
-        <v>-423695</v>
+        <v>-399567</v>
       </c>
       <c r="U338" t="n">
-        <v>0</v>
+        <v>9000</v>
       </c>
       <c r="V338" t="n">
-        <v>0</v>
+        <v>238012</v>
       </c>
       <c r="W338" t="n">
-        <v>0</v>
+        <v>-232948</v>
       </c>
       <c r="X338" t="n">
-        <v>0</v>
+        <v>206052</v>
       </c>
       <c r="Y338" t="n">
-        <v>24225</v>
+        <v>-7091</v>
       </c>
       <c r="Z338" t="n">
-        <v>-13469</v>
+        <v>-15287</v>
       </c>
       <c r="AA338" t="n">
-        <v>-51070</v>
+        <v>-4024</v>
       </c>
       <c r="AB338" t="n">
-        <v>-156240</v>
+        <v>45181</v>
       </c>
       <c r="AC338" t="n">
-        <v>-30</v>
+        <v>-28</v>
       </c>
       <c r="AD338" t="n">
-        <v>-30</v>
+        <v>-28</v>
       </c>
       <c r="AE338" t="n">
-        <v>-45</v>
+        <v>-5</v>
       </c>
       <c r="AF338" t="n">
-        <v>-30</v>
+        <v>-65</v>
       </c>
       <c r="AG338" t="n">
         <v>0</v>
@@ -46778,29 +46778,29 @@
       </c>
       <c r="AM338" t="inlineStr">
         <is>
-          <t>跌破5日線、空頭排列、量能未放大</t>
+          <t>跌破5日線、成交量放大</t>
         </is>
       </c>
       <c r="AN338" t="inlineStr">
         <is>
-          <t>5日法人明顯賣超</t>
+          <t>法人連續偏賣、5日法人賣超、外資投信同步賣超</t>
         </is>
       </c>
       <c r="AO338" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、空頭排列、量能未放大、5日法人明顯賣超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、成交量放大、法人連續偏賣、5日法人賣超、外資投信同步賣超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>1590.TW</t>
+          <t>3062.TW</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>亞德客-KY</t>
+          <t>建漢</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
@@ -46809,28 +46809,28 @@
         </is>
       </c>
       <c r="D339" t="n">
-        <v>1325</v>
+        <v>19.3</v>
       </c>
       <c r="E339" t="n">
-        <v>1359</v>
+        <v>19.41</v>
       </c>
       <c r="F339" t="n">
-        <v>1375</v>
+        <v>20.3</v>
       </c>
       <c r="G339" t="n">
-        <v>1358.5</v>
+        <v>21.96</v>
       </c>
       <c r="H339" t="n">
-        <v>1923066</v>
+        <v>1785247</v>
       </c>
       <c r="I339" t="n">
-        <v>1305164</v>
+        <v>2482827</v>
       </c>
       <c r="J339" t="n">
-        <v>1480</v>
+        <v>25.3</v>
       </c>
       <c r="K339" t="n">
-        <v>1245</v>
+        <v>18.15</v>
       </c>
       <c r="L339" t="inlineStr">
         <is>
@@ -46838,52 +46838,52 @@
         </is>
       </c>
       <c r="M339" t="n">
-        <v>-174334</v>
+        <v>121025</v>
       </c>
       <c r="N339" t="n">
-        <v>-120447</v>
+        <v>-519711</v>
       </c>
       <c r="O339" t="n">
-        <v>-368281</v>
+        <v>-655112</v>
       </c>
       <c r="P339" t="n">
-        <v>-148334</v>
+        <v>-579935</v>
       </c>
       <c r="Q339" t="n">
-        <v>-176243</v>
+        <v>96800</v>
       </c>
       <c r="R339" t="n">
-        <v>-343172</v>
+        <v>-506242</v>
       </c>
       <c r="S339" t="n">
-        <v>-131309</v>
+        <v>-604042</v>
       </c>
       <c r="T339" t="n">
-        <v>-399567</v>
+        <v>-423695</v>
       </c>
       <c r="U339" t="n">
-        <v>9000</v>
+        <v>0</v>
       </c>
       <c r="V339" t="n">
-        <v>238012</v>
+        <v>0</v>
       </c>
       <c r="W339" t="n">
-        <v>-232948</v>
+        <v>0</v>
       </c>
       <c r="X339" t="n">
-        <v>206052</v>
+        <v>0</v>
       </c>
       <c r="Y339" t="n">
-        <v>-7091</v>
+        <v>24225</v>
       </c>
       <c r="Z339" t="n">
-        <v>-15287</v>
+        <v>-13469</v>
       </c>
       <c r="AA339" t="n">
-        <v>-4024</v>
+        <v>-51070</v>
       </c>
       <c r="AB339" t="n">
-        <v>45181</v>
+        <v>-156240</v>
       </c>
       <c r="AC339" t="n">
         <v>-30</v>
@@ -46892,10 +46892,10 @@
         <v>-30</v>
       </c>
       <c r="AE339" t="n">
-        <v>-10</v>
+        <v>-45</v>
       </c>
       <c r="AF339" t="n">
-        <v>-65</v>
+        <v>-30</v>
       </c>
       <c r="AG339" t="n">
         <v>0</v>
@@ -46915,17 +46915,17 @@
       </c>
       <c r="AM339" t="inlineStr">
         <is>
-          <t>跌破5日線、量能溫和放大</t>
+          <t>跌破5日線、空頭排列、量能未放大</t>
         </is>
       </c>
       <c r="AN339" t="inlineStr">
         <is>
-          <t>法人連續偏賣、5日法人賣超、外資投信同步賣超</t>
+          <t>5日法人明顯賣超</t>
         </is>
       </c>
       <c r="AO339" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、量能溫和放大、法人連續偏賣、5日法人賣超、外資投信同步賣超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、空頭排列、量能未放大、5日法人明顯賣超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
@@ -47506,10 +47506,10 @@
         <v>3699.25</v>
       </c>
       <c r="H344" t="n">
-        <v>3224014</v>
+        <v>4033014</v>
       </c>
       <c r="I344" t="n">
-        <v>10923380</v>
+        <v>11085180</v>
       </c>
       <c r="J344" t="n">
         <v>4325</v>
@@ -47643,10 +47643,10 @@
         <v>160.05</v>
       </c>
       <c r="H345" t="n">
-        <v>17897666</v>
+        <v>21043331</v>
       </c>
       <c r="I345" t="n">
-        <v>98991194</v>
+        <v>99620327</v>
       </c>
       <c r="J345" t="n">
         <v>200</v>
@@ -48328,10 +48328,10 @@
         <v>843.65</v>
       </c>
       <c r="H350" t="n">
-        <v>3142252</v>
+        <v>3163252</v>
       </c>
       <c r="I350" t="n">
-        <v>23802285</v>
+        <v>23806485</v>
       </c>
       <c r="J350" t="n">
         <v>982</v>
@@ -50109,10 +50109,10 @@
         <v>22.88</v>
       </c>
       <c r="H363" t="n">
-        <v>3481856</v>
+        <v>3732856</v>
       </c>
       <c r="I363" t="n">
-        <v>2987076</v>
+        <v>3037276</v>
       </c>
       <c r="J363" t="n">
         <v>24.9</v>
@@ -51479,10 +51479,10 @@
         <v>342.18</v>
       </c>
       <c r="H373" t="n">
-        <v>48234092</v>
+        <v>49270092</v>
       </c>
       <c r="I373" t="n">
-        <v>35389916</v>
+        <v>35597116</v>
       </c>
       <c r="J373" t="n">
         <v>393</v>
@@ -52986,10 +52986,10 @@
         <v>730.38</v>
       </c>
       <c r="H384" t="n">
-        <v>6340641</v>
+        <v>6398641</v>
       </c>
       <c r="I384" t="n">
-        <v>51489641</v>
+        <v>51501241</v>
       </c>
       <c r="J384" t="n">
         <v>1075</v>
@@ -54904,10 +54904,10 @@
         <v>87.40000000000001</v>
       </c>
       <c r="H398" t="n">
-        <v>19913625</v>
+        <v>20467625</v>
       </c>
       <c r="I398" t="n">
-        <v>8175150</v>
+        <v>8285950</v>
       </c>
       <c r="J398" t="n">
         <v>93.59999999999999</v>
@@ -55041,10 +55041,10 @@
         <v>39.66</v>
       </c>
       <c r="H399" t="n">
-        <v>3763409</v>
+        <v>4214409</v>
       </c>
       <c r="I399" t="n">
-        <v>3437662</v>
+        <v>3527862</v>
       </c>
       <c r="J399" t="n">
         <v>42.25</v>
@@ -55178,10 +55178,10 @@
         <v>65.11</v>
       </c>
       <c r="H400" t="n">
-        <v>47176584</v>
+        <v>47178584</v>
       </c>
       <c r="I400" t="n">
-        <v>46558082</v>
+        <v>46558482</v>
       </c>
       <c r="J400" t="n">
         <v>77.59999999999999</v>

--- a/output/universe_analysis_result.xlsx
+++ b/output/universe_analysis_result.xlsx
@@ -789,10 +789,10 @@
         <v>160.32</v>
       </c>
       <c r="H3" t="n">
-        <v>147901367</v>
+        <v>153901367</v>
       </c>
       <c r="I3" t="n">
-        <v>137427768</v>
+        <v>138627768</v>
       </c>
       <c r="J3" t="n">
         <v>198</v>
@@ -1063,10 +1063,10 @@
         <v>3390.5</v>
       </c>
       <c r="H5" t="n">
-        <v>2780267</v>
+        <v>2786267</v>
       </c>
       <c r="I5" t="n">
-        <v>1881346</v>
+        <v>1882546</v>
       </c>
       <c r="J5" t="n">
         <v>4145</v>
@@ -1337,10 +1337,10 @@
         <v>734.85</v>
       </c>
       <c r="H7" t="n">
-        <v>4048111</v>
+        <v>4052111</v>
       </c>
       <c r="I7" t="n">
-        <v>5961399</v>
+        <v>5962199</v>
       </c>
       <c r="J7" t="n">
         <v>816</v>
@@ -2707,10 +2707,10 @@
         <v>96.88</v>
       </c>
       <c r="H17" t="n">
-        <v>25119993</v>
+        <v>25339993</v>
       </c>
       <c r="I17" t="n">
-        <v>30065284</v>
+        <v>30109284</v>
       </c>
       <c r="J17" t="n">
         <v>102.5</v>
@@ -2844,10 +2844,10 @@
         <v>242.62</v>
       </c>
       <c r="H18" t="n">
-        <v>41037656</v>
+        <v>41095656</v>
       </c>
       <c r="I18" t="n">
-        <v>71037558</v>
+        <v>71049158</v>
       </c>
       <c r="J18" t="n">
         <v>259.5</v>
@@ -4077,10 +4077,10 @@
         <v>498.5</v>
       </c>
       <c r="H27" t="n">
-        <v>4335914</v>
+        <v>4340914</v>
       </c>
       <c r="I27" t="n">
-        <v>5157693</v>
+        <v>5158693</v>
       </c>
       <c r="J27" t="n">
         <v>553</v>
@@ -10653,10 +10653,10 @@
         <v>838.8</v>
       </c>
       <c r="H75" t="n">
-        <v>53849638</v>
+        <v>54032638</v>
       </c>
       <c r="I75" t="n">
-        <v>32319304</v>
+        <v>32355904</v>
       </c>
       <c r="J75" t="n">
         <v>960</v>
@@ -24353,10 +24353,10 @@
         <v>462.2</v>
       </c>
       <c r="H175" t="n">
-        <v>5927218</v>
+        <v>5973218</v>
       </c>
       <c r="I175" t="n">
-        <v>5528571</v>
+        <v>5537771</v>
       </c>
       <c r="J175" t="n">
         <v>620</v>
@@ -27093,10 +27093,10 @@
         <v>6218</v>
       </c>
       <c r="H195" t="n">
-        <v>812749</v>
+        <v>910749</v>
       </c>
       <c r="I195" t="n">
-        <v>1162648</v>
+        <v>1182248</v>
       </c>
       <c r="J195" t="n">
         <v>6995</v>
@@ -28600,10 +28600,10 @@
         <v>101.76</v>
       </c>
       <c r="H206" t="n">
-        <v>10580734</v>
+        <v>11770734</v>
       </c>
       <c r="I206" t="n">
-        <v>15231106</v>
+        <v>15469106</v>
       </c>
       <c r="J206" t="n">
         <v>108.5</v>
@@ -36272,10 +36272,10 @@
         <v>3672</v>
       </c>
       <c r="H262" t="n">
-        <v>16854591</v>
+        <v>17318591</v>
       </c>
       <c r="I262" t="n">
-        <v>11740726</v>
+        <v>11833526</v>
       </c>
       <c r="J262" t="n">
         <v>4250</v>
@@ -42574,10 +42574,10 @@
         <v>1761</v>
       </c>
       <c r="H308" t="n">
-        <v>20957807</v>
+        <v>20958807</v>
       </c>
       <c r="I308" t="n">
-        <v>22956025</v>
+        <v>22956225</v>
       </c>
       <c r="J308" t="n">
         <v>2025</v>
@@ -44355,10 +44355,10 @@
         <v>683.77</v>
       </c>
       <c r="H321" t="n">
-        <v>86121584</v>
+        <v>97625584</v>
       </c>
       <c r="I321" t="n">
-        <v>54699219</v>
+        <v>57000019</v>
       </c>
       <c r="J321" t="n">
         <v>1025</v>
@@ -44492,10 +44492,10 @@
         <v>615.35</v>
       </c>
       <c r="H322" t="n">
-        <v>52231565</v>
+        <v>52645565</v>
       </c>
       <c r="I322" t="n">
-        <v>26366326</v>
+        <v>26449126</v>
       </c>
       <c r="J322" t="n">
         <v>702</v>
@@ -45862,10 +45862,10 @@
         <v>273.65</v>
       </c>
       <c r="H332" t="n">
-        <v>31596298</v>
+        <v>31680298</v>
       </c>
       <c r="I332" t="n">
-        <v>26026413</v>
+        <v>26043213</v>
       </c>
       <c r="J332" t="n">
         <v>355</v>
@@ -48328,10 +48328,10 @@
         <v>2370.75</v>
       </c>
       <c r="H350" t="n">
-        <v>40650199</v>
+        <v>41021199</v>
       </c>
       <c r="I350" t="n">
-        <v>52970031</v>
+        <v>53044231</v>
       </c>
       <c r="J350" t="n">
         <v>2500</v>
@@ -48739,10 +48739,10 @@
         <v>1951.75</v>
       </c>
       <c r="H353" t="n">
-        <v>6052684</v>
+        <v>6067684</v>
       </c>
       <c r="I353" t="n">
-        <v>5182189</v>
+        <v>5185189</v>
       </c>
       <c r="J353" t="n">
         <v>2215</v>
@@ -49013,10 +49013,10 @@
         <v>939.1</v>
       </c>
       <c r="H355" t="n">
-        <v>13583855</v>
+        <v>13604855</v>
       </c>
       <c r="I355" t="n">
-        <v>7846200</v>
+        <v>7850400</v>
       </c>
       <c r="J355" t="n">
         <v>1220</v>
@@ -52027,10 +52027,10 @@
         <v>59.88</v>
       </c>
       <c r="H377" t="n">
-        <v>23195509</v>
+        <v>23236509</v>
       </c>
       <c r="I377" t="n">
-        <v>36432620</v>
+        <v>36440820</v>
       </c>
       <c r="J377" t="n">
         <v>69.8</v>

--- a/output/universe_analysis_result.xlsx
+++ b/output/universe_analysis_result.xlsx
@@ -1885,10 +1885,10 @@
         <v>243.7</v>
       </c>
       <c r="H11" t="n">
-        <v>72613762</v>
+        <v>72633762</v>
       </c>
       <c r="I11" t="n">
-        <v>68584417</v>
+        <v>68588417</v>
       </c>
       <c r="J11" t="n">
         <v>260.5</v>
@@ -2707,10 +2707,10 @@
         <v>845.25</v>
       </c>
       <c r="H17" t="n">
-        <v>44511982</v>
+        <v>44514982</v>
       </c>
       <c r="I17" t="n">
-        <v>35060870</v>
+        <v>35061470</v>
       </c>
       <c r="J17" t="n">
         <v>1010</v>
@@ -2981,10 +2981,10 @@
         <v>213.2</v>
       </c>
       <c r="H19" t="n">
-        <v>90341678</v>
+        <v>90355678</v>
       </c>
       <c r="I19" t="n">
-        <v>44282561</v>
+        <v>44285361</v>
       </c>
       <c r="J19" t="n">
         <v>268.5</v>
@@ -5447,10 +5447,10 @@
         <v>3670.5</v>
       </c>
       <c r="H37" t="n">
-        <v>12448125</v>
+        <v>12935125</v>
       </c>
       <c r="I37" t="n">
-        <v>11088326</v>
+        <v>11185726</v>
       </c>
       <c r="J37" t="n">
         <v>4125</v>
@@ -10516,10 +10516,10 @@
         <v>156.43</v>
       </c>
       <c r="H74" t="n">
-        <v>230051989</v>
+        <v>232656923</v>
       </c>
       <c r="I74" t="n">
-        <v>132332074</v>
+        <v>132853060</v>
       </c>
       <c r="J74" t="n">
         <v>184</v>
@@ -12434,10 +12434,10 @@
         <v>558.25</v>
       </c>
       <c r="H88" t="n">
-        <v>4138154</v>
+        <v>4139154</v>
       </c>
       <c r="I88" t="n">
-        <v>4958019</v>
+        <v>4958219</v>
       </c>
       <c r="J88" t="n">
         <v>633</v>
@@ -17751,12 +17751,12 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>2546.TW</t>
+          <t>8215.TW</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>根基</t>
+          <t>明基材</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -17765,28 +17765,28 @@
         </is>
       </c>
       <c r="D127" t="n">
-        <v>99.2</v>
+        <v>23.85</v>
       </c>
       <c r="E127" t="n">
-        <v>98.14</v>
+        <v>22.88</v>
       </c>
       <c r="F127" t="n">
-        <v>95.45999999999999</v>
+        <v>23.18</v>
       </c>
       <c r="G127" t="n">
-        <v>94.31</v>
+        <v>24.84</v>
       </c>
       <c r="H127" t="n">
-        <v>346686</v>
+        <v>588117</v>
       </c>
       <c r="I127" t="n">
-        <v>305199</v>
+        <v>662808</v>
       </c>
       <c r="J127" t="n">
-        <v>105</v>
+        <v>29.1</v>
       </c>
       <c r="K127" t="n">
-        <v>86</v>
+        <v>21</v>
       </c>
       <c r="L127" t="inlineStr">
         <is>
@@ -17794,52 +17794,52 @@
         </is>
       </c>
       <c r="M127" t="n">
-        <v>-115540</v>
+        <v>143276</v>
       </c>
       <c r="N127" t="n">
-        <v>-227800</v>
+        <v>262343</v>
       </c>
       <c r="O127" t="n">
-        <v>85160</v>
+        <v>234967</v>
       </c>
       <c r="P127" t="n">
-        <v>348559</v>
+        <v>-475045</v>
       </c>
       <c r="Q127" t="n">
-        <v>-115540</v>
+        <v>144220</v>
       </c>
       <c r="R127" t="n">
-        <v>-358680</v>
+        <v>290698</v>
       </c>
       <c r="S127" t="n">
-        <v>-36720</v>
+        <v>248185</v>
       </c>
       <c r="T127" t="n">
-        <v>199679</v>
+        <v>-449513</v>
       </c>
       <c r="U127" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="V127" t="n">
-        <v>163000</v>
+        <v>1000</v>
       </c>
       <c r="W127" t="n">
-        <v>163000</v>
+        <v>13000</v>
       </c>
       <c r="X127" t="n">
-        <v>164000</v>
+        <v>15000</v>
       </c>
       <c r="Y127" t="n">
-        <v>0</v>
+        <v>-1944</v>
       </c>
       <c r="Z127" t="n">
-        <v>-32120</v>
+        <v>-29355</v>
       </c>
       <c r="AA127" t="n">
-        <v>-41120</v>
+        <v>-26218</v>
       </c>
       <c r="AB127" t="n">
-        <v>-15120</v>
+        <v>-40532</v>
       </c>
       <c r="AC127" t="n">
         <v>26</v>
@@ -17848,10 +17848,10 @@
         <v>26</v>
       </c>
       <c r="AE127" t="n">
-        <v>55</v>
+        <v>-5</v>
       </c>
       <c r="AF127" t="n">
-        <v>10</v>
+        <v>70</v>
       </c>
       <c r="AG127" t="n">
         <v>0</v>
@@ -17871,17 +17871,17 @@
       </c>
       <c r="AM127" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、量能溫和放大</t>
+          <t>站上5日線、空頭排列、量能未放大</t>
         </is>
       </c>
       <c r="AN127" t="inlineStr">
         <is>
-          <t>5日法人小幅買超、投信買外資賣</t>
+          <t>法人連續偏買、5日法人買超、外資投信同步買超</t>
         </is>
       </c>
       <c r="AO127" t="inlineStr">
         <is>
-          <t>整理觀察：站上5日線、多頭排列、量能溫和放大、5日法人小幅買超、投信買外資賣。多空訊號混合，建議降低追價衝動。</t>
+          <t>整理觀察：站上5日線、空頭排列、量能未放大、法人連續偏買、5日法人買超、外資投信同步買超。多空訊號混合，建議降低追價衝動。</t>
         </is>
       </c>
     </row>
@@ -18025,42 +18025,42 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>8215.TW</t>
+          <t>00946.TW</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>明基材</t>
+          <t>群益科技高息成長</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>個股</t>
+          <t>ETF</t>
         </is>
       </c>
       <c r="D129" t="n">
-        <v>23.85</v>
+        <v>15.06</v>
       </c>
       <c r="E129" t="n">
-        <v>22.88</v>
+        <v>14.5</v>
       </c>
       <c r="F129" t="n">
-        <v>23.18</v>
+        <v>14.61</v>
       </c>
       <c r="G129" t="n">
-        <v>24.84</v>
+        <v>14.72</v>
       </c>
       <c r="H129" t="n">
-        <v>588117</v>
+        <v>3021212</v>
       </c>
       <c r="I129" t="n">
-        <v>662808</v>
+        <v>3006206</v>
       </c>
       <c r="J129" t="n">
-        <v>29.1</v>
+        <v>15.6</v>
       </c>
       <c r="K129" t="n">
-        <v>21</v>
+        <v>13.64</v>
       </c>
       <c r="L129" t="inlineStr">
         <is>
@@ -18068,52 +18068,52 @@
         </is>
       </c>
       <c r="M129" t="n">
-        <v>143276</v>
+        <v>1794645</v>
       </c>
       <c r="N129" t="n">
-        <v>262343</v>
+        <v>3534695</v>
       </c>
       <c r="O129" t="n">
-        <v>234967</v>
+        <v>3615448</v>
       </c>
       <c r="P129" t="n">
-        <v>-475045</v>
+        <v>7574993</v>
       </c>
       <c r="Q129" t="n">
-        <v>144220</v>
+        <v>196000</v>
       </c>
       <c r="R129" t="n">
-        <v>290698</v>
+        <v>1411020</v>
       </c>
       <c r="S129" t="n">
-        <v>248185</v>
+        <v>54020</v>
       </c>
       <c r="T129" t="n">
-        <v>-449513</v>
+        <v>-1533900</v>
       </c>
       <c r="U129" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="V129" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="W129" t="n">
-        <v>13000</v>
+        <v>0</v>
       </c>
       <c r="X129" t="n">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="Y129" t="n">
-        <v>-1944</v>
+        <v>1598645</v>
       </c>
       <c r="Z129" t="n">
-        <v>-29355</v>
+        <v>2123675</v>
       </c>
       <c r="AA129" t="n">
-        <v>-26218</v>
+        <v>3561428</v>
       </c>
       <c r="AB129" t="n">
-        <v>-40532</v>
+        <v>9108893</v>
       </c>
       <c r="AC129" t="n">
         <v>26</v>
@@ -18122,10 +18122,10 @@
         <v>26</v>
       </c>
       <c r="AE129" t="n">
-        <v>-5</v>
+        <v>5</v>
       </c>
       <c r="AF129" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="AG129" t="n">
         <v>0</v>
@@ -18145,59 +18145,59 @@
       </c>
       <c r="AM129" t="inlineStr">
         <is>
-          <t>站上5日線、空頭排列、量能未放大</t>
+          <t>站上5日線、空頭排列、量能溫和放大</t>
         </is>
       </c>
       <c r="AN129" t="inlineStr">
         <is>
-          <t>法人連續偏買、5日法人買超、外資投信同步買超</t>
+          <t>法人連續偏買、5日法人明顯買超</t>
         </is>
       </c>
       <c r="AO129" t="inlineStr">
         <is>
-          <t>整理觀察：站上5日線、空頭排列、量能未放大、法人連續偏買、5日法人買超、外資投信同步買超。多空訊號混合，建議降低追價衝動。</t>
+          <t>整理觀察：站上5日線、空頭排列、量能溫和放大、法人連續偏買、5日法人明顯買超。多空訊號混合，建議降低追價衝動。</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>00946.TW</t>
+          <t>2471.TW</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>群益科技高息成長</t>
+          <t>資通</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>ETF</t>
+          <t>個股</t>
         </is>
       </c>
       <c r="D130" t="n">
-        <v>15.06</v>
+        <v>49</v>
       </c>
       <c r="E130" t="n">
-        <v>14.5</v>
+        <v>48.28</v>
       </c>
       <c r="F130" t="n">
-        <v>14.61</v>
+        <v>48.25</v>
       </c>
       <c r="G130" t="n">
-        <v>14.72</v>
+        <v>50.18</v>
       </c>
       <c r="H130" t="n">
-        <v>3021212</v>
+        <v>114848</v>
       </c>
       <c r="I130" t="n">
-        <v>3006206</v>
+        <v>122057</v>
       </c>
       <c r="J130" t="n">
-        <v>15.6</v>
+        <v>54.1</v>
       </c>
       <c r="K130" t="n">
-        <v>13.64</v>
+        <v>46.45</v>
       </c>
       <c r="L130" t="inlineStr">
         <is>
@@ -18205,28 +18205,28 @@
         </is>
       </c>
       <c r="M130" t="n">
-        <v>1794645</v>
+        <v>46970</v>
       </c>
       <c r="N130" t="n">
-        <v>3534695</v>
+        <v>83970</v>
       </c>
       <c r="O130" t="n">
-        <v>3615448</v>
+        <v>91970</v>
       </c>
       <c r="P130" t="n">
-        <v>7574993</v>
+        <v>-311261</v>
       </c>
       <c r="Q130" t="n">
-        <v>196000</v>
+        <v>47970</v>
       </c>
       <c r="R130" t="n">
-        <v>1411020</v>
+        <v>86970</v>
       </c>
       <c r="S130" t="n">
-        <v>54020</v>
+        <v>104970</v>
       </c>
       <c r="T130" t="n">
-        <v>-1533900</v>
+        <v>-258261</v>
       </c>
       <c r="U130" t="n">
         <v>0</v>
@@ -18241,28 +18241,28 @@
         <v>0</v>
       </c>
       <c r="Y130" t="n">
-        <v>1598645</v>
+        <v>-1000</v>
       </c>
       <c r="Z130" t="n">
-        <v>2123675</v>
+        <v>-3000</v>
       </c>
       <c r="AA130" t="n">
-        <v>3561428</v>
+        <v>-13000</v>
       </c>
       <c r="AB130" t="n">
-        <v>9108893</v>
+        <v>-53000</v>
       </c>
       <c r="AC130" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AD130" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AE130" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="AF130" t="n">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="AG130" t="n">
         <v>0</v>
@@ -18282,17 +18282,17 @@
       </c>
       <c r="AM130" t="inlineStr">
         <is>
-          <t>站上5日線、空頭排列、量能溫和放大</t>
+          <t>站上5日線、量能未放大</t>
         </is>
       </c>
       <c r="AN130" t="inlineStr">
         <is>
-          <t>法人連續偏買、5日法人明顯買超</t>
+          <t>法人連續偏買、5日法人小幅買超</t>
         </is>
       </c>
       <c r="AO130" t="inlineStr">
         <is>
-          <t>整理觀察：站上5日線、空頭排列、量能溫和放大、法人連續偏買、5日法人明顯買超。多空訊號混合，建議降低追價衝動。</t>
+          <t>整理觀察：站上5日線、量能未放大、法人連續偏買、5日法人小幅買超。多空訊號混合，建議降低追價衝動。</t>
         </is>
       </c>
     </row>
@@ -18436,12 +18436,12 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>2471.TW</t>
+          <t>1736.TW</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>資通</t>
+          <t>喬山</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -18450,28 +18450,28 @@
         </is>
       </c>
       <c r="D132" t="n">
-        <v>49</v>
+        <v>134.5</v>
       </c>
       <c r="E132" t="n">
-        <v>48.28</v>
+        <v>127.5</v>
       </c>
       <c r="F132" t="n">
-        <v>48.25</v>
+        <v>130.4</v>
       </c>
       <c r="G132" t="n">
-        <v>50.18</v>
+        <v>131.15</v>
       </c>
       <c r="H132" t="n">
-        <v>114848</v>
+        <v>1571420</v>
       </c>
       <c r="I132" t="n">
-        <v>122057</v>
+        <v>947488</v>
       </c>
       <c r="J132" t="n">
-        <v>54.1</v>
+        <v>142.5</v>
       </c>
       <c r="K132" t="n">
-        <v>46.45</v>
+        <v>120</v>
       </c>
       <c r="L132" t="inlineStr">
         <is>
@@ -18479,52 +18479,52 @@
         </is>
       </c>
       <c r="M132" t="n">
-        <v>46970</v>
+        <v>789882</v>
       </c>
       <c r="N132" t="n">
-        <v>83970</v>
+        <v>839389</v>
       </c>
       <c r="O132" t="n">
-        <v>91970</v>
+        <v>437385</v>
       </c>
       <c r="P132" t="n">
-        <v>-311261</v>
+        <v>87714</v>
       </c>
       <c r="Q132" t="n">
-        <v>47970</v>
+        <v>421380</v>
       </c>
       <c r="R132" t="n">
-        <v>86970</v>
+        <v>306887</v>
       </c>
       <c r="S132" t="n">
-        <v>104970</v>
+        <v>-103352</v>
       </c>
       <c r="T132" t="n">
-        <v>-258261</v>
+        <v>-593770</v>
       </c>
       <c r="U132" t="n">
-        <v>0</v>
+        <v>372000</v>
       </c>
       <c r="V132" t="n">
-        <v>0</v>
+        <v>561000</v>
       </c>
       <c r="W132" t="n">
-        <v>0</v>
+        <v>565000</v>
       </c>
       <c r="X132" t="n">
-        <v>0</v>
+        <v>690000</v>
       </c>
       <c r="Y132" t="n">
-        <v>-1000</v>
+        <v>-3498</v>
       </c>
       <c r="Z132" t="n">
-        <v>-3000</v>
+        <v>-28498</v>
       </c>
       <c r="AA132" t="n">
-        <v>-13000</v>
+        <v>-24263</v>
       </c>
       <c r="AB132" t="n">
-        <v>-53000</v>
+        <v>-8516</v>
       </c>
       <c r="AC132" t="n">
         <v>24</v>
@@ -18533,10 +18533,10 @@
         <v>24</v>
       </c>
       <c r="AE132" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="AF132" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="AG132" t="n">
         <v>0</v>
@@ -18556,17 +18556,17 @@
       </c>
       <c r="AM132" t="inlineStr">
         <is>
-          <t>站上5日線、量能未放大</t>
+          <t>站上5日線、空頭排列、成交量放大</t>
         </is>
       </c>
       <c r="AN132" t="inlineStr">
         <is>
-          <t>法人連續偏買、5日法人小幅買超</t>
+          <t>法人連續偏買、5日法人買超、投信買外資賣</t>
         </is>
       </c>
       <c r="AO132" t="inlineStr">
         <is>
-          <t>整理觀察：站上5日線、量能未放大、法人連續偏買、5日法人小幅買超。多空訊號混合，建議降低追價衝動。</t>
+          <t>整理觀察：站上5日線、空頭排列、成交量放大、法人連續偏買、5日法人買超、投信買外資賣。多空訊號混合，建議降低追價衝動。</t>
         </is>
       </c>
     </row>
@@ -18710,12 +18710,12 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>1736.TW</t>
+          <t>1513.TW</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>喬山</t>
+          <t>中興電</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -18724,28 +18724,28 @@
         </is>
       </c>
       <c r="D134" t="n">
-        <v>134.5</v>
+        <v>161</v>
       </c>
       <c r="E134" t="n">
-        <v>127.5</v>
+        <v>155.2</v>
       </c>
       <c r="F134" t="n">
-        <v>130.4</v>
+        <v>155.45</v>
       </c>
       <c r="G134" t="n">
-        <v>131.15</v>
+        <v>160.28</v>
       </c>
       <c r="H134" t="n">
-        <v>1571420</v>
+        <v>2416786</v>
       </c>
       <c r="I134" t="n">
-        <v>947488</v>
+        <v>2972268</v>
       </c>
       <c r="J134" t="n">
-        <v>142.5</v>
+        <v>177</v>
       </c>
       <c r="K134" t="n">
-        <v>120</v>
+        <v>145.5</v>
       </c>
       <c r="L134" t="inlineStr">
         <is>
@@ -18753,64 +18753,64 @@
         </is>
       </c>
       <c r="M134" t="n">
-        <v>789882</v>
+        <v>973971</v>
       </c>
       <c r="N134" t="n">
-        <v>839389</v>
+        <v>2664838</v>
       </c>
       <c r="O134" t="n">
-        <v>437385</v>
+        <v>3867882</v>
       </c>
       <c r="P134" t="n">
-        <v>87714</v>
+        <v>-544469</v>
       </c>
       <c r="Q134" t="n">
-        <v>421380</v>
+        <v>1000710</v>
       </c>
       <c r="R134" t="n">
-        <v>306887</v>
+        <v>2844427</v>
       </c>
       <c r="S134" t="n">
-        <v>-103352</v>
+        <v>4019376</v>
       </c>
       <c r="T134" t="n">
-        <v>-593770</v>
+        <v>793956</v>
       </c>
       <c r="U134" t="n">
-        <v>372000</v>
+        <v>-4330</v>
       </c>
       <c r="V134" t="n">
-        <v>561000</v>
+        <v>-166625</v>
       </c>
       <c r="W134" t="n">
-        <v>565000</v>
+        <v>-174120</v>
       </c>
       <c r="X134" t="n">
-        <v>690000</v>
+        <v>-799641</v>
       </c>
       <c r="Y134" t="n">
-        <v>-3498</v>
+        <v>-22409</v>
       </c>
       <c r="Z134" t="n">
-        <v>-28498</v>
+        <v>-12964</v>
       </c>
       <c r="AA134" t="n">
-        <v>-24263</v>
+        <v>22626</v>
       </c>
       <c r="AB134" t="n">
-        <v>-8516</v>
+        <v>-538784</v>
       </c>
       <c r="AC134" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AD134" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AE134" t="n">
-        <v>10</v>
+        <v>-5</v>
       </c>
       <c r="AF134" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="AG134" t="n">
         <v>0</v>
@@ -18830,17 +18830,17 @@
       </c>
       <c r="AM134" t="inlineStr">
         <is>
-          <t>站上5日線、空頭排列、成交量放大</t>
+          <t>站上5日線、空頭排列、量能未放大</t>
         </is>
       </c>
       <c r="AN134" t="inlineStr">
         <is>
-          <t>法人連續偏買、5日法人買超、投信買外資賣</t>
+          <t>法人連續偏買、5日法人明顯買超、外資買投信賣</t>
         </is>
       </c>
       <c r="AO134" t="inlineStr">
         <is>
-          <t>整理觀察：站上5日線、空頭排列、成交量放大、法人連續偏買、5日法人買超、投信買外資賣。多空訊號混合，建議降低追價衝動。</t>
+          <t>整理觀察：站上5日線、空頭排列、量能未放大、法人連續偏買、5日法人明顯買超、外資買投信賣。多空訊號混合，建議降低追價衝動。</t>
         </is>
       </c>
     </row>
@@ -19943,12 +19943,12 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>3673.TW</t>
+          <t>2457.TW</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>TPK-KY</t>
+          <t>飛宏</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -19957,28 +19957,28 @@
         </is>
       </c>
       <c r="D143" t="n">
-        <v>61.6</v>
+        <v>23.8</v>
       </c>
       <c r="E143" t="n">
-        <v>56.9</v>
+        <v>22.08</v>
       </c>
       <c r="F143" t="n">
-        <v>58.34</v>
+        <v>22.6</v>
       </c>
       <c r="G143" t="n">
-        <v>64.61</v>
+        <v>24.39</v>
       </c>
       <c r="H143" t="n">
-        <v>5819951</v>
+        <v>1544903</v>
       </c>
       <c r="I143" t="n">
-        <v>5372326</v>
+        <v>2276787</v>
       </c>
       <c r="J143" t="n">
-        <v>82.7</v>
+        <v>29</v>
       </c>
       <c r="K143" t="n">
-        <v>50.1</v>
+        <v>19.9</v>
       </c>
       <c r="L143" t="inlineStr">
         <is>
@@ -19986,28 +19986,28 @@
         </is>
       </c>
       <c r="M143" t="n">
-        <v>294328</v>
+        <v>618628</v>
       </c>
       <c r="N143" t="n">
-        <v>997677</v>
+        <v>1476178</v>
       </c>
       <c r="O143" t="n">
-        <v>419231</v>
+        <v>1689846</v>
       </c>
       <c r="P143" t="n">
-        <v>3269457</v>
+        <v>-1015703</v>
       </c>
       <c r="Q143" t="n">
-        <v>188212</v>
+        <v>587260</v>
       </c>
       <c r="R143" t="n">
-        <v>813119</v>
+        <v>1496038</v>
       </c>
       <c r="S143" t="n">
-        <v>347740</v>
+        <v>1700360</v>
       </c>
       <c r="T143" t="n">
-        <v>3724311</v>
+        <v>-713116</v>
       </c>
       <c r="U143" t="n">
         <v>0</v>
@@ -20019,19 +20019,19 @@
         <v>0</v>
       </c>
       <c r="X143" t="n">
-        <v>4000</v>
+        <v>0</v>
       </c>
       <c r="Y143" t="n">
-        <v>106116</v>
+        <v>31368</v>
       </c>
       <c r="Z143" t="n">
-        <v>184558</v>
+        <v>-19860</v>
       </c>
       <c r="AA143" t="n">
-        <v>71491</v>
+        <v>-10514</v>
       </c>
       <c r="AB143" t="n">
-        <v>-458854</v>
+        <v>-302587</v>
       </c>
       <c r="AC143" t="n">
         <v>22</v>
@@ -20040,10 +20040,10 @@
         <v>22</v>
       </c>
       <c r="AE143" t="n">
-        <v>5</v>
+        <v>-5</v>
       </c>
       <c r="AF143" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="AG143" t="n">
         <v>0</v>
@@ -20063,29 +20063,29 @@
       </c>
       <c r="AM143" t="inlineStr">
         <is>
-          <t>站上5日線、空頭排列、量能溫和放大</t>
+          <t>站上5日線、空頭排列、量能未放大</t>
         </is>
       </c>
       <c r="AN143" t="inlineStr">
         <is>
-          <t>法人連續偏買、5日法人買超</t>
+          <t>法人連續偏買、5日法人明顯買超</t>
         </is>
       </c>
       <c r="AO143" t="inlineStr">
         <is>
-          <t>整理觀察：站上5日線、空頭排列、量能溫和放大、法人連續偏買、5日法人買超。多空訊號混合，建議降低追價衝動。</t>
+          <t>整理觀察：站上5日線、空頭排列、量能未放大、法人連續偏買、5日法人明顯買超。多空訊號混合，建議降低追價衝動。</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>1513.TW</t>
+          <t>3673.TW</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>中興電</t>
+          <t>TPK-KY</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -20094,28 +20094,28 @@
         </is>
       </c>
       <c r="D144" t="n">
-        <v>161</v>
+        <v>61.6</v>
       </c>
       <c r="E144" t="n">
-        <v>155.2</v>
+        <v>56.9</v>
       </c>
       <c r="F144" t="n">
-        <v>155.45</v>
+        <v>58.34</v>
       </c>
       <c r="G144" t="n">
-        <v>160.28</v>
+        <v>64.61</v>
       </c>
       <c r="H144" t="n">
-        <v>2416786</v>
+        <v>5819951</v>
       </c>
       <c r="I144" t="n">
-        <v>2972268</v>
+        <v>5372326</v>
       </c>
       <c r="J144" t="n">
-        <v>177</v>
+        <v>82.7</v>
       </c>
       <c r="K144" t="n">
-        <v>145.5</v>
+        <v>50.1</v>
       </c>
       <c r="L144" t="inlineStr">
         <is>
@@ -20123,52 +20123,52 @@
         </is>
       </c>
       <c r="M144" t="n">
-        <v>973971</v>
+        <v>294328</v>
       </c>
       <c r="N144" t="n">
-        <v>2664838</v>
+        <v>997677</v>
       </c>
       <c r="O144" t="n">
-        <v>3867882</v>
+        <v>419231</v>
       </c>
       <c r="P144" t="n">
-        <v>-544469</v>
+        <v>3269457</v>
       </c>
       <c r="Q144" t="n">
-        <v>1000710</v>
+        <v>188212</v>
       </c>
       <c r="R144" t="n">
-        <v>2844427</v>
+        <v>813119</v>
       </c>
       <c r="S144" t="n">
-        <v>4019376</v>
+        <v>347740</v>
       </c>
       <c r="T144" t="n">
-        <v>793956</v>
+        <v>3724311</v>
       </c>
       <c r="U144" t="n">
-        <v>-4330</v>
+        <v>0</v>
       </c>
       <c r="V144" t="n">
-        <v>-166625</v>
+        <v>0</v>
       </c>
       <c r="W144" t="n">
-        <v>-174120</v>
+        <v>0</v>
       </c>
       <c r="X144" t="n">
-        <v>-799641</v>
+        <v>4000</v>
       </c>
       <c r="Y144" t="n">
-        <v>-22409</v>
+        <v>106116</v>
       </c>
       <c r="Z144" t="n">
-        <v>-12964</v>
+        <v>184558</v>
       </c>
       <c r="AA144" t="n">
-        <v>22626</v>
+        <v>71491</v>
       </c>
       <c r="AB144" t="n">
-        <v>-538784</v>
+        <v>-458854</v>
       </c>
       <c r="AC144" t="n">
         <v>22</v>
@@ -20177,10 +20177,10 @@
         <v>22</v>
       </c>
       <c r="AE144" t="n">
-        <v>-5</v>
+        <v>5</v>
       </c>
       <c r="AF144" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AG144" t="n">
         <v>0</v>
@@ -20200,17 +20200,17 @@
       </c>
       <c r="AM144" t="inlineStr">
         <is>
-          <t>站上5日線、空頭排列、量能未放大</t>
+          <t>站上5日線、空頭排列、量能溫和放大</t>
         </is>
       </c>
       <c r="AN144" t="inlineStr">
         <is>
-          <t>法人連續偏買、5日法人明顯買超、外資買投信賣</t>
+          <t>法人連續偏買、5日法人買超</t>
         </is>
       </c>
       <c r="AO144" t="inlineStr">
         <is>
-          <t>整理觀察：站上5日線、空頭排列、量能未放大、法人連續偏買、5日法人明顯買超、外資買投信賣。多空訊號混合，建議降低追價衝動。</t>
+          <t>整理觀察：站上5日線、空頭排列、量能溫和放大、法人連續偏買、5日法人買超。多空訊號混合，建議降低追價衝動。</t>
         </is>
       </c>
     </row>
@@ -20902,12 +20902,12 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>2405.TW</t>
+          <t>5880.TW</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>輔信</t>
+          <t>合庫金</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -20916,28 +20916,28 @@
         </is>
       </c>
       <c r="D150" t="n">
-        <v>16.3</v>
+        <v>26.6</v>
       </c>
       <c r="E150" t="n">
-        <v>15.78</v>
+        <v>26.93</v>
       </c>
       <c r="F150" t="n">
-        <v>15.86</v>
+        <v>26.39</v>
       </c>
       <c r="G150" t="n">
-        <v>16.41</v>
+        <v>25.88</v>
       </c>
       <c r="H150" t="n">
-        <v>1240343</v>
+        <v>18998546</v>
       </c>
       <c r="I150" t="n">
-        <v>1304826</v>
+        <v>40437237</v>
       </c>
       <c r="J150" t="n">
-        <v>18.4</v>
+        <v>27.65</v>
       </c>
       <c r="K150" t="n">
-        <v>14.5</v>
+        <v>24.85</v>
       </c>
       <c r="L150" t="inlineStr">
         <is>
@@ -20945,52 +20945,52 @@
         </is>
       </c>
       <c r="M150" t="n">
-        <v>170270</v>
+        <v>-803048</v>
       </c>
       <c r="N150" t="n">
-        <v>1009270</v>
+        <v>-8138821</v>
       </c>
       <c r="O150" t="n">
-        <v>1049560</v>
+        <v>62870695</v>
       </c>
       <c r="P150" t="n">
-        <v>-635440</v>
+        <v>111195163</v>
       </c>
       <c r="Q150" t="n">
-        <v>170270</v>
+        <v>-725397</v>
       </c>
       <c r="R150" t="n">
-        <v>1045270</v>
+        <v>-12660332</v>
       </c>
       <c r="S150" t="n">
-        <v>1090560</v>
+        <v>55964113</v>
       </c>
       <c r="T150" t="n">
-        <v>-625440</v>
+        <v>96148070</v>
       </c>
       <c r="U150" t="n">
-        <v>0</v>
+        <v>-24651</v>
       </c>
       <c r="V150" t="n">
-        <v>0</v>
+        <v>5819781</v>
       </c>
       <c r="W150" t="n">
-        <v>0</v>
+        <v>7368024</v>
       </c>
       <c r="X150" t="n">
-        <v>0</v>
+        <v>9236180</v>
       </c>
       <c r="Y150" t="n">
-        <v>0</v>
+        <v>-53000</v>
       </c>
       <c r="Z150" t="n">
-        <v>-36000</v>
+        <v>-1298270</v>
       </c>
       <c r="AA150" t="n">
-        <v>-41000</v>
+        <v>-461442</v>
       </c>
       <c r="AB150" t="n">
-        <v>-10000</v>
+        <v>5810913</v>
       </c>
       <c r="AC150" t="n">
         <v>22</v>
@@ -20999,10 +20999,10 @@
         <v>22</v>
       </c>
       <c r="AE150" t="n">
-        <v>-5</v>
+        <v>5</v>
       </c>
       <c r="AF150" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AG150" t="n">
         <v>0</v>
@@ -21022,29 +21022,29 @@
       </c>
       <c r="AM150" t="inlineStr">
         <is>
-          <t>站上5日線、空頭排列、量能未放大</t>
+          <t>跌破5日線、多頭排列、量能未放大</t>
         </is>
       </c>
       <c r="AN150" t="inlineStr">
         <is>
-          <t>法人連續偏買、5日法人明顯買超</t>
+          <t>5日法人明顯買超、外資投信同步買超</t>
         </is>
       </c>
       <c r="AO150" t="inlineStr">
         <is>
-          <t>整理觀察：站上5日線、空頭排列、量能未放大、法人連續偏買、5日法人明顯買超。多空訊號混合，建議降低追價衝動。</t>
+          <t>整理觀察：跌破5日線、多頭排列、量能未放大、5日法人明顯買超、外資投信同步買超。多空訊號混合，建議降低追價衝動。</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>2884.TW</t>
+          <t>2405.TW</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>玉山金</t>
+          <t>輔信</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -21053,28 +21053,28 @@
         </is>
       </c>
       <c r="D151" t="n">
-        <v>38.1</v>
+        <v>16.3</v>
       </c>
       <c r="E151" t="n">
-        <v>38.18</v>
+        <v>15.78</v>
       </c>
       <c r="F151" t="n">
-        <v>37.16</v>
+        <v>15.86</v>
       </c>
       <c r="G151" t="n">
-        <v>36.18</v>
+        <v>16.41</v>
       </c>
       <c r="H151" t="n">
-        <v>35004151</v>
+        <v>1240343</v>
       </c>
       <c r="I151" t="n">
-        <v>48186488</v>
+        <v>1304826</v>
       </c>
       <c r="J151" t="n">
-        <v>39.1</v>
+        <v>18.4</v>
       </c>
       <c r="K151" t="n">
-        <v>33.95</v>
+        <v>14.5</v>
       </c>
       <c r="L151" t="inlineStr">
         <is>
@@ -21082,52 +21082,52 @@
         </is>
       </c>
       <c r="M151" t="n">
-        <v>-1776201</v>
+        <v>170270</v>
       </c>
       <c r="N151" t="n">
-        <v>-11579529</v>
+        <v>1009270</v>
       </c>
       <c r="O151" t="n">
-        <v>37448556</v>
+        <v>1049560</v>
       </c>
       <c r="P151" t="n">
-        <v>68565492</v>
+        <v>-635440</v>
       </c>
       <c r="Q151" t="n">
-        <v>-903336</v>
+        <v>170270</v>
       </c>
       <c r="R151" t="n">
-        <v>-9400675</v>
+        <v>1045270</v>
       </c>
       <c r="S151" t="n">
-        <v>36722178</v>
+        <v>1090560</v>
       </c>
       <c r="T151" t="n">
-        <v>55376588</v>
+        <v>-625440</v>
       </c>
       <c r="U151" t="n">
-        <v>-135085</v>
+        <v>0</v>
       </c>
       <c r="V151" t="n">
-        <v>-788324</v>
+        <v>0</v>
       </c>
       <c r="W151" t="n">
-        <v>1016680</v>
+        <v>0</v>
       </c>
       <c r="X151" t="n">
-        <v>4090705</v>
+        <v>0</v>
       </c>
       <c r="Y151" t="n">
-        <v>-737780</v>
+        <v>0</v>
       </c>
       <c r="Z151" t="n">
-        <v>-1390530</v>
+        <v>-36000</v>
       </c>
       <c r="AA151" t="n">
-        <v>-290302</v>
+        <v>-41000</v>
       </c>
       <c r="AB151" t="n">
-        <v>9098199</v>
+        <v>-10000</v>
       </c>
       <c r="AC151" t="n">
         <v>22</v>
@@ -21136,10 +21136,10 @@
         <v>22</v>
       </c>
       <c r="AE151" t="n">
-        <v>5</v>
+        <v>-5</v>
       </c>
       <c r="AF151" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="AG151" t="n">
         <v>0</v>
@@ -21159,29 +21159,29 @@
       </c>
       <c r="AM151" t="inlineStr">
         <is>
-          <t>跌破5日線、多頭排列、量能未放大</t>
+          <t>站上5日線、空頭排列、量能未放大</t>
         </is>
       </c>
       <c r="AN151" t="inlineStr">
         <is>
-          <t>5日法人明顯買超、外資投信同步買超</t>
+          <t>法人連續偏買、5日法人明顯買超</t>
         </is>
       </c>
       <c r="AO151" t="inlineStr">
         <is>
-          <t>整理觀察：跌破5日線、多頭排列、量能未放大、5日法人明顯買超、外資投信同步買超。多空訊號混合，建議降低追價衝動。</t>
+          <t>整理觀察：站上5日線、空頭排列、量能未放大、法人連續偏買、5日法人明顯買超。多空訊號混合，建議降低追價衝動。</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>5880.TW</t>
+          <t>2884.TW</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>合庫金</t>
+          <t>玉山金</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -21190,28 +21190,28 @@
         </is>
       </c>
       <c r="D152" t="n">
-        <v>26.6</v>
+        <v>38.1</v>
       </c>
       <c r="E152" t="n">
-        <v>26.93</v>
+        <v>38.18</v>
       </c>
       <c r="F152" t="n">
-        <v>26.39</v>
+        <v>37.16</v>
       </c>
       <c r="G152" t="n">
-        <v>25.88</v>
+        <v>36.18</v>
       </c>
       <c r="H152" t="n">
-        <v>18998546</v>
+        <v>35004151</v>
       </c>
       <c r="I152" t="n">
-        <v>40437237</v>
+        <v>48186488</v>
       </c>
       <c r="J152" t="n">
-        <v>27.65</v>
+        <v>39.1</v>
       </c>
       <c r="K152" t="n">
-        <v>24.85</v>
+        <v>33.95</v>
       </c>
       <c r="L152" t="inlineStr">
         <is>
@@ -21219,52 +21219,52 @@
         </is>
       </c>
       <c r="M152" t="n">
-        <v>-803048</v>
+        <v>-1776201</v>
       </c>
       <c r="N152" t="n">
-        <v>-8138821</v>
+        <v>-11579529</v>
       </c>
       <c r="O152" t="n">
-        <v>62870695</v>
+        <v>37448556</v>
       </c>
       <c r="P152" t="n">
-        <v>111195163</v>
+        <v>68565492</v>
       </c>
       <c r="Q152" t="n">
-        <v>-725397</v>
+        <v>-903336</v>
       </c>
       <c r="R152" t="n">
-        <v>-12660332</v>
+        <v>-9400675</v>
       </c>
       <c r="S152" t="n">
-        <v>55964113</v>
+        <v>36722178</v>
       </c>
       <c r="T152" t="n">
-        <v>96148070</v>
+        <v>55376588</v>
       </c>
       <c r="U152" t="n">
-        <v>-24651</v>
+        <v>-135085</v>
       </c>
       <c r="V152" t="n">
-        <v>5819781</v>
+        <v>-788324</v>
       </c>
       <c r="W152" t="n">
-        <v>7368024</v>
+        <v>1016680</v>
       </c>
       <c r="X152" t="n">
-        <v>9236180</v>
+        <v>4090705</v>
       </c>
       <c r="Y152" t="n">
-        <v>-53000</v>
+        <v>-737780</v>
       </c>
       <c r="Z152" t="n">
-        <v>-1298270</v>
+        <v>-1390530</v>
       </c>
       <c r="AA152" t="n">
-        <v>-461442</v>
+        <v>-290302</v>
       </c>
       <c r="AB152" t="n">
-        <v>5810913</v>
+        <v>9098199</v>
       </c>
       <c r="AC152" t="n">
         <v>22</v>
@@ -21313,12 +21313,12 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>2457.TW</t>
+          <t>6757.TW</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>飛宏</t>
+          <t>台灣虎航</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -21327,28 +21327,28 @@
         </is>
       </c>
       <c r="D153" t="n">
-        <v>23.8</v>
+        <v>56.7</v>
       </c>
       <c r="E153" t="n">
-        <v>22.08</v>
+        <v>56.28</v>
       </c>
       <c r="F153" t="n">
-        <v>22.6</v>
+        <v>55.67</v>
       </c>
       <c r="G153" t="n">
-        <v>24.39</v>
+        <v>56.78</v>
       </c>
       <c r="H153" t="n">
-        <v>1544903</v>
+        <v>1136960</v>
       </c>
       <c r="I153" t="n">
-        <v>2276787</v>
+        <v>1638808</v>
       </c>
       <c r="J153" t="n">
-        <v>29</v>
+        <v>62.2</v>
       </c>
       <c r="K153" t="n">
-        <v>19.9</v>
+        <v>52.5</v>
       </c>
       <c r="L153" t="inlineStr">
         <is>
@@ -21356,28 +21356,28 @@
         </is>
       </c>
       <c r="M153" t="n">
-        <v>618628</v>
+        <v>96442</v>
       </c>
       <c r="N153" t="n">
-        <v>1476178</v>
+        <v>-784167</v>
       </c>
       <c r="O153" t="n">
-        <v>1689846</v>
+        <v>1653075</v>
       </c>
       <c r="P153" t="n">
-        <v>-1015703</v>
+        <v>349478</v>
       </c>
       <c r="Q153" t="n">
-        <v>587260</v>
+        <v>86253</v>
       </c>
       <c r="R153" t="n">
-        <v>1496038</v>
+        <v>-747361</v>
       </c>
       <c r="S153" t="n">
-        <v>1700360</v>
+        <v>1597577</v>
       </c>
       <c r="T153" t="n">
-        <v>-713116</v>
+        <v>325046</v>
       </c>
       <c r="U153" t="n">
         <v>0</v>
@@ -21392,28 +21392,28 @@
         <v>0</v>
       </c>
       <c r="Y153" t="n">
-        <v>31368</v>
+        <v>10189</v>
       </c>
       <c r="Z153" t="n">
-        <v>-19860</v>
+        <v>-36806</v>
       </c>
       <c r="AA153" t="n">
-        <v>-10514</v>
+        <v>55498</v>
       </c>
       <c r="AB153" t="n">
-        <v>-302587</v>
+        <v>24432</v>
       </c>
       <c r="AC153" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AD153" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AE153" t="n">
-        <v>-5</v>
+        <v>20</v>
       </c>
       <c r="AF153" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="AG153" t="n">
         <v>0</v>
@@ -21433,29 +21433,29 @@
       </c>
       <c r="AM153" t="inlineStr">
         <is>
-          <t>站上5日線、空頭排列、量能未放大</t>
+          <t>站上5日線、量能未放大</t>
         </is>
       </c>
       <c r="AN153" t="inlineStr">
         <is>
-          <t>法人連續偏買、5日法人明顯買超</t>
+          <t>5日法人明顯買超</t>
         </is>
       </c>
       <c r="AO153" t="inlineStr">
         <is>
-          <t>整理觀察：站上5日線、空頭排列、量能未放大、法人連續偏買、5日法人明顯買超。多空訊號混合，建議降低追價衝動。</t>
+          <t>整理觀察：站上5日線、量能未放大、5日法人明顯買超。多空訊號混合，建議降低追價衝動。</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>2455.TW</t>
+          <t>2330.TW</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>全新</t>
+          <t>台積電</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -21464,28 +21464,28 @@
         </is>
       </c>
       <c r="D154" t="n">
-        <v>388</v>
+        <v>2405</v>
       </c>
       <c r="E154" t="n">
-        <v>323.9</v>
+        <v>2345</v>
       </c>
       <c r="F154" t="n">
-        <v>319.9</v>
+        <v>2331</v>
       </c>
       <c r="G154" t="n">
-        <v>315.75</v>
+        <v>2369</v>
       </c>
       <c r="H154" t="n">
-        <v>10922747</v>
+        <v>36782301</v>
       </c>
       <c r="I154" t="n">
-        <v>7508029</v>
+        <v>46772753</v>
       </c>
       <c r="J154" t="n">
-        <v>388</v>
+        <v>2480</v>
       </c>
       <c r="K154" t="n">
-        <v>255</v>
+        <v>2180</v>
       </c>
       <c r="L154" t="inlineStr">
         <is>
@@ -21493,52 +21493,52 @@
         </is>
       </c>
       <c r="M154" t="n">
-        <v>-4303791</v>
+        <v>9930788</v>
       </c>
       <c r="N154" t="n">
-        <v>-3328801</v>
+        <v>-15308825</v>
       </c>
       <c r="O154" t="n">
-        <v>-3765606</v>
+        <v>6879274</v>
       </c>
       <c r="P154" t="n">
-        <v>-3671068</v>
+        <v>-22022756</v>
       </c>
       <c r="Q154" t="n">
-        <v>-4263473</v>
+        <v>12251238</v>
       </c>
       <c r="R154" t="n">
-        <v>-3743253</v>
+        <v>-9895226</v>
       </c>
       <c r="S154" t="n">
-        <v>-4359931</v>
+        <v>-72582</v>
       </c>
       <c r="T154" t="n">
-        <v>-4538947</v>
+        <v>-42855599</v>
       </c>
       <c r="U154" t="n">
-        <v>0</v>
+        <v>-1221434</v>
       </c>
       <c r="V154" t="n">
-        <v>245000</v>
+        <v>-400264</v>
       </c>
       <c r="W154" t="n">
-        <v>362000</v>
+        <v>7602992</v>
       </c>
       <c r="X154" t="n">
-        <v>878000</v>
+        <v>9713120</v>
       </c>
       <c r="Y154" t="n">
-        <v>-40318</v>
+        <v>-1099016</v>
       </c>
       <c r="Z154" t="n">
-        <v>169452</v>
+        <v>-5013335</v>
       </c>
       <c r="AA154" t="n">
-        <v>232325</v>
+        <v>-651136</v>
       </c>
       <c r="AB154" t="n">
-        <v>-10121</v>
+        <v>11119723</v>
       </c>
       <c r="AC154" t="n">
         <v>20</v>
@@ -21547,10 +21547,10 @@
         <v>20</v>
       </c>
       <c r="AE154" t="n">
-        <v>105</v>
+        <v>20</v>
       </c>
       <c r="AF154" t="n">
-        <v>-55</v>
+        <v>30</v>
       </c>
       <c r="AG154" t="n">
         <v>0</v>
@@ -21570,29 +21570,29 @@
       </c>
       <c r="AM154" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、黃金交叉、量能溫和放大、突破20日高點</t>
+          <t>站上5日線、量能未放大</t>
         </is>
       </c>
       <c r="AN154" t="inlineStr">
         <is>
-          <t>法人連續偏賣、5日法人明顯賣超、投信買外資賣</t>
+          <t>5日法人明顯買超、投信買外資賣</t>
         </is>
       </c>
       <c r="AO154" t="inlineStr">
         <is>
-          <t>整理觀察：站上5日線、多頭排列、黃金交叉、量能溫和放大、突破20日高點、法人連續偏賣、5日法人明顯賣超、投信買外資賣。多空訊號混合，建議降低追價衝動。</t>
+          <t>整理觀察：站上5日線、量能未放大、5日法人明顯買超、投信買外資賣。多空訊號混合，建議降低追價衝動。</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>6757.TW</t>
+          <t>2455.TW</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>台灣虎航</t>
+          <t>全新</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -21601,28 +21601,28 @@
         </is>
       </c>
       <c r="D155" t="n">
-        <v>56.7</v>
+        <v>388</v>
       </c>
       <c r="E155" t="n">
-        <v>56.28</v>
+        <v>323.9</v>
       </c>
       <c r="F155" t="n">
-        <v>55.67</v>
+        <v>319.9</v>
       </c>
       <c r="G155" t="n">
-        <v>56.78</v>
+        <v>315.75</v>
       </c>
       <c r="H155" t="n">
-        <v>1136960</v>
+        <v>10922747</v>
       </c>
       <c r="I155" t="n">
-        <v>1638808</v>
+        <v>7508029</v>
       </c>
       <c r="J155" t="n">
-        <v>62.2</v>
+        <v>388</v>
       </c>
       <c r="K155" t="n">
-        <v>52.5</v>
+        <v>255</v>
       </c>
       <c r="L155" t="inlineStr">
         <is>
@@ -21630,52 +21630,52 @@
         </is>
       </c>
       <c r="M155" t="n">
-        <v>96442</v>
+        <v>-4303791</v>
       </c>
       <c r="N155" t="n">
-        <v>-784167</v>
+        <v>-3328801</v>
       </c>
       <c r="O155" t="n">
-        <v>1653075</v>
+        <v>-3765606</v>
       </c>
       <c r="P155" t="n">
-        <v>349478</v>
+        <v>-3671068</v>
       </c>
       <c r="Q155" t="n">
-        <v>86253</v>
+        <v>-4263473</v>
       </c>
       <c r="R155" t="n">
-        <v>-747361</v>
+        <v>-3743253</v>
       </c>
       <c r="S155" t="n">
-        <v>1597577</v>
+        <v>-4359931</v>
       </c>
       <c r="T155" t="n">
-        <v>325046</v>
+        <v>-4538947</v>
       </c>
       <c r="U155" t="n">
         <v>0</v>
       </c>
       <c r="V155" t="n">
-        <v>0</v>
+        <v>245000</v>
       </c>
       <c r="W155" t="n">
-        <v>0</v>
+        <v>362000</v>
       </c>
       <c r="X155" t="n">
-        <v>0</v>
+        <v>878000</v>
       </c>
       <c r="Y155" t="n">
-        <v>10189</v>
+        <v>-40318</v>
       </c>
       <c r="Z155" t="n">
-        <v>-36806</v>
+        <v>169452</v>
       </c>
       <c r="AA155" t="n">
-        <v>55498</v>
+        <v>232325</v>
       </c>
       <c r="AB155" t="n">
-        <v>24432</v>
+        <v>-10121</v>
       </c>
       <c r="AC155" t="n">
         <v>20</v>
@@ -21684,10 +21684,10 @@
         <v>20</v>
       </c>
       <c r="AE155" t="n">
-        <v>20</v>
+        <v>105</v>
       </c>
       <c r="AF155" t="n">
-        <v>30</v>
+        <v>-55</v>
       </c>
       <c r="AG155" t="n">
         <v>0</v>
@@ -21707,17 +21707,17 @@
       </c>
       <c r="AM155" t="inlineStr">
         <is>
-          <t>站上5日線、量能未放大</t>
+          <t>站上5日線、多頭排列、黃金交叉、量能溫和放大、突破20日高點</t>
         </is>
       </c>
       <c r="AN155" t="inlineStr">
         <is>
-          <t>5日法人明顯買超</t>
+          <t>法人連續偏賣、5日法人明顯賣超、投信買外資賣</t>
         </is>
       </c>
       <c r="AO155" t="inlineStr">
         <is>
-          <t>整理觀察：站上5日線、量能未放大、5日法人明顯買超。多空訊號混合，建議降低追價衝動。</t>
+          <t>整理觀察：站上5日線、多頭排列、黃金交叉、量能溫和放大、突破20日高點、法人連續偏賣、5日法人明顯賣超、投信買外資賣。多空訊號混合，建議降低追價衝動。</t>
         </is>
       </c>
     </row>
@@ -21861,12 +21861,12 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>2330.TW</t>
+          <t>5871.TW</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>台積電</t>
+          <t>中租-KY</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -21875,28 +21875,28 @@
         </is>
       </c>
       <c r="D157" t="n">
-        <v>2405</v>
+        <v>112</v>
       </c>
       <c r="E157" t="n">
-        <v>2345</v>
+        <v>111.7</v>
       </c>
       <c r="F157" t="n">
-        <v>2331</v>
+        <v>115.15</v>
       </c>
       <c r="G157" t="n">
-        <v>2369</v>
+        <v>117.2</v>
       </c>
       <c r="H157" t="n">
-        <v>35268301</v>
+        <v>5407681</v>
       </c>
       <c r="I157" t="n">
-        <v>46469953</v>
+        <v>6922454</v>
       </c>
       <c r="J157" t="n">
-        <v>2480</v>
+        <v>124.5</v>
       </c>
       <c r="K157" t="n">
-        <v>2180</v>
+        <v>109.5</v>
       </c>
       <c r="L157" t="inlineStr">
         <is>
@@ -21904,64 +21904,64 @@
         </is>
       </c>
       <c r="M157" t="n">
-        <v>9930788</v>
+        <v>350008</v>
       </c>
       <c r="N157" t="n">
-        <v>-15308825</v>
+        <v>67171</v>
       </c>
       <c r="O157" t="n">
-        <v>6879274</v>
+        <v>3489895</v>
       </c>
       <c r="P157" t="n">
-        <v>-22022756</v>
+        <v>18482258</v>
       </c>
       <c r="Q157" t="n">
-        <v>12251238</v>
+        <v>334797</v>
       </c>
       <c r="R157" t="n">
-        <v>-9895226</v>
+        <v>1505353</v>
       </c>
       <c r="S157" t="n">
-        <v>-72582</v>
+        <v>5029491</v>
       </c>
       <c r="T157" t="n">
-        <v>-42855599</v>
+        <v>15176166</v>
       </c>
       <c r="U157" t="n">
-        <v>-1221434</v>
+        <v>25000</v>
       </c>
       <c r="V157" t="n">
-        <v>-400264</v>
+        <v>-975943</v>
       </c>
       <c r="W157" t="n">
-        <v>7602992</v>
+        <v>-1097076</v>
       </c>
       <c r="X157" t="n">
-        <v>9713120</v>
+        <v>3991412</v>
       </c>
       <c r="Y157" t="n">
-        <v>-1099016</v>
+        <v>-9789</v>
       </c>
       <c r="Z157" t="n">
-        <v>-5013335</v>
+        <v>-462239</v>
       </c>
       <c r="AA157" t="n">
-        <v>-651136</v>
+        <v>-442520</v>
       </c>
       <c r="AB157" t="n">
-        <v>11119723</v>
+        <v>-685320</v>
       </c>
       <c r="AC157" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AD157" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AE157" t="n">
-        <v>20</v>
+        <v>-15</v>
       </c>
       <c r="AF157" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="AG157" t="n">
         <v>0</v>
@@ -21971,27 +21971,27 @@
       <c r="AJ157" t="inlineStr"/>
       <c r="AK157" t="inlineStr">
         <is>
-          <t>⚠️整理</t>
+          <t>❌避開</t>
         </is>
       </c>
       <c r="AL157" t="inlineStr">
         <is>
-          <t>整理觀察</t>
+          <t>觀望</t>
         </is>
       </c>
       <c r="AM157" t="inlineStr">
         <is>
-          <t>站上5日線、量能未放大</t>
+          <t>站上5日線、空頭排列、量能未放大、接近20日低點</t>
         </is>
       </c>
       <c r="AN157" t="inlineStr">
         <is>
-          <t>5日法人明顯買超、投信買外資賣</t>
+          <t>法人連續偏買、5日法人明顯買超、外資買投信賣</t>
         </is>
       </c>
       <c r="AO157" t="inlineStr">
         <is>
-          <t>整理觀察：站上5日線、量能未放大、5日法人明顯買超、投信買外資賣。多空訊號混合，建議降低追價衝動。</t>
+          <t>風險偏高：站上5日線、空頭排列、量能未放大、接近20日低點、法人連續偏買、5日法人明顯買超、外資買投信賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
@@ -22135,12 +22135,12 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>5871.TW</t>
+          <t>2312.TW</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>中租-KY</t>
+          <t>金寶</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -22149,28 +22149,28 @@
         </is>
       </c>
       <c r="D159" t="n">
-        <v>112</v>
+        <v>32</v>
       </c>
       <c r="E159" t="n">
-        <v>111.7</v>
+        <v>30.74</v>
       </c>
       <c r="F159" t="n">
-        <v>115.15</v>
+        <v>30.88</v>
       </c>
       <c r="G159" t="n">
-        <v>117.2</v>
+        <v>31.98</v>
       </c>
       <c r="H159" t="n">
-        <v>5407681</v>
+        <v>16707379</v>
       </c>
       <c r="I159" t="n">
-        <v>6922454</v>
+        <v>17883544</v>
       </c>
       <c r="J159" t="n">
-        <v>124.5</v>
+        <v>35.9</v>
       </c>
       <c r="K159" t="n">
-        <v>109.5</v>
+        <v>27.3</v>
       </c>
       <c r="L159" t="inlineStr">
         <is>
@@ -22178,52 +22178,52 @@
         </is>
       </c>
       <c r="M159" t="n">
-        <v>350008</v>
+        <v>-320699</v>
       </c>
       <c r="N159" t="n">
-        <v>67171</v>
+        <v>10720311</v>
       </c>
       <c r="O159" t="n">
-        <v>3489895</v>
+        <v>12309116</v>
       </c>
       <c r="P159" t="n">
-        <v>18482258</v>
+        <v>11326450</v>
       </c>
       <c r="Q159" t="n">
-        <v>334797</v>
+        <v>-372133</v>
       </c>
       <c r="R159" t="n">
-        <v>1505353</v>
+        <v>9994857</v>
       </c>
       <c r="S159" t="n">
-        <v>5029491</v>
+        <v>11166326</v>
       </c>
       <c r="T159" t="n">
-        <v>15176166</v>
+        <v>11613769</v>
       </c>
       <c r="U159" t="n">
-        <v>25000</v>
+        <v>0</v>
       </c>
       <c r="V159" t="n">
-        <v>-975943</v>
+        <v>0</v>
       </c>
       <c r="W159" t="n">
-        <v>-1097076</v>
+        <v>28000</v>
       </c>
       <c r="X159" t="n">
-        <v>3991412</v>
+        <v>37000</v>
       </c>
       <c r="Y159" t="n">
-        <v>-9789</v>
+        <v>51434</v>
       </c>
       <c r="Z159" t="n">
-        <v>-462239</v>
+        <v>725454</v>
       </c>
       <c r="AA159" t="n">
-        <v>-442520</v>
+        <v>1114790</v>
       </c>
       <c r="AB159" t="n">
-        <v>-685320</v>
+        <v>-324319</v>
       </c>
       <c r="AC159" t="n">
         <v>18</v>
@@ -22232,10 +22232,10 @@
         <v>18</v>
       </c>
       <c r="AE159" t="n">
-        <v>-15</v>
+        <v>-5</v>
       </c>
       <c r="AF159" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AG159" t="n">
         <v>0</v>
@@ -22255,17 +22255,17 @@
       </c>
       <c r="AM159" t="inlineStr">
         <is>
-          <t>站上5日線、空頭排列、量能未放大、接近20日低點</t>
+          <t>站上5日線、空頭排列、量能未放大</t>
         </is>
       </c>
       <c r="AN159" t="inlineStr">
         <is>
-          <t>法人連續偏買、5日法人明顯買超、外資買投信賣</t>
+          <t>5日法人明顯買超、外資投信同步買超</t>
         </is>
       </c>
       <c r="AO159" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、空頭排列、量能未放大、接近20日低點、法人連續偏買、5日法人明顯買超、外資買投信賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、空頭排列、量能未放大、5日法人明顯買超、外資投信同步買超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
@@ -22683,12 +22683,12 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>2312.TW</t>
+          <t>2540.TW</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>金寶</t>
+          <t>愛山林</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -22697,28 +22697,28 @@
         </is>
       </c>
       <c r="D163" t="n">
-        <v>32</v>
+        <v>57.8</v>
       </c>
       <c r="E163" t="n">
-        <v>30.74</v>
+        <v>58.7</v>
       </c>
       <c r="F163" t="n">
-        <v>30.88</v>
+        <v>56.84</v>
       </c>
       <c r="G163" t="n">
-        <v>31.98</v>
+        <v>55.2</v>
       </c>
       <c r="H163" t="n">
-        <v>16707379</v>
+        <v>5856479</v>
       </c>
       <c r="I163" t="n">
-        <v>17883544</v>
+        <v>4744624</v>
       </c>
       <c r="J163" t="n">
-        <v>35.9</v>
+        <v>61.8</v>
       </c>
       <c r="K163" t="n">
-        <v>27.3</v>
+        <v>52.7</v>
       </c>
       <c r="L163" t="inlineStr">
         <is>
@@ -22726,28 +22726,28 @@
         </is>
       </c>
       <c r="M163" t="n">
-        <v>-320699</v>
+        <v>-45645</v>
       </c>
       <c r="N163" t="n">
-        <v>10720311</v>
+        <v>-811907</v>
       </c>
       <c r="O163" t="n">
-        <v>12309116</v>
+        <v>2787435</v>
       </c>
       <c r="P163" t="n">
-        <v>11326450</v>
+        <v>5624448</v>
       </c>
       <c r="Q163" t="n">
-        <v>-372133</v>
+        <v>-49645</v>
       </c>
       <c r="R163" t="n">
-        <v>9994857</v>
+        <v>-1891907</v>
       </c>
       <c r="S163" t="n">
-        <v>11166326</v>
+        <v>939435</v>
       </c>
       <c r="T163" t="n">
-        <v>11613769</v>
+        <v>2901448</v>
       </c>
       <c r="U163" t="n">
         <v>0</v>
@@ -22756,22 +22756,22 @@
         <v>0</v>
       </c>
       <c r="W163" t="n">
-        <v>28000</v>
+        <v>0</v>
       </c>
       <c r="X163" t="n">
-        <v>37000</v>
+        <v>0</v>
       </c>
       <c r="Y163" t="n">
-        <v>51434</v>
+        <v>4000</v>
       </c>
       <c r="Z163" t="n">
-        <v>725454</v>
+        <v>1080000</v>
       </c>
       <c r="AA163" t="n">
-        <v>1114790</v>
+        <v>1848000</v>
       </c>
       <c r="AB163" t="n">
-        <v>-324319</v>
+        <v>2723000</v>
       </c>
       <c r="AC163" t="n">
         <v>18</v>
@@ -22780,10 +22780,10 @@
         <v>18</v>
       </c>
       <c r="AE163" t="n">
-        <v>-5</v>
+        <v>15</v>
       </c>
       <c r="AF163" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="AG163" t="n">
         <v>0</v>
@@ -22803,17 +22803,17 @@
       </c>
       <c r="AM163" t="inlineStr">
         <is>
-          <t>站上5日線、空頭排列、量能未放大</t>
+          <t>跌破5日線、多頭排列、量能溫和放大</t>
         </is>
       </c>
       <c r="AN163" t="inlineStr">
         <is>
-          <t>5日法人明顯買超、外資投信同步買超</t>
+          <t>5日法人明顯買超</t>
         </is>
       </c>
       <c r="AO163" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、空頭排列、量能未放大、5日法人明顯買超、外資投信同步買超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、多頭排列、量能溫和放大、5日法人明顯買超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
@@ -24216,10 +24216,10 @@
         <v>101.66</v>
       </c>
       <c r="H174" t="n">
-        <v>7627037</v>
+        <v>8077037</v>
       </c>
       <c r="I174" t="n">
-        <v>13121612</v>
+        <v>13211612</v>
       </c>
       <c r="J174" t="n">
         <v>108.5</v>
@@ -25286,12 +25286,12 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>2467.TW</t>
+          <t>9105.TW</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>志聖</t>
+          <t>泰金寶-DR</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -25300,28 +25300,28 @@
         </is>
       </c>
       <c r="D182" t="n">
-        <v>517</v>
+        <v>8.210000000000001</v>
       </c>
       <c r="E182" t="n">
-        <v>487.8</v>
+        <v>8.07</v>
       </c>
       <c r="F182" t="n">
-        <v>499.3</v>
+        <v>8.1</v>
       </c>
       <c r="G182" t="n">
-        <v>529.85</v>
+        <v>8.4</v>
       </c>
       <c r="H182" t="n">
-        <v>908590</v>
+        <v>22609705</v>
       </c>
       <c r="I182" t="n">
-        <v>1554974</v>
+        <v>22489046</v>
       </c>
       <c r="J182" t="n">
-        <v>630</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="K182" t="n">
-        <v>430</v>
+        <v>7.16</v>
       </c>
       <c r="L182" t="inlineStr">
         <is>
@@ -25329,52 +25329,52 @@
         </is>
       </c>
       <c r="M182" t="n">
-        <v>139086</v>
+        <v>-5426233</v>
       </c>
       <c r="N182" t="n">
-        <v>268335</v>
+        <v>631060</v>
       </c>
       <c r="O182" t="n">
-        <v>71546</v>
+        <v>2279254</v>
       </c>
       <c r="P182" t="n">
-        <v>261966</v>
+        <v>4184623</v>
       </c>
       <c r="Q182" t="n">
-        <v>152090</v>
+        <v>-5414000</v>
       </c>
       <c r="R182" t="n">
-        <v>436451</v>
+        <v>528600</v>
       </c>
       <c r="S182" t="n">
-        <v>190040</v>
+        <v>1501400</v>
       </c>
       <c r="T182" t="n">
-        <v>130580</v>
+        <v>6236546</v>
       </c>
       <c r="U182" t="n">
-        <v>-10538</v>
+        <v>0</v>
       </c>
       <c r="V182" t="n">
-        <v>-130389</v>
+        <v>0</v>
       </c>
       <c r="W182" t="n">
-        <v>-96020</v>
+        <v>0</v>
       </c>
       <c r="X182" t="n">
-        <v>-89933</v>
+        <v>0</v>
       </c>
       <c r="Y182" t="n">
-        <v>-2466</v>
+        <v>-12233</v>
       </c>
       <c r="Z182" t="n">
-        <v>-37727</v>
+        <v>102460</v>
       </c>
       <c r="AA182" t="n">
-        <v>-22474</v>
+        <v>777854</v>
       </c>
       <c r="AB182" t="n">
-        <v>221319</v>
+        <v>-2051923</v>
       </c>
       <c r="AC182" t="n">
         <v>14</v>
@@ -25383,10 +25383,10 @@
         <v>14</v>
       </c>
       <c r="AE182" t="n">
-        <v>-5</v>
+        <v>5</v>
       </c>
       <c r="AF182" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="AG182" t="n">
         <v>0</v>
@@ -25406,29 +25406,29 @@
       </c>
       <c r="AM182" t="inlineStr">
         <is>
-          <t>站上5日線、空頭排列、量能未放大</t>
+          <t>站上5日線、空頭排列、量能溫和放大</t>
         </is>
       </c>
       <c r="AN182" t="inlineStr">
         <is>
-          <t>法人連續偏買、5日法人小幅買超、外資買投信賣</t>
+          <t>5日法人明顯買超</t>
         </is>
       </c>
       <c r="AO182" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、空頭排列、量能未放大、法人連續偏買、5日法人小幅買超、外資買投信賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、空頭排列、量能溫和放大、5日法人明顯買超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>2540.TW</t>
+          <t>2467.TW</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>愛山林</t>
+          <t>志聖</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -25437,28 +25437,28 @@
         </is>
       </c>
       <c r="D183" t="n">
-        <v>57.8</v>
+        <v>517</v>
       </c>
       <c r="E183" t="n">
-        <v>58.7</v>
+        <v>487.8</v>
       </c>
       <c r="F183" t="n">
-        <v>56.84</v>
+        <v>499.3</v>
       </c>
       <c r="G183" t="n">
-        <v>55.2</v>
+        <v>529.85</v>
       </c>
       <c r="H183" t="n">
-        <v>1826479</v>
+        <v>908590</v>
       </c>
       <c r="I183" t="n">
-        <v>3938624</v>
+        <v>1554974</v>
       </c>
       <c r="J183" t="n">
-        <v>61.8</v>
+        <v>630</v>
       </c>
       <c r="K183" t="n">
-        <v>52.7</v>
+        <v>430</v>
       </c>
       <c r="L183" t="inlineStr">
         <is>
@@ -25466,52 +25466,52 @@
         </is>
       </c>
       <c r="M183" t="n">
-        <v>-45645</v>
+        <v>139086</v>
       </c>
       <c r="N183" t="n">
-        <v>-811907</v>
+        <v>268335</v>
       </c>
       <c r="O183" t="n">
-        <v>2787435</v>
+        <v>71546</v>
       </c>
       <c r="P183" t="n">
-        <v>5624448</v>
+        <v>261966</v>
       </c>
       <c r="Q183" t="n">
-        <v>-49645</v>
+        <v>152090</v>
       </c>
       <c r="R183" t="n">
-        <v>-1891907</v>
+        <v>436451</v>
       </c>
       <c r="S183" t="n">
-        <v>939435</v>
+        <v>190040</v>
       </c>
       <c r="T183" t="n">
-        <v>2901448</v>
+        <v>130580</v>
       </c>
       <c r="U183" t="n">
-        <v>0</v>
+        <v>-10538</v>
       </c>
       <c r="V183" t="n">
-        <v>0</v>
+        <v>-130389</v>
       </c>
       <c r="W183" t="n">
-        <v>0</v>
+        <v>-96020</v>
       </c>
       <c r="X183" t="n">
-        <v>0</v>
+        <v>-89933</v>
       </c>
       <c r="Y183" t="n">
-        <v>4000</v>
+        <v>-2466</v>
       </c>
       <c r="Z183" t="n">
-        <v>1080000</v>
+        <v>-37727</v>
       </c>
       <c r="AA183" t="n">
-        <v>1848000</v>
+        <v>-22474</v>
       </c>
       <c r="AB183" t="n">
-        <v>2723000</v>
+        <v>221319</v>
       </c>
       <c r="AC183" t="n">
         <v>14</v>
@@ -25520,10 +25520,10 @@
         <v>14</v>
       </c>
       <c r="AE183" t="n">
-        <v>5</v>
+        <v>-5</v>
       </c>
       <c r="AF183" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="AG183" t="n">
         <v>0</v>
@@ -25543,17 +25543,17 @@
       </c>
       <c r="AM183" t="inlineStr">
         <is>
-          <t>跌破5日線、多頭排列、量能未放大</t>
+          <t>站上5日線、空頭排列、量能未放大</t>
         </is>
       </c>
       <c r="AN183" t="inlineStr">
         <is>
-          <t>5日法人明顯買超</t>
+          <t>法人連續偏買、5日法人小幅買超、外資買投信賣</t>
         </is>
       </c>
       <c r="AO183" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、多頭排列、量能未放大、5日法人明顯買超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、空頭排列、量能未放大、法人連續偏買、5日法人小幅買超、外資買投信賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
@@ -25697,12 +25697,12 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>9105.TW</t>
+          <t>2753.TW</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>泰金寶-DR</t>
+          <t>八方雲集</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -25711,28 +25711,28 @@
         </is>
       </c>
       <c r="D185" t="n">
-        <v>8.210000000000001</v>
+        <v>179</v>
       </c>
       <c r="E185" t="n">
-        <v>8.07</v>
+        <v>179.5</v>
       </c>
       <c r="F185" t="n">
-        <v>8.1</v>
+        <v>178.25</v>
       </c>
       <c r="G185" t="n">
-        <v>8.4</v>
+        <v>177.57</v>
       </c>
       <c r="H185" t="n">
-        <v>22609705</v>
+        <v>135180</v>
       </c>
       <c r="I185" t="n">
-        <v>22489046</v>
+        <v>313380</v>
       </c>
       <c r="J185" t="n">
-        <v>9.300000000000001</v>
+        <v>182.5</v>
       </c>
       <c r="K185" t="n">
-        <v>7.16</v>
+        <v>174</v>
       </c>
       <c r="L185" t="inlineStr">
         <is>
@@ -25740,64 +25740,64 @@
         </is>
       </c>
       <c r="M185" t="n">
-        <v>-5426233</v>
+        <v>-18366</v>
       </c>
       <c r="N185" t="n">
-        <v>631060</v>
+        <v>-163207</v>
       </c>
       <c r="O185" t="n">
-        <v>2279254</v>
+        <v>429121</v>
       </c>
       <c r="P185" t="n">
-        <v>4184623</v>
+        <v>798311</v>
       </c>
       <c r="Q185" t="n">
-        <v>-5414000</v>
+        <v>-17759</v>
       </c>
       <c r="R185" t="n">
-        <v>528600</v>
+        <v>-144429</v>
       </c>
       <c r="S185" t="n">
-        <v>1501400</v>
+        <v>451030</v>
       </c>
       <c r="T185" t="n">
-        <v>6236546</v>
+        <v>822664</v>
       </c>
       <c r="U185" t="n">
-        <v>0</v>
+        <v>-607</v>
       </c>
       <c r="V185" t="n">
-        <v>0</v>
+        <v>-4591</v>
       </c>
       <c r="W185" t="n">
-        <v>0</v>
+        <v>-4591</v>
       </c>
       <c r="X185" t="n">
-        <v>0</v>
+        <v>-9070</v>
       </c>
       <c r="Y185" t="n">
-        <v>-12233</v>
+        <v>0</v>
       </c>
       <c r="Z185" t="n">
-        <v>102460</v>
+        <v>-14187</v>
       </c>
       <c r="AA185" t="n">
-        <v>777854</v>
+        <v>-17318</v>
       </c>
       <c r="AB185" t="n">
-        <v>-2051923</v>
+        <v>-15283</v>
       </c>
       <c r="AC185" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AD185" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AE185" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="AF185" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="AG185" t="n">
         <v>0</v>
@@ -25817,17 +25817,17 @@
       </c>
       <c r="AM185" t="inlineStr">
         <is>
-          <t>站上5日線、空頭排列、量能溫和放大</t>
+          <t>跌破5日線、多頭排列、量能未放大、接近20日高點、接近20日低點</t>
         </is>
       </c>
       <c r="AN185" t="inlineStr">
         <is>
-          <t>5日法人明顯買超</t>
+          <t>5日法人買超、外資買投信賣</t>
         </is>
       </c>
       <c r="AO185" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、空頭排列、量能溫和放大、5日法人明顯買超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、多頭排列、量能未放大、接近20日高點、接近20日低點、5日法人買超、外資買投信賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
@@ -26108,12 +26108,12 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>2753.TW</t>
+          <t>9945.TW</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>八方雲集</t>
+          <t>潤泰新</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -26122,28 +26122,28 @@
         </is>
       </c>
       <c r="D188" t="n">
-        <v>179</v>
+        <v>26.4</v>
       </c>
       <c r="E188" t="n">
-        <v>179.5</v>
+        <v>26.76</v>
       </c>
       <c r="F188" t="n">
-        <v>178.25</v>
+        <v>26.46</v>
       </c>
       <c r="G188" t="n">
-        <v>177.57</v>
+        <v>26.3</v>
       </c>
       <c r="H188" t="n">
-        <v>135180</v>
+        <v>5984261</v>
       </c>
       <c r="I188" t="n">
-        <v>313380</v>
+        <v>8250456</v>
       </c>
       <c r="J188" t="n">
-        <v>182.5</v>
+        <v>27.5</v>
       </c>
       <c r="K188" t="n">
-        <v>174</v>
+        <v>25.2</v>
       </c>
       <c r="L188" t="inlineStr">
         <is>
@@ -26151,64 +26151,64 @@
         </is>
       </c>
       <c r="M188" t="n">
-        <v>-18366</v>
+        <v>-2500827</v>
       </c>
       <c r="N188" t="n">
-        <v>-163207</v>
+        <v>-6591049</v>
       </c>
       <c r="O188" t="n">
-        <v>429121</v>
+        <v>5143726</v>
       </c>
       <c r="P188" t="n">
-        <v>798311</v>
+        <v>13039248</v>
       </c>
       <c r="Q188" t="n">
-        <v>-17759</v>
+        <v>-2516785</v>
       </c>
       <c r="R188" t="n">
-        <v>-144429</v>
+        <v>-6138647</v>
       </c>
       <c r="S188" t="n">
-        <v>451030</v>
+        <v>5374625</v>
       </c>
       <c r="T188" t="n">
-        <v>822664</v>
+        <v>13167202</v>
       </c>
       <c r="U188" t="n">
-        <v>-607</v>
+        <v>0</v>
       </c>
       <c r="V188" t="n">
-        <v>-4591</v>
+        <v>-5000</v>
       </c>
       <c r="W188" t="n">
-        <v>-4591</v>
+        <v>-9000</v>
       </c>
       <c r="X188" t="n">
-        <v>-9070</v>
+        <v>26000</v>
       </c>
       <c r="Y188" t="n">
-        <v>0</v>
+        <v>15958</v>
       </c>
       <c r="Z188" t="n">
-        <v>-14187</v>
+        <v>-447402</v>
       </c>
       <c r="AA188" t="n">
-        <v>-17318</v>
+        <v>-221899</v>
       </c>
       <c r="AB188" t="n">
-        <v>-15283</v>
+        <v>-153954</v>
       </c>
       <c r="AC188" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AD188" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AE188" t="n">
-        <v>10</v>
+        <v>-5</v>
       </c>
       <c r="AF188" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="AG188" t="n">
         <v>0</v>
@@ -26228,17 +26228,17 @@
       </c>
       <c r="AM188" t="inlineStr">
         <is>
-          <t>跌破5日線、多頭排列、量能未放大、接近20日高點、接近20日低點</t>
+          <t>跌破5日線、多頭排列、量能未放大、接近20日低點</t>
         </is>
       </c>
       <c r="AN188" t="inlineStr">
         <is>
-          <t>5日法人買超、外資買投信賣</t>
+          <t>5日法人明顯買超、外資買投信賣</t>
         </is>
       </c>
       <c r="AO188" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、多頭排列、量能未放大、接近20日高點、接近20日低點、5日法人買超、外資買投信賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、多頭排列、量能未放大、接近20日低點、5日法人明顯買超、外資買投信賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
@@ -26519,12 +26519,12 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>2832.TW</t>
+          <t>4960.TW</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>台產</t>
+          <t>誠美材</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -26533,28 +26533,28 @@
         </is>
       </c>
       <c r="D191" t="n">
-        <v>58.6</v>
+        <v>21</v>
       </c>
       <c r="E191" t="n">
-        <v>58.9</v>
+        <v>19.54</v>
       </c>
       <c r="F191" t="n">
-        <v>57.74</v>
+        <v>19.99</v>
       </c>
       <c r="G191" t="n">
-        <v>57.16</v>
+        <v>21.31</v>
       </c>
       <c r="H191" t="n">
-        <v>163448</v>
+        <v>2617494</v>
       </c>
       <c r="I191" t="n">
-        <v>294877</v>
+        <v>2413701</v>
       </c>
       <c r="J191" t="n">
-        <v>60.4</v>
+        <v>24.85</v>
       </c>
       <c r="K191" t="n">
-        <v>55.3</v>
+        <v>17.8</v>
       </c>
       <c r="L191" t="inlineStr">
         <is>
@@ -26562,52 +26562,52 @@
         </is>
       </c>
       <c r="M191" t="n">
-        <v>-65391</v>
+        <v>-531552</v>
       </c>
       <c r="N191" t="n">
-        <v>-175395</v>
+        <v>-114973</v>
       </c>
       <c r="O191" t="n">
-        <v>264011</v>
+        <v>328987</v>
       </c>
       <c r="P191" t="n">
-        <v>352707</v>
+        <v>2462963</v>
       </c>
       <c r="Q191" t="n">
-        <v>-64000</v>
+        <v>-528200</v>
       </c>
       <c r="R191" t="n">
-        <v>-153000</v>
+        <v>-72722</v>
       </c>
       <c r="S191" t="n">
-        <v>313406</v>
+        <v>366769</v>
       </c>
       <c r="T191" t="n">
-        <v>311031</v>
+        <v>2499290</v>
       </c>
       <c r="U191" t="n">
-        <v>-1383</v>
+        <v>0</v>
       </c>
       <c r="V191" t="n">
-        <v>-3625</v>
+        <v>0</v>
       </c>
       <c r="W191" t="n">
-        <v>-3625</v>
+        <v>0</v>
       </c>
       <c r="X191" t="n">
-        <v>52446</v>
+        <v>0</v>
       </c>
       <c r="Y191" t="n">
-        <v>-8</v>
+        <v>-3352</v>
       </c>
       <c r="Z191" t="n">
-        <v>-18770</v>
+        <v>-42251</v>
       </c>
       <c r="AA191" t="n">
-        <v>-45770</v>
+        <v>-37782</v>
       </c>
       <c r="AB191" t="n">
-        <v>-10770</v>
+        <v>-36327</v>
       </c>
       <c r="AC191" t="n">
         <v>10</v>
@@ -26639,29 +26639,29 @@
       </c>
       <c r="AM191" t="inlineStr">
         <is>
-          <t>跌破5日線、多頭排列、量能未放大</t>
+          <t>站上5日線、空頭排列、量能溫和放大</t>
         </is>
       </c>
       <c r="AN191" t="inlineStr">
         <is>
-          <t>5日法人買超、外資買投信賣</t>
+          <t>5日法人買超</t>
         </is>
       </c>
       <c r="AO191" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、多頭排列、量能未放大、5日法人買超、外資買投信賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、空頭排列、量能溫和放大、5日法人買超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>9945.TW</t>
+          <t>2832.TW</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>潤泰新</t>
+          <t>台產</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -26670,28 +26670,28 @@
         </is>
       </c>
       <c r="D192" t="n">
-        <v>26.4</v>
+        <v>58.6</v>
       </c>
       <c r="E192" t="n">
-        <v>26.76</v>
+        <v>58.9</v>
       </c>
       <c r="F192" t="n">
-        <v>26.46</v>
+        <v>57.74</v>
       </c>
       <c r="G192" t="n">
-        <v>26.3</v>
+        <v>57.16</v>
       </c>
       <c r="H192" t="n">
-        <v>5984261</v>
+        <v>163448</v>
       </c>
       <c r="I192" t="n">
-        <v>8250456</v>
+        <v>294877</v>
       </c>
       <c r="J192" t="n">
-        <v>27.5</v>
+        <v>60.4</v>
       </c>
       <c r="K192" t="n">
-        <v>25.2</v>
+        <v>55.3</v>
       </c>
       <c r="L192" t="inlineStr">
         <is>
@@ -26699,52 +26699,52 @@
         </is>
       </c>
       <c r="M192" t="n">
-        <v>-2500827</v>
+        <v>-65391</v>
       </c>
       <c r="N192" t="n">
-        <v>-6591049</v>
+        <v>-175395</v>
       </c>
       <c r="O192" t="n">
-        <v>5143726</v>
+        <v>264011</v>
       </c>
       <c r="P192" t="n">
-        <v>13039248</v>
+        <v>352707</v>
       </c>
       <c r="Q192" t="n">
-        <v>-2516785</v>
+        <v>-64000</v>
       </c>
       <c r="R192" t="n">
-        <v>-6138647</v>
+        <v>-153000</v>
       </c>
       <c r="S192" t="n">
-        <v>5374625</v>
+        <v>313406</v>
       </c>
       <c r="T192" t="n">
-        <v>13167202</v>
+        <v>311031</v>
       </c>
       <c r="U192" t="n">
-        <v>0</v>
+        <v>-1383</v>
       </c>
       <c r="V192" t="n">
-        <v>-5000</v>
+        <v>-3625</v>
       </c>
       <c r="W192" t="n">
-        <v>-9000</v>
+        <v>-3625</v>
       </c>
       <c r="X192" t="n">
-        <v>26000</v>
+        <v>52446</v>
       </c>
       <c r="Y192" t="n">
-        <v>15958</v>
+        <v>-8</v>
       </c>
       <c r="Z192" t="n">
-        <v>-447402</v>
+        <v>-18770</v>
       </c>
       <c r="AA192" t="n">
-        <v>-221899</v>
+        <v>-45770</v>
       </c>
       <c r="AB192" t="n">
-        <v>-153954</v>
+        <v>-10770</v>
       </c>
       <c r="AC192" t="n">
         <v>10</v>
@@ -26753,10 +26753,10 @@
         <v>10</v>
       </c>
       <c r="AE192" t="n">
-        <v>-5</v>
+        <v>5</v>
       </c>
       <c r="AF192" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="AG192" t="n">
         <v>0</v>
@@ -26776,17 +26776,17 @@
       </c>
       <c r="AM192" t="inlineStr">
         <is>
-          <t>跌破5日線、多頭排列、量能未放大、接近20日低點</t>
+          <t>跌破5日線、多頭排列、量能未放大</t>
         </is>
       </c>
       <c r="AN192" t="inlineStr">
         <is>
-          <t>5日法人明顯買超、外資買投信賣</t>
+          <t>5日法人買超、外資買投信賣</t>
         </is>
       </c>
       <c r="AO192" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、多頭排列、量能未放大、接近20日低點、5日法人明顯買超、外資買投信賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、多頭排列、量能未放大、5日法人買超、外資買投信賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
@@ -27067,12 +27067,12 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>4960.TW</t>
+          <t>2609.TW</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>誠美材</t>
+          <t>陽明</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -27081,28 +27081,28 @@
         </is>
       </c>
       <c r="D195" t="n">
-        <v>21</v>
+        <v>50.6</v>
       </c>
       <c r="E195" t="n">
-        <v>19.54</v>
+        <v>50.64</v>
       </c>
       <c r="F195" t="n">
-        <v>19.99</v>
+        <v>50.71</v>
       </c>
       <c r="G195" t="n">
-        <v>21.31</v>
+        <v>50.5</v>
       </c>
       <c r="H195" t="n">
-        <v>2617494</v>
+        <v>16626510</v>
       </c>
       <c r="I195" t="n">
-        <v>2413701</v>
+        <v>14445585</v>
       </c>
       <c r="J195" t="n">
-        <v>24.85</v>
+        <v>52.5</v>
       </c>
       <c r="K195" t="n">
-        <v>17.8</v>
+        <v>47.25</v>
       </c>
       <c r="L195" t="inlineStr">
         <is>
@@ -27110,64 +27110,64 @@
         </is>
       </c>
       <c r="M195" t="n">
-        <v>-531552</v>
+        <v>-6172986</v>
       </c>
       <c r="N195" t="n">
-        <v>-114973</v>
+        <v>-3480592</v>
       </c>
       <c r="O195" t="n">
-        <v>328987</v>
+        <v>5484739</v>
       </c>
       <c r="P195" t="n">
-        <v>2462963</v>
+        <v>18292193</v>
       </c>
       <c r="Q195" t="n">
-        <v>-528200</v>
+        <v>-6067582</v>
       </c>
       <c r="R195" t="n">
-        <v>-72722</v>
+        <v>-3030362</v>
       </c>
       <c r="S195" t="n">
-        <v>366769</v>
+        <v>5984821</v>
       </c>
       <c r="T195" t="n">
-        <v>2499290</v>
+        <v>19031597</v>
       </c>
       <c r="U195" t="n">
-        <v>0</v>
+        <v>34373</v>
       </c>
       <c r="V195" t="n">
-        <v>0</v>
+        <v>3152</v>
       </c>
       <c r="W195" t="n">
-        <v>0</v>
+        <v>-29794</v>
       </c>
       <c r="X195" t="n">
-        <v>0</v>
+        <v>-13444</v>
       </c>
       <c r="Y195" t="n">
-        <v>-3352</v>
+        <v>-139777</v>
       </c>
       <c r="Z195" t="n">
-        <v>-42251</v>
+        <v>-453382</v>
       </c>
       <c r="AA195" t="n">
-        <v>-37782</v>
+        <v>-470288</v>
       </c>
       <c r="AB195" t="n">
-        <v>-36327</v>
+        <v>-725960</v>
       </c>
       <c r="AC195" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AD195" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AE195" t="n">
-        <v>5</v>
+        <v>-10</v>
       </c>
       <c r="AF195" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="AG195" t="n">
         <v>0</v>
@@ -27187,29 +27187,29 @@
       </c>
       <c r="AM195" t="inlineStr">
         <is>
-          <t>站上5日線、空頭排列、量能溫和放大</t>
+          <t>跌破5日線、量能溫和放大</t>
         </is>
       </c>
       <c r="AN195" t="inlineStr">
         <is>
-          <t>5日法人買超</t>
+          <t>5日法人明顯買超、外資買投信賣</t>
         </is>
       </c>
       <c r="AO195" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、空頭排列、量能溫和放大、5日法人買超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、量能溫和放大、5日法人明顯買超、外資買投信賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>2609.TW</t>
+          <t>2387.TW</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>陽明</t>
+          <t>精元</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -27218,28 +27218,28 @@
         </is>
       </c>
       <c r="D196" t="n">
-        <v>50.6</v>
+        <v>37.85</v>
       </c>
       <c r="E196" t="n">
-        <v>50.64</v>
+        <v>37.64</v>
       </c>
       <c r="F196" t="n">
-        <v>50.71</v>
+        <v>37.98</v>
       </c>
       <c r="G196" t="n">
-        <v>50.5</v>
+        <v>38.44</v>
       </c>
       <c r="H196" t="n">
-        <v>16626510</v>
+        <v>685825</v>
       </c>
       <c r="I196" t="n">
-        <v>14445585</v>
+        <v>432933</v>
       </c>
       <c r="J196" t="n">
-        <v>52.5</v>
+        <v>40.6</v>
       </c>
       <c r="K196" t="n">
-        <v>47.25</v>
+        <v>36.7</v>
       </c>
       <c r="L196" t="inlineStr">
         <is>
@@ -27247,52 +27247,52 @@
         </is>
       </c>
       <c r="M196" t="n">
-        <v>-6172986</v>
+        <v>36869</v>
       </c>
       <c r="N196" t="n">
-        <v>-3480592</v>
+        <v>-23939</v>
       </c>
       <c r="O196" t="n">
-        <v>5484739</v>
+        <v>138755</v>
       </c>
       <c r="P196" t="n">
-        <v>18292193</v>
+        <v>-158412</v>
       </c>
       <c r="Q196" t="n">
-        <v>-6067582</v>
+        <v>40842</v>
       </c>
       <c r="R196" t="n">
-        <v>-3030362</v>
+        <v>31742</v>
       </c>
       <c r="S196" t="n">
-        <v>5984821</v>
+        <v>217722</v>
       </c>
       <c r="T196" t="n">
-        <v>19031597</v>
+        <v>-269849</v>
       </c>
       <c r="U196" t="n">
-        <v>34373</v>
+        <v>-7943</v>
       </c>
       <c r="V196" t="n">
-        <v>3152</v>
+        <v>-17408</v>
       </c>
       <c r="W196" t="n">
-        <v>-29794</v>
+        <v>-17408</v>
       </c>
       <c r="X196" t="n">
-        <v>-13444</v>
+        <v>115060</v>
       </c>
       <c r="Y196" t="n">
-        <v>-139777</v>
+        <v>3970</v>
       </c>
       <c r="Z196" t="n">
-        <v>-453382</v>
+        <v>-38273</v>
       </c>
       <c r="AA196" t="n">
-        <v>-470288</v>
+        <v>-61559</v>
       </c>
       <c r="AB196" t="n">
-        <v>-725960</v>
+        <v>-3623</v>
       </c>
       <c r="AC196" t="n">
         <v>8</v>
@@ -27301,10 +27301,10 @@
         <v>8</v>
       </c>
       <c r="AE196" t="n">
-        <v>-10</v>
+        <v>0</v>
       </c>
       <c r="AF196" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="AG196" t="n">
         <v>0</v>
@@ -27324,17 +27324,17 @@
       </c>
       <c r="AM196" t="inlineStr">
         <is>
-          <t>跌破5日線、量能溫和放大</t>
+          <t>站上5日線、空頭排列、成交量放大、接近20日低點</t>
         </is>
       </c>
       <c r="AN196" t="inlineStr">
         <is>
-          <t>5日法人明顯買超、外資買投信賣</t>
+          <t>5日法人買超、外資買投信賣</t>
         </is>
       </c>
       <c r="AO196" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、量能溫和放大、5日法人明顯買超、外資買投信賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、空頭排列、成交量放大、接近20日低點、5日法人買超、外資買投信賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
@@ -27478,12 +27478,12 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>2002.TW</t>
+          <t>4908.TWO</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>中鋼</t>
+          <t>前鼎</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -27492,28 +27492,28 @@
         </is>
       </c>
       <c r="D198" t="n">
-        <v>18.9</v>
+        <v>165.5</v>
       </c>
       <c r="E198" t="n">
-        <v>18.9</v>
+        <v>141.8</v>
       </c>
       <c r="F198" t="n">
-        <v>18.99</v>
+        <v>139.55</v>
       </c>
       <c r="G198" t="n">
-        <v>18.82</v>
+        <v>145.28</v>
       </c>
       <c r="H198" t="n">
-        <v>18036777</v>
+        <v>547000</v>
       </c>
       <c r="I198" t="n">
-        <v>30506159</v>
+        <v>1355600</v>
       </c>
       <c r="J198" t="n">
-        <v>19.45</v>
+        <v>171.5</v>
       </c>
       <c r="K198" t="n">
-        <v>18.25</v>
+        <v>117</v>
       </c>
       <c r="L198" t="inlineStr">
         <is>
@@ -27521,52 +27521,52 @@
         </is>
       </c>
       <c r="M198" t="n">
-        <v>5700665</v>
+        <v>0</v>
       </c>
       <c r="N198" t="n">
-        <v>-12717506</v>
+        <v>0</v>
       </c>
       <c r="O198" t="n">
-        <v>10694554</v>
+        <v>0</v>
       </c>
       <c r="P198" t="n">
-        <v>122355656</v>
+        <v>0</v>
       </c>
       <c r="Q198" t="n">
-        <v>5655665</v>
+        <v>0</v>
       </c>
       <c r="R198" t="n">
-        <v>-9721923</v>
+        <v>0</v>
       </c>
       <c r="S198" t="n">
-        <v>12661155</v>
+        <v>0</v>
       </c>
       <c r="T198" t="n">
-        <v>119793944</v>
+        <v>0</v>
       </c>
       <c r="U198" t="n">
-        <v>7000</v>
+        <v>0</v>
       </c>
       <c r="V198" t="n">
-        <v>83264</v>
+        <v>0</v>
       </c>
       <c r="W198" t="n">
-        <v>274264</v>
+        <v>0</v>
       </c>
       <c r="X198" t="n">
-        <v>368264</v>
+        <v>0</v>
       </c>
       <c r="Y198" t="n">
-        <v>38000</v>
+        <v>0</v>
       </c>
       <c r="Z198" t="n">
-        <v>-3078847</v>
+        <v>0</v>
       </c>
       <c r="AA198" t="n">
-        <v>-2240865</v>
+        <v>0</v>
       </c>
       <c r="AB198" t="n">
-        <v>2193448</v>
+        <v>0</v>
       </c>
       <c r="AC198" t="n">
         <v>8</v>
@@ -27575,10 +27575,10 @@
         <v>8</v>
       </c>
       <c r="AE198" t="n">
-        <v>-30</v>
+        <v>20</v>
       </c>
       <c r="AF198" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="AG198" t="n">
         <v>0</v>
@@ -27598,29 +27598,29 @@
       </c>
       <c r="AM198" t="inlineStr">
         <is>
-          <t>跌破5日線、量能未放大、接近20日低點</t>
+          <t>站上5日線、量能未放大</t>
         </is>
       </c>
       <c r="AN198" t="inlineStr">
         <is>
-          <t>5日法人明顯買超、外資投信同步買超</t>
+          <t>籌碼中性</t>
         </is>
       </c>
       <c r="AO198" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、量能未放大、接近20日低點、5日法人明顯買超、外資投信同步買超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、量能未放大、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>3260.TWO</t>
+          <t>6510.TWO</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>威剛</t>
+          <t>精測</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -27629,28 +27629,28 @@
         </is>
       </c>
       <c r="D199" t="n">
-        <v>396</v>
+        <v>2755</v>
       </c>
       <c r="E199" t="n">
-        <v>392.6</v>
+        <v>2594</v>
       </c>
       <c r="F199" t="n">
-        <v>388.95</v>
+        <v>2583</v>
       </c>
       <c r="G199" t="n">
-        <v>389.15</v>
+        <v>2649.75</v>
       </c>
       <c r="H199" t="n">
-        <v>13937000</v>
+        <v>627000</v>
       </c>
       <c r="I199" t="n">
-        <v>16817400</v>
+        <v>656400</v>
       </c>
       <c r="J199" t="n">
-        <v>419.5</v>
+        <v>3000</v>
       </c>
       <c r="K199" t="n">
-        <v>334</v>
+        <v>2235</v>
       </c>
       <c r="L199" t="inlineStr">
         <is>
@@ -27752,12 +27752,12 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>2387.TW</t>
+          <t>2002.TW</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>精元</t>
+          <t>中鋼</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -27766,28 +27766,28 @@
         </is>
       </c>
       <c r="D200" t="n">
-        <v>37.85</v>
+        <v>18.9</v>
       </c>
       <c r="E200" t="n">
-        <v>37.64</v>
+        <v>18.9</v>
       </c>
       <c r="F200" t="n">
-        <v>37.98</v>
+        <v>18.99</v>
       </c>
       <c r="G200" t="n">
-        <v>38.44</v>
+        <v>18.82</v>
       </c>
       <c r="H200" t="n">
-        <v>685825</v>
+        <v>18036777</v>
       </c>
       <c r="I200" t="n">
-        <v>432933</v>
+        <v>30506159</v>
       </c>
       <c r="J200" t="n">
-        <v>40.6</v>
+        <v>19.45</v>
       </c>
       <c r="K200" t="n">
-        <v>36.7</v>
+        <v>18.25</v>
       </c>
       <c r="L200" t="inlineStr">
         <is>
@@ -27795,52 +27795,52 @@
         </is>
       </c>
       <c r="M200" t="n">
-        <v>36869</v>
+        <v>5700665</v>
       </c>
       <c r="N200" t="n">
-        <v>-23939</v>
+        <v>-12717506</v>
       </c>
       <c r="O200" t="n">
-        <v>138755</v>
+        <v>10694554</v>
       </c>
       <c r="P200" t="n">
-        <v>-158412</v>
+        <v>122355656</v>
       </c>
       <c r="Q200" t="n">
-        <v>40842</v>
+        <v>5655665</v>
       </c>
       <c r="R200" t="n">
-        <v>31742</v>
+        <v>-9721923</v>
       </c>
       <c r="S200" t="n">
-        <v>217722</v>
+        <v>12661155</v>
       </c>
       <c r="T200" t="n">
-        <v>-269849</v>
+        <v>119793944</v>
       </c>
       <c r="U200" t="n">
-        <v>-7943</v>
+        <v>7000</v>
       </c>
       <c r="V200" t="n">
-        <v>-17408</v>
+        <v>83264</v>
       </c>
       <c r="W200" t="n">
-        <v>-17408</v>
+        <v>274264</v>
       </c>
       <c r="X200" t="n">
-        <v>115060</v>
+        <v>368264</v>
       </c>
       <c r="Y200" t="n">
-        <v>3970</v>
+        <v>38000</v>
       </c>
       <c r="Z200" t="n">
-        <v>-38273</v>
+        <v>-3078847</v>
       </c>
       <c r="AA200" t="n">
-        <v>-61559</v>
+        <v>-2240865</v>
       </c>
       <c r="AB200" t="n">
-        <v>-3623</v>
+        <v>2193448</v>
       </c>
       <c r="AC200" t="n">
         <v>8</v>
@@ -27849,10 +27849,10 @@
         <v>8</v>
       </c>
       <c r="AE200" t="n">
-        <v>0</v>
+        <v>-30</v>
       </c>
       <c r="AF200" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="AG200" t="n">
         <v>0</v>
@@ -27872,17 +27872,17 @@
       </c>
       <c r="AM200" t="inlineStr">
         <is>
-          <t>站上5日線、空頭排列、成交量放大、接近20日低點</t>
+          <t>跌破5日線、量能未放大、接近20日低點</t>
         </is>
       </c>
       <c r="AN200" t="inlineStr">
         <is>
-          <t>5日法人買超、外資買投信賣</t>
+          <t>5日法人明顯買超、外資投信同步買超</t>
         </is>
       </c>
       <c r="AO200" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、空頭排列、成交量放大、接近20日低點、5日法人買超、外資買投信賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、量能未放大、接近20日低點、5日法人明顯買超、外資投信同步買超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
@@ -28026,12 +28026,12 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>4908.TWO</t>
+          <t>3260.TWO</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>前鼎</t>
+          <t>威剛</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -28040,28 +28040,28 @@
         </is>
       </c>
       <c r="D202" t="n">
-        <v>165.5</v>
+        <v>396</v>
       </c>
       <c r="E202" t="n">
-        <v>141.8</v>
+        <v>392.6</v>
       </c>
       <c r="F202" t="n">
-        <v>139.55</v>
+        <v>388.95</v>
       </c>
       <c r="G202" t="n">
-        <v>145.28</v>
+        <v>389.15</v>
       </c>
       <c r="H202" t="n">
-        <v>547000</v>
+        <v>13937000</v>
       </c>
       <c r="I202" t="n">
-        <v>1355600</v>
+        <v>16817400</v>
       </c>
       <c r="J202" t="n">
-        <v>171.5</v>
+        <v>419.5</v>
       </c>
       <c r="K202" t="n">
-        <v>117</v>
+        <v>334</v>
       </c>
       <c r="L202" t="inlineStr">
         <is>
@@ -28163,12 +28163,12 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>6510.TWO</t>
+          <t>2845.TW</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>精測</t>
+          <t>遠東銀</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -28177,28 +28177,28 @@
         </is>
       </c>
       <c r="D203" t="n">
-        <v>2755</v>
+        <v>13.3</v>
       </c>
       <c r="E203" t="n">
-        <v>2594</v>
+        <v>13.38</v>
       </c>
       <c r="F203" t="n">
-        <v>2583</v>
+        <v>13.34</v>
       </c>
       <c r="G203" t="n">
-        <v>2649.75</v>
+        <v>13.35</v>
       </c>
       <c r="H203" t="n">
-        <v>627000</v>
+        <v>4451076</v>
       </c>
       <c r="I203" t="n">
-        <v>656400</v>
+        <v>11676503</v>
       </c>
       <c r="J203" t="n">
-        <v>3000</v>
+        <v>13.65</v>
       </c>
       <c r="K203" t="n">
-        <v>2235</v>
+        <v>13.1</v>
       </c>
       <c r="L203" t="inlineStr">
         <is>
@@ -28206,52 +28206,52 @@
         </is>
       </c>
       <c r="M203" t="n">
-        <v>0</v>
+        <v>-875983</v>
       </c>
       <c r="N203" t="n">
-        <v>0</v>
+        <v>-4771808</v>
       </c>
       <c r="O203" t="n">
-        <v>0</v>
+        <v>16279035</v>
       </c>
       <c r="P203" t="n">
-        <v>0</v>
+        <v>26517674</v>
       </c>
       <c r="Q203" t="n">
-        <v>0</v>
+        <v>-898983</v>
       </c>
       <c r="R203" t="n">
-        <v>0</v>
+        <v>-4198113</v>
       </c>
       <c r="S203" t="n">
-        <v>0</v>
+        <v>16940517</v>
       </c>
       <c r="T203" t="n">
-        <v>0</v>
+        <v>24314924</v>
       </c>
       <c r="U203" t="n">
         <v>0</v>
       </c>
       <c r="V203" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="W203" t="n">
-        <v>0</v>
+        <v>6000</v>
       </c>
       <c r="X203" t="n">
-        <v>0</v>
+        <v>2561000</v>
       </c>
       <c r="Y203" t="n">
-        <v>0</v>
+        <v>23000</v>
       </c>
       <c r="Z203" t="n">
-        <v>0</v>
+        <v>-574695</v>
       </c>
       <c r="AA203" t="n">
-        <v>0</v>
+        <v>-667482</v>
       </c>
       <c r="AB203" t="n">
-        <v>0</v>
+        <v>-358250</v>
       </c>
       <c r="AC203" t="n">
         <v>8</v>
@@ -28260,10 +28260,10 @@
         <v>8</v>
       </c>
       <c r="AE203" t="n">
-        <v>20</v>
+        <v>-30</v>
       </c>
       <c r="AF203" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AG203" t="n">
         <v>0</v>
@@ -28283,17 +28283,17 @@
       </c>
       <c r="AM203" t="inlineStr">
         <is>
-          <t>站上5日線、量能未放大</t>
+          <t>跌破5日線、量能未放大、接近20日低點</t>
         </is>
       </c>
       <c r="AN203" t="inlineStr">
         <is>
-          <t>籌碼中性</t>
+          <t>5日法人明顯買超、外資投信同步買超</t>
         </is>
       </c>
       <c r="AO203" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、量能未放大、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、量能未放大、接近20日低點、5日法人明顯買超、外資投信同步買超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
@@ -28437,12 +28437,12 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>2845.TW</t>
+          <t>2412.TW</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>遠東銀</t>
+          <t>中華電</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
@@ -28451,28 +28451,28 @@
         </is>
       </c>
       <c r="D205" t="n">
-        <v>13.3</v>
+        <v>137</v>
       </c>
       <c r="E205" t="n">
-        <v>13.38</v>
+        <v>138.5</v>
       </c>
       <c r="F205" t="n">
-        <v>13.34</v>
+        <v>139.15</v>
       </c>
       <c r="G205" t="n">
-        <v>13.35</v>
+        <v>137.72</v>
       </c>
       <c r="H205" t="n">
-        <v>4451076</v>
+        <v>11911467</v>
       </c>
       <c r="I205" t="n">
-        <v>11676503</v>
+        <v>16057396</v>
       </c>
       <c r="J205" t="n">
-        <v>13.65</v>
+        <v>142.5</v>
       </c>
       <c r="K205" t="n">
-        <v>13.1</v>
+        <v>132</v>
       </c>
       <c r="L205" t="inlineStr">
         <is>
@@ -28480,52 +28480,52 @@
         </is>
       </c>
       <c r="M205" t="n">
-        <v>-875983</v>
+        <v>1242020</v>
       </c>
       <c r="N205" t="n">
-        <v>-4771808</v>
+        <v>-2058149</v>
       </c>
       <c r="O205" t="n">
-        <v>16279035</v>
+        <v>14332686</v>
       </c>
       <c r="P205" t="n">
-        <v>26517674</v>
+        <v>64638306</v>
       </c>
       <c r="Q205" t="n">
-        <v>-898983</v>
+        <v>1089905</v>
       </c>
       <c r="R205" t="n">
-        <v>-4198113</v>
+        <v>92869</v>
       </c>
       <c r="S205" t="n">
-        <v>16940517</v>
+        <v>14297808</v>
       </c>
       <c r="T205" t="n">
-        <v>24314924</v>
+        <v>60939678</v>
       </c>
       <c r="U205" t="n">
-        <v>0</v>
+        <v>-1274</v>
       </c>
       <c r="V205" t="n">
-        <v>1000</v>
+        <v>-1489647</v>
       </c>
       <c r="W205" t="n">
-        <v>6000</v>
+        <v>225599</v>
       </c>
       <c r="X205" t="n">
-        <v>2561000</v>
+        <v>469073</v>
       </c>
       <c r="Y205" t="n">
-        <v>23000</v>
+        <v>153389</v>
       </c>
       <c r="Z205" t="n">
-        <v>-574695</v>
+        <v>-661371</v>
       </c>
       <c r="AA205" t="n">
-        <v>-667482</v>
+        <v>-190721</v>
       </c>
       <c r="AB205" t="n">
-        <v>-358250</v>
+        <v>3229555</v>
       </c>
       <c r="AC205" t="n">
         <v>8</v>
@@ -28574,12 +28574,12 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>2412.TW</t>
+          <t>3008.TW</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>中華電</t>
+          <t>大立光</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
@@ -28588,96 +28588,96 @@
         </is>
       </c>
       <c r="D206" t="n">
-        <v>137</v>
+        <v>4575</v>
       </c>
       <c r="E206" t="n">
-        <v>138.5</v>
+        <v>4128</v>
       </c>
       <c r="F206" t="n">
-        <v>139.15</v>
+        <v>4054</v>
       </c>
       <c r="G206" t="n">
-        <v>137.72</v>
+        <v>4061</v>
       </c>
       <c r="H206" t="n">
-        <v>11911467</v>
+        <v>4740431</v>
       </c>
       <c r="I206" t="n">
-        <v>16057396</v>
+        <v>2865078</v>
       </c>
       <c r="J206" t="n">
-        <v>142.5</v>
+        <v>4730</v>
       </c>
       <c r="K206" t="n">
-        <v>132</v>
+        <v>3670</v>
       </c>
       <c r="L206" t="inlineStr">
         <is>
-          <t>無明顯異常</t>
+          <t>帶量突破20日高點</t>
         </is>
       </c>
       <c r="M206" t="n">
-        <v>1242020</v>
+        <v>-18047</v>
       </c>
       <c r="N206" t="n">
-        <v>-2058149</v>
+        <v>-412096</v>
       </c>
       <c r="O206" t="n">
-        <v>14332686</v>
+        <v>-790238</v>
       </c>
       <c r="P206" t="n">
-        <v>64638306</v>
+        <v>-1183769</v>
       </c>
       <c r="Q206" t="n">
-        <v>1089905</v>
+        <v>-389081</v>
       </c>
       <c r="R206" t="n">
-        <v>92869</v>
+        <v>-945754</v>
       </c>
       <c r="S206" t="n">
-        <v>14297808</v>
+        <v>-1592429</v>
       </c>
       <c r="T206" t="n">
-        <v>60939678</v>
+        <v>-2586202</v>
       </c>
       <c r="U206" t="n">
-        <v>-1274</v>
+        <v>421000</v>
       </c>
       <c r="V206" t="n">
-        <v>-1489647</v>
+        <v>506913</v>
       </c>
       <c r="W206" t="n">
-        <v>225599</v>
+        <v>739648</v>
       </c>
       <c r="X206" t="n">
-        <v>469073</v>
+        <v>1530710</v>
       </c>
       <c r="Y206" t="n">
-        <v>153389</v>
+        <v>-49966</v>
       </c>
       <c r="Z206" t="n">
-        <v>-661371</v>
+        <v>26745</v>
       </c>
       <c r="AA206" t="n">
-        <v>-190721</v>
+        <v>62543</v>
       </c>
       <c r="AB206" t="n">
-        <v>3229555</v>
+        <v>-128277</v>
       </c>
       <c r="AC206" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AD206" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AE206" t="n">
-        <v>-30</v>
+        <v>60</v>
       </c>
       <c r="AF206" t="n">
-        <v>50</v>
+        <v>-55</v>
       </c>
       <c r="AG206" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AH206" t="inlineStr"/>
       <c r="AI206" t="inlineStr"/>
@@ -28694,29 +28694,29 @@
       </c>
       <c r="AM206" t="inlineStr">
         <is>
-          <t>跌破5日線、量能未放大、接近20日低點</t>
+          <t>站上5日線、黃金交叉、成交量放大、帶量突破20日高點</t>
         </is>
       </c>
       <c r="AN206" t="inlineStr">
         <is>
-          <t>5日法人明顯買超、外資投信同步買超</t>
+          <t>法人連續偏賣、5日法人明顯賣超、投信買外資賣</t>
         </is>
       </c>
       <c r="AO206" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、量能未放大、接近20日低點、5日法人明顯買超、外資投信同步買超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、黃金交叉、成交量放大、帶量突破20日高點、法人連續偏賣、5日法人明顯賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>3008.TW</t>
+          <t>2338.TW</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>大立光</t>
+          <t>光罩</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
@@ -28725,96 +28725,96 @@
         </is>
       </c>
       <c r="D207" t="n">
-        <v>4575</v>
+        <v>39.7</v>
       </c>
       <c r="E207" t="n">
-        <v>4128</v>
+        <v>37.28</v>
       </c>
       <c r="F207" t="n">
-        <v>4054</v>
+        <v>38.36</v>
       </c>
       <c r="G207" t="n">
-        <v>4061</v>
+        <v>42.11</v>
       </c>
       <c r="H207" t="n">
-        <v>4740431</v>
+        <v>1694810</v>
       </c>
       <c r="I207" t="n">
-        <v>2865078</v>
+        <v>1854588</v>
       </c>
       <c r="J207" t="n">
-        <v>4730</v>
+        <v>49.75</v>
       </c>
       <c r="K207" t="n">
-        <v>3670</v>
+        <v>33.05</v>
       </c>
       <c r="L207" t="inlineStr">
         <is>
-          <t>帶量突破20日高點</t>
+          <t>無明顯異常</t>
         </is>
       </c>
       <c r="M207" t="n">
-        <v>-18047</v>
+        <v>-6583</v>
       </c>
       <c r="N207" t="n">
-        <v>-412096</v>
+        <v>345029</v>
       </c>
       <c r="O207" t="n">
-        <v>-790238</v>
+        <v>353416</v>
       </c>
       <c r="P207" t="n">
-        <v>-1183769</v>
+        <v>-1331057</v>
       </c>
       <c r="Q207" t="n">
-        <v>-389081</v>
+        <v>-5388</v>
       </c>
       <c r="R207" t="n">
-        <v>-945754</v>
+        <v>504238</v>
       </c>
       <c r="S207" t="n">
-        <v>-1592429</v>
+        <v>690578</v>
       </c>
       <c r="T207" t="n">
-        <v>-2586202</v>
+        <v>-814291</v>
       </c>
       <c r="U207" t="n">
-        <v>421000</v>
+        <v>0</v>
       </c>
       <c r="V207" t="n">
-        <v>506913</v>
+        <v>0</v>
       </c>
       <c r="W207" t="n">
-        <v>739648</v>
+        <v>0</v>
       </c>
       <c r="X207" t="n">
-        <v>1530710</v>
+        <v>0</v>
       </c>
       <c r="Y207" t="n">
-        <v>-49966</v>
+        <v>-1195</v>
       </c>
       <c r="Z207" t="n">
-        <v>26745</v>
+        <v>-159209</v>
       </c>
       <c r="AA207" t="n">
-        <v>62543</v>
+        <v>-337162</v>
       </c>
       <c r="AB207" t="n">
-        <v>-128277</v>
+        <v>-516766</v>
       </c>
       <c r="AC207" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AD207" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AE207" t="n">
-        <v>60</v>
+        <v>-5</v>
       </c>
       <c r="AF207" t="n">
-        <v>-55</v>
+        <v>20</v>
       </c>
       <c r="AG207" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="AH207" t="inlineStr"/>
       <c r="AI207" t="inlineStr"/>
@@ -28831,29 +28831,29 @@
       </c>
       <c r="AM207" t="inlineStr">
         <is>
-          <t>站上5日線、黃金交叉、成交量放大、帶量突破20日高點</t>
+          <t>站上5日線、空頭排列、量能未放大</t>
         </is>
       </c>
       <c r="AN207" t="inlineStr">
         <is>
-          <t>法人連續偏賣、5日法人明顯賣超、投信買外資賣</t>
+          <t>5日法人買超</t>
         </is>
       </c>
       <c r="AO207" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、黃金交叉、成交量放大、帶量突破20日高點、法人連續偏賣、5日法人明顯賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、空頭排列、量能未放大、5日法人買超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>2338.TW</t>
+          <t>8028.TW</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>光罩</t>
+          <t>昇陽半導體</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
@@ -28862,28 +28862,28 @@
         </is>
       </c>
       <c r="D208" t="n">
-        <v>39.7</v>
+        <v>282</v>
       </c>
       <c r="E208" t="n">
-        <v>37.28</v>
+        <v>256.6</v>
       </c>
       <c r="F208" t="n">
-        <v>38.36</v>
+        <v>272.7</v>
       </c>
       <c r="G208" t="n">
-        <v>42.11</v>
+        <v>291.8</v>
       </c>
       <c r="H208" t="n">
-        <v>1694810</v>
+        <v>1547396</v>
       </c>
       <c r="I208" t="n">
-        <v>1854588</v>
+        <v>1582576</v>
       </c>
       <c r="J208" t="n">
-        <v>49.75</v>
+        <v>351.5</v>
       </c>
       <c r="K208" t="n">
-        <v>33.05</v>
+        <v>227</v>
       </c>
       <c r="L208" t="inlineStr">
         <is>
@@ -28891,52 +28891,52 @@
         </is>
       </c>
       <c r="M208" t="n">
-        <v>-6583</v>
+        <v>36018</v>
       </c>
       <c r="N208" t="n">
-        <v>345029</v>
+        <v>-45479</v>
       </c>
       <c r="O208" t="n">
-        <v>353416</v>
+        <v>106847</v>
       </c>
       <c r="P208" t="n">
-        <v>-1331057</v>
+        <v>728991</v>
       </c>
       <c r="Q208" t="n">
-        <v>-5388</v>
+        <v>266479</v>
       </c>
       <c r="R208" t="n">
-        <v>504238</v>
+        <v>117384</v>
       </c>
       <c r="S208" t="n">
-        <v>690578</v>
+        <v>729323</v>
       </c>
       <c r="T208" t="n">
-        <v>-814291</v>
+        <v>1912847</v>
       </c>
       <c r="U208" t="n">
-        <v>0</v>
+        <v>-185000</v>
       </c>
       <c r="V208" t="n">
-        <v>0</v>
+        <v>-100000</v>
       </c>
       <c r="W208" t="n">
-        <v>0</v>
+        <v>-598000</v>
       </c>
       <c r="X208" t="n">
-        <v>0</v>
+        <v>-1079000</v>
       </c>
       <c r="Y208" t="n">
-        <v>-1195</v>
+        <v>-45461</v>
       </c>
       <c r="Z208" t="n">
-        <v>-159209</v>
+        <v>-62863</v>
       </c>
       <c r="AA208" t="n">
-        <v>-337162</v>
+        <v>-24476</v>
       </c>
       <c r="AB208" t="n">
-        <v>-516766</v>
+        <v>-104856</v>
       </c>
       <c r="AC208" t="n">
         <v>6</v>
@@ -28973,12 +28973,12 @@
       </c>
       <c r="AN208" t="inlineStr">
         <is>
-          <t>5日法人買超</t>
+          <t>5日法人買超、外資買投信賣</t>
         </is>
       </c>
       <c r="AO208" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、空頭排列、量能未放大、5日法人買超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、空頭排列、量能未放大、5日法人買超、外資買投信賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
@@ -29122,12 +29122,12 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>8028.TW</t>
+          <t>6409.TW</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>昇陽半導體</t>
+          <t>旭隼</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
@@ -29136,28 +29136,28 @@
         </is>
       </c>
       <c r="D210" t="n">
-        <v>282</v>
+        <v>963</v>
       </c>
       <c r="E210" t="n">
-        <v>256.6</v>
+        <v>936.6</v>
       </c>
       <c r="F210" t="n">
-        <v>272.7</v>
+        <v>955.1</v>
       </c>
       <c r="G210" t="n">
-        <v>291.8</v>
+        <v>998.65</v>
       </c>
       <c r="H210" t="n">
-        <v>1547396</v>
+        <v>350627</v>
       </c>
       <c r="I210" t="n">
-        <v>1582576</v>
+        <v>395899</v>
       </c>
       <c r="J210" t="n">
-        <v>351.5</v>
+        <v>1175</v>
       </c>
       <c r="K210" t="n">
-        <v>227</v>
+        <v>869</v>
       </c>
       <c r="L210" t="inlineStr">
         <is>
@@ -29165,52 +29165,52 @@
         </is>
       </c>
       <c r="M210" t="n">
-        <v>36018</v>
+        <v>-9415</v>
       </c>
       <c r="N210" t="n">
-        <v>-45479</v>
+        <v>-45062</v>
       </c>
       <c r="O210" t="n">
-        <v>106847</v>
+        <v>49337</v>
       </c>
       <c r="P210" t="n">
-        <v>728991</v>
+        <v>472887</v>
       </c>
       <c r="Q210" t="n">
-        <v>266479</v>
+        <v>-13393</v>
       </c>
       <c r="R210" t="n">
-        <v>117384</v>
+        <v>-27950</v>
       </c>
       <c r="S210" t="n">
-        <v>729323</v>
+        <v>42530</v>
       </c>
       <c r="T210" t="n">
-        <v>1912847</v>
+        <v>407315</v>
       </c>
       <c r="U210" t="n">
-        <v>-185000</v>
+        <v>-1265</v>
       </c>
       <c r="V210" t="n">
-        <v>-100000</v>
+        <v>-2534</v>
       </c>
       <c r="W210" t="n">
-        <v>-598000</v>
+        <v>5564</v>
       </c>
       <c r="X210" t="n">
-        <v>-1079000</v>
+        <v>78280</v>
       </c>
       <c r="Y210" t="n">
-        <v>-45461</v>
+        <v>5243</v>
       </c>
       <c r="Z210" t="n">
-        <v>-62863</v>
+        <v>-14578</v>
       </c>
       <c r="AA210" t="n">
-        <v>-24476</v>
+        <v>1243</v>
       </c>
       <c r="AB210" t="n">
-        <v>-104856</v>
+        <v>-12708</v>
       </c>
       <c r="AC210" t="n">
         <v>6</v>
@@ -29247,12 +29247,12 @@
       </c>
       <c r="AN210" t="inlineStr">
         <is>
-          <t>5日法人買超、外資買投信賣</t>
+          <t>籌碼中性、外資投信同步買超</t>
         </is>
       </c>
       <c r="AO210" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、空頭排列、量能未放大、5日法人買超、外資買投信賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、空頭排列、量能未放大、籌碼中性、外資投信同步買超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
@@ -29533,12 +29533,12 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>2851.TW</t>
+          <t>2436.TW</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>中再保</t>
+          <t>偉詮電</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
@@ -29547,28 +29547,28 @@
         </is>
       </c>
       <c r="D213" t="n">
-        <v>35</v>
+        <v>61</v>
       </c>
       <c r="E213" t="n">
-        <v>34.6</v>
+        <v>56.56</v>
       </c>
       <c r="F213" t="n">
-        <v>34.76</v>
+        <v>56.73</v>
       </c>
       <c r="G213" t="n">
-        <v>35.93</v>
+        <v>59.48</v>
       </c>
       <c r="H213" t="n">
-        <v>961679</v>
+        <v>10015844</v>
       </c>
       <c r="I213" t="n">
-        <v>1731530</v>
+        <v>3532379</v>
       </c>
       <c r="J213" t="n">
-        <v>38.9</v>
+        <v>71.3</v>
       </c>
       <c r="K213" t="n">
-        <v>32.95</v>
+        <v>49.7</v>
       </c>
       <c r="L213" t="inlineStr">
         <is>
@@ -29576,28 +29576,28 @@
         </is>
       </c>
       <c r="M213" t="n">
-        <v>-109761</v>
+        <v>-1530996</v>
       </c>
       <c r="N213" t="n">
-        <v>-354735</v>
+        <v>-311293</v>
       </c>
       <c r="O213" t="n">
-        <v>258022</v>
+        <v>15864</v>
       </c>
       <c r="P213" t="n">
-        <v>759375</v>
+        <v>-1850105</v>
       </c>
       <c r="Q213" t="n">
-        <v>-89000</v>
+        <v>-1623495</v>
       </c>
       <c r="R213" t="n">
-        <v>-250577</v>
+        <v>-407627</v>
       </c>
       <c r="S213" t="n">
-        <v>437715</v>
+        <v>-190354</v>
       </c>
       <c r="T213" t="n">
-        <v>900037</v>
+        <v>-1811604</v>
       </c>
       <c r="U213" t="n">
         <v>0</v>
@@ -29606,22 +29606,22 @@
         <v>0</v>
       </c>
       <c r="W213" t="n">
-        <v>0</v>
+        <v>30000</v>
       </c>
       <c r="X213" t="n">
-        <v>0</v>
+        <v>45000</v>
       </c>
       <c r="Y213" t="n">
-        <v>-20761</v>
+        <v>92499</v>
       </c>
       <c r="Z213" t="n">
-        <v>-104158</v>
+        <v>96334</v>
       </c>
       <c r="AA213" t="n">
-        <v>-179693</v>
+        <v>176218</v>
       </c>
       <c r="AB213" t="n">
-        <v>-140662</v>
+        <v>-83501</v>
       </c>
       <c r="AC213" t="n">
         <v>6</v>
@@ -29630,10 +29630,10 @@
         <v>6</v>
       </c>
       <c r="AE213" t="n">
-        <v>-5</v>
+        <v>15</v>
       </c>
       <c r="AF213" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AG213" t="n">
         <v>0</v>
@@ -29653,29 +29653,29 @@
       </c>
       <c r="AM213" t="inlineStr">
         <is>
-          <t>站上5日線、空頭排列、量能未放大</t>
+          <t>站上5日線、空頭排列、爆量</t>
         </is>
       </c>
       <c r="AN213" t="inlineStr">
         <is>
-          <t>5日法人買超</t>
+          <t>籌碼中性、投信買外資賣</t>
         </is>
       </c>
       <c r="AO213" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、空頭排列、量能未放大、5日法人買超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、空頭排列、爆量、籌碼中性、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>6409.TW</t>
+          <t>2851.TW</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>旭隼</t>
+          <t>中再保</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
@@ -29684,28 +29684,28 @@
         </is>
       </c>
       <c r="D214" t="n">
-        <v>963</v>
+        <v>35</v>
       </c>
       <c r="E214" t="n">
-        <v>936.6</v>
+        <v>34.6</v>
       </c>
       <c r="F214" t="n">
-        <v>955.1</v>
+        <v>34.76</v>
       </c>
       <c r="G214" t="n">
-        <v>998.65</v>
+        <v>35.93</v>
       </c>
       <c r="H214" t="n">
-        <v>350627</v>
+        <v>961679</v>
       </c>
       <c r="I214" t="n">
-        <v>395899</v>
+        <v>1731530</v>
       </c>
       <c r="J214" t="n">
-        <v>1175</v>
+        <v>38.9</v>
       </c>
       <c r="K214" t="n">
-        <v>869</v>
+        <v>32.95</v>
       </c>
       <c r="L214" t="inlineStr">
         <is>
@@ -29713,52 +29713,52 @@
         </is>
       </c>
       <c r="M214" t="n">
-        <v>-9415</v>
+        <v>-109761</v>
       </c>
       <c r="N214" t="n">
-        <v>-45062</v>
+        <v>-354735</v>
       </c>
       <c r="O214" t="n">
-        <v>49337</v>
+        <v>258022</v>
       </c>
       <c r="P214" t="n">
-        <v>472887</v>
+        <v>759375</v>
       </c>
       <c r="Q214" t="n">
-        <v>-13393</v>
+        <v>-89000</v>
       </c>
       <c r="R214" t="n">
-        <v>-27950</v>
+        <v>-250577</v>
       </c>
       <c r="S214" t="n">
-        <v>42530</v>
+        <v>437715</v>
       </c>
       <c r="T214" t="n">
-        <v>407315</v>
+        <v>900037</v>
       </c>
       <c r="U214" t="n">
-        <v>-1265</v>
+        <v>0</v>
       </c>
       <c r="V214" t="n">
-        <v>-2534</v>
+        <v>0</v>
       </c>
       <c r="W214" t="n">
-        <v>5564</v>
+        <v>0</v>
       </c>
       <c r="X214" t="n">
-        <v>78280</v>
+        <v>0</v>
       </c>
       <c r="Y214" t="n">
-        <v>5243</v>
+        <v>-20761</v>
       </c>
       <c r="Z214" t="n">
-        <v>-14578</v>
+        <v>-104158</v>
       </c>
       <c r="AA214" t="n">
-        <v>1243</v>
+        <v>-179693</v>
       </c>
       <c r="AB214" t="n">
-        <v>-12708</v>
+        <v>-140662</v>
       </c>
       <c r="AC214" t="n">
         <v>6</v>
@@ -29795,12 +29795,12 @@
       </c>
       <c r="AN214" t="inlineStr">
         <is>
-          <t>籌碼中性、外資投信同步買超</t>
+          <t>5日法人買超</t>
         </is>
       </c>
       <c r="AO214" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、空頭排列、量能未放大、籌碼中性、外資投信同步買超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、空頭排列、量能未放大、5日法人買超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
@@ -29833,10 +29833,10 @@
         <v>2237.5</v>
       </c>
       <c r="H215" t="n">
-        <v>2906548</v>
+        <v>2914548</v>
       </c>
       <c r="I215" t="n">
-        <v>3079370</v>
+        <v>3080970</v>
       </c>
       <c r="J215" t="n">
         <v>2565</v>
@@ -29944,12 +29944,12 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>2436.TW</t>
+          <t>2546.TW</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>偉詮電</t>
+          <t>根基</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
@@ -29958,28 +29958,28 @@
         </is>
       </c>
       <c r="D216" t="n">
-        <v>61</v>
+        <v>99.2</v>
       </c>
       <c r="E216" t="n">
-        <v>56.56</v>
+        <v>100.62</v>
       </c>
       <c r="F216" t="n">
-        <v>56.73</v>
+        <v>98.56999999999999</v>
       </c>
       <c r="G216" t="n">
-        <v>59.48</v>
+        <v>96.73</v>
       </c>
       <c r="H216" t="n">
-        <v>10015844</v>
+        <v>346686</v>
       </c>
       <c r="I216" t="n">
-        <v>3532379</v>
+        <v>381760</v>
       </c>
       <c r="J216" t="n">
-        <v>71.3</v>
+        <v>105</v>
       </c>
       <c r="K216" t="n">
-        <v>49.7</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="L216" t="inlineStr">
         <is>
@@ -29987,52 +29987,52 @@
         </is>
       </c>
       <c r="M216" t="n">
-        <v>-1530996</v>
+        <v>-115540</v>
       </c>
       <c r="N216" t="n">
-        <v>-311293</v>
+        <v>-227800</v>
       </c>
       <c r="O216" t="n">
-        <v>15864</v>
+        <v>85160</v>
       </c>
       <c r="P216" t="n">
-        <v>-1850105</v>
+        <v>348559</v>
       </c>
       <c r="Q216" t="n">
-        <v>-1623495</v>
+        <v>-115540</v>
       </c>
       <c r="R216" t="n">
-        <v>-407627</v>
+        <v>-358680</v>
       </c>
       <c r="S216" t="n">
-        <v>-190354</v>
+        <v>-36720</v>
       </c>
       <c r="T216" t="n">
-        <v>-1811604</v>
+        <v>199679</v>
       </c>
       <c r="U216" t="n">
         <v>0</v>
       </c>
       <c r="V216" t="n">
-        <v>0</v>
+        <v>163000</v>
       </c>
       <c r="W216" t="n">
-        <v>30000</v>
+        <v>163000</v>
       </c>
       <c r="X216" t="n">
-        <v>45000</v>
+        <v>164000</v>
       </c>
       <c r="Y216" t="n">
-        <v>92499</v>
+        <v>0</v>
       </c>
       <c r="Z216" t="n">
-        <v>96334</v>
+        <v>-32120</v>
       </c>
       <c r="AA216" t="n">
-        <v>176218</v>
+        <v>-41120</v>
       </c>
       <c r="AB216" t="n">
-        <v>-83501</v>
+        <v>-15120</v>
       </c>
       <c r="AC216" t="n">
         <v>6</v>
@@ -30041,10 +30041,10 @@
         <v>6</v>
       </c>
       <c r="AE216" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="AF216" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AG216" t="n">
         <v>0</v>
@@ -30064,17 +30064,17 @@
       </c>
       <c r="AM216" t="inlineStr">
         <is>
-          <t>站上5日線、空頭排列、爆量</t>
+          <t>跌破5日線、多頭排列、量能未放大</t>
         </is>
       </c>
       <c r="AN216" t="inlineStr">
         <is>
-          <t>籌碼中性、投信買外資賣</t>
+          <t>5日法人小幅買超、投信買外資賣</t>
         </is>
       </c>
       <c r="AO216" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、空頭排列、爆量、籌碼中性、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、多頭排列、量能未放大、5日法人小幅買超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
@@ -32025,10 +32025,10 @@
         <v>77.25</v>
       </c>
       <c r="H231" t="n">
-        <v>17443976</v>
+        <v>17477976</v>
       </c>
       <c r="I231" t="n">
-        <v>26236290</v>
+        <v>26243090</v>
       </c>
       <c r="J231" t="n">
         <v>80.7</v>
@@ -37231,10 +37231,10 @@
         <v>34.55</v>
       </c>
       <c r="H269" t="n">
-        <v>48626332</v>
+        <v>50836332</v>
       </c>
       <c r="I269" t="n">
-        <v>56124562</v>
+        <v>56566562</v>
       </c>
       <c r="J269" t="n">
         <v>36.9</v>
@@ -41204,10 +41204,10 @@
         <v>1749</v>
       </c>
       <c r="H298" t="n">
-        <v>13548461</v>
+        <v>16778461</v>
       </c>
       <c r="I298" t="n">
-        <v>21194624</v>
+        <v>21840624</v>
       </c>
       <c r="J298" t="n">
         <v>1980</v>
@@ -44766,10 +44766,10 @@
         <v>63.93</v>
       </c>
       <c r="H324" t="n">
-        <v>240801216</v>
+        <v>240808216</v>
       </c>
       <c r="I324" t="n">
-        <v>170398987</v>
+        <v>170400387</v>
       </c>
       <c r="J324" t="n">
         <v>79.5</v>
@@ -44903,10 +44903,10 @@
         <v>134.75</v>
       </c>
       <c r="H325" t="n">
-        <v>275919812</v>
+        <v>279502812</v>
       </c>
       <c r="I325" t="n">
-        <v>250427015</v>
+        <v>251143615</v>
       </c>
       <c r="J325" t="n">
         <v>168</v>
@@ -48054,10 +48054,10 @@
         <v>667.42</v>
       </c>
       <c r="H348" t="n">
-        <v>63100413</v>
+        <v>63678413</v>
       </c>
       <c r="I348" t="n">
-        <v>59278313</v>
+        <v>59393913</v>
       </c>
       <c r="J348" t="n">
         <v>948</v>
@@ -48602,10 +48602,10 @@
         <v>1947.75</v>
       </c>
       <c r="H352" t="n">
-        <v>3639717</v>
+        <v>3640717</v>
       </c>
       <c r="I352" t="n">
-        <v>5167836</v>
+        <v>5168036</v>
       </c>
       <c r="J352" t="n">
         <v>2215</v>
@@ -53114,22 +53114,22 @@
         <v>16.3</v>
       </c>
       <c r="E385" t="n">
-        <v>16.89</v>
+        <v>16.5</v>
       </c>
       <c r="F385" t="n">
-        <v>17.32</v>
+        <v>16.52</v>
       </c>
       <c r="G385" t="n">
-        <v>17.45</v>
+        <v>16.62</v>
       </c>
       <c r="H385" t="n">
         <v>1241628</v>
       </c>
       <c r="I385" t="n">
-        <v>3582534</v>
+        <v>2762297</v>
       </c>
       <c r="J385" t="n">
-        <v>18.05</v>
+        <v>17.35</v>
       </c>
       <c r="K385" t="n">
         <v>16.2</v>
@@ -54904,10 +54904,10 @@
         <v>86.62</v>
       </c>
       <c r="H398" t="n">
-        <v>6941793</v>
+        <v>7119793</v>
       </c>
       <c r="I398" t="n">
-        <v>9085898</v>
+        <v>9121498</v>
       </c>
       <c r="J398" t="n">
         <v>92</v>

--- a/output/universe_analysis_result.xlsx
+++ b/output/universe_analysis_result.xlsx
@@ -22957,12 +22957,12 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>2390.TW</t>
+          <t>5425.TWO</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>云辰</t>
+          <t>台半</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -22971,28 +22971,28 @@
         </is>
       </c>
       <c r="D165" t="n">
-        <v>10.45</v>
+        <v>95.2</v>
       </c>
       <c r="E165" t="n">
-        <v>10.39</v>
+        <v>90.8</v>
       </c>
       <c r="F165" t="n">
-        <v>10.29</v>
+        <v>90.3</v>
       </c>
       <c r="G165" t="n">
-        <v>10.37</v>
+        <v>86.73999999999999</v>
       </c>
       <c r="H165" t="n">
-        <v>636796</v>
+        <v>41848000</v>
       </c>
       <c r="I165" t="n">
-        <v>528249</v>
+        <v>21098200</v>
       </c>
       <c r="J165" t="n">
-        <v>10.95</v>
+        <v>98.5</v>
       </c>
       <c r="K165" t="n">
-        <v>10.1</v>
+        <v>70.5</v>
       </c>
       <c r="L165" t="inlineStr">
         <is>
@@ -23000,28 +23000,28 @@
         </is>
       </c>
       <c r="M165" t="n">
-        <v>151999</v>
+        <v>0</v>
       </c>
       <c r="N165" t="n">
-        <v>175135</v>
+        <v>0</v>
       </c>
       <c r="O165" t="n">
-        <v>-27240</v>
+        <v>0</v>
       </c>
       <c r="P165" t="n">
-        <v>-92378</v>
+        <v>0</v>
       </c>
       <c r="Q165" t="n">
-        <v>136999</v>
+        <v>0</v>
       </c>
       <c r="R165" t="n">
-        <v>154135</v>
+        <v>0</v>
       </c>
       <c r="S165" t="n">
-        <v>-48040</v>
+        <v>0</v>
       </c>
       <c r="T165" t="n">
-        <v>-50159</v>
+        <v>0</v>
       </c>
       <c r="U165" t="n">
         <v>0</v>
@@ -23036,16 +23036,16 @@
         <v>0</v>
       </c>
       <c r="Y165" t="n">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="Z165" t="n">
-        <v>21000</v>
+        <v>0</v>
       </c>
       <c r="AA165" t="n">
-        <v>20800</v>
+        <v>0</v>
       </c>
       <c r="AB165" t="n">
-        <v>-42219</v>
+        <v>0</v>
       </c>
       <c r="AC165" t="n">
         <v>24</v>
@@ -23054,10 +23054,10 @@
         <v>24</v>
       </c>
       <c r="AE165" t="n">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="AF165" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="AG165" t="n">
         <v>0</v>
@@ -23077,29 +23077,29 @@
       </c>
       <c r="AM165" t="inlineStr">
         <is>
-          <t>站上5日線、黃金交叉、量能溫和放大、接近20日低點</t>
+          <t>站上5日線、多頭排列、成交量放大</t>
         </is>
       </c>
       <c r="AN165" t="inlineStr">
         <is>
-          <t>短線籌碼止穩</t>
+          <t>籌碼中性</t>
         </is>
       </c>
       <c r="AO165" t="inlineStr">
         <is>
-          <t>整理觀察：站上5日線、黃金交叉、量能溫和放大、接近20日低點、短線籌碼止穩。多空訊號混合，建議降低追價衝動。</t>
+          <t>整理觀察：站上5日線、多頭排列、成交量放大、籌碼中性。多空訊號混合，建議降低追價衝動。</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>3008.TW</t>
+          <t>2020.TW</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>大立光</t>
+          <t>美亞</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -23108,28 +23108,28 @@
         </is>
       </c>
       <c r="D166" t="n">
-        <v>6915</v>
+        <v>21.85</v>
       </c>
       <c r="E166" t="n">
-        <v>5984</v>
+        <v>21.86</v>
       </c>
       <c r="F166" t="n">
-        <v>5595.5</v>
+        <v>21.7</v>
       </c>
       <c r="G166" t="n">
-        <v>4994.5</v>
+        <v>21.46</v>
       </c>
       <c r="H166" t="n">
-        <v>2913470</v>
+        <v>211233</v>
       </c>
       <c r="I166" t="n">
-        <v>2580123</v>
+        <v>249873</v>
       </c>
       <c r="J166" t="n">
-        <v>6915</v>
+        <v>22.15</v>
       </c>
       <c r="K166" t="n">
-        <v>3880</v>
+        <v>20.9</v>
       </c>
       <c r="L166" t="inlineStr">
         <is>
@@ -23137,52 +23137,52 @@
         </is>
       </c>
       <c r="M166" t="n">
-        <v>96279</v>
+        <v>61000</v>
       </c>
       <c r="N166" t="n">
-        <v>44978</v>
+        <v>149000</v>
       </c>
       <c r="O166" t="n">
-        <v>-348238</v>
+        <v>372049</v>
       </c>
       <c r="P166" t="n">
-        <v>452276</v>
+        <v>773268</v>
       </c>
       <c r="Q166" t="n">
-        <v>-141153</v>
+        <v>60000</v>
       </c>
       <c r="R166" t="n">
-        <v>-241711</v>
+        <v>158000</v>
       </c>
       <c r="S166" t="n">
-        <v>-860098</v>
+        <v>379049</v>
       </c>
       <c r="T166" t="n">
-        <v>-801952</v>
+        <v>779268</v>
       </c>
       <c r="U166" t="n">
-        <v>217966</v>
+        <v>0</v>
       </c>
       <c r="V166" t="n">
-        <v>153917</v>
+        <v>0</v>
       </c>
       <c r="W166" t="n">
-        <v>417966</v>
+        <v>0</v>
       </c>
       <c r="X166" t="n">
-        <v>834234</v>
+        <v>0</v>
       </c>
       <c r="Y166" t="n">
-        <v>19466</v>
+        <v>1000</v>
       </c>
       <c r="Z166" t="n">
-        <v>132772</v>
+        <v>-9000</v>
       </c>
       <c r="AA166" t="n">
-        <v>93894</v>
+        <v>-7000</v>
       </c>
       <c r="AB166" t="n">
-        <v>419994</v>
+        <v>-6000</v>
       </c>
       <c r="AC166" t="n">
         <v>24</v>
@@ -23191,10 +23191,10 @@
         <v>24</v>
       </c>
       <c r="AE166" t="n">
-        <v>80</v>
+        <v>10</v>
       </c>
       <c r="AF166" t="n">
-        <v>-20</v>
+        <v>50</v>
       </c>
       <c r="AG166" t="n">
         <v>0</v>
@@ -23214,17 +23214,17 @@
       </c>
       <c r="AM166" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、量能溫和放大、突破20日高點</t>
+          <t>跌破5日線、多頭排列、量能未放大、接近20日高點、接近20日低點</t>
         </is>
       </c>
       <c r="AN166" t="inlineStr">
         <is>
-          <t>5日法人賣超、投信買外資賣</t>
+          <t>法人連續偏買、5日法人買超</t>
         </is>
       </c>
       <c r="AO166" t="inlineStr">
         <is>
-          <t>整理觀察：站上5日線、多頭排列、量能溫和放大、突破20日高點、5日法人賣超、投信買外資賣。多空訊號混合，建議降低追價衝動。</t>
+          <t>整理觀察：跌破5日線、多頭排列、量能未放大、接近20日高點、接近20日低點、法人連續偏買、5日法人買超。多空訊號混合，建議降低追價衝動。</t>
         </is>
       </c>
     </row>
@@ -23642,12 +23642,12 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>3515.TW</t>
+          <t>3008.TW</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>華擎</t>
+          <t>大立光</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -23656,28 +23656,28 @@
         </is>
       </c>
       <c r="D170" t="n">
-        <v>218</v>
+        <v>6915</v>
       </c>
       <c r="E170" t="n">
-        <v>219.5</v>
+        <v>5984</v>
       </c>
       <c r="F170" t="n">
-        <v>219.95</v>
+        <v>5595.5</v>
       </c>
       <c r="G170" t="n">
-        <v>215.93</v>
+        <v>4994.5</v>
       </c>
       <c r="H170" t="n">
-        <v>286503</v>
+        <v>2913470</v>
       </c>
       <c r="I170" t="n">
-        <v>247587</v>
+        <v>2580123</v>
       </c>
       <c r="J170" t="n">
-        <v>237.5</v>
+        <v>6915</v>
       </c>
       <c r="K170" t="n">
-        <v>193.5</v>
+        <v>3880</v>
       </c>
       <c r="L170" t="inlineStr">
         <is>
@@ -23685,52 +23685,52 @@
         </is>
       </c>
       <c r="M170" t="n">
-        <v>91720</v>
+        <v>96279</v>
       </c>
       <c r="N170" t="n">
-        <v>70269</v>
+        <v>44978</v>
       </c>
       <c r="O170" t="n">
-        <v>188710</v>
+        <v>-348238</v>
       </c>
       <c r="P170" t="n">
-        <v>-464233</v>
+        <v>452276</v>
       </c>
       <c r="Q170" t="n">
-        <v>88736</v>
+        <v>-141153</v>
       </c>
       <c r="R170" t="n">
-        <v>71121</v>
+        <v>-241711</v>
       </c>
       <c r="S170" t="n">
-        <v>145639</v>
+        <v>-860098</v>
       </c>
       <c r="T170" t="n">
-        <v>-407372</v>
+        <v>-801952</v>
       </c>
       <c r="U170" t="n">
-        <v>3000</v>
+        <v>217966</v>
       </c>
       <c r="V170" t="n">
-        <v>4000</v>
+        <v>153917</v>
       </c>
       <c r="W170" t="n">
-        <v>4000</v>
+        <v>417966</v>
       </c>
       <c r="X170" t="n">
-        <v>4000</v>
+        <v>834234</v>
       </c>
       <c r="Y170" t="n">
-        <v>-16</v>
+        <v>19466</v>
       </c>
       <c r="Z170" t="n">
-        <v>-4852</v>
+        <v>132772</v>
       </c>
       <c r="AA170" t="n">
-        <v>39071</v>
+        <v>93894</v>
       </c>
       <c r="AB170" t="n">
-        <v>-60861</v>
+        <v>419994</v>
       </c>
       <c r="AC170" t="n">
         <v>24</v>
@@ -23739,10 +23739,10 @@
         <v>24</v>
       </c>
       <c r="AE170" t="n">
-        <v>-10</v>
+        <v>80</v>
       </c>
       <c r="AF170" t="n">
-        <v>70</v>
+        <v>-20</v>
       </c>
       <c r="AG170" t="n">
         <v>0</v>
@@ -23762,17 +23762,17 @@
       </c>
       <c r="AM170" t="inlineStr">
         <is>
-          <t>跌破5日線、量能溫和放大</t>
+          <t>站上5日線、多頭排列、量能溫和放大、突破20日高點</t>
         </is>
       </c>
       <c r="AN170" t="inlineStr">
         <is>
-          <t>法人連續偏買、5日法人買超、外資投信同步買超</t>
+          <t>5日法人賣超、投信買外資賣</t>
         </is>
       </c>
       <c r="AO170" t="inlineStr">
         <is>
-          <t>整理觀察：跌破5日線、量能溫和放大、法人連續偏買、5日法人買超、外資投信同步買超。多空訊號混合，建議降低追價衝動。</t>
+          <t>整理觀察：站上5日線、多頭排列、量能溫和放大、突破20日高點、5日法人賣超、投信買外資賣。多空訊號混合，建議降低追價衝動。</t>
         </is>
       </c>
     </row>
@@ -23916,12 +23916,12 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>5425.TWO</t>
+          <t>3491.TWO</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>台半</t>
+          <t>昇達科</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -23930,28 +23930,28 @@
         </is>
       </c>
       <c r="D172" t="n">
-        <v>95.2</v>
+        <v>1425</v>
       </c>
       <c r="E172" t="n">
-        <v>90.8</v>
+        <v>1322</v>
       </c>
       <c r="F172" t="n">
-        <v>90.3</v>
+        <v>1307.5</v>
       </c>
       <c r="G172" t="n">
-        <v>86.73999999999999</v>
+        <v>1266.2</v>
       </c>
       <c r="H172" t="n">
-        <v>41848000</v>
+        <v>2749000</v>
       </c>
       <c r="I172" t="n">
-        <v>21098200</v>
+        <v>1660600</v>
       </c>
       <c r="J172" t="n">
-        <v>98.5</v>
+        <v>1470</v>
       </c>
       <c r="K172" t="n">
-        <v>70.5</v>
+        <v>909</v>
       </c>
       <c r="L172" t="inlineStr">
         <is>
@@ -24053,12 +24053,12 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>3491.TWO</t>
+          <t>3680.TWO</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>昇達科</t>
+          <t>家登</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -24067,28 +24067,28 @@
         </is>
       </c>
       <c r="D173" t="n">
-        <v>1425</v>
+        <v>490.5</v>
       </c>
       <c r="E173" t="n">
-        <v>1322</v>
+        <v>475</v>
       </c>
       <c r="F173" t="n">
-        <v>1307.5</v>
+        <v>471.2</v>
       </c>
       <c r="G173" t="n">
-        <v>1266.2</v>
+        <v>455.75</v>
       </c>
       <c r="H173" t="n">
-        <v>2749000</v>
+        <v>938000</v>
       </c>
       <c r="I173" t="n">
-        <v>1660600</v>
+        <v>968000</v>
       </c>
       <c r="J173" t="n">
-        <v>1470</v>
+        <v>496</v>
       </c>
       <c r="K173" t="n">
-        <v>909</v>
+        <v>393.5</v>
       </c>
       <c r="L173" t="inlineStr">
         <is>
@@ -24173,7 +24173,7 @@
       </c>
       <c r="AM173" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、成交量放大</t>
+          <t>站上5日線、多頭排列、量能未放大、接近20日高點</t>
         </is>
       </c>
       <c r="AN173" t="inlineStr">
@@ -24183,19 +24183,19 @@
       </c>
       <c r="AO173" t="inlineStr">
         <is>
-          <t>整理觀察：站上5日線、多頭排列、成交量放大、籌碼中性。多空訊號混合，建議降低追價衝動。</t>
+          <t>整理觀察：站上5日線、多頭排列、量能未放大、接近20日高點、籌碼中性。多空訊號混合，建議降低追價衝動。</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>5530.TWO</t>
+          <t>3515.TW</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>龍巖</t>
+          <t>華擎</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -24204,28 +24204,28 @@
         </is>
       </c>
       <c r="D174" t="n">
-        <v>50.6</v>
+        <v>218</v>
       </c>
       <c r="E174" t="n">
-        <v>50.54</v>
+        <v>219.5</v>
       </c>
       <c r="F174" t="n">
-        <v>50.26</v>
+        <v>219.95</v>
       </c>
       <c r="G174" t="n">
-        <v>49.25</v>
+        <v>215.93</v>
       </c>
       <c r="H174" t="n">
-        <v>203000</v>
+        <v>286503</v>
       </c>
       <c r="I174" t="n">
-        <v>257400</v>
+        <v>247587</v>
       </c>
       <c r="J174" t="n">
-        <v>51.3</v>
+        <v>237.5</v>
       </c>
       <c r="K174" t="n">
-        <v>47</v>
+        <v>193.5</v>
       </c>
       <c r="L174" t="inlineStr">
         <is>
@@ -24233,52 +24233,52 @@
         </is>
       </c>
       <c r="M174" t="n">
-        <v>0</v>
+        <v>91720</v>
       </c>
       <c r="N174" t="n">
-        <v>0</v>
+        <v>70269</v>
       </c>
       <c r="O174" t="n">
-        <v>0</v>
+        <v>188710</v>
       </c>
       <c r="P174" t="n">
-        <v>0</v>
+        <v>-464233</v>
       </c>
       <c r="Q174" t="n">
-        <v>0</v>
+        <v>88736</v>
       </c>
       <c r="R174" t="n">
-        <v>0</v>
+        <v>71121</v>
       </c>
       <c r="S174" t="n">
-        <v>0</v>
+        <v>145639</v>
       </c>
       <c r="T174" t="n">
-        <v>0</v>
+        <v>-407372</v>
       </c>
       <c r="U174" t="n">
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="V174" t="n">
-        <v>0</v>
+        <v>4000</v>
       </c>
       <c r="W174" t="n">
-        <v>0</v>
+        <v>4000</v>
       </c>
       <c r="X174" t="n">
-        <v>0</v>
+        <v>4000</v>
       </c>
       <c r="Y174" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="Z174" t="n">
-        <v>0</v>
+        <v>-4852</v>
       </c>
       <c r="AA174" t="n">
-        <v>0</v>
+        <v>39071</v>
       </c>
       <c r="AB174" t="n">
-        <v>0</v>
+        <v>-60861</v>
       </c>
       <c r="AC174" t="n">
         <v>24</v>
@@ -24287,10 +24287,10 @@
         <v>24</v>
       </c>
       <c r="AE174" t="n">
-        <v>60</v>
+        <v>-10</v>
       </c>
       <c r="AF174" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AG174" t="n">
         <v>0</v>
@@ -24310,29 +24310,29 @@
       </c>
       <c r="AM174" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、量能未放大、接近20日高點</t>
+          <t>跌破5日線、量能溫和放大</t>
         </is>
       </c>
       <c r="AN174" t="inlineStr">
         <is>
-          <t>籌碼中性</t>
+          <t>法人連續偏買、5日法人買超、外資投信同步買超</t>
         </is>
       </c>
       <c r="AO174" t="inlineStr">
         <is>
-          <t>整理觀察：站上5日線、多頭排列、量能未放大、接近20日高點、籌碼中性。多空訊號混合，建議降低追價衝動。</t>
+          <t>整理觀察：跌破5日線、量能溫和放大、法人連續偏買、5日法人買超、外資投信同步買超。多空訊號混合，建議降低追價衝動。</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>2020.TW</t>
+          <t>2390.TW</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>美亞</t>
+          <t>云辰</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -24341,28 +24341,28 @@
         </is>
       </c>
       <c r="D175" t="n">
-        <v>21.85</v>
+        <v>10.45</v>
       </c>
       <c r="E175" t="n">
-        <v>21.86</v>
+        <v>10.39</v>
       </c>
       <c r="F175" t="n">
-        <v>21.7</v>
+        <v>10.29</v>
       </c>
       <c r="G175" t="n">
-        <v>21.46</v>
+        <v>10.37</v>
       </c>
       <c r="H175" t="n">
-        <v>211233</v>
+        <v>636796</v>
       </c>
       <c r="I175" t="n">
-        <v>249873</v>
+        <v>528249</v>
       </c>
       <c r="J175" t="n">
-        <v>22.15</v>
+        <v>10.95</v>
       </c>
       <c r="K175" t="n">
-        <v>20.9</v>
+        <v>10.1</v>
       </c>
       <c r="L175" t="inlineStr">
         <is>
@@ -24370,28 +24370,28 @@
         </is>
       </c>
       <c r="M175" t="n">
-        <v>61000</v>
+        <v>151999</v>
       </c>
       <c r="N175" t="n">
-        <v>149000</v>
+        <v>175135</v>
       </c>
       <c r="O175" t="n">
-        <v>372049</v>
+        <v>-27240</v>
       </c>
       <c r="P175" t="n">
-        <v>773268</v>
+        <v>-92378</v>
       </c>
       <c r="Q175" t="n">
-        <v>60000</v>
+        <v>136999</v>
       </c>
       <c r="R175" t="n">
-        <v>158000</v>
+        <v>154135</v>
       </c>
       <c r="S175" t="n">
-        <v>379049</v>
+        <v>-48040</v>
       </c>
       <c r="T175" t="n">
-        <v>779268</v>
+        <v>-50159</v>
       </c>
       <c r="U175" t="n">
         <v>0</v>
@@ -24406,16 +24406,16 @@
         <v>0</v>
       </c>
       <c r="Y175" t="n">
-        <v>1000</v>
+        <v>15000</v>
       </c>
       <c r="Z175" t="n">
-        <v>-9000</v>
+        <v>21000</v>
       </c>
       <c r="AA175" t="n">
-        <v>-7000</v>
+        <v>20800</v>
       </c>
       <c r="AB175" t="n">
-        <v>-6000</v>
+        <v>-42219</v>
       </c>
       <c r="AC175" t="n">
         <v>24</v>
@@ -24424,10 +24424,10 @@
         <v>24</v>
       </c>
       <c r="AE175" t="n">
-        <v>10</v>
+        <v>45</v>
       </c>
       <c r="AF175" t="n">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="AG175" t="n">
         <v>0</v>
@@ -24447,29 +24447,29 @@
       </c>
       <c r="AM175" t="inlineStr">
         <is>
-          <t>跌破5日線、多頭排列、量能未放大、接近20日高點、接近20日低點</t>
+          <t>站上5日線、黃金交叉、量能溫和放大、接近20日低點</t>
         </is>
       </c>
       <c r="AN175" t="inlineStr">
         <is>
-          <t>法人連續偏買、5日法人買超</t>
+          <t>短線籌碼止穩</t>
         </is>
       </c>
       <c r="AO175" t="inlineStr">
         <is>
-          <t>整理觀察：跌破5日線、多頭排列、量能未放大、接近20日高點、接近20日低點、法人連續偏買、5日法人買超。多空訊號混合，建議降低追價衝動。</t>
+          <t>整理觀察：站上5日線、黃金交叉、量能溫和放大、接近20日低點、短線籌碼止穩。多空訊號混合，建議降低追價衝動。</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>2543.TW</t>
+          <t>5530.TWO</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>皇昌</t>
+          <t>龍巖</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -24478,28 +24478,28 @@
         </is>
       </c>
       <c r="D176" t="n">
-        <v>38.6</v>
+        <v>50.6</v>
       </c>
       <c r="E176" t="n">
-        <v>38.66</v>
+        <v>50.54</v>
       </c>
       <c r="F176" t="n">
-        <v>38.62</v>
+        <v>50.26</v>
       </c>
       <c r="G176" t="n">
-        <v>38.53</v>
+        <v>49.25</v>
       </c>
       <c r="H176" t="n">
-        <v>543420</v>
+        <v>203000</v>
       </c>
       <c r="I176" t="n">
-        <v>482472</v>
+        <v>257400</v>
       </c>
       <c r="J176" t="n">
-        <v>41.75</v>
+        <v>51.3</v>
       </c>
       <c r="K176" t="n">
-        <v>35.95</v>
+        <v>47</v>
       </c>
       <c r="L176" t="inlineStr">
         <is>
@@ -24507,28 +24507,28 @@
         </is>
       </c>
       <c r="M176" t="n">
-        <v>130284</v>
+        <v>0</v>
       </c>
       <c r="N176" t="n">
-        <v>123397</v>
+        <v>0</v>
       </c>
       <c r="O176" t="n">
-        <v>96805</v>
+        <v>0</v>
       </c>
       <c r="P176" t="n">
-        <v>1154751</v>
+        <v>0</v>
       </c>
       <c r="Q176" t="n">
-        <v>128295</v>
+        <v>0</v>
       </c>
       <c r="R176" t="n">
-        <v>131263</v>
+        <v>0</v>
       </c>
       <c r="S176" t="n">
-        <v>93667</v>
+        <v>0</v>
       </c>
       <c r="T176" t="n">
-        <v>1138921</v>
+        <v>0</v>
       </c>
       <c r="U176" t="n">
         <v>0</v>
@@ -24540,31 +24540,31 @@
         <v>0</v>
       </c>
       <c r="X176" t="n">
-        <v>-3000</v>
+        <v>0</v>
       </c>
       <c r="Y176" t="n">
-        <v>1989</v>
+        <v>0</v>
       </c>
       <c r="Z176" t="n">
-        <v>-7866</v>
+        <v>0</v>
       </c>
       <c r="AA176" t="n">
-        <v>3138</v>
+        <v>0</v>
       </c>
       <c r="AB176" t="n">
-        <v>18830</v>
+        <v>0</v>
       </c>
       <c r="AC176" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AD176" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AE176" t="n">
-        <v>15</v>
+        <v>60</v>
       </c>
       <c r="AF176" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="AG176" t="n">
         <v>0</v>
@@ -24584,17 +24584,17 @@
       </c>
       <c r="AM176" t="inlineStr">
         <is>
-          <t>跌破5日線、多頭排列、量能溫和放大</t>
+          <t>站上5日線、多頭排列、量能未放大、接近20日高點</t>
         </is>
       </c>
       <c r="AN176" t="inlineStr">
         <is>
-          <t>法人連續偏買、5日法人小幅買超</t>
+          <t>籌碼中性</t>
         </is>
       </c>
       <c r="AO176" t="inlineStr">
         <is>
-          <t>整理觀察：跌破5日線、多頭排列、量能溫和放大、法人連續偏買、5日法人小幅買超。多空訊號混合，建議降低追價衝動。</t>
+          <t>整理觀察：站上5日線、多頭排列、量能未放大、接近20日高點、籌碼中性。多空訊號混合，建議降低追價衝動。</t>
         </is>
       </c>
     </row>
@@ -24738,12 +24738,12 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>3030.TW</t>
+          <t>2543.TW</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>德律</t>
+          <t>皇昌</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -24752,28 +24752,28 @@
         </is>
       </c>
       <c r="D178" t="n">
-        <v>296.5</v>
+        <v>38.6</v>
       </c>
       <c r="E178" t="n">
-        <v>286.8</v>
+        <v>38.66</v>
       </c>
       <c r="F178" t="n">
-        <v>289.25</v>
+        <v>38.62</v>
       </c>
       <c r="G178" t="n">
-        <v>291.85</v>
+        <v>38.53</v>
       </c>
       <c r="H178" t="n">
-        <v>839304</v>
+        <v>543420</v>
       </c>
       <c r="I178" t="n">
-        <v>619149</v>
+        <v>482472</v>
       </c>
       <c r="J178" t="n">
-        <v>313.5</v>
+        <v>41.75</v>
       </c>
       <c r="K178" t="n">
-        <v>265</v>
+        <v>35.95</v>
       </c>
       <c r="L178" t="inlineStr">
         <is>
@@ -24781,52 +24781,52 @@
         </is>
       </c>
       <c r="M178" t="n">
-        <v>142786</v>
+        <v>130284</v>
       </c>
       <c r="N178" t="n">
-        <v>326179</v>
+        <v>123397</v>
       </c>
       <c r="O178" t="n">
-        <v>168637</v>
+        <v>96805</v>
       </c>
       <c r="P178" t="n">
-        <v>138116</v>
+        <v>1154751</v>
       </c>
       <c r="Q178" t="n">
-        <v>98079</v>
+        <v>128295</v>
       </c>
       <c r="R178" t="n">
-        <v>261110</v>
+        <v>131263</v>
       </c>
       <c r="S178" t="n">
-        <v>159621</v>
+        <v>93667</v>
       </c>
       <c r="T178" t="n">
-        <v>259154</v>
+        <v>1138921</v>
       </c>
       <c r="U178" t="n">
-        <v>-1000</v>
+        <v>0</v>
       </c>
       <c r="V178" t="n">
-        <v>-2400</v>
+        <v>0</v>
       </c>
       <c r="W178" t="n">
-        <v>-1400</v>
+        <v>0</v>
       </c>
       <c r="X178" t="n">
-        <v>-6400</v>
+        <v>-3000</v>
       </c>
       <c r="Y178" t="n">
-        <v>45707</v>
+        <v>1989</v>
       </c>
       <c r="Z178" t="n">
-        <v>67469</v>
+        <v>-7866</v>
       </c>
       <c r="AA178" t="n">
-        <v>10416</v>
+        <v>3138</v>
       </c>
       <c r="AB178" t="n">
-        <v>-114638</v>
+        <v>18830</v>
       </c>
       <c r="AC178" t="n">
         <v>22</v>
@@ -24835,10 +24835,10 @@
         <v>22</v>
       </c>
       <c r="AE178" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="AF178" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="AG178" t="n">
         <v>0</v>
@@ -24858,17 +24858,17 @@
       </c>
       <c r="AM178" t="inlineStr">
         <is>
-          <t>站上5日線、空頭排列、量能溫和放大</t>
+          <t>跌破5日線、多頭排列、量能溫和放大</t>
         </is>
       </c>
       <c r="AN178" t="inlineStr">
         <is>
-          <t>法人連續偏買、5日法人買超、外資買投信賣</t>
+          <t>法人連續偏買、5日法人小幅買超</t>
         </is>
       </c>
       <c r="AO178" t="inlineStr">
         <is>
-          <t>整理觀察：站上5日線、空頭排列、量能溫和放大、法人連續偏買、5日法人買超、外資買投信賣。多空訊號混合，建議降低追價衝動。</t>
+          <t>整理觀察：跌破5日線、多頭排列、量能溫和放大、法人連續偏買、5日法人小幅買超。多空訊號混合，建議降低追價衝動。</t>
         </is>
       </c>
     </row>
@@ -25423,12 +25423,12 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>2451.TW</t>
+          <t>5871.TW</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>創見</t>
+          <t>中租-KY</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -25437,28 +25437,28 @@
         </is>
       </c>
       <c r="D183" t="n">
-        <v>298</v>
+        <v>114.5</v>
       </c>
       <c r="E183" t="n">
-        <v>305.3</v>
+        <v>115.5</v>
       </c>
       <c r="F183" t="n">
-        <v>295.45</v>
+        <v>112.8</v>
       </c>
       <c r="G183" t="n">
-        <v>293.18</v>
+        <v>112.3</v>
       </c>
       <c r="H183" t="n">
-        <v>3120478</v>
+        <v>4458129</v>
       </c>
       <c r="I183" t="n">
-        <v>9887720</v>
+        <v>6246091</v>
       </c>
       <c r="J183" t="n">
-        <v>329.5</v>
+        <v>117.5</v>
       </c>
       <c r="K183" t="n">
-        <v>271</v>
+        <v>108</v>
       </c>
       <c r="L183" t="inlineStr">
         <is>
@@ -25466,52 +25466,52 @@
         </is>
       </c>
       <c r="M183" t="n">
-        <v>-399641</v>
+        <v>-931135</v>
       </c>
       <c r="N183" t="n">
-        <v>-3805164</v>
+        <v>4412259</v>
       </c>
       <c r="O183" t="n">
-        <v>5167665</v>
+        <v>13447981</v>
       </c>
       <c r="P183" t="n">
-        <v>1793495</v>
+        <v>6270194</v>
       </c>
       <c r="Q183" t="n">
-        <v>-363002</v>
+        <v>-911565</v>
       </c>
       <c r="R183" t="n">
-        <v>-3643267</v>
+        <v>4455731</v>
       </c>
       <c r="S183" t="n">
-        <v>5099448</v>
+        <v>14101978</v>
       </c>
       <c r="T183" t="n">
-        <v>2460078</v>
+        <v>8256939</v>
       </c>
       <c r="U183" t="n">
-        <v>-36700</v>
+        <v>-17000</v>
       </c>
       <c r="V183" t="n">
-        <v>-29400</v>
+        <v>-1483</v>
       </c>
       <c r="W183" t="n">
-        <v>36600</v>
+        <v>11517</v>
       </c>
       <c r="X183" t="n">
-        <v>-505400</v>
+        <v>-1178022</v>
       </c>
       <c r="Y183" t="n">
-        <v>61</v>
+        <v>-2570</v>
       </c>
       <c r="Z183" t="n">
-        <v>-132497</v>
+        <v>-41989</v>
       </c>
       <c r="AA183" t="n">
-        <v>31617</v>
+        <v>-665514</v>
       </c>
       <c r="AB183" t="n">
-        <v>-161183</v>
+        <v>-808723</v>
       </c>
       <c r="AC183" t="n">
         <v>22</v>
@@ -25560,12 +25560,12 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>5871.TW</t>
+          <t>2451.TW</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>中租-KY</t>
+          <t>創見</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -25574,28 +25574,28 @@
         </is>
       </c>
       <c r="D184" t="n">
-        <v>114.5</v>
+        <v>298</v>
       </c>
       <c r="E184" t="n">
-        <v>115.5</v>
+        <v>305.3</v>
       </c>
       <c r="F184" t="n">
-        <v>112.8</v>
+        <v>295.45</v>
       </c>
       <c r="G184" t="n">
-        <v>112.3</v>
+        <v>293.18</v>
       </c>
       <c r="H184" t="n">
-        <v>4458129</v>
+        <v>3120478</v>
       </c>
       <c r="I184" t="n">
-        <v>6246091</v>
+        <v>9887720</v>
       </c>
       <c r="J184" t="n">
-        <v>117.5</v>
+        <v>329.5</v>
       </c>
       <c r="K184" t="n">
-        <v>108</v>
+        <v>271</v>
       </c>
       <c r="L184" t="inlineStr">
         <is>
@@ -25603,52 +25603,52 @@
         </is>
       </c>
       <c r="M184" t="n">
-        <v>-931135</v>
+        <v>-399641</v>
       </c>
       <c r="N184" t="n">
-        <v>4412259</v>
+        <v>-3805164</v>
       </c>
       <c r="O184" t="n">
-        <v>13447981</v>
+        <v>5167665</v>
       </c>
       <c r="P184" t="n">
-        <v>6270194</v>
+        <v>1793495</v>
       </c>
       <c r="Q184" t="n">
-        <v>-911565</v>
+        <v>-363002</v>
       </c>
       <c r="R184" t="n">
-        <v>4455731</v>
+        <v>-3643267</v>
       </c>
       <c r="S184" t="n">
-        <v>14101978</v>
+        <v>5099448</v>
       </c>
       <c r="T184" t="n">
-        <v>8256939</v>
+        <v>2460078</v>
       </c>
       <c r="U184" t="n">
-        <v>-17000</v>
+        <v>-36700</v>
       </c>
       <c r="V184" t="n">
-        <v>-1483</v>
+        <v>-29400</v>
       </c>
       <c r="W184" t="n">
-        <v>11517</v>
+        <v>36600</v>
       </c>
       <c r="X184" t="n">
-        <v>-1178022</v>
+        <v>-505400</v>
       </c>
       <c r="Y184" t="n">
-        <v>-2570</v>
+        <v>61</v>
       </c>
       <c r="Z184" t="n">
-        <v>-41989</v>
+        <v>-132497</v>
       </c>
       <c r="AA184" t="n">
-        <v>-665514</v>
+        <v>31617</v>
       </c>
       <c r="AB184" t="n">
-        <v>-808723</v>
+        <v>-161183</v>
       </c>
       <c r="AC184" t="n">
         <v>22</v>
@@ -25834,12 +25834,12 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>3081.TWO</t>
+          <t>3030.TW</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>聯亞</t>
+          <t>德律</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -25848,28 +25848,28 @@
         </is>
       </c>
       <c r="D186" t="n">
-        <v>3370</v>
+        <v>296.5</v>
       </c>
       <c r="E186" t="n">
-        <v>3054</v>
+        <v>286.8</v>
       </c>
       <c r="F186" t="n">
-        <v>2898.5</v>
+        <v>289.25</v>
       </c>
       <c r="G186" t="n">
-        <v>2580.75</v>
+        <v>291.85</v>
       </c>
       <c r="H186" t="n">
-        <v>6604000</v>
+        <v>839304</v>
       </c>
       <c r="I186" t="n">
-        <v>5440600</v>
+        <v>619149</v>
       </c>
       <c r="J186" t="n">
-        <v>3510</v>
+        <v>313.5</v>
       </c>
       <c r="K186" t="n">
-        <v>1630</v>
+        <v>265</v>
       </c>
       <c r="L186" t="inlineStr">
         <is>
@@ -25877,52 +25877,52 @@
         </is>
       </c>
       <c r="M186" t="n">
-        <v>0</v>
+        <v>142786</v>
       </c>
       <c r="N186" t="n">
-        <v>0</v>
+        <v>326179</v>
       </c>
       <c r="O186" t="n">
-        <v>0</v>
+        <v>168637</v>
       </c>
       <c r="P186" t="n">
-        <v>0</v>
+        <v>138116</v>
       </c>
       <c r="Q186" t="n">
-        <v>0</v>
+        <v>98079</v>
       </c>
       <c r="R186" t="n">
-        <v>0</v>
+        <v>261110</v>
       </c>
       <c r="S186" t="n">
-        <v>0</v>
+        <v>159621</v>
       </c>
       <c r="T186" t="n">
-        <v>0</v>
+        <v>259154</v>
       </c>
       <c r="U186" t="n">
-        <v>0</v>
+        <v>-1000</v>
       </c>
       <c r="V186" t="n">
-        <v>0</v>
+        <v>-2400</v>
       </c>
       <c r="W186" t="n">
-        <v>0</v>
+        <v>-1400</v>
       </c>
       <c r="X186" t="n">
-        <v>0</v>
+        <v>-6400</v>
       </c>
       <c r="Y186" t="n">
-        <v>0</v>
+        <v>45707</v>
       </c>
       <c r="Z186" t="n">
-        <v>0</v>
+        <v>67469</v>
       </c>
       <c r="AA186" t="n">
-        <v>0</v>
+        <v>10416</v>
       </c>
       <c r="AB186" t="n">
-        <v>0</v>
+        <v>-114638</v>
       </c>
       <c r="AC186" t="n">
         <v>22</v>
@@ -25931,10 +25931,10 @@
         <v>22</v>
       </c>
       <c r="AE186" t="n">
-        <v>55</v>
+        <v>5</v>
       </c>
       <c r="AF186" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AG186" t="n">
         <v>0</v>
@@ -25954,17 +25954,17 @@
       </c>
       <c r="AM186" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、量能溫和放大</t>
+          <t>站上5日線、空頭排列、量能溫和放大</t>
         </is>
       </c>
       <c r="AN186" t="inlineStr">
         <is>
-          <t>籌碼中性</t>
+          <t>法人連續偏買、5日法人買超、外資買投信賣</t>
         </is>
       </c>
       <c r="AO186" t="inlineStr">
         <is>
-          <t>整理觀察：站上5日線、多頭排列、量能溫和放大、籌碼中性。多空訊號混合，建議降低追價衝動。</t>
+          <t>整理觀察：站上5日線、空頭排列、量能溫和放大、法人連續偏買、5日法人買超、外資買投信賣。多空訊號混合，建議降低追價衝動。</t>
         </is>
       </c>
     </row>
@@ -26382,12 +26382,12 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>2609.TW</t>
+          <t>3081.TWO</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>陽明</t>
+          <t>聯亞</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -26396,28 +26396,28 @@
         </is>
       </c>
       <c r="D190" t="n">
-        <v>57.9</v>
+        <v>3370</v>
       </c>
       <c r="E190" t="n">
-        <v>61.52</v>
+        <v>3054</v>
       </c>
       <c r="F190" t="n">
-        <v>58.94</v>
+        <v>2898.5</v>
       </c>
       <c r="G190" t="n">
-        <v>55.01</v>
+        <v>2580.75</v>
       </c>
       <c r="H190" t="n">
-        <v>60493753</v>
+        <v>6604000</v>
       </c>
       <c r="I190" t="n">
-        <v>156060445</v>
+        <v>5440600</v>
       </c>
       <c r="J190" t="n">
-        <v>67.3</v>
+        <v>3510</v>
       </c>
       <c r="K190" t="n">
-        <v>49.8</v>
+        <v>1630</v>
       </c>
       <c r="L190" t="inlineStr">
         <is>
@@ -26425,52 +26425,52 @@
         </is>
       </c>
       <c r="M190" t="n">
-        <v>7686944</v>
+        <v>0</v>
       </c>
       <c r="N190" t="n">
-        <v>-19843091</v>
+        <v>0</v>
       </c>
       <c r="O190" t="n">
-        <v>50217998</v>
+        <v>0</v>
       </c>
       <c r="P190" t="n">
-        <v>181840755</v>
+        <v>0</v>
       </c>
       <c r="Q190" t="n">
-        <v>7193616</v>
+        <v>0</v>
       </c>
       <c r="R190" t="n">
-        <v>-17936033</v>
+        <v>0</v>
       </c>
       <c r="S190" t="n">
-        <v>49874121</v>
+        <v>0</v>
       </c>
       <c r="T190" t="n">
-        <v>175620267</v>
+        <v>0</v>
       </c>
       <c r="U190" t="n">
-        <v>-16223</v>
+        <v>0</v>
       </c>
       <c r="V190" t="n">
-        <v>51152</v>
+        <v>0</v>
       </c>
       <c r="W190" t="n">
-        <v>85152</v>
+        <v>0</v>
       </c>
       <c r="X190" t="n">
-        <v>506695</v>
+        <v>0</v>
       </c>
       <c r="Y190" t="n">
-        <v>509551</v>
+        <v>0</v>
       </c>
       <c r="Z190" t="n">
-        <v>-1958210</v>
+        <v>0</v>
       </c>
       <c r="AA190" t="n">
-        <v>258725</v>
+        <v>0</v>
       </c>
       <c r="AB190" t="n">
-        <v>5713793</v>
+        <v>0</v>
       </c>
       <c r="AC190" t="n">
         <v>22</v>
@@ -26479,10 +26479,10 @@
         <v>22</v>
       </c>
       <c r="AE190" t="n">
-        <v>5</v>
+        <v>55</v>
       </c>
       <c r="AF190" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="AG190" t="n">
         <v>0</v>
@@ -26502,17 +26502,17 @@
       </c>
       <c r="AM190" t="inlineStr">
         <is>
-          <t>跌破5日線、多頭排列、量能未放大</t>
+          <t>站上5日線、多頭排列、量能溫和放大</t>
         </is>
       </c>
       <c r="AN190" t="inlineStr">
         <is>
-          <t>5日法人明顯買超、外資投信同步買超</t>
+          <t>籌碼中性</t>
         </is>
       </c>
       <c r="AO190" t="inlineStr">
         <is>
-          <t>整理觀察：跌破5日線、多頭排列、量能未放大、5日法人明顯買超、外資投信同步買超。多空訊號混合，建議降低追價衝動。</t>
+          <t>整理觀察：站上5日線、多頭排列、量能溫和放大、籌碼中性。多空訊號混合，建議降低追價衝動。</t>
         </is>
       </c>
     </row>
@@ -26656,12 +26656,12 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>2607.TW</t>
+          <t>2609.TW</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>榮運</t>
+          <t>陽明</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -26670,28 +26670,28 @@
         </is>
       </c>
       <c r="D192" t="n">
-        <v>52.3</v>
+        <v>57.9</v>
       </c>
       <c r="E192" t="n">
-        <v>52.3</v>
+        <v>61.52</v>
       </c>
       <c r="F192" t="n">
-        <v>51.39</v>
+        <v>58.94</v>
       </c>
       <c r="G192" t="n">
-        <v>49.74</v>
+        <v>55.01</v>
       </c>
       <c r="H192" t="n">
-        <v>436418</v>
+        <v>60493753</v>
       </c>
       <c r="I192" t="n">
-        <v>698583</v>
+        <v>156060445</v>
       </c>
       <c r="J192" t="n">
-        <v>53.6</v>
+        <v>67.3</v>
       </c>
       <c r="K192" t="n">
-        <v>46.45</v>
+        <v>49.8</v>
       </c>
       <c r="L192" t="inlineStr">
         <is>
@@ -26699,52 +26699,52 @@
         </is>
       </c>
       <c r="M192" t="n">
-        <v>85991</v>
+        <v>7686944</v>
       </c>
       <c r="N192" t="n">
-        <v>141797</v>
+        <v>-19843091</v>
       </c>
       <c r="O192" t="n">
-        <v>459164</v>
+        <v>50217998</v>
       </c>
       <c r="P192" t="n">
-        <v>717335</v>
+        <v>181840755</v>
       </c>
       <c r="Q192" t="n">
-        <v>96554</v>
+        <v>7193616</v>
       </c>
       <c r="R192" t="n">
-        <v>166680</v>
+        <v>-17936033</v>
       </c>
       <c r="S192" t="n">
-        <v>469783</v>
+        <v>49874121</v>
       </c>
       <c r="T192" t="n">
-        <v>721129</v>
+        <v>175620267</v>
       </c>
       <c r="U192" t="n">
-        <v>0</v>
+        <v>-16223</v>
       </c>
       <c r="V192" t="n">
-        <v>0</v>
+        <v>51152</v>
       </c>
       <c r="W192" t="n">
-        <v>0</v>
+        <v>85152</v>
       </c>
       <c r="X192" t="n">
-        <v>0</v>
+        <v>506695</v>
       </c>
       <c r="Y192" t="n">
-        <v>-10563</v>
+        <v>509551</v>
       </c>
       <c r="Z192" t="n">
-        <v>-24883</v>
+        <v>-1958210</v>
       </c>
       <c r="AA192" t="n">
-        <v>-10619</v>
+        <v>258725</v>
       </c>
       <c r="AB192" t="n">
-        <v>-3794</v>
+        <v>5713793</v>
       </c>
       <c r="AC192" t="n">
         <v>22</v>
@@ -26781,24 +26781,24 @@
       </c>
       <c r="AN192" t="inlineStr">
         <is>
-          <t>法人連續偏買、5日法人買超</t>
+          <t>5日法人明顯買超、外資投信同步買超</t>
         </is>
       </c>
       <c r="AO192" t="inlineStr">
         <is>
-          <t>整理觀察：跌破5日線、多頭排列、量能未放大、法人連續偏買、5日法人買超。多空訊號混合，建議降低追價衝動。</t>
+          <t>整理觀察：跌破5日線、多頭排列、量能未放大、5日法人明顯買超、外資投信同步買超。多空訊號混合，建議降低追價衝動。</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>6230.TW</t>
+          <t>2607.TW</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>超眾</t>
+          <t>榮運</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -26807,28 +26807,28 @@
         </is>
       </c>
       <c r="D193" t="n">
-        <v>110</v>
+        <v>52.3</v>
       </c>
       <c r="E193" t="n">
-        <v>108</v>
+        <v>52.3</v>
       </c>
       <c r="F193" t="n">
-        <v>108.2</v>
+        <v>51.39</v>
       </c>
       <c r="G193" t="n">
-        <v>108.85</v>
+        <v>49.74</v>
       </c>
       <c r="H193" t="n">
-        <v>53744</v>
+        <v>436418</v>
       </c>
       <c r="I193" t="n">
-        <v>27708</v>
+        <v>698583</v>
       </c>
       <c r="J193" t="n">
-        <v>119</v>
+        <v>53.6</v>
       </c>
       <c r="K193" t="n">
-        <v>104.5</v>
+        <v>46.45</v>
       </c>
       <c r="L193" t="inlineStr">
         <is>
@@ -26836,28 +26836,28 @@
         </is>
       </c>
       <c r="M193" t="n">
-        <v>28000</v>
+        <v>85991</v>
       </c>
       <c r="N193" t="n">
-        <v>50060</v>
+        <v>141797</v>
       </c>
       <c r="O193" t="n">
-        <v>62024</v>
+        <v>459164</v>
       </c>
       <c r="P193" t="n">
-        <v>15122</v>
+        <v>717335</v>
       </c>
       <c r="Q193" t="n">
-        <v>28000</v>
+        <v>96554</v>
       </c>
       <c r="R193" t="n">
-        <v>49060</v>
+        <v>166680</v>
       </c>
       <c r="S193" t="n">
-        <v>59060</v>
+        <v>469783</v>
       </c>
       <c r="T193" t="n">
-        <v>12145</v>
+        <v>721129</v>
       </c>
       <c r="U193" t="n">
         <v>0</v>
@@ -26872,28 +26872,28 @@
         <v>0</v>
       </c>
       <c r="Y193" t="n">
-        <v>0</v>
+        <v>-10563</v>
       </c>
       <c r="Z193" t="n">
-        <v>1000</v>
+        <v>-24883</v>
       </c>
       <c r="AA193" t="n">
-        <v>2964</v>
+        <v>-10619</v>
       </c>
       <c r="AB193" t="n">
-        <v>2977</v>
+        <v>-3794</v>
       </c>
       <c r="AC193" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AD193" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AE193" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="AF193" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="AG193" t="n">
         <v>0</v>
@@ -26913,29 +26913,29 @@
       </c>
       <c r="AM193" t="inlineStr">
         <is>
-          <t>站上5日線、空頭排列、成交量放大</t>
+          <t>跌破5日線、多頭排列、量能未放大</t>
         </is>
       </c>
       <c r="AN193" t="inlineStr">
         <is>
-          <t>法人連續偏買、5日法人小幅買超</t>
+          <t>法人連續偏買、5日法人買超</t>
         </is>
       </c>
       <c r="AO193" t="inlineStr">
         <is>
-          <t>整理觀察：站上5日線、空頭排列、成交量放大、法人連續偏買、5日法人小幅買超。多空訊號混合，建議降低追價衝動。</t>
+          <t>整理觀察：跌破5日線、多頭排列、量能未放大、法人連續偏買、5日法人買超。多空訊號混合，建議降低追價衝動。</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>5484.TW</t>
+          <t>6230.TW</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>慧友</t>
+          <t>超眾</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -26944,28 +26944,28 @@
         </is>
       </c>
       <c r="D194" t="n">
-        <v>40.55</v>
+        <v>110</v>
       </c>
       <c r="E194" t="n">
-        <v>40.42</v>
+        <v>108</v>
       </c>
       <c r="F194" t="n">
-        <v>40.29</v>
+        <v>108.2</v>
       </c>
       <c r="G194" t="n">
-        <v>40.89</v>
+        <v>108.85</v>
       </c>
       <c r="H194" t="n">
-        <v>173908</v>
+        <v>53744</v>
       </c>
       <c r="I194" t="n">
-        <v>177889</v>
+        <v>27708</v>
       </c>
       <c r="J194" t="n">
-        <v>46.9</v>
+        <v>119</v>
       </c>
       <c r="K194" t="n">
-        <v>37.3</v>
+        <v>104.5</v>
       </c>
       <c r="L194" t="inlineStr">
         <is>
@@ -26973,52 +26973,52 @@
         </is>
       </c>
       <c r="M194" t="n">
-        <v>43000</v>
+        <v>28000</v>
       </c>
       <c r="N194" t="n">
-        <v>23000</v>
+        <v>50060</v>
       </c>
       <c r="O194" t="n">
+        <v>62024</v>
+      </c>
+      <c r="P194" t="n">
+        <v>15122</v>
+      </c>
+      <c r="Q194" t="n">
+        <v>28000</v>
+      </c>
+      <c r="R194" t="n">
+        <v>49060</v>
+      </c>
+      <c r="S194" t="n">
+        <v>59060</v>
+      </c>
+      <c r="T194" t="n">
+        <v>12145</v>
+      </c>
+      <c r="U194" t="n">
+        <v>0</v>
+      </c>
+      <c r="V194" t="n">
+        <v>0</v>
+      </c>
+      <c r="W194" t="n">
+        <v>0</v>
+      </c>
+      <c r="X194" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y194" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z194" t="n">
         <v>1000</v>
       </c>
-      <c r="P194" t="n">
-        <v>-56000</v>
-      </c>
-      <c r="Q194" t="n">
-        <v>45000</v>
-      </c>
-      <c r="R194" t="n">
-        <v>25000</v>
-      </c>
-      <c r="S194" t="n">
-        <v>3000</v>
-      </c>
-      <c r="T194" t="n">
-        <v>-58000</v>
-      </c>
-      <c r="U194" t="n">
-        <v>0</v>
-      </c>
-      <c r="V194" t="n">
-        <v>0</v>
-      </c>
-      <c r="W194" t="n">
-        <v>0</v>
-      </c>
-      <c r="X194" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y194" t="n">
-        <v>-2000</v>
-      </c>
-      <c r="Z194" t="n">
-        <v>-2000</v>
-      </c>
       <c r="AA194" t="n">
-        <v>-2000</v>
+        <v>2964</v>
       </c>
       <c r="AB194" t="n">
-        <v>2000</v>
+        <v>2977</v>
       </c>
       <c r="AC194" t="n">
         <v>20</v>
@@ -27027,10 +27027,10 @@
         <v>20</v>
       </c>
       <c r="AE194" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="AF194" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="AG194" t="n">
         <v>0</v>
@@ -27050,17 +27050,17 @@
       </c>
       <c r="AM194" t="inlineStr">
         <is>
-          <t>站上5日線、量能未放大</t>
+          <t>站上5日線、空頭排列、成交量放大</t>
         </is>
       </c>
       <c r="AN194" t="inlineStr">
         <is>
-          <t>法人連續偏買</t>
+          <t>法人連續偏買、5日法人小幅買超</t>
         </is>
       </c>
       <c r="AO194" t="inlineStr">
         <is>
-          <t>整理觀察：站上5日線、量能未放大、法人連續偏買。多空訊號混合，建議降低追價衝動。</t>
+          <t>整理觀察：站上5日線、空頭排列、成交量放大、法人連續偏買、5日法人小幅買超。多空訊號混合，建議降低追價衝動。</t>
         </is>
       </c>
     </row>
@@ -27478,12 +27478,12 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>3034.TW</t>
+          <t>5484.TW</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>聯詠</t>
+          <t>慧友</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -27492,28 +27492,28 @@
         </is>
       </c>
       <c r="D198" t="n">
-        <v>548</v>
+        <v>40.55</v>
       </c>
       <c r="E198" t="n">
-        <v>546.4</v>
+        <v>40.42</v>
       </c>
       <c r="F198" t="n">
-        <v>531.9</v>
+        <v>40.29</v>
       </c>
       <c r="G198" t="n">
-        <v>533.65</v>
+        <v>40.89</v>
       </c>
       <c r="H198" t="n">
-        <v>3361245</v>
+        <v>173908</v>
       </c>
       <c r="I198" t="n">
-        <v>3930742</v>
+        <v>177889</v>
       </c>
       <c r="J198" t="n">
-        <v>572</v>
+        <v>46.9</v>
       </c>
       <c r="K198" t="n">
-        <v>498.5</v>
+        <v>37.3</v>
       </c>
       <c r="L198" t="inlineStr">
         <is>
@@ -27521,52 +27521,52 @@
         </is>
       </c>
       <c r="M198" t="n">
-        <v>-14994</v>
+        <v>43000</v>
       </c>
       <c r="N198" t="n">
-        <v>4527932</v>
+        <v>23000</v>
       </c>
       <c r="O198" t="n">
-        <v>7022505</v>
+        <v>1000</v>
       </c>
       <c r="P198" t="n">
-        <v>7801832</v>
+        <v>-56000</v>
       </c>
       <c r="Q198" t="n">
-        <v>77105</v>
+        <v>45000</v>
       </c>
       <c r="R198" t="n">
-        <v>4566634</v>
+        <v>25000</v>
       </c>
       <c r="S198" t="n">
-        <v>6887013</v>
+        <v>3000</v>
       </c>
       <c r="T198" t="n">
-        <v>7215127</v>
+        <v>-58000</v>
       </c>
       <c r="U198" t="n">
-        <v>-64039</v>
+        <v>0</v>
       </c>
       <c r="V198" t="n">
-        <v>-93532</v>
+        <v>0</v>
       </c>
       <c r="W198" t="n">
-        <v>-132532</v>
+        <v>0</v>
       </c>
       <c r="X198" t="n">
-        <v>428724</v>
+        <v>0</v>
       </c>
       <c r="Y198" t="n">
-        <v>-28060</v>
+        <v>-2000</v>
       </c>
       <c r="Z198" t="n">
-        <v>54830</v>
+        <v>-2000</v>
       </c>
       <c r="AA198" t="n">
-        <v>268024</v>
+        <v>-2000</v>
       </c>
       <c r="AB198" t="n">
-        <v>157981</v>
+        <v>2000</v>
       </c>
       <c r="AC198" t="n">
         <v>20</v>
@@ -27603,24 +27603,24 @@
       </c>
       <c r="AN198" t="inlineStr">
         <is>
-          <t>5日法人明顯買超、外資買投信賣</t>
+          <t>法人連續偏買</t>
         </is>
       </c>
       <c r="AO198" t="inlineStr">
         <is>
-          <t>整理觀察：站上5日線、量能未放大、5日法人明顯買超、外資買投信賣。多空訊號混合，建議降低追價衝動。</t>
+          <t>整理觀察：站上5日線、量能未放大、法人連續偏買。多空訊號混合，建議降低追價衝動。</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>3416.TW</t>
+          <t>3034.TW</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>融程電</t>
+          <t>聯詠</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -27629,28 +27629,28 @@
         </is>
       </c>
       <c r="D199" t="n">
-        <v>182.5</v>
+        <v>548</v>
       </c>
       <c r="E199" t="n">
-        <v>178</v>
+        <v>546.4</v>
       </c>
       <c r="F199" t="n">
-        <v>178.85</v>
+        <v>531.9</v>
       </c>
       <c r="G199" t="n">
-        <v>181.28</v>
+        <v>533.65</v>
       </c>
       <c r="H199" t="n">
-        <v>287806</v>
+        <v>3361245</v>
       </c>
       <c r="I199" t="n">
-        <v>197361</v>
+        <v>3930742</v>
       </c>
       <c r="J199" t="n">
-        <v>200</v>
+        <v>572</v>
       </c>
       <c r="K199" t="n">
-        <v>162</v>
+        <v>498.5</v>
       </c>
       <c r="L199" t="inlineStr">
         <is>
@@ -27658,64 +27658,64 @@
         </is>
       </c>
       <c r="M199" t="n">
-        <v>104711</v>
+        <v>-14994</v>
       </c>
       <c r="N199" t="n">
-        <v>128881</v>
+        <v>4527932</v>
       </c>
       <c r="O199" t="n">
-        <v>93315</v>
+        <v>7022505</v>
       </c>
       <c r="P199" t="n">
-        <v>-243874</v>
+        <v>7801832</v>
       </c>
       <c r="Q199" t="n">
-        <v>105048</v>
+        <v>77105</v>
       </c>
       <c r="R199" t="n">
-        <v>126218</v>
+        <v>4566634</v>
       </c>
       <c r="S199" t="n">
-        <v>130218</v>
+        <v>6887013</v>
       </c>
       <c r="T199" t="n">
-        <v>-194126</v>
+        <v>7215127</v>
       </c>
       <c r="U199" t="n">
-        <v>0</v>
+        <v>-64039</v>
       </c>
       <c r="V199" t="n">
-        <v>0</v>
+        <v>-93532</v>
       </c>
       <c r="W199" t="n">
-        <v>0</v>
+        <v>-132532</v>
       </c>
       <c r="X199" t="n">
-        <v>0</v>
+        <v>428724</v>
       </c>
       <c r="Y199" t="n">
-        <v>-337</v>
+        <v>-28060</v>
       </c>
       <c r="Z199" t="n">
-        <v>2663</v>
+        <v>54830</v>
       </c>
       <c r="AA199" t="n">
-        <v>-36903</v>
+        <v>268024</v>
       </c>
       <c r="AB199" t="n">
-        <v>-49748</v>
+        <v>157981</v>
       </c>
       <c r="AC199" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AD199" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AE199" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="AF199" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="AG199" t="n">
         <v>0</v>
@@ -27725,27 +27725,27 @@
       <c r="AJ199" t="inlineStr"/>
       <c r="AK199" t="inlineStr">
         <is>
-          <t>❌避開</t>
+          <t>⚠️整理</t>
         </is>
       </c>
       <c r="AL199" t="inlineStr">
         <is>
-          <t>觀望</t>
+          <t>整理觀察</t>
         </is>
       </c>
       <c r="AM199" t="inlineStr">
         <is>
-          <t>站上5日線、空頭排列、量能溫和放大</t>
+          <t>站上5日線、量能未放大</t>
         </is>
       </c>
       <c r="AN199" t="inlineStr">
         <is>
-          <t>法人連續偏買、5日法人小幅買超</t>
+          <t>5日法人明顯買超、外資買投信賣</t>
         </is>
       </c>
       <c r="AO199" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、空頭排列、量能溫和放大、法人連續偏買、5日法人小幅買超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>整理觀察：站上5日線、量能未放大、5日法人明顯買超、外資買投信賣。多空訊號混合，建議降低追價衝動。</t>
         </is>
       </c>
     </row>
@@ -28574,12 +28574,12 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>3680.TWO</t>
+          <t>3416.TW</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>家登</t>
+          <t>融程電</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
@@ -28588,28 +28588,28 @@
         </is>
       </c>
       <c r="D206" t="n">
-        <v>490.5</v>
+        <v>182.5</v>
       </c>
       <c r="E206" t="n">
-        <v>475</v>
+        <v>178</v>
       </c>
       <c r="F206" t="n">
-        <v>471.2</v>
+        <v>178.85</v>
       </c>
       <c r="G206" t="n">
-        <v>461.2</v>
+        <v>181.28</v>
       </c>
       <c r="H206" t="n">
-        <v>938000</v>
+        <v>287806</v>
       </c>
       <c r="I206" t="n">
-        <v>968000</v>
+        <v>197361</v>
       </c>
       <c r="J206" t="n">
-        <v>516</v>
+        <v>200</v>
       </c>
       <c r="K206" t="n">
-        <v>398.5</v>
+        <v>162</v>
       </c>
       <c r="L206" t="inlineStr">
         <is>
@@ -28617,28 +28617,28 @@
         </is>
       </c>
       <c r="M206" t="n">
-        <v>0</v>
+        <v>104711</v>
       </c>
       <c r="N206" t="n">
-        <v>0</v>
+        <v>128881</v>
       </c>
       <c r="O206" t="n">
-        <v>0</v>
+        <v>93315</v>
       </c>
       <c r="P206" t="n">
-        <v>0</v>
+        <v>-243874</v>
       </c>
       <c r="Q206" t="n">
-        <v>0</v>
+        <v>105048</v>
       </c>
       <c r="R206" t="n">
-        <v>0</v>
+        <v>126218</v>
       </c>
       <c r="S206" t="n">
-        <v>0</v>
+        <v>130218</v>
       </c>
       <c r="T206" t="n">
-        <v>0</v>
+        <v>-194126</v>
       </c>
       <c r="U206" t="n">
         <v>0</v>
@@ -28653,16 +28653,16 @@
         <v>0</v>
       </c>
       <c r="Y206" t="n">
-        <v>0</v>
+        <v>-337</v>
       </c>
       <c r="Z206" t="n">
-        <v>0</v>
+        <v>2663</v>
       </c>
       <c r="AA206" t="n">
-        <v>0</v>
+        <v>-36903</v>
       </c>
       <c r="AB206" t="n">
-        <v>0</v>
+        <v>-49748</v>
       </c>
       <c r="AC206" t="n">
         <v>18</v>
@@ -28671,10 +28671,10 @@
         <v>18</v>
       </c>
       <c r="AE206" t="n">
-        <v>45</v>
+        <v>5</v>
       </c>
       <c r="AF206" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AG206" t="n">
         <v>0</v>
@@ -28694,17 +28694,17 @@
       </c>
       <c r="AM206" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、量能未放大</t>
+          <t>站上5日線、空頭排列、量能溫和放大</t>
         </is>
       </c>
       <c r="AN206" t="inlineStr">
         <is>
-          <t>籌碼中性</t>
+          <t>法人連續偏買、5日法人小幅買超</t>
         </is>
       </c>
       <c r="AO206" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、多頭排列、量能未放大、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、空頭排列、量能溫和放大、法人連續偏買、5日法人小幅買超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
@@ -35972,12 +35972,12 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>5009.TWO</t>
+          <t>3260.TWO</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>榮剛</t>
+          <t>威剛</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
@@ -35986,28 +35986,28 @@
         </is>
       </c>
       <c r="D260" t="n">
-        <v>33.6</v>
+        <v>415.5</v>
       </c>
       <c r="E260" t="n">
-        <v>34.05</v>
+        <v>422.2</v>
       </c>
       <c r="F260" t="n">
-        <v>33.62</v>
+        <v>409.6</v>
       </c>
       <c r="G260" t="n">
-        <v>33.25</v>
+        <v>407.62</v>
       </c>
       <c r="H260" t="n">
-        <v>1016000</v>
+        <v>5844000</v>
       </c>
       <c r="I260" t="n">
-        <v>2080200</v>
+        <v>17003200</v>
       </c>
       <c r="J260" t="n">
-        <v>35.5</v>
+        <v>459.5</v>
       </c>
       <c r="K260" t="n">
-        <v>31.5</v>
+        <v>375</v>
       </c>
       <c r="L260" t="inlineStr">
         <is>
@@ -36520,12 +36520,12 @@
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>3167.TW</t>
+          <t>5009.TWO</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>大量</t>
+          <t>榮剛</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
@@ -36534,28 +36534,28 @@
         </is>
       </c>
       <c r="D264" t="n">
-        <v>742</v>
+        <v>33.6</v>
       </c>
       <c r="E264" t="n">
-        <v>704.4</v>
+        <v>34.05</v>
       </c>
       <c r="F264" t="n">
-        <v>712.2</v>
+        <v>33.62</v>
       </c>
       <c r="G264" t="n">
-        <v>670.3</v>
+        <v>33.25</v>
       </c>
       <c r="H264" t="n">
-        <v>4258684</v>
+        <v>1016000</v>
       </c>
       <c r="I264" t="n">
-        <v>5121204</v>
+        <v>2080200</v>
       </c>
       <c r="J264" t="n">
-        <v>795</v>
+        <v>35.5</v>
       </c>
       <c r="K264" t="n">
-        <v>460.5</v>
+        <v>31.5</v>
       </c>
       <c r="L264" t="inlineStr">
         <is>
@@ -36563,52 +36563,52 @@
         </is>
       </c>
       <c r="M264" t="n">
-        <v>348903</v>
+        <v>0</v>
       </c>
       <c r="N264" t="n">
-        <v>408116</v>
+        <v>0</v>
       </c>
       <c r="O264" t="n">
-        <v>-1509777</v>
+        <v>0</v>
       </c>
       <c r="P264" t="n">
-        <v>-1222647</v>
+        <v>0</v>
       </c>
       <c r="Q264" t="n">
-        <v>384934</v>
+        <v>0</v>
       </c>
       <c r="R264" t="n">
-        <v>329093</v>
+        <v>0</v>
       </c>
       <c r="S264" t="n">
-        <v>-1557891</v>
+        <v>0</v>
       </c>
       <c r="T264" t="n">
-        <v>-1974124</v>
+        <v>0</v>
       </c>
       <c r="U264" t="n">
-        <v>-1000</v>
+        <v>0</v>
       </c>
       <c r="V264" t="n">
-        <v>149000</v>
+        <v>0</v>
       </c>
       <c r="W264" t="n">
-        <v>149000</v>
+        <v>0</v>
       </c>
       <c r="X264" t="n">
-        <v>833000</v>
+        <v>0</v>
       </c>
       <c r="Y264" t="n">
-        <v>-35031</v>
+        <v>0</v>
       </c>
       <c r="Z264" t="n">
-        <v>-69977</v>
+        <v>0</v>
       </c>
       <c r="AA264" t="n">
-        <v>-100886</v>
+        <v>0</v>
       </c>
       <c r="AB264" t="n">
-        <v>-81523</v>
+        <v>0</v>
       </c>
       <c r="AC264" t="n">
         <v>2</v>
@@ -36617,10 +36617,10 @@
         <v>2</v>
       </c>
       <c r="AE264" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="AF264" t="n">
-        <v>-15</v>
+        <v>0</v>
       </c>
       <c r="AG264" t="n">
         <v>0</v>
@@ -36640,29 +36640,29 @@
       </c>
       <c r="AM264" t="inlineStr">
         <is>
-          <t>站上5日線、量能未放大</t>
+          <t>跌破5日線、多頭排列、量能未放大</t>
         </is>
       </c>
       <c r="AN264" t="inlineStr">
         <is>
-          <t>短線籌碼止穩、5日法人明顯賣超、投信買外資賣</t>
+          <t>籌碼中性</t>
         </is>
       </c>
       <c r="AO264" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、量能未放大、短線籌碼止穩、5日法人明顯賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、多頭排列、量能未放大、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>3227.TWO</t>
+          <t>3167.TW</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>原相</t>
+          <t>大量</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
@@ -36671,28 +36671,28 @@
         </is>
       </c>
       <c r="D265" t="n">
-        <v>192</v>
+        <v>742</v>
       </c>
       <c r="E265" t="n">
-        <v>189.3</v>
+        <v>704.4</v>
       </c>
       <c r="F265" t="n">
-        <v>192.65</v>
+        <v>712.2</v>
       </c>
       <c r="G265" t="n">
-        <v>202.12</v>
+        <v>670.3</v>
       </c>
       <c r="H265" t="n">
-        <v>1504000</v>
+        <v>4258684</v>
       </c>
       <c r="I265" t="n">
-        <v>1184800</v>
+        <v>5121204</v>
       </c>
       <c r="J265" t="n">
-        <v>250</v>
+        <v>795</v>
       </c>
       <c r="K265" t="n">
-        <v>174.5</v>
+        <v>460.5</v>
       </c>
       <c r="L265" t="inlineStr">
         <is>
@@ -36700,52 +36700,52 @@
         </is>
       </c>
       <c r="M265" t="n">
-        <v>0</v>
+        <v>348903</v>
       </c>
       <c r="N265" t="n">
-        <v>0</v>
+        <v>408116</v>
       </c>
       <c r="O265" t="n">
-        <v>0</v>
+        <v>-1509777</v>
       </c>
       <c r="P265" t="n">
-        <v>0</v>
+        <v>-1222647</v>
       </c>
       <c r="Q265" t="n">
-        <v>0</v>
+        <v>384934</v>
       </c>
       <c r="R265" t="n">
-        <v>0</v>
+        <v>329093</v>
       </c>
       <c r="S265" t="n">
-        <v>0</v>
+        <v>-1557891</v>
       </c>
       <c r="T265" t="n">
-        <v>0</v>
+        <v>-1974124</v>
       </c>
       <c r="U265" t="n">
-        <v>0</v>
+        <v>-1000</v>
       </c>
       <c r="V265" t="n">
-        <v>0</v>
+        <v>149000</v>
       </c>
       <c r="W265" t="n">
-        <v>0</v>
+        <v>149000</v>
       </c>
       <c r="X265" t="n">
-        <v>0</v>
+        <v>833000</v>
       </c>
       <c r="Y265" t="n">
-        <v>0</v>
+        <v>-35031</v>
       </c>
       <c r="Z265" t="n">
-        <v>0</v>
+        <v>-69977</v>
       </c>
       <c r="AA265" t="n">
-        <v>0</v>
+        <v>-100886</v>
       </c>
       <c r="AB265" t="n">
-        <v>0</v>
+        <v>-81523</v>
       </c>
       <c r="AC265" t="n">
         <v>2</v>
@@ -36754,10 +36754,10 @@
         <v>2</v>
       </c>
       <c r="AE265" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="AF265" t="n">
-        <v>0</v>
+        <v>-15</v>
       </c>
       <c r="AG265" t="n">
         <v>0</v>
@@ -36777,29 +36777,29 @@
       </c>
       <c r="AM265" t="inlineStr">
         <is>
-          <t>站上5日線、空頭排列、量能溫和放大</t>
+          <t>站上5日線、量能未放大</t>
         </is>
       </c>
       <c r="AN265" t="inlineStr">
         <is>
-          <t>籌碼中性</t>
+          <t>短線籌碼止穩、5日法人明顯賣超、投信買外資賣</t>
         </is>
       </c>
       <c r="AO265" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、空頭排列、量能溫和放大、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、量能未放大、短線籌碼止穩、5日法人明顯賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>3260.TWO</t>
+          <t>6485.TWO</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>威剛</t>
+          <t>點序</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
@@ -36808,28 +36808,28 @@
         </is>
       </c>
       <c r="D266" t="n">
-        <v>415.5</v>
+        <v>61.5</v>
       </c>
       <c r="E266" t="n">
-        <v>422.2</v>
+        <v>60.58</v>
       </c>
       <c r="F266" t="n">
-        <v>409.6</v>
+        <v>60.8</v>
       </c>
       <c r="G266" t="n">
-        <v>407.62</v>
+        <v>61.91</v>
       </c>
       <c r="H266" t="n">
-        <v>5844000</v>
+        <v>246000</v>
       </c>
       <c r="I266" t="n">
-        <v>17003200</v>
+        <v>177800</v>
       </c>
       <c r="J266" t="n">
-        <v>459.5</v>
+        <v>69.3</v>
       </c>
       <c r="K266" t="n">
-        <v>375</v>
+        <v>55.4</v>
       </c>
       <c r="L266" t="inlineStr">
         <is>
@@ -36914,7 +36914,7 @@
       </c>
       <c r="AM266" t="inlineStr">
         <is>
-          <t>跌破5日線、多頭排列、量能未放大</t>
+          <t>站上5日線、空頭排列、量能溫和放大</t>
         </is>
       </c>
       <c r="AN266" t="inlineStr">
@@ -36924,7 +36924,7 @@
       </c>
       <c r="AO266" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、多頭排列、量能未放大、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、空頭排列、量能溫和放大、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
@@ -38027,12 +38027,12 @@
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>6485.TWO</t>
+          <t>1906.TW</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>點序</t>
+          <t>寶隆</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
@@ -38041,28 +38041,28 @@
         </is>
       </c>
       <c r="D275" t="n">
-        <v>61.5</v>
+        <v>11.5</v>
       </c>
       <c r="E275" t="n">
-        <v>60.58</v>
+        <v>11.56</v>
       </c>
       <c r="F275" t="n">
-        <v>60.8</v>
+        <v>11.49</v>
       </c>
       <c r="G275" t="n">
-        <v>61.91</v>
+        <v>11.34</v>
       </c>
       <c r="H275" t="n">
-        <v>246000</v>
+        <v>36583</v>
       </c>
       <c r="I275" t="n">
-        <v>177800</v>
+        <v>128253</v>
       </c>
       <c r="J275" t="n">
-        <v>69.3</v>
+        <v>12.2</v>
       </c>
       <c r="K275" t="n">
-        <v>55.4</v>
+        <v>10.85</v>
       </c>
       <c r="L275" t="inlineStr">
         <is>
@@ -38070,28 +38070,28 @@
         </is>
       </c>
       <c r="M275" t="n">
-        <v>0</v>
+        <v>911</v>
       </c>
       <c r="N275" t="n">
-        <v>0</v>
+        <v>-6096</v>
       </c>
       <c r="O275" t="n">
-        <v>0</v>
+        <v>11897</v>
       </c>
       <c r="P275" t="n">
-        <v>0</v>
+        <v>105571</v>
       </c>
       <c r="Q275" t="n">
-        <v>0</v>
+        <v>2911</v>
       </c>
       <c r="R275" t="n">
-        <v>0</v>
+        <v>-96</v>
       </c>
       <c r="S275" t="n">
-        <v>0</v>
+        <v>15897</v>
       </c>
       <c r="T275" t="n">
-        <v>0</v>
+        <v>96571</v>
       </c>
       <c r="U275" t="n">
         <v>0</v>
@@ -38106,16 +38106,16 @@
         <v>0</v>
       </c>
       <c r="Y275" t="n">
-        <v>0</v>
+        <v>-2000</v>
       </c>
       <c r="Z275" t="n">
-        <v>0</v>
+        <v>-6000</v>
       </c>
       <c r="AA275" t="n">
-        <v>0</v>
+        <v>-4000</v>
       </c>
       <c r="AB275" t="n">
-        <v>0</v>
+        <v>9000</v>
       </c>
       <c r="AC275" t="n">
         <v>2</v>
@@ -38147,7 +38147,7 @@
       </c>
       <c r="AM275" t="inlineStr">
         <is>
-          <t>站上5日線、空頭排列、量能溫和放大</t>
+          <t>跌破5日線、多頭排列、量能未放大</t>
         </is>
       </c>
       <c r="AN275" t="inlineStr">
@@ -38157,19 +38157,19 @@
       </c>
       <c r="AO275" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、空頭排列、量能溫和放大、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、多頭排列、量能未放大、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>1906.TW</t>
+          <t>1609.TW</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>寶隆</t>
+          <t>大亞</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
@@ -38178,96 +38178,96 @@
         </is>
       </c>
       <c r="D276" t="n">
-        <v>11.5</v>
+        <v>37.75</v>
       </c>
       <c r="E276" t="n">
-        <v>11.56</v>
+        <v>37.5</v>
       </c>
       <c r="F276" t="n">
-        <v>11.49</v>
+        <v>37.38</v>
       </c>
       <c r="G276" t="n">
-        <v>11.34</v>
+        <v>36.8</v>
       </c>
       <c r="H276" t="n">
-        <v>36583</v>
+        <v>9333873</v>
       </c>
       <c r="I276" t="n">
-        <v>128253</v>
+        <v>3707384</v>
       </c>
       <c r="J276" t="n">
-        <v>12.2</v>
+        <v>38.8</v>
       </c>
       <c r="K276" t="n">
-        <v>10.85</v>
+        <v>33.4</v>
       </c>
       <c r="L276" t="inlineStr">
         <is>
-          <t>無明顯異常</t>
+          <t>爆量價未漲</t>
         </is>
       </c>
       <c r="M276" t="n">
-        <v>911</v>
+        <v>-2057871</v>
       </c>
       <c r="N276" t="n">
-        <v>-6096</v>
+        <v>-1724513</v>
       </c>
       <c r="O276" t="n">
-        <v>11897</v>
+        <v>-1268975</v>
       </c>
       <c r="P276" t="n">
-        <v>105571</v>
+        <v>-1040314</v>
       </c>
       <c r="Q276" t="n">
-        <v>2911</v>
+        <v>-2067973</v>
       </c>
       <c r="R276" t="n">
-        <v>-96</v>
+        <v>-1767491</v>
       </c>
       <c r="S276" t="n">
-        <v>15897</v>
+        <v>-1319159</v>
       </c>
       <c r="T276" t="n">
-        <v>96571</v>
+        <v>-982335</v>
       </c>
       <c r="U276" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="V276" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="W276" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="X276" t="n">
-        <v>0</v>
+        <v>-3000</v>
       </c>
       <c r="Y276" t="n">
-        <v>-2000</v>
+        <v>9102</v>
       </c>
       <c r="Z276" t="n">
-        <v>-6000</v>
+        <v>41978</v>
       </c>
       <c r="AA276" t="n">
-        <v>-4000</v>
+        <v>49184</v>
       </c>
       <c r="AB276" t="n">
-        <v>9000</v>
+        <v>-54979</v>
       </c>
       <c r="AC276" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD276" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AE276" t="n">
-        <v>5</v>
+        <v>65</v>
       </c>
       <c r="AF276" t="n">
-        <v>0</v>
+        <v>-55</v>
       </c>
       <c r="AG276" t="n">
-        <v>0</v>
+        <v>-20</v>
       </c>
       <c r="AH276" t="inlineStr"/>
       <c r="AI276" t="inlineStr"/>
@@ -38284,17 +38284,17 @@
       </c>
       <c r="AM276" t="inlineStr">
         <is>
-          <t>跌破5日線、多頭排列、量能未放大</t>
+          <t>站上5日線、多頭排列、爆量、爆量價未漲</t>
         </is>
       </c>
       <c r="AN276" t="inlineStr">
         <is>
-          <t>籌碼中性</t>
+          <t>法人連續偏賣、5日法人明顯賣超、投信買外資賣</t>
         </is>
       </c>
       <c r="AO276" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、多頭排列、量能未放大、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、多頭排列、爆量、爆量價未漲、法人連續偏賣、5日法人明顯賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
@@ -38575,12 +38575,12 @@
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>1609.TW</t>
+          <t>3010.TW</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>大亞</t>
+          <t>華立</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
@@ -38589,81 +38589,81 @@
         </is>
       </c>
       <c r="D279" t="n">
-        <v>37.75</v>
+        <v>129</v>
       </c>
       <c r="E279" t="n">
-        <v>37.5</v>
+        <v>128.4</v>
       </c>
       <c r="F279" t="n">
-        <v>37.38</v>
+        <v>128.2</v>
       </c>
       <c r="G279" t="n">
-        <v>36.8</v>
+        <v>124.92</v>
       </c>
       <c r="H279" t="n">
-        <v>9333873</v>
+        <v>448172</v>
       </c>
       <c r="I279" t="n">
-        <v>3707384</v>
+        <v>465561</v>
       </c>
       <c r="J279" t="n">
-        <v>38.8</v>
+        <v>135.5</v>
       </c>
       <c r="K279" t="n">
-        <v>33.4</v>
+        <v>112</v>
       </c>
       <c r="L279" t="inlineStr">
         <is>
-          <t>爆量價未漲</t>
+          <t>無明顯異常</t>
         </is>
       </c>
       <c r="M279" t="n">
-        <v>-2057871</v>
+        <v>-95571</v>
       </c>
       <c r="N279" t="n">
-        <v>-1724513</v>
+        <v>-467549</v>
       </c>
       <c r="O279" t="n">
-        <v>-1268975</v>
+        <v>-458525</v>
       </c>
       <c r="P279" t="n">
-        <v>-1040314</v>
+        <v>-1114714</v>
       </c>
       <c r="Q279" t="n">
-        <v>-2067973</v>
+        <v>-111735</v>
       </c>
       <c r="R279" t="n">
-        <v>-1767491</v>
+        <v>-483878</v>
       </c>
       <c r="S279" t="n">
-        <v>-1319159</v>
+        <v>-486343</v>
       </c>
       <c r="T279" t="n">
-        <v>-982335</v>
+        <v>-1168116</v>
       </c>
       <c r="U279" t="n">
-        <v>1000</v>
+        <v>-1000</v>
       </c>
       <c r="V279" t="n">
-        <v>1000</v>
+        <v>-1000</v>
       </c>
       <c r="W279" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="X279" t="n">
-        <v>-3000</v>
+        <v>-2000</v>
       </c>
       <c r="Y279" t="n">
-        <v>9102</v>
+        <v>17164</v>
       </c>
       <c r="Z279" t="n">
-        <v>41978</v>
+        <v>17329</v>
       </c>
       <c r="AA279" t="n">
-        <v>49184</v>
+        <v>27818</v>
       </c>
       <c r="AB279" t="n">
-        <v>-54979</v>
+        <v>55402</v>
       </c>
       <c r="AC279" t="n">
         <v>0</v>
@@ -38672,13 +38672,13 @@
         <v>0</v>
       </c>
       <c r="AE279" t="n">
-        <v>65</v>
+        <v>45</v>
       </c>
       <c r="AF279" t="n">
-        <v>-55</v>
+        <v>-45</v>
       </c>
       <c r="AG279" t="n">
-        <v>-20</v>
+        <v>0</v>
       </c>
       <c r="AH279" t="inlineStr"/>
       <c r="AI279" t="inlineStr"/>
@@ -38695,17 +38695,17 @@
       </c>
       <c r="AM279" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、爆量、爆量價未漲</t>
+          <t>站上5日線、多頭排列、量能未放大</t>
         </is>
       </c>
       <c r="AN279" t="inlineStr">
         <is>
-          <t>法人連續偏賣、5日法人明顯賣超、投信買外資賣</t>
+          <t>法人連續偏賣、5日法人賣超</t>
         </is>
       </c>
       <c r="AO279" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、多頭排列、爆量、爆量價未漲、法人連續偏賣、5日法人明顯賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、多頭排列、量能未放大、法人連續偏賣、5日法人賣超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
@@ -38849,12 +38849,12 @@
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>3010.TW</t>
+          <t>2002.TW</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>華立</t>
+          <t>中鋼</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
@@ -38863,28 +38863,28 @@
         </is>
       </c>
       <c r="D281" t="n">
-        <v>129</v>
+        <v>19.15</v>
       </c>
       <c r="E281" t="n">
-        <v>128.4</v>
+        <v>19.24</v>
       </c>
       <c r="F281" t="n">
-        <v>128.2</v>
+        <v>19.13</v>
       </c>
       <c r="G281" t="n">
-        <v>124.92</v>
+        <v>19.16</v>
       </c>
       <c r="H281" t="n">
-        <v>448172</v>
+        <v>16519030</v>
       </c>
       <c r="I281" t="n">
-        <v>465561</v>
+        <v>24029124</v>
       </c>
       <c r="J281" t="n">
-        <v>135.5</v>
+        <v>19.9</v>
       </c>
       <c r="K281" t="n">
-        <v>112</v>
+        <v>18.65</v>
       </c>
       <c r="L281" t="inlineStr">
         <is>
@@ -38892,52 +38892,52 @@
         </is>
       </c>
       <c r="M281" t="n">
-        <v>-95571</v>
+        <v>-2601415</v>
       </c>
       <c r="N281" t="n">
-        <v>-467549</v>
+        <v>-3198701</v>
       </c>
       <c r="O281" t="n">
-        <v>-458525</v>
+        <v>8533878</v>
       </c>
       <c r="P281" t="n">
-        <v>-1114714</v>
+        <v>12839252</v>
       </c>
       <c r="Q281" t="n">
-        <v>-111735</v>
+        <v>-1735539</v>
       </c>
       <c r="R281" t="n">
-        <v>-483878</v>
+        <v>-2478672</v>
       </c>
       <c r="S281" t="n">
-        <v>-486343</v>
+        <v>10214219</v>
       </c>
       <c r="T281" t="n">
-        <v>-1168116</v>
+        <v>14825152</v>
       </c>
       <c r="U281" t="n">
-        <v>-1000</v>
+        <v>-4000</v>
       </c>
       <c r="V281" t="n">
-        <v>-1000</v>
+        <v>-4000</v>
       </c>
       <c r="W281" t="n">
-        <v>0</v>
+        <v>-19000</v>
       </c>
       <c r="X281" t="n">
-        <v>-2000</v>
+        <v>-172000</v>
       </c>
       <c r="Y281" t="n">
-        <v>17164</v>
+        <v>-861876</v>
       </c>
       <c r="Z281" t="n">
-        <v>17329</v>
+        <v>-716029</v>
       </c>
       <c r="AA281" t="n">
-        <v>27818</v>
+        <v>-1661341</v>
       </c>
       <c r="AB281" t="n">
-        <v>55402</v>
+        <v>-1813900</v>
       </c>
       <c r="AC281" t="n">
         <v>0</v>
@@ -38946,10 +38946,10 @@
         <v>0</v>
       </c>
       <c r="AE281" t="n">
-        <v>45</v>
+        <v>-30</v>
       </c>
       <c r="AF281" t="n">
-        <v>-45</v>
+        <v>30</v>
       </c>
       <c r="AG281" t="n">
         <v>0</v>
@@ -38969,29 +38969,29 @@
       </c>
       <c r="AM281" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、量能未放大</t>
+          <t>跌破5日線、量能未放大、接近20日低點</t>
         </is>
       </c>
       <c r="AN281" t="inlineStr">
         <is>
-          <t>法人連續偏賣、5日法人賣超</t>
+          <t>5日法人明顯買超、外資買投信賣</t>
         </is>
       </c>
       <c r="AO281" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、多頭排列、量能未放大、法人連續偏賣、5日法人賣超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、量能未放大、接近20日低點、5日法人明顯買超、外資買投信賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>2002.TW</t>
+          <t>2409.TW</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>中鋼</t>
+          <t>友達</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
@@ -39000,28 +39000,28 @@
         </is>
       </c>
       <c r="D282" t="n">
-        <v>19.15</v>
+        <v>25.25</v>
       </c>
       <c r="E282" t="n">
-        <v>19.24</v>
+        <v>25.45</v>
       </c>
       <c r="F282" t="n">
-        <v>19.13</v>
+        <v>25.86</v>
       </c>
       <c r="G282" t="n">
-        <v>19.16</v>
+        <v>25.49</v>
       </c>
       <c r="H282" t="n">
-        <v>16519030</v>
+        <v>58110008</v>
       </c>
       <c r="I282" t="n">
-        <v>24029124</v>
+        <v>69977618</v>
       </c>
       <c r="J282" t="n">
-        <v>19.9</v>
+        <v>27.9</v>
       </c>
       <c r="K282" t="n">
-        <v>18.65</v>
+        <v>23.4</v>
       </c>
       <c r="L282" t="inlineStr">
         <is>
@@ -39029,52 +39029,52 @@
         </is>
       </c>
       <c r="M282" t="n">
-        <v>-2601415</v>
+        <v>-906979</v>
       </c>
       <c r="N282" t="n">
-        <v>-3198701</v>
+        <v>12953594</v>
       </c>
       <c r="O282" t="n">
-        <v>8533878</v>
+        <v>111879</v>
       </c>
       <c r="P282" t="n">
-        <v>12839252</v>
+        <v>1344132</v>
       </c>
       <c r="Q282" t="n">
-        <v>-1735539</v>
+        <v>425358</v>
       </c>
       <c r="R282" t="n">
-        <v>-2478672</v>
+        <v>14163208</v>
       </c>
       <c r="S282" t="n">
-        <v>10214219</v>
+        <v>1638026</v>
       </c>
       <c r="T282" t="n">
-        <v>14825152</v>
+        <v>6258104</v>
       </c>
       <c r="U282" t="n">
-        <v>-4000</v>
+        <v>-51450</v>
       </c>
       <c r="V282" t="n">
-        <v>-4000</v>
+        <v>-155657</v>
       </c>
       <c r="W282" t="n">
-        <v>-19000</v>
+        <v>-151657</v>
       </c>
       <c r="X282" t="n">
-        <v>-172000</v>
+        <v>-290598</v>
       </c>
       <c r="Y282" t="n">
-        <v>-861876</v>
+        <v>-1280887</v>
       </c>
       <c r="Z282" t="n">
-        <v>-716029</v>
+        <v>-1053957</v>
       </c>
       <c r="AA282" t="n">
-        <v>-1661341</v>
+        <v>-1374490</v>
       </c>
       <c r="AB282" t="n">
-        <v>-1813900</v>
+        <v>-4623374</v>
       </c>
       <c r="AC282" t="n">
         <v>0</v>
@@ -39083,10 +39083,10 @@
         <v>0</v>
       </c>
       <c r="AE282" t="n">
-        <v>-30</v>
+        <v>-20</v>
       </c>
       <c r="AF282" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="AG282" t="n">
         <v>0</v>
@@ -39106,17 +39106,17 @@
       </c>
       <c r="AM282" t="inlineStr">
         <is>
-          <t>跌破5日線、量能未放大、接近20日低點</t>
+          <t>跌破5日線、量能未放大</t>
         </is>
       </c>
       <c r="AN282" t="inlineStr">
         <is>
-          <t>5日法人明顯買超、外資買投信賣</t>
+          <t>5日法人買超、外資買投信賣</t>
         </is>
       </c>
       <c r="AO282" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、量能未放大、接近20日低點、5日法人明顯買超、外資買投信賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、量能未放大、5日法人買超、外資買投信賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
@@ -39534,12 +39534,12 @@
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>2409.TW</t>
+          <t>2880.TW</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>友達</t>
+          <t>華南金</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
@@ -39548,28 +39548,28 @@
         </is>
       </c>
       <c r="D286" t="n">
-        <v>25.25</v>
+        <v>39.35</v>
       </c>
       <c r="E286" t="n">
-        <v>25.45</v>
+        <v>39.52</v>
       </c>
       <c r="F286" t="n">
-        <v>25.86</v>
+        <v>39.33</v>
       </c>
       <c r="G286" t="n">
-        <v>25.49</v>
+        <v>41.27</v>
       </c>
       <c r="H286" t="n">
-        <v>58110008</v>
+        <v>9459728</v>
       </c>
       <c r="I286" t="n">
-        <v>69977618</v>
+        <v>14256704</v>
       </c>
       <c r="J286" t="n">
-        <v>27.9</v>
+        <v>45.15</v>
       </c>
       <c r="K286" t="n">
-        <v>23.4</v>
+        <v>38</v>
       </c>
       <c r="L286" t="inlineStr">
         <is>
@@ -39577,52 +39577,52 @@
         </is>
       </c>
       <c r="M286" t="n">
-        <v>-906979</v>
+        <v>-639542</v>
       </c>
       <c r="N286" t="n">
-        <v>12953594</v>
+        <v>3520486</v>
       </c>
       <c r="O286" t="n">
-        <v>111879</v>
+        <v>8605213</v>
       </c>
       <c r="P286" t="n">
-        <v>1344132</v>
+        <v>31128145</v>
       </c>
       <c r="Q286" t="n">
-        <v>425358</v>
+        <v>386335</v>
       </c>
       <c r="R286" t="n">
-        <v>14163208</v>
+        <v>6068852</v>
       </c>
       <c r="S286" t="n">
-        <v>1638026</v>
+        <v>14499399</v>
       </c>
       <c r="T286" t="n">
-        <v>6258104</v>
+        <v>13243522</v>
       </c>
       <c r="U286" t="n">
-        <v>-51450</v>
+        <v>-50407</v>
       </c>
       <c r="V286" t="n">
-        <v>-155657</v>
+        <v>-1139407</v>
       </c>
       <c r="W286" t="n">
-        <v>-151657</v>
+        <v>-4309519</v>
       </c>
       <c r="X286" t="n">
-        <v>-290598</v>
+        <v>23558777</v>
       </c>
       <c r="Y286" t="n">
-        <v>-1280887</v>
+        <v>-975470</v>
       </c>
       <c r="Z286" t="n">
-        <v>-1053957</v>
+        <v>-1408959</v>
       </c>
       <c r="AA286" t="n">
-        <v>-1374490</v>
+        <v>-1584667</v>
       </c>
       <c r="AB286" t="n">
-        <v>-4623374</v>
+        <v>-5674154</v>
       </c>
       <c r="AC286" t="n">
         <v>0</v>
@@ -39631,10 +39631,10 @@
         <v>0</v>
       </c>
       <c r="AE286" t="n">
-        <v>-20</v>
+        <v>-30</v>
       </c>
       <c r="AF286" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="AG286" t="n">
         <v>0</v>
@@ -39654,29 +39654,29 @@
       </c>
       <c r="AM286" t="inlineStr">
         <is>
-          <t>跌破5日線、量能未放大</t>
+          <t>跌破5日線、量能未放大、接近20日低點</t>
         </is>
       </c>
       <c r="AN286" t="inlineStr">
         <is>
-          <t>5日法人買超、外資買投信賣</t>
+          <t>5日法人明顯買超、外資買投信賣</t>
         </is>
       </c>
       <c r="AO286" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、量能未放大、5日法人買超、外資買投信賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、量能未放大、接近20日低點、5日法人明顯買超、外資買投信賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>2880.TW</t>
+          <t>2014.TW</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>華南金</t>
+          <t>中鴻</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
@@ -39685,28 +39685,28 @@
         </is>
       </c>
       <c r="D287" t="n">
-        <v>39.35</v>
+        <v>17.15</v>
       </c>
       <c r="E287" t="n">
-        <v>39.52</v>
+        <v>17.28</v>
       </c>
       <c r="F287" t="n">
-        <v>39.33</v>
+        <v>17.16</v>
       </c>
       <c r="G287" t="n">
-        <v>41.27</v>
+        <v>17.18</v>
       </c>
       <c r="H287" t="n">
-        <v>9459728</v>
+        <v>981261</v>
       </c>
       <c r="I287" t="n">
-        <v>14256704</v>
+        <v>1477632</v>
       </c>
       <c r="J287" t="n">
-        <v>45.15</v>
+        <v>18.1</v>
       </c>
       <c r="K287" t="n">
-        <v>38</v>
+        <v>16.45</v>
       </c>
       <c r="L287" t="inlineStr">
         <is>
@@ -39714,52 +39714,52 @@
         </is>
       </c>
       <c r="M287" t="n">
-        <v>-639542</v>
+        <v>-65642</v>
       </c>
       <c r="N287" t="n">
-        <v>3520486</v>
+        <v>256313</v>
       </c>
       <c r="O287" t="n">
-        <v>8605213</v>
+        <v>1447188</v>
       </c>
       <c r="P287" t="n">
-        <v>31128145</v>
+        <v>949379</v>
       </c>
       <c r="Q287" t="n">
-        <v>386335</v>
+        <v>-69642</v>
       </c>
       <c r="R287" t="n">
-        <v>6068852</v>
+        <v>232313</v>
       </c>
       <c r="S287" t="n">
-        <v>14499399</v>
+        <v>1405188</v>
       </c>
       <c r="T287" t="n">
-        <v>13243522</v>
+        <v>915379</v>
       </c>
       <c r="U287" t="n">
-        <v>-50407</v>
+        <v>0</v>
       </c>
       <c r="V287" t="n">
-        <v>-1139407</v>
+        <v>0</v>
       </c>
       <c r="W287" t="n">
-        <v>-4309519</v>
+        <v>0</v>
       </c>
       <c r="X287" t="n">
-        <v>23558777</v>
+        <v>0</v>
       </c>
       <c r="Y287" t="n">
-        <v>-975470</v>
+        <v>4000</v>
       </c>
       <c r="Z287" t="n">
-        <v>-1408959</v>
+        <v>24000</v>
       </c>
       <c r="AA287" t="n">
-        <v>-1584667</v>
+        <v>42000</v>
       </c>
       <c r="AB287" t="n">
-        <v>-5674154</v>
+        <v>34000</v>
       </c>
       <c r="AC287" t="n">
         <v>0</v>
@@ -39796,12 +39796,12 @@
       </c>
       <c r="AN287" t="inlineStr">
         <is>
-          <t>5日法人明顯買超、外資買投信賣</t>
+          <t>5日法人明顯買超</t>
         </is>
       </c>
       <c r="AO287" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、量能未放大、接近20日低點、5日法人明顯買超、外資買投信賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、量能未放大、接近20日低點、5日法人明顯買超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
@@ -39945,12 +39945,12 @@
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>2014.TW</t>
+          <t>3529.TWO</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>中鴻</t>
+          <t>力旺</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
@@ -39959,28 +39959,28 @@
         </is>
       </c>
       <c r="D289" t="n">
-        <v>17.15</v>
+        <v>2650</v>
       </c>
       <c r="E289" t="n">
-        <v>17.28</v>
+        <v>2322</v>
       </c>
       <c r="F289" t="n">
-        <v>17.16</v>
+        <v>2346.5</v>
       </c>
       <c r="G289" t="n">
-        <v>17.18</v>
+        <v>2488.75</v>
       </c>
       <c r="H289" t="n">
-        <v>981261</v>
+        <v>545000</v>
       </c>
       <c r="I289" t="n">
-        <v>1477632</v>
+        <v>746400</v>
       </c>
       <c r="J289" t="n">
-        <v>18.1</v>
+        <v>2995</v>
       </c>
       <c r="K289" t="n">
-        <v>16.45</v>
+        <v>2090</v>
       </c>
       <c r="L289" t="inlineStr">
         <is>
@@ -39988,28 +39988,28 @@
         </is>
       </c>
       <c r="M289" t="n">
-        <v>-65642</v>
+        <v>0</v>
       </c>
       <c r="N289" t="n">
-        <v>256313</v>
+        <v>0</v>
       </c>
       <c r="O289" t="n">
-        <v>1447188</v>
+        <v>0</v>
       </c>
       <c r="P289" t="n">
-        <v>949379</v>
+        <v>0</v>
       </c>
       <c r="Q289" t="n">
-        <v>-69642</v>
+        <v>0</v>
       </c>
       <c r="R289" t="n">
-        <v>232313</v>
+        <v>0</v>
       </c>
       <c r="S289" t="n">
-        <v>1405188</v>
+        <v>0</v>
       </c>
       <c r="T289" t="n">
-        <v>915379</v>
+        <v>0</v>
       </c>
       <c r="U289" t="n">
         <v>0</v>
@@ -40024,28 +40024,28 @@
         <v>0</v>
       </c>
       <c r="Y289" t="n">
-        <v>4000</v>
+        <v>0</v>
       </c>
       <c r="Z289" t="n">
-        <v>24000</v>
+        <v>0</v>
       </c>
       <c r="AA289" t="n">
-        <v>42000</v>
+        <v>0</v>
       </c>
       <c r="AB289" t="n">
-        <v>34000</v>
+        <v>0</v>
       </c>
       <c r="AC289" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="AD289" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="AE289" t="n">
-        <v>-30</v>
+        <v>-5</v>
       </c>
       <c r="AF289" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="AG289" t="n">
         <v>0</v>
@@ -40065,29 +40065,29 @@
       </c>
       <c r="AM289" t="inlineStr">
         <is>
-          <t>跌破5日線、量能未放大、接近20日低點</t>
+          <t>站上5日線、空頭排列、量能未放大</t>
         </is>
       </c>
       <c r="AN289" t="inlineStr">
         <is>
-          <t>5日法人明顯買超</t>
+          <t>籌碼中性</t>
         </is>
       </c>
       <c r="AO289" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、量能未放大、接近20日低點、5日法人明顯買超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、空頭排列、量能未放大、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>1726.TW</t>
+          <t>3227.TWO</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>永記</t>
+          <t>原相</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
@@ -40096,57 +40096,57 @@
         </is>
       </c>
       <c r="D290" t="n">
-        <v>77.7</v>
+        <v>198</v>
       </c>
       <c r="E290" t="n">
-        <v>77.8</v>
+        <v>195.5</v>
       </c>
       <c r="F290" t="n">
-        <v>77.56</v>
+        <v>196.85</v>
       </c>
       <c r="G290" t="n">
-        <v>77.47</v>
+        <v>200.32</v>
       </c>
       <c r="H290" t="n">
-        <v>91703</v>
+        <v>563000</v>
       </c>
       <c r="I290" t="n">
-        <v>29714</v>
+        <v>667800</v>
       </c>
       <c r="J290" t="n">
-        <v>78.59999999999999</v>
+        <v>214.5</v>
       </c>
       <c r="K290" t="n">
-        <v>76.09999999999999</v>
+        <v>188</v>
       </c>
       <c r="L290" t="inlineStr">
         <is>
-          <t>爆量價未漲</t>
+          <t>無明顯異常</t>
         </is>
       </c>
       <c r="M290" t="n">
-        <v>-18000</v>
+        <v>0</v>
       </c>
       <c r="N290" t="n">
-        <v>-8000</v>
+        <v>0</v>
       </c>
       <c r="O290" t="n">
-        <v>-6115</v>
+        <v>0</v>
       </c>
       <c r="P290" t="n">
-        <v>-59426</v>
+        <v>0</v>
       </c>
       <c r="Q290" t="n">
-        <v>-16000</v>
+        <v>0</v>
       </c>
       <c r="R290" t="n">
-        <v>-8000</v>
+        <v>0</v>
       </c>
       <c r="S290" t="n">
-        <v>-6115</v>
+        <v>0</v>
       </c>
       <c r="T290" t="n">
-        <v>-62426</v>
+        <v>0</v>
       </c>
       <c r="U290" t="n">
         <v>0</v>
@@ -40161,7 +40161,7 @@
         <v>0</v>
       </c>
       <c r="Y290" t="n">
-        <v>-2000</v>
+        <v>0</v>
       </c>
       <c r="Z290" t="n">
         <v>0</v>
@@ -40170,7 +40170,7 @@
         <v>0</v>
       </c>
       <c r="AB290" t="n">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="AC290" t="n">
         <v>-2</v>
@@ -40179,13 +40179,13 @@
         <v>-2</v>
       </c>
       <c r="AE290" t="n">
-        <v>30</v>
+        <v>-5</v>
       </c>
       <c r="AF290" t="n">
-        <v>-25</v>
+        <v>0</v>
       </c>
       <c r="AG290" t="n">
-        <v>-20</v>
+        <v>0</v>
       </c>
       <c r="AH290" t="inlineStr"/>
       <c r="AI290" t="inlineStr"/>
@@ -40202,29 +40202,29 @@
       </c>
       <c r="AM290" t="inlineStr">
         <is>
-          <t>跌破5日線、多頭排列、爆量、接近20日高點、接近20日低點、爆量價未漲</t>
+          <t>站上5日線、空頭排列、量能未放大</t>
         </is>
       </c>
       <c r="AN290" t="inlineStr">
         <is>
-          <t>法人連續偏賣</t>
+          <t>籌碼中性</t>
         </is>
       </c>
       <c r="AO290" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、多頭排列、爆量、接近20日高點、接近20日低點、爆量價未漲、法人連續偏賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、空頭排列、量能未放大、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>3529.TWO</t>
+          <t>6274.TWO</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>力旺</t>
+          <t>台燿</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
@@ -40233,28 +40233,28 @@
         </is>
       </c>
       <c r="D291" t="n">
-        <v>2650</v>
+        <v>1445</v>
       </c>
       <c r="E291" t="n">
-        <v>2322</v>
+        <v>1482</v>
       </c>
       <c r="F291" t="n">
-        <v>2346.5</v>
+        <v>1530.5</v>
       </c>
       <c r="G291" t="n">
-        <v>2488.75</v>
+        <v>1484</v>
       </c>
       <c r="H291" t="n">
-        <v>545000</v>
+        <v>9023000</v>
       </c>
       <c r="I291" t="n">
-        <v>746400</v>
+        <v>5906200</v>
       </c>
       <c r="J291" t="n">
-        <v>2995</v>
+        <v>1730</v>
       </c>
       <c r="K291" t="n">
-        <v>2090</v>
+        <v>1110</v>
       </c>
       <c r="L291" t="inlineStr">
         <is>
@@ -40339,7 +40339,7 @@
       </c>
       <c r="AM291" t="inlineStr">
         <is>
-          <t>站上5日線、空頭排列、量能未放大</t>
+          <t>跌破5日線、成交量放大</t>
         </is>
       </c>
       <c r="AN291" t="inlineStr">
@@ -40349,19 +40349,19 @@
       </c>
       <c r="AO291" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、空頭排列、量能未放大、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、成交量放大、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>6274.TWO</t>
+          <t>1726.TW</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>台燿</t>
+          <t>永記</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
@@ -40370,57 +40370,57 @@
         </is>
       </c>
       <c r="D292" t="n">
-        <v>1445</v>
+        <v>77.7</v>
       </c>
       <c r="E292" t="n">
-        <v>1482</v>
+        <v>77.8</v>
       </c>
       <c r="F292" t="n">
-        <v>1530.5</v>
+        <v>77.56</v>
       </c>
       <c r="G292" t="n">
-        <v>1484</v>
+        <v>77.47</v>
       </c>
       <c r="H292" t="n">
-        <v>9023000</v>
+        <v>91703</v>
       </c>
       <c r="I292" t="n">
-        <v>5906200</v>
+        <v>29714</v>
       </c>
       <c r="J292" t="n">
-        <v>1730</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="K292" t="n">
-        <v>1110</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="L292" t="inlineStr">
         <is>
-          <t>無明顯異常</t>
+          <t>爆量價未漲</t>
         </is>
       </c>
       <c r="M292" t="n">
-        <v>0</v>
+        <v>-18000</v>
       </c>
       <c r="N292" t="n">
-        <v>0</v>
+        <v>-8000</v>
       </c>
       <c r="O292" t="n">
-        <v>0</v>
+        <v>-6115</v>
       </c>
       <c r="P292" t="n">
-        <v>0</v>
+        <v>-59426</v>
       </c>
       <c r="Q292" t="n">
-        <v>0</v>
+        <v>-16000</v>
       </c>
       <c r="R292" t="n">
-        <v>0</v>
+        <v>-8000</v>
       </c>
       <c r="S292" t="n">
-        <v>0</v>
+        <v>-6115</v>
       </c>
       <c r="T292" t="n">
-        <v>0</v>
+        <v>-62426</v>
       </c>
       <c r="U292" t="n">
         <v>0</v>
@@ -40435,7 +40435,7 @@
         <v>0</v>
       </c>
       <c r="Y292" t="n">
-        <v>0</v>
+        <v>-2000</v>
       </c>
       <c r="Z292" t="n">
         <v>0</v>
@@ -40444,7 +40444,7 @@
         <v>0</v>
       </c>
       <c r="AB292" t="n">
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="AC292" t="n">
         <v>-2</v>
@@ -40453,13 +40453,13 @@
         <v>-2</v>
       </c>
       <c r="AE292" t="n">
-        <v>-5</v>
+        <v>30</v>
       </c>
       <c r="AF292" t="n">
-        <v>0</v>
+        <v>-25</v>
       </c>
       <c r="AG292" t="n">
-        <v>0</v>
+        <v>-20</v>
       </c>
       <c r="AH292" t="inlineStr"/>
       <c r="AI292" t="inlineStr"/>
@@ -40476,17 +40476,17 @@
       </c>
       <c r="AM292" t="inlineStr">
         <is>
-          <t>跌破5日線、成交量放大</t>
+          <t>跌破5日線、多頭排列、爆量、接近20日高點、接近20日低點、爆量價未漲</t>
         </is>
       </c>
       <c r="AN292" t="inlineStr">
         <is>
-          <t>籌碼中性</t>
+          <t>法人連續偏賣</t>
         </is>
       </c>
       <c r="AO292" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、成交量放大、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、多頭排列、爆量、接近20日高點、接近20日低點、爆量價未漲、法人連續偏賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>

--- a/output/universe_analysis_result.xlsx
+++ b/output/universe_analysis_result.xlsx
@@ -25971,12 +25971,12 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>3260.TWO</t>
+          <t>5314.TWO</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>威剛</t>
+          <t>世紀</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -25985,28 +25985,28 @@
         </is>
       </c>
       <c r="D187" t="n">
-        <v>398.5</v>
+        <v>36</v>
       </c>
       <c r="E187" t="n">
-        <v>388.4</v>
+        <v>34.84</v>
       </c>
       <c r="F187" t="n">
-        <v>380</v>
+        <v>29.35</v>
       </c>
       <c r="G187" t="n">
-        <v>391.15</v>
+        <v>40.37</v>
       </c>
       <c r="H187" t="n">
-        <v>24347000</v>
+        <v>12104000</v>
       </c>
       <c r="I187" t="n">
-        <v>18842400</v>
+        <v>8903000</v>
       </c>
       <c r="J187" t="n">
-        <v>420</v>
+        <v>63.4</v>
       </c>
       <c r="K187" t="n">
-        <v>334</v>
+        <v>16.2</v>
       </c>
       <c r="L187" t="inlineStr">
         <is>
@@ -26108,12 +26108,12 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>5314.TWO</t>
+          <t>4919.TW</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>世紀</t>
+          <t>新唐</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -26122,28 +26122,28 @@
         </is>
       </c>
       <c r="D188" t="n">
-        <v>36</v>
+        <v>120</v>
       </c>
       <c r="E188" t="n">
-        <v>34.84</v>
+        <v>120.5</v>
       </c>
       <c r="F188" t="n">
-        <v>29.35</v>
+        <v>118.55</v>
       </c>
       <c r="G188" t="n">
-        <v>40.37</v>
+        <v>122.15</v>
       </c>
       <c r="H188" t="n">
-        <v>12104000</v>
+        <v>1982506</v>
       </c>
       <c r="I188" t="n">
-        <v>8903000</v>
+        <v>2552659</v>
       </c>
       <c r="J188" t="n">
-        <v>63.4</v>
+        <v>135.5</v>
       </c>
       <c r="K188" t="n">
-        <v>16.2</v>
+        <v>111</v>
       </c>
       <c r="L188" t="inlineStr">
         <is>
@@ -26151,52 +26151,52 @@
         </is>
       </c>
       <c r="M188" t="n">
-        <v>0</v>
+        <v>251046</v>
       </c>
       <c r="N188" t="n">
-        <v>0</v>
+        <v>155616</v>
       </c>
       <c r="O188" t="n">
-        <v>0</v>
+        <v>474302</v>
       </c>
       <c r="P188" t="n">
-        <v>0</v>
+        <v>-179435</v>
       </c>
       <c r="Q188" t="n">
-        <v>0</v>
+        <v>252789</v>
       </c>
       <c r="R188" t="n">
-        <v>0</v>
+        <v>268221</v>
       </c>
       <c r="S188" t="n">
-        <v>0</v>
+        <v>444691</v>
       </c>
       <c r="T188" t="n">
-        <v>0</v>
+        <v>-457000</v>
       </c>
       <c r="U188" t="n">
         <v>0</v>
       </c>
       <c r="V188" t="n">
-        <v>0</v>
+        <v>-3000</v>
       </c>
       <c r="W188" t="n">
-        <v>0</v>
+        <v>-11089</v>
       </c>
       <c r="X188" t="n">
-        <v>0</v>
+        <v>-21089</v>
       </c>
       <c r="Y188" t="n">
-        <v>0</v>
+        <v>-1743</v>
       </c>
       <c r="Z188" t="n">
-        <v>0</v>
+        <v>-109605</v>
       </c>
       <c r="AA188" t="n">
-        <v>0</v>
+        <v>40700</v>
       </c>
       <c r="AB188" t="n">
-        <v>0</v>
+        <v>298654</v>
       </c>
       <c r="AC188" t="n">
         <v>12</v>
@@ -26205,10 +26205,10 @@
         <v>12</v>
       </c>
       <c r="AE188" t="n">
-        <v>30</v>
+        <v>-20</v>
       </c>
       <c r="AF188" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AG188" t="n">
         <v>0</v>
@@ -26228,17 +26228,17 @@
       </c>
       <c r="AM188" t="inlineStr">
         <is>
-          <t>站上5日線、量能溫和放大</t>
+          <t>跌破5日線、量能未放大</t>
         </is>
       </c>
       <c r="AN188" t="inlineStr">
         <is>
-          <t>籌碼中性</t>
+          <t>法人連續偏買、5日法人買超、外資買投信賣</t>
         </is>
       </c>
       <c r="AO188" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、量能溫和放大、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、量能未放大、法人連續偏買、5日法人買超、外資買投信賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
@@ -27341,12 +27341,12 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>4919.TW</t>
+          <t>2903.TW</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>新唐</t>
+          <t>遠百</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -27355,28 +27355,28 @@
         </is>
       </c>
       <c r="D197" t="n">
-        <v>120</v>
+        <v>22.35</v>
       </c>
       <c r="E197" t="n">
-        <v>120.5</v>
+        <v>22.41</v>
       </c>
       <c r="F197" t="n">
-        <v>118.55</v>
+        <v>22.44</v>
       </c>
       <c r="G197" t="n">
-        <v>122.15</v>
+        <v>22.16</v>
       </c>
       <c r="H197" t="n">
-        <v>1982506</v>
+        <v>2230377</v>
       </c>
       <c r="I197" t="n">
-        <v>2552659</v>
+        <v>1701036</v>
       </c>
       <c r="J197" t="n">
-        <v>135.5</v>
+        <v>23.05</v>
       </c>
       <c r="K197" t="n">
-        <v>111</v>
+        <v>21.55</v>
       </c>
       <c r="L197" t="inlineStr">
         <is>
@@ -27384,52 +27384,52 @@
         </is>
       </c>
       <c r="M197" t="n">
-        <v>251046</v>
+        <v>-33000</v>
       </c>
       <c r="N197" t="n">
-        <v>155616</v>
+        <v>92071</v>
       </c>
       <c r="O197" t="n">
-        <v>474302</v>
+        <v>1235121</v>
       </c>
       <c r="P197" t="n">
-        <v>-179435</v>
+        <v>11140871</v>
       </c>
       <c r="Q197" t="n">
-        <v>252789</v>
+        <v>-25000</v>
       </c>
       <c r="R197" t="n">
-        <v>268221</v>
+        <v>68071</v>
       </c>
       <c r="S197" t="n">
-        <v>444691</v>
+        <v>1192121</v>
       </c>
       <c r="T197" t="n">
-        <v>-457000</v>
+        <v>10300584</v>
       </c>
       <c r="U197" t="n">
         <v>0</v>
       </c>
       <c r="V197" t="n">
-        <v>-3000</v>
+        <v>1000</v>
       </c>
       <c r="W197" t="n">
-        <v>-11089</v>
+        <v>1000</v>
       </c>
       <c r="X197" t="n">
-        <v>-21089</v>
+        <v>806000</v>
       </c>
       <c r="Y197" t="n">
-        <v>-1743</v>
+        <v>-8000</v>
       </c>
       <c r="Z197" t="n">
-        <v>-109605</v>
+        <v>23000</v>
       </c>
       <c r="AA197" t="n">
-        <v>40700</v>
+        <v>42000</v>
       </c>
       <c r="AB197" t="n">
-        <v>298654</v>
+        <v>34287</v>
       </c>
       <c r="AC197" t="n">
         <v>12</v>
@@ -27461,29 +27461,29 @@
       </c>
       <c r="AM197" t="inlineStr">
         <is>
-          <t>跌破5日線、量能未放大</t>
+          <t>跌破5日線、量能溫和放大、接近20日低點</t>
         </is>
       </c>
       <c r="AN197" t="inlineStr">
         <is>
-          <t>法人連續偏買、5日法人買超、外資買投信賣</t>
+          <t>5日法人明顯買超、外資投信同步買超</t>
         </is>
       </c>
       <c r="AO197" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、量能未放大、法人連續偏買、5日法人買超、外資買投信賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、量能溫和放大、接近20日低點、5日法人明顯買超、外資投信同步買超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>2903.TW</t>
+          <t>2020.TW</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>遠百</t>
+          <t>美亞</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -27492,28 +27492,28 @@
         </is>
       </c>
       <c r="D198" t="n">
-        <v>22.35</v>
+        <v>21.8</v>
       </c>
       <c r="E198" t="n">
-        <v>22.41</v>
+        <v>21.84</v>
       </c>
       <c r="F198" t="n">
-        <v>22.44</v>
+        <v>21.77</v>
       </c>
       <c r="G198" t="n">
-        <v>22.16</v>
+        <v>21.52</v>
       </c>
       <c r="H198" t="n">
-        <v>2230377</v>
+        <v>110322</v>
       </c>
       <c r="I198" t="n">
-        <v>1701036</v>
+        <v>177330</v>
       </c>
       <c r="J198" t="n">
-        <v>23.05</v>
+        <v>22.15</v>
       </c>
       <c r="K198" t="n">
-        <v>21.55</v>
+        <v>20.9</v>
       </c>
       <c r="L198" t="inlineStr">
         <is>
@@ -27521,52 +27521,52 @@
         </is>
       </c>
       <c r="M198" t="n">
-        <v>-33000</v>
+        <v>-8000</v>
       </c>
       <c r="N198" t="n">
-        <v>92071</v>
+        <v>54481</v>
       </c>
       <c r="O198" t="n">
-        <v>1235121</v>
+        <v>142481</v>
       </c>
       <c r="P198" t="n">
-        <v>11140871</v>
+        <v>495290</v>
       </c>
       <c r="Q198" t="n">
-        <v>-25000</v>
+        <v>-7000</v>
       </c>
       <c r="R198" t="n">
-        <v>68071</v>
+        <v>54481</v>
       </c>
       <c r="S198" t="n">
-        <v>1192121</v>
+        <v>152481</v>
       </c>
       <c r="T198" t="n">
-        <v>10300584</v>
+        <v>519290</v>
       </c>
       <c r="U198" t="n">
         <v>0</v>
       </c>
       <c r="V198" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="W198" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="X198" t="n">
-        <v>806000</v>
+        <v>0</v>
       </c>
       <c r="Y198" t="n">
-        <v>-8000</v>
+        <v>-1000</v>
       </c>
       <c r="Z198" t="n">
-        <v>23000</v>
+        <v>0</v>
       </c>
       <c r="AA198" t="n">
-        <v>42000</v>
+        <v>-10000</v>
       </c>
       <c r="AB198" t="n">
-        <v>34287</v>
+        <v>-24000</v>
       </c>
       <c r="AC198" t="n">
         <v>12</v>
@@ -27575,10 +27575,10 @@
         <v>12</v>
       </c>
       <c r="AE198" t="n">
-        <v>-20</v>
+        <v>10</v>
       </c>
       <c r="AF198" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="AG198" t="n">
         <v>0</v>
@@ -27598,29 +27598,29 @@
       </c>
       <c r="AM198" t="inlineStr">
         <is>
-          <t>跌破5日線、量能溫和放大、接近20日低點</t>
+          <t>跌破5日線、多頭排列、量能未放大、接近20日高點、接近20日低點</t>
         </is>
       </c>
       <c r="AN198" t="inlineStr">
         <is>
-          <t>5日法人明顯買超、外資投信同步買超</t>
+          <t>5日法人買超</t>
         </is>
       </c>
       <c r="AO198" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、量能溫和放大、接近20日低點、5日法人明顯買超、外資投信同步買超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、多頭排列、量能未放大、接近20日高點、接近20日低點、5日法人買超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>2020.TW</t>
+          <t>3056.TW</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>美亞</t>
+          <t>總太</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -27629,28 +27629,28 @@
         </is>
       </c>
       <c r="D199" t="n">
-        <v>21.8</v>
+        <v>14.05</v>
       </c>
       <c r="E199" t="n">
-        <v>21.84</v>
+        <v>14.2</v>
       </c>
       <c r="F199" t="n">
-        <v>21.77</v>
+        <v>14.18</v>
       </c>
       <c r="G199" t="n">
-        <v>21.52</v>
+        <v>14.12</v>
       </c>
       <c r="H199" t="n">
-        <v>110322</v>
+        <v>622010</v>
       </c>
       <c r="I199" t="n">
-        <v>177330</v>
+        <v>562845</v>
       </c>
       <c r="J199" t="n">
-        <v>22.15</v>
+        <v>14.45</v>
       </c>
       <c r="K199" t="n">
-        <v>20.9</v>
+        <v>13.7</v>
       </c>
       <c r="L199" t="inlineStr">
         <is>
@@ -27658,28 +27658,28 @@
         </is>
       </c>
       <c r="M199" t="n">
-        <v>-8000</v>
+        <v>-285585</v>
       </c>
       <c r="N199" t="n">
-        <v>54481</v>
+        <v>-47890</v>
       </c>
       <c r="O199" t="n">
-        <v>142481</v>
+        <v>209298</v>
       </c>
       <c r="P199" t="n">
-        <v>495290</v>
+        <v>1784683</v>
       </c>
       <c r="Q199" t="n">
-        <v>-7000</v>
+        <v>-289585</v>
       </c>
       <c r="R199" t="n">
-        <v>54481</v>
+        <v>-54890</v>
       </c>
       <c r="S199" t="n">
-        <v>152481</v>
+        <v>187920</v>
       </c>
       <c r="T199" t="n">
-        <v>519290</v>
+        <v>1751346</v>
       </c>
       <c r="U199" t="n">
         <v>0</v>
@@ -27694,25 +27694,25 @@
         <v>0</v>
       </c>
       <c r="Y199" t="n">
-        <v>-1000</v>
+        <v>4000</v>
       </c>
       <c r="Z199" t="n">
-        <v>0</v>
+        <v>7000</v>
       </c>
       <c r="AA199" t="n">
-        <v>-10000</v>
+        <v>21378</v>
       </c>
       <c r="AB199" t="n">
-        <v>-24000</v>
+        <v>33337</v>
       </c>
       <c r="AC199" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AD199" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AE199" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="AF199" t="n">
         <v>20</v>
@@ -27735,7 +27735,7 @@
       </c>
       <c r="AM199" t="inlineStr">
         <is>
-          <t>跌破5日線、多頭排列、量能未放大、接近20日高點、接近20日低點</t>
+          <t>跌破5日線、多頭排列、量能溫和放大、接近20日低點</t>
         </is>
       </c>
       <c r="AN199" t="inlineStr">
@@ -27745,7 +27745,7 @@
       </c>
       <c r="AO199" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、多頭排列、量能未放大、接近20日高點、接近20日低點、5日法人買超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、多頭排列、量能溫和放大、接近20日低點、5日法人買超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
@@ -28026,12 +28026,12 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>3056.TW</t>
+          <t>6409.TW</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>總太</t>
+          <t>旭隼</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -28040,28 +28040,28 @@
         </is>
       </c>
       <c r="D202" t="n">
-        <v>14.05</v>
+        <v>1035</v>
       </c>
       <c r="E202" t="n">
-        <v>14.2</v>
+        <v>1032</v>
       </c>
       <c r="F202" t="n">
-        <v>14.18</v>
+        <v>1030</v>
       </c>
       <c r="G202" t="n">
-        <v>14.12</v>
+        <v>1012.2</v>
       </c>
       <c r="H202" t="n">
-        <v>622010</v>
+        <v>322202</v>
       </c>
       <c r="I202" t="n">
-        <v>562845</v>
+        <v>400975</v>
       </c>
       <c r="J202" t="n">
-        <v>14.45</v>
+        <v>1105</v>
       </c>
       <c r="K202" t="n">
-        <v>13.7</v>
+        <v>917</v>
       </c>
       <c r="L202" t="inlineStr">
         <is>
@@ -28069,64 +28069,64 @@
         </is>
       </c>
       <c r="M202" t="n">
-        <v>-285585</v>
+        <v>169</v>
       </c>
       <c r="N202" t="n">
-        <v>-47890</v>
+        <v>-101599</v>
       </c>
       <c r="O202" t="n">
-        <v>209298</v>
+        <v>-1705</v>
       </c>
       <c r="P202" t="n">
-        <v>1784683</v>
+        <v>110554</v>
       </c>
       <c r="Q202" t="n">
-        <v>-289585</v>
+        <v>-47139</v>
       </c>
       <c r="R202" t="n">
-        <v>-54890</v>
+        <v>-138511</v>
       </c>
       <c r="S202" t="n">
-        <v>187920</v>
+        <v>-44775</v>
       </c>
       <c r="T202" t="n">
-        <v>1751346</v>
+        <v>-64928</v>
       </c>
       <c r="U202" t="n">
-        <v>0</v>
+        <v>44000</v>
       </c>
       <c r="V202" t="n">
-        <v>0</v>
+        <v>38984</v>
       </c>
       <c r="W202" t="n">
-        <v>0</v>
+        <v>38948</v>
       </c>
       <c r="X202" t="n">
-        <v>0</v>
+        <v>154916</v>
       </c>
       <c r="Y202" t="n">
-        <v>4000</v>
+        <v>3308</v>
       </c>
       <c r="Z202" t="n">
-        <v>7000</v>
+        <v>-2072</v>
       </c>
       <c r="AA202" t="n">
-        <v>21378</v>
+        <v>4122</v>
       </c>
       <c r="AB202" t="n">
-        <v>33337</v>
+        <v>20566</v>
       </c>
       <c r="AC202" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AD202" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AE202" t="n">
-        <v>5</v>
+        <v>45</v>
       </c>
       <c r="AF202" t="n">
-        <v>20</v>
+        <v>-25</v>
       </c>
       <c r="AG202" t="n">
         <v>0</v>
@@ -28146,17 +28146,17 @@
       </c>
       <c r="AM202" t="inlineStr">
         <is>
-          <t>跌破5日線、多頭排列、量能溫和放大、接近20日低點</t>
+          <t>站上5日線、多頭排列、量能未放大</t>
         </is>
       </c>
       <c r="AN202" t="inlineStr">
         <is>
-          <t>5日法人買超</t>
+          <t>中期買超轉短線賣壓、投信買外資賣</t>
         </is>
       </c>
       <c r="AO202" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、多頭排列、量能溫和放大、接近20日低點、5日法人買超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、多頭排列、量能未放大、中期買超轉短線賣壓、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
@@ -28711,12 +28711,12 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>6409.TW</t>
+          <t>6121.TWO</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>旭隼</t>
+          <t>新普</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
@@ -28725,28 +28725,28 @@
         </is>
       </c>
       <c r="D207" t="n">
-        <v>1035</v>
+        <v>404</v>
       </c>
       <c r="E207" t="n">
-        <v>1032</v>
+        <v>403.2</v>
       </c>
       <c r="F207" t="n">
-        <v>1030</v>
+        <v>398.9</v>
       </c>
       <c r="G207" t="n">
-        <v>1012.2</v>
+        <v>399.93</v>
       </c>
       <c r="H207" t="n">
-        <v>322202</v>
+        <v>401000</v>
       </c>
       <c r="I207" t="n">
-        <v>400975</v>
+        <v>444800</v>
       </c>
       <c r="J207" t="n">
-        <v>1105</v>
+        <v>440</v>
       </c>
       <c r="K207" t="n">
-        <v>917</v>
+        <v>358</v>
       </c>
       <c r="L207" t="inlineStr">
         <is>
@@ -28754,52 +28754,52 @@
         </is>
       </c>
       <c r="M207" t="n">
-        <v>169</v>
+        <v>0</v>
       </c>
       <c r="N207" t="n">
-        <v>-101599</v>
+        <v>0</v>
       </c>
       <c r="O207" t="n">
-        <v>-1705</v>
+        <v>0</v>
       </c>
       <c r="P207" t="n">
-        <v>110554</v>
+        <v>0</v>
       </c>
       <c r="Q207" t="n">
-        <v>-47139</v>
+        <v>0</v>
       </c>
       <c r="R207" t="n">
-        <v>-138511</v>
+        <v>0</v>
       </c>
       <c r="S207" t="n">
-        <v>-44775</v>
+        <v>0</v>
       </c>
       <c r="T207" t="n">
-        <v>-64928</v>
+        <v>0</v>
       </c>
       <c r="U207" t="n">
-        <v>44000</v>
+        <v>0</v>
       </c>
       <c r="V207" t="n">
-        <v>38984</v>
+        <v>0</v>
       </c>
       <c r="W207" t="n">
-        <v>38948</v>
+        <v>0</v>
       </c>
       <c r="X207" t="n">
-        <v>154916</v>
+        <v>0</v>
       </c>
       <c r="Y207" t="n">
-        <v>3308</v>
+        <v>0</v>
       </c>
       <c r="Z207" t="n">
-        <v>-2072</v>
+        <v>0</v>
       </c>
       <c r="AA207" t="n">
-        <v>4122</v>
+        <v>0</v>
       </c>
       <c r="AB207" t="n">
-        <v>20566</v>
+        <v>0</v>
       </c>
       <c r="AC207" t="n">
         <v>8</v>
@@ -28808,10 +28808,10 @@
         <v>8</v>
       </c>
       <c r="AE207" t="n">
-        <v>45</v>
+        <v>20</v>
       </c>
       <c r="AF207" t="n">
-        <v>-25</v>
+        <v>0</v>
       </c>
       <c r="AG207" t="n">
         <v>0</v>
@@ -28831,17 +28831,17 @@
       </c>
       <c r="AM207" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、量能未放大</t>
+          <t>站上5日線、量能未放大</t>
         </is>
       </c>
       <c r="AN207" t="inlineStr">
         <is>
-          <t>中期買超轉短線賣壓、投信買外資賣</t>
+          <t>籌碼中性</t>
         </is>
       </c>
       <c r="AO207" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、多頭排列、量能未放大、中期買超轉短線賣壓、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、量能未放大、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
@@ -29122,12 +29122,12 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>6121.TWO</t>
+          <t>2542.TW</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>新普</t>
+          <t>興富發</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
@@ -29136,28 +29136,28 @@
         </is>
       </c>
       <c r="D210" t="n">
-        <v>404</v>
+        <v>46.65</v>
       </c>
       <c r="E210" t="n">
-        <v>403.2</v>
+        <v>47.38</v>
       </c>
       <c r="F210" t="n">
-        <v>398.9</v>
+        <v>47.82</v>
       </c>
       <c r="G210" t="n">
-        <v>399.93</v>
+        <v>46.39</v>
       </c>
       <c r="H210" t="n">
-        <v>401000</v>
+        <v>5554761</v>
       </c>
       <c r="I210" t="n">
-        <v>444800</v>
+        <v>5383836</v>
       </c>
       <c r="J210" t="n">
-        <v>440</v>
+        <v>49</v>
       </c>
       <c r="K210" t="n">
-        <v>358</v>
+        <v>43.45</v>
       </c>
       <c r="L210" t="inlineStr">
         <is>
@@ -29165,52 +29165,52 @@
         </is>
       </c>
       <c r="M210" t="n">
-        <v>0</v>
+        <v>-571253</v>
       </c>
       <c r="N210" t="n">
-        <v>0</v>
+        <v>-527777</v>
       </c>
       <c r="O210" t="n">
-        <v>0</v>
+        <v>2314699</v>
       </c>
       <c r="P210" t="n">
-        <v>0</v>
+        <v>28044863</v>
       </c>
       <c r="Q210" t="n">
-        <v>0</v>
+        <v>-1803408</v>
       </c>
       <c r="R210" t="n">
-        <v>0</v>
+        <v>-2184816</v>
       </c>
       <c r="S210" t="n">
-        <v>0</v>
+        <v>-771606</v>
       </c>
       <c r="T210" t="n">
-        <v>0</v>
+        <v>23724152</v>
       </c>
       <c r="U210" t="n">
-        <v>0</v>
+        <v>1016000</v>
       </c>
       <c r="V210" t="n">
-        <v>0</v>
+        <v>1017000</v>
       </c>
       <c r="W210" t="n">
-        <v>0</v>
+        <v>2585300</v>
       </c>
       <c r="X210" t="n">
-        <v>0</v>
+        <v>3656300</v>
       </c>
       <c r="Y210" t="n">
-        <v>0</v>
+        <v>216155</v>
       </c>
       <c r="Z210" t="n">
-        <v>0</v>
+        <v>640039</v>
       </c>
       <c r="AA210" t="n">
-        <v>0</v>
+        <v>501005</v>
       </c>
       <c r="AB210" t="n">
-        <v>0</v>
+        <v>664411</v>
       </c>
       <c r="AC210" t="n">
         <v>8</v>
@@ -29219,10 +29219,10 @@
         <v>8</v>
       </c>
       <c r="AE210" t="n">
-        <v>20</v>
+        <v>-10</v>
       </c>
       <c r="AF210" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AG210" t="n">
         <v>0</v>
@@ -29242,29 +29242,29 @@
       </c>
       <c r="AM210" t="inlineStr">
         <is>
-          <t>站上5日線、量能未放大</t>
+          <t>跌破5日線、量能溫和放大</t>
         </is>
       </c>
       <c r="AN210" t="inlineStr">
         <is>
-          <t>籌碼中性</t>
+          <t>5日法人明顯買超、投信買外資賣</t>
         </is>
       </c>
       <c r="AO210" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、量能未放大、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、量能溫和放大、5日法人明顯買超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>2542.TW</t>
+          <t>5483.TWO</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>興富發</t>
+          <t>中美晶</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
@@ -29273,28 +29273,28 @@
         </is>
       </c>
       <c r="D211" t="n">
-        <v>46.65</v>
+        <v>178</v>
       </c>
       <c r="E211" t="n">
-        <v>47.38</v>
+        <v>181.3</v>
       </c>
       <c r="F211" t="n">
-        <v>47.82</v>
+        <v>181.2</v>
       </c>
       <c r="G211" t="n">
-        <v>46.39</v>
+        <v>180.1</v>
       </c>
       <c r="H211" t="n">
-        <v>5554761</v>
+        <v>15765000</v>
       </c>
       <c r="I211" t="n">
-        <v>5383836</v>
+        <v>14784400</v>
       </c>
       <c r="J211" t="n">
-        <v>49</v>
+        <v>203</v>
       </c>
       <c r="K211" t="n">
-        <v>43.45</v>
+        <v>165</v>
       </c>
       <c r="L211" t="inlineStr">
         <is>
@@ -29302,64 +29302,64 @@
         </is>
       </c>
       <c r="M211" t="n">
-        <v>-571253</v>
+        <v>0</v>
       </c>
       <c r="N211" t="n">
-        <v>-527777</v>
+        <v>0</v>
       </c>
       <c r="O211" t="n">
-        <v>2314699</v>
+        <v>0</v>
       </c>
       <c r="P211" t="n">
-        <v>28044863</v>
+        <v>0</v>
       </c>
       <c r="Q211" t="n">
-        <v>-1803408</v>
+        <v>0</v>
       </c>
       <c r="R211" t="n">
-        <v>-2184816</v>
+        <v>0</v>
       </c>
       <c r="S211" t="n">
-        <v>-771606</v>
+        <v>0</v>
       </c>
       <c r="T211" t="n">
-        <v>23724152</v>
+        <v>0</v>
       </c>
       <c r="U211" t="n">
-        <v>1016000</v>
+        <v>0</v>
       </c>
       <c r="V211" t="n">
-        <v>1017000</v>
+        <v>0</v>
       </c>
       <c r="W211" t="n">
-        <v>2585300</v>
+        <v>0</v>
       </c>
       <c r="X211" t="n">
-        <v>3656300</v>
+        <v>0</v>
       </c>
       <c r="Y211" t="n">
-        <v>216155</v>
+        <v>0</v>
       </c>
       <c r="Z211" t="n">
-        <v>640039</v>
+        <v>0</v>
       </c>
       <c r="AA211" t="n">
-        <v>501005</v>
+        <v>0</v>
       </c>
       <c r="AB211" t="n">
-        <v>664411</v>
+        <v>0</v>
       </c>
       <c r="AC211" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AD211" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AE211" t="n">
-        <v>-10</v>
+        <v>15</v>
       </c>
       <c r="AF211" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="AG211" t="n">
         <v>0</v>
@@ -29379,17 +29379,17 @@
       </c>
       <c r="AM211" t="inlineStr">
         <is>
-          <t>跌破5日線、量能溫和放大</t>
+          <t>跌破5日線、多頭排列、量能溫和放大</t>
         </is>
       </c>
       <c r="AN211" t="inlineStr">
         <is>
-          <t>5日法人明顯買超、投信買外資賣</t>
+          <t>籌碼中性</t>
         </is>
       </c>
       <c r="AO211" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、量能溫和放大、5日法人明顯買超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、多頭排列、量能溫和放大、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
@@ -29533,12 +29533,12 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>2515.TW</t>
+          <t>2360.TW</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>中工</t>
+          <t>致茂</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
@@ -29547,28 +29547,28 @@
         </is>
       </c>
       <c r="D213" t="n">
-        <v>12.05</v>
+        <v>1960</v>
       </c>
       <c r="E213" t="n">
-        <v>12.01</v>
+        <v>1981</v>
       </c>
       <c r="F213" t="n">
-        <v>11.96</v>
+        <v>2064</v>
       </c>
       <c r="G213" t="n">
-        <v>11.96</v>
+        <v>2086</v>
       </c>
       <c r="H213" t="n">
-        <v>5904713</v>
+        <v>2334427</v>
       </c>
       <c r="I213" t="n">
-        <v>4891453</v>
+        <v>2277375</v>
       </c>
       <c r="J213" t="n">
-        <v>12.2</v>
+        <v>2400</v>
       </c>
       <c r="K213" t="n">
-        <v>11.7</v>
+        <v>1845</v>
       </c>
       <c r="L213" t="inlineStr">
         <is>
@@ -29576,52 +29576,52 @@
         </is>
       </c>
       <c r="M213" t="n">
-        <v>1012900</v>
+        <v>281256</v>
       </c>
       <c r="N213" t="n">
-        <v>-872886</v>
+        <v>238728</v>
       </c>
       <c r="O213" t="n">
-        <v>-195293</v>
+        <v>140665</v>
       </c>
       <c r="P213" t="n">
-        <v>7350571</v>
+        <v>-321928</v>
       </c>
       <c r="Q213" t="n">
-        <v>1016954</v>
+        <v>300416</v>
       </c>
       <c r="R213" t="n">
-        <v>-870374</v>
+        <v>540223</v>
       </c>
       <c r="S213" t="n">
-        <v>-268781</v>
+        <v>1343995</v>
       </c>
       <c r="T213" t="n">
-        <v>7378738</v>
+        <v>1990282</v>
       </c>
       <c r="U213" t="n">
-        <v>0</v>
+        <v>-33205</v>
       </c>
       <c r="V213" t="n">
-        <v>0</v>
+        <v>-334249</v>
       </c>
       <c r="W213" t="n">
-        <v>0</v>
+        <v>-1353186</v>
       </c>
       <c r="X213" t="n">
-        <v>-14000</v>
+        <v>-2455791</v>
       </c>
       <c r="Y213" t="n">
-        <v>-4054</v>
+        <v>14045</v>
       </c>
       <c r="Z213" t="n">
-        <v>-2512</v>
+        <v>32754</v>
       </c>
       <c r="AA213" t="n">
-        <v>73488</v>
+        <v>149856</v>
       </c>
       <c r="AB213" t="n">
-        <v>-14167</v>
+        <v>143581</v>
       </c>
       <c r="AC213" t="n">
         <v>6</v>
@@ -29630,10 +29630,10 @@
         <v>6</v>
       </c>
       <c r="AE213" t="n">
-        <v>60</v>
+        <v>-35</v>
       </c>
       <c r="AF213" t="n">
-        <v>-45</v>
+        <v>50</v>
       </c>
       <c r="AG213" t="n">
         <v>0</v>
@@ -29653,17 +29653,17 @@
       </c>
       <c r="AM213" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、量能溫和放大、接近20日高點、接近20日低點</t>
+          <t>跌破5日線、空頭排列、量能溫和放大</t>
         </is>
       </c>
       <c r="AN213" t="inlineStr">
         <is>
-          <t>中期買超轉短線賣壓、5日法人賣超</t>
+          <t>法人連續偏買、5日法人買超、外資買投信賣</t>
         </is>
       </c>
       <c r="AO213" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、多頭排列、量能溫和放大、接近20日高點、接近20日低點、中期買超轉短線賣壓、5日法人賣超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、空頭排列、量能溫和放大、法人連續偏買、5日法人買超、外資買投信賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
@@ -30355,12 +30355,12 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>5483.TWO</t>
+          <t>2515.TW</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>中美晶</t>
+          <t>中工</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
@@ -30369,28 +30369,28 @@
         </is>
       </c>
       <c r="D219" t="n">
-        <v>178</v>
+        <v>12.05</v>
       </c>
       <c r="E219" t="n">
-        <v>181.3</v>
+        <v>12.01</v>
       </c>
       <c r="F219" t="n">
-        <v>181.2</v>
+        <v>11.96</v>
       </c>
       <c r="G219" t="n">
-        <v>180.1</v>
+        <v>11.96</v>
       </c>
       <c r="H219" t="n">
-        <v>15765000</v>
+        <v>5904713</v>
       </c>
       <c r="I219" t="n">
-        <v>14784400</v>
+        <v>4891453</v>
       </c>
       <c r="J219" t="n">
-        <v>203</v>
+        <v>12.2</v>
       </c>
       <c r="K219" t="n">
-        <v>165</v>
+        <v>11.7</v>
       </c>
       <c r="L219" t="inlineStr">
         <is>
@@ -30398,28 +30398,28 @@
         </is>
       </c>
       <c r="M219" t="n">
-        <v>0</v>
+        <v>1012900</v>
       </c>
       <c r="N219" t="n">
-        <v>0</v>
+        <v>-872886</v>
       </c>
       <c r="O219" t="n">
-        <v>0</v>
+        <v>-195293</v>
       </c>
       <c r="P219" t="n">
-        <v>0</v>
+        <v>7350571</v>
       </c>
       <c r="Q219" t="n">
-        <v>0</v>
+        <v>1016954</v>
       </c>
       <c r="R219" t="n">
-        <v>0</v>
+        <v>-870374</v>
       </c>
       <c r="S219" t="n">
-        <v>0</v>
+        <v>-268781</v>
       </c>
       <c r="T219" t="n">
-        <v>0</v>
+        <v>7378738</v>
       </c>
       <c r="U219" t="n">
         <v>0</v>
@@ -30431,19 +30431,19 @@
         <v>0</v>
       </c>
       <c r="X219" t="n">
-        <v>0</v>
+        <v>-14000</v>
       </c>
       <c r="Y219" t="n">
-        <v>0</v>
+        <v>-4054</v>
       </c>
       <c r="Z219" t="n">
-        <v>0</v>
+        <v>-2512</v>
       </c>
       <c r="AA219" t="n">
-        <v>0</v>
+        <v>73488</v>
       </c>
       <c r="AB219" t="n">
-        <v>0</v>
+        <v>-14167</v>
       </c>
       <c r="AC219" t="n">
         <v>6</v>
@@ -30452,10 +30452,10 @@
         <v>6</v>
       </c>
       <c r="AE219" t="n">
-        <v>15</v>
+        <v>60</v>
       </c>
       <c r="AF219" t="n">
-        <v>0</v>
+        <v>-45</v>
       </c>
       <c r="AG219" t="n">
         <v>0</v>
@@ -30475,17 +30475,17 @@
       </c>
       <c r="AM219" t="inlineStr">
         <is>
-          <t>跌破5日線、多頭排列、量能溫和放大</t>
+          <t>站上5日線、多頭排列、量能溫和放大、接近20日高點、接近20日低點</t>
         </is>
       </c>
       <c r="AN219" t="inlineStr">
         <is>
-          <t>籌碼中性</t>
+          <t>中期買超轉短線賣壓、5日法人賣超</t>
         </is>
       </c>
       <c r="AO219" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、多頭排列、量能溫和放大、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、多頭排列、量能溫和放大、接近20日高點、接近20日低點、中期買超轉短線賣壓、5日法人賣超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
@@ -30629,12 +30629,12 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>2360.TW</t>
+          <t>2603.TW</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>致茂</t>
+          <t>長榮</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
@@ -30643,28 +30643,28 @@
         </is>
       </c>
       <c r="D221" t="n">
-        <v>1960</v>
+        <v>233.5</v>
       </c>
       <c r="E221" t="n">
-        <v>1981</v>
+        <v>234.9</v>
       </c>
       <c r="F221" t="n">
-        <v>2064</v>
+        <v>240.1</v>
       </c>
       <c r="G221" t="n">
-        <v>2086</v>
+        <v>226.8</v>
       </c>
       <c r="H221" t="n">
-        <v>2334427</v>
+        <v>10805315</v>
       </c>
       <c r="I221" t="n">
-        <v>2277375</v>
+        <v>18473202</v>
       </c>
       <c r="J221" t="n">
-        <v>2400</v>
+        <v>256.5</v>
       </c>
       <c r="K221" t="n">
-        <v>1845</v>
+        <v>202</v>
       </c>
       <c r="L221" t="inlineStr">
         <is>
@@ -30672,64 +30672,64 @@
         </is>
       </c>
       <c r="M221" t="n">
-        <v>281256</v>
+        <v>-261121</v>
       </c>
       <c r="N221" t="n">
-        <v>238728</v>
+        <v>1552164</v>
       </c>
       <c r="O221" t="n">
-        <v>140665</v>
+        <v>5744942</v>
       </c>
       <c r="P221" t="n">
-        <v>-321928</v>
+        <v>62783231</v>
       </c>
       <c r="Q221" t="n">
-        <v>300416</v>
+        <v>-289998</v>
       </c>
       <c r="R221" t="n">
-        <v>540223</v>
+        <v>6510228</v>
       </c>
       <c r="S221" t="n">
-        <v>1343995</v>
+        <v>13401384</v>
       </c>
       <c r="T221" t="n">
-        <v>1990282</v>
+        <v>69983286</v>
       </c>
       <c r="U221" t="n">
-        <v>-33205</v>
+        <v>202984</v>
       </c>
       <c r="V221" t="n">
-        <v>-334249</v>
+        <v>-5044014</v>
       </c>
       <c r="W221" t="n">
-        <v>-1353186</v>
+        <v>-5710272</v>
       </c>
       <c r="X221" t="n">
-        <v>-2455791</v>
+        <v>-4836890</v>
       </c>
       <c r="Y221" t="n">
-        <v>14045</v>
+        <v>-174107</v>
       </c>
       <c r="Z221" t="n">
-        <v>32754</v>
+        <v>85950</v>
       </c>
       <c r="AA221" t="n">
-        <v>149856</v>
+        <v>-1946170</v>
       </c>
       <c r="AB221" t="n">
-        <v>143581</v>
+        <v>-2363165</v>
       </c>
       <c r="AC221" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AD221" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AE221" t="n">
-        <v>-35</v>
+        <v>-20</v>
       </c>
       <c r="AF221" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="AG221" t="n">
         <v>0</v>
@@ -30749,17 +30749,17 @@
       </c>
       <c r="AM221" t="inlineStr">
         <is>
-          <t>跌破5日線、空頭排列、量能溫和放大</t>
+          <t>跌破5日線、量能未放大</t>
         </is>
       </c>
       <c r="AN221" t="inlineStr">
         <is>
-          <t>法人連續偏買、5日法人買超、外資買投信賣</t>
+          <t>5日法人明顯買超、外資買投信賣</t>
         </is>
       </c>
       <c r="AO221" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、空頭排列、量能溫和放大、法人連續偏買、5日法人買超、外資買投信賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、量能未放大、5日法人明顯買超、外資買投信賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
@@ -30903,12 +30903,12 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>2603.TW</t>
+          <t>2908.TW</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>長榮</t>
+          <t>特力</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
@@ -30917,28 +30917,28 @@
         </is>
       </c>
       <c r="D223" t="n">
-        <v>233.5</v>
+        <v>21.9</v>
       </c>
       <c r="E223" t="n">
-        <v>234.9</v>
+        <v>21.98</v>
       </c>
       <c r="F223" t="n">
-        <v>240.1</v>
+        <v>21.9</v>
       </c>
       <c r="G223" t="n">
-        <v>226.8</v>
+        <v>21.84</v>
       </c>
       <c r="H223" t="n">
-        <v>10805315</v>
+        <v>251357</v>
       </c>
       <c r="I223" t="n">
-        <v>18473202</v>
+        <v>220617</v>
       </c>
       <c r="J223" t="n">
-        <v>256.5</v>
+        <v>22.6</v>
       </c>
       <c r="K223" t="n">
-        <v>202</v>
+        <v>21.35</v>
       </c>
       <c r="L223" t="inlineStr">
         <is>
@@ -30946,64 +30946,64 @@
         </is>
       </c>
       <c r="M223" t="n">
-        <v>-261121</v>
+        <v>-29113</v>
       </c>
       <c r="N223" t="n">
-        <v>1552164</v>
+        <v>-82113</v>
       </c>
       <c r="O223" t="n">
-        <v>5744942</v>
+        <v>17375</v>
       </c>
       <c r="P223" t="n">
-        <v>62783231</v>
+        <v>56375</v>
       </c>
       <c r="Q223" t="n">
-        <v>-289998</v>
+        <v>-28113</v>
       </c>
       <c r="R223" t="n">
-        <v>6510228</v>
+        <v>-47113</v>
       </c>
       <c r="S223" t="n">
-        <v>13401384</v>
+        <v>47375</v>
       </c>
       <c r="T223" t="n">
-        <v>69983286</v>
+        <v>51375</v>
       </c>
       <c r="U223" t="n">
-        <v>202984</v>
+        <v>0</v>
       </c>
       <c r="V223" t="n">
-        <v>-5044014</v>
+        <v>0</v>
       </c>
       <c r="W223" t="n">
-        <v>-5710272</v>
+        <v>0</v>
       </c>
       <c r="X223" t="n">
-        <v>-4836890</v>
+        <v>0</v>
       </c>
       <c r="Y223" t="n">
-        <v>-174107</v>
+        <v>-1000</v>
       </c>
       <c r="Z223" t="n">
-        <v>85950</v>
+        <v>-35000</v>
       </c>
       <c r="AA223" t="n">
-        <v>-1946170</v>
+        <v>-30000</v>
       </c>
       <c r="AB223" t="n">
-        <v>-2363165</v>
+        <v>5000</v>
       </c>
       <c r="AC223" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AD223" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AE223" t="n">
-        <v>-20</v>
+        <v>5</v>
       </c>
       <c r="AF223" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="AG223" t="n">
         <v>0</v>
@@ -31023,29 +31023,29 @@
       </c>
       <c r="AM223" t="inlineStr">
         <is>
-          <t>跌破5日線、量能未放大</t>
+          <t>跌破5日線、多頭排列、量能溫和放大、接近20日低點</t>
         </is>
       </c>
       <c r="AN223" t="inlineStr">
         <is>
-          <t>5日法人明顯買超、外資買投信賣</t>
+          <t>籌碼中性</t>
         </is>
       </c>
       <c r="AO223" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、量能未放大、5日法人明顯買超、外資買投信賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、多頭排列、量能溫和放大、接近20日低點、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>2908.TW</t>
+          <t>3260.TWO</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>特力</t>
+          <t>威剛</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
@@ -31054,28 +31054,28 @@
         </is>
       </c>
       <c r="D224" t="n">
-        <v>21.9</v>
+        <v>413.5</v>
       </c>
       <c r="E224" t="n">
-        <v>21.98</v>
+        <v>415.1</v>
       </c>
       <c r="F224" t="n">
-        <v>21.9</v>
+        <v>411.95</v>
       </c>
       <c r="G224" t="n">
-        <v>21.84</v>
+        <v>409.4</v>
       </c>
       <c r="H224" t="n">
-        <v>251357</v>
+        <v>4711000</v>
       </c>
       <c r="I224" t="n">
-        <v>220617</v>
+        <v>8588600</v>
       </c>
       <c r="J224" t="n">
-        <v>22.6</v>
+        <v>459.5</v>
       </c>
       <c r="K224" t="n">
-        <v>21.35</v>
+        <v>375</v>
       </c>
       <c r="L224" t="inlineStr">
         <is>
@@ -31083,28 +31083,28 @@
         </is>
       </c>
       <c r="M224" t="n">
-        <v>-29113</v>
+        <v>0</v>
       </c>
       <c r="N224" t="n">
-        <v>-82113</v>
+        <v>0</v>
       </c>
       <c r="O224" t="n">
-        <v>17375</v>
+        <v>0</v>
       </c>
       <c r="P224" t="n">
-        <v>56375</v>
+        <v>0</v>
       </c>
       <c r="Q224" t="n">
-        <v>-28113</v>
+        <v>0</v>
       </c>
       <c r="R224" t="n">
-        <v>-47113</v>
+        <v>0</v>
       </c>
       <c r="S224" t="n">
-        <v>47375</v>
+        <v>0</v>
       </c>
       <c r="T224" t="n">
-        <v>51375</v>
+        <v>0</v>
       </c>
       <c r="U224" t="n">
         <v>0</v>
@@ -31119,16 +31119,16 @@
         <v>0</v>
       </c>
       <c r="Y224" t="n">
-        <v>-1000</v>
+        <v>0</v>
       </c>
       <c r="Z224" t="n">
-        <v>-35000</v>
+        <v>0</v>
       </c>
       <c r="AA224" t="n">
-        <v>-30000</v>
+        <v>0</v>
       </c>
       <c r="AB224" t="n">
-        <v>5000</v>
+        <v>0</v>
       </c>
       <c r="AC224" t="n">
         <v>2</v>
@@ -31160,7 +31160,7 @@
       </c>
       <c r="AM224" t="inlineStr">
         <is>
-          <t>跌破5日線、多頭排列、量能溫和放大、接近20日低點</t>
+          <t>跌破5日線、多頭排列、量能未放大</t>
         </is>
       </c>
       <c r="AN224" t="inlineStr">
@@ -31170,7 +31170,7 @@
       </c>
       <c r="AO224" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、多頭排列、量能溫和放大、接近20日低點、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、多頭排列、量能未放大、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>

--- a/output/universe_analysis_result.xlsx
+++ b/output/universe_analysis_result.xlsx
@@ -1148,16 +1148,16 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>15083127</v>
+        <v>15056127</v>
       </c>
       <c r="N5" t="n">
-        <v>15299445</v>
+        <v>15272445</v>
       </c>
       <c r="O5" t="n">
-        <v>24235551</v>
+        <v>24208551</v>
       </c>
       <c r="P5" t="n">
-        <v>33383131</v>
+        <v>33356131</v>
       </c>
       <c r="Q5" t="n">
         <v>14303460</v>
@@ -1172,16 +1172,16 @@
         <v>26523362</v>
       </c>
       <c r="U5" t="n">
-        <v>192000</v>
+        <v>165000</v>
       </c>
       <c r="V5" t="n">
-        <v>3273577</v>
+        <v>3246577</v>
       </c>
       <c r="W5" t="n">
-        <v>7047039</v>
+        <v>7020039</v>
       </c>
       <c r="X5" t="n">
-        <v>7078460</v>
+        <v>7051460</v>
       </c>
       <c r="Y5" t="n">
         <v>587667</v>
@@ -1607,16 +1607,16 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>2551323</v>
+        <v>2560323</v>
       </c>
       <c r="N8" t="n">
-        <v>3853021</v>
+        <v>3862021</v>
       </c>
       <c r="O8" t="n">
-        <v>7783384</v>
+        <v>7792384</v>
       </c>
       <c r="P8" t="n">
-        <v>9574886</v>
+        <v>9583886</v>
       </c>
       <c r="Q8" t="n">
         <v>2385514</v>
@@ -1631,16 +1631,16 @@
         <v>7250841</v>
       </c>
       <c r="U8" t="n">
-        <v>104722</v>
+        <v>113722</v>
       </c>
       <c r="V8" t="n">
-        <v>893431</v>
+        <v>902431</v>
       </c>
       <c r="W8" t="n">
-        <v>2409481</v>
+        <v>2418481</v>
       </c>
       <c r="X8" t="n">
-        <v>2374995</v>
+        <v>2383995</v>
       </c>
       <c r="Y8" t="n">
         <v>61087</v>
@@ -3749,16 +3749,16 @@
         </is>
       </c>
       <c r="M22" t="n">
-        <v>4560193</v>
+        <v>5301193</v>
       </c>
       <c r="N22" t="n">
-        <v>5318057</v>
+        <v>6059057</v>
       </c>
       <c r="O22" t="n">
-        <v>13600675</v>
+        <v>14341675</v>
       </c>
       <c r="P22" t="n">
-        <v>32346786</v>
+        <v>33087786</v>
       </c>
       <c r="Q22" t="n">
         <v>3876584</v>
@@ -3773,16 +3773,16 @@
         <v>17264269</v>
       </c>
       <c r="U22" t="n">
-        <v>45000</v>
+        <v>786000</v>
       </c>
       <c r="V22" t="n">
-        <v>1506000</v>
+        <v>2247000</v>
       </c>
       <c r="W22" t="n">
-        <v>7152000</v>
+        <v>7893000</v>
       </c>
       <c r="X22" t="n">
-        <v>13785000</v>
+        <v>14526000</v>
       </c>
       <c r="Y22" t="n">
         <v>638609</v>
@@ -3902,16 +3902,16 @@
         </is>
       </c>
       <c r="M23" t="n">
-        <v>27681004</v>
+        <v>27727004</v>
       </c>
       <c r="N23" t="n">
-        <v>59393083</v>
+        <v>59439083</v>
       </c>
       <c r="O23" t="n">
-        <v>58801114</v>
+        <v>58847114</v>
       </c>
       <c r="P23" t="n">
-        <v>33392278</v>
+        <v>33438278</v>
       </c>
       <c r="Q23" t="n">
         <v>23925305</v>
@@ -3926,16 +3926,16 @@
         <v>5179388</v>
       </c>
       <c r="U23" t="n">
-        <v>3389000</v>
+        <v>3435000</v>
       </c>
       <c r="V23" t="n">
-        <v>24518800</v>
+        <v>24564800</v>
       </c>
       <c r="W23" t="n">
-        <v>26872535</v>
+        <v>26918535</v>
       </c>
       <c r="X23" t="n">
-        <v>27052180</v>
+        <v>27098180</v>
       </c>
       <c r="Y23" t="n">
         <v>366699</v>
@@ -6197,16 +6197,16 @@
         </is>
       </c>
       <c r="M38" t="n">
-        <v>396407</v>
+        <v>365407</v>
       </c>
       <c r="N38" t="n">
-        <v>7498325</v>
+        <v>7467325</v>
       </c>
       <c r="O38" t="n">
-        <v>10777840</v>
+        <v>10746840</v>
       </c>
       <c r="P38" t="n">
-        <v>17221739</v>
+        <v>17190739</v>
       </c>
       <c r="Q38" t="n">
         <v>1267333</v>
@@ -6221,16 +6221,16 @@
         <v>12782858</v>
       </c>
       <c r="U38" t="n">
-        <v>-67000</v>
+        <v>-98000</v>
       </c>
       <c r="V38" t="n">
-        <v>2067000</v>
+        <v>2036000</v>
       </c>
       <c r="W38" t="n">
-        <v>4104000</v>
+        <v>4073000</v>
       </c>
       <c r="X38" t="n">
-        <v>4019000</v>
+        <v>3988000</v>
       </c>
       <c r="Y38" t="n">
         <v>-803926</v>
@@ -9716,16 +9716,16 @@
         </is>
       </c>
       <c r="M61" t="n">
-        <v>28933250</v>
+        <v>28923250</v>
       </c>
       <c r="N61" t="n">
-        <v>17380642</v>
+        <v>17370642</v>
       </c>
       <c r="O61" t="n">
-        <v>28432561</v>
+        <v>28422561</v>
       </c>
       <c r="P61" t="n">
-        <v>24059850</v>
+        <v>24049850</v>
       </c>
       <c r="Q61" t="n">
         <v>26407791</v>
@@ -9740,16 +9740,16 @@
         <v>19588441</v>
       </c>
       <c r="U61" t="n">
-        <v>1155278</v>
+        <v>1145278</v>
       </c>
       <c r="V61" t="n">
-        <v>1119542</v>
+        <v>1109542</v>
       </c>
       <c r="W61" t="n">
-        <v>1984879</v>
+        <v>1974879</v>
       </c>
       <c r="X61" t="n">
-        <v>1801127</v>
+        <v>1791127</v>
       </c>
       <c r="Y61" t="n">
         <v>1370181</v>
@@ -11858,16 +11858,16 @@
         </is>
       </c>
       <c r="M75" t="n">
-        <v>987357</v>
+        <v>977157</v>
       </c>
       <c r="N75" t="n">
-        <v>2365903</v>
+        <v>2355703</v>
       </c>
       <c r="O75" t="n">
-        <v>1317233</v>
+        <v>1307033</v>
       </c>
       <c r="P75" t="n">
-        <v>3244005</v>
+        <v>3233805</v>
       </c>
       <c r="Q75" t="n">
         <v>534504</v>
@@ -11882,16 +11882,16 @@
         <v>1896669</v>
       </c>
       <c r="U75" t="n">
-        <v>349561</v>
+        <v>339361</v>
       </c>
       <c r="V75" t="n">
-        <v>1655707</v>
+        <v>1645507</v>
       </c>
       <c r="W75" t="n">
-        <v>1323712</v>
+        <v>1313512</v>
       </c>
       <c r="X75" t="n">
-        <v>716702</v>
+        <v>706502</v>
       </c>
       <c r="Y75" t="n">
         <v>103292</v>
@@ -16754,16 +16754,16 @@
         </is>
       </c>
       <c r="M107" t="n">
-        <v>306415</v>
+        <v>303653</v>
       </c>
       <c r="N107" t="n">
-        <v>913528</v>
+        <v>910766</v>
       </c>
       <c r="O107" t="n">
-        <v>879407</v>
+        <v>876645</v>
       </c>
       <c r="P107" t="n">
-        <v>467728</v>
+        <v>464966</v>
       </c>
       <c r="Q107" t="n">
         <v>294436</v>
@@ -16778,16 +16778,16 @@
         <v>126658</v>
       </c>
       <c r="U107" t="n">
-        <v>9000</v>
+        <v>6238</v>
       </c>
       <c r="V107" t="n">
-        <v>130920</v>
+        <v>128158</v>
       </c>
       <c r="W107" t="n">
-        <v>395438</v>
+        <v>392676</v>
       </c>
       <c r="X107" t="n">
-        <v>402606</v>
+        <v>399844</v>
       </c>
       <c r="Y107" t="n">
         <v>2979</v>
@@ -19049,16 +19049,16 @@
         </is>
       </c>
       <c r="M122" t="n">
-        <v>595182</v>
+        <v>588274</v>
       </c>
       <c r="N122" t="n">
-        <v>751394</v>
+        <v>744486</v>
       </c>
       <c r="O122" t="n">
-        <v>729870</v>
+        <v>722962</v>
       </c>
       <c r="P122" t="n">
-        <v>-311989</v>
+        <v>-318897</v>
       </c>
       <c r="Q122" t="n">
         <v>527180</v>
@@ -19073,16 +19073,16 @@
         <v>-688216</v>
       </c>
       <c r="U122" t="n">
-        <v>58000</v>
+        <v>51092</v>
       </c>
       <c r="V122" t="n">
-        <v>106000</v>
+        <v>99092</v>
       </c>
       <c r="W122" t="n">
-        <v>244000</v>
+        <v>237092</v>
       </c>
       <c r="X122" t="n">
-        <v>296000</v>
+        <v>289092</v>
       </c>
       <c r="Y122" t="n">
         <v>10002</v>
@@ -32666,16 +32666,16 @@
         </is>
       </c>
       <c r="M211" t="n">
-        <v>1963801</v>
+        <v>1969801</v>
       </c>
       <c r="N211" t="n">
-        <v>-11785765</v>
+        <v>-11779765</v>
       </c>
       <c r="O211" t="n">
-        <v>-11514834</v>
+        <v>-11508834</v>
       </c>
       <c r="P211" t="n">
-        <v>-2524675</v>
+        <v>-2518675</v>
       </c>
       <c r="Q211" t="n">
         <v>1885085</v>
@@ -32690,16 +32690,16 @@
         <v>78700</v>
       </c>
       <c r="U211" t="n">
-        <v>-328024</v>
+        <v>-322024</v>
       </c>
       <c r="V211" t="n">
-        <v>-1113437</v>
+        <v>-1107437</v>
       </c>
       <c r="W211" t="n">
-        <v>-1970698</v>
+        <v>-1964698</v>
       </c>
       <c r="X211" t="n">
-        <v>-3758047</v>
+        <v>-3752047</v>
       </c>
       <c r="Y211" t="n">
         <v>406740</v>
@@ -34961,16 +34961,16 @@
         </is>
       </c>
       <c r="M226" t="n">
-        <v>27289660</v>
+        <v>28186660</v>
       </c>
       <c r="N226" t="n">
-        <v>-5078612</v>
+        <v>-4181612</v>
       </c>
       <c r="O226" t="n">
-        <v>-32705561</v>
+        <v>-31808561</v>
       </c>
       <c r="P226" t="n">
-        <v>3275154</v>
+        <v>4172154</v>
       </c>
       <c r="Q226" t="n">
         <v>26550699</v>
@@ -34985,16 +34985,16 @@
         <v>-11813314</v>
       </c>
       <c r="U226" t="n">
-        <v>1577000</v>
+        <v>2474000</v>
       </c>
       <c r="V226" t="n">
-        <v>-9919689</v>
+        <v>-9022689</v>
       </c>
       <c r="W226" t="n">
-        <v>7519327</v>
+        <v>8416327</v>
       </c>
       <c r="X226" t="n">
-        <v>5747887</v>
+        <v>6644887</v>
       </c>
       <c r="Y226" t="n">
         <v>-838039</v>
@@ -40775,16 +40775,16 @@
         </is>
       </c>
       <c r="M264" t="n">
-        <v>1895987</v>
+        <v>1794987</v>
       </c>
       <c r="N264" t="n">
-        <v>-4041170</v>
+        <v>-4142170</v>
       </c>
       <c r="O264" t="n">
-        <v>-4101256</v>
+        <v>-4202256</v>
       </c>
       <c r="P264" t="n">
-        <v>-6485726</v>
+        <v>-6586726</v>
       </c>
       <c r="Q264" t="n">
         <v>1406988</v>
@@ -40799,16 +40799,16 @@
         <v>-3489944</v>
       </c>
       <c r="U264" t="n">
-        <v>365940</v>
+        <v>264940</v>
       </c>
       <c r="V264" t="n">
-        <v>-527658</v>
+        <v>-628658</v>
       </c>
       <c r="W264" t="n">
-        <v>-493082</v>
+        <v>-594082</v>
       </c>
       <c r="X264" t="n">
-        <v>-3821272</v>
+        <v>-3922272</v>
       </c>
       <c r="Y264" t="n">
         <v>123059</v>
@@ -44447,16 +44447,16 @@
         </is>
       </c>
       <c r="M288" t="n">
-        <v>18739425</v>
+        <v>18745425</v>
       </c>
       <c r="N288" t="n">
-        <v>-5945499</v>
+        <v>-5939499</v>
       </c>
       <c r="O288" t="n">
-        <v>-17125732</v>
+        <v>-17119732</v>
       </c>
       <c r="P288" t="n">
-        <v>-28789323</v>
+        <v>-28783323</v>
       </c>
       <c r="Q288" t="n">
         <v>18525832</v>
@@ -44471,16 +44471,16 @@
         <v>-8209045</v>
       </c>
       <c r="U288" t="n">
-        <v>-48000</v>
+        <v>-42000</v>
       </c>
       <c r="V288" t="n">
-        <v>-2411966</v>
+        <v>-2405966</v>
       </c>
       <c r="W288" t="n">
-        <v>-10184182</v>
+        <v>-10178182</v>
       </c>
       <c r="X288" t="n">
-        <v>-21897300</v>
+        <v>-21891300</v>
       </c>
       <c r="Y288" t="n">
         <v>261593</v>
@@ -53168,16 +53168,16 @@
         </is>
       </c>
       <c r="M345" t="n">
-        <v>1780</v>
+        <v>11280</v>
       </c>
       <c r="N345" t="n">
-        <v>-251430</v>
+        <v>-241930</v>
       </c>
       <c r="O345" t="n">
-        <v>-225652</v>
+        <v>-216152</v>
       </c>
       <c r="P345" t="n">
-        <v>-151637</v>
+        <v>-142137</v>
       </c>
       <c r="Q345" t="n">
         <v>2023</v>
@@ -53192,16 +53192,16 @@
         <v>-245709</v>
       </c>
       <c r="U345" t="n">
-        <v>4970</v>
+        <v>14470</v>
       </c>
       <c r="V345" t="n">
-        <v>46954</v>
+        <v>56454</v>
       </c>
       <c r="W345" t="n">
-        <v>91856</v>
+        <v>101356</v>
       </c>
       <c r="X345" t="n">
-        <v>100804</v>
+        <v>110304</v>
       </c>
       <c r="Y345" t="n">
         <v>-5213</v>
@@ -54392,16 +54392,16 @@
         </is>
       </c>
       <c r="M353" t="n">
-        <v>-19927300</v>
+        <v>-19937676</v>
       </c>
       <c r="N353" t="n">
-        <v>-39627408</v>
+        <v>-39637784</v>
       </c>
       <c r="O353" t="n">
-        <v>-14107607</v>
+        <v>-14117983</v>
       </c>
       <c r="P353" t="n">
-        <v>-37494008</v>
+        <v>-37504384</v>
       </c>
       <c r="Q353" t="n">
         <v>-19378086</v>
@@ -54416,16 +54416,16 @@
         <v>-26792198</v>
       </c>
       <c r="U353" t="n">
-        <v>-377940</v>
+        <v>-388316</v>
       </c>
       <c r="V353" t="n">
-        <v>-4963680</v>
+        <v>-4974056</v>
       </c>
       <c r="W353" t="n">
-        <v>-11075541</v>
+        <v>-11085917</v>
       </c>
       <c r="X353" t="n">
-        <v>-11129521</v>
+        <v>-11139897</v>
       </c>
       <c r="Y353" t="n">
         <v>-171274</v>
@@ -56687,16 +56687,16 @@
         </is>
       </c>
       <c r="M368" t="n">
-        <v>-1015961</v>
+        <v>-1234961</v>
       </c>
       <c r="N368" t="n">
-        <v>-39420882</v>
+        <v>-39639882</v>
       </c>
       <c r="O368" t="n">
-        <v>-74150482</v>
+        <v>-74369482</v>
       </c>
       <c r="P368" t="n">
-        <v>-53774298</v>
+        <v>-53993298</v>
       </c>
       <c r="Q368" t="n">
         <v>429943</v>
@@ -56711,16 +56711,16 @@
         <v>-43638138</v>
       </c>
       <c r="U368" t="n">
-        <v>-1735000</v>
+        <v>-1954000</v>
       </c>
       <c r="V368" t="n">
-        <v>-4131744</v>
+        <v>-4350744</v>
       </c>
       <c r="W368" t="n">
-        <v>-5402176</v>
+        <v>-5621176</v>
       </c>
       <c r="X368" t="n">
-        <v>-5207913</v>
+        <v>-5426913</v>
       </c>
       <c r="Y368" t="n">
         <v>289096</v>
@@ -57911,16 +57911,16 @@
         </is>
       </c>
       <c r="M376" t="n">
-        <v>1712683</v>
+        <v>957683</v>
       </c>
       <c r="N376" t="n">
-        <v>-6682746</v>
+        <v>-7437746</v>
       </c>
       <c r="O376" t="n">
-        <v>-7371046</v>
+        <v>-8126046</v>
       </c>
       <c r="P376" t="n">
-        <v>-9497987</v>
+        <v>-10252987</v>
       </c>
       <c r="Q376" t="n">
         <v>2022145</v>
@@ -57935,16 +57935,16 @@
         <v>-6839693</v>
       </c>
       <c r="U376" t="n">
-        <v>-408000</v>
+        <v>-1163000</v>
       </c>
       <c r="V376" t="n">
-        <v>-3378118</v>
+        <v>-4133118</v>
       </c>
       <c r="W376" t="n">
-        <v>-4116118</v>
+        <v>-4871118</v>
       </c>
       <c r="X376" t="n">
-        <v>-2059373</v>
+        <v>-2814373</v>
       </c>
       <c r="Y376" t="n">
         <v>98538</v>

--- a/output/universe_analysis_result.xlsx
+++ b/output/universe_analysis_result.xlsx
@@ -17782,42 +17782,42 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>00757.TW</t>
+          <t>4919.TW</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>統一FANG+</t>
+          <t>新唐</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>ETF</t>
+          <t>個股</t>
         </is>
       </c>
       <c r="D114" t="n">
-        <v>139.9</v>
+        <v>122.5</v>
       </c>
       <c r="E114" t="n">
-        <v>139.44</v>
+        <v>120.4</v>
       </c>
       <c r="F114" t="n">
-        <v>138.83</v>
+        <v>120.45</v>
       </c>
       <c r="G114" t="n">
-        <v>138.95</v>
+        <v>120.65</v>
       </c>
       <c r="H114" t="n">
-        <v>615612</v>
+        <v>3275935</v>
       </c>
       <c r="I114" t="n">
-        <v>545451</v>
+        <v>2301016</v>
       </c>
       <c r="J114" t="n">
-        <v>142.35</v>
+        <v>131.5</v>
       </c>
       <c r="K114" t="n">
-        <v>136.2</v>
+        <v>111</v>
       </c>
       <c r="L114" t="inlineStr">
         <is>
@@ -17825,28 +17825,28 @@
         </is>
       </c>
       <c r="M114" t="n">
-        <v>-375126</v>
+        <v>-28337</v>
       </c>
       <c r="N114" t="n">
-        <v>268746</v>
+        <v>338601</v>
       </c>
       <c r="O114" t="n">
-        <v>395647</v>
+        <v>690912</v>
       </c>
       <c r="P114" t="n">
-        <v>1324588</v>
+        <v>1165214</v>
       </c>
       <c r="Q114" t="n">
-        <v>-7062</v>
+        <v>-174815</v>
       </c>
       <c r="R114" t="n">
-        <v>66921</v>
+        <v>313915</v>
       </c>
       <c r="S114" t="n">
-        <v>68099</v>
+        <v>633801</v>
       </c>
       <c r="T114" t="n">
-        <v>234886</v>
+        <v>1078492</v>
       </c>
       <c r="U114" t="n">
         <v>0</v>
@@ -17855,22 +17855,22 @@
         <v>0</v>
       </c>
       <c r="W114" t="n">
-        <v>0</v>
+        <v>4000</v>
       </c>
       <c r="X114" t="n">
-        <v>0</v>
+        <v>-7089</v>
       </c>
       <c r="Y114" t="n">
-        <v>-368064</v>
+        <v>146478</v>
       </c>
       <c r="Z114" t="n">
-        <v>201825</v>
+        <v>24686</v>
       </c>
       <c r="AA114" t="n">
-        <v>327548</v>
+        <v>53111</v>
       </c>
       <c r="AB114" t="n">
-        <v>1089702</v>
+        <v>93811</v>
       </c>
       <c r="AC114" t="n">
         <v>22</v>
@@ -17879,10 +17879,10 @@
         <v>22</v>
       </c>
       <c r="AE114" t="n">
-        <v>35</v>
+        <v>5</v>
       </c>
       <c r="AF114" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="AG114" t="n">
         <v>0</v>
@@ -17891,19 +17891,19 @@
       <c r="AI114" t="inlineStr"/>
       <c r="AJ114" t="inlineStr"/>
       <c r="AK114" t="n">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="AL114" t="n">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="AM114" t="inlineStr">
         <is>
-          <t>偏高或條件不足</t>
+          <t>等待拉回確認</t>
         </is>
       </c>
       <c r="AN114" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA、位於20日區間中上緣</t>
+          <t>DT尚未轉強、貼近5MA、位於20日區間中上緣、量能溫和放大</t>
         </is>
       </c>
       <c r="AO114" t="inlineStr">
@@ -17918,59 +17918,59 @@
       </c>
       <c r="AQ114" t="inlineStr">
         <is>
-          <t>站上5日線、量能溫和放大、接近20日高點、接近20日低點</t>
+          <t>站上5日線、空頭排列、量能溫和放大</t>
         </is>
       </c>
       <c r="AR114" t="inlineStr">
         <is>
-          <t>5日法人買超</t>
+          <t>5日法人明顯買超、外資投信同步買超</t>
         </is>
       </c>
       <c r="AS114" t="inlineStr">
         <is>
-          <t>整理觀察：站上5日線、量能溫和放大、接近20日高點、接近20日低點、5日法人買超。多空訊號混合，建議降低追價衝動。</t>
+          <t>整理觀察：站上5日線、空頭排列、量能溫和放大、5日法人明顯買超、外資投信同步買超。多空訊號混合，建議降低追價衝動。</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>6510.TWO</t>
+          <t>00757.TW</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>精測</t>
+          <t>統一FANG+</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>個股</t>
+          <t>ETF</t>
         </is>
       </c>
       <c r="D115" t="n">
-        <v>3470</v>
+        <v>139.9</v>
       </c>
       <c r="E115" t="n">
-        <v>3346</v>
+        <v>139.44</v>
       </c>
       <c r="F115" t="n">
-        <v>3029.5</v>
+        <v>138.83</v>
       </c>
       <c r="G115" t="n">
-        <v>2904.75</v>
+        <v>138.95</v>
       </c>
       <c r="H115" t="n">
-        <v>1561000</v>
+        <v>615612</v>
       </c>
       <c r="I115" t="n">
-        <v>1493600</v>
+        <v>545451</v>
       </c>
       <c r="J115" t="n">
-        <v>3645</v>
+        <v>142.35</v>
       </c>
       <c r="K115" t="n">
-        <v>2570</v>
+        <v>136.2</v>
       </c>
       <c r="L115" t="inlineStr">
         <is>
@@ -17978,28 +17978,28 @@
         </is>
       </c>
       <c r="M115" t="n">
-        <v>0</v>
+        <v>-375126</v>
       </c>
       <c r="N115" t="n">
-        <v>0</v>
+        <v>268746</v>
       </c>
       <c r="O115" t="n">
-        <v>0</v>
+        <v>395647</v>
       </c>
       <c r="P115" t="n">
-        <v>0</v>
+        <v>1324588</v>
       </c>
       <c r="Q115" t="n">
-        <v>0</v>
+        <v>-7062</v>
       </c>
       <c r="R115" t="n">
-        <v>0</v>
+        <v>66921</v>
       </c>
       <c r="S115" t="n">
-        <v>0</v>
+        <v>68099</v>
       </c>
       <c r="T115" t="n">
-        <v>0</v>
+        <v>234886</v>
       </c>
       <c r="U115" t="n">
         <v>0</v>
@@ -18014,16 +18014,16 @@
         <v>0</v>
       </c>
       <c r="Y115" t="n">
-        <v>0</v>
+        <v>-368064</v>
       </c>
       <c r="Z115" t="n">
-        <v>0</v>
+        <v>201825</v>
       </c>
       <c r="AA115" t="n">
-        <v>0</v>
+        <v>327548</v>
       </c>
       <c r="AB115" t="n">
-        <v>0</v>
+        <v>1089702</v>
       </c>
       <c r="AC115" t="n">
         <v>22</v>
@@ -18032,10 +18032,10 @@
         <v>22</v>
       </c>
       <c r="AE115" t="n">
-        <v>55</v>
+        <v>35</v>
       </c>
       <c r="AF115" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AG115" t="n">
         <v>0</v>
@@ -18044,19 +18044,19 @@
       <c r="AI115" t="inlineStr"/>
       <c r="AJ115" t="inlineStr"/>
       <c r="AK115" t="n">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="AL115" t="n">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="AM115" t="inlineStr">
         <is>
-          <t>等待拉回確認</t>
+          <t>偏高或條件不足</t>
         </is>
       </c>
       <c r="AN115" t="inlineStr">
         <is>
-          <t>DT尚未轉強、5MA乖離尚可、均線多頭排列、位於20日區間中上緣</t>
+          <t>DT尚未轉強、貼近5MA、位於20日區間中上緣</t>
         </is>
       </c>
       <c r="AO115" t="inlineStr">
@@ -18071,29 +18071,29 @@
       </c>
       <c r="AQ115" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、量能溫和放大</t>
+          <t>站上5日線、量能溫和放大、接近20日高點、接近20日低點</t>
         </is>
       </c>
       <c r="AR115" t="inlineStr">
         <is>
-          <t>籌碼中性</t>
+          <t>5日法人買超</t>
         </is>
       </c>
       <c r="AS115" t="inlineStr">
         <is>
-          <t>整理觀察：站上5日線、多頭排列、量能溫和放大、籌碼中性。多空訊號混合，建議降低追價衝動。</t>
+          <t>整理觀察：站上5日線、量能溫和放大、接近20日高點、接近20日低點、5日法人買超。多空訊號混合，建議降低追價衝動。</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>3680.TWO</t>
+          <t>6510.TWO</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>家登</t>
+          <t>精測</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -18102,28 +18102,28 @@
         </is>
       </c>
       <c r="D116" t="n">
-        <v>493</v>
+        <v>3470</v>
       </c>
       <c r="E116" t="n">
-        <v>486.6</v>
+        <v>3346</v>
       </c>
       <c r="F116" t="n">
-        <v>477.05</v>
+        <v>3029.5</v>
       </c>
       <c r="G116" t="n">
-        <v>464.48</v>
+        <v>2904.75</v>
       </c>
       <c r="H116" t="n">
-        <v>1361000</v>
+        <v>1561000</v>
       </c>
       <c r="I116" t="n">
-        <v>1221200</v>
+        <v>1493600</v>
       </c>
       <c r="J116" t="n">
-        <v>516</v>
+        <v>3645</v>
       </c>
       <c r="K116" t="n">
-        <v>418</v>
+        <v>2570</v>
       </c>
       <c r="L116" t="inlineStr">
         <is>
@@ -18197,10 +18197,10 @@
       <c r="AI116" t="inlineStr"/>
       <c r="AJ116" t="inlineStr"/>
       <c r="AK116" t="n">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="AL116" t="n">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="AM116" t="inlineStr">
         <is>
@@ -18209,7 +18209,7 @@
       </c>
       <c r="AN116" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA、均線多頭排列、位於20日區間中上緣</t>
+          <t>DT尚未轉強、5MA乖離尚可、均線多頭排列、位於20日區間中上緣</t>
         </is>
       </c>
       <c r="AO116" t="inlineStr">
@@ -18394,12 +18394,12 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>4919.TW</t>
+          <t>2464.TW</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>新唐</t>
+          <t>盟立</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -18408,28 +18408,28 @@
         </is>
       </c>
       <c r="D118" t="n">
-        <v>122.5</v>
+        <v>203</v>
       </c>
       <c r="E118" t="n">
-        <v>120.4</v>
+        <v>204.5</v>
       </c>
       <c r="F118" t="n">
-        <v>120.45</v>
+        <v>198.85</v>
       </c>
       <c r="G118" t="n">
-        <v>120.65</v>
+        <v>192.65</v>
       </c>
       <c r="H118" t="n">
-        <v>3275935</v>
+        <v>16856438</v>
       </c>
       <c r="I118" t="n">
-        <v>2301016</v>
+        <v>25340507</v>
       </c>
       <c r="J118" t="n">
-        <v>131.5</v>
+        <v>224</v>
       </c>
       <c r="K118" t="n">
-        <v>111</v>
+        <v>172</v>
       </c>
       <c r="L118" t="inlineStr">
         <is>
@@ -18437,52 +18437,52 @@
         </is>
       </c>
       <c r="M118" t="n">
-        <v>-28337</v>
+        <v>-3508714</v>
       </c>
       <c r="N118" t="n">
-        <v>338601</v>
+        <v>-2238928</v>
       </c>
       <c r="O118" t="n">
-        <v>690912</v>
+        <v>8346366</v>
       </c>
       <c r="P118" t="n">
-        <v>1165214</v>
+        <v>2997803</v>
       </c>
       <c r="Q118" t="n">
-        <v>-174815</v>
+        <v>-3790164</v>
       </c>
       <c r="R118" t="n">
-        <v>313915</v>
+        <v>-2732754</v>
       </c>
       <c r="S118" t="n">
-        <v>633801</v>
+        <v>7181448</v>
       </c>
       <c r="T118" t="n">
-        <v>1078492</v>
+        <v>1725656</v>
       </c>
       <c r="U118" t="n">
-        <v>0</v>
+        <v>64000</v>
       </c>
       <c r="V118" t="n">
-        <v>0</v>
+        <v>184000</v>
       </c>
       <c r="W118" t="n">
-        <v>4000</v>
+        <v>516000</v>
       </c>
       <c r="X118" t="n">
-        <v>-7089</v>
+        <v>666000</v>
       </c>
       <c r="Y118" t="n">
-        <v>146478</v>
+        <v>217450</v>
       </c>
       <c r="Z118" t="n">
-        <v>24686</v>
+        <v>309826</v>
       </c>
       <c r="AA118" t="n">
-        <v>53111</v>
+        <v>648918</v>
       </c>
       <c r="AB118" t="n">
-        <v>93811</v>
+        <v>606147</v>
       </c>
       <c r="AC118" t="n">
         <v>22</v>
@@ -18503,19 +18503,19 @@
       <c r="AI118" t="inlineStr"/>
       <c r="AJ118" t="inlineStr"/>
       <c r="AK118" t="n">
-        <v>55</v>
+        <v>20</v>
       </c>
       <c r="AL118" t="n">
-        <v>55</v>
+        <v>20</v>
       </c>
       <c r="AM118" t="inlineStr">
         <is>
-          <t>等待拉回確認</t>
+          <t>暫不追價</t>
         </is>
       </c>
       <c r="AN118" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA、位於20日區間中上緣、量能溫和放大</t>
+          <t>DT尚未轉強、尚未站上5MA、均線多頭排列、位於20日區間中上緣</t>
         </is>
       </c>
       <c r="AO118" t="inlineStr">
@@ -18530,7 +18530,7 @@
       </c>
       <c r="AQ118" t="inlineStr">
         <is>
-          <t>站上5日線、空頭排列、量能溫和放大</t>
+          <t>跌破5日線、多頭排列、量能未放大</t>
         </is>
       </c>
       <c r="AR118" t="inlineStr">
@@ -18540,7 +18540,7 @@
       </c>
       <c r="AS118" t="inlineStr">
         <is>
-          <t>整理觀察：站上5日線、空頭排列、量能溫和放大、5日法人明顯買超、外資投信同步買超。多空訊號混合，建議降低追價衝動。</t>
+          <t>整理觀察：跌破5日線、多頭排列、量能未放大、5日法人明顯買超、外資投信同步買超。多空訊號混合，建議降低追價衝動。</t>
         </is>
       </c>
     </row>
@@ -18700,12 +18700,12 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>2464.TW</t>
+          <t>2395.TW</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>盟立</t>
+          <t>研華</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -18714,28 +18714,28 @@
         </is>
       </c>
       <c r="D120" t="n">
-        <v>203</v>
+        <v>680</v>
       </c>
       <c r="E120" t="n">
-        <v>204.5</v>
+        <v>693.6</v>
       </c>
       <c r="F120" t="n">
-        <v>198.85</v>
+        <v>684.7</v>
       </c>
       <c r="G120" t="n">
-        <v>192.65</v>
+        <v>680.1</v>
       </c>
       <c r="H120" t="n">
-        <v>16856438</v>
+        <v>3571608</v>
       </c>
       <c r="I120" t="n">
-        <v>25340507</v>
+        <v>3947960</v>
       </c>
       <c r="J120" t="n">
-        <v>224</v>
+        <v>727</v>
       </c>
       <c r="K120" t="n">
-        <v>172</v>
+        <v>643</v>
       </c>
       <c r="L120" t="inlineStr">
         <is>
@@ -18743,52 +18743,52 @@
         </is>
       </c>
       <c r="M120" t="n">
-        <v>-3508714</v>
+        <v>-1646719</v>
       </c>
       <c r="N120" t="n">
-        <v>-2238928</v>
+        <v>-362874</v>
       </c>
       <c r="O120" t="n">
-        <v>8346366</v>
+        <v>1246900</v>
       </c>
       <c r="P120" t="n">
-        <v>2997803</v>
+        <v>1357465</v>
       </c>
       <c r="Q120" t="n">
-        <v>-3790164</v>
+        <v>-1495197</v>
       </c>
       <c r="R120" t="n">
-        <v>-2732754</v>
+        <v>-696316</v>
       </c>
       <c r="S120" t="n">
-        <v>7181448</v>
+        <v>393707</v>
       </c>
       <c r="T120" t="n">
-        <v>1725656</v>
+        <v>-35010</v>
       </c>
       <c r="U120" t="n">
-        <v>64000</v>
+        <v>-121000</v>
       </c>
       <c r="V120" t="n">
-        <v>184000</v>
+        <v>310000</v>
       </c>
       <c r="W120" t="n">
-        <v>516000</v>
+        <v>744746</v>
       </c>
       <c r="X120" t="n">
-        <v>666000</v>
+        <v>1338563</v>
       </c>
       <c r="Y120" t="n">
-        <v>217450</v>
+        <v>-30522</v>
       </c>
       <c r="Z120" t="n">
-        <v>309826</v>
+        <v>23442</v>
       </c>
       <c r="AA120" t="n">
-        <v>648918</v>
+        <v>108447</v>
       </c>
       <c r="AB120" t="n">
-        <v>606147</v>
+        <v>53912</v>
       </c>
       <c r="AC120" t="n">
         <v>22</v>
@@ -18809,10 +18809,10 @@
       <c r="AI120" t="inlineStr"/>
       <c r="AJ120" t="inlineStr"/>
       <c r="AK120" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="AL120" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="AM120" t="inlineStr">
         <is>
@@ -18821,7 +18821,7 @@
       </c>
       <c r="AN120" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、均線多頭排列、位於20日區間中上緣</t>
+          <t>DT尚未轉強、尚未站上5MA、均線多頭排列</t>
         </is>
       </c>
       <c r="AO120" t="inlineStr">
@@ -18853,12 +18853,12 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>2395.TW</t>
+          <t>1102.TW</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>研華</t>
+          <t>亞泥</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -18867,28 +18867,28 @@
         </is>
       </c>
       <c r="D121" t="n">
-        <v>680</v>
+        <v>35.05</v>
       </c>
       <c r="E121" t="n">
-        <v>693.6</v>
+        <v>35.1</v>
       </c>
       <c r="F121" t="n">
-        <v>684.7</v>
+        <v>34.98</v>
       </c>
       <c r="G121" t="n">
-        <v>680.1</v>
+        <v>34.25</v>
       </c>
       <c r="H121" t="n">
-        <v>3571608</v>
+        <v>7148594</v>
       </c>
       <c r="I121" t="n">
-        <v>3947960</v>
+        <v>7505345</v>
       </c>
       <c r="J121" t="n">
-        <v>727</v>
+        <v>35.35</v>
       </c>
       <c r="K121" t="n">
-        <v>643</v>
+        <v>31.6</v>
       </c>
       <c r="L121" t="inlineStr">
         <is>
@@ -18896,64 +18896,64 @@
         </is>
       </c>
       <c r="M121" t="n">
-        <v>-1646719</v>
+        <v>-1380153</v>
       </c>
       <c r="N121" t="n">
-        <v>-362874</v>
+        <v>428249</v>
       </c>
       <c r="O121" t="n">
-        <v>1246900</v>
+        <v>4534588</v>
       </c>
       <c r="P121" t="n">
-        <v>1357465</v>
+        <v>10539499</v>
       </c>
       <c r="Q121" t="n">
-        <v>-1495197</v>
+        <v>-1896791</v>
       </c>
       <c r="R121" t="n">
-        <v>-696316</v>
+        <v>-3394741</v>
       </c>
       <c r="S121" t="n">
-        <v>393707</v>
+        <v>-1235283</v>
       </c>
       <c r="T121" t="n">
-        <v>-35010</v>
+        <v>7866820</v>
       </c>
       <c r="U121" t="n">
-        <v>-121000</v>
+        <v>455956</v>
       </c>
       <c r="V121" t="n">
-        <v>310000</v>
+        <v>3911410</v>
       </c>
       <c r="W121" t="n">
-        <v>744746</v>
+        <v>6288479</v>
       </c>
       <c r="X121" t="n">
-        <v>1338563</v>
+        <v>5887727</v>
       </c>
       <c r="Y121" t="n">
-        <v>-30522</v>
+        <v>60682</v>
       </c>
       <c r="Z121" t="n">
-        <v>23442</v>
+        <v>-88420</v>
       </c>
       <c r="AA121" t="n">
-        <v>108447</v>
+        <v>-518608</v>
       </c>
       <c r="AB121" t="n">
-        <v>53912</v>
+        <v>-3215048</v>
       </c>
       <c r="AC121" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AD121" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AE121" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="AF121" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="AG121" t="n">
         <v>0</v>
@@ -18989,29 +18989,29 @@
       </c>
       <c r="AQ121" t="inlineStr">
         <is>
-          <t>跌破5日線、多頭排列、量能未放大</t>
+          <t>跌破5日線、多頭排列、量能未放大、接近20日高點</t>
         </is>
       </c>
       <c r="AR121" t="inlineStr">
         <is>
-          <t>5日法人明顯買超、外資投信同步買超</t>
+          <t>5日法人明顯買超、投信買外資賣</t>
         </is>
       </c>
       <c r="AS121" t="inlineStr">
         <is>
-          <t>整理觀察：跌破5日線、多頭排列、量能未放大、5日法人明顯買超、外資投信同步買超。多空訊號混合，建議降低追價衝動。</t>
+          <t>整理觀察：跌破5日線、多頭排列、量能未放大、接近20日高點、5日法人明顯買超、投信買外資賣。多空訊號混合，建議降低追價衝動。</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>1102.TW</t>
+          <t>2610.TW</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>亞泥</t>
+          <t>華航</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -19020,28 +19020,28 @@
         </is>
       </c>
       <c r="D122" t="n">
-        <v>35.05</v>
+        <v>20.45</v>
       </c>
       <c r="E122" t="n">
-        <v>35.1</v>
+        <v>20.45</v>
       </c>
       <c r="F122" t="n">
-        <v>34.98</v>
+        <v>20.48</v>
       </c>
       <c r="G122" t="n">
-        <v>34.25</v>
+        <v>20.32</v>
       </c>
       <c r="H122" t="n">
-        <v>7148594</v>
+        <v>13861205</v>
       </c>
       <c r="I122" t="n">
-        <v>7505345</v>
+        <v>14714267</v>
       </c>
       <c r="J122" t="n">
-        <v>35.35</v>
+        <v>21</v>
       </c>
       <c r="K122" t="n">
-        <v>31.6</v>
+        <v>19.85</v>
       </c>
       <c r="L122" t="inlineStr">
         <is>
@@ -19049,52 +19049,52 @@
         </is>
       </c>
       <c r="M122" t="n">
-        <v>-1380153</v>
+        <v>2582498</v>
       </c>
       <c r="N122" t="n">
-        <v>428249</v>
+        <v>13796844</v>
       </c>
       <c r="O122" t="n">
-        <v>4534588</v>
+        <v>18604056</v>
       </c>
       <c r="P122" t="n">
-        <v>10539499</v>
+        <v>18078074</v>
       </c>
       <c r="Q122" t="n">
-        <v>-1896791</v>
+        <v>1101916</v>
       </c>
       <c r="R122" t="n">
-        <v>-3394741</v>
+        <v>11784485</v>
       </c>
       <c r="S122" t="n">
-        <v>-1235283</v>
+        <v>13808933</v>
       </c>
       <c r="T122" t="n">
-        <v>7866820</v>
+        <v>12643233</v>
       </c>
       <c r="U122" t="n">
-        <v>455956</v>
+        <v>1261000</v>
       </c>
       <c r="V122" t="n">
-        <v>3911410</v>
+        <v>2088000</v>
       </c>
       <c r="W122" t="n">
-        <v>6288479</v>
+        <v>5262000</v>
       </c>
       <c r="X122" t="n">
-        <v>5887727</v>
+        <v>6097156</v>
       </c>
       <c r="Y122" t="n">
-        <v>60682</v>
+        <v>219582</v>
       </c>
       <c r="Z122" t="n">
-        <v>-88420</v>
+        <v>-75641</v>
       </c>
       <c r="AA122" t="n">
-        <v>-518608</v>
+        <v>-466877</v>
       </c>
       <c r="AB122" t="n">
-        <v>-3215048</v>
+        <v>-662315</v>
       </c>
       <c r="AC122" t="n">
         <v>20</v>
@@ -19103,10 +19103,10 @@
         <v>20</v>
       </c>
       <c r="AE122" t="n">
-        <v>20</v>
+        <v>-30</v>
       </c>
       <c r="AF122" t="n">
-        <v>30</v>
+        <v>80</v>
       </c>
       <c r="AG122" t="n">
         <v>0</v>
@@ -19127,7 +19127,7 @@
       </c>
       <c r="AN122" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、均線多頭排列</t>
+          <t>DT尚未轉強、尚未站上5MA、位於20日區間中上緣</t>
         </is>
       </c>
       <c r="AO122" t="inlineStr">
@@ -19142,17 +19142,17 @@
       </c>
       <c r="AQ122" t="inlineStr">
         <is>
-          <t>跌破5日線、多頭排列、量能未放大、接近20日高點</t>
+          <t>跌破5日線、量能未放大、接近20日低點</t>
         </is>
       </c>
       <c r="AR122" t="inlineStr">
         <is>
-          <t>5日法人明顯買超、投信買外資賣</t>
+          <t>法人連續偏買、5日法人明顯買超、外資投信同步買超</t>
         </is>
       </c>
       <c r="AS122" t="inlineStr">
         <is>
-          <t>整理觀察：跌破5日線、多頭排列、量能未放大、接近20日高點、5日法人明顯買超、投信買外資賣。多空訊號混合，建議降低追價衝動。</t>
+          <t>整理觀察：跌破5日線、量能未放大、接近20日低點、法人連續偏買、5日法人明顯買超、外資投信同步買超。多空訊號混合，建議降低追價衝動。</t>
         </is>
       </c>
     </row>
@@ -19312,12 +19312,12 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>2610.TW</t>
+          <t>3324.TWO</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>華航</t>
+          <t>雙鴻</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -19326,28 +19326,28 @@
         </is>
       </c>
       <c r="D124" t="n">
-        <v>20.45</v>
+        <v>1440</v>
       </c>
       <c r="E124" t="n">
-        <v>20.45</v>
+        <v>1417</v>
       </c>
       <c r="F124" t="n">
-        <v>20.48</v>
+        <v>1267.5</v>
       </c>
       <c r="G124" t="n">
-        <v>20.32</v>
+        <v>1138.2</v>
       </c>
       <c r="H124" t="n">
-        <v>13861205</v>
+        <v>2118000</v>
       </c>
       <c r="I124" t="n">
-        <v>14714267</v>
+        <v>5543800</v>
       </c>
       <c r="J124" t="n">
-        <v>21</v>
+        <v>1505</v>
       </c>
       <c r="K124" t="n">
-        <v>19.85</v>
+        <v>955</v>
       </c>
       <c r="L124" t="inlineStr">
         <is>
@@ -19355,64 +19355,64 @@
         </is>
       </c>
       <c r="M124" t="n">
-        <v>2582498</v>
+        <v>0</v>
       </c>
       <c r="N124" t="n">
-        <v>13796844</v>
+        <v>0</v>
       </c>
       <c r="O124" t="n">
-        <v>18604056</v>
+        <v>0</v>
       </c>
       <c r="P124" t="n">
-        <v>18078074</v>
+        <v>0</v>
       </c>
       <c r="Q124" t="n">
-        <v>1101916</v>
+        <v>0</v>
       </c>
       <c r="R124" t="n">
-        <v>11784485</v>
+        <v>0</v>
       </c>
       <c r="S124" t="n">
-        <v>13808933</v>
+        <v>0</v>
       </c>
       <c r="T124" t="n">
-        <v>12643233</v>
+        <v>0</v>
       </c>
       <c r="U124" t="n">
-        <v>1261000</v>
+        <v>0</v>
       </c>
       <c r="V124" t="n">
-        <v>2088000</v>
+        <v>0</v>
       </c>
       <c r="W124" t="n">
-        <v>5262000</v>
+        <v>0</v>
       </c>
       <c r="X124" t="n">
-        <v>6097156</v>
+        <v>0</v>
       </c>
       <c r="Y124" t="n">
-        <v>219582</v>
+        <v>0</v>
       </c>
       <c r="Z124" t="n">
-        <v>-75641</v>
+        <v>0</v>
       </c>
       <c r="AA124" t="n">
-        <v>-466877</v>
+        <v>0</v>
       </c>
       <c r="AB124" t="n">
-        <v>-662315</v>
+        <v>0</v>
       </c>
       <c r="AC124" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AD124" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AE124" t="n">
-        <v>-30</v>
+        <v>45</v>
       </c>
       <c r="AF124" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="AG124" t="n">
         <v>0</v>
@@ -19421,44 +19421,44 @@
       <c r="AI124" t="inlineStr"/>
       <c r="AJ124" t="inlineStr"/>
       <c r="AK124" t="n">
-        <v>5</v>
+        <v>40</v>
       </c>
       <c r="AL124" t="n">
-        <v>5</v>
+        <v>40</v>
       </c>
       <c r="AM124" t="inlineStr">
         <is>
-          <t>暫不追價</t>
+          <t>偏高或條件不足</t>
         </is>
       </c>
       <c r="AN124" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位於20日區間中上緣</t>
+          <t>DT尚未轉強、貼近5MA、均線多頭排列</t>
         </is>
       </c>
       <c r="AO124" t="inlineStr">
         <is>
-          <t>⚠️整理</t>
+          <t>❌避開</t>
         </is>
       </c>
       <c r="AP124" t="inlineStr">
         <is>
-          <t>整理觀察</t>
+          <t>觀望</t>
         </is>
       </c>
       <c r="AQ124" t="inlineStr">
         <is>
-          <t>跌破5日線、量能未放大、接近20日低點</t>
+          <t>站上5日線、多頭排列、量能未放大</t>
         </is>
       </c>
       <c r="AR124" t="inlineStr">
         <is>
-          <t>法人連續偏買、5日法人明顯買超、外資投信同步買超</t>
+          <t>籌碼中性</t>
         </is>
       </c>
       <c r="AS124" t="inlineStr">
         <is>
-          <t>整理觀察：跌破5日線、量能未放大、接近20日低點、法人連續偏買、5日法人明顯買超、外資投信同步買超。多空訊號混合，建議降低追價衝動。</t>
+          <t>風險偏高：站上5日線、多頭排列、量能未放大、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
@@ -19771,12 +19771,12 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>3324.TWO</t>
+          <t>3680.TWO</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>雙鴻</t>
+          <t>家登</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -19785,28 +19785,28 @@
         </is>
       </c>
       <c r="D127" t="n">
-        <v>1440</v>
+        <v>529</v>
       </c>
       <c r="E127" t="n">
-        <v>1417</v>
+        <v>524.2</v>
       </c>
       <c r="F127" t="n">
-        <v>1267.5</v>
+        <v>505.4</v>
       </c>
       <c r="G127" t="n">
-        <v>1138.2</v>
+        <v>484.77</v>
       </c>
       <c r="H127" t="n">
-        <v>2118000</v>
+        <v>1267000</v>
       </c>
       <c r="I127" t="n">
-        <v>5543800</v>
+        <v>1980400</v>
       </c>
       <c r="J127" t="n">
-        <v>1505</v>
+        <v>544</v>
       </c>
       <c r="K127" t="n">
-        <v>955</v>
+        <v>445</v>
       </c>
       <c r="L127" t="inlineStr">
         <is>
@@ -19880,19 +19880,19 @@
       <c r="AI127" t="inlineStr"/>
       <c r="AJ127" t="inlineStr"/>
       <c r="AK127" t="n">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="AL127" t="n">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="AM127" t="inlineStr">
         <is>
-          <t>偏高或條件不足</t>
+          <t>等待拉回確認</t>
         </is>
       </c>
       <c r="AN127" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA、均線多頭排列</t>
+          <t>DT尚未轉強、貼近5MA、均線多頭排列、位於20日區間中上緣</t>
         </is>
       </c>
       <c r="AO127" t="inlineStr">
@@ -29257,12 +29257,12 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>4903.TWO</t>
+          <t>3363.TWO</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>聯光通</t>
+          <t>上詮</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -29271,28 +29271,28 @@
         </is>
       </c>
       <c r="D189" t="n">
-        <v>36.5</v>
+        <v>723</v>
       </c>
       <c r="E189" t="n">
-        <v>37.27</v>
+        <v>759.6</v>
       </c>
       <c r="F189" t="n">
-        <v>36.89</v>
+        <v>722.3</v>
       </c>
       <c r="G189" t="n">
-        <v>36.42</v>
+        <v>660.8</v>
       </c>
       <c r="H189" t="n">
-        <v>702000</v>
+        <v>4159000</v>
       </c>
       <c r="I189" t="n">
-        <v>1476000</v>
+        <v>7359000</v>
       </c>
       <c r="J189" t="n">
-        <v>39.15</v>
+        <v>850</v>
       </c>
       <c r="K189" t="n">
-        <v>34.3</v>
+        <v>549</v>
       </c>
       <c r="L189" t="inlineStr">
         <is>
@@ -30022,12 +30022,12 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>3363.TWO</t>
+          <t>4903.TWO</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>上詮</t>
+          <t>聯光通</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -30036,28 +30036,28 @@
         </is>
       </c>
       <c r="D194" t="n">
-        <v>723</v>
+        <v>36.5</v>
       </c>
       <c r="E194" t="n">
-        <v>759.6</v>
+        <v>37.27</v>
       </c>
       <c r="F194" t="n">
-        <v>722.3</v>
+        <v>36.89</v>
       </c>
       <c r="G194" t="n">
-        <v>660.8</v>
+        <v>36.42</v>
       </c>
       <c r="H194" t="n">
-        <v>4159000</v>
+        <v>702000</v>
       </c>
       <c r="I194" t="n">
-        <v>7359000</v>
+        <v>1476000</v>
       </c>
       <c r="J194" t="n">
-        <v>850</v>
+        <v>39.15</v>
       </c>
       <c r="K194" t="n">
-        <v>549</v>
+        <v>34.3</v>
       </c>
       <c r="L194" t="inlineStr">
         <is>
@@ -30787,12 +30787,12 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>1722.TW</t>
+          <t>3163.TWO</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>台肥</t>
+          <t>波若威</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -30801,28 +30801,28 @@
         </is>
       </c>
       <c r="D199" t="n">
-        <v>44.6</v>
+        <v>741</v>
       </c>
       <c r="E199" t="n">
-        <v>44.66</v>
+        <v>763.6</v>
       </c>
       <c r="F199" t="n">
-        <v>44.62</v>
+        <v>748.5</v>
       </c>
       <c r="G199" t="n">
-        <v>45.27</v>
+        <v>725.2</v>
       </c>
       <c r="H199" t="n">
-        <v>2518924</v>
+        <v>1159000</v>
       </c>
       <c r="I199" t="n">
-        <v>3197740</v>
+        <v>4936600</v>
       </c>
       <c r="J199" t="n">
-        <v>46.75</v>
+        <v>814</v>
       </c>
       <c r="K199" t="n">
-        <v>44.35</v>
+        <v>630</v>
       </c>
       <c r="L199" t="inlineStr">
         <is>
@@ -30830,64 +30830,64 @@
         </is>
       </c>
       <c r="M199" t="n">
-        <v>-115693</v>
+        <v>0</v>
       </c>
       <c r="N199" t="n">
-        <v>608085</v>
+        <v>0</v>
       </c>
       <c r="O199" t="n">
-        <v>3101879</v>
+        <v>0</v>
       </c>
       <c r="P199" t="n">
-        <v>2900148</v>
+        <v>0</v>
       </c>
       <c r="Q199" t="n">
-        <v>-132000</v>
+        <v>0</v>
       </c>
       <c r="R199" t="n">
-        <v>595633</v>
+        <v>0</v>
       </c>
       <c r="S199" t="n">
-        <v>3363401</v>
+        <v>0</v>
       </c>
       <c r="T199" t="n">
-        <v>3172244</v>
+        <v>0</v>
       </c>
       <c r="U199" t="n">
-        <v>-6000</v>
+        <v>0</v>
       </c>
       <c r="V199" t="n">
-        <v>-16000</v>
+        <v>0</v>
       </c>
       <c r="W199" t="n">
-        <v>-15000</v>
+        <v>0</v>
       </c>
       <c r="X199" t="n">
-        <v>-8000</v>
+        <v>0</v>
       </c>
       <c r="Y199" t="n">
-        <v>22307</v>
+        <v>0</v>
       </c>
       <c r="Z199" t="n">
-        <v>28452</v>
+        <v>0</v>
       </c>
       <c r="AA199" t="n">
-        <v>-246522</v>
+        <v>0</v>
       </c>
       <c r="AB199" t="n">
-        <v>-264096</v>
+        <v>0</v>
       </c>
       <c r="AC199" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD199" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AE199" t="n">
-        <v>-30</v>
+        <v>5</v>
       </c>
       <c r="AF199" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="AG199" t="n">
         <v>0</v>
@@ -30896,10 +30896,10 @@
       <c r="AI199" t="inlineStr"/>
       <c r="AJ199" t="inlineStr"/>
       <c r="AK199" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AL199" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AM199" t="inlineStr">
         <is>
@@ -30908,7 +30908,7 @@
       </c>
       <c r="AN199" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強</t>
+          <t>DT尚未轉強、尚未站上5MA、均線多頭排列、位於20日區間中上緣</t>
         </is>
       </c>
       <c r="AO199" t="inlineStr">
@@ -30923,17 +30923,17 @@
       </c>
       <c r="AQ199" t="inlineStr">
         <is>
-          <t>跌破5日線、量能未放大、接近20日低點</t>
+          <t>跌破5日線、多頭排列、量能未放大</t>
         </is>
       </c>
       <c r="AR199" t="inlineStr">
         <is>
-          <t>5日法人明顯買超、外資買投信賣</t>
+          <t>籌碼中性</t>
         </is>
       </c>
       <c r="AS199" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、量能未放大、接近20日低點、5日法人明顯買超、外資買投信賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、多頭排列、量能未放大、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
@@ -31093,12 +31093,12 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>2485.TW</t>
+          <t>1722.TW</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>兆赫</t>
+          <t>台肥</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -31107,28 +31107,28 @@
         </is>
       </c>
       <c r="D201" t="n">
-        <v>40.7</v>
+        <v>44.6</v>
       </c>
       <c r="E201" t="n">
-        <v>41.58</v>
+        <v>44.66</v>
       </c>
       <c r="F201" t="n">
-        <v>42.18</v>
+        <v>44.62</v>
       </c>
       <c r="G201" t="n">
-        <v>42.13</v>
+        <v>45.27</v>
       </c>
       <c r="H201" t="n">
-        <v>2147493</v>
+        <v>2518924</v>
       </c>
       <c r="I201" t="n">
-        <v>2115233</v>
+        <v>3197740</v>
       </c>
       <c r="J201" t="n">
-        <v>45.65</v>
+        <v>46.75</v>
       </c>
       <c r="K201" t="n">
-        <v>39.3</v>
+        <v>44.35</v>
       </c>
       <c r="L201" t="inlineStr">
         <is>
@@ -31136,52 +31136,52 @@
         </is>
       </c>
       <c r="M201" t="n">
-        <v>-671936</v>
+        <v>-115693</v>
       </c>
       <c r="N201" t="n">
-        <v>-466704</v>
+        <v>608085</v>
       </c>
       <c r="O201" t="n">
-        <v>225625</v>
+        <v>3101879</v>
       </c>
       <c r="P201" t="n">
-        <v>-518347</v>
+        <v>2900148</v>
       </c>
       <c r="Q201" t="n">
-        <v>-648281</v>
+        <v>-132000</v>
       </c>
       <c r="R201" t="n">
-        <v>-319628</v>
+        <v>595633</v>
       </c>
       <c r="S201" t="n">
-        <v>338429</v>
+        <v>3363401</v>
       </c>
       <c r="T201" t="n">
-        <v>-618589</v>
+        <v>3172244</v>
       </c>
       <c r="U201" t="n">
-        <v>0</v>
+        <v>-6000</v>
       </c>
       <c r="V201" t="n">
-        <v>0</v>
+        <v>-16000</v>
       </c>
       <c r="W201" t="n">
-        <v>0</v>
+        <v>-15000</v>
       </c>
       <c r="X201" t="n">
-        <v>0</v>
+        <v>-8000</v>
       </c>
       <c r="Y201" t="n">
-        <v>-23655</v>
+        <v>22307</v>
       </c>
       <c r="Z201" t="n">
-        <v>-147076</v>
+        <v>28452</v>
       </c>
       <c r="AA201" t="n">
-        <v>-112804</v>
+        <v>-246522</v>
       </c>
       <c r="AB201" t="n">
-        <v>100242</v>
+        <v>-264096</v>
       </c>
       <c r="AC201" t="n">
         <v>0</v>
@@ -31190,10 +31190,10 @@
         <v>0</v>
       </c>
       <c r="AE201" t="n">
-        <v>-20</v>
+        <v>-30</v>
       </c>
       <c r="AF201" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="AG201" t="n">
         <v>0</v>
@@ -31229,17 +31229,17 @@
       </c>
       <c r="AQ201" t="inlineStr">
         <is>
-          <t>跌破5日線、量能溫和放大、接近20日低點</t>
+          <t>跌破5日線、量能未放大、接近20日低點</t>
         </is>
       </c>
       <c r="AR201" t="inlineStr">
         <is>
-          <t>5日法人買超</t>
+          <t>5日法人明顯買超、外資買投信賣</t>
         </is>
       </c>
       <c r="AS201" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、量能溫和放大、接近20日低點、5日法人買超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、量能未放大、接近20日低點、5日法人明顯買超、外資買投信賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
@@ -32011,12 +32011,12 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>3533.TW</t>
+          <t>2393.TW</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>嘉澤</t>
+          <t>億光</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
@@ -32025,28 +32025,28 @@
         </is>
       </c>
       <c r="D207" t="n">
-        <v>1695</v>
+        <v>63.5</v>
       </c>
       <c r="E207" t="n">
-        <v>1700</v>
+        <v>64.86</v>
       </c>
       <c r="F207" t="n">
-        <v>1678</v>
+        <v>65.51000000000001</v>
       </c>
       <c r="G207" t="n">
-        <v>1703.5</v>
+        <v>64.97</v>
       </c>
       <c r="H207" t="n">
-        <v>628390</v>
+        <v>1601153</v>
       </c>
       <c r="I207" t="n">
-        <v>889808</v>
+        <v>1314460</v>
       </c>
       <c r="J207" t="n">
-        <v>2030</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="K207" t="n">
-        <v>1540</v>
+        <v>61.6</v>
       </c>
       <c r="L207" t="inlineStr">
         <is>
@@ -32054,52 +32054,52 @@
         </is>
       </c>
       <c r="M207" t="n">
-        <v>17358</v>
+        <v>-455580</v>
       </c>
       <c r="N207" t="n">
-        <v>-68448</v>
+        <v>-459778</v>
       </c>
       <c r="O207" t="n">
-        <v>122191</v>
+        <v>107884</v>
       </c>
       <c r="P207" t="n">
-        <v>-1252866</v>
+        <v>1514234</v>
       </c>
       <c r="Q207" t="n">
-        <v>13167</v>
+        <v>-508000</v>
       </c>
       <c r="R207" t="n">
-        <v>8585</v>
+        <v>-331356</v>
       </c>
       <c r="S207" t="n">
-        <v>236027</v>
+        <v>1133026</v>
       </c>
       <c r="T207" t="n">
-        <v>-524811</v>
+        <v>3240239</v>
       </c>
       <c r="U207" t="n">
-        <v>989</v>
+        <v>46990</v>
       </c>
       <c r="V207" t="n">
-        <v>-37372</v>
+        <v>-148615</v>
       </c>
       <c r="W207" t="n">
-        <v>-67372</v>
+        <v>-1009906</v>
       </c>
       <c r="X207" t="n">
-        <v>-758856</v>
+        <v>-1030246</v>
       </c>
       <c r="Y207" t="n">
-        <v>3202</v>
+        <v>5430</v>
       </c>
       <c r="Z207" t="n">
-        <v>-39661</v>
+        <v>20193</v>
       </c>
       <c r="AA207" t="n">
-        <v>-46464</v>
+        <v>-15236</v>
       </c>
       <c r="AB207" t="n">
-        <v>30801</v>
+        <v>-695759</v>
       </c>
       <c r="AC207" t="n">
         <v>0</v>
@@ -32120,10 +32120,10 @@
       <c r="AI207" t="inlineStr"/>
       <c r="AJ207" t="inlineStr"/>
       <c r="AK207" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AL207" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AM207" t="inlineStr">
         <is>
@@ -32132,7 +32132,7 @@
       </c>
       <c r="AN207" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強</t>
+          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、量能溫和放大</t>
         </is>
       </c>
       <c r="AO207" t="inlineStr">
@@ -32147,7 +32147,7 @@
       </c>
       <c r="AQ207" t="inlineStr">
         <is>
-          <t>跌破5日線、量能未放大</t>
+          <t>跌破5日線、量能溫和放大、接近20日低點</t>
         </is>
       </c>
       <c r="AR207" t="inlineStr">
@@ -32157,19 +32157,19 @@
       </c>
       <c r="AS207" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、量能未放大、5日法人買超、外資買投信賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、量能溫和放大、接近20日低點、5日法人買超、外資買投信賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>2393.TW</t>
+          <t>3533.TW</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>億光</t>
+          <t>嘉澤</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
@@ -32178,28 +32178,28 @@
         </is>
       </c>
       <c r="D208" t="n">
-        <v>63.5</v>
+        <v>1695</v>
       </c>
       <c r="E208" t="n">
-        <v>64.86</v>
+        <v>1700</v>
       </c>
       <c r="F208" t="n">
-        <v>65.51000000000001</v>
+        <v>1678</v>
       </c>
       <c r="G208" t="n">
-        <v>64.97</v>
+        <v>1703.5</v>
       </c>
       <c r="H208" t="n">
-        <v>1601153</v>
+        <v>628390</v>
       </c>
       <c r="I208" t="n">
-        <v>1314460</v>
+        <v>889808</v>
       </c>
       <c r="J208" t="n">
-        <v>67.09999999999999</v>
+        <v>2030</v>
       </c>
       <c r="K208" t="n">
-        <v>61.6</v>
+        <v>1540</v>
       </c>
       <c r="L208" t="inlineStr">
         <is>
@@ -32207,52 +32207,52 @@
         </is>
       </c>
       <c r="M208" t="n">
-        <v>-455580</v>
+        <v>17358</v>
       </c>
       <c r="N208" t="n">
-        <v>-459778</v>
+        <v>-68448</v>
       </c>
       <c r="O208" t="n">
-        <v>107884</v>
+        <v>122191</v>
       </c>
       <c r="P208" t="n">
-        <v>1514234</v>
+        <v>-1252866</v>
       </c>
       <c r="Q208" t="n">
-        <v>-508000</v>
+        <v>13167</v>
       </c>
       <c r="R208" t="n">
-        <v>-331356</v>
+        <v>8585</v>
       </c>
       <c r="S208" t="n">
-        <v>1133026</v>
+        <v>236027</v>
       </c>
       <c r="T208" t="n">
-        <v>3240239</v>
+        <v>-524811</v>
       </c>
       <c r="U208" t="n">
-        <v>46990</v>
+        <v>989</v>
       </c>
       <c r="V208" t="n">
-        <v>-148615</v>
+        <v>-37372</v>
       </c>
       <c r="W208" t="n">
-        <v>-1009906</v>
+        <v>-67372</v>
       </c>
       <c r="X208" t="n">
-        <v>-1030246</v>
+        <v>-758856</v>
       </c>
       <c r="Y208" t="n">
-        <v>5430</v>
+        <v>3202</v>
       </c>
       <c r="Z208" t="n">
-        <v>20193</v>
+        <v>-39661</v>
       </c>
       <c r="AA208" t="n">
-        <v>-15236</v>
+        <v>-46464</v>
       </c>
       <c r="AB208" t="n">
-        <v>-695759</v>
+        <v>30801</v>
       </c>
       <c r="AC208" t="n">
         <v>0</v>
@@ -32273,10 +32273,10 @@
       <c r="AI208" t="inlineStr"/>
       <c r="AJ208" t="inlineStr"/>
       <c r="AK208" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AL208" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AM208" t="inlineStr">
         <is>
@@ -32285,7 +32285,7 @@
       </c>
       <c r="AN208" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、量能溫和放大</t>
+          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強</t>
         </is>
       </c>
       <c r="AO208" t="inlineStr">
@@ -32300,7 +32300,7 @@
       </c>
       <c r="AQ208" t="inlineStr">
         <is>
-          <t>跌破5日線、量能溫和放大、接近20日低點</t>
+          <t>跌破5日線、量能未放大</t>
         </is>
       </c>
       <c r="AR208" t="inlineStr">
@@ -32310,19 +32310,19 @@
       </c>
       <c r="AS208" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、量能溫和放大、接近20日低點、5日法人買超、外資買投信賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、量能未放大、5日法人買超、外資買投信賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>2505.TW</t>
+          <t>2485.TW</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>國揚</t>
+          <t>兆赫</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
@@ -32331,28 +32331,28 @@
         </is>
       </c>
       <c r="D209" t="n">
-        <v>17.25</v>
+        <v>40.7</v>
       </c>
       <c r="E209" t="n">
-        <v>17.09</v>
+        <v>41.58</v>
       </c>
       <c r="F209" t="n">
-        <v>17.2</v>
+        <v>42.18</v>
       </c>
       <c r="G209" t="n">
-        <v>17.54</v>
+        <v>42.13</v>
       </c>
       <c r="H209" t="n">
-        <v>169941</v>
+        <v>2147493</v>
       </c>
       <c r="I209" t="n">
-        <v>171890</v>
+        <v>2115233</v>
       </c>
       <c r="J209" t="n">
-        <v>18.4</v>
+        <v>45.65</v>
       </c>
       <c r="K209" t="n">
-        <v>16.85</v>
+        <v>39.3</v>
       </c>
       <c r="L209" t="inlineStr">
         <is>
@@ -32360,28 +32360,28 @@
         </is>
       </c>
       <c r="M209" t="n">
-        <v>20473</v>
+        <v>-671936</v>
       </c>
       <c r="N209" t="n">
-        <v>100624</v>
+        <v>-466704</v>
       </c>
       <c r="O209" t="n">
-        <v>-5376</v>
+        <v>225625</v>
       </c>
       <c r="P209" t="n">
-        <v>-417376</v>
+        <v>-518347</v>
       </c>
       <c r="Q209" t="n">
-        <v>11473</v>
+        <v>-648281</v>
       </c>
       <c r="R209" t="n">
-        <v>88624</v>
+        <v>-319628</v>
       </c>
       <c r="S209" t="n">
-        <v>-17376</v>
+        <v>338429</v>
       </c>
       <c r="T209" t="n">
-        <v>-436376</v>
+        <v>-618589</v>
       </c>
       <c r="U209" t="n">
         <v>0</v>
@@ -32396,16 +32396,16 @@
         <v>0</v>
       </c>
       <c r="Y209" t="n">
-        <v>9000</v>
+        <v>-23655</v>
       </c>
       <c r="Z209" t="n">
-        <v>12000</v>
+        <v>-147076</v>
       </c>
       <c r="AA209" t="n">
-        <v>12000</v>
+        <v>-112804</v>
       </c>
       <c r="AB209" t="n">
-        <v>19000</v>
+        <v>100242</v>
       </c>
       <c r="AC209" t="n">
         <v>0</v>
@@ -32414,10 +32414,10 @@
         <v>0</v>
       </c>
       <c r="AE209" t="n">
-        <v>-15</v>
+        <v>-20</v>
       </c>
       <c r="AF209" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="AG209" t="n">
         <v>0</v>
@@ -32426,19 +32426,19 @@
       <c r="AI209" t="inlineStr"/>
       <c r="AJ209" t="inlineStr"/>
       <c r="AK209" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="AL209" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="AM209" t="inlineStr">
         <is>
-          <t>偏高或條件不足</t>
+          <t>暫不追價</t>
         </is>
       </c>
       <c r="AN209" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA、位置偏低但需等轉強</t>
+          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強</t>
         </is>
       </c>
       <c r="AO209" t="inlineStr">
@@ -32453,29 +32453,29 @@
       </c>
       <c r="AQ209" t="inlineStr">
         <is>
-          <t>站上5日線、空頭排列、量能未放大、接近20日低點</t>
+          <t>跌破5日線、量能溫和放大、接近20日低點</t>
         </is>
       </c>
       <c r="AR209" t="inlineStr">
         <is>
-          <t>短線籌碼止穩</t>
+          <t>5日法人買超</t>
         </is>
       </c>
       <c r="AS209" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、空頭排列、量能未放大、接近20日低點、短線籌碼止穩。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、量能溫和放大、接近20日低點、5日法人買超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>2233.TW</t>
+          <t>2505.TW</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>宇隆</t>
+          <t>國揚</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
@@ -32484,28 +32484,28 @@
         </is>
       </c>
       <c r="D210" t="n">
-        <v>168.5</v>
+        <v>17.25</v>
       </c>
       <c r="E210" t="n">
-        <v>169.8</v>
+        <v>17.09</v>
       </c>
       <c r="F210" t="n">
-        <v>171.15</v>
+        <v>17.2</v>
       </c>
       <c r="G210" t="n">
-        <v>181.5</v>
+        <v>17.54</v>
       </c>
       <c r="H210" t="n">
-        <v>342844</v>
+        <v>169941</v>
       </c>
       <c r="I210" t="n">
-        <v>441683</v>
+        <v>171890</v>
       </c>
       <c r="J210" t="n">
-        <v>210.5</v>
+        <v>18.4</v>
       </c>
       <c r="K210" t="n">
-        <v>157.5</v>
+        <v>16.85</v>
       </c>
       <c r="L210" t="inlineStr">
         <is>
@@ -32513,64 +32513,64 @@
         </is>
       </c>
       <c r="M210" t="n">
-        <v>70531</v>
+        <v>20473</v>
       </c>
       <c r="N210" t="n">
-        <v>86927</v>
+        <v>100624</v>
       </c>
       <c r="O210" t="n">
-        <v>55765</v>
+        <v>-5376</v>
       </c>
       <c r="P210" t="n">
-        <v>-76985</v>
+        <v>-417376</v>
       </c>
       <c r="Q210" t="n">
-        <v>67531</v>
+        <v>11473</v>
       </c>
       <c r="R210" t="n">
-        <v>185146</v>
+        <v>88624</v>
       </c>
       <c r="S210" t="n">
-        <v>153491</v>
+        <v>-17376</v>
       </c>
       <c r="T210" t="n">
-        <v>37643</v>
+        <v>-436376</v>
       </c>
       <c r="U210" t="n">
         <v>0</v>
       </c>
       <c r="V210" t="n">
-        <v>-100000</v>
+        <v>0</v>
       </c>
       <c r="W210" t="n">
-        <v>-100000</v>
+        <v>0</v>
       </c>
       <c r="X210" t="n">
-        <v>-200000</v>
+        <v>0</v>
       </c>
       <c r="Y210" t="n">
-        <v>3000</v>
+        <v>9000</v>
       </c>
       <c r="Z210" t="n">
-        <v>1781</v>
+        <v>12000</v>
       </c>
       <c r="AA210" t="n">
-        <v>2274</v>
+        <v>12000</v>
       </c>
       <c r="AB210" t="n">
-        <v>85372</v>
+        <v>19000</v>
       </c>
       <c r="AC210" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="AD210" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="AE210" t="n">
-        <v>-45</v>
+        <v>-15</v>
       </c>
       <c r="AF210" t="n">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="AG210" t="n">
         <v>0</v>
@@ -32579,19 +32579,19 @@
       <c r="AI210" t="inlineStr"/>
       <c r="AJ210" t="inlineStr"/>
       <c r="AK210" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AL210" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AM210" t="inlineStr">
         <is>
-          <t>暫不追價</t>
+          <t>偏高或條件不足</t>
         </is>
       </c>
       <c r="AN210" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強</t>
+          <t>DT尚未轉強、貼近5MA、位置偏低但需等轉強</t>
         </is>
       </c>
       <c r="AO210" t="inlineStr">
@@ -32606,59 +32606,59 @@
       </c>
       <c r="AQ210" t="inlineStr">
         <is>
-          <t>跌破5日線、空頭排列、量能未放大</t>
+          <t>站上5日線、空頭排列、量能未放大、接近20日低點</t>
         </is>
       </c>
       <c r="AR210" t="inlineStr">
         <is>
-          <t>法人連續偏買、5日法人小幅買超、外資買投信賣</t>
+          <t>短線籌碼止穩</t>
         </is>
       </c>
       <c r="AS210" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、空頭排列、量能未放大、法人連續偏買、5日法人小幅買超、外資買投信賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、空頭排列、量能未放大、接近20日低點、短線籌碼止穩。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>6485.TWO</t>
+          <t>00919.TW</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>點序</t>
+          <t>群益台灣精選高息</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>個股</t>
+          <t>ETF</t>
         </is>
       </c>
       <c r="D211" t="n">
-        <v>61.8</v>
+        <v>32.91</v>
       </c>
       <c r="E211" t="n">
-        <v>61.22</v>
+        <v>32.62</v>
       </c>
       <c r="F211" t="n">
-        <v>61.51</v>
+        <v>32.01</v>
       </c>
       <c r="G211" t="n">
-        <v>62</v>
+        <v>31.21</v>
       </c>
       <c r="H211" t="n">
-        <v>138000</v>
+        <v>161595216</v>
       </c>
       <c r="I211" t="n">
-        <v>210400</v>
+        <v>113281824</v>
       </c>
       <c r="J211" t="n">
-        <v>69.3</v>
+        <v>33.19</v>
       </c>
       <c r="K211" t="n">
-        <v>57.5</v>
+        <v>30.01</v>
       </c>
       <c r="L211" t="inlineStr">
         <is>
@@ -32666,52 +32666,52 @@
         </is>
       </c>
       <c r="M211" t="n">
-        <v>0</v>
+        <v>-111729379</v>
       </c>
       <c r="N211" t="n">
-        <v>0</v>
+        <v>-136479451</v>
       </c>
       <c r="O211" t="n">
-        <v>0</v>
+        <v>-240612277</v>
       </c>
       <c r="P211" t="n">
-        <v>0</v>
+        <v>-228627619</v>
       </c>
       <c r="Q211" t="n">
-        <v>0</v>
+        <v>-25097891</v>
       </c>
       <c r="R211" t="n">
-        <v>0</v>
+        <v>-30458638</v>
       </c>
       <c r="S211" t="n">
-        <v>0</v>
+        <v>-43929658</v>
       </c>
       <c r="T211" t="n">
-        <v>0</v>
+        <v>-49674405</v>
       </c>
       <c r="U211" t="n">
-        <v>0</v>
+        <v>-1500000</v>
       </c>
       <c r="V211" t="n">
-        <v>0</v>
+        <v>-1500000</v>
       </c>
       <c r="W211" t="n">
-        <v>0</v>
+        <v>-317000</v>
       </c>
       <c r="X211" t="n">
-        <v>0</v>
+        <v>-317000</v>
       </c>
       <c r="Y211" t="n">
-        <v>0</v>
+        <v>-85131488</v>
       </c>
       <c r="Z211" t="n">
-        <v>0</v>
+        <v>-104520813</v>
       </c>
       <c r="AA211" t="n">
-        <v>0</v>
+        <v>-196365619</v>
       </c>
       <c r="AB211" t="n">
-        <v>0</v>
+        <v>-178636214</v>
       </c>
       <c r="AC211" t="n">
         <v>-2</v>
@@ -32720,10 +32720,10 @@
         <v>-2</v>
       </c>
       <c r="AE211" t="n">
-        <v>-5</v>
+        <v>70</v>
       </c>
       <c r="AF211" t="n">
-        <v>0</v>
+        <v>-75</v>
       </c>
       <c r="AG211" t="n">
         <v>0</v>
@@ -32732,19 +32732,19 @@
       <c r="AI211" t="inlineStr"/>
       <c r="AJ211" t="inlineStr"/>
       <c r="AK211" t="n">
-        <v>25</v>
+        <v>55</v>
       </c>
       <c r="AL211" t="n">
-        <v>25</v>
+        <v>55</v>
       </c>
       <c r="AM211" t="inlineStr">
         <is>
-          <t>暫不追價</t>
+          <t>等待拉回確認</t>
         </is>
       </c>
       <c r="AN211" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA</t>
+          <t>DT尚未轉強、貼近5MA、均線多頭排列、量能溫和放大</t>
         </is>
       </c>
       <c r="AO211" t="inlineStr">
@@ -32759,17 +32759,17 @@
       </c>
       <c r="AQ211" t="inlineStr">
         <is>
-          <t>站上5日線、空頭排列、量能未放大</t>
+          <t>站上5日線、多頭排列、量能溫和放大、接近20日高點</t>
         </is>
       </c>
       <c r="AR211" t="inlineStr">
         <is>
-          <t>籌碼中性</t>
+          <t>法人連續偏賣、5日法人明顯賣超、外資投信同步賣超</t>
         </is>
       </c>
       <c r="AS211" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、空頭排列、量能未放大、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、多頭排列、量能溫和放大、接近20日高點、法人連續偏賣、5日法人明顯賣超、外資投信同步賣超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
@@ -32929,42 +32929,42 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>00919.TW</t>
+          <t>2608.TW</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>群益台灣精選高息</t>
+          <t>嘉里大榮</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>ETF</t>
+          <t>個股</t>
         </is>
       </c>
       <c r="D213" t="n">
-        <v>32.91</v>
+        <v>28.55</v>
       </c>
       <c r="E213" t="n">
-        <v>32.62</v>
+        <v>28.53</v>
       </c>
       <c r="F213" t="n">
-        <v>32.01</v>
+        <v>28.6</v>
       </c>
       <c r="G213" t="n">
-        <v>31.21</v>
+        <v>28.59</v>
       </c>
       <c r="H213" t="n">
-        <v>161595216</v>
+        <v>256199</v>
       </c>
       <c r="I213" t="n">
-        <v>113281824</v>
+        <v>158553</v>
       </c>
       <c r="J213" t="n">
-        <v>33.19</v>
+        <v>29.05</v>
       </c>
       <c r="K213" t="n">
-        <v>30.01</v>
+        <v>28.35</v>
       </c>
       <c r="L213" t="inlineStr">
         <is>
@@ -32972,52 +32972,52 @@
         </is>
       </c>
       <c r="M213" t="n">
-        <v>-111729379</v>
+        <v>-51070</v>
       </c>
       <c r="N213" t="n">
-        <v>-136479451</v>
+        <v>-212601</v>
       </c>
       <c r="O213" t="n">
-        <v>-240612277</v>
+        <v>-251272</v>
       </c>
       <c r="P213" t="n">
-        <v>-228627619</v>
+        <v>-500158</v>
       </c>
       <c r="Q213" t="n">
-        <v>-25097891</v>
+        <v>-78000</v>
       </c>
       <c r="R213" t="n">
-        <v>-30458638</v>
+        <v>-242000</v>
       </c>
       <c r="S213" t="n">
-        <v>-43929658</v>
+        <v>-282000</v>
       </c>
       <c r="T213" t="n">
-        <v>-49674405</v>
+        <v>-488962</v>
       </c>
       <c r="U213" t="n">
-        <v>-1500000</v>
+        <v>0</v>
       </c>
       <c r="V213" t="n">
-        <v>-1500000</v>
+        <v>0</v>
       </c>
       <c r="W213" t="n">
-        <v>-317000</v>
+        <v>0</v>
       </c>
       <c r="X213" t="n">
-        <v>-317000</v>
+        <v>0</v>
       </c>
       <c r="Y213" t="n">
-        <v>-85131488</v>
+        <v>26930</v>
       </c>
       <c r="Z213" t="n">
-        <v>-104520813</v>
+        <v>29399</v>
       </c>
       <c r="AA213" t="n">
-        <v>-196365619</v>
+        <v>30728</v>
       </c>
       <c r="AB213" t="n">
-        <v>-178636214</v>
+        <v>-11196</v>
       </c>
       <c r="AC213" t="n">
         <v>-2</v>
@@ -33026,10 +33026,10 @@
         <v>-2</v>
       </c>
       <c r="AE213" t="n">
-        <v>70</v>
+        <v>40</v>
       </c>
       <c r="AF213" t="n">
-        <v>-75</v>
+        <v>-45</v>
       </c>
       <c r="AG213" t="n">
         <v>0</v>
@@ -33038,10 +33038,10 @@
       <c r="AI213" t="inlineStr"/>
       <c r="AJ213" t="inlineStr"/>
       <c r="AK213" t="n">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="AL213" t="n">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="AM213" t="inlineStr">
         <is>
@@ -33050,7 +33050,7 @@
       </c>
       <c r="AN213" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA、均線多頭排列、量能溫和放大</t>
+          <t>DT尚未轉強、貼近5MA、位置偏低但需等轉強、量能溫和放大</t>
         </is>
       </c>
       <c r="AO213" t="inlineStr">
@@ -33065,29 +33065,29 @@
       </c>
       <c r="AQ213" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、量能溫和放大、接近20日高點</t>
+          <t>站上5日線、成交量放大、接近20日高點、接近20日低點</t>
         </is>
       </c>
       <c r="AR213" t="inlineStr">
         <is>
-          <t>法人連續偏賣、5日法人明顯賣超、外資投信同步賣超</t>
+          <t>法人連續偏賣、5日法人賣超</t>
         </is>
       </c>
       <c r="AS213" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、多頭排列、量能溫和放大、接近20日高點、法人連續偏賣、5日法人明顯賣超、外資投信同步賣超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、成交量放大、接近20日高點、接近20日低點、法人連續偏賣、5日法人賣超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>2608.TW</t>
+          <t>2233.TW</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>嘉里大榮</t>
+          <t>宇隆</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
@@ -33096,28 +33096,28 @@
         </is>
       </c>
       <c r="D214" t="n">
-        <v>28.55</v>
+        <v>168.5</v>
       </c>
       <c r="E214" t="n">
-        <v>28.53</v>
+        <v>169.8</v>
       </c>
       <c r="F214" t="n">
-        <v>28.6</v>
+        <v>171.15</v>
       </c>
       <c r="G214" t="n">
-        <v>28.59</v>
+        <v>181.5</v>
       </c>
       <c r="H214" t="n">
-        <v>256199</v>
+        <v>342844</v>
       </c>
       <c r="I214" t="n">
-        <v>158553</v>
+        <v>441683</v>
       </c>
       <c r="J214" t="n">
-        <v>29.05</v>
+        <v>210.5</v>
       </c>
       <c r="K214" t="n">
-        <v>28.35</v>
+        <v>157.5</v>
       </c>
       <c r="L214" t="inlineStr">
         <is>
@@ -33125,52 +33125,52 @@
         </is>
       </c>
       <c r="M214" t="n">
-        <v>-51070</v>
+        <v>70531</v>
       </c>
       <c r="N214" t="n">
-        <v>-212601</v>
+        <v>86927</v>
       </c>
       <c r="O214" t="n">
-        <v>-251272</v>
+        <v>55765</v>
       </c>
       <c r="P214" t="n">
-        <v>-500158</v>
+        <v>-76985</v>
       </c>
       <c r="Q214" t="n">
-        <v>-78000</v>
+        <v>67531</v>
       </c>
       <c r="R214" t="n">
-        <v>-242000</v>
+        <v>185146</v>
       </c>
       <c r="S214" t="n">
-        <v>-282000</v>
+        <v>153491</v>
       </c>
       <c r="T214" t="n">
-        <v>-488962</v>
+        <v>37643</v>
       </c>
       <c r="U214" t="n">
         <v>0</v>
       </c>
       <c r="V214" t="n">
-        <v>0</v>
+        <v>-100000</v>
       </c>
       <c r="W214" t="n">
-        <v>0</v>
+        <v>-100000</v>
       </c>
       <c r="X214" t="n">
-        <v>0</v>
+        <v>-200000</v>
       </c>
       <c r="Y214" t="n">
-        <v>26930</v>
+        <v>3000</v>
       </c>
       <c r="Z214" t="n">
-        <v>29399</v>
+        <v>1781</v>
       </c>
       <c r="AA214" t="n">
-        <v>30728</v>
+        <v>2274</v>
       </c>
       <c r="AB214" t="n">
-        <v>-11196</v>
+        <v>85372</v>
       </c>
       <c r="AC214" t="n">
         <v>-2</v>
@@ -33179,10 +33179,10 @@
         <v>-2</v>
       </c>
       <c r="AE214" t="n">
+        <v>-45</v>
+      </c>
+      <c r="AF214" t="n">
         <v>40</v>
-      </c>
-      <c r="AF214" t="n">
-        <v>-45</v>
       </c>
       <c r="AG214" t="n">
         <v>0</v>
@@ -33191,19 +33191,19 @@
       <c r="AI214" t="inlineStr"/>
       <c r="AJ214" t="inlineStr"/>
       <c r="AK214" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="AL214" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="AM214" t="inlineStr">
         <is>
-          <t>等待拉回確認</t>
+          <t>暫不追價</t>
         </is>
       </c>
       <c r="AN214" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA、位置偏低但需等轉強、量能溫和放大</t>
+          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強</t>
         </is>
       </c>
       <c r="AO214" t="inlineStr">
@@ -33218,17 +33218,17 @@
       </c>
       <c r="AQ214" t="inlineStr">
         <is>
-          <t>站上5日線、成交量放大、接近20日高點、接近20日低點</t>
+          <t>跌破5日線、空頭排列、量能未放大</t>
         </is>
       </c>
       <c r="AR214" t="inlineStr">
         <is>
-          <t>法人連續偏賣、5日法人賣超</t>
+          <t>法人連續偏買、5日法人小幅買超、外資買投信賣</t>
         </is>
       </c>
       <c r="AS214" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、成交量放大、接近20日高點、接近20日低點、法人連續偏賣、5日法人賣超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、空頭排列、量能未放大、法人連續偏買、5日法人小幅買超、外資買投信賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
@@ -33541,12 +33541,12 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>5706.TW</t>
+          <t>6485.TWO</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>鳳凰</t>
+          <t>點序</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
@@ -33555,28 +33555,28 @@
         </is>
       </c>
       <c r="D217" t="n">
-        <v>45</v>
+        <v>61.8</v>
       </c>
       <c r="E217" t="n">
-        <v>44.85</v>
+        <v>61.22</v>
       </c>
       <c r="F217" t="n">
-        <v>45.03</v>
+        <v>61.51</v>
       </c>
       <c r="G217" t="n">
-        <v>45.2</v>
+        <v>62</v>
       </c>
       <c r="H217" t="n">
-        <v>93218</v>
+        <v>138000</v>
       </c>
       <c r="I217" t="n">
-        <v>88956</v>
+        <v>210400</v>
       </c>
       <c r="J217" t="n">
-        <v>45.95</v>
+        <v>69.3</v>
       </c>
       <c r="K217" t="n">
-        <v>44.5</v>
+        <v>57.5</v>
       </c>
       <c r="L217" t="inlineStr">
         <is>
@@ -33584,28 +33584,28 @@
         </is>
       </c>
       <c r="M217" t="n">
-        <v>-8000</v>
+        <v>0</v>
       </c>
       <c r="N217" t="n">
-        <v>20000</v>
+        <v>0</v>
       </c>
       <c r="O217" t="n">
-        <v>33279</v>
+        <v>0</v>
       </c>
       <c r="P217" t="n">
-        <v>66852</v>
+        <v>0</v>
       </c>
       <c r="Q217" t="n">
-        <v>-29000</v>
+        <v>0</v>
       </c>
       <c r="R217" t="n">
-        <v>-4000</v>
+        <v>0</v>
       </c>
       <c r="S217" t="n">
-        <v>14279</v>
+        <v>0</v>
       </c>
       <c r="T217" t="n">
-        <v>61852</v>
+        <v>0</v>
       </c>
       <c r="U217" t="n">
         <v>0</v>
@@ -33620,16 +33620,16 @@
         <v>0</v>
       </c>
       <c r="Y217" t="n">
-        <v>21000</v>
+        <v>0</v>
       </c>
       <c r="Z217" t="n">
-        <v>24000</v>
+        <v>0</v>
       </c>
       <c r="AA217" t="n">
-        <v>19000</v>
+        <v>0</v>
       </c>
       <c r="AB217" t="n">
-        <v>5000</v>
+        <v>0</v>
       </c>
       <c r="AC217" t="n">
         <v>-2</v>
@@ -33650,19 +33650,19 @@
       <c r="AI217" t="inlineStr"/>
       <c r="AJ217" t="inlineStr"/>
       <c r="AK217" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="AL217" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="AM217" t="inlineStr">
         <is>
-          <t>偏高或條件不足</t>
+          <t>暫不追價</t>
         </is>
       </c>
       <c r="AN217" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA、位置偏低但需等轉強</t>
+          <t>DT尚未轉強、貼近5MA</t>
         </is>
       </c>
       <c r="AO217" t="inlineStr">
@@ -33677,7 +33677,7 @@
       </c>
       <c r="AQ217" t="inlineStr">
         <is>
-          <t>站上5日線、空頭排列、量能溫和放大、接近20日低點</t>
+          <t>站上5日線、空頭排列、量能未放大</t>
         </is>
       </c>
       <c r="AR217" t="inlineStr">
@@ -33687,7 +33687,7 @@
       </c>
       <c r="AS217" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、空頭排列、量能溫和放大、接近20日低點、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、空頭排列、量能未放大、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
@@ -33847,12 +33847,12 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>1303.TW</t>
+          <t>5706.TW</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>南亞</t>
+          <t>鳳凰</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
@@ -33861,28 +33861,28 @@
         </is>
       </c>
       <c r="D219" t="n">
-        <v>230.5</v>
+        <v>45</v>
       </c>
       <c r="E219" t="n">
-        <v>229.8</v>
+        <v>44.85</v>
       </c>
       <c r="F219" t="n">
-        <v>223.5</v>
+        <v>45.03</v>
       </c>
       <c r="G219" t="n">
-        <v>207.82</v>
+        <v>45.2</v>
       </c>
       <c r="H219" t="n">
-        <v>75938138</v>
+        <v>93218</v>
       </c>
       <c r="I219" t="n">
-        <v>100977562</v>
+        <v>88956</v>
       </c>
       <c r="J219" t="n">
-        <v>250</v>
+        <v>45.95</v>
       </c>
       <c r="K219" t="n">
-        <v>172.5</v>
+        <v>44.5</v>
       </c>
       <c r="L219" t="inlineStr">
         <is>
@@ -33890,64 +33890,64 @@
         </is>
       </c>
       <c r="M219" t="n">
-        <v>4093937</v>
+        <v>-8000</v>
       </c>
       <c r="N219" t="n">
-        <v>-9657802</v>
+        <v>20000</v>
       </c>
       <c r="O219" t="n">
-        <v>-11270683</v>
+        <v>33279</v>
       </c>
       <c r="P219" t="n">
-        <v>52295173</v>
+        <v>66852</v>
       </c>
       <c r="Q219" t="n">
-        <v>-1305492</v>
+        <v>-29000</v>
       </c>
       <c r="R219" t="n">
-        <v>-13825100</v>
+        <v>-4000</v>
       </c>
       <c r="S219" t="n">
-        <v>-21244287</v>
+        <v>14279</v>
       </c>
       <c r="T219" t="n">
-        <v>18312111</v>
+        <v>61852</v>
       </c>
       <c r="U219" t="n">
-        <v>5483000</v>
+        <v>0</v>
       </c>
       <c r="V219" t="n">
-        <v>5609000</v>
+        <v>0</v>
       </c>
       <c r="W219" t="n">
-        <v>12956287</v>
+        <v>0</v>
       </c>
       <c r="X219" t="n">
-        <v>33853523</v>
+        <v>0</v>
       </c>
       <c r="Y219" t="n">
-        <v>-83571</v>
+        <v>21000</v>
       </c>
       <c r="Z219" t="n">
-        <v>-1441702</v>
+        <v>24000</v>
       </c>
       <c r="AA219" t="n">
-        <v>-2982683</v>
+        <v>19000</v>
       </c>
       <c r="AB219" t="n">
-        <v>129539</v>
+        <v>5000</v>
       </c>
       <c r="AC219" t="n">
-        <v>-4</v>
+        <v>-2</v>
       </c>
       <c r="AD219" t="n">
-        <v>-4</v>
+        <v>-2</v>
       </c>
       <c r="AE219" t="n">
-        <v>45</v>
+        <v>-5</v>
       </c>
       <c r="AF219" t="n">
-        <v>-55</v>
+        <v>0</v>
       </c>
       <c r="AG219" t="n">
         <v>0</v>
@@ -33956,19 +33956,19 @@
       <c r="AI219" t="inlineStr"/>
       <c r="AJ219" t="inlineStr"/>
       <c r="AK219" t="n">
-        <v>55</v>
+        <v>30</v>
       </c>
       <c r="AL219" t="n">
-        <v>55</v>
+        <v>30</v>
       </c>
       <c r="AM219" t="inlineStr">
         <is>
-          <t>等待拉回確認</t>
+          <t>偏高或條件不足</t>
         </is>
       </c>
       <c r="AN219" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA、均線多頭排列、位於20日區間中上緣</t>
+          <t>DT尚未轉強、貼近5MA、位置偏低但需等轉強</t>
         </is>
       </c>
       <c r="AO219" t="inlineStr">
@@ -33983,29 +33983,29 @@
       </c>
       <c r="AQ219" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、量能未放大</t>
+          <t>站上5日線、空頭排列、量能溫和放大、接近20日低點</t>
         </is>
       </c>
       <c r="AR219" t="inlineStr">
         <is>
-          <t>中期買超轉短線賣壓、5日法人明顯賣超、投信買外資賣</t>
+          <t>籌碼中性</t>
         </is>
       </c>
       <c r="AS219" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、多頭排列、量能未放大、中期買超轉短線賣壓、5日法人明顯賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、空頭排列、量能溫和放大、接近20日低點、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>3163.TWO</t>
+          <t>2006.TW</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>波若威</t>
+          <t>東和鋼鐵</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
@@ -34014,81 +34014,81 @@
         </is>
       </c>
       <c r="D220" t="n">
-        <v>752</v>
+        <v>80.8</v>
       </c>
       <c r="E220" t="n">
-        <v>754.8</v>
+        <v>81.78</v>
       </c>
       <c r="F220" t="n">
-        <v>759.2</v>
+        <v>81.53</v>
       </c>
       <c r="G220" t="n">
-        <v>740.6</v>
+        <v>81.95</v>
       </c>
       <c r="H220" t="n">
-        <v>4777000</v>
+        <v>1203974</v>
       </c>
       <c r="I220" t="n">
-        <v>1752400</v>
+        <v>1842802</v>
       </c>
       <c r="J220" t="n">
-        <v>814</v>
+        <v>86.5</v>
       </c>
       <c r="K220" t="n">
-        <v>673</v>
+        <v>78.5</v>
       </c>
       <c r="L220" t="inlineStr">
         <is>
-          <t>爆量價未漲</t>
+          <t>無明顯異常</t>
         </is>
       </c>
       <c r="M220" t="n">
-        <v>0</v>
+        <v>-450934</v>
       </c>
       <c r="N220" t="n">
-        <v>0</v>
+        <v>-502689</v>
       </c>
       <c r="O220" t="n">
-        <v>0</v>
+        <v>160798</v>
       </c>
       <c r="P220" t="n">
-        <v>0</v>
+        <v>-80384</v>
       </c>
       <c r="Q220" t="n">
-        <v>0</v>
+        <v>-470622</v>
       </c>
       <c r="R220" t="n">
-        <v>0</v>
+        <v>-1397498</v>
       </c>
       <c r="S220" t="n">
-        <v>0</v>
+        <v>-1325664</v>
       </c>
       <c r="T220" t="n">
-        <v>0</v>
+        <v>-1467725</v>
       </c>
       <c r="U220" t="n">
-        <v>0</v>
+        <v>-4000</v>
       </c>
       <c r="V220" t="n">
-        <v>0</v>
+        <v>860237</v>
       </c>
       <c r="W220" t="n">
-        <v>0</v>
+        <v>1482741</v>
       </c>
       <c r="X220" t="n">
-        <v>0</v>
+        <v>1464494</v>
       </c>
       <c r="Y220" t="n">
-        <v>0</v>
+        <v>23688</v>
       </c>
       <c r="Z220" t="n">
-        <v>0</v>
+        <v>34572</v>
       </c>
       <c r="AA220" t="n">
-        <v>0</v>
+        <v>3721</v>
       </c>
       <c r="AB220" t="n">
-        <v>0</v>
+        <v>-77153</v>
       </c>
       <c r="AC220" t="n">
         <v>-4</v>
@@ -34097,13 +34097,13 @@
         <v>-4</v>
       </c>
       <c r="AE220" t="n">
-        <v>0</v>
+        <v>-30</v>
       </c>
       <c r="AF220" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AG220" t="n">
-        <v>-20</v>
+        <v>0</v>
       </c>
       <c r="AH220" t="inlineStr"/>
       <c r="AI220" t="inlineStr"/>
@@ -34121,7 +34121,7 @@
       </c>
       <c r="AN220" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位於20日區間中上緣、爆量後不追價</t>
+          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強</t>
         </is>
       </c>
       <c r="AO220" t="inlineStr">
@@ -34136,17 +34136,17 @@
       </c>
       <c r="AQ220" t="inlineStr">
         <is>
-          <t>跌破5日線、爆量、爆量價未漲</t>
+          <t>跌破5日線、量能未放大、接近20日低點</t>
         </is>
       </c>
       <c r="AR220" t="inlineStr">
         <is>
-          <t>籌碼中性</t>
+          <t>5日法人買超、投信買外資賣</t>
         </is>
       </c>
       <c r="AS220" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、爆量、爆量價未漲、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、量能未放大、接近20日低點、5日法人買超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
@@ -35071,12 +35071,12 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>2006.TW</t>
+          <t>1303.TW</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>東和鋼鐵</t>
+          <t>南亞</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
@@ -35085,28 +35085,28 @@
         </is>
       </c>
       <c r="D227" t="n">
-        <v>80.8</v>
+        <v>230.5</v>
       </c>
       <c r="E227" t="n">
-        <v>81.78</v>
+        <v>229.8</v>
       </c>
       <c r="F227" t="n">
-        <v>81.53</v>
+        <v>223.5</v>
       </c>
       <c r="G227" t="n">
-        <v>81.95</v>
+        <v>207.82</v>
       </c>
       <c r="H227" t="n">
-        <v>1203974</v>
+        <v>75938138</v>
       </c>
       <c r="I227" t="n">
-        <v>1842802</v>
+        <v>100977562</v>
       </c>
       <c r="J227" t="n">
-        <v>86.5</v>
+        <v>250</v>
       </c>
       <c r="K227" t="n">
-        <v>78.5</v>
+        <v>172.5</v>
       </c>
       <c r="L227" t="inlineStr">
         <is>
@@ -35114,52 +35114,52 @@
         </is>
       </c>
       <c r="M227" t="n">
-        <v>-450934</v>
+        <v>4093937</v>
       </c>
       <c r="N227" t="n">
-        <v>-502689</v>
+        <v>-9657802</v>
       </c>
       <c r="O227" t="n">
-        <v>160798</v>
+        <v>-11270683</v>
       </c>
       <c r="P227" t="n">
-        <v>-80384</v>
+        <v>52295173</v>
       </c>
       <c r="Q227" t="n">
-        <v>-470622</v>
+        <v>-1305492</v>
       </c>
       <c r="R227" t="n">
-        <v>-1397498</v>
+        <v>-13825100</v>
       </c>
       <c r="S227" t="n">
-        <v>-1325664</v>
+        <v>-21244287</v>
       </c>
       <c r="T227" t="n">
-        <v>-1467725</v>
+        <v>18312111</v>
       </c>
       <c r="U227" t="n">
-        <v>-4000</v>
+        <v>5483000</v>
       </c>
       <c r="V227" t="n">
-        <v>860237</v>
+        <v>5609000</v>
       </c>
       <c r="W227" t="n">
-        <v>1482741</v>
+        <v>12956287</v>
       </c>
       <c r="X227" t="n">
-        <v>1464494</v>
+        <v>33853523</v>
       </c>
       <c r="Y227" t="n">
-        <v>23688</v>
+        <v>-83571</v>
       </c>
       <c r="Z227" t="n">
-        <v>34572</v>
+        <v>-1441702</v>
       </c>
       <c r="AA227" t="n">
-        <v>3721</v>
+        <v>-2982683</v>
       </c>
       <c r="AB227" t="n">
-        <v>-77153</v>
+        <v>129539</v>
       </c>
       <c r="AC227" t="n">
         <v>-4</v>
@@ -35168,10 +35168,10 @@
         <v>-4</v>
       </c>
       <c r="AE227" t="n">
-        <v>-30</v>
+        <v>45</v>
       </c>
       <c r="AF227" t="n">
-        <v>20</v>
+        <v>-55</v>
       </c>
       <c r="AG227" t="n">
         <v>0</v>
@@ -35180,19 +35180,19 @@
       <c r="AI227" t="inlineStr"/>
       <c r="AJ227" t="inlineStr"/>
       <c r="AK227" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AL227" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AM227" t="inlineStr">
         <is>
-          <t>暫不追價</t>
+          <t>等待拉回確認</t>
         </is>
       </c>
       <c r="AN227" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強</t>
+          <t>DT尚未轉強、貼近5MA、均線多頭排列、位於20日區間中上緣</t>
         </is>
       </c>
       <c r="AO227" t="inlineStr">
@@ -35207,17 +35207,17 @@
       </c>
       <c r="AQ227" t="inlineStr">
         <is>
-          <t>跌破5日線、量能未放大、接近20日低點</t>
+          <t>站上5日線、多頭排列、量能未放大</t>
         </is>
       </c>
       <c r="AR227" t="inlineStr">
         <is>
-          <t>5日法人買超、投信買外資賣</t>
+          <t>中期買超轉短線賣壓、5日法人明顯賣超、投信買外資賣</t>
         </is>
       </c>
       <c r="AS227" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、量能未放大、接近20日低點、5日法人買超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、多頭排列、量能未放大、中期買超轉短線賣壓、5日法人明顯賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
